--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\Artículo\CODIGO\Codigos ORC_SBCR_Solar_Biomass - Segunda Actualizacion Jos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301377DA-2131-4F35-B59D-431B342283DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFA6E58-72D9-427F-BF37-C3222BA4DFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Energy_Exergy" sheetId="2" r:id="rId1"/>
@@ -650,9 +650,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -690,7 +690,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -796,7 +796,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -938,7 +938,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1001,26 +1001,26 @@
         <v>1</v>
       </c>
       <c r="C3" s="4">
-        <v>1073.1500000000001</v>
+        <v>773.15</v>
       </c>
       <c r="D3" s="5">
         <v>25</v>
       </c>
       <c r="E3" s="4">
-        <v>1350.0381316636626</v>
+        <v>969.22761234812413</v>
       </c>
       <c r="F3" s="7">
-        <v>3.0305681085599816</v>
+        <v>2.614766418080567</v>
       </c>
       <c r="G3" s="4">
         <v>10</v>
       </c>
       <c r="H3" s="4">
-        <v>756.61237274082237</v>
+        <v>499.7731274417215</v>
       </c>
       <c r="I3" s="4">
         <f>C3-273.15</f>
-        <v>800.00000000000011</v>
+        <v>500</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>40</v>
@@ -1046,44 +1046,44 @@
         <v>2</v>
       </c>
       <c r="C4" s="4">
-        <v>1018.1289616795918</v>
+        <v>728.45135112026719</v>
       </c>
       <c r="D4" s="5">
         <v>17.482517482517483</v>
       </c>
       <c r="E4" s="4">
-        <v>1281.2341664776559</v>
+        <v>920.93965105155189</v>
       </c>
       <c r="F4" s="7">
-        <v>3.035664888414034</v>
+        <v>2.6197661286628455</v>
       </c>
       <c r="G4" s="4">
         <v>10</v>
       </c>
       <c r="H4" s="4">
-        <v>686.28880264133011</v>
+        <v>449.99450243504293</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" ref="I4:I42" si="0">C4-273.15</f>
-        <v>744.97896167959186</v>
+        <v>455.30135112026721</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>42</v>
       </c>
       <c r="L4" s="7">
-        <v>1.7979758880009502</v>
+        <v>1.2616622448371713</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>66</v>
       </c>
       <c r="O4" s="10">
-        <v>688.03965186006621</v>
+        <v>482.87961296572234</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>98</v>
       </c>
       <c r="R4">
-        <v>916.98727526679568</v>
+        <v>130055.70705438507</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
@@ -1091,44 +1091,44 @@
         <v>3</v>
       </c>
       <c r="C5" s="4">
-        <v>1073.1500000000001</v>
+        <v>773.15</v>
       </c>
       <c r="D5" s="5">
         <v>17.482517482517483</v>
       </c>
       <c r="E5" s="4">
-        <v>1351.4823193165744</v>
+        <v>975.50549339380814</v>
       </c>
       <c r="F5" s="7">
-        <v>3.1028601038812176</v>
+        <v>2.6924623805995864</v>
       </c>
       <c r="G5" s="4">
         <v>10</v>
       </c>
       <c r="H5" s="4">
-        <v>736.50270198870771</v>
+        <v>482.88595726235974</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="0"/>
-        <v>800.00000000000011</v>
+        <v>500</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>43</v>
       </c>
       <c r="L5" s="7">
-        <v>0.70248152838918376</v>
+        <v>0.54565842342256221</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>67</v>
       </c>
       <c r="O5" s="10">
-        <v>1199.1350689643341</v>
+        <v>842.93566294255663</v>
       </c>
       <c r="Q5" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R5">
-        <v>830.65281683265493</v>
+        <v>927277.70682172745</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
@@ -1136,44 +1136,44 @@
         <v>4</v>
       </c>
       <c r="C6" s="4">
-        <v>976.11427576830124</v>
+        <v>695.01503073542415</v>
       </c>
       <c r="D6" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E6" s="4">
-        <v>1231.5688124201411</v>
+        <v>891.21192709955244</v>
       </c>
       <c r="F6" s="7">
-        <v>3.1121411727413726</v>
+        <v>2.7016269704938249</v>
       </c>
       <c r="G6" s="4">
         <v>10</v>
       </c>
       <c r="H6" s="4">
-        <v>613.82204441161923</v>
+        <v>395.8599684911369</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="0"/>
-        <v>702.96427576830126</v>
+        <v>421.86503073542417</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>47</v>
       </c>
       <c r="L6" s="7">
-        <v>2.5004574163901339</v>
+        <v>1.8073206682597334</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="O6" s="10">
-        <v>71.774211786387255</v>
+        <v>57.523574052581495</v>
       </c>
       <c r="Q6" s="13" t="s">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>6850.0253590880538</v>
+        <v>196542.52607265621</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -1181,38 +1181,38 @@
         <v>5</v>
       </c>
       <c r="C7" s="4">
-        <v>580.59332858273865</v>
+        <v>543.48173263613626</v>
       </c>
       <c r="D7" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E7" s="4">
-        <v>758.75704305028523</v>
+        <v>716.30407434487142</v>
       </c>
       <c r="F7" s="7">
-        <v>2.4934653765384365</v>
+        <v>2.4179049497412306</v>
       </c>
       <c r="G7" s="4">
         <v>10</v>
       </c>
       <c r="H7" s="4">
-        <v>325.46846367966873</v>
+        <v>305.54383622384188</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="0"/>
-        <v>307.44332858273867</v>
+        <v>270.33173263613628</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>44</v>
       </c>
       <c r="L7" s="7">
-        <v>4.8493514799902702</v>
+        <v>1.7939266881176714</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>69</v>
       </c>
       <c r="O7" s="10">
-        <v>-386.40079286911646</v>
+        <v>-365.4747826578693</v>
       </c>
       <c r="Q7" s="13" t="s">
         <v>105</v>
@@ -1226,38 +1226,38 @@
         <v>6</v>
       </c>
       <c r="C8" s="4">
-        <v>435.43287838933054</v>
+        <v>421.37703255538463</v>
       </c>
       <c r="D8" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E8" s="4">
-        <v>591.19593244306282</v>
+        <v>574.17808817703337</v>
       </c>
       <c r="F8" s="7">
-        <v>2.1610419768753544</v>
+        <v>2.1213123773587061</v>
       </c>
       <c r="G8" s="4">
         <v>10</v>
       </c>
       <c r="H8" s="4">
-        <v>257.0193896819942</v>
+        <v>251.84692551185341</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
+        <v>148.22703255538465</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>45</v>
       </c>
       <c r="L8" s="7">
-        <v>1.6756111060722243</v>
+        <v>1.4212598619940109</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>70</v>
       </c>
       <c r="O8" s="10">
-        <v>-188.73788675888972</v>
+        <v>-218.21983132529576</v>
       </c>
       <c r="Q8" s="13" t="s">
         <v>104</v>
@@ -1271,38 +1271,38 @@
         <v>29</v>
       </c>
       <c r="C9" s="4">
-        <v>435.43287838933054</v>
+        <v>421.37703255538463</v>
       </c>
       <c r="D9" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E9" s="4">
-        <v>591.19593244306282</v>
+        <v>574.17808817703337</v>
       </c>
       <c r="F9" s="7">
-        <v>2.1610419768753544</v>
+        <v>2.1213123773587061</v>
       </c>
       <c r="G9" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H9" s="4">
-        <v>257.0193896819942</v>
+        <v>251.84692551185341</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
+        <v>148.22703255538465</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>48</v>
       </c>
       <c r="L9" s="7">
-        <v>0.11033034486553291</v>
+        <v>9.191992371611768E-2</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>71</v>
       </c>
       <c r="O9" s="10">
-        <v>-5.8779815586019524E-2</v>
+        <v>-4.8971442727741191E-2</v>
       </c>
       <c r="Q9" s="23" t="s">
         <v>101</v>
@@ -1316,38 +1316,38 @@
         <v>30</v>
       </c>
       <c r="C10" s="4">
-        <v>423.3557736165609</v>
+        <v>414.09144532798098</v>
       </c>
       <c r="D10" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E10" s="4">
-        <v>0.57659650223683723</v>
+        <v>0.56519773365306714</v>
       </c>
       <c r="F10" s="7">
-        <v>2.1270382629381421E-3</v>
+        <v>2.099813627811903E-3</v>
       </c>
       <c r="G10" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H10" s="4">
-        <v>0.25257199616171355</v>
+        <v>0.24929025254083162</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="0"/>
-        <v>150.20577361656092</v>
+        <v>140.941445327981</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="7">
-        <v>0.68666556854253946</v>
+        <v>0.57208419638170538</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>72</v>
       </c>
       <c r="O10" s="10">
-        <v>1312.0360411963943</v>
+        <v>742.12066192511395</v>
       </c>
       <c r="Q10" s="13" t="s">
         <v>102</v>
@@ -1373,7 +1373,7 @@
         <v>1.8961819516546078E-3</v>
       </c>
       <c r="G11" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H11" s="4">
         <v>0.23185738014859708</v>
@@ -1386,13 +1386,13 @@
         <v>50</v>
       </c>
       <c r="L11" s="7">
-        <v>0.12544275752191905</v>
+        <v>7.3321697591537435E-2</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="O11" s="10">
-        <v>71.715431970801234</v>
+        <v>57.474602609853754</v>
       </c>
       <c r="Q11" s="13" t="s">
         <v>103</v>
@@ -1406,38 +1406,38 @@
         <v>32</v>
       </c>
       <c r="C12" s="4">
-        <v>346.62433578909861</v>
+        <v>348.11288652158407</v>
       </c>
       <c r="D12" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E12" s="4">
-        <v>0.46883148724964824</v>
+        <v>0.4715328051471645</v>
       </c>
       <c r="F12" s="7">
-        <v>1.844389053247172E-3</v>
+        <v>1.8521656410056229E-3</v>
       </c>
       <c r="G12" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H12" s="4">
-        <v>0.22907884304388729</v>
+        <v>0.22946157130122152</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" si="0"/>
-        <v>73.474335789098632</v>
+        <v>74.962886521584096</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L12" s="7">
-        <v>0.92243867092999143</v>
+        <v>0.73732581768936045</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>74</v>
       </c>
       <c r="O12" s="12">
-        <v>1383.7514731671954</v>
+        <v>799.59526453496767</v>
       </c>
       <c r="Q12" s="13" t="s">
         <v>106</v>
@@ -1451,32 +1451,32 @@
         <v>33</v>
       </c>
       <c r="C13" s="4">
-        <v>344.39458549639238</v>
+        <v>345.58184628905991</v>
       </c>
       <c r="D13" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E13" s="4">
-        <v>464.67130036926602</v>
+        <v>466.90431100010727</v>
       </c>
       <c r="F13" s="7">
-        <v>1.8323480555267959</v>
+        <v>1.8388208125565038</v>
       </c>
       <c r="G13" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H13" s="4">
-        <v>228.50867963383527</v>
+        <v>228.81183775626909</v>
       </c>
       <c r="I13" s="4">
         <f t="shared" si="0"/>
-        <v>71.244585496392403</v>
+        <v>72.431846289059933</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>52</v>
       </c>
       <c r="L13" s="7">
-        <v>0.72305037797389082</v>
+        <v>0.60239760572916501</v>
       </c>
       <c r="Q13" s="13" t="s">
         <v>107</v>
@@ -1490,32 +1490,32 @@
         <v>34</v>
       </c>
       <c r="C14" s="4">
-        <v>435.43287838933054</v>
+        <v>421.37703255538463</v>
       </c>
       <c r="D14" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E14" s="4">
-        <v>591.19593244306282</v>
+        <v>574.17808817703337</v>
       </c>
       <c r="F14" s="7">
-        <v>2.1610419768753544</v>
+        <v>2.1213123773587061</v>
       </c>
       <c r="G14" s="4">
-        <v>2.0055144227139889</v>
+        <v>2.4384656223783785</v>
       </c>
       <c r="H14" s="4">
-        <v>257.0193896819942</v>
+        <v>251.84692551185341</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
+        <v>148.22703255538465</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>54</v>
       </c>
       <c r="L14" s="7">
-        <v>0.12767286098529926</v>
+        <v>7.7453609350341693E-2</v>
       </c>
       <c r="N14" s="27" t="s">
         <v>75</v>
@@ -1545,7 +1545,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G15" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H15" s="4">
         <v>224.33075530171814</v>
@@ -1558,13 +1558,13 @@
         <v>53</v>
       </c>
       <c r="L15" s="7">
-        <v>0.85072323895919011</v>
+        <v>0.67985121507950674</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="O15" s="10">
-        <v>7.7745474285568061</v>
+        <v>7.7950074757952033</v>
       </c>
       <c r="Q15" s="13" t="s">
         <v>109</v>
@@ -1590,7 +1590,7 @@
         <v>1.7343043486568708</v>
       </c>
       <c r="G16" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H16" s="4">
         <v>268.76481394998945</v>
@@ -1603,13 +1603,13 @@
         <v>46</v>
       </c>
       <c r="L16" s="7">
-        <v>3.3258554014030113E-2</v>
+        <v>3.4998517609593639E-2</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>81</v>
       </c>
       <c r="O16" s="10">
-        <v>52.471841055808</v>
+        <v>41.061925255339496</v>
       </c>
       <c r="Q16" s="13" t="s">
         <v>110</v>
@@ -1623,38 +1623,38 @@
         <v>9</v>
       </c>
       <c r="C17" s="4">
-        <v>547.68745921507718</v>
+        <v>531.29690522457895</v>
       </c>
       <c r="D17" s="5">
         <v>25</v>
       </c>
       <c r="E17" s="4">
-        <v>685.30539614040072</v>
+        <v>663.66872086122646</v>
       </c>
       <c r="F17" s="7">
-        <v>2.1800807088725671</v>
+        <v>2.1399703638183678</v>
       </c>
       <c r="G17" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H17" s="4">
-        <v>345.45245543436323</v>
+        <v>335.77467953309849</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" si="0"/>
-        <v>274.53745921507721</v>
+        <v>258.14690522457897</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>55</v>
       </c>
       <c r="L17" s="16">
-        <v>-0.29815580239591893</v>
+        <v>-0.29889379483142398</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>82</v>
       </c>
       <c r="O17" s="10">
-        <v>53.374586045417935</v>
+        <v>54.391713608301288</v>
       </c>
       <c r="Q17" s="13" t="s">
         <v>111</v>
@@ -1668,32 +1668,32 @@
         <v>10</v>
       </c>
       <c r="C18" s="4">
-        <v>547.68745921507718</v>
+        <v>531.29690522457895</v>
       </c>
       <c r="D18" s="5">
         <v>25</v>
       </c>
       <c r="E18" s="4">
-        <v>685.30539614040072</v>
+        <v>663.66872086122646</v>
       </c>
       <c r="F18" s="7">
-        <v>2.1800807088725671</v>
+        <v>2.1399703638183678</v>
       </c>
       <c r="G18" s="4">
-        <v>2.0055144227139889</v>
+        <v>2.4384656223783785</v>
       </c>
       <c r="H18" s="4">
-        <v>345.45245543436323</v>
+        <v>335.77467953309849</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" si="0"/>
-        <v>274.53745921507721</v>
+        <v>258.14690522457897</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>83</v>
       </c>
       <c r="O18" s="10">
-        <v>54.014275766007323</v>
+        <v>42.805350727912341</v>
       </c>
       <c r="Q18" s="13" t="s">
         <v>112</v>
@@ -1707,26 +1707,26 @@
         <v>11</v>
       </c>
       <c r="C19" s="4">
-        <v>547.68745921507718</v>
+        <v>531.29690522457895</v>
       </c>
       <c r="D19" s="5">
         <v>25</v>
       </c>
       <c r="E19" s="4">
-        <v>685.30539614040072</v>
+        <v>663.66872086122646</v>
       </c>
       <c r="F19" s="7">
-        <v>2.1800807088725671</v>
+        <v>2.1399703638183678</v>
       </c>
       <c r="G19" s="4">
         <v>10</v>
       </c>
       <c r="H19" s="4">
-        <v>345.45245543436323</v>
+        <v>335.77467953309849</v>
       </c>
       <c r="I19" s="4">
         <f t="shared" si="0"/>
-        <v>274.53745921507721</v>
+        <v>258.14690522457897</v>
       </c>
       <c r="K19" s="27" t="s">
         <v>58</v>
@@ -1736,7 +1736,7 @@
         <v>84</v>
       </c>
       <c r="O19" s="10">
-        <v>55.339933569630354</v>
+        <v>44.242025146810107</v>
       </c>
       <c r="Q19" s="13" t="s">
         <v>124</v>
@@ -1750,38 +1750,38 @@
         <v>12</v>
       </c>
       <c r="C20" s="4">
-        <v>932.83907702081467</v>
+        <v>671.98403317850523</v>
       </c>
       <c r="D20" s="5">
         <v>25</v>
       </c>
       <c r="E20" s="4">
-        <v>1170.2405428635675</v>
+        <v>843.06138786440704</v>
       </c>
       <c r="F20" s="7">
-        <v>2.8510501836319815</v>
+        <v>2.4398731199336656</v>
       </c>
       <c r="G20" s="4">
         <v>10</v>
       </c>
       <c r="H20" s="4">
-        <v>630.33805325801075</v>
+        <v>425.75133980050299</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" si="0"/>
-        <v>659.68907702081469</v>
+        <v>398.83403317850525</v>
       </c>
       <c r="K20" s="13" t="s">
         <v>59</v>
       </c>
       <c r="L20" s="4">
-        <v>159.02185344711796</v>
+        <v>132.46214147940952</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>85</v>
       </c>
       <c r="O20" s="10">
-        <v>3.4933609588634824</v>
+        <v>3.020822903667709</v>
       </c>
       <c r="Q20" s="28" t="s">
         <v>117</v>
@@ -1805,7 +1805,7 @@
         <v>-0.37994748587359245</v>
       </c>
       <c r="G21" s="4">
-        <v>1.7897056695309543</v>
+        <v>1.4910640297380351</v>
       </c>
       <c r="H21" s="4">
         <v>0.52460446529691762</v>
@@ -1818,13 +1818,13 @@
         <v>60</v>
       </c>
       <c r="L21" s="4">
-        <v>63.229887799023224</v>
+        <v>161.85540883388524</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>86</v>
       </c>
       <c r="O21" s="10">
-        <v>22.489305649899514</v>
+        <v>21.395115312629525</v>
       </c>
       <c r="Q21" s="22" t="s">
         <v>118</v>
@@ -1850,7 +1850,7 @@
         <v>-0.37994748587359245</v>
       </c>
       <c r="G22" s="4">
-        <v>1.7897056695309543</v>
+        <v>1.4910640297380351</v>
       </c>
       <c r="H22" s="4">
         <v>0.55744775153482984</v>
@@ -1863,19 +1863,19 @@
         <v>61</v>
       </c>
       <c r="L22" s="4">
-        <v>21.287660768567079</v>
+        <v>20.961570352690121</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>87</v>
       </c>
       <c r="O22" s="6">
-        <v>52.415130655682205</v>
+        <v>53.43053490915559</v>
       </c>
       <c r="Q22" s="23" t="s">
         <v>113</v>
       </c>
       <c r="R22" s="24">
-        <v>37353.391068248107</v>
+        <v>131829.09853620338</v>
       </c>
       <c r="T22" s="25"/>
     </row>
@@ -1896,7 +1896,7 @@
         <v>-0.19317568283781225</v>
       </c>
       <c r="G23" s="4">
-        <v>1.7897056695309543</v>
+        <v>1.4910640297380351</v>
       </c>
       <c r="H23" s="4">
         <v>6.518635522826691</v>
@@ -1909,19 +1909,19 @@
         <v>62</v>
       </c>
       <c r="L23" s="4">
-        <v>19.283425035580251</v>
+        <v>16.416344792437251</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>88</v>
       </c>
       <c r="O23" s="6">
-        <v>23.133959295545651</v>
+        <v>22.280941712184308</v>
       </c>
       <c r="Q23" s="23" t="s">
         <v>114</v>
       </c>
       <c r="R23" s="24">
-        <v>2135419.8232024489</v>
+        <v>1116326.6169003651</v>
       </c>
       <c r="T23" s="25"/>
     </row>
@@ -1942,7 +1942,7 @@
         <v>0.91173151933586583</v>
       </c>
       <c r="G24" s="4">
-        <v>1.7897056695309543</v>
+        <v>1.4910640297380351</v>
       </c>
       <c r="H24" s="4">
         <v>60.765690527522125</v>
@@ -1955,19 +1955,19 @@
         <v>63</v>
       </c>
       <c r="L24" s="4">
-        <v>3.5021630107067545</v>
+        <v>3.6308891960099743</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>89</v>
       </c>
       <c r="O24" s="15">
-        <v>23.136921933126388</v>
+        <v>22.285012708851948</v>
       </c>
       <c r="Q24" s="23" t="s">
         <v>115</v>
       </c>
       <c r="R24" s="24">
-        <v>101198.51533209301</v>
+        <v>52084.109853286493</v>
       </c>
       <c r="S24" s="9"/>
       <c r="T24" s="25"/>
@@ -1982,32 +1982,32 @@
         <v>15</v>
       </c>
       <c r="C25" s="4">
-        <v>396.43287838933054</v>
+        <v>382.37703255538463</v>
       </c>
       <c r="D25" s="5">
         <v>31.569242975234697</v>
       </c>
       <c r="E25" s="4">
-        <v>383.09182021380718</v>
+        <v>362.17461939089003</v>
       </c>
       <c r="F25" s="7">
-        <v>1.1002468147744369</v>
+        <v>1.0465306128007958</v>
       </c>
       <c r="G25" s="4">
-        <v>1.7897056695309543</v>
+        <v>1.4910640297380351</v>
       </c>
       <c r="H25" s="4">
-        <v>74.651133136999675</v>
+        <v>69.749417932523528</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" si="0"/>
-        <v>123.28287838933056</v>
+        <v>109.22703255538465</v>
       </c>
       <c r="K25" s="13" t="s">
         <v>64</v>
       </c>
       <c r="L25" s="4">
-        <v>110.44125389851233</v>
+        <v>134.41650108074617</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -2024,26 +2024,26 @@
         <v>16</v>
       </c>
       <c r="C26" s="4">
-        <v>368.13790080168786</v>
+        <v>354.03463903030661</v>
       </c>
       <c r="D26" s="5">
         <v>7.8923107438086744</v>
       </c>
       <c r="E26" s="4">
-        <v>342.98790088879446</v>
+        <v>323.59574356441874</v>
       </c>
       <c r="F26" s="7">
-        <v>1.119604713516257</v>
+        <v>1.0658995739454769</v>
       </c>
       <c r="G26" s="4">
-        <v>1.7897056695309543</v>
+        <v>1.4910640297380351</v>
       </c>
       <c r="H26" s="4">
-        <v>28.775656302113202</v>
+        <v>25.395686340765561</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" si="0"/>
-        <v>94.987900801687886</v>
+        <v>80.88463903030663</v>
       </c>
       <c r="N26" s="27" t="s">
         <v>76</v>
@@ -2076,7 +2076,7 @@
         <v>0.91018564327057938</v>
       </c>
       <c r="G27" s="4">
-        <v>1.7897056695309543</v>
+        <v>1.4910640297380351</v>
       </c>
       <c r="H27" s="4">
         <v>19.876601402460075</v>
@@ -2089,7 +2089,7 @@
         <v>77</v>
       </c>
       <c r="O27" s="6">
-        <v>0.71269346475761464</v>
+        <v>0.86641977356205369</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2118,7 +2118,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G28" s="4">
-        <v>34.591753259051274</v>
+        <v>28.819553901096199</v>
       </c>
       <c r="H28" s="4">
         <v>2.5073905791015251E-5</v>
@@ -2160,7 +2160,7 @@
         <v>0.43672528196163279</v>
       </c>
       <c r="G29" s="4">
-        <v>34.591753259051274</v>
+        <v>28.819553901096199</v>
       </c>
       <c r="H29" s="4">
         <v>0.17334706272843686</v>
@@ -2190,26 +2190,26 @@
         <v>39</v>
       </c>
       <c r="C30" s="4">
-        <v>304.03303316959324</v>
+        <v>303.79298846046936</v>
       </c>
       <c r="D30" s="5">
         <v>101.325</v>
       </c>
       <c r="E30" s="4">
-        <v>129.51335809758132</v>
+        <v>128.51004804133865</v>
       </c>
       <c r="F30" s="7">
-        <v>0.44888256955875044</v>
+        <v>0.44558126268734799</v>
       </c>
       <c r="G30" s="4">
-        <v>34.591753259051274</v>
+        <v>28.819553901096199</v>
       </c>
       <c r="H30" s="4">
-        <v>0.23949854144378332</v>
+        <v>0.22047312890975446</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" si="0"/>
-        <v>30.883033169593261</v>
+        <v>30.642988460469383</v>
       </c>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
@@ -2226,26 +2226,26 @@
         <v>29</v>
       </c>
       <c r="C31" s="4">
-        <v>435.43287838933054</v>
+        <v>421.37703255538463</v>
       </c>
       <c r="D31" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E31" s="4">
-        <v>591.19593244282169</v>
+        <v>574.17808817632817</v>
       </c>
       <c r="F31" s="7">
-        <v>2.1610419768753544</v>
+        <v>2.1213123773587061</v>
       </c>
       <c r="G31" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H31" s="4">
-        <v>257.03321905731815</v>
+        <v>251.86075488671338</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
+        <v>148.22703255538465</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -2262,26 +2262,26 @@
         <v>30</v>
       </c>
       <c r="C32" s="4">
-        <v>423.3557736165609</v>
+        <v>414.09144532798098</v>
       </c>
       <c r="D32" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E32" s="4">
-        <v>576.59650223683718</v>
+        <v>565.19773365306719</v>
       </c>
       <c r="F32" s="7">
-        <v>2.1270382629381421</v>
+        <v>2.0998136278119031</v>
       </c>
       <c r="G32" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H32" s="4">
-        <v>252.57199616171354</v>
+        <v>249.29025254083163</v>
       </c>
       <c r="I32" s="4">
         <f t="shared" si="0"/>
-        <v>150.20577361656092</v>
+        <v>140.941445327981</v>
       </c>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
@@ -2310,7 +2310,7 @@
         <v>1.8961819516546079</v>
       </c>
       <c r="G33" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H33" s="4">
         <v>231.85738014859709</v>
@@ -2334,26 +2334,26 @@
         <v>32</v>
       </c>
       <c r="C34" s="4">
-        <v>346.62433578909861</v>
+        <v>348.11288652158407</v>
       </c>
       <c r="D34" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E34" s="4">
-        <v>468.83148724964826</v>
+        <v>471.53280514716448</v>
       </c>
       <c r="F34" s="7">
-        <v>1.8443890532471721</v>
+        <v>1.8521656410056229</v>
       </c>
       <c r="G34" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H34" s="4">
-        <v>229.07884304388728</v>
+        <v>229.46157130122151</v>
       </c>
       <c r="I34" s="4">
         <f t="shared" si="0"/>
-        <v>73.474335789098632</v>
+        <v>74.962886521584096</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.3">
@@ -2394,16 +2394,16 @@
         <v>0.101325</v>
       </c>
       <c r="E36" s="4">
-        <v>453.10722153513228</v>
+        <v>454.60719015199737</v>
       </c>
       <c r="F36" s="7">
-        <v>3.9723323134988857</v>
+        <v>3.9769142162865401</v>
       </c>
       <c r="G36" s="4">
         <v>1.1599999999999999</v>
       </c>
       <c r="H36" s="4">
-        <v>1.3091135519945019</v>
+        <v>1.4429878527205291</v>
       </c>
       <c r="I36" s="4">
         <f t="shared" si="0"/>
@@ -2415,26 +2415,26 @@
         <v>32</v>
       </c>
       <c r="C37" s="4">
-        <v>346.62433578909861</v>
+        <v>348.11288652158407</v>
       </c>
       <c r="D37" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E37" s="4">
-        <v>468.83148724964826</v>
+        <v>471.53280514716448</v>
       </c>
       <c r="F37" s="7">
-        <v>1.8443890532471721</v>
+        <v>1.8521656410056229</v>
       </c>
       <c r="G37" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H37" s="4">
-        <v>229.07884304388728</v>
+        <v>229.46157130122151</v>
       </c>
       <c r="I37" s="4">
         <f t="shared" si="0"/>
-        <v>73.474335789098632</v>
+        <v>74.962886521584096</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.3">
@@ -2442,26 +2442,26 @@
         <v>33</v>
       </c>
       <c r="C38" s="4">
-        <v>344.39458549639238</v>
+        <v>345.58184628905991</v>
       </c>
       <c r="D38" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E38" s="4">
-        <v>464.67130036926602</v>
+        <v>466.90431100010727</v>
       </c>
       <c r="F38" s="7">
-        <v>1.8323480555267959</v>
+        <v>1.8388208125565038</v>
       </c>
       <c r="G38" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H38" s="4">
-        <v>228.50867963383527</v>
+        <v>228.81183775626909</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" si="0"/>
-        <v>71.244585496392403</v>
+        <v>72.431846289059933</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.3">
@@ -2469,26 +2469,26 @@
         <v>33</v>
       </c>
       <c r="C39" s="4">
-        <v>344.39458549639238</v>
+        <v>345.58184628905991</v>
       </c>
       <c r="D39" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E39" s="4">
-        <v>464.67130036356895</v>
+        <v>466.90431099381976</v>
       </c>
       <c r="F39" s="7">
-        <v>1.8323480555267959</v>
+        <v>1.8388208125565038</v>
       </c>
       <c r="G39" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H39" s="4">
-        <v>228.5086796281382</v>
+        <v>228.81183774998161</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" si="0"/>
-        <v>71.244585496392403</v>
+        <v>72.431846289059933</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.3">
@@ -2508,7 +2508,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G40" s="4">
-        <v>7.9944855772860111</v>
+        <v>7.5615343776216211</v>
       </c>
       <c r="H40" s="4">
         <v>224.34458467728319</v>
@@ -2535,7 +2535,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G41" s="4">
-        <v>2.8698525619149113E-3</v>
+        <v>2.3446171377681925E-3</v>
       </c>
       <c r="H41" s="4">
         <v>2.5073905791015251E-5</v>
@@ -2550,26 +2550,26 @@
         <v>20</v>
       </c>
       <c r="C42" s="4">
-        <v>343.39458549639238</v>
+        <v>344.58184628905991</v>
       </c>
       <c r="D42" s="5">
         <v>101.325</v>
       </c>
       <c r="E42" s="4">
-        <v>294.14738747128831</v>
+        <v>299.12268215996386</v>
       </c>
       <c r="F42" s="7">
-        <v>0.95807613660276081</v>
+        <v>0.97253971167408337</v>
       </c>
       <c r="G42" s="4">
-        <v>2.8698525619149113E-3</v>
+        <v>2.3446171377681925E-3</v>
       </c>
       <c r="H42" s="4">
-        <v>13.057465900979093</v>
+        <v>13.720445682139834</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="0"/>
-        <v>70.244585496392403</v>
+        <v>71.431846289059933</v>
       </c>
     </row>
   </sheetData>

--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFA6E58-72D9-427F-BF37-C3222BA4DFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE12C29-6477-450E-8E2B-B159E2797215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Energy_Exergy" sheetId="2" r:id="rId1"/>
@@ -1001,26 +1001,26 @@
         <v>1</v>
       </c>
       <c r="C3" s="4">
-        <v>773.15</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D3" s="5">
         <v>25</v>
       </c>
       <c r="E3" s="4">
-        <v>969.22761234812413</v>
+        <v>1350.0381316636626</v>
       </c>
       <c r="F3" s="7">
-        <v>2.614766418080567</v>
+        <v>3.0305681085599816</v>
       </c>
       <c r="G3" s="4">
         <v>10</v>
       </c>
       <c r="H3" s="4">
-        <v>499.7731274417215</v>
+        <v>756.61237274082237</v>
       </c>
       <c r="I3" s="4">
         <f>C3-273.15</f>
-        <v>500</v>
+        <v>800.00000000000011</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>40</v>
@@ -1046,44 +1046,44 @@
         <v>2</v>
       </c>
       <c r="C4" s="4">
-        <v>728.45135112026719</v>
+        <v>1018.1289616795918</v>
       </c>
       <c r="D4" s="5">
         <v>17.482517482517483</v>
       </c>
       <c r="E4" s="4">
-        <v>920.93965105155189</v>
+        <v>1281.2341664776559</v>
       </c>
       <c r="F4" s="7">
-        <v>2.6197661286628455</v>
+        <v>3.035664888414034</v>
       </c>
       <c r="G4" s="4">
         <v>10</v>
       </c>
       <c r="H4" s="4">
-        <v>449.99450243504293</v>
+        <v>686.28880264133011</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" ref="I4:I42" si="0">C4-273.15</f>
-        <v>455.30135112026721</v>
+        <v>744.97896167959186</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>42</v>
       </c>
       <c r="L4" s="7">
-        <v>1.2616622448371713</v>
+        <v>1.7979758880009502</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>66</v>
       </c>
       <c r="O4" s="10">
-        <v>482.87961296572234</v>
+        <v>688.03965186006621</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>98</v>
       </c>
       <c r="R4">
-        <v>130055.70705438507</v>
+        <v>916.98727526679568</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
@@ -1091,44 +1091,44 @@
         <v>3</v>
       </c>
       <c r="C5" s="4">
-        <v>773.15</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D5" s="5">
         <v>17.482517482517483</v>
       </c>
       <c r="E5" s="4">
-        <v>975.50549339380814</v>
+        <v>1351.4823193165744</v>
       </c>
       <c r="F5" s="7">
-        <v>2.6924623805995864</v>
+        <v>3.1028601038812176</v>
       </c>
       <c r="G5" s="4">
         <v>10</v>
       </c>
       <c r="H5" s="4">
-        <v>482.88595726235974</v>
+        <v>736.50270198870771</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>800.00000000000011</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>43</v>
       </c>
       <c r="L5" s="7">
-        <v>0.54565842342256221</v>
+        <v>0.70248152838918376</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>67</v>
       </c>
       <c r="O5" s="10">
-        <v>842.93566294255663</v>
+        <v>1199.1350689643341</v>
       </c>
       <c r="Q5" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R5">
-        <v>927277.70682172745</v>
+        <v>830.65281683265493</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
@@ -1136,44 +1136,44 @@
         <v>4</v>
       </c>
       <c r="C6" s="4">
-        <v>695.01503073542415</v>
+        <v>976.11427576830124</v>
       </c>
       <c r="D6" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E6" s="4">
-        <v>891.21192709955244</v>
+        <v>1231.5688124201411</v>
       </c>
       <c r="F6" s="7">
-        <v>2.7016269704938249</v>
+        <v>3.1121411727413726</v>
       </c>
       <c r="G6" s="4">
         <v>10</v>
       </c>
       <c r="H6" s="4">
-        <v>395.8599684911369</v>
+        <v>613.82204441161923</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="0"/>
-        <v>421.86503073542417</v>
+        <v>702.96427576830126</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>47</v>
       </c>
       <c r="L6" s="7">
-        <v>1.8073206682597334</v>
+        <v>2.5004574163901339</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="O6" s="10">
-        <v>57.523574052581495</v>
+        <v>71.774211786387255</v>
       </c>
       <c r="Q6" s="13" t="s">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>196542.52607265621</v>
+        <v>6850.0253590880538</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -1181,38 +1181,38 @@
         <v>5</v>
       </c>
       <c r="C7" s="4">
-        <v>543.48173263613626</v>
+        <v>580.59332858273865</v>
       </c>
       <c r="D7" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E7" s="4">
-        <v>716.30407434487142</v>
+        <v>758.75704305028523</v>
       </c>
       <c r="F7" s="7">
-        <v>2.4179049497412306</v>
+        <v>2.4934653765384365</v>
       </c>
       <c r="G7" s="4">
         <v>10</v>
       </c>
       <c r="H7" s="4">
-        <v>305.54383622384188</v>
+        <v>325.46846367966873</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="0"/>
-        <v>270.33173263613628</v>
+        <v>307.44332858273867</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>44</v>
       </c>
       <c r="L7" s="7">
-        <v>1.7939266881176714</v>
+        <v>4.8493514799902702</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>69</v>
       </c>
       <c r="O7" s="10">
-        <v>-365.4747826578693</v>
+        <v>-386.40079286911646</v>
       </c>
       <c r="Q7" s="13" t="s">
         <v>105</v>
@@ -1226,38 +1226,38 @@
         <v>6</v>
       </c>
       <c r="C8" s="4">
-        <v>421.37703255538463</v>
+        <v>435.43287838933054</v>
       </c>
       <c r="D8" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E8" s="4">
-        <v>574.17808817703337</v>
+        <v>591.19593244306282</v>
       </c>
       <c r="F8" s="7">
-        <v>2.1213123773587061</v>
+        <v>2.1610419768753544</v>
       </c>
       <c r="G8" s="4">
         <v>10</v>
       </c>
       <c r="H8" s="4">
-        <v>251.84692551185341</v>
+        <v>257.0193896819942</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="0"/>
-        <v>148.22703255538465</v>
+        <v>162.28287838933056</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>45</v>
       </c>
       <c r="L8" s="7">
-        <v>1.4212598619940109</v>
+        <v>1.6756111060722243</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>70</v>
       </c>
       <c r="O8" s="10">
-        <v>-218.21983132529576</v>
+        <v>-188.73788675888972</v>
       </c>
       <c r="Q8" s="13" t="s">
         <v>104</v>
@@ -1271,38 +1271,38 @@
         <v>29</v>
       </c>
       <c r="C9" s="4">
-        <v>421.37703255538463</v>
+        <v>435.43287838933054</v>
       </c>
       <c r="D9" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E9" s="4">
-        <v>574.17808817703337</v>
+        <v>591.19593244306282</v>
       </c>
       <c r="F9" s="7">
-        <v>2.1213123773587061</v>
+        <v>2.1610419768753544</v>
       </c>
       <c r="G9" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H9" s="4">
-        <v>251.84692551185341</v>
+        <v>257.0193896819942</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" si="0"/>
-        <v>148.22703255538465</v>
+        <v>162.28287838933056</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>48</v>
       </c>
       <c r="L9" s="7">
-        <v>9.191992371611768E-2</v>
+        <v>0.11033034486553291</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>71</v>
       </c>
       <c r="O9" s="10">
-        <v>-4.8971442727741191E-2</v>
+        <v>-5.8779815586019524E-2</v>
       </c>
       <c r="Q9" s="23" t="s">
         <v>101</v>
@@ -1316,38 +1316,38 @@
         <v>30</v>
       </c>
       <c r="C10" s="4">
-        <v>414.09144532798098</v>
+        <v>423.3557736165609</v>
       </c>
       <c r="D10" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E10" s="4">
-        <v>0.56519773365306714</v>
+        <v>0.57659650223683723</v>
       </c>
       <c r="F10" s="7">
-        <v>2.099813627811903E-3</v>
+        <v>2.1270382629381421E-3</v>
       </c>
       <c r="G10" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H10" s="4">
-        <v>0.24929025254083162</v>
+        <v>0.25257199616171355</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="0"/>
-        <v>140.941445327981</v>
+        <v>150.20577361656092</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="7">
-        <v>0.57208419638170538</v>
+        <v>0.68666556854253946</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>72</v>
       </c>
       <c r="O10" s="10">
-        <v>742.12066192511395</v>
+        <v>1312.0360411963943</v>
       </c>
       <c r="Q10" s="13" t="s">
         <v>102</v>
@@ -1373,7 +1373,7 @@
         <v>1.8961819516546078E-3</v>
       </c>
       <c r="G11" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H11" s="4">
         <v>0.23185738014859708</v>
@@ -1386,13 +1386,13 @@
         <v>50</v>
       </c>
       <c r="L11" s="7">
-        <v>7.3321697591537435E-2</v>
+        <v>0.12544275752191905</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="O11" s="10">
-        <v>57.474602609853754</v>
+        <v>71.715431970801234</v>
       </c>
       <c r="Q11" s="13" t="s">
         <v>103</v>
@@ -1406,38 +1406,38 @@
         <v>32</v>
       </c>
       <c r="C12" s="4">
-        <v>348.11288652158407</v>
+        <v>346.62433578909861</v>
       </c>
       <c r="D12" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E12" s="4">
-        <v>0.4715328051471645</v>
+        <v>0.46883148724964824</v>
       </c>
       <c r="F12" s="7">
-        <v>1.8521656410056229E-3</v>
+        <v>1.844389053247172E-3</v>
       </c>
       <c r="G12" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H12" s="4">
-        <v>0.22946157130122152</v>
+        <v>0.22907884304388729</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" si="0"/>
-        <v>74.962886521584096</v>
+        <v>73.474335789098632</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L12" s="7">
-        <v>0.73732581768936045</v>
+        <v>0.92243867092999143</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>74</v>
       </c>
       <c r="O12" s="12">
-        <v>799.59526453496767</v>
+        <v>1383.7514731671954</v>
       </c>
       <c r="Q12" s="13" t="s">
         <v>106</v>
@@ -1451,32 +1451,32 @@
         <v>33</v>
       </c>
       <c r="C13" s="4">
-        <v>345.58184628905991</v>
+        <v>344.39458549639238</v>
       </c>
       <c r="D13" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E13" s="4">
-        <v>466.90431100010727</v>
+        <v>464.67130036926602</v>
       </c>
       <c r="F13" s="7">
-        <v>1.8388208125565038</v>
+        <v>1.8323480555267959</v>
       </c>
       <c r="G13" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H13" s="4">
-        <v>228.81183775626909</v>
+        <v>228.50867963383527</v>
       </c>
       <c r="I13" s="4">
         <f t="shared" si="0"/>
-        <v>72.431846289059933</v>
+        <v>71.244585496392403</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>52</v>
       </c>
       <c r="L13" s="7">
-        <v>0.60239760572916501</v>
+        <v>0.72305037797389082</v>
       </c>
       <c r="Q13" s="13" t="s">
         <v>107</v>
@@ -1490,32 +1490,32 @@
         <v>34</v>
       </c>
       <c r="C14" s="4">
-        <v>421.37703255538463</v>
+        <v>435.43287838933054</v>
       </c>
       <c r="D14" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E14" s="4">
-        <v>574.17808817703337</v>
+        <v>591.19593244306282</v>
       </c>
       <c r="F14" s="7">
-        <v>2.1213123773587061</v>
+        <v>2.1610419768753544</v>
       </c>
       <c r="G14" s="4">
-        <v>2.4384656223783785</v>
+        <v>2.0055144227139889</v>
       </c>
       <c r="H14" s="4">
-        <v>251.84692551185341</v>
+        <v>257.0193896819942</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="0"/>
-        <v>148.22703255538465</v>
+        <v>162.28287838933056</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>54</v>
       </c>
       <c r="L14" s="7">
-        <v>7.7453609350341693E-2</v>
+        <v>0.12767286098529926</v>
       </c>
       <c r="N14" s="27" t="s">
         <v>75</v>
@@ -1545,7 +1545,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G15" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H15" s="4">
         <v>224.33075530171814</v>
@@ -1558,13 +1558,13 @@
         <v>53</v>
       </c>
       <c r="L15" s="7">
-        <v>0.67985121507950674</v>
+        <v>0.85072323895919011</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="O15" s="10">
-        <v>7.7950074757952033</v>
+        <v>7.7745474285568061</v>
       </c>
       <c r="Q15" s="13" t="s">
         <v>109</v>
@@ -1590,7 +1590,7 @@
         <v>1.7343043486568708</v>
       </c>
       <c r="G16" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H16" s="4">
         <v>268.76481394998945</v>
@@ -1603,13 +1603,13 @@
         <v>46</v>
       </c>
       <c r="L16" s="7">
-        <v>3.4998517609593639E-2</v>
+        <v>3.3258554014030113E-2</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>81</v>
       </c>
       <c r="O16" s="10">
-        <v>41.061925255339496</v>
+        <v>52.471841055808</v>
       </c>
       <c r="Q16" s="13" t="s">
         <v>110</v>
@@ -1623,38 +1623,38 @@
         <v>9</v>
       </c>
       <c r="C17" s="4">
-        <v>531.29690522457895</v>
+        <v>547.68745921507718</v>
       </c>
       <c r="D17" s="5">
         <v>25</v>
       </c>
       <c r="E17" s="4">
-        <v>663.66872086122646</v>
+        <v>685.30539614040072</v>
       </c>
       <c r="F17" s="7">
-        <v>2.1399703638183678</v>
+        <v>2.1800807088725671</v>
       </c>
       <c r="G17" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H17" s="4">
-        <v>335.77467953309849</v>
+        <v>345.45245543436323</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" si="0"/>
-        <v>258.14690522457897</v>
+        <v>274.53745921507721</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>55</v>
       </c>
       <c r="L17" s="16">
-        <v>-0.29889379483142398</v>
+        <v>-0.29815580239591893</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>82</v>
       </c>
       <c r="O17" s="10">
-        <v>54.391713608301288</v>
+        <v>53.374586045417935</v>
       </c>
       <c r="Q17" s="13" t="s">
         <v>111</v>
@@ -1668,38 +1668,38 @@
         <v>10</v>
       </c>
       <c r="C18" s="4">
-        <v>531.29690522457895</v>
+        <v>547.68745921507718</v>
       </c>
       <c r="D18" s="5">
         <v>25</v>
       </c>
       <c r="E18" s="4">
-        <v>663.66872086122646</v>
+        <v>685.30539614040072</v>
       </c>
       <c r="F18" s="7">
-        <v>2.1399703638183678</v>
+        <v>2.1800807088725671</v>
       </c>
       <c r="G18" s="4">
-        <v>2.4384656223783785</v>
+        <v>2.0055144227139889</v>
       </c>
       <c r="H18" s="4">
-        <v>335.77467953309849</v>
+        <v>345.45245543436323</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" si="0"/>
-        <v>258.14690522457897</v>
+        <v>274.53745921507721</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>83</v>
       </c>
       <c r="O18" s="10">
-        <v>42.805350727912341</v>
+        <v>54.014275766007323</v>
       </c>
       <c r="Q18" s="13" t="s">
         <v>112</v>
       </c>
       <c r="R18">
-        <v>2032352.056903265</v>
+        <v>1765185.6442090091</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
@@ -1707,26 +1707,26 @@
         <v>11</v>
       </c>
       <c r="C19" s="4">
-        <v>531.29690522457895</v>
+        <v>547.68745921507718</v>
       </c>
       <c r="D19" s="5">
         <v>25</v>
       </c>
       <c r="E19" s="4">
-        <v>663.66872086122646</v>
+        <v>685.30539614040072</v>
       </c>
       <c r="F19" s="7">
-        <v>2.1399703638183678</v>
+        <v>2.1800807088725671</v>
       </c>
       <c r="G19" s="4">
         <v>10</v>
       </c>
       <c r="H19" s="4">
-        <v>335.77467953309849</v>
+        <v>345.45245543436323</v>
       </c>
       <c r="I19" s="4">
         <f t="shared" si="0"/>
-        <v>258.14690522457897</v>
+        <v>274.53745921507721</v>
       </c>
       <c r="K19" s="27" t="s">
         <v>58</v>
@@ -1736,7 +1736,7 @@
         <v>84</v>
       </c>
       <c r="O19" s="10">
-        <v>44.242025146810107</v>
+        <v>55.339933569630354</v>
       </c>
       <c r="Q19" s="13" t="s">
         <v>124</v>
@@ -1750,38 +1750,38 @@
         <v>12</v>
       </c>
       <c r="C20" s="4">
-        <v>671.98403317850523</v>
+        <v>932.83907702081467</v>
       </c>
       <c r="D20" s="5">
         <v>25</v>
       </c>
       <c r="E20" s="4">
-        <v>843.06138786440704</v>
+        <v>1170.2405428635675</v>
       </c>
       <c r="F20" s="7">
-        <v>2.4398731199336656</v>
+        <v>2.8510501836319815</v>
       </c>
       <c r="G20" s="4">
         <v>10</v>
       </c>
       <c r="H20" s="4">
-        <v>425.75133980050299</v>
+        <v>630.33805325801075</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" si="0"/>
-        <v>398.83403317850525</v>
+        <v>659.68907702081469</v>
       </c>
       <c r="K20" s="13" t="s">
         <v>59</v>
       </c>
       <c r="L20" s="4">
-        <v>132.46214147940952</v>
+        <v>159.02185344711796</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>85</v>
       </c>
       <c r="O20" s="10">
-        <v>3.020822903667709</v>
+        <v>3.4933609588634824</v>
       </c>
       <c r="Q20" s="28" t="s">
         <v>117</v>
@@ -1805,7 +1805,7 @@
         <v>-0.37994748587359245</v>
       </c>
       <c r="G21" s="4">
-        <v>1.4910640297380351</v>
+        <v>1.7897056695309543</v>
       </c>
       <c r="H21" s="4">
         <v>0.52460446529691762</v>
@@ -1818,13 +1818,13 @@
         <v>60</v>
       </c>
       <c r="L21" s="4">
-        <v>161.85540883388524</v>
+        <v>63.229887799023224</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>86</v>
       </c>
       <c r="O21" s="10">
-        <v>21.395115312629525</v>
+        <v>22.489305649899514</v>
       </c>
       <c r="Q21" s="22" t="s">
         <v>118</v>
@@ -1850,7 +1850,7 @@
         <v>-0.37994748587359245</v>
       </c>
       <c r="G22" s="4">
-        <v>1.4910640297380351</v>
+        <v>1.7897056695309543</v>
       </c>
       <c r="H22" s="4">
         <v>0.55744775153482984</v>
@@ -1863,21 +1863,23 @@
         <v>61</v>
       </c>
       <c r="L22" s="4">
-        <v>20.961570352690121</v>
+        <v>21.287660768567079</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>87</v>
       </c>
       <c r="O22" s="6">
-        <v>53.43053490915559</v>
+        <v>52.415130655682205</v>
       </c>
       <c r="Q22" s="23" t="s">
         <v>113</v>
       </c>
       <c r="R22" s="24">
-        <v>131829.09853620338</v>
-      </c>
-      <c r="T22" s="25"/>
+        <v>189927.66233550836</v>
+      </c>
+      <c r="T22" s="25">
+        <v>141781.626188147</v>
+      </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
@@ -1896,7 +1898,7 @@
         <v>-0.19317568283781225</v>
       </c>
       <c r="G23" s="4">
-        <v>1.4910640297380351</v>
+        <v>1.7897056695309543</v>
       </c>
       <c r="H23" s="4">
         <v>6.518635522826691</v>
@@ -1909,21 +1911,23 @@
         <v>62</v>
       </c>
       <c r="L23" s="4">
-        <v>16.416344792437251</v>
+        <v>19.283425035580251</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>88</v>
       </c>
       <c r="O23" s="6">
-        <v>22.280941712184308</v>
+        <v>23.133959295545651</v>
       </c>
       <c r="Q23" s="23" t="s">
         <v>114</v>
       </c>
       <c r="R23" s="24">
-        <v>1116326.6169003651</v>
-      </c>
-      <c r="T23" s="25"/>
+        <v>2003923.2325693402</v>
+      </c>
+      <c r="T23" s="25">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
@@ -1942,7 +1946,7 @@
         <v>0.91173151933586583</v>
       </c>
       <c r="G24" s="4">
-        <v>1.4910640297380351</v>
+        <v>1.7897056695309543</v>
       </c>
       <c r="H24" s="4">
         <v>60.765690527522125</v>
@@ -1955,22 +1959,24 @@
         <v>63</v>
       </c>
       <c r="L24" s="4">
-        <v>3.6308891960099743</v>
+        <v>3.5021630107067545</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>89</v>
       </c>
       <c r="O24" s="15">
-        <v>22.285012708851948</v>
+        <v>23.136921933126388</v>
       </c>
       <c r="Q24" s="23" t="s">
         <v>115</v>
       </c>
       <c r="R24" s="24">
-        <v>52084.109853286493</v>
+        <v>88160.301000562598</v>
       </c>
       <c r="S24" s="9"/>
-      <c r="T24" s="25"/>
+      <c r="T24" s="25">
+        <v>187521.96275412751</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -1982,32 +1988,32 @@
         <v>15</v>
       </c>
       <c r="C25" s="4">
-        <v>382.37703255538463</v>
+        <v>396.43287838933054</v>
       </c>
       <c r="D25" s="5">
         <v>31.569242975234697</v>
       </c>
       <c r="E25" s="4">
-        <v>362.17461939089003</v>
+        <v>383.09182021380718</v>
       </c>
       <c r="F25" s="7">
-        <v>1.0465306128007958</v>
+        <v>1.1002468147744369</v>
       </c>
       <c r="G25" s="4">
-        <v>1.4910640297380351</v>
+        <v>1.7897056695309543</v>
       </c>
       <c r="H25" s="4">
-        <v>69.749417932523528</v>
+        <v>74.651133136999675</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" si="0"/>
-        <v>109.22703255538465</v>
+        <v>123.28287838933056</v>
       </c>
       <c r="K25" s="13" t="s">
         <v>64</v>
       </c>
       <c r="L25" s="4">
-        <v>134.41650108074617</v>
+        <v>110.44125389851233</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -2024,26 +2030,26 @@
         <v>16</v>
       </c>
       <c r="C26" s="4">
-        <v>354.03463903030661</v>
+        <v>368.13790080168786</v>
       </c>
       <c r="D26" s="5">
         <v>7.8923107438086744</v>
       </c>
       <c r="E26" s="4">
-        <v>323.59574356441874</v>
+        <v>342.98790088879446</v>
       </c>
       <c r="F26" s="7">
-        <v>1.0658995739454769</v>
+        <v>1.119604713516257</v>
       </c>
       <c r="G26" s="4">
-        <v>1.4910640297380351</v>
+        <v>1.7897056695309543</v>
       </c>
       <c r="H26" s="4">
-        <v>25.395686340765561</v>
+        <v>28.775656302113202</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" si="0"/>
-        <v>80.88463903030663</v>
+        <v>94.987900801687886</v>
       </c>
       <c r="N26" s="27" t="s">
         <v>76</v>
@@ -2076,7 +2082,7 @@
         <v>0.91018564327057938</v>
       </c>
       <c r="G27" s="4">
-        <v>1.4910640297380351</v>
+        <v>1.7897056695309543</v>
       </c>
       <c r="H27" s="4">
         <v>19.876601402460075</v>
@@ -2089,7 +2095,7 @@
         <v>77</v>
       </c>
       <c r="O27" s="6">
-        <v>0.86641977356205369</v>
+        <v>0.71269346475761464</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2118,7 +2124,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G28" s="4">
-        <v>28.819553901096199</v>
+        <v>34.591753259051274</v>
       </c>
       <c r="H28" s="4">
         <v>2.5073905791015251E-5</v>
@@ -2160,7 +2166,7 @@
         <v>0.43672528196163279</v>
       </c>
       <c r="G29" s="4">
-        <v>28.819553901096199</v>
+        <v>34.591753259051274</v>
       </c>
       <c r="H29" s="4">
         <v>0.17334706272843686</v>
@@ -2190,26 +2196,26 @@
         <v>39</v>
       </c>
       <c r="C30" s="4">
-        <v>303.79298846046936</v>
+        <v>304.03303316959324</v>
       </c>
       <c r="D30" s="5">
         <v>101.325</v>
       </c>
       <c r="E30" s="4">
-        <v>128.51004804133865</v>
+        <v>129.51335809758132</v>
       </c>
       <c r="F30" s="7">
-        <v>0.44558126268734799</v>
+        <v>0.44888256955875044</v>
       </c>
       <c r="G30" s="4">
-        <v>28.819553901096199</v>
+        <v>34.591753259051274</v>
       </c>
       <c r="H30" s="4">
-        <v>0.22047312890975446</v>
+        <v>0.23949854144378332</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" si="0"/>
-        <v>30.642988460469383</v>
+        <v>30.883033169593261</v>
       </c>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
@@ -2226,26 +2232,26 @@
         <v>29</v>
       </c>
       <c r="C31" s="4">
-        <v>421.37703255538463</v>
+        <v>435.43287838933054</v>
       </c>
       <c r="D31" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E31" s="4">
-        <v>574.17808817632817</v>
+        <v>591.19593244282169</v>
       </c>
       <c r="F31" s="7">
-        <v>2.1213123773587061</v>
+        <v>2.1610419768753544</v>
       </c>
       <c r="G31" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H31" s="4">
-        <v>251.86075488671338</v>
+        <v>257.03321905731815</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" si="0"/>
-        <v>148.22703255538465</v>
+        <v>162.28287838933056</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -2262,26 +2268,26 @@
         <v>30</v>
       </c>
       <c r="C32" s="4">
-        <v>414.09144532798098</v>
+        <v>423.3557736165609</v>
       </c>
       <c r="D32" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E32" s="4">
-        <v>565.19773365306719</v>
+        <v>576.59650223683718</v>
       </c>
       <c r="F32" s="7">
-        <v>2.0998136278119031</v>
+        <v>2.1270382629381421</v>
       </c>
       <c r="G32" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H32" s="4">
-        <v>249.29025254083163</v>
+        <v>252.57199616171354</v>
       </c>
       <c r="I32" s="4">
         <f t="shared" si="0"/>
-        <v>140.941445327981</v>
+        <v>150.20577361656092</v>
       </c>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
@@ -2310,7 +2316,7 @@
         <v>1.8961819516546079</v>
       </c>
       <c r="G33" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H33" s="4">
         <v>231.85738014859709</v>
@@ -2334,26 +2340,26 @@
         <v>32</v>
       </c>
       <c r="C34" s="4">
-        <v>348.11288652158407</v>
+        <v>346.62433578909861</v>
       </c>
       <c r="D34" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E34" s="4">
-        <v>471.53280514716448</v>
+        <v>468.83148724964826</v>
       </c>
       <c r="F34" s="7">
-        <v>1.8521656410056229</v>
+        <v>1.8443890532471721</v>
       </c>
       <c r="G34" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H34" s="4">
-        <v>229.46157130122151</v>
+        <v>229.07884304388728</v>
       </c>
       <c r="I34" s="4">
         <f t="shared" si="0"/>
-        <v>74.962886521584096</v>
+        <v>73.474335789098632</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.3">
@@ -2394,16 +2400,16 @@
         <v>0.101325</v>
       </c>
       <c r="E36" s="4">
-        <v>454.60719015199737</v>
+        <v>453.10722153513228</v>
       </c>
       <c r="F36" s="7">
-        <v>3.9769142162865401</v>
+        <v>3.9723323134988857</v>
       </c>
       <c r="G36" s="4">
         <v>1.1599999999999999</v>
       </c>
       <c r="H36" s="4">
-        <v>1.4429878527205291</v>
+        <v>1.3091135519945019</v>
       </c>
       <c r="I36" s="4">
         <f t="shared" si="0"/>
@@ -2415,26 +2421,26 @@
         <v>32</v>
       </c>
       <c r="C37" s="4">
-        <v>348.11288652158407</v>
+        <v>346.62433578909861</v>
       </c>
       <c r="D37" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E37" s="4">
-        <v>471.53280514716448</v>
+        <v>468.83148724964826</v>
       </c>
       <c r="F37" s="7">
-        <v>1.8521656410056229</v>
+        <v>1.8443890532471721</v>
       </c>
       <c r="G37" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H37" s="4">
-        <v>229.46157130122151</v>
+        <v>229.07884304388728</v>
       </c>
       <c r="I37" s="4">
         <f t="shared" si="0"/>
-        <v>74.962886521584096</v>
+        <v>73.474335789098632</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.3">
@@ -2442,26 +2448,26 @@
         <v>33</v>
       </c>
       <c r="C38" s="4">
-        <v>345.58184628905991</v>
+        <v>344.39458549639238</v>
       </c>
       <c r="D38" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E38" s="4">
-        <v>466.90431100010727</v>
+        <v>464.67130036926602</v>
       </c>
       <c r="F38" s="7">
-        <v>1.8388208125565038</v>
+        <v>1.8323480555267959</v>
       </c>
       <c r="G38" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H38" s="4">
-        <v>228.81183775626909</v>
+        <v>228.50867963383527</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" si="0"/>
-        <v>72.431846289059933</v>
+        <v>71.244585496392403</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.3">
@@ -2469,26 +2475,26 @@
         <v>33</v>
       </c>
       <c r="C39" s="4">
-        <v>345.58184628905991</v>
+        <v>344.39458549639238</v>
       </c>
       <c r="D39" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E39" s="4">
-        <v>466.90431099381976</v>
+        <v>464.67130036356895</v>
       </c>
       <c r="F39" s="7">
-        <v>1.8388208125565038</v>
+        <v>1.8323480555267959</v>
       </c>
       <c r="G39" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H39" s="4">
-        <v>228.81183774998161</v>
+        <v>228.5086796281382</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" si="0"/>
-        <v>72.431846289059933</v>
+        <v>71.244585496392403</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.3">
@@ -2508,7 +2514,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G40" s="4">
-        <v>7.5615343776216211</v>
+        <v>7.9944855772860111</v>
       </c>
       <c r="H40" s="4">
         <v>224.34458467728319</v>
@@ -2535,7 +2541,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G41" s="4">
-        <v>2.3446171377681925E-3</v>
+        <v>2.8698525619149113E-3</v>
       </c>
       <c r="H41" s="4">
         <v>2.5073905791015251E-5</v>
@@ -2550,26 +2556,26 @@
         <v>20</v>
       </c>
       <c r="C42" s="4">
-        <v>344.58184628905991</v>
+        <v>343.39458549639238</v>
       </c>
       <c r="D42" s="5">
         <v>101.325</v>
       </c>
       <c r="E42" s="4">
-        <v>299.12268215996386</v>
+        <v>294.14738747128831</v>
       </c>
       <c r="F42" s="7">
-        <v>0.97253971167408337</v>
+        <v>0.95807613660276081</v>
       </c>
       <c r="G42" s="4">
-        <v>2.3446171377681925E-3</v>
+        <v>2.8698525619149113E-3</v>
       </c>
       <c r="H42" s="4">
-        <v>13.720445682139834</v>
+        <v>13.057465900979093</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="0"/>
-        <v>71.431846289059933</v>
+        <v>70.244585496392403</v>
       </c>
     </row>
   </sheetData>
@@ -3786,12 +3792,14 @@
         <v>0.28670070585885776</v>
       </c>
       <c r="F29" s="21">
-        <v>1.2022886783692854E-2</v>
+        <v>1.4007219538951258E-2</v>
       </c>
       <c r="G29">
-        <v>5.0653940370668825E-3</v>
-      </c>
-      <c r="H29"/>
+        <v>0.12170799846495922</v>
+      </c>
+      <c r="H29">
+        <v>22.285012708851948</v>
+      </c>
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
     </row>
@@ -3809,12 +3817,14 @@
         <v>0.30067005258822227</v>
       </c>
       <c r="F30" s="21">
-        <v>1.1913802929697966E-2</v>
+        <v>1.3848264588861221E-2</v>
       </c>
       <c r="G30">
-        <v>5.0653940370668817E-3</v>
-      </c>
-      <c r="H30"/>
+        <v>0.1173518380577417</v>
+      </c>
+      <c r="H30">
+        <v>23.11953495485881</v>
+      </c>
       <c r="I30" s="26"/>
       <c r="J30" s="26"/>
     </row>
@@ -3832,12 +3842,14 @@
         <v>0.30977819265992745</v>
       </c>
       <c r="F31" s="21">
-        <v>1.1830214503815288E-2</v>
+        <v>1.3725498879163738E-2</v>
       </c>
       <c r="G31">
-        <v>5.0653940370668825E-3</v>
-      </c>
-      <c r="H31"/>
+        <v>0.11398744378348222</v>
+      </c>
+      <c r="H31">
+        <v>23.654019155799176</v>
+      </c>
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
     </row>
@@ -3855,12 +3867,14 @@
         <v>0.31422916243513799</v>
       </c>
       <c r="F32" s="21">
-        <v>1.1767698260098285E-2</v>
+        <v>1.3635956101139515E-2</v>
       </c>
       <c r="G32">
-        <v>5.0653940370668808E-3</v>
-      </c>
-      <c r="H32"/>
+        <v>0.11153352395172841</v>
+      </c>
+      <c r="H32">
+        <v>23.912447460853958</v>
+      </c>
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
     </row>
@@ -3878,12 +3892,14 @@
         <v>0.31416773033409162</v>
       </c>
       <c r="F33" s="21">
-        <v>1.1715674035762768E-2</v>
+        <v>1.3559849083433204E-2</v>
       </c>
       <c r="G33">
-        <v>5.0653940370668808E-3</v>
-      </c>
-      <c r="H33"/>
+        <v>0.10944781113148691</v>
+      </c>
+      <c r="H33">
+        <v>23.908753202037392</v>
+      </c>
       <c r="I33" s="26"/>
       <c r="J33" s="26"/>
     </row>
@@ -3901,12 +3917,14 @@
         <v>0.30971185580038957</v>
       </c>
       <c r="F34" s="21">
-        <v>1.1674561793569536E-2</v>
+        <v>1.3500952893573077E-2</v>
       </c>
       <c r="G34">
-        <v>5.0653940370668825E-3</v>
-      </c>
-      <c r="H34"/>
+        <v>0.10783376104837018</v>
+      </c>
+      <c r="H34">
+        <v>23.649736075630877</v>
+      </c>
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
     </row>
@@ -3924,12 +3942,14 @@
         <v>0.30097622782447353</v>
       </c>
       <c r="F35" s="21">
-        <v>1.163821212092399E-2</v>
+        <v>1.3447065884090755E-2</v>
       </c>
       <c r="G35">
-        <v>5.0653940370668817E-3</v>
-      </c>
-      <c r="H35"/>
+        <v>0.10635698755350709</v>
+      </c>
+      <c r="H35">
+        <v>23.136921933126388</v>
+      </c>
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
     </row>

--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE12C29-6477-450E-8E2B-B159E2797215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D98ABF-8DCE-4C1D-BF6A-695997D41D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Energy_Exergy" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="130">
   <si>
     <t>T [°C]</t>
   </si>
@@ -406,13 +406,25 @@
     <t>XD PEM [kW]</t>
   </si>
   <si>
-    <t>Y PEM R</t>
-  </si>
-  <si>
     <t>Y.PEM</t>
   </si>
   <si>
     <t>Y total [kgCO2-eq/kWh]</t>
+  </si>
+  <si>
+    <t>n_ex2 [%]</t>
+  </si>
+  <si>
+    <t>Y PEM [kgCO2-eq/kgH2]</t>
+  </si>
+  <si>
+    <t>Yom PEM</t>
+  </si>
+  <si>
+    <t>Yco PEM</t>
+  </si>
+  <si>
+    <t>Yde PEM</t>
   </si>
 </sst>
 </file>
@@ -524,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -572,16 +584,19 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -610,8 +625,8 @@
       <xdr:rowOff>27709</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>80850</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>518172</xdr:colOff>
       <xdr:row>57</xdr:row>
       <xdr:rowOff>102952</xdr:rowOff>
     </xdr:to>
@@ -955,7 +970,9 @@
     <col min="13" max="13" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="24.109375" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.6640625" customWidth="1"/>
+    <col min="20" max="20" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.3">
@@ -1082,7 +1099,7 @@
       <c r="Q4" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="6">
         <v>916.98727526679568</v>
       </c>
     </row>
@@ -1127,7 +1144,7 @@
       <c r="Q5" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="6">
         <v>830.65281683265493</v>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       <c r="Q6" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="6">
         <v>6850.0253590880538</v>
       </c>
     </row>
@@ -1217,7 +1234,7 @@
       <c r="Q7" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="6">
         <v>2723.6906468307247</v>
       </c>
     </row>
@@ -1262,7 +1279,7 @@
       <c r="Q8" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="6">
         <v>150.85917384920415</v>
       </c>
     </row>
@@ -1304,10 +1321,10 @@
       <c r="O9" s="10">
         <v>-5.8779815586019524E-2</v>
       </c>
-      <c r="Q9" s="23" t="s">
+      <c r="Q9" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="R9" s="24">
+      <c r="R9" s="31">
         <v>4757.3674529323171</v>
       </c>
     </row>
@@ -1352,7 +1369,7 @@
       <c r="Q10" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="6">
         <v>58326.910191272655</v>
       </c>
     </row>
@@ -1397,7 +1414,7 @@
       <c r="Q11" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="6">
         <v>101653.79754728591</v>
       </c>
     </row>
@@ -1442,7 +1459,7 @@
       <c r="Q12" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="6">
         <v>6084.4865460826932</v>
       </c>
     </row>
@@ -1481,7 +1498,7 @@
       <c r="Q13" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="6">
         <v>-14690.262623456645</v>
       </c>
     </row>
@@ -1524,7 +1541,7 @@
       <c r="Q14" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="6">
         <v>-7175.4747263768222</v>
       </c>
     </row>
@@ -1569,7 +1586,7 @@
       <c r="Q15" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="6">
         <v>-2.2347027849124075</v>
       </c>
     </row>
@@ -1614,7 +1631,7 @@
       <c r="Q16" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="6">
         <v>14936.432649657721</v>
       </c>
     </row>
@@ -1659,7 +1676,7 @@
       <c r="Q17" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="6">
         <v>12158.725147647143</v>
       </c>
     </row>
@@ -1698,8 +1715,8 @@
       <c r="Q18" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="R18">
-        <v>1765185.6442090091</v>
+      <c r="R18" s="6">
+        <v>2143439.7108252258</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
@@ -1739,10 +1756,10 @@
         <v>55.339933569630354</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="R19">
-        <v>54097.709945397604</v>
+        <v>123</v>
+      </c>
+      <c r="R19" s="6">
+        <v>2503125.0768078174</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
@@ -1787,6 +1804,10 @@
         <v>117</v>
       </c>
       <c r="R20" s="28"/>
+      <c r="S20" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T20" s="28"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
@@ -1832,6 +1853,12 @@
       <c r="R21" s="22" t="s">
         <v>41</v>
       </c>
+      <c r="S21" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="T21" s="22" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
@@ -1875,10 +1902,13 @@
         <v>113</v>
       </c>
       <c r="R22" s="24">
-        <v>189927.66233550836</v>
-      </c>
-      <c r="T22" s="25">
-        <v>141781.626188147</v>
+        <v>2505530.7763891984</v>
+      </c>
+      <c r="S22" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="T22" s="29">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.3">
@@ -1923,9 +1953,12 @@
         <v>114</v>
       </c>
       <c r="R23" s="24">
-        <v>2003923.2325693402</v>
-      </c>
-      <c r="T23" s="25">
+        <v>4269212.9393934794</v>
+      </c>
+      <c r="S23" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="T23" s="29">
         <v>0</v>
       </c>
     </row>
@@ -1971,13 +2004,14 @@
         <v>115</v>
       </c>
       <c r="R24" s="24">
-        <v>88160.301000562598</v>
-      </c>
-      <c r="S24" s="9"/>
-      <c r="T24" s="25">
-        <v>187521.96275412751</v>
-      </c>
-      <c r="U24" s="9"/>
+        <v>202782.7454297191</v>
+      </c>
+      <c r="S24" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="T24" s="29">
+        <v>2503125.0768078174</v>
+      </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
       <c r="X24" s="9"/>
@@ -2018,8 +2052,7 @@
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
+      <c r="T25" s="26"/>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
       <c r="X25" s="9"/>
@@ -2059,7 +2092,6 @@
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
       <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -2579,7 +2611,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="S20:T20"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="K19:L19"/>
@@ -2604,7 +2637,7 @@
     <col min="3" max="4" width="18.6640625" style="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.44140625" style="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.5546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.88671875" style="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.77734375" style="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" style="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.44140625" style="17" bestFit="1" customWidth="1"/>
@@ -3771,12 +3804,14 @@
         <v>121</v>
       </c>
       <c r="F28" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="G28" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="H28" s="21"/>
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B29" s="17">
@@ -3792,16 +3827,16 @@
         <v>0.28670070585885776</v>
       </c>
       <c r="F29" s="21">
-        <v>1.4007219538951258E-2</v>
+        <v>1.1542250716925242E-2</v>
       </c>
       <c r="G29">
-        <v>0.12170799846495922</v>
+        <v>0.67842275179467249</v>
       </c>
       <c r="H29">
         <v>22.285012708851948</v>
       </c>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B30" s="17">
@@ -3817,16 +3852,16 @@
         <v>0.30067005258822227</v>
       </c>
       <c r="F30" s="21">
-        <v>1.3848264588861221E-2</v>
+        <v>1.147679867865287E-2</v>
       </c>
       <c r="G30">
-        <v>0.1173518380577417</v>
+        <v>0.6748353255769638</v>
       </c>
       <c r="H30">
         <v>23.11953495485881</v>
       </c>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
     </row>
     <row r="31" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B31" s="17">
@@ -3842,16 +3877,16 @@
         <v>0.30977819265992745</v>
       </c>
       <c r="F31" s="21">
-        <v>1.3725498879163738E-2</v>
+        <v>1.1426248092306848E-2</v>
       </c>
       <c r="G31">
-        <v>0.11398744378348222</v>
+        <v>0.6720646479393384</v>
       </c>
       <c r="H31">
         <v>23.654019155799176</v>
       </c>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B32" s="17">
@@ -3867,16 +3902,16 @@
         <v>0.31422916243513799</v>
       </c>
       <c r="F32" s="21">
-        <v>1.3635956101139515E-2</v>
+        <v>1.1389377536649816E-2</v>
       </c>
       <c r="G32">
-        <v>0.11153352395172841</v>
+        <v>0.67004377278377647</v>
       </c>
       <c r="H32">
         <v>23.912447460853958</v>
       </c>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="17">
@@ -3892,16 +3927,16 @@
         <v>0.31416773033409162</v>
       </c>
       <c r="F33" s="21">
-        <v>1.3559849083433204E-2</v>
+        <v>1.1358039352888392E-2</v>
       </c>
       <c r="G33">
-        <v>0.10944781113148691</v>
+        <v>0.66832612693181281</v>
       </c>
       <c r="H33">
         <v>23.908753202037392</v>
       </c>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="17">
@@ -3917,16 +3952,16 @@
         <v>0.30971185580038957</v>
       </c>
       <c r="F34" s="21">
-        <v>1.3500952893573077E-2</v>
+        <v>1.1333787980593049E-2</v>
       </c>
       <c r="G34">
-        <v>0.10783376104837018</v>
+        <v>0.66699690921630506</v>
       </c>
       <c r="H34">
         <v>23.649736075630877</v>
       </c>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="17">
@@ -3942,16 +3977,16 @@
         <v>0.30097622782447353</v>
       </c>
       <c r="F35" s="21">
-        <v>1.3447065884090755E-2</v>
+        <v>1.131159921198268E-2</v>
       </c>
       <c r="G35">
-        <v>0.10635698755350709</v>
+        <v>0.66578074280877075</v>
       </c>
       <c r="H35">
         <v>23.136921933126388</v>
       </c>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F36" s="21"/>
@@ -3965,7 +4000,7 @@
       <c r="E37" s="20"/>
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
-      <c r="H37" s="21"/>
+      <c r="H37" s="20"/>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H38" s="21"/>

--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D98ABF-8DCE-4C1D-BF6A-695997D41D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696BD113-F08B-433B-BCFC-F1438E51495D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" activeTab="2" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Energy_Exergy" sheetId="2" r:id="rId1"/>
-    <sheet name="T" sheetId="3" r:id="rId2"/>
+    <sheet name="T" sheetId="3" r:id="rId1"/>
+    <sheet name="Energy_Exergy" sheetId="2" r:id="rId2"/>
+    <sheet name="EXERGO" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="202">
   <si>
     <t>T [°C]</t>
   </si>
@@ -425,6 +426,222 @@
   </si>
   <si>
     <t>Yde PEM</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5 </t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C6AI</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>CWT1</t>
+  </si>
+  <si>
+    <t>CNETO</t>
+  </si>
+  <si>
+    <t>CWT2</t>
+  </si>
+  <si>
+    <t>CWC1</t>
+  </si>
+  <si>
+    <t>CWC2</t>
+  </si>
+  <si>
+    <t>CH2</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>CWT3</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>"-ZT1"</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>"-ZT2"</t>
+  </si>
+  <si>
+    <t>"-ZC1"</t>
+  </si>
+  <si>
+    <t>"-ZC2"</t>
+  </si>
+  <si>
+    <t>"-ZHTR"</t>
+  </si>
+  <si>
+    <t>"-ZLTR"</t>
+  </si>
+  <si>
+    <t>COOLER</t>
+  </si>
+  <si>
+    <t>"-ZCOOLER"</t>
+  </si>
+  <si>
+    <t>"-ZHE"</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>"-ZT3"</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>"-ZB2"</t>
+  </si>
+  <si>
+    <t>COND</t>
+  </si>
+  <si>
+    <t>"-ZCOND"</t>
+  </si>
+  <si>
+    <t>EVAP</t>
+  </si>
+  <si>
+    <t>"-ZEVAP"</t>
+  </si>
+  <si>
+    <t>PEM</t>
+  </si>
+  <si>
+    <t>"-ZPEM"</t>
+  </si>
+  <si>
+    <t>AUX</t>
+  </si>
+  <si>
+    <t>AUX T1</t>
+  </si>
+  <si>
+    <t>E1/E2</t>
+  </si>
+  <si>
+    <t>E3/E4</t>
+  </si>
+  <si>
+    <t>AUX HTR</t>
+  </si>
+  <si>
+    <t>AUX LTR</t>
+  </si>
+  <si>
+    <t>E4/E5</t>
+  </si>
+  <si>
+    <t>E5/E6</t>
+  </si>
+  <si>
+    <t>AUX LTR 2</t>
+  </si>
+  <si>
+    <t>AUX HE</t>
+  </si>
+  <si>
+    <t>E6AO/E7</t>
+  </si>
+  <si>
+    <t>AUX T3</t>
+  </si>
+  <si>
+    <t>AUX T2</t>
+  </si>
+  <si>
+    <t>E15/E16</t>
+  </si>
+  <si>
+    <t>AUX B2</t>
+  </si>
+  <si>
+    <t>WB2</t>
+  </si>
+  <si>
+    <t>WB2/WT3</t>
+  </si>
+  <si>
+    <t>AUX EVAP</t>
+  </si>
+  <si>
+    <t>C6BI</t>
+  </si>
+  <si>
+    <t>C6AO</t>
+  </si>
+  <si>
+    <t>C6AO3</t>
+  </si>
+  <si>
+    <t>E6AI/E6AO3</t>
+  </si>
+  <si>
+    <t>30 incognitas</t>
+  </si>
+  <si>
+    <t>AUX COOLER</t>
+  </si>
+  <si>
+    <t>E6AO3/E6AO</t>
+  </si>
+  <si>
+    <t>E16/E17</t>
+  </si>
+  <si>
+    <t>24 ecuaciones</t>
   </si>
 </sst>
 </file>
@@ -536,7 +753,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -588,15 +805,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -651,8 +866,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7855527" y="5444836"/>
-          <a:ext cx="10325995" cy="4938188"/>
+          <a:off x="7904319" y="5593622"/>
+          <a:ext cx="10358514" cy="5084565"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -960,1674 +1175,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E91C93-8228-4E85-B9E3-FB80BE715EB6}">
-  <dimension ref="B2:Y42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="4" max="4" width="11.5546875" style="2"/>
-    <col min="11" max="11" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.109375" customWidth="1"/>
-    <col min="18" max="18" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.6640625" customWidth="1"/>
-    <col min="20" max="20" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="L2" s="28"/>
-      <c r="N2" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="O2" s="28"/>
-      <c r="Q2" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="R2" s="28"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1073.1500000000001</v>
-      </c>
-      <c r="D3" s="5">
-        <v>25</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1350.0381316636626</v>
-      </c>
-      <c r="F3" s="7">
-        <v>3.0305681085599816</v>
-      </c>
-      <c r="G3" s="4">
-        <v>10</v>
-      </c>
-      <c r="H3" s="4">
-        <v>756.61237274082237</v>
-      </c>
-      <c r="I3" s="4">
-        <f>C3-273.15</f>
-        <v>800.00000000000011</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q3" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" s="22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1018.1289616795918</v>
-      </c>
-      <c r="D4" s="5">
-        <v>17.482517482517483</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1281.2341664776559</v>
-      </c>
-      <c r="F4" s="7">
-        <v>3.035664888414034</v>
-      </c>
-      <c r="G4" s="4">
-        <v>10</v>
-      </c>
-      <c r="H4" s="4">
-        <v>686.28880264133011</v>
-      </c>
-      <c r="I4" s="4">
-        <f t="shared" ref="I4:I42" si="0">C4-273.15</f>
-        <v>744.97896167959186</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" s="7">
-        <v>1.7979758880009502</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O4" s="10">
-        <v>688.03965186006621</v>
-      </c>
-      <c r="Q4" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="R4" s="6">
-        <v>916.98727526679568</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
-        <v>3</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1073.1500000000001</v>
-      </c>
-      <c r="D5" s="5">
-        <v>17.482517482517483</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1351.4823193165744</v>
-      </c>
-      <c r="F5" s="7">
-        <v>3.1028601038812176</v>
-      </c>
-      <c r="G5" s="4">
-        <v>10</v>
-      </c>
-      <c r="H5" s="4">
-        <v>736.50270198870771</v>
-      </c>
-      <c r="I5" s="4">
-        <f t="shared" si="0"/>
-        <v>800.00000000000011</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0.70248152838918376</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="O5" s="10">
-        <v>1199.1350689643341</v>
-      </c>
-      <c r="Q5" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="R5" s="6">
-        <v>830.65281683265493</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B6" s="3">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4">
-        <v>976.11427576830124</v>
-      </c>
-      <c r="D6" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1231.5688124201411</v>
-      </c>
-      <c r="F6" s="7">
-        <v>3.1121411727413726</v>
-      </c>
-      <c r="G6" s="4">
-        <v>10</v>
-      </c>
-      <c r="H6" s="4">
-        <v>613.82204441161923</v>
-      </c>
-      <c r="I6" s="4">
-        <f t="shared" si="0"/>
-        <v>702.96427576830126</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="7">
-        <v>2.5004574163901339</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O6" s="10">
-        <v>71.774211786387255</v>
-      </c>
-      <c r="Q6" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="R6" s="6">
-        <v>6850.0253590880538</v>
-      </c>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B7" s="3">
-        <v>5</v>
-      </c>
-      <c r="C7" s="4">
-        <v>580.59332858273865</v>
-      </c>
-      <c r="D7" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E7" s="4">
-        <v>758.75704305028523</v>
-      </c>
-      <c r="F7" s="7">
-        <v>2.4934653765384365</v>
-      </c>
-      <c r="G7" s="4">
-        <v>10</v>
-      </c>
-      <c r="H7" s="4">
-        <v>325.46846367966873</v>
-      </c>
-      <c r="I7" s="4">
-        <f t="shared" si="0"/>
-        <v>307.44332858273867</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="7">
-        <v>4.8493514799902702</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O7" s="10">
-        <v>-386.40079286911646</v>
-      </c>
-      <c r="Q7" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="R7" s="6">
-        <v>2723.6906468307247</v>
-      </c>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B8" s="3">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4">
-        <v>435.43287838933054</v>
-      </c>
-      <c r="D8" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E8" s="4">
-        <v>591.19593244306282</v>
-      </c>
-      <c r="F8" s="7">
-        <v>2.1610419768753544</v>
-      </c>
-      <c r="G8" s="4">
-        <v>10</v>
-      </c>
-      <c r="H8" s="4">
-        <v>257.0193896819942</v>
-      </c>
-      <c r="I8" s="4">
-        <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="7">
-        <v>1.6756111060722243</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="O8" s="10">
-        <v>-188.73788675888972</v>
-      </c>
-      <c r="Q8" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="R8" s="6">
-        <v>150.85917384920415</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="4">
-        <v>435.43287838933054</v>
-      </c>
-      <c r="D9" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E9" s="4">
-        <v>591.19593244306282</v>
-      </c>
-      <c r="F9" s="7">
-        <v>2.1610419768753544</v>
-      </c>
-      <c r="G9" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H9" s="4">
-        <v>257.0193896819942</v>
-      </c>
-      <c r="I9" s="4">
-        <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="7">
-        <v>0.11033034486553291</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O9" s="10">
-        <v>-5.8779815586019524E-2</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="R9" s="31">
-        <v>4757.3674529323171</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="4">
-        <v>423.3557736165609</v>
-      </c>
-      <c r="D10" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0.57659650223683723</v>
-      </c>
-      <c r="F10" s="7">
-        <v>2.1270382629381421E-3</v>
-      </c>
-      <c r="G10" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0.25257199616171355</v>
-      </c>
-      <c r="I10" s="4">
-        <f t="shared" si="0"/>
-        <v>150.20577361656092</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" s="7">
-        <v>0.68666556854253946</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="O10" s="10">
-        <v>1312.0360411963943</v>
-      </c>
-      <c r="Q10" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="R10" s="6">
-        <v>58326.910191272655</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="4">
-        <v>357.24648058947918</v>
-      </c>
-      <c r="D11" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0.48705207701453501</v>
-      </c>
-      <c r="F11" s="7">
-        <v>1.8961819516546078E-3</v>
-      </c>
-      <c r="G11" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0.23185738014859708</v>
-      </c>
-      <c r="I11" s="4">
-        <f t="shared" si="0"/>
-        <v>84.096480589479199</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11" s="7">
-        <v>0.12544275752191905</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="O11" s="10">
-        <v>71.715431970801234</v>
-      </c>
-      <c r="Q11" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="R11" s="6">
-        <v>101653.79754728591</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="4">
-        <v>346.62433578909861</v>
-      </c>
-      <c r="D12" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0.46883148724964824</v>
-      </c>
-      <c r="F12" s="7">
-        <v>1.844389053247172E-3</v>
-      </c>
-      <c r="G12" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0.22907884304388729</v>
-      </c>
-      <c r="I12" s="4">
-        <f t="shared" si="0"/>
-        <v>73.474335789098632</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="L12" s="7">
-        <v>0.92243867092999143</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="O12" s="12">
-        <v>1383.7514731671954</v>
-      </c>
-      <c r="Q12" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="R12" s="6">
-        <v>6084.4865460826932</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="4">
-        <v>344.39458549639238</v>
-      </c>
-      <c r="D13" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E13" s="4">
-        <v>464.67130036926602</v>
-      </c>
-      <c r="F13" s="7">
-        <v>1.8323480555267959</v>
-      </c>
-      <c r="G13" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H13" s="4">
-        <v>228.50867963383527</v>
-      </c>
-      <c r="I13" s="4">
-        <f t="shared" si="0"/>
-        <v>71.244585496392403</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="L13" s="7">
-        <v>0.72305037797389082</v>
-      </c>
-      <c r="Q13" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="R13" s="6">
-        <v>-14690.262623456645</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="4">
-        <v>435.43287838933054</v>
-      </c>
-      <c r="D14" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E14" s="4">
-        <v>591.19593244306282</v>
-      </c>
-      <c r="F14" s="7">
-        <v>2.1610419768753544</v>
-      </c>
-      <c r="G14" s="4">
-        <v>2.0055144227139889</v>
-      </c>
-      <c r="H14" s="4">
-        <v>257.0193896819942</v>
-      </c>
-      <c r="I14" s="4">
-        <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="L14" s="7">
-        <v>0.12767286098529926</v>
-      </c>
-      <c r="N14" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="O14" s="27"/>
-      <c r="Q14" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="R14" s="6">
-        <v>-7175.4747263768222</v>
-      </c>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="3">
-        <v>7</v>
-      </c>
-      <c r="C15" s="4">
-        <v>328.15</v>
-      </c>
-      <c r="D15" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E15" s="4">
-        <v>427.37611738856413</v>
-      </c>
-      <c r="F15" s="7">
-        <v>1.72122584179495</v>
-      </c>
-      <c r="G15" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H15" s="4">
-        <v>224.33075530171814</v>
-      </c>
-      <c r="I15" s="4">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" s="7">
-        <v>0.85072323895919011</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="O15" s="10">
-        <v>7.7745474285568061</v>
-      </c>
-      <c r="Q15" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="R15" s="6">
-        <v>-2.2347027849124075</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="3">
-        <v>8</v>
-      </c>
-      <c r="C16" s="4">
-        <v>407.92598052767181</v>
-      </c>
-      <c r="D16" s="5">
-        <v>25</v>
-      </c>
-      <c r="E16" s="4">
-        <v>475.70953285771714</v>
-      </c>
-      <c r="F16" s="7">
-        <v>1.7343043486568708</v>
-      </c>
-      <c r="G16" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H16" s="4">
-        <v>268.76481394998945</v>
-      </c>
-      <c r="I16" s="4">
-        <f t="shared" si="0"/>
-        <v>134.77598052767183</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" s="7">
-        <v>3.3258554014030113E-2</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="O16" s="10">
-        <v>52.471841055808</v>
-      </c>
-      <c r="Q16" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="R16" s="6">
-        <v>14936.432649657721</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B17" s="3">
-        <v>9</v>
-      </c>
-      <c r="C17" s="4">
-        <v>547.68745921507718</v>
-      </c>
-      <c r="D17" s="5">
-        <v>25</v>
-      </c>
-      <c r="E17" s="4">
-        <v>685.30539614040072</v>
-      </c>
-      <c r="F17" s="7">
-        <v>2.1800807088725671</v>
-      </c>
-      <c r="G17" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H17" s="4">
-        <v>345.45245543436323</v>
-      </c>
-      <c r="I17" s="4">
-        <f t="shared" si="0"/>
-        <v>274.53745921507721</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17" s="16">
-        <v>-0.29815580239591893</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="O17" s="10">
-        <v>53.374586045417935</v>
-      </c>
-      <c r="Q17" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="R17" s="6">
-        <v>12158.725147647143</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="3">
-        <v>10</v>
-      </c>
-      <c r="C18" s="4">
-        <v>547.68745921507718</v>
-      </c>
-      <c r="D18" s="5">
-        <v>25</v>
-      </c>
-      <c r="E18" s="4">
-        <v>685.30539614040072</v>
-      </c>
-      <c r="F18" s="7">
-        <v>2.1800807088725671</v>
-      </c>
-      <c r="G18" s="4">
-        <v>2.0055144227139889</v>
-      </c>
-      <c r="H18" s="4">
-        <v>345.45245543436323</v>
-      </c>
-      <c r="I18" s="4">
-        <f t="shared" si="0"/>
-        <v>274.53745921507721</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="O18" s="10">
-        <v>54.014275766007323</v>
-      </c>
-      <c r="Q18" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="R18" s="6">
-        <v>2143439.7108252258</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B19" s="3">
-        <v>11</v>
-      </c>
-      <c r="C19" s="4">
-        <v>547.68745921507718</v>
-      </c>
-      <c r="D19" s="5">
-        <v>25</v>
-      </c>
-      <c r="E19" s="4">
-        <v>685.30539614040072</v>
-      </c>
-      <c r="F19" s="7">
-        <v>2.1800807088725671</v>
-      </c>
-      <c r="G19" s="4">
-        <v>10</v>
-      </c>
-      <c r="H19" s="4">
-        <v>345.45245543436323</v>
-      </c>
-      <c r="I19" s="4">
-        <f t="shared" si="0"/>
-        <v>274.53745921507721</v>
-      </c>
-      <c r="K19" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="L19" s="27"/>
-      <c r="N19" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="O19" s="10">
-        <v>55.339933569630354</v>
-      </c>
-      <c r="Q19" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="R19" s="6">
-        <v>2503125.0768078174</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B20" s="3">
-        <v>12</v>
-      </c>
-      <c r="C20" s="4">
-        <v>932.83907702081467</v>
-      </c>
-      <c r="D20" s="5">
-        <v>25</v>
-      </c>
-      <c r="E20" s="4">
-        <v>1170.2405428635675</v>
-      </c>
-      <c r="F20" s="7">
-        <v>2.8510501836319815</v>
-      </c>
-      <c r="G20" s="4">
-        <v>10</v>
-      </c>
-      <c r="H20" s="4">
-        <v>630.33805325801075</v>
-      </c>
-      <c r="I20" s="4">
-        <f t="shared" si="0"/>
-        <v>659.68907702081469</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="L20" s="4">
-        <v>159.02185344711796</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="O20" s="10">
-        <v>3.4933609588634824</v>
-      </c>
-      <c r="Q20" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="T20" s="28"/>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B21" s="3">
-        <v>17</v>
-      </c>
-      <c r="C21" s="4">
-        <v>313.14999999999998</v>
-      </c>
-      <c r="D21" s="5">
-        <v>7.8923107438086744</v>
-      </c>
-      <c r="E21" s="4">
-        <v>-132.35463919610541</v>
-      </c>
-      <c r="F21" s="7">
-        <v>-0.37994748587359245</v>
-      </c>
-      <c r="G21" s="4">
-        <v>1.7897056695309543</v>
-      </c>
-      <c r="H21" s="4">
-        <v>0.52460446529691762</v>
-      </c>
-      <c r="I21" s="4">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="L21" s="4">
-        <v>63.229887799023224</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="O21" s="10">
-        <v>22.489305649899514</v>
-      </c>
-      <c r="Q21" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="R21" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="S21" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="T21" s="22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B22" s="3">
-        <v>18</v>
-      </c>
-      <c r="C22" s="4">
-        <v>313.1583575108412</v>
-      </c>
-      <c r="D22" s="5">
-        <v>31.569242975234697</v>
-      </c>
-      <c r="E22" s="4">
-        <v>-132.32179590986752</v>
-      </c>
-      <c r="F22" s="7">
-        <v>-0.37994748587359245</v>
-      </c>
-      <c r="G22" s="4">
-        <v>1.7897056695309543</v>
-      </c>
-      <c r="H22" s="4">
-        <v>0.55744775153482984</v>
-      </c>
-      <c r="I22" s="4">
-        <f t="shared" si="0"/>
-        <v>40.008357510841222</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="L22" s="4">
-        <v>21.287660768567079</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O22" s="6">
-        <v>52.415130655682205</v>
-      </c>
-      <c r="Q22" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="R22" s="24">
-        <v>2505530.7763891984</v>
-      </c>
-      <c r="S22" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="T22" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="4">
-        <v>347.24648058947918</v>
-      </c>
-      <c r="D23" s="5">
-        <v>31.569242975234697</v>
-      </c>
-      <c r="E23" s="4">
-        <v>-70.674595063457787</v>
-      </c>
-      <c r="F23" s="7">
-        <v>-0.19317568283781225</v>
-      </c>
-      <c r="G23" s="4">
-        <v>1.7897056695309543</v>
-      </c>
-      <c r="H23" s="4">
-        <v>6.518635522826691</v>
-      </c>
-      <c r="I23" s="4">
-        <f t="shared" si="0"/>
-        <v>74.096480589479199</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L23" s="4">
-        <v>19.283425035580251</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="O23" s="6">
-        <v>23.133959295545651</v>
-      </c>
-      <c r="Q23" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="R23" s="24">
-        <v>4269212.9393934794</v>
-      </c>
-      <c r="S23" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="T23" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="4">
-        <v>347.24648058947918</v>
-      </c>
-      <c r="D24" s="5">
-        <v>31.569242975234697</v>
-      </c>
-      <c r="E24" s="4">
-        <v>313.00054226931974</v>
-      </c>
-      <c r="F24" s="7">
-        <v>0.91173151933586583</v>
-      </c>
-      <c r="G24" s="4">
-        <v>1.7897056695309543</v>
-      </c>
-      <c r="H24" s="4">
-        <v>60.765690527522125</v>
-      </c>
-      <c r="I24" s="4">
-        <f t="shared" si="0"/>
-        <v>74.096480589479199</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="L24" s="4">
-        <v>3.5021630107067545</v>
-      </c>
-      <c r="N24" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="O24" s="15">
-        <v>23.136921933126388</v>
-      </c>
-      <c r="Q24" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="R24" s="24">
-        <v>202782.7454297191</v>
-      </c>
-      <c r="S24" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="T24" s="29">
-        <v>2503125.0768078174</v>
-      </c>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="9"/>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B25" s="3">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>396.43287838933054</v>
-      </c>
-      <c r="D25" s="5">
-        <v>31.569242975234697</v>
-      </c>
-      <c r="E25" s="4">
-        <v>383.09182021380718</v>
-      </c>
-      <c r="F25" s="7">
-        <v>1.1002468147744369</v>
-      </c>
-      <c r="G25" s="4">
-        <v>1.7897056695309543</v>
-      </c>
-      <c r="H25" s="4">
-        <v>74.651133136999675</v>
-      </c>
-      <c r="I25" s="4">
-        <f t="shared" si="0"/>
-        <v>123.28287838933056</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="L25" s="4">
-        <v>110.44125389851233</v>
-      </c>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="26"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="9"/>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B26" s="3">
-        <v>16</v>
-      </c>
-      <c r="C26" s="4">
-        <v>368.13790080168786</v>
-      </c>
-      <c r="D26" s="5">
-        <v>7.8923107438086744</v>
-      </c>
-      <c r="E26" s="4">
-        <v>342.98790088879446</v>
-      </c>
-      <c r="F26" s="7">
-        <v>1.119604713516257</v>
-      </c>
-      <c r="G26" s="4">
-        <v>1.7897056695309543</v>
-      </c>
-      <c r="H26" s="4">
-        <v>28.775656302113202</v>
-      </c>
-      <c r="I26" s="4">
-        <f t="shared" si="0"/>
-        <v>94.987900801687886</v>
-      </c>
-      <c r="N26" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="O26" s="27"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="4">
-        <v>313.14999999999998</v>
-      </c>
-      <c r="D27" s="5">
-        <v>7.8923107438086744</v>
-      </c>
-      <c r="E27" s="4">
-        <v>271.65055019539255</v>
-      </c>
-      <c r="F27" s="7">
-        <v>0.91018564327057938</v>
-      </c>
-      <c r="G27" s="4">
-        <v>1.7897056695309543</v>
-      </c>
-      <c r="H27" s="4">
-        <v>19.876601402460075</v>
-      </c>
-      <c r="I27" s="4">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="N27" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="O27" s="6">
-        <v>0.71269346475761464</v>
-      </c>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="4">
-        <v>298.14999999999998</v>
-      </c>
-      <c r="D28" s="5">
-        <v>101.325</v>
-      </c>
-      <c r="E28" s="4">
-        <v>104.92011957080643</v>
-      </c>
-      <c r="F28" s="7">
-        <v>0.36719964130372146</v>
-      </c>
-      <c r="G28" s="4">
-        <v>34.591753259051274</v>
-      </c>
-      <c r="H28" s="4">
-        <v>2.5073905791015251E-5</v>
-      </c>
-      <c r="I28" s="4">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="N28" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="O28" s="6">
-        <v>0.99770990140218263</v>
-      </c>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="4">
-        <v>303.14999999999998</v>
-      </c>
-      <c r="D29" s="5">
-        <v>101.325</v>
-      </c>
-      <c r="E29" s="4">
-        <v>125.82251132178534</v>
-      </c>
-      <c r="F29" s="7">
-        <v>0.43672528196163279</v>
-      </c>
-      <c r="G29" s="4">
-        <v>34.591753259051274</v>
-      </c>
-      <c r="H29" s="4">
-        <v>0.17334706272843686</v>
-      </c>
-      <c r="I29" s="4">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="N29" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="O29" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="9"/>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="4">
-        <v>304.03303316959324</v>
-      </c>
-      <c r="D30" s="5">
-        <v>101.325</v>
-      </c>
-      <c r="E30" s="4">
-        <v>129.51335809758132</v>
-      </c>
-      <c r="F30" s="7">
-        <v>0.44888256955875044</v>
-      </c>
-      <c r="G30" s="4">
-        <v>34.591753259051274</v>
-      </c>
-      <c r="H30" s="4">
-        <v>0.23949854144378332</v>
-      </c>
-      <c r="I30" s="4">
-        <f t="shared" si="0"/>
-        <v>30.883033169593261</v>
-      </c>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B31" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="4">
-        <v>435.43287838933054</v>
-      </c>
-      <c r="D31" s="5">
-        <v>9124.0875912408756</v>
-      </c>
-      <c r="E31" s="4">
-        <v>591.19593244282169</v>
-      </c>
-      <c r="F31" s="7">
-        <v>2.1610419768753544</v>
-      </c>
-      <c r="G31" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H31" s="4">
-        <v>257.03321905731815</v>
-      </c>
-      <c r="I31" s="4">
-        <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
-      </c>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="4">
-        <v>423.3557736165609</v>
-      </c>
-      <c r="D32" s="5">
-        <v>9124.0875912408756</v>
-      </c>
-      <c r="E32" s="4">
-        <v>576.59650223683718</v>
-      </c>
-      <c r="F32" s="7">
-        <v>2.1270382629381421</v>
-      </c>
-      <c r="G32" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H32" s="4">
-        <v>252.57199616171354</v>
-      </c>
-      <c r="I32" s="4">
-        <f t="shared" si="0"/>
-        <v>150.20577361656092</v>
-      </c>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="9"/>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="4">
-        <v>357.24648058947918</v>
-      </c>
-      <c r="D33" s="5">
-        <v>9124.0875912408756</v>
-      </c>
-      <c r="E33" s="4">
-        <v>487.05207701453503</v>
-      </c>
-      <c r="F33" s="7">
-        <v>1.8961819516546079</v>
-      </c>
-      <c r="G33" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H33" s="4">
-        <v>231.85738014859709</v>
-      </c>
-      <c r="I33" s="4">
-        <f t="shared" si="0"/>
-        <v>84.096480589479199</v>
-      </c>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B34" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="4">
-        <v>346.62433578909861</v>
-      </c>
-      <c r="D34" s="5">
-        <v>9124.0875912408756</v>
-      </c>
-      <c r="E34" s="4">
-        <v>468.83148724964826</v>
-      </c>
-      <c r="F34" s="7">
-        <v>1.8443890532471721</v>
-      </c>
-      <c r="G34" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H34" s="4">
-        <v>229.07884304388728</v>
-      </c>
-      <c r="I34" s="4">
-        <f t="shared" si="0"/>
-        <v>73.474335789098632</v>
-      </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B35" s="2">
-        <v>13</v>
-      </c>
-      <c r="C35" s="4">
-        <v>298.14999999999998</v>
-      </c>
-      <c r="D35" s="5">
-        <v>0.101325</v>
-      </c>
-      <c r="E35" s="4">
-        <v>424.43605428165802</v>
-      </c>
-      <c r="F35" s="7">
-        <v>3.8804887263997387</v>
-      </c>
-      <c r="G35" s="4">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="H35" s="4">
-        <v>2.1111792130950945E-2</v>
-      </c>
-      <c r="I35" s="4">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B36" s="2">
-        <v>14</v>
-      </c>
-      <c r="C36" s="4">
-        <v>278.14999999999998</v>
-      </c>
-      <c r="D36" s="5">
-        <v>0.101325</v>
-      </c>
-      <c r="E36" s="4">
-        <v>453.10722153513228</v>
-      </c>
-      <c r="F36" s="7">
-        <v>3.9723323134988857</v>
-      </c>
-      <c r="G36" s="4">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="H36" s="4">
-        <v>1.3091135519945019</v>
-      </c>
-      <c r="I36" s="4">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B37" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="4">
-        <v>346.62433578909861</v>
-      </c>
-      <c r="D37" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E37" s="4">
-        <v>468.83148724964826</v>
-      </c>
-      <c r="F37" s="7">
-        <v>1.8443890532471721</v>
-      </c>
-      <c r="G37" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H37" s="4">
-        <v>229.07884304388728</v>
-      </c>
-      <c r="I37" s="4">
-        <f t="shared" si="0"/>
-        <v>73.474335789098632</v>
-      </c>
-    </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B38" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="4">
-        <v>344.39458549639238</v>
-      </c>
-      <c r="D38" s="5">
-        <v>9.1240875912408761</v>
-      </c>
-      <c r="E38" s="4">
-        <v>464.67130036926602</v>
-      </c>
-      <c r="F38" s="7">
-        <v>1.8323480555267959</v>
-      </c>
-      <c r="G38" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H38" s="4">
-        <v>228.50867963383527</v>
-      </c>
-      <c r="I38" s="4">
-        <f t="shared" si="0"/>
-        <v>71.244585496392403</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B39" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="4">
-        <v>344.39458549639238</v>
-      </c>
-      <c r="D39" s="5">
-        <v>9124.0875912408756</v>
-      </c>
-      <c r="E39" s="4">
-        <v>464.67130036356895</v>
-      </c>
-      <c r="F39" s="7">
-        <v>1.8323480555267959</v>
-      </c>
-      <c r="G39" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H39" s="4">
-        <v>228.5086796281382</v>
-      </c>
-      <c r="I39" s="4">
-        <f t="shared" si="0"/>
-        <v>71.244585496392403</v>
-      </c>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B40" s="2">
-        <v>7</v>
-      </c>
-      <c r="C40" s="4">
-        <v>328.15</v>
-      </c>
-      <c r="D40" s="5">
-        <v>9124.0875912408756</v>
-      </c>
-      <c r="E40" s="4">
-        <v>427.37611738856413</v>
-      </c>
-      <c r="F40" s="7">
-        <v>1.72122584179495</v>
-      </c>
-      <c r="G40" s="4">
-        <v>7.9944855772860111</v>
-      </c>
-      <c r="H40" s="4">
-        <v>224.34458467728319</v>
-      </c>
-      <c r="I40" s="4">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B41" s="2">
-        <v>19</v>
-      </c>
-      <c r="C41" s="4">
-        <v>298.14999999999998</v>
-      </c>
-      <c r="D41" s="5">
-        <v>101.325</v>
-      </c>
-      <c r="E41" s="4">
-        <v>104.92011957080643</v>
-      </c>
-      <c r="F41" s="7">
-        <v>0.36719964130372146</v>
-      </c>
-      <c r="G41" s="4">
-        <v>2.8698525619149113E-3</v>
-      </c>
-      <c r="H41" s="4">
-        <v>2.5073905791015251E-5</v>
-      </c>
-      <c r="I41" s="4">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B42" s="2">
-        <v>20</v>
-      </c>
-      <c r="C42" s="4">
-        <v>343.39458549639238</v>
-      </c>
-      <c r="D42" s="5">
-        <v>101.325</v>
-      </c>
-      <c r="E42" s="4">
-        <v>294.14738747128831</v>
-      </c>
-      <c r="F42" s="7">
-        <v>0.95807613660276081</v>
-      </c>
-      <c r="G42" s="4">
-        <v>2.8698525619149113E-3</v>
-      </c>
-      <c r="H42" s="4">
-        <v>13.057465900979093</v>
-      </c>
-      <c r="I42" s="4">
-        <f t="shared" si="0"/>
-        <v>70.244585496392403</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="N14:O14"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959889D7-F248-4C3B-B68C-D47001A5CC86}">
   <dimension ref="B2:AH39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4013,4 +2560,2171 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E91C93-8228-4E85-B9E3-FB80BE715EB6}">
+  <dimension ref="B2:Y42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="11.5546875" style="2"/>
+    <col min="11" max="11" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.109375" customWidth="1"/>
+    <col min="18" max="18" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.6640625" customWidth="1"/>
+    <col min="20" max="20" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="28"/>
+      <c r="N2" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" s="28"/>
+      <c r="Q2" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="R2" s="28"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1073.1500000000001</v>
+      </c>
+      <c r="D3" s="5">
+        <v>25</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1350.0381316636626</v>
+      </c>
+      <c r="F3" s="7">
+        <v>3.0305681085599816</v>
+      </c>
+      <c r="G3" s="4">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4">
+        <v>756.61237274082237</v>
+      </c>
+      <c r="I3" s="4">
+        <f>C3-273.15</f>
+        <v>800.00000000000011</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1018.1289616795918</v>
+      </c>
+      <c r="D4" s="5">
+        <v>17.482517482517483</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1281.2341664776559</v>
+      </c>
+      <c r="F4" s="7">
+        <v>3.035664888414034</v>
+      </c>
+      <c r="G4" s="4">
+        <v>10</v>
+      </c>
+      <c r="H4" s="4">
+        <v>686.28880264133011</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" ref="I4:I42" si="0">C4-273.15</f>
+        <v>744.97896167959186</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" s="7">
+        <v>1.7979758880009502</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" s="10">
+        <v>688.03965186006621</v>
+      </c>
+      <c r="Q4" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="R4" s="6">
+        <v>916.98727526679568</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1073.1500000000001</v>
+      </c>
+      <c r="D5" s="5">
+        <v>17.482517482517483</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1351.4823193165744</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3.1028601038812176</v>
+      </c>
+      <c r="G5" s="4">
+        <v>10</v>
+      </c>
+      <c r="H5" s="4">
+        <v>736.50270198870771</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="0"/>
+        <v>800.00000000000011</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0.70248152838918376</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="10">
+        <v>1199.1350689643341</v>
+      </c>
+      <c r="Q5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="R5" s="6">
+        <v>830.65281683265493</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4">
+        <v>976.11427576830124</v>
+      </c>
+      <c r="D6" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1231.5688124201411</v>
+      </c>
+      <c r="F6" s="7">
+        <v>3.1121411727413726</v>
+      </c>
+      <c r="G6" s="4">
+        <v>10</v>
+      </c>
+      <c r="H6" s="4">
+        <v>613.82204441161923</v>
+      </c>
+      <c r="I6" s="4">
+        <f t="shared" si="0"/>
+        <v>702.96427576830126</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="7">
+        <v>2.5004574163901339</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6" s="10">
+        <v>71.774211786387255</v>
+      </c>
+      <c r="Q6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="R6" s="6">
+        <v>6850.0253590880538</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4">
+        <v>580.59332858273865</v>
+      </c>
+      <c r="D7" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E7" s="4">
+        <v>758.75704305028523</v>
+      </c>
+      <c r="F7" s="7">
+        <v>2.4934653765384365</v>
+      </c>
+      <c r="G7" s="4">
+        <v>10</v>
+      </c>
+      <c r="H7" s="4">
+        <v>325.46846367966873</v>
+      </c>
+      <c r="I7" s="4">
+        <f t="shared" si="0"/>
+        <v>307.44332858273867</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" s="7">
+        <v>4.8493514799902702</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O7" s="10">
+        <v>-386.40079286911646</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="R7" s="6">
+        <v>2723.6906468307247</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4">
+        <v>435.43287838933054</v>
+      </c>
+      <c r="D8" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E8" s="4">
+        <v>591.19593244306282</v>
+      </c>
+      <c r="F8" s="7">
+        <v>2.1610419768753544</v>
+      </c>
+      <c r="G8" s="4">
+        <v>10</v>
+      </c>
+      <c r="H8" s="4">
+        <v>257.0193896819942</v>
+      </c>
+      <c r="I8" s="4">
+        <f t="shared" si="0"/>
+        <v>162.28287838933056</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="7">
+        <v>1.6756111060722243</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="O8" s="10">
+        <v>-188.73788675888972</v>
+      </c>
+      <c r="Q8" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R8" s="6">
+        <v>150.85917384920415</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="4">
+        <v>435.43287838933054</v>
+      </c>
+      <c r="D9" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E9" s="4">
+        <v>591.19593244306282</v>
+      </c>
+      <c r="F9" s="7">
+        <v>2.1610419768753544</v>
+      </c>
+      <c r="G9" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H9" s="4">
+        <v>257.0193896819942</v>
+      </c>
+      <c r="I9" s="4">
+        <f t="shared" si="0"/>
+        <v>162.28287838933056</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0.11033034486553291</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O9" s="10">
+        <v>-5.8779815586019524E-2</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="R9" s="6">
+        <v>4757.3674529323171</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="4">
+        <v>423.3557736165609</v>
+      </c>
+      <c r="D10" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.57659650223683723</v>
+      </c>
+      <c r="F10" s="7">
+        <v>2.1270382629381421E-3</v>
+      </c>
+      <c r="G10" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.25257199616171355</v>
+      </c>
+      <c r="I10" s="4">
+        <f t="shared" si="0"/>
+        <v>150.20577361656092</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0.68666556854253946</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O10" s="10">
+        <v>1312.0360411963943</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="R10" s="6">
+        <v>58326.910191272655</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="4">
+        <v>357.24648058947918</v>
+      </c>
+      <c r="D11" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.48705207701453501</v>
+      </c>
+      <c r="F11" s="7">
+        <v>1.8961819516546078E-3</v>
+      </c>
+      <c r="G11" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.23185738014859708</v>
+      </c>
+      <c r="I11" s="4">
+        <f t="shared" si="0"/>
+        <v>84.096480589479199</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11" s="7">
+        <v>0.12544275752191905</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11" s="10">
+        <v>71.715431970801234</v>
+      </c>
+      <c r="Q11" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="R11" s="6">
+        <v>101653.79754728591</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="4">
+        <v>346.62433578909861</v>
+      </c>
+      <c r="D12" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0.46883148724964824</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1.844389053247172E-3</v>
+      </c>
+      <c r="G12" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.22907884304388729</v>
+      </c>
+      <c r="I12" s="4">
+        <f t="shared" si="0"/>
+        <v>73.474335789098632</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" s="7">
+        <v>0.92243867092999143</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="O12" s="12">
+        <v>1383.7514731671954</v>
+      </c>
+      <c r="Q12" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="R12" s="6">
+        <v>6084.4865460826932</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="4">
+        <v>344.39458549639238</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E13" s="4">
+        <v>464.67130036926602</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1.8323480555267959</v>
+      </c>
+      <c r="G13" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H13" s="4">
+        <v>228.50867963383527</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" si="0"/>
+        <v>71.244585496392403</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="7">
+        <v>0.72305037797389082</v>
+      </c>
+      <c r="Q13" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="R13" s="6">
+        <v>-14690.262623456645</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="4">
+        <v>435.43287838933054</v>
+      </c>
+      <c r="D14" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E14" s="4">
+        <v>591.19593244306282</v>
+      </c>
+      <c r="F14" s="7">
+        <v>2.1610419768753544</v>
+      </c>
+      <c r="G14" s="4">
+        <v>2.0055144227139889</v>
+      </c>
+      <c r="H14" s="4">
+        <v>257.0193896819942</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="0"/>
+        <v>162.28287838933056</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" s="7">
+        <v>0.12767286098529926</v>
+      </c>
+      <c r="N14" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="O14" s="29"/>
+      <c r="Q14" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="R14" s="6">
+        <v>-7175.4747263768222</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B15" s="3">
+        <v>7</v>
+      </c>
+      <c r="C15" s="4">
+        <v>328.15</v>
+      </c>
+      <c r="D15" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E15" s="4">
+        <v>427.37611738856413</v>
+      </c>
+      <c r="F15" s="7">
+        <v>1.72122584179495</v>
+      </c>
+      <c r="G15" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H15" s="4">
+        <v>224.33075530171814</v>
+      </c>
+      <c r="I15" s="4">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="7">
+        <v>0.85072323895919011</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="O15" s="10">
+        <v>7.7745474285568061</v>
+      </c>
+      <c r="Q15" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="R15" s="6">
+        <v>-2.2347027849124075</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B16" s="3">
+        <v>8</v>
+      </c>
+      <c r="C16" s="4">
+        <v>407.92598052767181</v>
+      </c>
+      <c r="D16" s="5">
+        <v>25</v>
+      </c>
+      <c r="E16" s="4">
+        <v>475.70953285771714</v>
+      </c>
+      <c r="F16" s="7">
+        <v>1.7343043486568708</v>
+      </c>
+      <c r="G16" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H16" s="4">
+        <v>268.76481394998945</v>
+      </c>
+      <c r="I16" s="4">
+        <f t="shared" si="0"/>
+        <v>134.77598052767183</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" s="7">
+        <v>3.3258554014030113E-2</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="O16" s="10">
+        <v>52.471841055808</v>
+      </c>
+      <c r="Q16" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="R16" s="6">
+        <v>14936.432649657721</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
+        <v>9</v>
+      </c>
+      <c r="C17" s="4">
+        <v>547.68745921507718</v>
+      </c>
+      <c r="D17" s="5">
+        <v>25</v>
+      </c>
+      <c r="E17" s="4">
+        <v>685.30539614040072</v>
+      </c>
+      <c r="F17" s="7">
+        <v>2.1800807088725671</v>
+      </c>
+      <c r="G17" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H17" s="4">
+        <v>345.45245543436323</v>
+      </c>
+      <c r="I17" s="4">
+        <f t="shared" si="0"/>
+        <v>274.53745921507721</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L17" s="16">
+        <v>-0.29815580239591893</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="O17" s="10">
+        <v>53.374586045417935</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="R17" s="6">
+        <v>12158.725147647143</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B18" s="3">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4">
+        <v>547.68745921507718</v>
+      </c>
+      <c r="D18" s="5">
+        <v>25</v>
+      </c>
+      <c r="E18" s="4">
+        <v>685.30539614040072</v>
+      </c>
+      <c r="F18" s="7">
+        <v>2.1800807088725671</v>
+      </c>
+      <c r="G18" s="4">
+        <v>2.0055144227139889</v>
+      </c>
+      <c r="H18" s="4">
+        <v>345.45245543436323</v>
+      </c>
+      <c r="I18" s="4">
+        <f t="shared" si="0"/>
+        <v>274.53745921507721</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="O18" s="10">
+        <v>54.014275766007323</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="R18" s="6">
+        <v>2143439.7108252258</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B19" s="3">
+        <v>11</v>
+      </c>
+      <c r="C19" s="4">
+        <v>547.68745921507718</v>
+      </c>
+      <c r="D19" s="5">
+        <v>25</v>
+      </c>
+      <c r="E19" s="4">
+        <v>685.30539614040072</v>
+      </c>
+      <c r="F19" s="7">
+        <v>2.1800807088725671</v>
+      </c>
+      <c r="G19" s="4">
+        <v>10</v>
+      </c>
+      <c r="H19" s="4">
+        <v>345.45245543436323</v>
+      </c>
+      <c r="I19" s="4">
+        <f t="shared" si="0"/>
+        <v>274.53745921507721</v>
+      </c>
+      <c r="K19" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="29"/>
+      <c r="N19" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="O19" s="10">
+        <v>55.339933569630354</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="R19" s="6">
+        <v>2503125.0768078174</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B20" s="3">
+        <v>12</v>
+      </c>
+      <c r="C20" s="4">
+        <v>932.83907702081467</v>
+      </c>
+      <c r="D20" s="5">
+        <v>25</v>
+      </c>
+      <c r="E20" s="4">
+        <v>1170.2405428635675</v>
+      </c>
+      <c r="F20" s="7">
+        <v>2.8510501836319815</v>
+      </c>
+      <c r="G20" s="4">
+        <v>10</v>
+      </c>
+      <c r="H20" s="4">
+        <v>630.33805325801075</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="0"/>
+        <v>659.68907702081469</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="4">
+        <v>159.02185344711796</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="O20" s="10">
+        <v>3.4933609588634824</v>
+      </c>
+      <c r="Q20" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T20" s="28"/>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
+        <v>17</v>
+      </c>
+      <c r="C21" s="4">
+        <v>313.14999999999998</v>
+      </c>
+      <c r="D21" s="5">
+        <v>7.8923107438086744</v>
+      </c>
+      <c r="E21" s="4">
+        <v>-132.35463919610541</v>
+      </c>
+      <c r="F21" s="7">
+        <v>-0.37994748587359245</v>
+      </c>
+      <c r="G21" s="4">
+        <v>1.7897056695309543</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.52460446529691762</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" s="4">
+        <v>63.229887799023224</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="O21" s="10">
+        <v>22.489305649899514</v>
+      </c>
+      <c r="Q21" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="R21" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="S21" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="T21" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B22" s="3">
+        <v>18</v>
+      </c>
+      <c r="C22" s="4">
+        <v>313.1583575108412</v>
+      </c>
+      <c r="D22" s="5">
+        <v>31.569242975234697</v>
+      </c>
+      <c r="E22" s="4">
+        <v>-132.32179590986752</v>
+      </c>
+      <c r="F22" s="7">
+        <v>-0.37994748587359245</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1.7897056695309543</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0.55744775153482984</v>
+      </c>
+      <c r="I22" s="4">
+        <f t="shared" si="0"/>
+        <v>40.008357510841222</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" s="4">
+        <v>21.287660768567079</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="O22" s="6">
+        <v>52.415130655682205</v>
+      </c>
+      <c r="Q22" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="R22" s="24">
+        <v>2505530.7763891984</v>
+      </c>
+      <c r="S22" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="T22" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="4">
+        <v>347.24648058947918</v>
+      </c>
+      <c r="D23" s="5">
+        <v>31.569242975234697</v>
+      </c>
+      <c r="E23" s="4">
+        <v>-70.674595063457787</v>
+      </c>
+      <c r="F23" s="7">
+        <v>-0.19317568283781225</v>
+      </c>
+      <c r="G23" s="4">
+        <v>1.7897056695309543</v>
+      </c>
+      <c r="H23" s="4">
+        <v>6.518635522826691</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="0"/>
+        <v>74.096480589479199</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L23" s="4">
+        <v>19.283425035580251</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="O23" s="6">
+        <v>23.133959295545651</v>
+      </c>
+      <c r="Q23" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="R23" s="24">
+        <v>4269212.9393934794</v>
+      </c>
+      <c r="S23" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="T23" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="4">
+        <v>347.24648058947918</v>
+      </c>
+      <c r="D24" s="5">
+        <v>31.569242975234697</v>
+      </c>
+      <c r="E24" s="4">
+        <v>313.00054226931974</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0.91173151933586583</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1.7897056695309543</v>
+      </c>
+      <c r="H24" s="4">
+        <v>60.765690527522125</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" si="0"/>
+        <v>74.096480589479199</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="L24" s="4">
+        <v>3.5021630107067545</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="O24" s="15">
+        <v>23.136921933126388</v>
+      </c>
+      <c r="Q24" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="R24" s="24">
+        <v>202782.7454297191</v>
+      </c>
+      <c r="S24" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="T24" s="27">
+        <v>2503125.0768078174</v>
+      </c>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B25" s="3">
+        <v>15</v>
+      </c>
+      <c r="C25" s="4">
+        <v>396.43287838933054</v>
+      </c>
+      <c r="D25" s="5">
+        <v>31.569242975234697</v>
+      </c>
+      <c r="E25" s="4">
+        <v>383.09182021380718</v>
+      </c>
+      <c r="F25" s="7">
+        <v>1.1002468147744369</v>
+      </c>
+      <c r="G25" s="4">
+        <v>1.7897056695309543</v>
+      </c>
+      <c r="H25" s="4">
+        <v>74.651133136999675</v>
+      </c>
+      <c r="I25" s="4">
+        <f t="shared" si="0"/>
+        <v>123.28287838933056</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="L25" s="4">
+        <v>110.44125389851233</v>
+      </c>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="26"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B26" s="3">
+        <v>16</v>
+      </c>
+      <c r="C26" s="4">
+        <v>368.13790080168786</v>
+      </c>
+      <c r="D26" s="5">
+        <v>7.8923107438086744</v>
+      </c>
+      <c r="E26" s="4">
+        <v>342.98790088879446</v>
+      </c>
+      <c r="F26" s="7">
+        <v>1.119604713516257</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.7897056695309543</v>
+      </c>
+      <c r="H26" s="4">
+        <v>28.775656302113202</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="0"/>
+        <v>94.987900801687886</v>
+      </c>
+      <c r="N26" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="O26" s="29"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="4">
+        <v>313.14999999999998</v>
+      </c>
+      <c r="D27" s="5">
+        <v>7.8923107438086744</v>
+      </c>
+      <c r="E27" s="4">
+        <v>271.65055019539255</v>
+      </c>
+      <c r="F27" s="7">
+        <v>0.91018564327057938</v>
+      </c>
+      <c r="G27" s="4">
+        <v>1.7897056695309543</v>
+      </c>
+      <c r="H27" s="4">
+        <v>19.876601402460075</v>
+      </c>
+      <c r="I27" s="4">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="O27" s="6">
+        <v>0.71269346475761464</v>
+      </c>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="4">
+        <v>298.14999999999998</v>
+      </c>
+      <c r="D28" s="5">
+        <v>101.325</v>
+      </c>
+      <c r="E28" s="4">
+        <v>104.92011957080643</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0.36719964130372146</v>
+      </c>
+      <c r="G28" s="4">
+        <v>34.591753259051274</v>
+      </c>
+      <c r="H28" s="4">
+        <v>2.5073905791015251E-5</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O28" s="6">
+        <v>0.99770990140218263</v>
+      </c>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="4">
+        <v>303.14999999999998</v>
+      </c>
+      <c r="D29" s="5">
+        <v>101.325</v>
+      </c>
+      <c r="E29" s="4">
+        <v>125.82251132178534</v>
+      </c>
+      <c r="F29" s="7">
+        <v>0.43672528196163279</v>
+      </c>
+      <c r="G29" s="4">
+        <v>34.591753259051274</v>
+      </c>
+      <c r="H29" s="4">
+        <v>0.17334706272843686</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="N29" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="O29" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="4">
+        <v>304.03303316959324</v>
+      </c>
+      <c r="D30" s="5">
+        <v>101.325</v>
+      </c>
+      <c r="E30" s="4">
+        <v>129.51335809758132</v>
+      </c>
+      <c r="F30" s="7">
+        <v>0.44888256955875044</v>
+      </c>
+      <c r="G30" s="4">
+        <v>34.591753259051274</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0.23949854144378332</v>
+      </c>
+      <c r="I30" s="4">
+        <f t="shared" si="0"/>
+        <v>30.883033169593261</v>
+      </c>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="4">
+        <v>435.43287838933054</v>
+      </c>
+      <c r="D31" s="5">
+        <v>9124.0875912408756</v>
+      </c>
+      <c r="E31" s="4">
+        <v>591.19593244282169</v>
+      </c>
+      <c r="F31" s="7">
+        <v>2.1610419768753544</v>
+      </c>
+      <c r="G31" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H31" s="4">
+        <v>257.03321905731815</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="0"/>
+        <v>162.28287838933056</v>
+      </c>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="4">
+        <v>423.3557736165609</v>
+      </c>
+      <c r="D32" s="5">
+        <v>9124.0875912408756</v>
+      </c>
+      <c r="E32" s="4">
+        <v>576.59650223683718</v>
+      </c>
+      <c r="F32" s="7">
+        <v>2.1270382629381421</v>
+      </c>
+      <c r="G32" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H32" s="4">
+        <v>252.57199616171354</v>
+      </c>
+      <c r="I32" s="4">
+        <f t="shared" si="0"/>
+        <v>150.20577361656092</v>
+      </c>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="4">
+        <v>357.24648058947918</v>
+      </c>
+      <c r="D33" s="5">
+        <v>9124.0875912408756</v>
+      </c>
+      <c r="E33" s="4">
+        <v>487.05207701453503</v>
+      </c>
+      <c r="F33" s="7">
+        <v>1.8961819516546079</v>
+      </c>
+      <c r="G33" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H33" s="4">
+        <v>231.85738014859709</v>
+      </c>
+      <c r="I33" s="4">
+        <f t="shared" si="0"/>
+        <v>84.096480589479199</v>
+      </c>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="4">
+        <v>346.62433578909861</v>
+      </c>
+      <c r="D34" s="5">
+        <v>9124.0875912408756</v>
+      </c>
+      <c r="E34" s="4">
+        <v>468.83148724964826</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1.8443890532471721</v>
+      </c>
+      <c r="G34" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H34" s="4">
+        <v>229.07884304388728</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="0"/>
+        <v>73.474335789098632</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B35" s="2">
+        <v>13</v>
+      </c>
+      <c r="C35" s="4">
+        <v>298.14999999999998</v>
+      </c>
+      <c r="D35" s="5">
+        <v>0.101325</v>
+      </c>
+      <c r="E35" s="4">
+        <v>424.43605428165802</v>
+      </c>
+      <c r="F35" s="7">
+        <v>3.8804887263997387</v>
+      </c>
+      <c r="G35" s="4">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="H35" s="4">
+        <v>2.1111792130950945E-2</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B36" s="2">
+        <v>14</v>
+      </c>
+      <c r="C36" s="4">
+        <v>278.14999999999998</v>
+      </c>
+      <c r="D36" s="5">
+        <v>0.101325</v>
+      </c>
+      <c r="E36" s="4">
+        <v>453.10722153513228</v>
+      </c>
+      <c r="F36" s="7">
+        <v>3.9723323134988857</v>
+      </c>
+      <c r="G36" s="4">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="H36" s="4">
+        <v>1.3091135519945019</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="4">
+        <v>346.62433578909861</v>
+      </c>
+      <c r="D37" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E37" s="4">
+        <v>468.83148724964826</v>
+      </c>
+      <c r="F37" s="7">
+        <v>1.8443890532471721</v>
+      </c>
+      <c r="G37" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H37" s="4">
+        <v>229.07884304388728</v>
+      </c>
+      <c r="I37" s="4">
+        <f t="shared" si="0"/>
+        <v>73.474335789098632</v>
+      </c>
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="4">
+        <v>344.39458549639238</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.1240875912408761</v>
+      </c>
+      <c r="E38" s="4">
+        <v>464.67130036926602</v>
+      </c>
+      <c r="F38" s="7">
+        <v>1.8323480555267959</v>
+      </c>
+      <c r="G38" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H38" s="4">
+        <v>228.50867963383527</v>
+      </c>
+      <c r="I38" s="4">
+        <f t="shared" si="0"/>
+        <v>71.244585496392403</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="4">
+        <v>344.39458549639238</v>
+      </c>
+      <c r="D39" s="5">
+        <v>9124.0875912408756</v>
+      </c>
+      <c r="E39" s="4">
+        <v>464.67130036356895</v>
+      </c>
+      <c r="F39" s="7">
+        <v>1.8323480555267959</v>
+      </c>
+      <c r="G39" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H39" s="4">
+        <v>228.5086796281382</v>
+      </c>
+      <c r="I39" s="4">
+        <f t="shared" si="0"/>
+        <v>71.244585496392403</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B40" s="2">
+        <v>7</v>
+      </c>
+      <c r="C40" s="4">
+        <v>328.15</v>
+      </c>
+      <c r="D40" s="5">
+        <v>9124.0875912408756</v>
+      </c>
+      <c r="E40" s="4">
+        <v>427.37611738856413</v>
+      </c>
+      <c r="F40" s="7">
+        <v>1.72122584179495</v>
+      </c>
+      <c r="G40" s="4">
+        <v>7.9944855772860111</v>
+      </c>
+      <c r="H40" s="4">
+        <v>224.34458467728319</v>
+      </c>
+      <c r="I40" s="4">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B41" s="2">
+        <v>19</v>
+      </c>
+      <c r="C41" s="4">
+        <v>298.14999999999998</v>
+      </c>
+      <c r="D41" s="5">
+        <v>101.325</v>
+      </c>
+      <c r="E41" s="4">
+        <v>104.92011957080643</v>
+      </c>
+      <c r="F41" s="7">
+        <v>0.36719964130372146</v>
+      </c>
+      <c r="G41" s="4">
+        <v>2.8698525619149113E-3</v>
+      </c>
+      <c r="H41" s="4">
+        <v>2.5073905791015251E-5</v>
+      </c>
+      <c r="I41" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B42" s="2">
+        <v>20</v>
+      </c>
+      <c r="C42" s="4">
+        <v>343.39458549639238</v>
+      </c>
+      <c r="D42" s="5">
+        <v>101.325</v>
+      </c>
+      <c r="E42" s="4">
+        <v>294.14738747128831</v>
+      </c>
+      <c r="F42" s="7">
+        <v>0.95807613660276081</v>
+      </c>
+      <c r="G42" s="4">
+        <v>2.8698525619149113E-3</v>
+      </c>
+      <c r="H42" s="4">
+        <v>13.057465900979093</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="0"/>
+        <v>70.244585496392403</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="N14:O14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E0693F-D387-4367-8A44-8725A6CA7BA7}">
+  <dimension ref="A1:AF33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K1" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1" t="s">
+        <v>195</v>
+      </c>
+      <c r="M1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N1" t="s">
+        <v>136</v>
+      </c>
+      <c r="O1" t="s">
+        <v>137</v>
+      </c>
+      <c r="P1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>139</v>
+      </c>
+      <c r="R1" t="s">
+        <v>140</v>
+      </c>
+      <c r="S1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U1" t="s">
+        <v>143</v>
+      </c>
+      <c r="V1" t="s">
+        <v>144</v>
+      </c>
+      <c r="W1" t="s">
+        <v>145</v>
+      </c>
+      <c r="X1" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>-1</v>
+      </c>
+      <c r="X2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>-1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>-1</v>
+      </c>
+      <c r="Z4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>-1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>-1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>-1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>-1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>-1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" t="s">
+        <v>163</v>
+      </c>
+      <c r="K13">
+        <v>-1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>199</v>
+      </c>
+      <c r="L14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" t="s">
+        <v>164</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>-1</v>
+      </c>
+      <c r="W15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>-1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" t="s">
+        <v>166</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>-1</v>
+      </c>
+      <c r="AE17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>-1</v>
+      </c>
+      <c r="T18" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" t="s">
+        <v>168</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>-1</v>
+      </c>
+      <c r="AF19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>191</v>
+      </c>
+      <c r="AF20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B21" t="s">
+        <v>170</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>-1</v>
+      </c>
+      <c r="U22" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>171</v>
+      </c>
+      <c r="B23" t="s">
+        <v>172</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>-1</v>
+      </c>
+      <c r="S23">
+        <v>-1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>192</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>-1</v>
+      </c>
+      <c r="K24" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" t="s">
+        <v>174</v>
+      </c>
+      <c r="W25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="AC25">
+        <v>-1</v>
+      </c>
+      <c r="AD25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>201</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -1,42 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696BD113-F08B-433B-BCFC-F1438E51495D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25F4501-37D5-40F4-BAAB-3B9377582E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" activeTab="2" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="3" r:id="rId1"/>
     <sheet name="Energy_Exergy" sheetId="2" r:id="rId2"/>
-    <sheet name="EXERGO" sheetId="4" r:id="rId3"/>
+    <sheet name="Exergoeconomico" sheetId="5" r:id="rId3"/>
+    <sheet name="EXERGO" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="243">
   <si>
     <t>T [°C]</t>
   </si>
@@ -642,6 +635,129 @@
   </si>
   <si>
     <t>24 ecuaciones</t>
+  </si>
+  <si>
+    <t>Cdot (USD/h)</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>c4</t>
+  </si>
+  <si>
+    <t>c5</t>
+  </si>
+  <si>
+    <t>c6</t>
+  </si>
+  <si>
+    <t>c7</t>
+  </si>
+  <si>
+    <t>c8</t>
+  </si>
+  <si>
+    <t>c9</t>
+  </si>
+  <si>
+    <t>c10</t>
+  </si>
+  <si>
+    <t>c11</t>
+  </si>
+  <si>
+    <t>c12</t>
+  </si>
+  <si>
+    <t>c6BI</t>
+  </si>
+  <si>
+    <t>c6AI</t>
+  </si>
+  <si>
+    <t>c6AO3</t>
+  </si>
+  <si>
+    <t>c6AO</t>
+  </si>
+  <si>
+    <t>c20</t>
+  </si>
+  <si>
+    <t>c15</t>
+  </si>
+  <si>
+    <t>c16</t>
+  </si>
+  <si>
+    <t>c17</t>
+  </si>
+  <si>
+    <t>c18</t>
+  </si>
+  <si>
+    <t>cH2</t>
+  </si>
+  <si>
+    <t>cO2</t>
+  </si>
+  <si>
+    <t>cel</t>
+  </si>
+  <si>
+    <t>Componente</t>
+  </si>
+  <si>
+    <t>c19</t>
+  </si>
+  <si>
+    <t>Evaporador ORC</t>
+  </si>
+  <si>
+    <t>Turbina ORC</t>
+  </si>
+  <si>
+    <t>Bomba ORC</t>
+  </si>
+  <si>
+    <t>Condensador ORC</t>
+  </si>
+  <si>
+    <t>HE-PEM</t>
+  </si>
+  <si>
+    <t>Punto</t>
+  </si>
+  <si>
+    <t>Costo Unit. (USD/kWhex)</t>
+  </si>
+  <si>
+    <t>Zdot (USD/h)</t>
+  </si>
+  <si>
+    <t>ED (kW)</t>
+  </si>
+  <si>
+    <t>CD (USD/h)</t>
+  </si>
+  <si>
+    <t>f (%)</t>
+  </si>
+  <si>
+    <t>LCOEn(USD/kWh)</t>
+  </si>
+  <si>
+    <t>cH2 [USD/kWhex]</t>
+  </si>
+  <si>
+    <t>cElectricidad [USD/kWhex]</t>
   </si>
 </sst>
 </file>
@@ -753,7 +869,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -812,6 +928,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -880,9 +998,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -920,7 +1038,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1026,7 +1144,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1168,7 +1286,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1266,34 +1384,34 @@
         <v>500</v>
       </c>
       <c r="C3" s="19">
-        <v>0.79959526453496776</v>
+        <v>7.9817560813786423</v>
       </c>
       <c r="D3" s="17">
-        <v>5.7474602609853757E-2</v>
+        <v>0.57478365564259748</v>
       </c>
       <c r="E3" s="19">
-        <v>44.242025146810107</v>
+        <v>44.197489238670407</v>
       </c>
       <c r="F3" s="19">
-        <v>22.280941712184308</v>
+        <v>22.006324234413263</v>
       </c>
       <c r="G3" s="19">
-        <v>42.805350727912341</v>
+        <v>42.266069418369199</v>
       </c>
       <c r="H3" s="19">
-        <v>54.391713608301288</v>
+        <v>39.083036578748462</v>
       </c>
       <c r="I3" s="19">
-        <v>53.43053490915559</v>
+        <v>38.322157470640676</v>
       </c>
       <c r="J3" s="19">
-        <v>71.431846289059933</v>
+        <v>73.705196115616388</v>
       </c>
       <c r="K3" s="19">
-        <v>0.94449159071981759</v>
+        <v>6.7738392475312912</v>
       </c>
       <c r="L3" s="17">
-        <v>8.4406216959654934</v>
+        <v>60.535652280525397</v>
       </c>
       <c r="M3" s="21"/>
       <c r="N3" s="21"/>
@@ -1323,34 +1441,34 @@
         <v>550</v>
       </c>
       <c r="C4" s="17">
-        <v>0.89972160669047219</v>
+        <v>8.9819868548594588</v>
       </c>
       <c r="D4" s="17">
-        <v>5.9775959042112747E-2</v>
+        <v>0.59780007016897552</v>
       </c>
       <c r="E4" s="17">
-        <v>46.738186634220291</v>
+        <v>46.69526627123269</v>
       </c>
       <c r="F4" s="17">
-        <v>23.115653468129583</v>
+        <v>22.850005374764851</v>
       </c>
       <c r="G4" s="17">
-        <v>45.32985739384808</v>
+        <v>44.797301420947292</v>
       </c>
       <c r="H4" s="17">
-        <v>54.219471799935384</v>
+        <v>38.702038861674041</v>
       </c>
       <c r="I4" s="17">
-        <v>53.258556160364932</v>
+        <v>37.945565695998773</v>
       </c>
       <c r="J4" s="17">
-        <v>71.235617634821836</v>
+        <v>73.460227385209635</v>
       </c>
       <c r="K4" s="17">
-        <v>0.97914227476891347</v>
+        <v>6.9757969550625445</v>
       </c>
       <c r="L4" s="17">
-        <v>8.7502838660033913</v>
+        <v>62.340484239438453</v>
       </c>
       <c r="M4" s="21"/>
       <c r="N4" s="21"/>
@@ -1380,34 +1498,34 @@
         <v>600</v>
       </c>
       <c r="C5" s="17">
-        <v>0.99841792896138692</v>
+        <v>9.9679334582948602</v>
       </c>
       <c r="D5" s="17">
-        <v>6.2107603556281796E-2</v>
+        <v>0.62111932846844753</v>
       </c>
       <c r="E5" s="17">
-        <v>48.905256206618859</v>
+        <v>48.863771870449504</v>
       </c>
       <c r="F5" s="17">
-        <v>23.650319962765966</v>
+        <v>23.39359126526438</v>
       </c>
       <c r="G5" s="17">
-        <v>47.52015705474146</v>
+        <v>46.992751286845909</v>
       </c>
       <c r="H5" s="17">
-        <v>54.048316611557979</v>
+        <v>38.328127919305047</v>
       </c>
       <c r="I5" s="17">
-        <v>53.087671766748116</v>
+        <v>37.576039107764217</v>
       </c>
       <c r="J5" s="17">
-        <v>71.038424425410881</v>
+        <v>73.215836655735927</v>
       </c>
       <c r="K5" s="17">
-        <v>1.0140645281447851</v>
+        <v>7.1772698736697782</v>
       </c>
       <c r="L5" s="17">
-        <v>9.0623729649563405</v>
+        <v>64.140983793542134</v>
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
@@ -1437,34 +1555,34 @@
         <v>650</v>
       </c>
       <c r="C6" s="17">
-        <v>1.095976970270373</v>
+        <v>10.942520132883478</v>
       </c>
       <c r="D6" s="17">
-        <v>6.4468832600220724E-2</v>
+        <v>0.6447344000410401</v>
       </c>
       <c r="E6" s="17">
-        <v>50.80680659983301</v>
+        <v>50.766607886856718</v>
       </c>
       <c r="F6" s="17">
-        <v>23.908927906115419</v>
+        <v>23.661351320584064</v>
       </c>
       <c r="G6" s="17">
-        <v>49.440886587190505</v>
+        <v>48.91739667752401</v>
       </c>
       <c r="H6" s="17">
-        <v>53.878220178726544</v>
+        <v>37.961182417304968</v>
       </c>
       <c r="I6" s="17">
-        <v>52.917855462200883</v>
+        <v>37.213454717865027</v>
       </c>
       <c r="J6" s="17">
-        <v>70.840471045585389</v>
+        <v>72.972155033057845</v>
       </c>
       <c r="K6" s="17">
-        <v>1.0492439615518117</v>
+        <v>7.3782020252319311</v>
       </c>
       <c r="L6" s="17">
-        <v>9.3767604002545415</v>
+        <v>65.936650684128182</v>
       </c>
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
@@ -1494,34 +1612,34 @@
         <v>700</v>
       </c>
       <c r="C7" s="17">
-        <v>1.1926154214167359</v>
+        <v>11.907911442755228</v>
       </c>
       <c r="D7" s="17">
-        <v>6.6858338839570361E-2</v>
+        <v>0.66863221481329138</v>
       </c>
       <c r="E7" s="17">
-        <v>52.490240359052798</v>
+        <v>52.451199641588161</v>
       </c>
       <c r="F7" s="17">
-        <v>23.905414304807127</v>
+        <v>23.667463179486298</v>
       </c>
       <c r="G7" s="17">
-        <v>51.140240176954421</v>
+        <v>50.619687111767362</v>
       </c>
       <c r="H7" s="17">
-        <v>53.709201785475713</v>
+        <v>37.60117137295029</v>
       </c>
       <c r="I7" s="17">
-        <v>52.749127913968607</v>
+        <v>36.857778908474963</v>
       </c>
       <c r="J7" s="17">
-        <v>70.642003533187847</v>
+        <v>72.729372195994642</v>
       </c>
       <c r="K7" s="17">
-        <v>1.08465748785521</v>
+        <v>7.5784907719207091</v>
       </c>
       <c r="L7" s="17">
-        <v>9.6932398494990846</v>
+        <v>67.726567669488134</v>
       </c>
       <c r="M7" s="21"/>
       <c r="N7" s="21"/>
@@ -1551,34 +1669,34 @@
         <v>750</v>
       </c>
       <c r="C8" s="17">
-        <v>1.2884976984183187</v>
+        <v>12.865749758364128</v>
       </c>
       <c r="D8" s="17">
-        <v>6.9274475184734868E-2</v>
+        <v>0.6927963040732894</v>
       </c>
       <c r="E8" s="17">
-        <v>53.991830167895671</v>
+        <v>53.953838014043107</v>
       </c>
       <c r="F8" s="17">
-        <v>23.646581930865896</v>
+        <v>23.418942554906867</v>
       </c>
       <c r="G8" s="17">
-        <v>52.655094193700535</v>
+        <v>52.136694846180184</v>
       </c>
       <c r="H8" s="17">
-        <v>53.541305493071732</v>
+        <v>37.248102901082589</v>
       </c>
       <c r="I8" s="17">
-        <v>52.581534383252716</v>
+        <v>36.50901673542819</v>
       </c>
       <c r="J8" s="17">
-        <v>70.44328600163891</v>
+        <v>72.487705338327999</v>
       </c>
       <c r="K8" s="17">
-        <v>1.1202774409417275</v>
+        <v>7.7780119622835953</v>
       </c>
       <c r="L8" s="17">
-        <v>10.011564069413204</v>
+        <v>69.509625247479235</v>
       </c>
       <c r="M8" s="21"/>
       <c r="N8" s="21"/>
@@ -1608,34 +1726,34 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C9" s="17">
-        <v>1.3837514731671954</v>
+        <v>13.817310399416089</v>
       </c>
       <c r="D9" s="17">
-        <v>7.1715431970801227E-2</v>
+        <v>0.71720857262984272</v>
       </c>
       <c r="E9" s="17">
-        <v>55.339933569630354</v>
+        <v>55.302895315550685</v>
       </c>
       <c r="F9" s="17">
-        <v>23.133959295545651</v>
+        <v>22.917512377362197</v>
       </c>
       <c r="G9" s="17">
-        <v>54.014275766007323</v>
+        <v>53.497400064021491</v>
       </c>
       <c r="H9" s="17">
-        <v>53.374586045417935</v>
+        <v>36.901993581878948</v>
       </c>
       <c r="I9" s="17">
-        <v>52.415130655682205</v>
+        <v>36.167181648495081</v>
       </c>
       <c r="J9" s="17">
-        <v>70.244585496392403</v>
+        <v>72.247379706631875</v>
       </c>
       <c r="K9" s="17">
-        <v>1.1560742978764087</v>
+        <v>7.9766358915200142</v>
       </c>
       <c r="L9" s="17">
-        <v>10.331469222893681</v>
+        <v>71.284664287449004</v>
       </c>
       <c r="M9" s="21"/>
       <c r="N9" s="21"/>
@@ -1839,64 +1957,64 @@
         <v>500</v>
       </c>
       <c r="C16" s="17">
-        <v>29.485120651710428</v>
+        <v>294.85614292537934</v>
       </c>
       <c r="D16" s="17">
-        <v>13.564888381060969</v>
+        <v>135.64262301173875</v>
       </c>
       <c r="E16" s="17">
-        <v>14.906637101063389</v>
+        <v>151.19146157877427</v>
       </c>
       <c r="F16" s="17">
-        <v>27.324224769671563</v>
+        <v>277.13026251072807</v>
       </c>
       <c r="G16" s="17">
-        <v>8.6106797085443318</v>
+        <v>86.111522976340609</v>
       </c>
       <c r="H16" s="17">
-        <v>3.3947199989052024</v>
+        <v>34.017747966403839</v>
       </c>
       <c r="I16" s="17">
-        <v>30.271704873401731</v>
+        <v>302.81716564914211</v>
       </c>
       <c r="J16" s="17">
-        <v>118.03699553521798</v>
+        <v>1179.4615416517445</v>
       </c>
       <c r="K16" s="17">
-        <v>1387.4581203814137</v>
+        <v>13863.903314567468</v>
       </c>
       <c r="L16" s="17">
-        <v>894.0177603515491</v>
+        <v>8932.9858804423748</v>
       </c>
       <c r="M16" s="17">
-        <v>3.2636063061677061</v>
+        <v>3.3626344503154937</v>
       </c>
       <c r="N16" s="17">
-        <v>1.6493762302839108</v>
+        <v>1.6493321533075163</v>
       </c>
       <c r="O16" s="17">
-        <v>66.202538828775772</v>
+        <v>662.01750343054505</v>
       </c>
       <c r="P16" s="17">
-        <v>30.731160961602338</v>
+        <v>307.33893335012613</v>
       </c>
       <c r="Q16" s="17">
-        <v>0</v>
+        <v>6.9940860806835592E-2</v>
       </c>
       <c r="R16" s="17">
-        <v>6.3532146035785448</v>
+        <v>63.537030855789887</v>
       </c>
       <c r="S16" s="17">
-        <v>33.747118549449517</v>
+        <v>381.6564040682814</v>
       </c>
       <c r="T16" s="17">
-        <v>3468.6453009535339</v>
+        <v>34659.75828641867</v>
       </c>
       <c r="U16" s="17">
-        <v>26.639387578646851</v>
+        <v>353.65731761283195</v>
       </c>
       <c r="V16" s="17">
-        <v>2695.657254811043</v>
+        <v>27031.406760062098</v>
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.3">
@@ -1904,64 +2022,64 @@
         <v>550</v>
       </c>
       <c r="C17" s="17">
-        <v>29.781783917630268</v>
+        <v>297.82296698241635</v>
       </c>
       <c r="D17" s="17">
-        <v>13.187459854217858</v>
+        <v>131.86805418472457</v>
       </c>
       <c r="E17" s="17">
-        <v>15.005112575197126</v>
+        <v>152.19025287038554</v>
       </c>
       <c r="F17" s="17">
-        <v>27.447206193680177</v>
+        <v>278.37767920301479</v>
       </c>
       <c r="G17" s="17">
-        <v>8.8978395707103122</v>
+        <v>88.983413920749442</v>
       </c>
       <c r="H17" s="17">
-        <v>8.045436130908783</v>
+        <v>80.540884684346381</v>
       </c>
       <c r="I17" s="17">
-        <v>36.484341624139283</v>
+        <v>364.95425807604568</v>
       </c>
       <c r="J17" s="17">
-        <v>159.28762450721621</v>
+        <v>1591.6416778681469</v>
       </c>
       <c r="K17" s="17">
-        <v>1508.5865165479815</v>
+        <v>15074.172785462781</v>
       </c>
       <c r="L17" s="17">
-        <v>917.31651422341099</v>
+        <v>9165.742924421842</v>
       </c>
       <c r="M17" s="17">
-        <v>3.229940708208169</v>
+        <v>3.3261513919689558</v>
       </c>
       <c r="N17" s="17">
-        <v>1.6227368839905512</v>
+        <v>1.6226905804250538</v>
       </c>
       <c r="O17" s="17">
-        <v>70.030539355826804</v>
+        <v>700.30101822417953</v>
       </c>
       <c r="P17" s="17">
-        <v>32.431629299966701</v>
+        <v>324.34672934535394</v>
       </c>
       <c r="Q17" s="17">
-        <v>0</v>
+        <v>7.2279964988682083E-2</v>
       </c>
       <c r="R17" s="17">
-        <v>6.6540307771452101</v>
+        <v>66.545635698113529</v>
       </c>
       <c r="S17" s="17">
-        <v>33.7028919835547</v>
+        <v>380.67789920895763</v>
       </c>
       <c r="T17" s="17">
-        <v>3771.4662913699544</v>
+        <v>37685.431963656949</v>
       </c>
       <c r="U17" s="17">
-        <v>27.809219672175992</v>
+        <v>370.07849924618142</v>
       </c>
       <c r="V17" s="17">
-        <v>2899.5208238259606</v>
+        <v>29073.265801334615</v>
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.3">
@@ -1969,64 +2087,64 @@
         <v>600</v>
       </c>
       <c r="C18" s="17">
-        <v>30.072126059584438</v>
+        <v>300.72656005696859</v>
       </c>
       <c r="D18" s="17">
-        <v>12.815757813462639</v>
+        <v>128.15077235300279</v>
       </c>
       <c r="E18" s="17">
-        <v>15.074997029094375</v>
+        <v>152.89907199523319</v>
       </c>
       <c r="F18" s="17">
-        <v>27.53273934130091</v>
+        <v>279.2453075698167</v>
       </c>
       <c r="G18" s="17">
-        <v>9.1850023844852036</v>
+        <v>91.855320754454354</v>
       </c>
       <c r="H18" s="17">
-        <v>13.191794613489183</v>
+        <v>132.01571327555575</v>
       </c>
       <c r="I18" s="17">
-        <v>42.957817343885893</v>
+        <v>429.70000918122383</v>
       </c>
       <c r="J18" s="17">
-        <v>212.54457106783326</v>
+        <v>2123.7887994432162</v>
       </c>
       <c r="K18" s="17">
-        <v>1639.3855942730463</v>
+        <v>16381.075957825688</v>
       </c>
       <c r="L18" s="17">
-        <v>943.66296676565219</v>
+        <v>9428.9610392787527</v>
       </c>
       <c r="M18" s="17">
-        <v>3.1964045904803005</v>
+        <v>3.2898953561125701</v>
       </c>
       <c r="N18" s="17">
-        <v>1.5963807829348928</v>
+        <v>1.5963324264198737</v>
       </c>
       <c r="O18" s="17">
-        <v>73.974395706709728</v>
+        <v>739.74316456090378</v>
       </c>
       <c r="P18" s="17">
-        <v>34.216175837851559</v>
+        <v>342.19548588824279</v>
       </c>
       <c r="Q18" s="17">
-        <v>0</v>
+        <v>7.4619661227411427E-2</v>
       </c>
       <c r="R18" s="17">
-        <v>6.9630843835348282</v>
+        <v>69.636622761948459</v>
       </c>
       <c r="S18" s="17">
-        <v>33.642267122887539</v>
+        <v>379.53905784855749</v>
       </c>
       <c r="T18" s="17">
-        <v>4098.4639856826152</v>
+        <v>40952.68989456421</v>
       </c>
       <c r="U18" s="17">
-        <v>29.00045429948581</v>
+        <v>386.81822347694612</v>
       </c>
       <c r="V18" s="17">
-        <v>3129.0125294157187</v>
+        <v>31371.31195371427</v>
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.3">
@@ -2034,64 +2152,64 @@
         <v>650</v>
       </c>
       <c r="C19" s="17">
-        <v>30.356348204785782</v>
+        <v>303.5689357492202</v>
       </c>
       <c r="D19" s="17">
-        <v>12.44961559979507</v>
+        <v>124.48910840925201</v>
       </c>
       <c r="E19" s="17">
-        <v>15.124260333639103</v>
+        <v>153.39874970301798</v>
       </c>
       <c r="F19" s="17">
-        <v>27.591578472916037</v>
+        <v>279.8422102253549</v>
       </c>
       <c r="G19" s="17">
-        <v>9.4719934814589077</v>
+        <v>94.725497642047941</v>
       </c>
       <c r="H19" s="17">
-        <v>18.57419322769216</v>
+        <v>185.84739014316</v>
       </c>
       <c r="I19" s="17">
-        <v>49.691064890158593</v>
+        <v>497.04374229533039</v>
       </c>
       <c r="J19" s="17">
-        <v>281.0885470546134</v>
+        <v>2808.6836717508977</v>
       </c>
       <c r="K19" s="17">
-        <v>1782.8354646964092</v>
+        <v>17814.38949249798</v>
       </c>
       <c r="L19" s="17">
-        <v>974.191411747036</v>
+        <v>9733.9721439540208</v>
       </c>
       <c r="M19" s="17">
-        <v>3.1630198633730169</v>
+        <v>3.2538839114981575</v>
       </c>
       <c r="N19" s="17">
-        <v>1.5703191740388991</v>
+        <v>1.570268926036658</v>
       </c>
       <c r="O19" s="17">
-        <v>78.033235234910777</v>
+        <v>780.3352173446757</v>
       </c>
       <c r="P19" s="17">
-        <v>36.089167156528923</v>
+        <v>360.9288825433681</v>
       </c>
       <c r="Q19" s="17">
-        <v>0</v>
+        <v>7.6958539798279726E-2</v>
       </c>
       <c r="R19" s="17">
-        <v>7.2805324924249097</v>
+        <v>72.811563723715722</v>
       </c>
       <c r="S19" s="17">
-        <v>33.566067839114389</v>
+        <v>378.24841917647922</v>
       </c>
       <c r="T19" s="17">
-        <v>4457.0886617410233</v>
+        <v>44535.973731244943</v>
       </c>
       <c r="U19" s="17">
-        <v>30.212857749627148</v>
+        <v>403.8712905190423</v>
       </c>
       <c r="V19" s="17">
-        <v>3391.2896772185222</v>
+        <v>33997.057427054897</v>
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.3">
@@ -2099,64 +2217,64 @@
         <v>700</v>
       </c>
       <c r="C20" s="17">
-        <v>30.634572596853715</v>
+        <v>306.35131841675008</v>
       </c>
       <c r="D20" s="17">
-        <v>12.088966631737916</v>
+        <v>120.88239449501667</v>
       </c>
       <c r="E20" s="17">
-        <v>15.158362934418255</v>
+        <v>153.74467368248199</v>
       </c>
       <c r="F20" s="17">
-        <v>27.631189878644655</v>
+        <v>280.24408784225767</v>
       </c>
       <c r="G20" s="17">
-        <v>9.7585717022123273</v>
+        <v>97.59153362218035</v>
       </c>
       <c r="H20" s="17">
-        <v>24.020430877263426</v>
+        <v>240.31475528596201</v>
       </c>
       <c r="I20" s="17">
-        <v>56.681040389213244</v>
+        <v>566.95500958230537</v>
       </c>
       <c r="J20" s="17">
-        <v>369.23294106569756</v>
+        <v>3689.4255484164842</v>
       </c>
       <c r="K20" s="17">
-        <v>1942.7283156258552</v>
+        <v>19412.004412755879</v>
       </c>
       <c r="L20" s="17">
-        <v>1010.2197197239223</v>
+        <v>10093.94296158151</v>
       </c>
       <c r="M20" s="17">
-        <v>3.1298159081650674</v>
+        <v>3.2181430517416656</v>
       </c>
       <c r="N20" s="17">
-        <v>1.5445691713135157</v>
+        <v>1.544517183389571</v>
       </c>
       <c r="O20" s="17">
-        <v>82.204971307235269</v>
+        <v>822.05630927133234</v>
       </c>
       <c r="P20" s="17">
-        <v>38.054574357161769</v>
+        <v>380.58664247568697</v>
       </c>
       <c r="Q20" s="17">
-        <v>0</v>
+        <v>7.9294647204591173E-2</v>
       </c>
       <c r="R20" s="17">
-        <v>7.6064535049367379</v>
+        <v>76.071243546232026</v>
       </c>
       <c r="S20" s="17">
-        <v>33.475120850675864</v>
+        <v>376.81466876953999</v>
       </c>
       <c r="T20" s="17">
-        <v>4856.8207890646372</v>
+        <v>48530.011031889699</v>
       </c>
       <c r="U20" s="17">
-        <v>31.445876616620488</v>
+        <v>421.22798507395089</v>
       </c>
       <c r="V20" s="17">
-        <v>3695.6154931419278</v>
+        <v>37043.055499699934</v>
       </c>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.3">
@@ -2164,64 +2282,64 @@
         <v>750</v>
       </c>
       <c r="C21" s="17">
-        <v>30.906883731184411</v>
+        <v>309.07455465127805</v>
       </c>
       <c r="D21" s="17">
-        <v>11.733793427656783</v>
+        <v>117.33045407099952</v>
       </c>
       <c r="E21" s="17">
-        <v>15.181449948766968</v>
+        <v>153.97884766306913</v>
       </c>
       <c r="F21" s="17">
-        <v>27.656590211398434</v>
+        <v>280.50183820071442</v>
       </c>
       <c r="G21" s="17">
-        <v>10.044465293963134</v>
+        <v>100.45071167206741</v>
       </c>
       <c r="H21" s="17">
-        <v>29.414976429465458</v>
+        <v>294.26310690947577</v>
       </c>
       <c r="I21" s="17">
-        <v>63.923314061612821</v>
+        <v>639.38950186234808</v>
       </c>
       <c r="J21" s="17">
-        <v>482.7644158839729</v>
+        <v>4823.8346125543394</v>
       </c>
       <c r="K21" s="17">
-        <v>2124.0584594927946</v>
+        <v>21223.823419605003</v>
       </c>
       <c r="L21" s="17">
-        <v>1053.3975711688122</v>
+        <v>10525.356004225263</v>
       </c>
       <c r="M21" s="17">
-        <v>3.096825295401116</v>
+        <v>3.182702476477075</v>
       </c>
       <c r="N21" s="17">
-        <v>1.5191502375896373</v>
+        <v>1.519096652861311</v>
       </c>
       <c r="O21" s="17">
-        <v>86.486698692361983</v>
+        <v>864.87738547050515</v>
       </c>
       <c r="P21" s="17">
-        <v>40.11610028928925</v>
+        <v>401.20580558999745</v>
       </c>
       <c r="Q21" s="17">
-        <v>0</v>
+        <v>8.1625778220241155E-2</v>
       </c>
       <c r="R21" s="17">
-        <v>7.940877684283616</v>
+        <v>79.415965355949552</v>
       </c>
       <c r="S21" s="17">
-        <v>33.370260142907128</v>
+        <v>375.24661356442857</v>
       </c>
       <c r="T21" s="17">
-        <v>5310.1461487319866</v>
+        <v>53059.558549012494</v>
       </c>
       <c r="U21" s="17">
-        <v>32.698767335133454</v>
+        <v>438.8758961478494</v>
       </c>
       <c r="V21" s="17">
-        <v>4054.3105993265945</v>
+        <v>40632.408142450848</v>
       </c>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.3">
@@ -2229,64 +2347,64 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C22" s="17">
-        <v>31.17335186523071</v>
+        <v>311.73934843303778</v>
       </c>
       <c r="D22" s="17">
-        <v>11.384097947699106</v>
+        <v>113.83330527634081</v>
       </c>
       <c r="E22" s="17">
-        <v>15.196049134857022</v>
+        <v>154.12694860114715</v>
       </c>
       <c r="F22" s="17">
-        <v>27.671506806551477</v>
+        <v>280.65325482354871</v>
       </c>
       <c r="G22" s="17">
-        <v>10.329389197445023</v>
+        <v>103.30018156282743</v>
       </c>
       <c r="H22" s="17">
-        <v>34.679829083029183</v>
+        <v>346.91288051130834</v>
       </c>
       <c r="I22" s="17">
-        <v>71.412496173838846</v>
+        <v>714.29330882120883</v>
       </c>
       <c r="J22" s="17">
-        <v>629.63432798074223</v>
+        <v>6291.3606293226931</v>
       </c>
       <c r="K22" s="17">
-        <v>2333.6176965557079</v>
+        <v>23317.709736516052</v>
       </c>
       <c r="L22" s="17">
-        <v>1105.9100285509264</v>
+        <v>11050.043569183621</v>
       </c>
       <c r="M22" s="17">
-        <v>3.0640811169153399</v>
+        <v>3.1475926729674328</v>
       </c>
       <c r="N22" s="17">
-        <v>1.4940820414417189</v>
+        <v>1.4940269956205496</v>
       </c>
       <c r="O22" s="17">
-        <v>90.874967050593952</v>
+        <v>908.7639387171597</v>
       </c>
       <c r="P22" s="17">
-        <v>42.277260541399329</v>
+        <v>422.82153795985045</v>
       </c>
       <c r="Q22" s="17">
-        <v>0</v>
+        <v>8.3949658717157039E-2</v>
       </c>
       <c r="R22" s="17">
-        <v>8.2838071011636547</v>
+        <v>82.84575052116061</v>
       </c>
       <c r="S22" s="17">
-        <v>33.252324097050263</v>
+        <v>373.5531104491323</v>
       </c>
       <c r="T22" s="17">
-        <v>5834.0442413892697</v>
+        <v>58294.274341290125</v>
       </c>
       <c r="U22" s="17">
-        <v>33.970684470386352</v>
+        <v>456.8011680060402</v>
       </c>
       <c r="V22" s="17">
-        <v>4484.2259797149791</v>
+        <v>44933.484238032433</v>
       </c>
       <c r="W22" s="21"/>
       <c r="X22" s="21"/>
@@ -2365,22 +2483,22 @@
         <v>500</v>
       </c>
       <c r="C29" s="17">
-        <v>0.77714987291148052</v>
+        <v>0.77990753820849013</v>
       </c>
       <c r="D29" s="17">
-        <v>3.4879579281269653</v>
+        <v>3.5440154834621529</v>
       </c>
       <c r="E29" s="21">
-        <v>0.28670070585885776</v>
+        <v>0.28216581012876918</v>
       </c>
       <c r="F29" s="21">
-        <v>1.1542250716925242E-2</v>
+        <v>1.1512137739935889E-2</v>
       </c>
       <c r="G29">
-        <v>0.67842275179467249</v>
+        <v>0.67677225952588616</v>
       </c>
       <c r="H29">
-        <v>22.285012708851948</v>
+        <v>22.009246179150999</v>
       </c>
       <c r="I29" s="25"/>
       <c r="J29" s="25"/>
@@ -2390,22 +2508,22 @@
         <v>550</v>
       </c>
       <c r="C30" s="17">
-        <v>0.76880465045141189</v>
+        <v>0.77147227154971376</v>
       </c>
       <c r="D30" s="17">
-        <v>3.3259048960540598</v>
+        <v>3.3762454708291418</v>
       </c>
       <c r="E30" s="21">
-        <v>0.30067005258822227</v>
+        <v>0.29618699488530348</v>
       </c>
       <c r="F30" s="21">
-        <v>1.147679867865287E-2</v>
+        <v>1.1448741730107946E-2</v>
       </c>
       <c r="G30">
-        <v>0.6748353255769638</v>
+        <v>0.67329752422721656</v>
       </c>
       <c r="H30">
-        <v>23.11953495485881</v>
+        <v>22.852772845028625</v>
       </c>
       <c r="I30" s="25"/>
       <c r="J30" s="25"/>
@@ -2415,22 +2533,22 @@
         <v>600</v>
       </c>
       <c r="C31" s="17">
-        <v>0.76345980844200811</v>
+        <v>0.76603788504447645</v>
       </c>
       <c r="D31" s="17">
-        <v>3.2281161931169047</v>
+        <v>3.2745630047059779</v>
       </c>
       <c r="E31" s="21">
-        <v>0.30977819265992745</v>
+        <v>0.30538425999526303</v>
       </c>
       <c r="F31" s="21">
-        <v>1.1426248092306848E-2</v>
+        <v>1.1402542302703553E-2</v>
       </c>
       <c r="G31">
-        <v>0.6720646479393384</v>
+        <v>0.67076533361118174</v>
       </c>
       <c r="H31">
-        <v>23.654019155799176</v>
+        <v>23.396211495552354</v>
       </c>
       <c r="I31" s="25"/>
       <c r="J31" s="25"/>
@@ -2440,22 +2558,22 @@
         <v>650</v>
       </c>
       <c r="C32" s="17">
-        <v>0.76087552539146053</v>
+        <v>0.76336171815198695</v>
       </c>
       <c r="D32" s="17">
-        <v>3.1823908139220412</v>
+        <v>3.2261966267662174</v>
       </c>
       <c r="E32" s="21">
-        <v>0.31422916243513799</v>
+        <v>0.30996250870250008</v>
       </c>
       <c r="F32" s="21">
-        <v>1.1389377536649816E-2</v>
+        <v>1.1366515645355346E-2</v>
       </c>
       <c r="G32">
-        <v>0.67004377278377647</v>
+        <v>0.66879071252192657</v>
       </c>
       <c r="H32">
-        <v>23.912447460853958</v>
+        <v>23.663828184801304</v>
       </c>
       <c r="I32" s="25"/>
       <c r="J32" s="25"/>
@@ -2465,22 +2583,22 @@
         <v>700</v>
       </c>
       <c r="C33" s="17">
-        <v>0.76091246797962597</v>
+        <v>0.76330202099806788</v>
       </c>
       <c r="D33" s="17">
-        <v>3.1830130960190659</v>
+        <v>3.2251112643946462</v>
       </c>
       <c r="E33" s="21">
-        <v>0.31416773033409162</v>
+        <v>0.31006682189232937</v>
       </c>
       <c r="F33" s="21">
-        <v>1.1358039352888392E-2</v>
+        <v>1.1337655298378537E-2</v>
       </c>
       <c r="G33">
-        <v>0.66832612693181281</v>
+        <v>0.66720887690412767</v>
       </c>
       <c r="H33">
-        <v>23.908753202037392</v>
+        <v>23.669797900193213</v>
       </c>
       <c r="I33" s="25"/>
       <c r="J33" s="25"/>
@@ -2490,22 +2608,22 @@
         <v>750</v>
       </c>
       <c r="C34" s="17">
-        <v>0.76350263924369122</v>
+        <v>0.76578865813437991</v>
       </c>
       <c r="D34" s="17">
-        <v>3.2288076199591909</v>
+        <v>3.269954039722121</v>
       </c>
       <c r="E34" s="21">
-        <v>0.30971185580038957</v>
+        <v>0.30581469581908238</v>
       </c>
       <c r="F34" s="21">
-        <v>1.1333787980593049E-2</v>
+        <v>1.1313771415970319E-2</v>
       </c>
       <c r="G34">
-        <v>0.66699690921630506</v>
+        <v>0.66589980130933324</v>
       </c>
       <c r="H34">
-        <v>23.649736075630877</v>
+        <v>23.421134186562</v>
       </c>
       <c r="I34" s="25"/>
       <c r="J34" s="25"/>
@@ -2515,22 +2633,22 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C35" s="17">
-        <v>0.76863078066873625</v>
+        <v>0.77080441854314019</v>
       </c>
       <c r="D35" s="17">
-        <v>3.3225215400838581</v>
+        <v>3.3633860684833179</v>
       </c>
       <c r="E35" s="21">
-        <v>0.30097622782447353</v>
+        <v>0.29731942145165008</v>
       </c>
       <c r="F35" s="21">
-        <v>1.131159921198268E-2</v>
+        <v>1.1293500510283605E-2</v>
       </c>
       <c r="G35">
-        <v>0.66578074280877075</v>
+        <v>0.66478875296864437</v>
       </c>
       <c r="H35">
-        <v>23.136921933126388</v>
+        <v>22.919558145685983</v>
       </c>
       <c r="I35" s="25"/>
       <c r="J35" s="25"/>
@@ -2575,7 +2693,7 @@
     <col min="17" max="17" width="24.109375" customWidth="1"/>
     <col min="18" max="18" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.6640625" customWidth="1"/>
-    <col min="20" max="20" width="13.21875" customWidth="1"/>
+    <col min="20" max="20" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.3">
@@ -2633,7 +2751,7 @@
         <v>3.0305681085599816</v>
       </c>
       <c r="G3" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H3" s="4">
         <v>756.61237274082237</v>
@@ -2666,44 +2784,44 @@
         <v>2</v>
       </c>
       <c r="C4" s="4">
-        <v>1018.1289616795918</v>
+        <v>1018.1871360117831</v>
       </c>
       <c r="D4" s="5">
         <v>17.482517482517483</v>
       </c>
       <c r="E4" s="4">
-        <v>1281.2341664776559</v>
+        <v>1281.3081492359206</v>
       </c>
       <c r="F4" s="7">
-        <v>3.035664888414034</v>
+        <v>3.0357375517463359</v>
       </c>
       <c r="G4" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H4" s="4">
-        <v>686.28880264133011</v>
+        <v>686.34112082706883</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" ref="I4:I42" si="0">C4-273.15</f>
-        <v>744.97896167959186</v>
+        <v>745.0371360117831</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>42</v>
       </c>
       <c r="L4" s="7">
-        <v>1.7979758880009502</v>
+        <v>17.967369630276828</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>66</v>
       </c>
       <c r="O4" s="10">
-        <v>688.03965186006621</v>
+        <v>6872.9982427742098</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>98</v>
       </c>
       <c r="R4" s="6">
-        <v>916.98727526679568</v>
+        <v>3089.4573260227485</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
@@ -2723,7 +2841,7 @@
         <v>3.1028601038812176</v>
       </c>
       <c r="G5" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H5" s="4">
         <v>736.50270198870771</v>
@@ -2736,19 +2854,19 @@
         <v>43</v>
       </c>
       <c r="L5" s="7">
-        <v>0.70248152838918376</v>
+        <v>7.0174170080653857</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>67</v>
       </c>
       <c r="O5" s="10">
-        <v>1199.1350689643341</v>
+        <v>11978.456764170598</v>
       </c>
       <c r="Q5" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R5" s="6">
-        <v>830.65281683265493</v>
+        <v>2963.220148019665</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
@@ -2756,44 +2874,44 @@
         <v>4</v>
       </c>
       <c r="C6" s="4">
-        <v>976.11427576830124</v>
+        <v>976.21764828798996</v>
       </c>
       <c r="D6" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E6" s="4">
-        <v>1231.5688124201411</v>
+        <v>1231.6977516748684</v>
       </c>
       <c r="F6" s="7">
-        <v>3.1121411727413726</v>
+        <v>3.112273260172465</v>
       </c>
       <c r="G6" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H6" s="4">
-        <v>613.82204441161923</v>
+        <v>613.91160179876624</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="0"/>
-        <v>702.96427576830126</v>
+        <v>703.06764828798998</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>47</v>
       </c>
       <c r="L6" s="7">
-        <v>2.5004574163901339</v>
+        <v>24.984786638342218</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="O6" s="10">
-        <v>71.774211786387255</v>
+        <v>717.79640670783738</v>
       </c>
       <c r="Q6" s="13" t="s">
         <v>100</v>
       </c>
       <c r="R6" s="6">
-        <v>6850.0253590880538</v>
+        <v>48628.817203007362</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -2801,44 +2919,44 @@
         <v>5</v>
       </c>
       <c r="C7" s="4">
-        <v>580.59332858273865</v>
+        <v>580.60739984606084</v>
       </c>
       <c r="D7" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E7" s="4">
-        <v>758.75704305028523</v>
+        <v>758.77316593152807</v>
       </c>
       <c r="F7" s="7">
-        <v>2.4934653765384365</v>
+        <v>2.493493145865219</v>
       </c>
       <c r="G7" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H7" s="4">
-        <v>325.46846367966873</v>
+        <v>325.47630713613137</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="0"/>
-        <v>307.44332858273867</v>
+        <v>307.45739984606087</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>44</v>
       </c>
       <c r="L7" s="7">
-        <v>4.8493514799902702</v>
+        <v>48.505085709943238</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>69</v>
       </c>
       <c r="O7" s="10">
-        <v>-386.40079286911646</v>
+        <v>-3864.0801901504483</v>
       </c>
       <c r="Q7" s="13" t="s">
         <v>105</v>
       </c>
       <c r="R7" s="6">
-        <v>2723.6906468307247</v>
+        <v>14404.513844749421</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
@@ -2846,44 +2964,44 @@
         <v>6</v>
       </c>
       <c r="C8" s="4">
-        <v>435.43287838933054</v>
+        <v>435.4382571755965</v>
       </c>
       <c r="D8" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E8" s="4">
-        <v>591.19593244306282</v>
+        <v>591.20237940579909</v>
       </c>
       <c r="F8" s="7">
-        <v>2.1610419768753544</v>
+        <v>2.1610567826542426</v>
       </c>
       <c r="G8" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H8" s="4">
-        <v>257.0193896819942</v>
+        <v>257.02142230175508</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
+        <v>162.28825717559653</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>45</v>
       </c>
       <c r="L8" s="7">
-        <v>1.6756111060722243</v>
+        <v>16.757078652572897</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>70</v>
       </c>
       <c r="O8" s="10">
-        <v>-188.73788675888972</v>
+        <v>-1887.2729900081154</v>
       </c>
       <c r="Q8" s="13" t="s">
         <v>104</v>
       </c>
       <c r="R8" s="6">
-        <v>150.85917384920415</v>
+        <v>125.94776703314032</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
@@ -2891,44 +3009,44 @@
         <v>29</v>
       </c>
       <c r="C9" s="4">
-        <v>435.43287838933054</v>
+        <v>435.4382571755965</v>
       </c>
       <c r="D9" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E9" s="4">
-        <v>591.19593244306282</v>
+        <v>591.20237940579909</v>
       </c>
       <c r="F9" s="7">
-        <v>2.1610419768753544</v>
+        <v>2.1610567826542426</v>
       </c>
       <c r="G9" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H9" s="4">
-        <v>257.0193896819942</v>
+        <v>257.02142230175508</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
+        <v>162.28825717559653</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>48</v>
       </c>
       <c r="L9" s="7">
-        <v>0.11033034486553291</v>
+        <v>1.1033708748874791</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>71</v>
       </c>
       <c r="O9" s="10">
-        <v>-5.8779815586019524E-2</v>
+        <v>-0.58783407799472909</v>
       </c>
       <c r="Q9" s="13" t="s">
         <v>101</v>
       </c>
       <c r="R9" s="6">
-        <v>4757.3674529323171</v>
+        <v>54938.398428688655</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
@@ -2936,44 +3054,44 @@
         <v>30</v>
       </c>
       <c r="C10" s="4">
-        <v>423.3557736165609</v>
+        <v>423.35913575479753</v>
       </c>
       <c r="D10" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E10" s="4">
-        <v>0.57659650223683723</v>
+        <v>0.57660060448894723</v>
       </c>
       <c r="F10" s="7">
-        <v>2.1270382629381421E-3</v>
+        <v>2.1270479527453361E-3</v>
       </c>
       <c r="G10" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H10" s="4">
-        <v>0.25257199616171355</v>
+        <v>0.25257320939780875</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="0"/>
-        <v>150.20577361656092</v>
+        <v>150.20913575479756</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="7">
-        <v>0.68666556854253946</v>
+        <v>6.8670753276560994</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>72</v>
       </c>
       <c r="O10" s="10">
-        <v>1312.0360411963943</v>
+        <v>13100.101826786246</v>
       </c>
       <c r="Q10" s="13" t="s">
         <v>102</v>
       </c>
       <c r="R10" s="6">
-        <v>58326.910191272655</v>
+        <v>582641.93083540094</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
@@ -2993,7 +3111,7 @@
         <v>1.8961819516546078E-3</v>
       </c>
       <c r="G11" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H11" s="4">
         <v>0.23185738014859708</v>
@@ -3006,19 +3124,19 @@
         <v>50</v>
       </c>
       <c r="L11" s="7">
-        <v>0.12544275752191905</v>
+        <v>1.2546499075118689</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="O11" s="10">
-        <v>71.715431970801234</v>
+        <v>717.20857262984271</v>
       </c>
       <c r="Q11" s="13" t="s">
         <v>103</v>
       </c>
       <c r="R11" s="6">
-        <v>101653.79754728591</v>
+        <v>1015444.9238863285</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
@@ -3026,44 +3144,44 @@
         <v>32</v>
       </c>
       <c r="C12" s="4">
-        <v>346.62433578909861</v>
+        <v>346.62379557580101</v>
       </c>
       <c r="D12" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E12" s="4">
-        <v>0.46883148724964824</v>
+        <v>0.46883049635692192</v>
       </c>
       <c r="F12" s="7">
-        <v>1.844389053247172E-3</v>
+        <v>1.8443861945514714E-3</v>
       </c>
       <c r="G12" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H12" s="4">
-        <v>0.22907884304388729</v>
+        <v>0.22907870447128417</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" si="0"/>
-        <v>73.474335789098632</v>
+        <v>73.473795575801034</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L12" s="7">
-        <v>0.92243867092999143</v>
+        <v>9.2250961100554463</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>74</v>
       </c>
       <c r="O12" s="12">
-        <v>1383.7514731671954</v>
+        <v>13817.310399416088</v>
       </c>
       <c r="Q12" s="13" t="s">
         <v>106</v>
       </c>
       <c r="R12" s="6">
-        <v>6084.4865460826932</v>
+        <v>60849.467667280827</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
@@ -3071,38 +3189,38 @@
         <v>33</v>
       </c>
       <c r="C13" s="4">
-        <v>344.39458549639238</v>
+        <v>346.39737970663185</v>
       </c>
       <c r="D13" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E13" s="4">
-        <v>464.67130036926602</v>
+        <v>468.41449334690572</v>
       </c>
       <c r="F13" s="7">
-        <v>1.8323480555267959</v>
+        <v>1.8431856450668949</v>
       </c>
       <c r="G13" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H13" s="4">
-        <v>228.50867963383527</v>
+        <v>229.02064529009442</v>
       </c>
       <c r="I13" s="4">
         <f t="shared" si="0"/>
-        <v>71.244585496392403</v>
+        <v>73.247379706631875</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>52</v>
       </c>
       <c r="L13" s="7">
-        <v>0.72305037797389082</v>
+        <v>7.2309456578341926</v>
       </c>
       <c r="Q13" s="13" t="s">
         <v>107</v>
       </c>
       <c r="R13" s="6">
-        <v>-14690.262623456645</v>
+        <v>-146905.37348517781</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
@@ -3110,32 +3228,32 @@
         <v>34</v>
       </c>
       <c r="C14" s="4">
-        <v>435.43287838933054</v>
+        <v>435.4382571755965</v>
       </c>
       <c r="D14" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E14" s="4">
-        <v>591.19593244306282</v>
+        <v>591.20237940579909</v>
       </c>
       <c r="F14" s="7">
-        <v>2.1610419768753544</v>
+        <v>2.1610567826542426</v>
       </c>
       <c r="G14" s="4">
-        <v>2.0055144227139889</v>
+        <v>20.053649165005705</v>
       </c>
       <c r="H14" s="4">
-        <v>257.0193896819942</v>
+        <v>257.02142230175508</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
+        <v>162.28825717559653</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>54</v>
       </c>
       <c r="L14" s="7">
-        <v>0.12767286098529926</v>
+        <v>1.2769418795914116</v>
       </c>
       <c r="N14" s="29" t="s">
         <v>75</v>
@@ -3145,7 +3263,7 @@
         <v>108</v>
       </c>
       <c r="R14" s="6">
-        <v>-7175.4747263768222</v>
+        <v>-71750.721988726538</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
@@ -3165,7 +3283,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G15" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H15" s="4">
         <v>224.33075530171814</v>
@@ -3178,19 +3296,19 @@
         <v>53</v>
       </c>
       <c r="L15" s="7">
-        <v>0.85072323895919011</v>
+        <v>8.5078875374256029</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="O15" s="10">
-        <v>7.7745474285568061</v>
+        <v>7.7745376749850683</v>
       </c>
       <c r="Q15" s="13" t="s">
         <v>109</v>
       </c>
       <c r="R15" s="6">
-        <v>-2.2347027849124075</v>
+        <v>-22.348393544019206</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
@@ -3210,7 +3328,7 @@
         <v>1.7343043486568708</v>
       </c>
       <c r="G16" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H16" s="4">
         <v>268.76481394998945</v>
@@ -3223,19 +3341,19 @@
         <v>46</v>
       </c>
       <c r="L16" s="7">
-        <v>3.3258554014030113E-2</v>
+        <v>3.3257922587167379E-2</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>81</v>
       </c>
       <c r="O16" s="10">
-        <v>52.471841055808</v>
+        <v>52.432314177470438</v>
       </c>
       <c r="Q16" s="13" t="s">
         <v>110</v>
       </c>
       <c r="R16" s="6">
-        <v>14936.432649657721</v>
+        <v>149375.6241707881</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
@@ -3243,44 +3361,44 @@
         <v>9</v>
       </c>
       <c r="C17" s="4">
-        <v>547.68745921507718</v>
+        <v>547.69370647629023</v>
       </c>
       <c r="D17" s="5">
         <v>25</v>
       </c>
       <c r="E17" s="4">
-        <v>685.30539614040072</v>
+        <v>685.31357954095802</v>
       </c>
       <c r="F17" s="7">
-        <v>2.1800807088725671</v>
+        <v>2.180095650521598</v>
       </c>
       <c r="G17" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H17" s="4">
-        <v>345.45245543436323</v>
+        <v>345.4561839822619</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" si="0"/>
-        <v>274.53745921507721</v>
+        <v>274.54370647629025</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>55</v>
       </c>
       <c r="L17" s="16">
-        <v>-0.29815580239591893</v>
+        <v>-3.2808684015299132</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>82</v>
       </c>
       <c r="O17" s="10">
-        <v>53.374586045417935</v>
+        <v>36.901993581878948</v>
       </c>
       <c r="Q17" s="13" t="s">
         <v>111</v>
       </c>
       <c r="R17" s="6">
-        <v>12158.725147647143</v>
+        <v>121456.51249638916</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
@@ -3288,38 +3406,38 @@
         <v>10</v>
       </c>
       <c r="C18" s="4">
-        <v>547.68745921507718</v>
+        <v>547.69370647629023</v>
       </c>
       <c r="D18" s="5">
         <v>25</v>
       </c>
       <c r="E18" s="4">
-        <v>685.30539614040072</v>
+        <v>685.31357954095802</v>
       </c>
       <c r="F18" s="7">
-        <v>2.1800807088725671</v>
+        <v>2.180095650521598</v>
       </c>
       <c r="G18" s="4">
-        <v>2.0055144227139889</v>
+        <v>20.053649165005705</v>
       </c>
       <c r="H18" s="4">
-        <v>345.45245543436323</v>
+        <v>345.4561839822619</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" si="0"/>
-        <v>274.53745921507721</v>
+        <v>274.54370647629025</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>83</v>
       </c>
       <c r="O18" s="10">
-        <v>54.014275766007323</v>
+        <v>53.497400064021491</v>
       </c>
       <c r="Q18" s="13" t="s">
         <v>112</v>
       </c>
       <c r="R18" s="6">
-        <v>2143439.7108252258</v>
+        <v>21403100.470866345</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
@@ -3327,26 +3445,26 @@
         <v>11</v>
       </c>
       <c r="C19" s="4">
-        <v>547.68745921507718</v>
+        <v>547.69370647629023</v>
       </c>
       <c r="D19" s="5">
         <v>25</v>
       </c>
       <c r="E19" s="4">
-        <v>685.30539614040072</v>
+        <v>685.31357954095802</v>
       </c>
       <c r="F19" s="7">
-        <v>2.1800807088725671</v>
+        <v>2.180095650521598</v>
       </c>
       <c r="G19" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H19" s="4">
-        <v>345.45245543436323</v>
+        <v>345.4561839822619</v>
       </c>
       <c r="I19" s="4">
         <f t="shared" si="0"/>
-        <v>274.53745921507721</v>
+        <v>274.54370647629025</v>
       </c>
       <c r="K19" s="29" t="s">
         <v>58</v>
@@ -3356,13 +3474,13 @@
         <v>84</v>
       </c>
       <c r="O19" s="10">
-        <v>55.339933569630354</v>
+        <v>55.302895315550685</v>
       </c>
       <c r="Q19" s="13" t="s">
         <v>123</v>
       </c>
       <c r="R19" s="6">
-        <v>2503125.0768078174</v>
+        <v>24957461.093185224</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
@@ -3370,38 +3488,38 @@
         <v>12</v>
       </c>
       <c r="C20" s="4">
-        <v>932.83907702081467</v>
+        <v>932.93660164805499</v>
       </c>
       <c r="D20" s="5">
         <v>25</v>
       </c>
       <c r="E20" s="4">
-        <v>1170.2405428635675</v>
+        <v>1170.3644353608943</v>
       </c>
       <c r="F20" s="7">
-        <v>2.8510501836319815</v>
+        <v>2.8511829889834948</v>
       </c>
       <c r="G20" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H20" s="4">
-        <v>630.33805325801075</v>
+        <v>630.42234983978369</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" si="0"/>
-        <v>659.68907702081469</v>
+        <v>659.78660164805501</v>
       </c>
       <c r="K20" s="13" t="s">
         <v>59</v>
       </c>
       <c r="L20" s="4">
-        <v>159.02185344711796</v>
+        <v>1128.9074473722574</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>85</v>
       </c>
       <c r="O20" s="10">
-        <v>3.4933609588634824</v>
+        <v>3.4935322440475987</v>
       </c>
       <c r="Q20" s="28" t="s">
         <v>117</v>
@@ -3429,7 +3547,7 @@
         <v>-0.37994748587359245</v>
       </c>
       <c r="G21" s="4">
-        <v>1.7897056695309543</v>
+        <v>17.89815043892197</v>
       </c>
       <c r="H21" s="4">
         <v>0.52460446529691762</v>
@@ -3442,13 +3560,13 @@
         <v>60</v>
       </c>
       <c r="L21" s="4">
-        <v>63.229887799023224</v>
+        <v>334.39766563166074</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>86</v>
       </c>
       <c r="O21" s="10">
-        <v>22.489305649899514</v>
+        <v>22.472364524327524</v>
       </c>
       <c r="Q21" s="22" t="s">
         <v>118</v>
@@ -3477,13 +3595,13 @@
         <v>-132.32179590986752</v>
       </c>
       <c r="F22" s="7">
-        <v>-0.37994748587359245</v>
+        <v>-0.37993175416231956</v>
       </c>
       <c r="G22" s="4">
-        <v>1.7897056695309543</v>
+        <v>17.89815043892197</v>
       </c>
       <c r="H22" s="4">
-        <v>0.55744775153482984</v>
+        <v>0.55275734181882941</v>
       </c>
       <c r="I22" s="4">
         <f t="shared" si="0"/>
@@ -3493,19 +3611,19 @@
         <v>61</v>
       </c>
       <c r="L22" s="4">
-        <v>21.287660768567079</v>
+        <v>71.721081948712694</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>87</v>
       </c>
       <c r="O22" s="6">
-        <v>52.415130655682205</v>
+        <v>36.167181648495081</v>
       </c>
       <c r="Q22" s="23" t="s">
         <v>113</v>
       </c>
       <c r="R22" s="24">
-        <v>2505530.7763891984</v>
+        <v>24046.390970622553</v>
       </c>
       <c r="S22" s="23" t="s">
         <v>129</v>
@@ -3531,7 +3649,7 @@
         <v>-0.19317568283781225</v>
       </c>
       <c r="G23" s="4">
-        <v>1.7897056695309543</v>
+        <v>17.89815043892197</v>
       </c>
       <c r="H23" s="4">
         <v>6.518635522826691</v>
@@ -3544,19 +3662,19 @@
         <v>62</v>
       </c>
       <c r="L23" s="4">
-        <v>19.283425035580251</v>
+        <v>68.790513232882915</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>88</v>
       </c>
       <c r="O23" s="6">
-        <v>23.133959295545651</v>
+        <v>22.917512377362197</v>
       </c>
       <c r="Q23" s="23" t="s">
         <v>114</v>
       </c>
       <c r="R23" s="24">
-        <v>4269212.9393934794</v>
+        <v>42594227.213088371</v>
       </c>
       <c r="S23" s="23" t="s">
         <v>128</v>
@@ -3582,7 +3700,7 @@
         <v>0.91173151933586583</v>
       </c>
       <c r="G24" s="4">
-        <v>1.7897056695309543</v>
+        <v>17.89815043892197</v>
       </c>
       <c r="H24" s="4">
         <v>60.765690527522125</v>
@@ -3595,25 +3713,25 @@
         <v>63</v>
       </c>
       <c r="L24" s="4">
-        <v>3.5021630107067545</v>
+        <v>2.9238501029143915</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>89</v>
       </c>
       <c r="O24" s="15">
-        <v>23.136921933126388</v>
+        <v>22.919558145685983</v>
       </c>
       <c r="Q24" s="23" t="s">
         <v>115</v>
       </c>
       <c r="R24" s="24">
-        <v>202782.7454297191</v>
+        <v>2023167.7075799552</v>
       </c>
       <c r="S24" s="23" t="s">
         <v>127</v>
       </c>
       <c r="T24" s="27">
-        <v>2503125.0768078174</v>
+        <v>24957461.093185224</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3625,37 +3743,39 @@
         <v>15</v>
       </c>
       <c r="C25" s="4">
-        <v>396.43287838933054</v>
+        <v>396.4382571755965</v>
       </c>
       <c r="D25" s="5">
         <v>31.569242975234697</v>
       </c>
       <c r="E25" s="4">
-        <v>383.09182021380718</v>
+        <v>383.09995906623425</v>
       </c>
       <c r="F25" s="7">
-        <v>1.1002468147744369</v>
+        <v>1.100267344850671</v>
       </c>
       <c r="G25" s="4">
-        <v>1.7897056695309543</v>
+        <v>17.89815043892197</v>
       </c>
       <c r="H25" s="4">
-        <v>74.651133136999675</v>
+        <v>74.65315094719746</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" si="0"/>
-        <v>123.28287838933056</v>
+        <v>123.28825717559653</v>
       </c>
       <c r="K25" s="13" t="s">
         <v>64</v>
       </c>
       <c r="L25" s="4">
-        <v>110.44125389851233</v>
+        <v>1275.3830074447171</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="26"/>
+      <c r="T25" s="26">
+        <v>48195801.93395783</v>
+      </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
       <c r="X25" s="9"/>
@@ -3666,26 +3786,26 @@
         <v>16</v>
       </c>
       <c r="C26" s="4">
-        <v>368.13790080168786</v>
+        <v>368.14329244204333</v>
       </c>
       <c r="D26" s="5">
         <v>7.8923107438086744</v>
       </c>
       <c r="E26" s="4">
-        <v>342.98790088879446</v>
+        <v>342.99545725431005</v>
       </c>
       <c r="F26" s="7">
-        <v>1.119604713516257</v>
+        <v>1.1196252392794583</v>
       </c>
       <c r="G26" s="4">
-        <v>1.7897056695309543</v>
+        <v>17.89815043892197</v>
       </c>
       <c r="H26" s="4">
-        <v>28.775656302113202</v>
+        <v>28.777092911330342</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" si="0"/>
-        <v>94.987900801687886</v>
+        <v>94.993292442043355</v>
       </c>
       <c r="N26" s="29" t="s">
         <v>76</v>
@@ -3717,7 +3837,7 @@
         <v>0.91018564327057938</v>
       </c>
       <c r="G27" s="4">
-        <v>1.7897056695309543</v>
+        <v>17.89815043892197</v>
       </c>
       <c r="H27" s="4">
         <v>19.876601402460075</v>
@@ -3759,7 +3879,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G28" s="4">
-        <v>34.591753259051274</v>
+        <v>345.9386726638856</v>
       </c>
       <c r="H28" s="4">
         <v>2.5073905791015251E-5</v>
@@ -3801,7 +3921,7 @@
         <v>0.43672528196163279</v>
       </c>
       <c r="G29" s="4">
-        <v>34.591753259051274</v>
+        <v>345.9386726638856</v>
       </c>
       <c r="H29" s="4">
         <v>0.17334706272843686</v>
@@ -3831,26 +3951,26 @@
         <v>39</v>
       </c>
       <c r="C30" s="4">
-        <v>304.03303316959324</v>
+        <v>304.03312670606874</v>
       </c>
       <c r="D30" s="5">
         <v>101.325</v>
       </c>
       <c r="E30" s="4">
-        <v>129.51335809758132</v>
+        <v>129.51374904828285</v>
       </c>
       <c r="F30" s="7">
-        <v>0.44888256955875044</v>
+        <v>0.44888385544072534</v>
       </c>
       <c r="G30" s="4">
-        <v>34.591753259051274</v>
+        <v>345.9386726638856</v>
       </c>
       <c r="H30" s="4">
-        <v>0.23949854144378332</v>
+        <v>0.23950610643450637</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" si="0"/>
-        <v>30.883033169593261</v>
+        <v>30.883126706068765</v>
       </c>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
@@ -3867,26 +3987,26 @@
         <v>29</v>
       </c>
       <c r="C31" s="4">
-        <v>435.43287838933054</v>
+        <v>435.4382571755965</v>
       </c>
       <c r="D31" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E31" s="4">
-        <v>591.19593244282169</v>
+        <v>591.20237940555796</v>
       </c>
       <c r="F31" s="7">
-        <v>2.1610419768753544</v>
+        <v>2.1610567826542426</v>
       </c>
       <c r="G31" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H31" s="4">
-        <v>257.03321905731815</v>
+        <v>257.03525167707909</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" si="0"/>
-        <v>162.28287838933056</v>
+        <v>162.28825717559653</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3903,26 +4023,26 @@
         <v>30</v>
       </c>
       <c r="C32" s="4">
-        <v>423.3557736165609</v>
+        <v>423.35913575479753</v>
       </c>
       <c r="D32" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E32" s="4">
-        <v>576.59650223683718</v>
+        <v>576.60060448894728</v>
       </c>
       <c r="F32" s="7">
-        <v>2.1270382629381421</v>
+        <v>2.1270479527453361</v>
       </c>
       <c r="G32" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H32" s="4">
-        <v>252.57199616171354</v>
+        <v>252.57320939780874</v>
       </c>
       <c r="I32" s="4">
         <f t="shared" si="0"/>
-        <v>150.20577361656092</v>
+        <v>150.20913575479756</v>
       </c>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
@@ -3951,7 +4071,7 @@
         <v>1.8961819516546079</v>
       </c>
       <c r="G33" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H33" s="4">
         <v>231.85738014859709</v>
@@ -3975,26 +4095,26 @@
         <v>32</v>
       </c>
       <c r="C34" s="4">
-        <v>346.62433578909861</v>
+        <v>346.62379557580101</v>
       </c>
       <c r="D34" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E34" s="4">
-        <v>468.83148724964826</v>
+        <v>468.83049635692191</v>
       </c>
       <c r="F34" s="7">
-        <v>1.8443890532471721</v>
+        <v>1.8443861945514715</v>
       </c>
       <c r="G34" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H34" s="4">
-        <v>229.07884304388728</v>
+        <v>229.07870447128417</v>
       </c>
       <c r="I34" s="4">
         <f t="shared" si="0"/>
-        <v>73.474335789098632</v>
+        <v>73.473795575801034</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.3">
@@ -4035,16 +4155,16 @@
         <v>0.101325</v>
       </c>
       <c r="E36" s="4">
-        <v>453.10722153513228</v>
+        <v>453.10667720162991</v>
       </c>
       <c r="F36" s="7">
-        <v>3.9723323134988857</v>
+        <v>3.9723306469545014</v>
       </c>
       <c r="G36" s="4">
         <v>1.1599999999999999</v>
       </c>
       <c r="H36" s="4">
-        <v>1.3091135519945019</v>
+        <v>1.3090660987003904</v>
       </c>
       <c r="I36" s="4">
         <f t="shared" si="0"/>
@@ -4056,26 +4176,26 @@
         <v>32</v>
       </c>
       <c r="C37" s="4">
-        <v>346.62433578909861</v>
+        <v>346.62379557580101</v>
       </c>
       <c r="D37" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E37" s="4">
-        <v>468.83148724964826</v>
+        <v>468.83049635692191</v>
       </c>
       <c r="F37" s="7">
-        <v>1.8443890532471721</v>
+        <v>1.8443861945514715</v>
       </c>
       <c r="G37" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H37" s="4">
-        <v>229.07884304388728</v>
+        <v>229.07870447128417</v>
       </c>
       <c r="I37" s="4">
         <f t="shared" si="0"/>
-        <v>73.474335789098632</v>
+        <v>73.473795575801034</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.3">
@@ -4083,26 +4203,26 @@
         <v>33</v>
       </c>
       <c r="C38" s="4">
-        <v>344.39458549639238</v>
+        <v>346.39737970663185</v>
       </c>
       <c r="D38" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E38" s="4">
-        <v>464.67130036926602</v>
+        <v>468.41449334690572</v>
       </c>
       <c r="F38" s="7">
-        <v>1.8323480555267959</v>
+        <v>1.8431856450668949</v>
       </c>
       <c r="G38" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H38" s="4">
-        <v>228.50867963383527</v>
+        <v>229.02064529009442</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" si="0"/>
-        <v>71.244585496392403</v>
+        <v>73.247379706631875</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.3">
@@ -4110,26 +4230,26 @@
         <v>33</v>
       </c>
       <c r="C39" s="4">
-        <v>344.39458549639238</v>
+        <v>346.39737970663185</v>
       </c>
       <c r="D39" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E39" s="4">
-        <v>464.67130036356895</v>
+        <v>468.41449334022548</v>
       </c>
       <c r="F39" s="7">
-        <v>1.8323480555267959</v>
+        <v>1.8431856450668949</v>
       </c>
       <c r="G39" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H39" s="4">
-        <v>228.5086796281382</v>
+        <v>229.02064528341415</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" si="0"/>
-        <v>71.244585496392403</v>
+        <v>73.247379706631875</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.3">
@@ -4149,7 +4269,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G40" s="4">
-        <v>7.9944855772860111</v>
+        <v>79.946350834994291</v>
       </c>
       <c r="H40" s="4">
         <v>224.34458467728319</v>
@@ -4176,7 +4296,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G41" s="4">
-        <v>2.8698525619149113E-3</v>
+        <v>1.9801295635402501E-2</v>
       </c>
       <c r="H41" s="4">
         <v>2.5073905791015251E-5</v>
@@ -4191,26 +4311,26 @@
         <v>20</v>
       </c>
       <c r="C42" s="4">
-        <v>343.39458549639238</v>
+        <v>345.39737970663185</v>
       </c>
       <c r="D42" s="5">
         <v>101.325</v>
       </c>
       <c r="E42" s="4">
-        <v>294.14738747128831</v>
+        <v>302.54072536549046</v>
       </c>
       <c r="F42" s="7">
-        <v>0.95807613660276081</v>
+        <v>0.98244738595667158</v>
       </c>
       <c r="G42" s="4">
-        <v>2.8698525619149113E-3</v>
+        <v>1.9801295635402501E-2</v>
       </c>
       <c r="H42" s="4">
-        <v>13.057465900979093</v>
+        <v>14.184515800312743</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="0"/>
-        <v>70.244585496392403</v>
+        <v>72.247379706631875</v>
       </c>
     </row>
   </sheetData>
@@ -4231,6 +4351,540 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BBA90F-813A-493D-869A-57A3178EDC43}">
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2">
+        <v>5.1731913323680587E-2</v>
+      </c>
+      <c r="C2">
+        <v>3914.1005686252538</v>
+      </c>
+      <c r="E2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2">
+        <v>2503.1935161652605</v>
+      </c>
+      <c r="G2">
+        <v>154.12694860114715</v>
+      </c>
+      <c r="H2">
+        <v>7.9732819458779174</v>
+      </c>
+      <c r="I2">
+        <v>99.682486963754258</v>
+      </c>
+      <c r="K2" s="31">
+        <v>0.34909743323706877</v>
+      </c>
+      <c r="L2" s="31">
+        <v>0.91088630043789787</v>
+      </c>
+      <c r="M2" s="31">
+        <v>0.27584737694031641</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3">
+        <v>5.1731913323680594E-2</v>
+      </c>
+      <c r="C3">
+        <v>3550.5739373103711</v>
+      </c>
+      <c r="E3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3">
+        <v>888.25965020835133</v>
+      </c>
+      <c r="G3">
+        <v>280.65325482354871</v>
+      </c>
+      <c r="H3">
+        <v>13.912184589022015</v>
+      </c>
+      <c r="I3">
+        <v>98.457922975156208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4">
+        <v>4.9570722412497346E-2</v>
+      </c>
+      <c r="C4">
+        <v>3650.8970996336493</v>
+      </c>
+      <c r="E4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4">
+        <v>27.111169102991425</v>
+      </c>
+      <c r="G4">
+        <v>311.73934843303778</v>
+      </c>
+      <c r="H4">
+        <v>85.992481554336806</v>
+      </c>
+      <c r="I4">
+        <v>23.970198084171948</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5">
+        <v>4.9570722412497353E-2</v>
+      </c>
+      <c r="C5">
+        <v>3043.2041598578253</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5">
+        <v>6.8005339576619255</v>
+      </c>
+      <c r="G5">
+        <v>113.83330527634081</v>
+      </c>
+      <c r="H5">
+        <v>31.400618668924892</v>
+      </c>
+      <c r="I5">
+        <v>17.801907770000021</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6">
+        <v>4.9570722412497326E-2</v>
+      </c>
+      <c r="C6">
+        <v>1613.4095672889889</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6">
+        <v>10.532285533619728</v>
+      </c>
+      <c r="G6">
+        <v>346.91288051130834</v>
+      </c>
+      <c r="H6">
+        <v>17.19672210114593</v>
+      </c>
+      <c r="I6">
+        <v>37.98291548095186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7">
+        <v>4.9570722412497346E-2</v>
+      </c>
+      <c r="C7">
+        <v>1274.0737578985556</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7">
+        <v>5.1377091499340155</v>
+      </c>
+      <c r="G7">
+        <v>714.29330882120883</v>
+      </c>
+      <c r="H7">
+        <v>35.40803533268037</v>
+      </c>
+      <c r="I7">
+        <v>12.67138935415778</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8">
+        <v>5.6564567203107923E-5</v>
+      </c>
+      <c r="C8">
+        <v>1.01445300323212</v>
+      </c>
+      <c r="E8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F8">
+        <v>2.0715042857927268</v>
+      </c>
+      <c r="G8">
+        <v>908.7639387171597</v>
+      </c>
+      <c r="H8">
+        <v>45.048084944636095</v>
+      </c>
+      <c r="I8">
+        <v>4.3962698309241492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9">
+        <v>5.09160848747457E-2</v>
+      </c>
+      <c r="C9">
+        <v>1094.0220068462638</v>
+      </c>
+      <c r="E9" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9">
+        <v>14.87368048383521</v>
+      </c>
+      <c r="G9">
+        <v>103.30018156282743</v>
+      </c>
+      <c r="H9">
+        <v>128.39674035958012</v>
+      </c>
+      <c r="I9">
+        <v>10.381543096108523</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10">
+        <v>5.2085507350043407E-2</v>
+      </c>
+      <c r="C10">
+        <v>1438.4955253866315</v>
+      </c>
+      <c r="E10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10">
+        <v>3.0925794872948675E-2</v>
+      </c>
+      <c r="G10">
+        <v>8.3949658717157039E-2</v>
+      </c>
+      <c r="H10">
+        <v>2.3157293152162538E-2</v>
+      </c>
+      <c r="I10">
+        <v>57.182006431640112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11">
+        <v>0.11301051802733234</v>
+      </c>
+      <c r="C11">
+        <v>782.89811933408907</v>
+      </c>
+      <c r="E11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11">
+        <v>0.64803276948092892</v>
+      </c>
+      <c r="G11">
+        <v>422.82153795985045</v>
+      </c>
+      <c r="H11">
+        <v>525.54512883262078</v>
+      </c>
+      <c r="I11">
+        <v>0.12315492043033435</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12">
+        <v>6.4303195245009187E-2</v>
+      </c>
+      <c r="C12">
+        <v>2221.3936447207207</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12">
+        <v>0.12782276758325392</v>
+      </c>
+      <c r="G12">
+        <v>3.1475926729674328</v>
+      </c>
+      <c r="H12">
+        <v>0.15602844265927923</v>
+      </c>
+      <c r="I12">
+        <v>45.031609156796392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13">
+        <v>5.8083608929057957E-2</v>
+      </c>
+      <c r="C13">
+        <v>3661.7205228231765</v>
+      </c>
+      <c r="E13" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13">
+        <v>2.9067425972745697</v>
+      </c>
+      <c r="G13">
+        <v>373.5531104491323</v>
+      </c>
+      <c r="H13">
+        <v>2.1129870019932807E-2</v>
+      </c>
+      <c r="I13">
+        <v>99.278320000069613</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14">
+        <v>4.9570722412497333E-2</v>
+      </c>
+      <c r="C14">
+        <v>255.49828151238043</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F14" s="30">
+        <v>38.53098439483005</v>
+      </c>
+      <c r="G14" s="30">
+        <v>456.8011680060402</v>
+      </c>
+      <c r="H14" s="30">
+        <v>126.00740397773897</v>
+      </c>
+      <c r="I14" s="30">
+        <v>23.417625987428071</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15">
+        <v>4.9570722412497367E-2</v>
+      </c>
+      <c r="C15">
+        <v>1018.5754763861755</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16">
+        <v>4.9570722412497367E-2</v>
+      </c>
+      <c r="C16">
+        <v>0.90783853130662884</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>218</v>
+      </c>
+      <c r="B17">
+        <v>5.6564567203115594E-5</v>
+      </c>
+      <c r="C17">
+        <v>1.0356612988898828</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18">
+        <v>2E-3</v>
+      </c>
+      <c r="C18">
+        <v>9.9299164260424743E-10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19">
+        <v>10.424510362939218</v>
+      </c>
+      <c r="C19">
+        <v>2.9279508939251864</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>220</v>
+      </c>
+      <c r="B20">
+        <v>1.2429478672454113</v>
+      </c>
+      <c r="C20">
+        <v>1660.7689273524077</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>221</v>
+      </c>
+      <c r="B21">
+        <v>1.2429478672454113</v>
+      </c>
+      <c r="C21">
+        <v>640.18867415890122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22">
+        <v>68.250720909430768</v>
+      </c>
+      <c r="C22">
+        <v>640.83670692838211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23">
+        <v>64.794110996165372</v>
+      </c>
+      <c r="C23">
+        <v>641.029785211746</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>224</v>
+      </c>
+      <c r="B24">
+        <v>0.91088630043789787</v>
+      </c>
+      <c r="C24">
+        <v>236.37108787388058</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="30">
+        <v>0.27584737694031641</v>
+      </c>
+      <c r="C26" s="30">
+        <v>197.84010347905053</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E0693F-D387-4367-8A44-8725A6CA7BA7}">
   <dimension ref="A1:AF33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -5,21 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tes2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25F4501-37D5-40F4-BAAB-3B9377582E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E4C203-A930-4E70-B4A7-E9A2E9CD2DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="3" r:id="rId1"/>
-    <sheet name="Energy_Exergy" sheetId="2" r:id="rId2"/>
-    <sheet name="Exergoeconomico" sheetId="5" r:id="rId3"/>
-    <sheet name="EXERGO" sheetId="4" r:id="rId4"/>
+    <sheet name="rc" sheetId="6" r:id="rId2"/>
+    <sheet name="nt" sheetId="7" r:id="rId3"/>
+    <sheet name="nc" sheetId="8" r:id="rId4"/>
+    <sheet name="Energy_Exergy" sheetId="2" r:id="rId5"/>
+    <sheet name="Exergoeconomico" sheetId="5" r:id="rId6"/>
+    <sheet name="EXERGO" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="245">
   <si>
     <t>T [°C]</t>
   </si>
@@ -733,12 +735,6 @@
     <t>HE-PEM</t>
   </si>
   <si>
-    <t>Punto</t>
-  </si>
-  <si>
-    <t>Costo Unit. (USD/kWhex)</t>
-  </si>
-  <si>
     <t>Zdot (USD/h)</t>
   </si>
   <si>
@@ -751,13 +747,25 @@
     <t>f (%)</t>
   </si>
   <si>
-    <t>LCOEn(USD/kWh)</t>
-  </si>
-  <si>
-    <t>cH2 [USD/kWhex]</t>
-  </si>
-  <si>
-    <t>cElectricidad [USD/kWhex]</t>
+    <t>Fluido</t>
+  </si>
+  <si>
+    <t>Costo Unit. (USD/kWh_ex)</t>
+  </si>
+  <si>
+    <t>LCOEn sistema [USD/kWh]</t>
+  </si>
+  <si>
+    <t>c_H2 [USD/kWh_ex]</t>
+  </si>
+  <si>
+    <t>c_el_bus interno [USD/kWh_ex]</t>
+  </si>
+  <si>
+    <t>rc</t>
+  </si>
+  <si>
+    <t>nc</t>
   </si>
 </sst>
 </file>
@@ -922,14 +930,14 @@
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1384,34 +1392,34 @@
         <v>500</v>
       </c>
       <c r="C3" s="19">
-        <v>7.9817560813786423</v>
+        <v>79.817560813786429</v>
       </c>
       <c r="D3" s="17">
-        <v>0.57478365564259748</v>
+        <v>5.747836556425975</v>
       </c>
       <c r="E3" s="19">
         <v>44.197489238670407</v>
       </c>
       <c r="F3" s="19">
-        <v>22.006324234413263</v>
+        <v>21.672347119588974</v>
       </c>
       <c r="G3" s="19">
-        <v>42.266069418369199</v>
+        <v>41.608757546050079</v>
       </c>
       <c r="H3" s="19">
-        <v>39.083036578748462</v>
+        <v>18.611139031996345</v>
       </c>
       <c r="I3" s="19">
-        <v>38.322157470640676</v>
+        <v>18.196209309538482</v>
       </c>
       <c r="J3" s="19">
-        <v>73.705196115616388</v>
+        <v>73.740628070018715</v>
       </c>
       <c r="K3" s="19">
-        <v>6.7738392475312912</v>
+        <v>32.15627223010955</v>
       </c>
       <c r="L3" s="17">
-        <v>60.535652280525397</v>
+        <v>287.37040299107491</v>
       </c>
       <c r="M3" s="21"/>
       <c r="N3" s="21"/>
@@ -1441,34 +1449,34 @@
         <v>550</v>
       </c>
       <c r="C4" s="17">
-        <v>8.9819868548594588</v>
+        <v>89.81986854859457</v>
       </c>
       <c r="D4" s="17">
-        <v>0.59780007016897552</v>
+        <v>5.9780007016897558</v>
       </c>
       <c r="E4" s="17">
-        <v>46.69526627123269</v>
+        <v>46.695266271232683</v>
       </c>
       <c r="F4" s="17">
-        <v>22.850005374764851</v>
+        <v>22.53176363727647</v>
       </c>
       <c r="G4" s="17">
-        <v>44.797301420947292</v>
+        <v>44.157918300212081</v>
       </c>
       <c r="H4" s="17">
-        <v>38.702038861674041</v>
+        <v>18.305365479551135</v>
       </c>
       <c r="I4" s="17">
-        <v>37.945565695998773</v>
+        <v>17.896265272539772</v>
       </c>
       <c r="J4" s="17">
-        <v>73.460227385209635</v>
+        <v>73.494893490611787</v>
       </c>
       <c r="K4" s="17">
-        <v>6.9757969550625445</v>
+        <v>32.892461846891408</v>
       </c>
       <c r="L4" s="17">
-        <v>62.340484239438453</v>
+        <v>293.94949603203861</v>
       </c>
       <c r="M4" s="21"/>
       <c r="N4" s="21"/>
@@ -1498,34 +1506,34 @@
         <v>600</v>
       </c>
       <c r="C5" s="17">
-        <v>9.9679334582948602</v>
+        <v>99.679334582948613</v>
       </c>
       <c r="D5" s="17">
-        <v>0.62111932846844753</v>
+        <v>6.2111932846844748</v>
       </c>
       <c r="E5" s="17">
-        <v>48.863771870449504</v>
+        <v>48.86377187044944</v>
       </c>
       <c r="F5" s="17">
-        <v>23.39359126526438</v>
+        <v>23.090535501160087</v>
       </c>
       <c r="G5" s="17">
-        <v>46.992751286845909</v>
+        <v>46.368848492904625</v>
       </c>
       <c r="H5" s="17">
-        <v>38.328127919305047</v>
+        <v>18.010297345414219</v>
       </c>
       <c r="I5" s="17">
-        <v>37.576039107764217</v>
+        <v>17.606853714622613</v>
       </c>
       <c r="J5" s="17">
-        <v>73.215836655735927</v>
+        <v>73.249761451685686</v>
       </c>
       <c r="K5" s="17">
-        <v>7.1772698736697782</v>
+        <v>33.62269663607109</v>
       </c>
       <c r="L5" s="17">
-        <v>64.140983793542134</v>
+        <v>300.47537266795587</v>
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
@@ -1555,34 +1563,34 @@
         <v>650</v>
       </c>
       <c r="C6" s="17">
-        <v>10.942520132883478</v>
+        <v>109.4252013288348</v>
       </c>
       <c r="D6" s="17">
-        <v>0.6447344000410401</v>
+        <v>6.4473440004104017</v>
       </c>
       <c r="E6" s="17">
         <v>50.766607886856718</v>
       </c>
       <c r="F6" s="17">
-        <v>23.661351320584064</v>
+        <v>23.373292335921985</v>
       </c>
       <c r="G6" s="17">
-        <v>48.91739667752401</v>
+        <v>48.307040618031941</v>
       </c>
       <c r="H6" s="17">
-        <v>37.961182417304968</v>
+        <v>17.725397978085738</v>
       </c>
       <c r="I6" s="17">
-        <v>37.213454717865027</v>
+        <v>17.327445115447762</v>
       </c>
       <c r="J6" s="17">
-        <v>72.972155033057845</v>
+        <v>73.005361875421784</v>
       </c>
       <c r="K6" s="17">
-        <v>7.3782020252319311</v>
+        <v>34.3470096026928</v>
       </c>
       <c r="L6" s="17">
-        <v>65.936650684128182</v>
+        <v>306.94832785443566</v>
       </c>
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
@@ -1612,34 +1620,34 @@
         <v>700</v>
       </c>
       <c r="C7" s="17">
-        <v>11.907911442755228</v>
+        <v>119.07911442755226</v>
       </c>
       <c r="D7" s="17">
-        <v>0.66863221481329138</v>
+        <v>6.6863221481329127</v>
       </c>
       <c r="E7" s="17">
-        <v>52.451199641588161</v>
+        <v>52.451199641588154</v>
       </c>
       <c r="F7" s="17">
-        <v>23.667463179486298</v>
+        <v>23.394499986052235</v>
       </c>
       <c r="G7" s="17">
-        <v>50.619687111767362</v>
+        <v>50.021324566011295</v>
       </c>
       <c r="H7" s="17">
-        <v>37.60117137295029</v>
+        <v>17.45023537663441</v>
       </c>
       <c r="I7" s="17">
-        <v>36.857778908474963</v>
+        <v>17.057612887314626</v>
       </c>
       <c r="J7" s="17">
-        <v>72.729372195994642</v>
+        <v>72.761883525800215</v>
       </c>
       <c r="K7" s="17">
-        <v>7.5784907719207091</v>
+        <v>35.065255025061845</v>
       </c>
       <c r="L7" s="17">
-        <v>67.726567669488134</v>
+        <v>313.36705932292415</v>
       </c>
       <c r="M7" s="21"/>
       <c r="N7" s="21"/>
@@ -1669,34 +1677,34 @@
         <v>750</v>
       </c>
       <c r="C8" s="17">
-        <v>12.865749758364128</v>
+        <v>128.65749758364126</v>
       </c>
       <c r="D8" s="17">
-        <v>0.6927963040732894</v>
+        <v>6.9279630407328954</v>
       </c>
       <c r="E8" s="17">
-        <v>53.953838014043107</v>
+        <v>53.9538380140431</v>
       </c>
       <c r="F8" s="17">
-        <v>23.418942554906867</v>
+        <v>23.161413501793739</v>
       </c>
       <c r="G8" s="17">
-        <v>52.136694846180184</v>
+        <v>51.549060463654037</v>
       </c>
       <c r="H8" s="17">
-        <v>37.248102901082589</v>
+        <v>17.184435616492426</v>
       </c>
       <c r="I8" s="17">
-        <v>36.50901673542819</v>
+        <v>16.796987643527324</v>
       </c>
       <c r="J8" s="17">
-        <v>72.487705338327999</v>
+        <v>72.519542832587035</v>
       </c>
       <c r="K8" s="17">
-        <v>7.7780119622835953</v>
+        <v>35.77720301027054</v>
       </c>
       <c r="L8" s="17">
-        <v>69.509625247479235</v>
+        <v>319.72951259344148</v>
       </c>
       <c r="M8" s="21"/>
       <c r="N8" s="21"/>
@@ -1726,34 +1734,34 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C9" s="17">
-        <v>13.817310399416089</v>
+        <v>138.17310399416084</v>
       </c>
       <c r="D9" s="17">
-        <v>0.71720857262984272</v>
+        <v>7.1720857262984268</v>
       </c>
       <c r="E9" s="17">
-        <v>55.302895315550685</v>
+        <v>55.302895315550607</v>
       </c>
       <c r="F9" s="17">
-        <v>22.917512377362197</v>
+        <v>22.675961009681458</v>
       </c>
       <c r="G9" s="17">
-        <v>53.497400064021491</v>
+        <v>52.919450623537898</v>
       </c>
       <c r="H9" s="17">
-        <v>36.901993581878948</v>
+        <v>16.927655814797117</v>
       </c>
       <c r="I9" s="17">
-        <v>36.167181648495081</v>
+        <v>16.545230654544902</v>
       </c>
       <c r="J9" s="17">
-        <v>72.247379706631875</v>
+        <v>72.278564361019221</v>
       </c>
       <c r="K9" s="17">
-        <v>7.9766358915200142</v>
+        <v>36.482598340988282</v>
       </c>
       <c r="L9" s="17">
-        <v>71.284664287449004</v>
+        <v>326.03340686967459</v>
       </c>
       <c r="M9" s="21"/>
       <c r="N9" s="21"/>
@@ -1779,6 +1787,39 @@
       <c r="AH9" s="21"/>
     </row>
     <row r="10" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B10" s="17">
+        <v>850.00000000000011</v>
+      </c>
+      <c r="C10" s="17">
+        <v>147.63591018797939</v>
+      </c>
+      <c r="D10" s="17">
+        <v>7.4185008301883553</v>
+      </c>
+      <c r="E10" s="17">
+        <v>56.520932003665223</v>
+      </c>
+      <c r="F10" s="17">
+        <v>21.935982366012645</v>
+      </c>
+      <c r="G10" s="17">
+        <v>54.155710029492219</v>
+      </c>
+      <c r="H10" s="17">
+        <v>16.679572745563277</v>
+      </c>
+      <c r="I10" s="17">
+        <v>16.302022661184491</v>
+      </c>
+      <c r="J10" s="17">
+        <v>72.039169748600216</v>
+      </c>
+      <c r="K10" s="17">
+        <v>37.181184456678366</v>
+      </c>
+      <c r="L10" s="17">
+        <v>332.2764493515034</v>
+      </c>
       <c r="M10" s="21"/>
       <c r="N10" s="21"/>
       <c r="O10" s="21"/>
@@ -1803,17 +1844,39 @@
       <c r="AH10" s="21"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
+      <c r="B11" s="20">
+        <v>900.00000000000011</v>
+      </c>
+      <c r="C11" s="20">
+        <v>157.05390229949612</v>
+      </c>
+      <c r="D11" s="20">
+        <v>7.6670200718972215</v>
+      </c>
+      <c r="E11" s="20">
+        <v>57.626171655998625</v>
+      </c>
+      <c r="F11" s="20">
+        <v>20.936093045670965</v>
+      </c>
+      <c r="G11" s="20">
+        <v>55.276585278728227</v>
+      </c>
+      <c r="H11" s="20">
+        <v>16.439872677110039</v>
+      </c>
+      <c r="I11" s="20">
+        <v>16.067053897149204</v>
+      </c>
+      <c r="J11" s="20">
+        <v>71.80157092940965</v>
+      </c>
+      <c r="K11" s="20">
+        <v>37.872730091857683</v>
+      </c>
+      <c r="L11" s="20">
+        <v>338.45657329267715</v>
+      </c>
       <c r="M11" s="21"/>
       <c r="N11" s="21"/>
       <c r="O11" s="21"/>
@@ -1957,64 +2020,64 @@
         <v>500</v>
       </c>
       <c r="C16" s="17">
-        <v>294.85614292537934</v>
+        <v>2948.5614292537944</v>
       </c>
       <c r="D16" s="17">
-        <v>135.64262301173875</v>
+        <v>1356.4262301173844</v>
       </c>
       <c r="E16" s="17">
-        <v>151.19146157877427</v>
+        <v>1511.9146157877444</v>
       </c>
       <c r="F16" s="17">
-        <v>277.13026251072807</v>
+        <v>2771.3026251072883</v>
       </c>
       <c r="G16" s="17">
-        <v>86.111522976340609</v>
+        <v>861.11522976340632</v>
       </c>
       <c r="H16" s="17">
-        <v>34.017747966403839</v>
+        <v>340.1774796640384</v>
       </c>
       <c r="I16" s="17">
-        <v>302.81716564914211</v>
+        <v>3028.1716564914286</v>
       </c>
       <c r="J16" s="17">
-        <v>1179.4615416517445</v>
+        <v>11794.615416517447</v>
       </c>
       <c r="K16" s="17">
-        <v>13863.903314567468</v>
+        <v>138639.03314567471</v>
       </c>
       <c r="L16" s="17">
-        <v>8932.9858804423748</v>
+        <v>89329.858804423799</v>
       </c>
       <c r="M16" s="17">
-        <v>3.3626344503154937</v>
+        <v>29.001404664759903</v>
       </c>
       <c r="N16" s="17">
-        <v>1.6493321533075163</v>
+        <v>14.218380631961351</v>
       </c>
       <c r="O16" s="17">
-        <v>662.01750343054505</v>
+        <v>6620.1750343054518</v>
       </c>
       <c r="P16" s="17">
-        <v>307.33893335012613</v>
+        <v>3073.3893335012617</v>
       </c>
       <c r="Q16" s="17">
-        <v>6.9940860806835592E-2</v>
+        <v>0.69940860806835647</v>
       </c>
       <c r="R16" s="17">
-        <v>63.537030855789887</v>
+        <v>635.37030855789897</v>
       </c>
       <c r="S16" s="17">
-        <v>381.6564040682814</v>
+        <v>3824.7899825655463</v>
       </c>
       <c r="T16" s="17">
-        <v>34659.75828641867</v>
+        <v>346597.58286418673</v>
       </c>
       <c r="U16" s="17">
-        <v>353.65731761283195</v>
+        <v>4698.1235087791883</v>
       </c>
       <c r="V16" s="17">
-        <v>27031.406760062098</v>
+        <v>271476.94399441523</v>
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.3">
@@ -2022,64 +2085,64 @@
         <v>550</v>
       </c>
       <c r="C17" s="17">
-        <v>297.82296698241635</v>
+        <v>2978.2296698241607</v>
       </c>
       <c r="D17" s="17">
-        <v>131.86805418472457</v>
+        <v>1318.6805418472477</v>
       </c>
       <c r="E17" s="17">
-        <v>152.19025287038554</v>
+        <v>1521.902528703846</v>
       </c>
       <c r="F17" s="17">
-        <v>278.37767920301479</v>
+        <v>2783.7767920301558</v>
       </c>
       <c r="G17" s="17">
-        <v>88.983413920749442</v>
+        <v>889.83413920749445</v>
       </c>
       <c r="H17" s="17">
-        <v>80.540884684346381</v>
+        <v>805.40884684346383</v>
       </c>
       <c r="I17" s="17">
-        <v>364.95425807604568</v>
+        <v>3649.5425807604643</v>
       </c>
       <c r="J17" s="17">
-        <v>1591.6416778681469</v>
+        <v>15916.416778681467</v>
       </c>
       <c r="K17" s="17">
-        <v>15074.172785462781</v>
+        <v>150741.7278546278</v>
       </c>
       <c r="L17" s="17">
-        <v>9165.742924421842</v>
+        <v>91657.429244218394</v>
       </c>
       <c r="M17" s="17">
-        <v>3.3261513919689558</v>
+        <v>28.686520857027716</v>
       </c>
       <c r="N17" s="17">
-        <v>1.6226905804250538</v>
+        <v>13.988711900215982</v>
       </c>
       <c r="O17" s="17">
-        <v>700.30101822417953</v>
+        <v>7003.0101822417919</v>
       </c>
       <c r="P17" s="17">
-        <v>324.34672934535394</v>
+        <v>3243.4672934535392</v>
       </c>
       <c r="Q17" s="17">
-        <v>7.2279964988682083E-2</v>
+        <v>0.72279964988682055</v>
       </c>
       <c r="R17" s="17">
-        <v>66.545635698113529</v>
+        <v>665.4563569811354</v>
       </c>
       <c r="S17" s="17">
-        <v>380.67789920895763</v>
+        <v>3814.9529664057522</v>
       </c>
       <c r="T17" s="17">
-        <v>37685.431963656949</v>
+        <v>376854.31963656942</v>
       </c>
       <c r="U17" s="17">
-        <v>370.07849924618142</v>
+        <v>4904.2436020032346</v>
       </c>
       <c r="V17" s="17">
-        <v>29073.265801334615</v>
+        <v>291937.47741023701</v>
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.3">
@@ -2087,64 +2150,64 @@
         <v>600</v>
       </c>
       <c r="C18" s="17">
-        <v>300.72656005696859</v>
+        <v>3007.2656005696876</v>
       </c>
       <c r="D18" s="17">
-        <v>128.15077235300279</v>
+        <v>1281.507723530028</v>
       </c>
       <c r="E18" s="17">
-        <v>152.89907199523319</v>
+        <v>1528.99071995233</v>
       </c>
       <c r="F18" s="17">
-        <v>279.2453075698167</v>
+        <v>2792.4530756981671</v>
       </c>
       <c r="G18" s="17">
-        <v>91.855320754454354</v>
+        <v>918.55320754454283</v>
       </c>
       <c r="H18" s="17">
-        <v>132.01571327555575</v>
+        <v>1320.1571327557904</v>
       </c>
       <c r="I18" s="17">
-        <v>429.70000918122383</v>
+        <v>4297.0000918122378</v>
       </c>
       <c r="J18" s="17">
-        <v>2123.7887994432162</v>
+        <v>21237.887994432185</v>
       </c>
       <c r="K18" s="17">
-        <v>16381.075957825688</v>
+        <v>163810.75957825704</v>
       </c>
       <c r="L18" s="17">
-        <v>9428.9610392787527</v>
+        <v>94289.610392787596</v>
       </c>
       <c r="M18" s="17">
-        <v>3.2898953561125701</v>
+        <v>28.373607129403915</v>
       </c>
       <c r="N18" s="17">
-        <v>1.5963324264198737</v>
+        <v>13.761486434654085</v>
       </c>
       <c r="O18" s="17">
-        <v>739.74316456090378</v>
+        <v>7397.4316456090419</v>
       </c>
       <c r="P18" s="17">
-        <v>342.19548588824279</v>
+        <v>3421.9548588824719</v>
       </c>
       <c r="Q18" s="17">
-        <v>7.4619661227411427E-2</v>
+        <v>0.74619661227411505</v>
       </c>
       <c r="R18" s="17">
-        <v>69.636622761948459</v>
+        <v>696.36622761943977</v>
       </c>
       <c r="S18" s="17">
-        <v>379.53905784855749</v>
+        <v>3803.5124922584241</v>
       </c>
       <c r="T18" s="17">
-        <v>40952.68989456421</v>
+        <v>409526.89894564264</v>
       </c>
       <c r="U18" s="17">
-        <v>386.81822347694612</v>
+        <v>5113.586081630544</v>
       </c>
       <c r="V18" s="17">
-        <v>31371.31195371427</v>
+        <v>314959.91811351595</v>
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.3">
@@ -2152,64 +2215,64 @@
         <v>650</v>
       </c>
       <c r="C19" s="17">
-        <v>303.5689357492202</v>
+        <v>3035.689357492201</v>
       </c>
       <c r="D19" s="17">
-        <v>124.48910840925201</v>
+        <v>1244.8910840925203</v>
       </c>
       <c r="E19" s="17">
-        <v>153.39874970301798</v>
+        <v>1533.9874970301762</v>
       </c>
       <c r="F19" s="17">
-        <v>279.8422102253549</v>
+        <v>2798.4221022535266</v>
       </c>
       <c r="G19" s="17">
-        <v>94.725497642047941</v>
+        <v>947.25497642047981</v>
       </c>
       <c r="H19" s="17">
-        <v>185.84739014316</v>
+        <v>1858.4739014316001</v>
       </c>
       <c r="I19" s="17">
-        <v>497.04374229533039</v>
+        <v>4970.4374229533005</v>
       </c>
       <c r="J19" s="17">
-        <v>2808.6836717508977</v>
+        <v>28086.836717508984</v>
       </c>
       <c r="K19" s="17">
-        <v>17814.38949249798</v>
+        <v>178143.89492497977</v>
       </c>
       <c r="L19" s="17">
-        <v>9733.9721439540208</v>
+        <v>97339.721439540212</v>
       </c>
       <c r="M19" s="17">
-        <v>3.2538839114981575</v>
+        <v>28.062814357106859</v>
       </c>
       <c r="N19" s="17">
-        <v>1.570268926036658</v>
+        <v>13.536801086522916</v>
       </c>
       <c r="O19" s="17">
-        <v>780.3352173446757</v>
+        <v>7803.3521734467595</v>
       </c>
       <c r="P19" s="17">
-        <v>360.9288825433681</v>
+        <v>3609.2888254336344</v>
       </c>
       <c r="Q19" s="17">
-        <v>7.6958539798279726E-2</v>
+        <v>0.76958539798279801</v>
       </c>
       <c r="R19" s="17">
-        <v>72.811563723715722</v>
+        <v>728.11563723720315</v>
       </c>
       <c r="S19" s="17">
-        <v>378.24841917647922</v>
+        <v>3790.5539859561754</v>
       </c>
       <c r="T19" s="17">
-        <v>44535.973731244943</v>
+        <v>445359.73731244943</v>
       </c>
       <c r="U19" s="17">
-        <v>403.8712905190423</v>
+        <v>5326.0795830377938</v>
       </c>
       <c r="V19" s="17">
-        <v>33997.057427054897</v>
+        <v>341259.36882965587</v>
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.3">
@@ -2217,64 +2280,64 @@
         <v>700</v>
       </c>
       <c r="C20" s="17">
-        <v>306.35131841675008</v>
+        <v>3063.5131841675043</v>
       </c>
       <c r="D20" s="17">
-        <v>120.88239449501667</v>
+        <v>1208.8239449501671</v>
       </c>
       <c r="E20" s="17">
-        <v>153.74467368248199</v>
+        <v>1537.4467368248106</v>
       </c>
       <c r="F20" s="17">
-        <v>280.24408784225767</v>
+        <v>2802.440878422588</v>
       </c>
       <c r="G20" s="17">
-        <v>97.59153362218035</v>
+        <v>975.91533622180293</v>
       </c>
       <c r="H20" s="17">
-        <v>240.31475528596201</v>
+        <v>2403.1475528596202</v>
       </c>
       <c r="I20" s="17">
-        <v>566.95500958230537</v>
+        <v>5669.5500958230568</v>
       </c>
       <c r="J20" s="17">
-        <v>3689.4255484164842</v>
+        <v>36894.255484164853</v>
       </c>
       <c r="K20" s="17">
-        <v>19412.004412755879</v>
+        <v>194120.04412755879</v>
       </c>
       <c r="L20" s="17">
-        <v>10093.94296158151</v>
+        <v>100939.4296158151</v>
       </c>
       <c r="M20" s="17">
-        <v>3.2181430517416656</v>
+        <v>27.754366169382649</v>
       </c>
       <c r="N20" s="17">
-        <v>1.544517183389571</v>
+        <v>13.31480330508251</v>
       </c>
       <c r="O20" s="17">
-        <v>822.05630927133234</v>
+        <v>8220.5630927133225</v>
       </c>
       <c r="P20" s="17">
-        <v>380.58664247568697</v>
+        <v>3805.8664245570199</v>
       </c>
       <c r="Q20" s="17">
-        <v>7.9294647204591173E-2</v>
+        <v>0.79294647204591096</v>
       </c>
       <c r="R20" s="17">
-        <v>76.071243546232026</v>
+        <v>760.71243566216992</v>
       </c>
       <c r="S20" s="17">
-        <v>376.81466876953999</v>
+        <v>3776.1643515211672</v>
       </c>
       <c r="T20" s="17">
-        <v>48530.011031889699</v>
+        <v>485300.110318897</v>
       </c>
       <c r="U20" s="17">
-        <v>421.22798507395089</v>
+        <v>5541.5981837227364</v>
       </c>
       <c r="V20" s="17">
-        <v>37043.055499699934</v>
+        <v>371761.33356093121</v>
       </c>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.3">
@@ -2282,64 +2345,64 @@
         <v>750</v>
       </c>
       <c r="C21" s="17">
-        <v>309.07455465127805</v>
+        <v>3090.7455465127828</v>
       </c>
       <c r="D21" s="17">
-        <v>117.33045407099952</v>
+        <v>1173.3045407099946</v>
       </c>
       <c r="E21" s="17">
-        <v>153.97884766306913</v>
+        <v>1539.7884766306952</v>
       </c>
       <c r="F21" s="17">
-        <v>280.50183820071442</v>
+        <v>2805.018382007137</v>
       </c>
       <c r="G21" s="17">
-        <v>100.45071167206741</v>
+        <v>1004.5071167206745</v>
       </c>
       <c r="H21" s="17">
-        <v>294.26310690947577</v>
+        <v>2942.6310690947575</v>
       </c>
       <c r="I21" s="17">
-        <v>639.38950186234808</v>
+        <v>6393.8950186234715</v>
       </c>
       <c r="J21" s="17">
-        <v>4823.8346125543394</v>
+        <v>48238.346125543401</v>
       </c>
       <c r="K21" s="17">
-        <v>21223.823419605003</v>
+        <v>212238.23419605001</v>
       </c>
       <c r="L21" s="17">
-        <v>10525.356004225263</v>
+        <v>105253.56004225269</v>
       </c>
       <c r="M21" s="17">
-        <v>3.182702476477075</v>
+        <v>27.448518212909715</v>
       </c>
       <c r="N21" s="17">
-        <v>1.519096652861311</v>
+        <v>13.095660800528545</v>
       </c>
       <c r="O21" s="17">
-        <v>864.87738547050515</v>
+        <v>8648.773854705054</v>
       </c>
       <c r="P21" s="17">
-        <v>401.20580558999745</v>
+        <v>4012.0580558999745</v>
       </c>
       <c r="Q21" s="17">
-        <v>8.1625778220241155E-2</v>
+        <v>0.81625778220241141</v>
       </c>
       <c r="R21" s="17">
-        <v>79.415965355949552</v>
+        <v>794.15965355949538</v>
       </c>
       <c r="S21" s="17">
-        <v>375.24661356442857</v>
+        <v>3760.4317142229957</v>
       </c>
       <c r="T21" s="17">
-        <v>53059.558549012494</v>
+        <v>530595.58549012512</v>
       </c>
       <c r="U21" s="17">
-        <v>438.8758961478494</v>
+        <v>5759.9847247347689</v>
       </c>
       <c r="V21" s="17">
-        <v>40632.408142450848</v>
+        <v>407696.79895406356</v>
       </c>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.3">
@@ -2347,64 +2410,64 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C22" s="17">
-        <v>311.73934843303778</v>
+        <v>3117.3934843303709</v>
       </c>
       <c r="D22" s="17">
-        <v>113.83330527634081</v>
+        <v>1138.33305276341</v>
       </c>
       <c r="E22" s="17">
-        <v>154.12694860114715</v>
+        <v>1541.2694860114752</v>
       </c>
       <c r="F22" s="17">
-        <v>280.65325482354871</v>
+        <v>2806.532548235491</v>
       </c>
       <c r="G22" s="17">
-        <v>103.30018156282743</v>
+        <v>1033.0018156282754</v>
       </c>
       <c r="H22" s="17">
-        <v>346.91288051130834</v>
+        <v>3469.1288051136653</v>
       </c>
       <c r="I22" s="17">
-        <v>714.29330882120883</v>
+        <v>7142.9330882120803</v>
       </c>
       <c r="J22" s="17">
-        <v>6291.3606293226931</v>
+        <v>62913.606293226985</v>
       </c>
       <c r="K22" s="17">
-        <v>23317.709736516052</v>
+        <v>233177.09736516071</v>
       </c>
       <c r="L22" s="17">
-        <v>11050.043569183621</v>
+        <v>110500.43569183591</v>
       </c>
       <c r="M22" s="17">
-        <v>3.1475926729674328</v>
+        <v>27.145532961161859</v>
       </c>
       <c r="N22" s="17">
-        <v>1.4940269956205496</v>
+        <v>12.879543065694394</v>
       </c>
       <c r="O22" s="17">
-        <v>908.7639387171597</v>
+        <v>9087.6393871715918</v>
       </c>
       <c r="P22" s="17">
-        <v>422.82153795985045</v>
+        <v>4228.2153795985059</v>
       </c>
       <c r="Q22" s="17">
-        <v>8.3949658717157039E-2</v>
+        <v>0.8394965871715695</v>
       </c>
       <c r="R22" s="17">
-        <v>82.84575052116061</v>
+        <v>828.45750521160619</v>
       </c>
       <c r="S22" s="17">
-        <v>373.5531104491323</v>
+        <v>3743.4447022741656</v>
       </c>
       <c r="T22" s="17">
-        <v>58294.274341290125</v>
+        <v>582942.74341290176</v>
       </c>
       <c r="U22" s="17">
-        <v>456.8011680060402</v>
+        <v>5981.0666103429439</v>
       </c>
       <c r="V22" s="17">
-        <v>44933.484238032433</v>
+        <v>450749.41978773114</v>
       </c>
       <c r="W22" s="21"/>
       <c r="X22" s="21"/>
@@ -2412,33 +2475,138 @@
       <c r="Z22" s="21"/>
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B23" s="17">
+        <v>850.00000000000011</v>
+      </c>
+      <c r="C23" s="17">
+        <v>3143.463834922105</v>
+      </c>
+      <c r="D23" s="17">
+        <v>1103.9100202102625</v>
+      </c>
+      <c r="E23" s="17">
+        <v>1542.1068241741657</v>
+      </c>
+      <c r="F23" s="17">
+        <v>2807.2526540154367</v>
+      </c>
+      <c r="G23" s="17">
+        <v>1061.3726985385092</v>
+      </c>
+      <c r="H23" s="17">
+        <v>3977.3664473134559</v>
+      </c>
+      <c r="I23" s="17">
+        <v>7916.0573066213656</v>
+      </c>
+      <c r="J23" s="17">
+        <v>82043.236087615151</v>
+      </c>
+      <c r="K23" s="17">
+        <v>257890.4091378501</v>
+      </c>
+      <c r="L23" s="17">
+        <v>116982.91458223342</v>
+      </c>
+      <c r="M23" s="17">
+        <v>26.84566568218715</v>
+      </c>
+      <c r="N23" s="17">
+        <v>12.666611299755765</v>
+      </c>
+      <c r="O23" s="17">
+        <v>9536.7775019646579</v>
+      </c>
+      <c r="P23" s="17">
+        <v>4454.6760841453606</v>
+      </c>
+      <c r="Q23" s="17">
+        <v>0.86264049813098698</v>
+      </c>
+      <c r="R23" s="17">
+        <v>863.60461913449035</v>
+      </c>
+      <c r="S23" s="17">
+        <v>3725.2917177400277</v>
+      </c>
+      <c r="T23" s="17">
+        <v>644726.02284462529</v>
+      </c>
+      <c r="U23" s="17">
+        <v>6204.6628666425377</v>
+      </c>
+      <c r="V23" s="17">
+        <v>503293.47730060096</v>
+      </c>
       <c r="W23" s="21"/>
       <c r="X23" s="21"/>
       <c r="Y23" s="21"/>
       <c r="Z23" s="21"/>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="20"/>
+      <c r="B24" s="20">
+        <v>900.00000000000011</v>
+      </c>
+      <c r="C24" s="20">
+        <v>3168.9638838626593</v>
+      </c>
+      <c r="D24" s="20">
+        <v>1070.0354556951188</v>
+      </c>
+      <c r="E24" s="20">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F24" s="20">
+        <v>2807.373846715212</v>
+      </c>
+      <c r="G24" s="20">
+        <v>1089.5931909999586</v>
+      </c>
+      <c r="H24" s="20">
+        <v>4463.8000501786591</v>
+      </c>
+      <c r="I24" s="20">
+        <v>8712.6139107183735</v>
+      </c>
+      <c r="J24" s="20">
+        <v>107270.29753288905</v>
+      </c>
+      <c r="K24" s="20">
+        <v>287768.98644095648</v>
+      </c>
+      <c r="L24" s="20">
+        <v>125140.03470369184</v>
+      </c>
+      <c r="M24" s="20">
+        <v>26.549156075515601</v>
+      </c>
+      <c r="N24" s="20">
+        <v>12.457012607361445</v>
+      </c>
+      <c r="O24" s="20">
+        <v>9995.7814728890007</v>
+      </c>
+      <c r="P24" s="20">
+        <v>4691.7661365454696</v>
+      </c>
+      <c r="Q24" s="20">
+        <v>0.88566811717443028</v>
+      </c>
+      <c r="R24" s="20">
+        <v>899.59878338048634</v>
+      </c>
+      <c r="S24" s="20">
+        <v>3706.0602091987898</v>
+      </c>
+      <c r="T24" s="20">
+        <v>719422.46610239113</v>
+      </c>
+      <c r="U24" s="20">
+        <v>6430.5927883464301</v>
+      </c>
+      <c r="V24" s="20">
+        <v>568797.84695296281</v>
+      </c>
       <c r="W24" s="21"/>
       <c r="X24" s="21"/>
       <c r="Y24" s="21"/>
@@ -2483,22 +2651,22 @@
         <v>500</v>
       </c>
       <c r="C29" s="17">
-        <v>0.77990753820849013</v>
+        <v>0.78326265795336691</v>
       </c>
       <c r="D29" s="17">
-        <v>3.5440154834621529</v>
+        <v>3.6141108927025245</v>
       </c>
       <c r="E29" s="21">
-        <v>0.28216581012876918</v>
+        <v>0.27669322544008323</v>
       </c>
       <c r="F29" s="21">
-        <v>1.1512137739935889E-2</v>
+        <v>1.2361084819537911E-2</v>
       </c>
       <c r="G29">
-        <v>0.67677225952588616</v>
+        <v>0.72330304895887298</v>
       </c>
       <c r="H29">
-        <v>22.009246179150999</v>
+        <v>21.673734204663308</v>
       </c>
       <c r="I29" s="25"/>
       <c r="J29" s="25"/>
@@ -2508,22 +2676,22 @@
         <v>550</v>
       </c>
       <c r="C30" s="17">
-        <v>0.77147227154971376</v>
+        <v>0.77466931437000774</v>
       </c>
       <c r="D30" s="17">
-        <v>3.3762454708291418</v>
+        <v>3.4381210758326861</v>
       </c>
       <c r="E30" s="21">
-        <v>0.29618699488530348</v>
+        <v>0.29085653993665939</v>
       </c>
       <c r="F30" s="21">
-        <v>1.1448741730107946E-2</v>
+        <v>1.2174947164356329E-2</v>
       </c>
       <c r="G30">
-        <v>0.67329752422721656</v>
+        <v>0.71310084407837038</v>
       </c>
       <c r="H30">
-        <v>22.852772845028625</v>
+        <v>22.533068562999215</v>
       </c>
       <c r="I30" s="25"/>
       <c r="J30" s="25"/>
@@ -2533,22 +2701,22 @@
         <v>600</v>
       </c>
       <c r="C31" s="17">
-        <v>0.76603788504447645</v>
+        <v>0.76908237022867998</v>
       </c>
       <c r="D31" s="17">
-        <v>3.2745630047059779</v>
+        <v>3.3307255701802183</v>
       </c>
       <c r="E31" s="21">
-        <v>0.30538425999526303</v>
+        <v>0.30023488243911134</v>
       </c>
       <c r="F31" s="21">
-        <v>1.1402542302703553E-2</v>
+        <v>1.2032304792923087E-2</v>
       </c>
       <c r="G31">
-        <v>0.67076533361118174</v>
+        <v>0.70528261570011441</v>
       </c>
       <c r="H31">
-        <v>23.396211495552354</v>
+        <v>23.091762977132003</v>
       </c>
       <c r="I31" s="25"/>
       <c r="J31" s="25"/>
@@ -2558,22 +2726,22 @@
         <v>650</v>
       </c>
       <c r="C32" s="17">
-        <v>0.76336171815198695</v>
+        <v>0.76625554633431037</v>
       </c>
       <c r="D32" s="17">
-        <v>3.2261966267662174</v>
+        <v>3.2783380934172728</v>
       </c>
       <c r="E32" s="21">
-        <v>0.30996250870250008</v>
+        <v>0.3050326023444459</v>
       </c>
       <c r="F32" s="21">
-        <v>1.1366515645355346E-2</v>
+        <v>1.1918890450311831E-2</v>
       </c>
       <c r="G32">
-        <v>0.66879071252192657</v>
+        <v>0.69906637558159146</v>
       </c>
       <c r="H32">
-        <v>23.663828184801304</v>
+        <v>23.374445366568963</v>
       </c>
       <c r="I32" s="25"/>
       <c r="J32" s="25"/>
@@ -2583,22 +2751,22 @@
         <v>700</v>
       </c>
       <c r="C33" s="17">
-        <v>0.76330202099806788</v>
+        <v>0.76604419751036534</v>
       </c>
       <c r="D33" s="17">
-        <v>3.2251112643946462</v>
+        <v>3.274462792395989</v>
       </c>
       <c r="E33" s="21">
-        <v>0.31006682189232937</v>
+        <v>0.30539360603584087</v>
       </c>
       <c r="F33" s="21">
-        <v>1.1337655298378537E-2</v>
+        <v>1.1826368829128379E-2</v>
       </c>
       <c r="G33">
-        <v>0.66720887690412767</v>
+        <v>0.69399526552452651</v>
       </c>
       <c r="H33">
-        <v>23.669797900193213</v>
+        <v>23.395580248963466</v>
       </c>
       <c r="I33" s="25"/>
       <c r="J33" s="25"/>
@@ -2608,22 +2776,22 @@
         <v>750</v>
       </c>
       <c r="C34" s="17">
-        <v>0.76578865813437991</v>
+        <v>0.76837578393620309</v>
       </c>
       <c r="D34" s="17">
-        <v>3.269954039722121</v>
+        <v>3.3174822593478424</v>
       </c>
       <c r="E34" s="21">
-        <v>0.30581469581908238</v>
+        <v>0.30143341299934551</v>
       </c>
       <c r="F34" s="21">
-        <v>1.1313771415970319E-2</v>
+        <v>1.1749324463843415E-2</v>
       </c>
       <c r="G34">
-        <v>0.66589980130933324</v>
+        <v>0.68977246386325763</v>
       </c>
       <c r="H34">
-        <v>23.421134186562</v>
+        <v>23.162421606379691</v>
       </c>
       <c r="I34" s="25"/>
       <c r="J34" s="25"/>
@@ -2633,39 +2801,71 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C35" s="17">
-        <v>0.77080441854314019</v>
+        <v>0.77323103320365494</v>
       </c>
       <c r="D35" s="17">
-        <v>3.3633860684833179</v>
+        <v>3.4099151646694286</v>
       </c>
       <c r="E35" s="21">
-        <v>0.29731942145165008</v>
+        <v>0.29326242786363987</v>
       </c>
       <c r="F35" s="21">
-        <v>1.1293500510283605E-2</v>
+        <v>1.1684219661096553E-2</v>
       </c>
       <c r="G35">
-        <v>0.66478875296864437</v>
+        <v>0.68620406962470215</v>
       </c>
       <c r="H35">
-        <v>22.919558145685983</v>
+        <v>22.676896679634506</v>
       </c>
       <c r="I35" s="25"/>
       <c r="J35" s="25"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="F36" s="21"/>
-      <c r="G36"/>
-      <c r="H36"/>
+      <c r="B36" s="17">
+        <v>850.00000000000011</v>
+      </c>
+      <c r="C36" s="17">
+        <v>0.78063155428409226</v>
+      </c>
+      <c r="D36" s="17">
+        <v>3.5586806246416098</v>
+      </c>
+      <c r="E36" s="17">
+        <v>0.28100301923011389</v>
+      </c>
+      <c r="F36" s="21">
+        <v>1.1628483332333845E-2</v>
+      </c>
+      <c r="G36">
+        <v>0.68314916144521809</v>
+      </c>
+      <c r="H36">
+        <v>21.936844571590786</v>
+      </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
+      <c r="B37" s="20">
+        <v>900.00000000000011</v>
+      </c>
+      <c r="C37" s="20">
+        <v>0.79063119898734036</v>
+      </c>
+      <c r="D37" s="20">
+        <v>3.7764027761178784</v>
+      </c>
+      <c r="E37" s="20">
+        <v>0.26480226270461399</v>
+      </c>
+      <c r="F37" s="20">
+        <v>1.1580256134364322E-2</v>
+      </c>
+      <c r="G37" s="20">
+        <v>0.68050582872450849</v>
+      </c>
+      <c r="H37" s="20">
+        <v>20.936880101265952</v>
+      </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H38" s="21"/>
@@ -2681,6 +2881,2876 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC8F8E6-609F-4748-8A52-08E74E409D1F}">
+  <dimension ref="B2:V34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="9" width="11.5546875" style="17"/>
+    <col min="10" max="10" width="15" style="17" customWidth="1"/>
+    <col min="11" max="16384" width="11.5546875" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B2" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B3" s="17">
+        <v>2.5</v>
+      </c>
+      <c r="C3" s="17">
+        <v>148.16689369741928</v>
+      </c>
+      <c r="D3" s="17">
+        <v>6.7342358759702696</v>
+      </c>
+      <c r="E3" s="17">
+        <v>56.964645761388169</v>
+      </c>
+      <c r="F3" s="17">
+        <v>20.76638257848656</v>
+      </c>
+      <c r="G3" s="17">
+        <v>54.828330497626311</v>
+      </c>
+      <c r="H3" s="17">
+        <v>17.441013464225993</v>
+      </c>
+      <c r="I3" s="17">
+        <v>17.0490261992745</v>
+      </c>
+      <c r="J3" s="17">
+        <v>73.324154648869751</v>
+      </c>
+      <c r="K3" s="17">
+        <v>35.298899030097473</v>
+      </c>
+      <c r="L3" s="17">
+        <v>315.45506166980897</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B4" s="17">
+        <v>2.7</v>
+      </c>
+      <c r="C4" s="17">
+        <v>155.66697058060771</v>
+      </c>
+      <c r="D4" s="17">
+        <v>7.5293584802110809</v>
+      </c>
+      <c r="E4" s="17">
+        <v>57.545256030232359</v>
+      </c>
+      <c r="F4" s="17">
+        <v>20.916342885012611</v>
+      </c>
+      <c r="G4" s="17">
+        <v>55.224424495132965</v>
+      </c>
+      <c r="H4" s="17">
+        <v>16.577598279744681</v>
+      </c>
+      <c r="I4" s="17">
+        <v>16.202117630865612</v>
+      </c>
+      <c r="J4" s="17">
+        <v>72.020515667514871</v>
+      </c>
+      <c r="K4" s="17">
+        <v>37.505487197563291</v>
+      </c>
+      <c r="L4" s="17">
+        <v>335.17464005819699</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B5" s="17">
+        <v>2.9</v>
+      </c>
+      <c r="C5" s="17">
+        <v>162.27893989998952</v>
+      </c>
+      <c r="D5" s="17">
+        <v>8.1624683336946049</v>
+      </c>
+      <c r="E5" s="17">
+        <v>57.867796024364083</v>
+      </c>
+      <c r="F5" s="17">
+        <v>20.991532723655869</v>
+      </c>
+      <c r="G5" s="17">
+        <v>55.422986423214837</v>
+      </c>
+      <c r="H5" s="17">
+        <v>15.969258491659119</v>
+      </c>
+      <c r="I5" s="17">
+        <v>15.605596060142126</v>
+      </c>
+      <c r="J5" s="17">
+        <v>71.029884266576062</v>
+      </c>
+      <c r="K5" s="17">
+        <v>39.161674085045284</v>
+      </c>
+      <c r="L5" s="17">
+        <v>349.9754568282014</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B6" s="17">
+        <v>3.1</v>
+      </c>
+      <c r="C6" s="17">
+        <v>168.16932560061701</v>
+      </c>
+      <c r="D6" s="17">
+        <v>8.686527999868952</v>
+      </c>
+      <c r="E6" s="17">
+        <v>58.033954827081338</v>
+      </c>
+      <c r="F6" s="17">
+        <v>21.021563313236495</v>
+      </c>
+      <c r="G6" s="17">
+        <v>55.502260178915265</v>
+      </c>
+      <c r="H6" s="17">
+        <v>15.510178237410971</v>
+      </c>
+      <c r="I6" s="17">
+        <v>15.155540354724605</v>
+      </c>
+      <c r="J6" s="17">
+        <v>70.243600700525974</v>
+      </c>
+      <c r="K6" s="17">
+        <v>40.473691505924258</v>
+      </c>
+      <c r="L6" s="17">
+        <v>361.70054026670601</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B7" s="17">
+        <v>3.3</v>
+      </c>
+      <c r="C7" s="17">
+        <v>173.45261418436411</v>
+      </c>
+      <c r="D7" s="17">
+        <v>9.1364978290003886</v>
+      </c>
+      <c r="E7" s="17">
+        <v>58.09849493424899</v>
+      </c>
+      <c r="F7" s="17">
+        <v>21.021719048004329</v>
+      </c>
+      <c r="G7" s="17">
+        <v>55.502633418048816</v>
+      </c>
+      <c r="H7" s="17">
+        <v>15.144272525361949</v>
+      </c>
+      <c r="I7" s="17">
+        <v>14.796895802750958</v>
+      </c>
+      <c r="J7" s="17">
+        <v>69.596354166304025</v>
+      </c>
+      <c r="K7" s="17">
+        <v>41.562555762188133</v>
+      </c>
+      <c r="L7" s="17">
+        <v>371.43137467083</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B8" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="C8" s="17">
+        <v>178.21771118453276</v>
+      </c>
+      <c r="D8" s="17">
+        <v>9.5336854968264078</v>
+      </c>
+      <c r="E8" s="17">
+        <v>58.093587340872247</v>
+      </c>
+      <c r="F8" s="17">
+        <v>21.001060822403193</v>
+      </c>
+      <c r="G8" s="17">
+        <v>55.448045028227412</v>
+      </c>
+      <c r="H8" s="17">
+        <v>14.840909759490916</v>
+      </c>
+      <c r="I8" s="17">
+        <v>14.499600926667302</v>
+      </c>
+      <c r="J8" s="17">
+        <v>69.048904190007818</v>
+      </c>
+      <c r="K8" s="17">
+        <v>42.497762640748867</v>
+      </c>
+      <c r="L8" s="17">
+        <v>379.78902183990635</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B15" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="M15" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="O15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="P15" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="R15" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="S15" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="U15" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="V15" s="18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B16" s="17">
+        <v>2.5</v>
+      </c>
+      <c r="C16" s="17">
+        <v>2664.8478767473252</v>
+      </c>
+      <c r="D16" s="17">
+        <v>986.37006924873401</v>
+      </c>
+      <c r="E16" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F16" s="17">
+        <v>2398.8101530183258</v>
+      </c>
+      <c r="G16" s="17">
+        <v>997.03770676192551</v>
+      </c>
+      <c r="H16" s="17">
+        <v>6947.6550741795809</v>
+      </c>
+      <c r="I16" s="17">
+        <v>9249.2997745483663</v>
+      </c>
+      <c r="J16" s="17">
+        <v>102375.56157213112</v>
+      </c>
+      <c r="K16" s="17">
+        <v>274638.10828811495</v>
+      </c>
+      <c r="L16" s="17">
+        <v>119161.08401865959</v>
+      </c>
+      <c r="M16" s="17">
+        <v>28.439355661207351</v>
+      </c>
+      <c r="N16" s="17">
+        <v>13.800941887616878</v>
+      </c>
+      <c r="O16" s="17">
+        <v>8175.1551300820374</v>
+      </c>
+      <c r="P16" s="17">
+        <v>3700.0428190667417</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0.809941181583682</v>
+      </c>
+      <c r="R16" s="17">
+        <v>754.06058026615347</v>
+      </c>
+      <c r="S16" s="17">
+        <v>4793.5371512133352</v>
+      </c>
+      <c r="T16" s="17">
+        <v>686595.27072028746</v>
+      </c>
+      <c r="U16" s="17">
+        <v>5581.9131402913681</v>
+      </c>
+      <c r="V16" s="17">
+        <v>544008.9903031555</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B17" s="17">
+        <v>2.7</v>
+      </c>
+      <c r="C17" s="17">
+        <v>3087.3746791042909</v>
+      </c>
+      <c r="D17" s="17">
+        <v>1058.1726709377524</v>
+      </c>
+      <c r="E17" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F17" s="17">
+        <v>2741.5191927130818</v>
+      </c>
+      <c r="G17" s="17">
+        <v>1076.5328210015157</v>
+      </c>
+      <c r="H17" s="17">
+        <v>4812.2007797128163</v>
+      </c>
+      <c r="I17" s="17">
+        <v>8798.3787257595359</v>
+      </c>
+      <c r="J17" s="17">
+        <v>106472.50431367061</v>
+      </c>
+      <c r="K17" s="17">
+        <v>285628.78406094934</v>
+      </c>
+      <c r="L17" s="17">
+        <v>124163.1956881715</v>
+      </c>
+      <c r="M17" s="17">
+        <v>26.818318458563386</v>
+      </c>
+      <c r="N17" s="17">
+        <v>12.646116251516156</v>
+      </c>
+      <c r="O17" s="17">
+        <v>9724.4418843231942</v>
+      </c>
+      <c r="P17" s="17">
+        <v>4529.4501957169959</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>0.87497071764366408</v>
+      </c>
+      <c r="R17" s="17">
+        <v>877.17648611728293</v>
+      </c>
+      <c r="S17" s="17">
+        <v>3851.153404008046</v>
+      </c>
+      <c r="T17" s="17">
+        <v>714071.9601523733</v>
+      </c>
+      <c r="U17" s="17">
+        <v>6304.9321542947046</v>
+      </c>
+      <c r="V17" s="17">
+        <v>564708.61317200388</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B18" s="17">
+        <v>2.9</v>
+      </c>
+      <c r="C18" s="17">
+        <v>3483.3349591886849</v>
+      </c>
+      <c r="D18" s="17">
+        <v>1112.8283922583832</v>
+      </c>
+      <c r="E18" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F18" s="17">
+        <v>3062.6461462244392</v>
+      </c>
+      <c r="G18" s="17">
+        <v>1134.9118833301486</v>
+      </c>
+      <c r="H18" s="17">
+        <v>3261.9581509413547</v>
+      </c>
+      <c r="I18" s="17">
+        <v>8389.0102350076741</v>
+      </c>
+      <c r="J18" s="17">
+        <v>110376.27722141369</v>
+      </c>
+      <c r="K18" s="17">
+        <v>296101.25219792326</v>
+      </c>
+      <c r="L18" s="17">
+        <v>128951.81516126439</v>
+      </c>
+      <c r="M18" s="17">
+        <v>25.606427123562518</v>
+      </c>
+      <c r="N18" s="17">
+        <v>11.801660538249831</v>
+      </c>
+      <c r="O18" s="17">
+        <v>10979.19765967354</v>
+      </c>
+      <c r="P18" s="17">
+        <v>5326.8577223470802</v>
+      </c>
+      <c r="Q18" s="17">
+        <v>0.92282153852808912</v>
+      </c>
+      <c r="R18" s="17">
+        <v>983.24170106960253</v>
+      </c>
+      <c r="S18" s="17">
+        <v>3228.7579140535781</v>
+      </c>
+      <c r="T18" s="17">
+        <v>740253.13049480808</v>
+      </c>
+      <c r="U18" s="17">
+        <v>6883.9186704482818</v>
+      </c>
+      <c r="V18" s="17">
+        <v>584856.79563444015</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B19" s="17">
+        <v>3.1</v>
+      </c>
+      <c r="C19" s="17">
+        <v>3849.8455050005987</v>
+      </c>
+      <c r="D19" s="17">
+        <v>1159.2727723247745</v>
+      </c>
+      <c r="E19" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F19" s="17">
+        <v>3364.9348540762367</v>
+      </c>
+      <c r="G19" s="17">
+        <v>1180.0986703582332</v>
+      </c>
+      <c r="H19" s="17">
+        <v>2088.2936759883305</v>
+      </c>
+      <c r="I19" s="17">
+        <v>8025.6331977169812</v>
+      </c>
+      <c r="J19" s="17">
+        <v>114055.21230881629</v>
+      </c>
+      <c r="K19" s="17">
+        <v>305970.5584796489</v>
+      </c>
+      <c r="L19" s="17">
+        <v>133484.92502395887</v>
+      </c>
+      <c r="M19" s="17">
+        <v>24.66020890619394</v>
+      </c>
+      <c r="N19" s="17">
+        <v>11.151730495964454</v>
+      </c>
+      <c r="O19" s="17">
+        <v>12030.465799378224</v>
+      </c>
+      <c r="P19" s="17">
+        <v>6091.4841011854433</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>0.9599212273135399</v>
+      </c>
+      <c r="R19" s="17">
+        <v>1077.0012172548297</v>
+      </c>
+      <c r="S19" s="17">
+        <v>2798.8045602279121</v>
+      </c>
+      <c r="T19" s="17">
+        <v>764926.39619912219</v>
+      </c>
+      <c r="U19" s="17">
+        <v>7365.0996693036432</v>
+      </c>
+      <c r="V19" s="17">
+        <v>604120.85840596433</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="17">
+        <v>3.3</v>
+      </c>
+      <c r="C20" s="17">
+        <v>4189.7807746840863</v>
+      </c>
+      <c r="D20" s="17">
+        <v>1200.5121499819197</v>
+      </c>
+      <c r="E20" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F20" s="17">
+        <v>3650.6399459165932</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1216.8194568160066</v>
+      </c>
+      <c r="H20" s="17">
+        <v>1173.6306340101291</v>
+      </c>
+      <c r="I20" s="17">
+        <v>7700.3977334383871</v>
+      </c>
+      <c r="J20" s="17">
+        <v>117507.74436055892</v>
+      </c>
+      <c r="K20" s="17">
+        <v>315232.50397653977</v>
+      </c>
+      <c r="L20" s="17">
+        <v>137757.25064697993</v>
+      </c>
+      <c r="M20" s="17">
+        <v>23.887054558579301</v>
+      </c>
+      <c r="N20" s="17">
+        <v>10.630116297173496</v>
+      </c>
+      <c r="O20" s="17">
+        <v>12941.619902553473</v>
+      </c>
+      <c r="P20" s="17">
+        <v>6829.2880756010709</v>
+      </c>
+      <c r="Q20" s="17">
+        <v>0.99011228412205488</v>
+      </c>
+      <c r="R20" s="17">
+        <v>1162.0598783187363</v>
+      </c>
+      <c r="S20" s="17">
+        <v>2487.1201872007637</v>
+      </c>
+      <c r="T20" s="17">
+        <v>788081.2599413495</v>
+      </c>
+      <c r="U20" s="17">
+        <v>7779.4824577979125</v>
+      </c>
+      <c r="V20" s="17">
+        <v>622406.814173633</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="C21" s="17">
+        <v>4506.4720702113282</v>
+      </c>
+      <c r="D21" s="17">
+        <v>1237.8443466263898</v>
+      </c>
+      <c r="E21" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F21" s="17">
+        <v>3921.6241291317938</v>
+      </c>
+      <c r="G21" s="17">
+        <v>1247.7923804527093</v>
+      </c>
+      <c r="H21" s="17">
+        <v>447.74442370759789</v>
+      </c>
+      <c r="I21" s="17">
+        <v>7405.7577728634324</v>
+      </c>
+      <c r="J21" s="17">
+        <v>120746.12116199643</v>
+      </c>
+      <c r="K21" s="17">
+        <v>323919.94524683047</v>
+      </c>
+      <c r="L21" s="17">
+        <v>141780.80722790223</v>
+      </c>
+      <c r="M21" s="17">
+        <v>23.242725160827526</v>
+      </c>
+      <c r="N21" s="17">
+        <v>10.198269471027357</v>
+      </c>
+      <c r="O21" s="17">
+        <v>13751.892148659181</v>
+      </c>
+      <c r="P21" s="17">
+        <v>7545.4352560223924</v>
+      </c>
+      <c r="Q21" s="17">
+        <v>1.0156068599449528</v>
+      </c>
+      <c r="R21" s="17">
+        <v>1240.7425352944572</v>
+      </c>
+      <c r="S21" s="17">
+        <v>2251.7511475437595</v>
+      </c>
+      <c r="T21" s="17">
+        <v>809799.86311707599</v>
+      </c>
+      <c r="U21" s="17">
+        <v>8146.1043519154309</v>
+      </c>
+      <c r="V21" s="17">
+        <v>639726.94751074491</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B28" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B29" s="17">
+        <v>2.5</v>
+      </c>
+      <c r="C29" s="17">
+        <v>0.7923284844832259</v>
+      </c>
+      <c r="D29" s="17">
+        <v>3.8154381558204453</v>
+      </c>
+      <c r="E29" s="17">
+        <v>0.26209309629996269</v>
+      </c>
+      <c r="F29" s="17">
+        <v>1.1916757448054462E-2</v>
+      </c>
+      <c r="G29" s="17">
+        <v>0.69894946572786509</v>
+      </c>
+      <c r="H29" s="17">
+        <v>20.767151551677422</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="17">
+        <v>2.7</v>
+      </c>
+      <c r="C30" s="17">
+        <v>0.79082871851109049</v>
+      </c>
+      <c r="D30" s="17">
+        <v>3.7809129581526921</v>
+      </c>
+      <c r="E30" s="17">
+        <v>0.26448638492026744</v>
+      </c>
+      <c r="F30" s="17">
+        <v>1.161515776460759E-2</v>
+      </c>
+      <c r="G30" s="17">
+        <v>0.68241878707814208</v>
+      </c>
+      <c r="H30" s="17">
+        <v>20.917128148890953</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="17">
+        <v>2.9</v>
+      </c>
+      <c r="C31" s="17">
+        <v>0.79007676096351509</v>
+      </c>
+      <c r="D31" s="17">
+        <v>3.7637878632519213</v>
+      </c>
+      <c r="E31" s="17">
+        <v>0.26568978814230981</v>
+      </c>
+      <c r="F31" s="17">
+        <v>1.1484389958345869E-2</v>
+      </c>
+      <c r="G31" s="17">
+        <v>0.67525140361693714</v>
+      </c>
+      <c r="H31" s="17">
+        <v>20.992323903648501</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="17">
+        <v>3.1</v>
+      </c>
+      <c r="C32" s="17">
+        <v>0.78977645615030179</v>
+      </c>
+      <c r="D32" s="17">
+        <v>3.7569825059252802</v>
+      </c>
+      <c r="E32" s="17">
+        <v>0.26617105574030808</v>
+      </c>
+      <c r="F32" s="17">
+        <v>1.1421118297927127E-2</v>
+      </c>
+      <c r="G32" s="17">
+        <v>0.6717834839093858</v>
+      </c>
+      <c r="H32" s="17">
+        <v>21.022354384969834</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="17">
+        <v>3.3</v>
+      </c>
+      <c r="C33" s="17">
+        <v>0.78977492019027795</v>
+      </c>
+      <c r="D33" s="17">
+        <v>3.7569473666106021</v>
+      </c>
+      <c r="E33" s="17">
+        <v>0.26617354527970616</v>
+      </c>
+      <c r="F33" s="17">
+        <v>1.1388229853412446E-2</v>
+      </c>
+      <c r="G33" s="17">
+        <v>0.66998086826553627</v>
+      </c>
+      <c r="H33" s="17">
+        <v>21.022507980972204</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="C34" s="17">
+        <v>0.78998154562327583</v>
+      </c>
+      <c r="D34" s="17">
+        <v>3.7616268640132273</v>
+      </c>
+      <c r="E34" s="17">
+        <v>0.26584242301298167</v>
+      </c>
+      <c r="F34" s="17">
+        <v>1.1370614920618203E-2</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0.6690153937990837</v>
+      </c>
+      <c r="H34" s="17">
+        <v>21.001845437672419</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5BF8E15-0944-4FE7-87E9-AAA093D2FC4F}">
+  <dimension ref="B2:V35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="11.5546875" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B2" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B3" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="C3" s="17">
+        <v>84.211561976013954</v>
+      </c>
+      <c r="D3" s="17">
+        <v>7.8630926606964033</v>
+      </c>
+      <c r="E3" s="17">
+        <v>41.852285461263897</v>
+      </c>
+      <c r="F3" s="17">
+        <v>14.609756931868748</v>
+      </c>
+      <c r="G3" s="17">
+        <v>38.581243760380737</v>
+      </c>
+      <c r="H3" s="17">
+        <v>16.25771923391715</v>
+      </c>
+      <c r="I3" s="17">
+        <v>15.888509699581155</v>
+      </c>
+      <c r="J3" s="17">
+        <v>71.616789037388912</v>
+      </c>
+      <c r="K3" s="17">
+        <v>38.409525516739883</v>
+      </c>
+      <c r="L3" s="17">
+        <v>343.25374370062394</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B4" s="17">
+        <v>0.65</v>
+      </c>
+      <c r="C4" s="17">
+        <v>95.281754998553794</v>
+      </c>
+      <c r="D4" s="17">
+        <v>7.8332887957953403</v>
+      </c>
+      <c r="E4" s="17">
+        <v>44.933380647869939</v>
+      </c>
+      <c r="F4" s="17">
+        <v>15.845474212445962</v>
+      </c>
+      <c r="G4" s="17">
+        <v>41.842329326986977</v>
+      </c>
+      <c r="H4" s="17">
+        <v>16.28502694489416</v>
+      </c>
+      <c r="I4" s="17">
+        <v>15.915275564920073</v>
+      </c>
+      <c r="J4" s="17">
+        <v>71.644726145929837</v>
+      </c>
+      <c r="K4" s="17">
+        <v>38.328417839914948</v>
+      </c>
+      <c r="L4" s="17">
+        <v>342.528910125138</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B5" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="C5" s="17">
+        <v>106.35197332921997</v>
+      </c>
+      <c r="D5" s="17">
+        <v>7.8034867682354951</v>
+      </c>
+      <c r="E5" s="17">
+        <v>47.714779598232667</v>
+      </c>
+      <c r="F5" s="17">
+        <v>16.960993627423512</v>
+      </c>
+      <c r="G5" s="17">
+        <v>44.786209962074224</v>
+      </c>
+      <c r="H5" s="17">
+        <v>16.312467590576237</v>
+      </c>
+      <c r="I5" s="17">
+        <v>15.942171998171231</v>
+      </c>
+      <c r="J5" s="17">
+        <v>71.672715315581797</v>
+      </c>
+      <c r="K5" s="17">
+        <v>38.247141925589851</v>
+      </c>
+      <c r="L5" s="17">
+        <v>341.80257306448817</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B6" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="C6" s="17">
+        <v>117.42221717459931</v>
+      </c>
+      <c r="D6" s="17">
+        <v>7.7736866894088301</v>
+      </c>
+      <c r="E6" s="17">
+        <v>50.238175942453644</v>
+      </c>
+      <c r="F6" s="17">
+        <v>17.973037039039568</v>
+      </c>
+      <c r="G6" s="17">
+        <v>47.457015044388491</v>
+      </c>
+      <c r="H6" s="17">
+        <v>16.340042169130623</v>
+      </c>
+      <c r="I6" s="17">
+        <v>15.969199981553711</v>
+      </c>
+      <c r="J6" s="17">
+        <v>71.700756546104344</v>
+      </c>
+      <c r="K6" s="17">
+        <v>38.165697124592612</v>
+      </c>
+      <c r="L6" s="17">
+        <v>341.07472671723065</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B7" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="C7" s="17">
+        <v>128.49248674250657</v>
+      </c>
+      <c r="D7" s="17">
+        <v>7.743888671611427</v>
+      </c>
+      <c r="E7" s="17">
+        <v>52.537872183380294</v>
+      </c>
+      <c r="F7" s="17">
+        <v>18.895361985772201</v>
+      </c>
+      <c r="G7" s="17">
+        <v>49.891051034146052</v>
+      </c>
+      <c r="H7" s="17">
+        <v>16.36775168897524</v>
+      </c>
+      <c r="I7" s="17">
+        <v>15.996360507390436</v>
+      </c>
+      <c r="J7" s="17">
+        <v>71.728849836347308</v>
+      </c>
+      <c r="K7" s="17">
+        <v>38.084082784419742</v>
+      </c>
+      <c r="L7" s="17">
+        <v>340.34536525214861</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B8" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="C8" s="17">
+        <v>139.56278198500698</v>
+      </c>
+      <c r="D8" s="17">
+        <v>7.7140927853093819</v>
+      </c>
+      <c r="E8" s="17">
+        <v>54.642345188567155</v>
+      </c>
+      <c r="F8" s="17">
+        <v>19.73938966239082</v>
+      </c>
+      <c r="G8" s="17">
+        <v>52.118458725483521</v>
+      </c>
+      <c r="H8" s="17">
+        <v>16.395597206045643</v>
+      </c>
+      <c r="I8" s="17">
+        <v>16.023654614611125</v>
+      </c>
+      <c r="J8" s="17">
+        <v>71.756995183209312</v>
+      </c>
+      <c r="K8" s="17">
+        <v>38.002298124925424</v>
+      </c>
+      <c r="L8" s="17">
+        <v>339.61448169732654</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B9" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="C9" s="17">
+        <v>150.63310366538568</v>
+      </c>
+      <c r="D9" s="17">
+        <v>7.6842992366371705</v>
+      </c>
+      <c r="E9" s="17">
+        <v>56.575443092400867</v>
+      </c>
+      <c r="F9" s="17">
+        <v>20.51468447118021</v>
+      </c>
+      <c r="G9" s="17">
+        <v>54.164478798760605</v>
+      </c>
+      <c r="H9" s="17">
+        <v>16.423579669894796</v>
+      </c>
+      <c r="I9" s="17">
+        <v>16.051083238013277</v>
+      </c>
+      <c r="J9" s="17">
+        <v>71.785192585913705</v>
+      </c>
+      <c r="K9" s="17">
+        <v>37.920342754213891</v>
+      </c>
+      <c r="L9" s="17">
+        <v>338.88207255051623</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B15" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="M15" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="O15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="P15" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="R15" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="S15" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="U15" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="V15" s="18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B16" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="C16" s="17">
+        <v>3188.5506685029641</v>
+      </c>
+      <c r="D16" s="17">
+        <v>1043.876310747346</v>
+      </c>
+      <c r="E16" s="17">
+        <v>8610.2319558728486</v>
+      </c>
+      <c r="F16" s="17">
+        <v>15551.202889850705</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1111.5831277611805</v>
+      </c>
+      <c r="H16" s="17">
+        <v>4828.1167891059304</v>
+      </c>
+      <c r="I16" s="17">
+        <v>9352.6697515099131</v>
+      </c>
+      <c r="J16" s="17">
+        <v>79195.96700526237</v>
+      </c>
+      <c r="K16" s="17">
+        <v>212455.29917849187</v>
+      </c>
+      <c r="L16" s="17">
+        <v>91682.455189337765</v>
+      </c>
+      <c r="M16" s="17">
+        <v>26.319321122467287</v>
+      </c>
+      <c r="N16" s="17">
+        <v>12.295199599041567</v>
+      </c>
+      <c r="O16" s="17">
+        <v>10362.045100531313</v>
+      </c>
+      <c r="P16" s="17">
+        <v>4885.1662034555775</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0.90361665491794607</v>
+      </c>
+      <c r="R16" s="17">
+        <v>928.39153384896269</v>
+      </c>
+      <c r="S16" s="17">
+        <v>3690.2939294248226</v>
+      </c>
+      <c r="T16" s="17">
+        <v>531138.24794622965</v>
+      </c>
+      <c r="U16" s="17">
+        <v>6609.1306684771125</v>
+      </c>
+      <c r="V16" s="17">
+        <v>453534.49843955727</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B17" s="17">
+        <v>0.65</v>
+      </c>
+      <c r="C17" s="17">
+        <v>3185.6026611351294</v>
+      </c>
+      <c r="D17" s="17">
+        <v>1047.8213709567915</v>
+      </c>
+      <c r="E17" s="17">
+        <v>7544.4300571883768</v>
+      </c>
+      <c r="F17" s="17">
+        <v>13641.822894306615</v>
+      </c>
+      <c r="G17" s="17">
+        <v>1108.2559641090977</v>
+      </c>
+      <c r="H17" s="17">
+        <v>4773.8608169536465</v>
+      </c>
+      <c r="I17" s="17">
+        <v>9254.7297393386671</v>
+      </c>
+      <c r="J17" s="17">
+        <v>83462.458846271998</v>
+      </c>
+      <c r="K17" s="17">
+        <v>223900.81635317404</v>
+      </c>
+      <c r="L17" s="17">
+        <v>96731.337537772473</v>
+      </c>
+      <c r="M17" s="17">
+        <v>26.354027026530865</v>
+      </c>
+      <c r="N17" s="17">
+        <v>12.319597142596336</v>
+      </c>
+      <c r="O17" s="17">
+        <v>10306.14186292257</v>
+      </c>
+      <c r="P17" s="17">
+        <v>4855.401858262283</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>0.90090077122570711</v>
+      </c>
+      <c r="R17" s="17">
+        <v>923.99223502528923</v>
+      </c>
+      <c r="S17" s="17">
+        <v>3692.7222397455644</v>
+      </c>
+      <c r="T17" s="17">
+        <v>559752.04088293505</v>
+      </c>
+      <c r="U17" s="17">
+        <v>6581.9762457248316</v>
+      </c>
+      <c r="V17" s="17">
+        <v>471050.94520782772</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B18" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="C18" s="17">
+        <v>3182.644455056779</v>
+      </c>
+      <c r="D18" s="17">
+        <v>1051.7772748712823</v>
+      </c>
+      <c r="E18" s="17">
+        <v>6475.6703599589018</v>
+      </c>
+      <c r="F18" s="17">
+        <v>11722.797219174221</v>
+      </c>
+      <c r="G18" s="17">
+        <v>1104.923475024757</v>
+      </c>
+      <c r="H18" s="17">
+        <v>4719.2041314713424</v>
+      </c>
+      <c r="I18" s="17">
+        <v>9157.0271064838616</v>
+      </c>
+      <c r="J18" s="17">
+        <v>87728.994646362858</v>
+      </c>
+      <c r="K18" s="17">
+        <v>235346.45145481778</v>
+      </c>
+      <c r="L18" s="17">
+        <v>101792.88253725517</v>
+      </c>
+      <c r="M18" s="17">
+        <v>26.388812877572651</v>
+      </c>
+      <c r="N18" s="17">
+        <v>12.344064045004503</v>
+      </c>
+      <c r="O18" s="17">
+        <v>10250.323800790415</v>
+      </c>
+      <c r="P18" s="17">
+        <v>4825.7715495631974</v>
+      </c>
+      <c r="Q18" s="17">
+        <v>0.89818063269454707</v>
+      </c>
+      <c r="R18" s="17">
+        <v>919.60136568056782</v>
+      </c>
+      <c r="S18" s="17">
+        <v>3695.1392369119085</v>
+      </c>
+      <c r="T18" s="17">
+        <v>588366.12863704446</v>
+      </c>
+      <c r="U18" s="17">
+        <v>6554.8291499897132</v>
+      </c>
+      <c r="V18" s="17">
+        <v>488567.6688209679</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B19" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="C19" s="17">
+        <v>3179.6759917278887</v>
+      </c>
+      <c r="D19" s="17">
+        <v>1055.7440776822809</v>
+      </c>
+      <c r="E19" s="17">
+        <v>5403.9352110712753</v>
+      </c>
+      <c r="F19" s="17">
+        <v>9794.0194828991152</v>
+      </c>
+      <c r="G19" s="17">
+        <v>1101.5856640998954</v>
+      </c>
+      <c r="H19" s="17">
+        <v>4664.1478209078205</v>
+      </c>
+      <c r="I19" s="17">
+        <v>9059.5629791777956</v>
+      </c>
+      <c r="J19" s="17">
+        <v>91995.574525781194</v>
+      </c>
+      <c r="K19" s="17">
+        <v>246792.20480600206</v>
+      </c>
+      <c r="L19" s="17">
+        <v>106867.21213527194</v>
+      </c>
+      <c r="M19" s="17">
+        <v>26.423678762950853</v>
+      </c>
+      <c r="N19" s="17">
+        <v>12.368600444652017</v>
+      </c>
+      <c r="O19" s="17">
+        <v>10194.591485539635</v>
+      </c>
+      <c r="P19" s="17">
+        <v>4796.2748915086886</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>0.89545624248824884</v>
+      </c>
+      <c r="R19" s="17">
+        <v>915.21892164972576</v>
+      </c>
+      <c r="S19" s="17">
+        <v>3697.5447688577583</v>
+      </c>
+      <c r="T19" s="17">
+        <v>616980.51201500499</v>
+      </c>
+      <c r="U19" s="17">
+        <v>6527.6895138187447</v>
+      </c>
+      <c r="V19" s="17">
+        <v>506084.670011446</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="C20" s="17">
+        <v>3176.6972121346889</v>
+      </c>
+      <c r="D20" s="17">
+        <v>1059.721835024003</v>
+      </c>
+      <c r="E20" s="17">
+        <v>4329.206793663554</v>
+      </c>
+      <c r="F20" s="17">
+        <v>7855.3814543741792</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1098.2430498994579</v>
+      </c>
+      <c r="H20" s="17">
+        <v>4608.6931025683307</v>
+      </c>
+      <c r="I20" s="17">
+        <v>8962.3384882152895</v>
+      </c>
+      <c r="J20" s="17">
+        <v>96262.198605157217</v>
+      </c>
+      <c r="K20" s="17">
+        <v>258238.07673033568</v>
+      </c>
+      <c r="L20" s="17">
+        <v>111954.45016030467</v>
+      </c>
+      <c r="M20" s="17">
+        <v>26.45862476931628</v>
+      </c>
+      <c r="N20" s="17">
+        <v>12.393206479507223</v>
+      </c>
+      <c r="O20" s="17">
+        <v>10138.94548999074</v>
+      </c>
+      <c r="P20" s="17">
+        <v>4766.910980901248</v>
+      </c>
+      <c r="Q20" s="17">
+        <v>0.89272760389944328</v>
+      </c>
+      <c r="R20" s="17">
+        <v>910.84489976972441</v>
+      </c>
+      <c r="S20" s="17">
+        <v>3699.9386821275457</v>
+      </c>
+      <c r="T20" s="17">
+        <v>645595.19182583911</v>
+      </c>
+      <c r="U20" s="17">
+        <v>6500.5574707715496</v>
+      </c>
+      <c r="V20" s="17">
+        <v>523601.94951409067</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="C21" s="17">
+        <v>3173.7080391990989</v>
+      </c>
+      <c r="D21" s="17">
+        <v>1063.7106287563015</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3251.4671250847132</v>
+      </c>
+      <c r="F21" s="17">
+        <v>5906.7693275598585</v>
+      </c>
+      <c r="G21" s="17">
+        <v>1094.8945809626541</v>
+      </c>
+      <c r="H21" s="17">
+        <v>4552.8544882684373</v>
+      </c>
+      <c r="I21" s="17">
+        <v>8865.3546420253879</v>
+      </c>
+      <c r="J21" s="17">
+        <v>100528.87198471166</v>
+      </c>
+      <c r="K21" s="17">
+        <v>269684.0809099414</v>
+      </c>
+      <c r="L21" s="17">
+        <v>117054.72843049669</v>
+      </c>
+      <c r="M21" s="17">
+        <v>26.493650980813314</v>
+      </c>
+      <c r="N21" s="17">
+        <v>12.417882287122572</v>
+      </c>
+      <c r="O21" s="17">
+        <v>10083.386332505124</v>
+      </c>
+      <c r="P21" s="17">
+        <v>4737.680452731639</v>
+      </c>
+      <c r="Q21" s="17">
+        <v>0.88999471541966435</v>
+      </c>
+      <c r="R21" s="17">
+        <v>906.47929000459351</v>
+      </c>
+      <c r="S21" s="17">
+        <v>3702.3208011292131</v>
+      </c>
+      <c r="T21" s="17">
+        <v>674210.20227485348</v>
+      </c>
+      <c r="U21" s="17">
+        <v>6473.4331167445353</v>
+      </c>
+      <c r="V21" s="17">
+        <v>541119.54167810467</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B22" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="C22" s="17">
+        <v>3170.7084507537484</v>
+      </c>
+      <c r="D22" s="17">
+        <v>1067.7104599818438</v>
+      </c>
+      <c r="E22" s="17">
+        <v>2170.6980548234433</v>
+      </c>
+      <c r="F22" s="17">
+        <v>3948.0789449175445</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1091.540809577046</v>
+      </c>
+      <c r="H22" s="17">
+        <v>4496.6051596002653</v>
+      </c>
+      <c r="I22" s="17">
+        <v>8768.6128540601658</v>
+      </c>
+      <c r="J22" s="17">
+        <v>104795.58407176075</v>
+      </c>
+      <c r="K22" s="17">
+        <v>281130.18892832403</v>
+      </c>
+      <c r="L22" s="17">
+        <v>122168.16161023772</v>
+      </c>
+      <c r="M22" s="17">
+        <v>26.52875748258317</v>
+      </c>
+      <c r="N22" s="17">
+        <v>12.442628004623598</v>
+      </c>
+      <c r="O22" s="17">
+        <v>10027.914709061537</v>
+      </c>
+      <c r="P22" s="17">
+        <v>4708.5824367404157</v>
+      </c>
+      <c r="Q22" s="17">
+        <v>0.88725759121543613</v>
+      </c>
+      <c r="R22" s="17">
+        <v>902.12210022993486</v>
+      </c>
+      <c r="S22" s="17">
+        <v>3704.6910141341332</v>
+      </c>
+      <c r="T22" s="17">
+        <v>702825.47232081008</v>
+      </c>
+      <c r="U22" s="17">
+        <v>6446.3166706272159</v>
+      </c>
+      <c r="V22" s="17">
+        <v>558637.37491790799</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B28" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B29" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="C29" s="17">
+        <v>0.85389161897727106</v>
+      </c>
+      <c r="D29" s="17">
+        <v>5.8446668412028737</v>
+      </c>
+      <c r="E29" s="17">
+        <v>0.17109615093033992</v>
+      </c>
+      <c r="F29" s="17">
+        <v>1.2054140014573155E-2</v>
+      </c>
+      <c r="G29" s="17">
+        <v>0.70647940419875466</v>
+      </c>
+      <c r="H29" s="17">
+        <v>14.610838102272893</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="17">
+        <v>0.65</v>
+      </c>
+      <c r="C30" s="17">
+        <v>0.84153502051516771</v>
+      </c>
+      <c r="D30" s="17">
+        <v>5.3108856777172182</v>
+      </c>
+      <c r="E30" s="17">
+        <v>0.18829251102046518</v>
+      </c>
+      <c r="F30" s="17">
+        <v>1.1935407594307215E-2</v>
+      </c>
+      <c r="G30" s="17">
+        <v>0.69997168024397849</v>
+      </c>
+      <c r="H30" s="17">
+        <v>15.846497948483229</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="C31" s="17">
+        <v>0.83038034489296564</v>
+      </c>
+      <c r="D31" s="17">
+        <v>4.8958236948474463</v>
+      </c>
+      <c r="E31" s="17">
+        <v>0.20425572126962793</v>
+      </c>
+      <c r="F31" s="17">
+        <v>1.1841379034640441E-2</v>
+      </c>
+      <c r="G31" s="17">
+        <v>0.69481797488864261</v>
+      </c>
+      <c r="H31" s="17">
+        <v>16.961965510703447</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="C32" s="17">
+        <v>0.82026038125356215</v>
+      </c>
+      <c r="D32" s="17">
+        <v>4.5638384846804652</v>
+      </c>
+      <c r="E32" s="17">
+        <v>0.21911380154155796</v>
+      </c>
+      <c r="F32" s="17">
+        <v>1.176511508779335E-2</v>
+      </c>
+      <c r="G32" s="17">
+        <v>0.69063794796195355</v>
+      </c>
+      <c r="H32" s="17">
+        <v>17.973961874643784</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="C33" s="17">
+        <v>0.81103756060088761</v>
+      </c>
+      <c r="D33" s="17">
+        <v>4.2922573338980294</v>
+      </c>
+      <c r="E33" s="17">
+        <v>0.2329776437452892</v>
+      </c>
+      <c r="F33" s="17">
+        <v>1.1701992017364047E-2</v>
+      </c>
+      <c r="G33" s="17">
+        <v>0.68717817247172341</v>
+      </c>
+      <c r="H33" s="17">
+        <v>18.896243939911241</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="C34" s="17">
+        <v>0.8025976762919228</v>
+      </c>
+      <c r="D34" s="17">
+        <v>4.0659700731330144</v>
+      </c>
+      <c r="E34" s="17">
+        <v>0.24594376791107433</v>
+      </c>
+      <c r="F34" s="17">
+        <v>1.1648885335282464E-2</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0.68426739522683189</v>
+      </c>
+      <c r="H34" s="17">
+        <v>19.740232370807721</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="C35" s="17">
+        <v>0.79484508874333115</v>
+      </c>
+      <c r="D35" s="17">
+        <v>3.8745177380620159</v>
+      </c>
+      <c r="E35" s="17">
+        <v>0.2580966374669863</v>
+      </c>
+      <c r="F35" s="17">
+        <v>1.1603605702897936E-2</v>
+      </c>
+      <c r="G35" s="17">
+        <v>0.68178561857583586</v>
+      </c>
+      <c r="H35" s="17">
+        <v>20.515491125666873</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609148A7-EAA7-4F28-BBF6-02D6EA60B99E}">
+  <dimension ref="B2:V35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="11.5546875" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B2" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B3" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="C3" s="17">
+        <v>130.86918068201132</v>
+      </c>
+      <c r="D3" s="17">
+        <v>8.8141654444115058</v>
+      </c>
+      <c r="E3" s="17">
+        <v>49.878796554537139</v>
+      </c>
+      <c r="F3" s="17">
+        <v>17.815192680590009</v>
+      </c>
+      <c r="G3" s="17">
+        <v>47.03974603996263</v>
+      </c>
+      <c r="H3" s="17">
+        <v>15.454823679518492</v>
+      </c>
+      <c r="I3" s="17">
+        <v>15.101699640128905</v>
+      </c>
+      <c r="J3" s="17">
+        <v>70.81030342479761</v>
+      </c>
+      <c r="K3" s="17">
+        <v>40.922629894870369</v>
+      </c>
+      <c r="L3" s="17">
+        <v>365.71256021809842</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B4" s="17">
+        <v>0.65</v>
+      </c>
+      <c r="C4" s="17">
+        <v>137.01888853317391</v>
+      </c>
+      <c r="D4" s="17">
+        <v>8.5397213545798163</v>
+      </c>
+      <c r="E4" s="17">
+        <v>51.771991448655704</v>
+      </c>
+      <c r="F4" s="17">
+        <v>18.577736186967428</v>
+      </c>
+      <c r="G4" s="17">
+        <v>49.052303063086939</v>
+      </c>
+      <c r="H4" s="17">
+        <v>15.67755876168555</v>
+      </c>
+      <c r="I4" s="17">
+        <v>15.319976571220023</v>
+      </c>
+      <c r="J4" s="17">
+        <v>71.083142907569311</v>
+      </c>
+      <c r="K4" s="17">
+        <v>40.221665830556631</v>
+      </c>
+      <c r="L4" s="17">
+        <v>359.44826676385026</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B5" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="C5" s="17">
+        <v>142.30508065956138</v>
+      </c>
+      <c r="D5" s="17">
+        <v>8.3060695450992057</v>
+      </c>
+      <c r="E5" s="17">
+        <v>53.363862994038215</v>
+      </c>
+      <c r="F5" s="17">
+        <v>19.218978885217201</v>
+      </c>
+      <c r="G5" s="17">
+        <v>50.744709448083036</v>
+      </c>
+      <c r="H5" s="17">
+        <v>15.874683129121278</v>
+      </c>
+      <c r="I5" s="17">
+        <v>15.513171109606835</v>
+      </c>
+      <c r="J5" s="17">
+        <v>71.319466062871072</v>
+      </c>
+      <c r="K5" s="17">
+        <v>39.614661310623802</v>
+      </c>
+      <c r="L5" s="17">
+        <v>354.02365994803995</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B6" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="C6" s="17">
+        <v>146.89827318466655</v>
+      </c>
+      <c r="D6" s="17">
+        <v>8.1049138972325512</v>
+      </c>
+      <c r="E6" s="17">
+        <v>54.719894700628537</v>
+      </c>
+      <c r="F6" s="17">
+        <v>19.765266768229527</v>
+      </c>
+      <c r="G6" s="17">
+        <v>52.186501352649742</v>
+      </c>
+      <c r="H6" s="17">
+        <v>16.050273489693183</v>
+      </c>
+      <c r="I6" s="17">
+        <v>15.685273418138657</v>
+      </c>
+      <c r="J6" s="17">
+        <v>71.526102579273243</v>
+      </c>
+      <c r="K6" s="17">
+        <v>39.084241310864769</v>
+      </c>
+      <c r="L6" s="17">
+        <v>349.28346469174556</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B7" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="C7" s="17">
+        <v>150.92661980778519</v>
+      </c>
+      <c r="D7" s="17">
+        <v>7.9300370676916589</v>
+      </c>
+      <c r="E7" s="17">
+        <v>55.888023789679387</v>
+      </c>
+      <c r="F7" s="17">
+        <v>20.235891351627959</v>
+      </c>
+      <c r="G7" s="17">
+        <v>53.42859555121403</v>
+      </c>
+      <c r="H7" s="17">
+        <v>16.207600873594352</v>
+      </c>
+      <c r="I7" s="17">
+        <v>15.839485575111897</v>
+      </c>
+      <c r="J7" s="17">
+        <v>71.708294275735227</v>
+      </c>
+      <c r="K7" s="17">
+        <v>38.617016986964416</v>
+      </c>
+      <c r="L7" s="17">
+        <v>345.10802914108001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B8" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="C8" s="17">
+        <v>154.48837379671122</v>
+      </c>
+      <c r="D8" s="17">
+        <v>7.7766933290369442</v>
+      </c>
+      <c r="E8" s="17">
+        <v>56.904129154565318</v>
+      </c>
+      <c r="F8" s="17">
+        <v>20.645294276473038</v>
+      </c>
+      <c r="G8" s="17">
+        <v>54.509108246619817</v>
+      </c>
+      <c r="H8" s="17">
+        <v>16.349317243377286</v>
+      </c>
+      <c r="I8" s="17">
+        <v>15.978403991712717</v>
+      </c>
+      <c r="J8" s="17">
+        <v>71.870125868264836</v>
+      </c>
+      <c r="K8" s="17">
+        <v>38.202512795285671</v>
+      </c>
+      <c r="L8" s="17">
+        <v>341.40373668603996</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B9" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="C9" s="17">
+        <v>157.6601720704559</v>
+      </c>
+      <c r="D9" s="17">
+        <v>7.6412011923432459</v>
+      </c>
+      <c r="E9" s="17">
+        <v>57.795583221044943</v>
+      </c>
+      <c r="F9" s="17">
+        <v>21.004494873055776</v>
+      </c>
+      <c r="G9" s="17">
+        <v>55.457122957656523</v>
+      </c>
+      <c r="H9" s="17">
+        <v>16.477593217708954</v>
+      </c>
+      <c r="I9" s="17">
+        <v>16.104154074250307</v>
+      </c>
+      <c r="J9" s="17">
+        <v>72.014824656586995</v>
+      </c>
+      <c r="K9" s="17">
+        <v>37.832420978038627</v>
+      </c>
+      <c r="L9" s="17">
+        <v>338.09634353098392</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B15" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="M15" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="O15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="P15" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="R15" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="S15" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="U15" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="V15" s="18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B16" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="C16" s="17">
+        <v>17223.530390651405</v>
+      </c>
+      <c r="D16" s="17">
+        <v>5103.7799140514026</v>
+      </c>
+      <c r="E16" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F16" s="17">
+        <v>2807.373846715212</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1210.8751990759354</v>
+      </c>
+      <c r="H16" s="17">
+        <v>1104.7199639895116</v>
+      </c>
+      <c r="I16" s="17">
+        <v>9283.7734881358447</v>
+      </c>
+      <c r="J16" s="17">
+        <v>103269.46782608512</v>
+      </c>
+      <c r="K16" s="17">
+        <v>277036.14858994889</v>
+      </c>
+      <c r="L16" s="17">
+        <v>120250.45822234853</v>
+      </c>
+      <c r="M16" s="17">
+        <v>0.2517453525309708</v>
+      </c>
+      <c r="N16" s="17">
+        <v>0.11458911717440511</v>
+      </c>
+      <c r="O16" s="17">
+        <v>12258.929861073375</v>
+      </c>
+      <c r="P16" s="17">
+        <v>5968.311954203029</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0.98477814386777573</v>
+      </c>
+      <c r="R16" s="17">
+        <v>1077.6192924360903</v>
+      </c>
+      <c r="S16" s="17">
+        <v>3581.036050913548</v>
+      </c>
+      <c r="T16" s="17">
+        <v>692590.37147487211</v>
+      </c>
+      <c r="U16" s="17">
+        <v>7478.1116504062575</v>
+      </c>
+      <c r="V16" s="17">
+        <v>569197.94407274295</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B17" s="17">
+        <v>0.65</v>
+      </c>
+      <c r="C17" s="17">
+        <v>13889.07170678319</v>
+      </c>
+      <c r="D17" s="17">
+        <v>4246.1216538053413</v>
+      </c>
+      <c r="E17" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F17" s="17">
+        <v>2807.373846715212</v>
+      </c>
+      <c r="G17" s="17">
+        <v>1182.6470103258118</v>
+      </c>
+      <c r="H17" s="17">
+        <v>1791.6358617457445</v>
+      </c>
+      <c r="I17" s="17">
+        <v>9173.6007419972721</v>
+      </c>
+      <c r="J17" s="17">
+        <v>104168.42351101463</v>
+      </c>
+      <c r="K17" s="17">
+        <v>279447.73476298235</v>
+      </c>
+      <c r="L17" s="17">
+        <v>121347.12487858563</v>
+      </c>
+      <c r="M17" s="17">
+        <v>0.25506000082520519</v>
+      </c>
+      <c r="N17" s="17">
+        <v>0.11686810867505278</v>
+      </c>
+      <c r="O17" s="17">
+        <v>11706.898845704814</v>
+      </c>
+      <c r="P17" s="17">
+        <v>5640.9449889946964</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>0.96169692888734515</v>
+      </c>
+      <c r="R17" s="17">
+        <v>1033.7214813554442</v>
+      </c>
+      <c r="S17" s="17">
+        <v>3620.0084021298612</v>
+      </c>
+      <c r="T17" s="17">
+        <v>698619.33690745581</v>
+      </c>
+      <c r="U17" s="17">
+        <v>7226.5680808477873</v>
+      </c>
+      <c r="V17" s="17">
+        <v>568825.66610812175</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B18" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="C18" s="17">
+        <v>11038.113043195457</v>
+      </c>
+      <c r="D18" s="17">
+        <v>3465.8458866495639</v>
+      </c>
+      <c r="E18" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F18" s="17">
+        <v>2807.373846715212</v>
+      </c>
+      <c r="G18" s="17">
+        <v>1158.2224463140453</v>
+      </c>
+      <c r="H18" s="17">
+        <v>2430.7471421233495</v>
+      </c>
+      <c r="I18" s="17">
+        <v>9066.7993777505453</v>
+      </c>
+      <c r="J18" s="17">
+        <v>104959.96261811555</v>
+      </c>
+      <c r="K18" s="17">
+        <v>281571.15953029942</v>
+      </c>
+      <c r="L18" s="17">
+        <v>122313.69926104051</v>
+      </c>
+      <c r="M18" s="17">
+        <v>0.25794191262521177</v>
+      </c>
+      <c r="N18" s="17">
+        <v>0.11885920781892506</v>
+      </c>
+      <c r="O18" s="17">
+        <v>11242.094633094242</v>
+      </c>
+      <c r="P18" s="17">
+        <v>5373.4938759398001</v>
+      </c>
+      <c r="Q18" s="17">
+        <v>0.94173270359819072</v>
+      </c>
+      <c r="R18" s="17">
+        <v>997.01597907764994</v>
+      </c>
+      <c r="S18" s="17">
+        <v>3653.1722462794478</v>
+      </c>
+      <c r="T18" s="17">
+        <v>703927.89882574859</v>
+      </c>
+      <c r="U18" s="17">
+        <v>7012.7467667503342</v>
+      </c>
+      <c r="V18" s="17">
+        <v>568634.22189726471</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B19" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="C19" s="17">
+        <v>8573.5098078967039</v>
+      </c>
+      <c r="D19" s="17">
+        <v>2754.6230259247086</v>
+      </c>
+      <c r="E19" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F19" s="17">
+        <v>2807.373846715212</v>
+      </c>
+      <c r="G19" s="17">
+        <v>1136.9071821083016</v>
+      </c>
+      <c r="H19" s="17">
+        <v>3023.7047411040985</v>
+      </c>
+      <c r="I19" s="17">
+        <v>8965.1619450556045</v>
+      </c>
+      <c r="J19" s="17">
+        <v>105662.76220008062</v>
+      </c>
+      <c r="K19" s="17">
+        <v>283456.52694350353</v>
+      </c>
+      <c r="L19" s="17">
+        <v>123172.65806338149</v>
+      </c>
+      <c r="M19" s="17">
+        <v>0.2604700610476795</v>
+      </c>
+      <c r="N19" s="17">
+        <v>0.12061319440397289</v>
+      </c>
+      <c r="O19" s="17">
+        <v>10845.814830466486</v>
+      </c>
+      <c r="P19" s="17">
+        <v>5151.2288603062889</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>0.92431500080570184</v>
+      </c>
+      <c r="R19" s="17">
+        <v>965.89147864161771</v>
+      </c>
+      <c r="S19" s="17">
+        <v>3681.7827674106129</v>
+      </c>
+      <c r="T19" s="17">
+        <v>708641.31735875877</v>
+      </c>
+      <c r="U19" s="17">
+        <v>6828.9193675282904</v>
+      </c>
+      <c r="V19" s="17">
+        <v>568570.62716847542</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="C20" s="17">
+        <v>6422.209445343934</v>
+      </c>
+      <c r="D20" s="17">
+        <v>2104.9796883973145</v>
+      </c>
+      <c r="E20" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F20" s="17">
+        <v>2807.373846715212</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1118.1613002894633</v>
+      </c>
+      <c r="H20" s="17">
+        <v>3573.3140356715885</v>
+      </c>
+      <c r="I20" s="17">
+        <v>8869.4633253153861</v>
+      </c>
+      <c r="J20" s="17">
+        <v>106291.27448128449</v>
+      </c>
+      <c r="K20" s="17">
+        <v>285142.60730579839</v>
+      </c>
+      <c r="L20" s="17">
+        <v>123941.42024869514</v>
+      </c>
+      <c r="M20" s="17">
+        <v>0.26270550768952727</v>
+      </c>
+      <c r="N20" s="17">
+        <v>0.12216974083650543</v>
+      </c>
+      <c r="O20" s="17">
+        <v>10504.258527002828</v>
+      </c>
+      <c r="P20" s="17">
+        <v>4963.8129009404247</v>
+      </c>
+      <c r="Q20" s="17">
+        <v>0.90900061105456553</v>
+      </c>
+      <c r="R20" s="17">
+        <v>939.18089232948137</v>
+      </c>
+      <c r="S20" s="17">
+        <v>3706.7615776450862</v>
+      </c>
+      <c r="T20" s="17">
+        <v>712856.518264496</v>
+      </c>
+      <c r="U20" s="17">
+        <v>6669.3060430568084</v>
+      </c>
+      <c r="V20" s="17">
+        <v>568597.87420444074</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="C21" s="17">
+        <v>4528.3030015852082</v>
+      </c>
+      <c r="D21" s="17">
+        <v>1510.2579346330949</v>
+      </c>
+      <c r="E21" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F21" s="17">
+        <v>2807.373846715212</v>
+      </c>
+      <c r="G21" s="17">
+        <v>1101.5597781977049</v>
+      </c>
+      <c r="H21" s="17">
+        <v>4082.8254225992714</v>
+      </c>
+      <c r="I21" s="17">
+        <v>8779.9064915337567</v>
+      </c>
+      <c r="J21" s="17">
+        <v>106856.89298365323</v>
+      </c>
+      <c r="K21" s="17">
+        <v>286659.96548306081</v>
+      </c>
+      <c r="L21" s="17">
+        <v>124633.73733801451</v>
+      </c>
+      <c r="M21" s="17">
+        <v>0.26469613987200663</v>
+      </c>
+      <c r="N21" s="17">
+        <v>0.12356023428108251</v>
+      </c>
+      <c r="O21" s="17">
+        <v>10207.040222168094</v>
+      </c>
+      <c r="P21" s="17">
+        <v>4803.7955825387162</v>
+      </c>
+      <c r="Q21" s="17">
+        <v>0.89544089482254818</v>
+      </c>
+      <c r="R21" s="17">
+        <v>916.01886380869257</v>
+      </c>
+      <c r="S21" s="17">
+        <v>3728.7978136515972</v>
+      </c>
+      <c r="T21" s="17">
+        <v>716649.91370765201</v>
+      </c>
+      <c r="U21" s="17">
+        <v>6529.5033613763208</v>
+      </c>
+      <c r="V21" s="17">
+        <v>568689.71853090066</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B22" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="C22" s="17">
+        <v>2848.3263976414578</v>
+      </c>
+      <c r="D22" s="17">
+        <v>964.55767849983272</v>
+      </c>
+      <c r="E22" s="17">
+        <v>1542.4567100955248</v>
+      </c>
+      <c r="F22" s="17">
+        <v>2807.373846715212</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1086.7646432466843</v>
+      </c>
+      <c r="H22" s="17">
+        <v>4555.56180201401</v>
+      </c>
+      <c r="I22" s="17">
+        <v>8696.3788936835081</v>
+      </c>
+      <c r="J22" s="17">
+        <v>107368.74274104465</v>
+      </c>
+      <c r="K22" s="17">
+        <v>288033.08077482571</v>
+      </c>
+      <c r="L22" s="17">
+        <v>125260.63692308396</v>
+      </c>
+      <c r="M22" s="17">
+        <v>0.2664800015417999</v>
+      </c>
+      <c r="N22" s="17">
+        <v>0.12480980050803024</v>
+      </c>
+      <c r="O22" s="17">
+        <v>9946.2077370741645</v>
+      </c>
+      <c r="P22" s="17">
+        <v>4665.6811406944789</v>
+      </c>
+      <c r="Q22" s="17">
+        <v>0.88335841987004737</v>
+      </c>
+      <c r="R22" s="17">
+        <v>895.75064737944081</v>
+      </c>
+      <c r="S22" s="17">
+        <v>3748.4156267159824</v>
+      </c>
+      <c r="T22" s="17">
+        <v>720082.70193706418</v>
+      </c>
+      <c r="U22" s="17">
+        <v>6406.1012876481363</v>
+      </c>
+      <c r="V22" s="17">
+        <v>568827.31149858458</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B28" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B29" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="C29" s="17">
+        <v>0.82183923934812309</v>
+      </c>
+      <c r="D29" s="17">
+        <v>4.6131369673230234</v>
+      </c>
+      <c r="E29" s="17">
+        <v>0.21677223266585433</v>
+      </c>
+      <c r="F29" s="17">
+        <v>1.1717456361388412E-2</v>
+      </c>
+      <c r="G29" s="17">
+        <v>0.68802577316769886</v>
+      </c>
+      <c r="H29" s="17">
+        <v>17.81607606518768</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="17">
+        <v>0.65</v>
+      </c>
+      <c r="C30" s="17">
+        <v>0.81421403052786179</v>
+      </c>
+      <c r="D30" s="17">
+        <v>4.3827408373849428</v>
+      </c>
+      <c r="E30" s="17">
+        <v>0.22816772360116819</v>
+      </c>
+      <c r="F30" s="17">
+        <v>1.1681244010233967E-2</v>
+      </c>
+      <c r="G30" s="17">
+        <v>0.6860409742009238</v>
+      </c>
+      <c r="H30" s="17">
+        <v>18.578596947213832</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="C31" s="17">
+        <v>0.80780179737985547</v>
+      </c>
+      <c r="D31" s="17">
+        <v>4.2031462868258735</v>
+      </c>
+      <c r="E31" s="17">
+        <v>0.23791701067706084</v>
+      </c>
+      <c r="F31" s="17">
+        <v>1.1653403544510034E-2</v>
+      </c>
+      <c r="G31" s="17">
+        <v>0.68451503827459503</v>
+      </c>
+      <c r="H31" s="17">
+        <v>19.219820262014466</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="C32" s="17">
+        <v>0.8023390864191301</v>
+      </c>
+      <c r="D32" s="17">
+        <v>4.0593385145137582</v>
+      </c>
+      <c r="E32" s="17">
+        <v>0.24634555517471632</v>
+      </c>
+      <c r="F32" s="17">
+        <v>1.1631437078375764E-2</v>
+      </c>
+      <c r="G32" s="17">
+        <v>0.6833110562657756</v>
+      </c>
+      <c r="H32" s="17">
+        <v>19.766091358086978</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="C33" s="17">
+        <v>0.7976329873348651</v>
+      </c>
+      <c r="D33" s="17">
+        <v>3.9416745893464</v>
+      </c>
+      <c r="E33" s="17">
+        <v>0.25369927865248204</v>
+      </c>
+      <c r="F33" s="17">
+        <v>1.1613742892744807E-2</v>
+      </c>
+      <c r="G33" s="17">
+        <v>0.68234123795134294</v>
+      </c>
+      <c r="H33" s="17">
+        <v>20.236701266513492</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="C34" s="17">
+        <v>0.79353908743075674</v>
+      </c>
+      <c r="D34" s="17">
+        <v>3.8436801956127011</v>
+      </c>
+      <c r="E34" s="17">
+        <v>0.26016732639240692</v>
+      </c>
+      <c r="F34" s="17">
+        <v>1.1599271059708104E-2</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0.68154803678260123</v>
+      </c>
+      <c r="H34" s="17">
+        <v>20.646091256924336</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="C35" s="17">
+        <v>0.78994719629898924</v>
+      </c>
+      <c r="D35" s="17">
+        <v>3.7608483378113542</v>
+      </c>
+      <c r="E35" s="17">
+        <v>0.26589745455727559</v>
+      </c>
+      <c r="F35" s="17">
+        <v>1.1587241111668242E-2</v>
+      </c>
+      <c r="G35" s="17">
+        <v>0.68088867533053643</v>
+      </c>
+      <c r="H35" s="17">
+        <v>21.005280370101076</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E91C93-8228-4E85-B9E3-FB80BE715EB6}">
   <dimension ref="B2:Y42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2721,44 +5791,44 @@
       <c r="I2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="28"/>
-      <c r="N2" s="28" t="s">
+      <c r="L2" s="30"/>
+      <c r="N2" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="O2" s="28"/>
-      <c r="Q2" s="28" t="s">
+      <c r="O2" s="30"/>
+      <c r="Q2" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="R2" s="28"/>
+      <c r="R2" s="30"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3" s="4">
-        <v>1073.1500000000001</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D3" s="5">
         <v>25</v>
       </c>
       <c r="E3" s="4">
-        <v>1350.0381316636626</v>
+        <v>1480.0123118353019</v>
       </c>
       <c r="F3" s="7">
-        <v>3.0305681085599816</v>
+        <v>3.1463579096737231</v>
       </c>
       <c r="G3" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H3" s="4">
-        <v>756.61237274082237</v>
+        <v>852.0638237103999</v>
       </c>
       <c r="I3" s="4">
         <f>C3-273.15</f>
-        <v>800.00000000000011</v>
+        <v>900.00000000000011</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>40</v>
@@ -2784,44 +5854,44 @@
         <v>2</v>
       </c>
       <c r="C4" s="4">
-        <v>1018.1871360117831</v>
+        <v>1114.5692189136419</v>
       </c>
       <c r="D4" s="5">
         <v>17.482517482517483</v>
       </c>
       <c r="E4" s="4">
-        <v>1281.3081492359206</v>
+        <v>1404.7163794364055</v>
       </c>
       <c r="F4" s="7">
-        <v>3.0357375517463359</v>
+        <v>3.1515313348291665</v>
       </c>
       <c r="G4" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="4">
-        <v>686.34112082706883</v>
+        <v>775.22543460140798</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" ref="I4:I42" si="0">C4-273.15</f>
-        <v>745.0371360117831</v>
+        <v>841.41921891364188</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>42</v>
       </c>
       <c r="L4" s="7">
-        <v>17.967369630276828</v>
+        <v>197.01139918140578</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>66</v>
       </c>
       <c r="O4" s="10">
-        <v>6872.9982427742098</v>
+        <v>75295.932398896432</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>98</v>
       </c>
       <c r="R4" s="6">
-        <v>3089.4573260227485</v>
+        <v>15996.693529577993</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
@@ -2829,44 +5899,44 @@
         <v>3</v>
       </c>
       <c r="C5" s="4">
-        <v>1073.1500000000001</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D5" s="5">
         <v>17.482517482517483</v>
       </c>
       <c r="E5" s="4">
-        <v>1351.4823193165744</v>
+        <v>1480.4942892017907</v>
       </c>
       <c r="F5" s="7">
-        <v>3.1028601038812176</v>
+        <v>3.2177913111550378</v>
       </c>
       <c r="G5" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="4">
-        <v>736.50270198870771</v>
+        <v>831.24793242523447</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="0"/>
-        <v>800.00000000000011</v>
+        <v>900.00000000000011</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>43</v>
       </c>
       <c r="L5" s="7">
-        <v>7.0174170080653857</v>
+        <v>75.77790976538509</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>67</v>
       </c>
       <c r="O5" s="10">
-        <v>11978.456764170598</v>
+        <v>131294.66508372221</v>
       </c>
       <c r="Q5" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R5" s="6">
-        <v>2963.220148019665</v>
+        <v>17275.788325127607</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
@@ -2874,44 +5944,44 @@
         <v>4</v>
       </c>
       <c r="C6" s="4">
-        <v>976.21764828798996</v>
+        <v>1069.6344049057263</v>
       </c>
       <c r="D6" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E6" s="4">
-        <v>1231.6977516748684</v>
+        <v>1349.1996241180684</v>
       </c>
       <c r="F6" s="7">
-        <v>3.112273260172465</v>
+        <v>3.227207289175213</v>
       </c>
       <c r="G6" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H6" s="4">
-        <v>613.91160179876624</v>
+        <v>697.14589349479706</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="0"/>
-        <v>703.06764828798998</v>
+        <v>796.48440490572636</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>47</v>
       </c>
       <c r="L6" s="7">
-        <v>24.984786638342218</v>
+        <v>272.78930894679087</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="O6" s="10">
-        <v>717.79640670783738</v>
+        <v>7647.3866633769367</v>
       </c>
       <c r="Q6" s="13" t="s">
         <v>100</v>
       </c>
       <c r="R6" s="6">
-        <v>48628.817203007362</v>
+        <v>476246.11519307818</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -2919,44 +5989,44 @@
         <v>5</v>
       </c>
       <c r="C7" s="4">
-        <v>580.60739984606084</v>
+        <v>592.37305460286814</v>
       </c>
       <c r="D7" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E7" s="4">
-        <v>758.77316593152807</v>
+        <v>772.2645689933064</v>
       </c>
       <c r="F7" s="7">
-        <v>2.493493145865219</v>
+        <v>2.5164974849797748</v>
       </c>
       <c r="G7" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H7" s="4">
-        <v>325.47630713613137</v>
+        <v>332.10896649090478</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="0"/>
-        <v>307.45739984606087</v>
+        <v>319.22305460286816</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>44</v>
       </c>
       <c r="L7" s="7">
-        <v>48.505085709943238</v>
+        <v>591.7282511386129</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>69</v>
       </c>
       <c r="O7" s="10">
-        <v>-3864.0801901504483</v>
+        <v>-38822.704532947573</v>
       </c>
       <c r="Q7" s="13" t="s">
         <v>105</v>
       </c>
       <c r="R7" s="6">
-        <v>14404.513844749421</v>
+        <v>92272.151831478855</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
@@ -2964,44 +6034,44 @@
         <v>6</v>
       </c>
       <c r="C8" s="4">
-        <v>435.4382571755965</v>
+        <v>440.06898750789043</v>
       </c>
       <c r="D8" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E8" s="4">
-        <v>591.20237940579909</v>
+        <v>596.73677012773305</v>
       </c>
       <c r="F8" s="7">
-        <v>2.1610567826542426</v>
+        <v>2.1736996704556586</v>
       </c>
       <c r="G8" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H8" s="4">
-        <v>257.02142230175508</v>
+        <v>258.78633602569676</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="0"/>
-        <v>162.28825717559653</v>
+        <v>166.91898750789045</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>45</v>
       </c>
       <c r="L8" s="7">
-        <v>16.757078652572897</v>
+        <v>175.52779886557337</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>70</v>
       </c>
       <c r="O8" s="10">
-        <v>-1887.2729900081154</v>
+        <v>-17748.922071558391</v>
       </c>
       <c r="Q8" s="13" t="s">
         <v>104</v>
       </c>
       <c r="R8" s="6">
-        <v>125.94776703314032</v>
+        <v>33.890151114468985</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
@@ -3009,44 +6079,44 @@
         <v>29</v>
       </c>
       <c r="C9" s="4">
-        <v>435.4382571755965</v>
+        <v>440.06898750789043</v>
       </c>
       <c r="D9" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E9" s="4">
-        <v>591.20237940579909</v>
+        <v>596.73677012773305</v>
       </c>
       <c r="F9" s="7">
-        <v>2.1610567826542426</v>
+        <v>2.1736996704556586</v>
       </c>
       <c r="G9" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H9" s="4">
-        <v>257.02142230175508</v>
+        <v>258.78633602569676</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" si="0"/>
-        <v>162.28825717559653</v>
+        <v>166.91898750789045</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>48</v>
       </c>
       <c r="L9" s="7">
-        <v>1.1033708748874791</v>
+        <v>11.61019553224269</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>71</v>
       </c>
       <c r="O9" s="10">
-        <v>-0.58783407799472909</v>
+        <v>-6.1854710336906438</v>
       </c>
       <c r="Q9" s="13" t="s">
         <v>101</v>
       </c>
       <c r="R9" s="6">
-        <v>54938.398428688655</v>
+        <v>8302555.2567487583</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
@@ -3054,44 +6124,44 @@
         <v>30</v>
       </c>
       <c r="C10" s="4">
-        <v>423.35913575479753</v>
+        <v>426.20393967688454</v>
       </c>
       <c r="D10" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E10" s="4">
-        <v>0.57660060448894723</v>
+        <v>0.58006351274370938</v>
       </c>
       <c r="F10" s="7">
-        <v>2.1270479527453361E-3</v>
+        <v>2.1352002142002785E-3</v>
       </c>
       <c r="G10" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H10" s="4">
-        <v>0.25257320939780875</v>
+        <v>0.25360552089977978</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="0"/>
-        <v>150.20913575479756</v>
+        <v>153.05393967688457</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="7">
-        <v>6.8670753276560994</v>
+        <v>72.258647661746068</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>72</v>
       </c>
       <c r="O10" s="10">
-        <v>13100.101826786246</v>
+        <v>150018.97087811268</v>
       </c>
       <c r="Q10" s="13" t="s">
         <v>102</v>
       </c>
       <c r="R10" s="6">
-        <v>582641.93083540094</v>
+        <v>6383031.9588786885</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
@@ -3111,7 +6181,7 @@
         <v>1.8961819516546078E-3</v>
       </c>
       <c r="G11" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H11" s="4">
         <v>0.23185738014859708</v>
@@ -3124,19 +6194,19 @@
         <v>50</v>
       </c>
       <c r="L11" s="7">
-        <v>1.2546499075118689</v>
+        <v>14.52880688025372</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="O11" s="10">
-        <v>717.20857262984271</v>
+        <v>7641.2011923432465</v>
       </c>
       <c r="Q11" s="13" t="s">
         <v>103</v>
       </c>
       <c r="R11" s="6">
-        <v>1015444.9238863285</v>
+        <v>11130190.125276349</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
@@ -3144,44 +6214,44 @@
         <v>32</v>
       </c>
       <c r="C12" s="4">
-        <v>346.62379557580101</v>
+        <v>346.16670523637293</v>
       </c>
       <c r="D12" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E12" s="4">
-        <v>0.46883049635692192</v>
+        <v>0.46798922255412118</v>
       </c>
       <c r="F12" s="7">
-        <v>1.8443861945514714E-3</v>
+        <v>1.8419575395601402E-3</v>
       </c>
       <c r="G12" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H12" s="4">
-        <v>0.22907870447128417</v>
+        <v>0.22896153415414877</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" si="0"/>
-        <v>73.473795575801034</v>
+        <v>73.016705236372957</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L12" s="7">
-        <v>9.2250961100554463</v>
+        <v>98.397650074242492</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>74</v>
       </c>
       <c r="O12" s="12">
-        <v>13817.310399416088</v>
+        <v>157660.17207045591</v>
       </c>
       <c r="Q12" s="13" t="s">
         <v>106</v>
       </c>
       <c r="R12" s="6">
-        <v>60849.467667280827</v>
+        <v>648288.85065978777</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
@@ -3189,38 +6259,38 @@
         <v>33</v>
       </c>
       <c r="C13" s="4">
-        <v>346.39737970663185</v>
+        <v>346.16482465658697</v>
       </c>
       <c r="D13" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E13" s="4">
-        <v>468.41449334690572</v>
+        <v>467.9857494877009</v>
       </c>
       <c r="F13" s="7">
-        <v>1.8431856450668949</v>
+        <v>1.8419475065836266</v>
       </c>
       <c r="G13" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H13" s="4">
-        <v>229.02064529009442</v>
+        <v>228.96105241967604</v>
       </c>
       <c r="I13" s="4">
         <f t="shared" si="0"/>
-        <v>73.247379706631875</v>
+        <v>73.014824656586995</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>52</v>
       </c>
       <c r="L13" s="7">
-        <v>7.2309456578341926</v>
+        <v>76.087465131828566</v>
       </c>
       <c r="Q13" s="13" t="s">
         <v>107</v>
       </c>
       <c r="R13" s="6">
-        <v>-146905.37348517781</v>
+        <v>-1475969.3454745074</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
@@ -3228,42 +6298,42 @@
         <v>34</v>
       </c>
       <c r="C14" s="4">
-        <v>435.4382571755965</v>
+        <v>440.06898750789043</v>
       </c>
       <c r="D14" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E14" s="4">
-        <v>591.20237940579909</v>
+        <v>596.73677012773305</v>
       </c>
       <c r="F14" s="7">
-        <v>2.1610567826542426</v>
+        <v>2.1736996704556586</v>
       </c>
       <c r="G14" s="4">
-        <v>20.053649165005705</v>
+        <v>187.74797280166001</v>
       </c>
       <c r="H14" s="4">
-        <v>257.02142230175508</v>
+        <v>258.78633602569676</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="0"/>
-        <v>162.28825717559653</v>
+        <v>166.91898750789045</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>54</v>
       </c>
       <c r="L14" s="7">
-        <v>1.2769418795914116</v>
-      </c>
-      <c r="N14" s="29" t="s">
+        <v>14.668983750070673</v>
+      </c>
+      <c r="N14" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="O14" s="29"/>
+      <c r="O14" s="31"/>
       <c r="Q14" s="13" t="s">
         <v>108</v>
       </c>
       <c r="R14" s="6">
-        <v>-71750.721988726538</v>
+        <v>-674782.06910092139</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
@@ -3283,7 +6353,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G15" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H15" s="4">
         <v>224.33075530171814</v>
@@ -3296,19 +6366,19 @@
         <v>53</v>
       </c>
       <c r="L15" s="7">
-        <v>8.5078875374256029</v>
+        <v>90.756448881899232</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="O15" s="10">
-        <v>7.7745376749850683</v>
+        <v>7.7656338200941244</v>
       </c>
       <c r="Q15" s="13" t="s">
         <v>109</v>
       </c>
       <c r="R15" s="6">
-        <v>-22.348393544019206</v>
+        <v>-235.16047485305765</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
@@ -3316,44 +6386,44 @@
         <v>8</v>
       </c>
       <c r="C16" s="4">
-        <v>407.92598052767181</v>
+        <v>407.64113086711654</v>
       </c>
       <c r="D16" s="5">
         <v>25</v>
       </c>
       <c r="E16" s="4">
-        <v>475.70953285771714</v>
+        <v>475.17249490805983</v>
       </c>
       <c r="F16" s="7">
-        <v>1.7343043486568708</v>
+        <v>1.7329873803681137</v>
       </c>
       <c r="G16" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H16" s="4">
-        <v>268.76481394998945</v>
+        <v>268.62043009562507</v>
       </c>
       <c r="I16" s="4">
         <f t="shared" si="0"/>
-        <v>134.77598052767183</v>
+        <v>134.49113086711657</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>46</v>
       </c>
       <c r="L16" s="7">
-        <v>3.3257922587167379E-2</v>
+        <v>2.8210052404935883E-3</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>81</v>
       </c>
       <c r="O16" s="10">
-        <v>52.432314177470438</v>
+        <v>54.994446614245696</v>
       </c>
       <c r="Q16" s="13" t="s">
         <v>110</v>
       </c>
       <c r="R16" s="6">
-        <v>149375.6241707881</v>
+        <v>1591444.5174733943</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
@@ -3361,44 +6431,44 @@
         <v>9</v>
       </c>
       <c r="C17" s="4">
-        <v>547.69370647629023</v>
+        <v>552.25174153326532</v>
       </c>
       <c r="D17" s="5">
         <v>25</v>
       </c>
       <c r="E17" s="4">
-        <v>685.31357954095802</v>
+        <v>691.27266208278832</v>
       </c>
       <c r="F17" s="7">
-        <v>2.180095650521598</v>
+        <v>2.1909309739824532</v>
       </c>
       <c r="G17" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H17" s="4">
-        <v>345.4561839822619</v>
+        <v>348.18471483423826</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" si="0"/>
-        <v>274.54370647629025</v>
+        <v>279.10174153326534</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>55</v>
       </c>
       <c r="L17" s="16">
-        <v>-3.2808684015299132</v>
+        <v>-32.985255990966728</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>82</v>
       </c>
       <c r="O17" s="10">
-        <v>36.901993581878948</v>
+        <v>16.477593217708954</v>
       </c>
       <c r="Q17" s="13" t="s">
         <v>111</v>
       </c>
       <c r="R17" s="6">
-        <v>121456.51249638916</v>
+        <v>1331025.8266823676</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
@@ -3406,38 +6476,38 @@
         <v>10</v>
       </c>
       <c r="C18" s="4">
-        <v>547.69370647629023</v>
+        <v>552.25174153326532</v>
       </c>
       <c r="D18" s="5">
         <v>25</v>
       </c>
       <c r="E18" s="4">
-        <v>685.31357954095802</v>
+        <v>691.27266208278832</v>
       </c>
       <c r="F18" s="7">
-        <v>2.180095650521598</v>
+        <v>2.1909309739824532</v>
       </c>
       <c r="G18" s="4">
-        <v>20.053649165005705</v>
+        <v>187.74797280166001</v>
       </c>
       <c r="H18" s="4">
-        <v>345.4561839822619</v>
+        <v>348.18471483423826</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" si="0"/>
-        <v>274.54370647629025</v>
+        <v>279.10174153326534</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>83</v>
       </c>
       <c r="O18" s="10">
-        <v>53.497400064021491</v>
+        <v>55.457122957656523</v>
       </c>
       <c r="Q18" s="13" t="s">
         <v>112</v>
       </c>
       <c r="R18" s="6">
-        <v>21403100.470866345</v>
+        <v>244216595.38173544</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
@@ -3445,42 +6515,42 @@
         <v>11</v>
       </c>
       <c r="C19" s="4">
-        <v>547.69370647629023</v>
+        <v>552.25174153326532</v>
       </c>
       <c r="D19" s="5">
         <v>25</v>
       </c>
       <c r="E19" s="4">
-        <v>685.31357954095802</v>
+        <v>691.27266208278832</v>
       </c>
       <c r="F19" s="7">
-        <v>2.180095650521598</v>
+        <v>2.1909309739824532</v>
       </c>
       <c r="G19" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H19" s="4">
-        <v>345.4561839822619</v>
+        <v>348.18471483423826</v>
       </c>
       <c r="I19" s="4">
         <f t="shared" si="0"/>
-        <v>274.54370647629025</v>
-      </c>
-      <c r="K19" s="29" t="s">
+        <v>279.10174153326534</v>
+      </c>
+      <c r="K19" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="L19" s="29"/>
+      <c r="L19" s="31"/>
       <c r="N19" s="9" t="s">
         <v>84</v>
       </c>
       <c r="O19" s="10">
-        <v>55.302895315550685</v>
+        <v>57.795583221044943</v>
       </c>
       <c r="Q19" s="13" t="s">
         <v>123</v>
       </c>
       <c r="R19" s="6">
-        <v>24957461.093185224</v>
+        <v>291669711.90011054</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
@@ -3488,47 +6558,47 @@
         <v>12</v>
       </c>
       <c r="C20" s="4">
-        <v>932.93660164805499</v>
+        <v>1021.1165618252154</v>
       </c>
       <c r="D20" s="5">
         <v>25</v>
       </c>
       <c r="E20" s="4">
-        <v>1170.3644353608943</v>
+        <v>1283.0009126538962</v>
       </c>
       <c r="F20" s="7">
-        <v>2.8511829889834948</v>
+        <v>2.9665368279795343</v>
       </c>
       <c r="G20" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H20" s="4">
-        <v>630.42234983978369</v>
+        <v>708.66608003611657</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" si="0"/>
-        <v>659.78660164805501</v>
+        <v>747.96656182521542</v>
       </c>
       <c r="K20" s="13" t="s">
         <v>59</v>
       </c>
       <c r="L20" s="4">
-        <v>1128.9074473722574</v>
+        <v>11055.95030163149</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>85</v>
       </c>
       <c r="O20" s="10">
-        <v>3.4935322440475987</v>
-      </c>
-      <c r="Q20" s="28" t="s">
+        <v>3.6384289766431053</v>
+      </c>
+      <c r="Q20" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28" t="s">
+      <c r="R20" s="30"/>
+      <c r="S20" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="T20" s="28"/>
+      <c r="T20" s="30"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
@@ -3547,7 +6617,7 @@
         <v>-0.37994748587359245</v>
       </c>
       <c r="G21" s="4">
-        <v>17.89815043892197</v>
+        <v>188.33289059090924</v>
       </c>
       <c r="H21" s="4">
         <v>0.52460446529691762</v>
@@ -3560,13 +6630,13 @@
         <v>60</v>
       </c>
       <c r="L21" s="4">
-        <v>334.39766563166074</v>
+        <v>2142.0779977592824</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>86</v>
       </c>
       <c r="O21" s="10">
-        <v>22.472364524327524</v>
+        <v>20.833575153875099</v>
       </c>
       <c r="Q21" s="22" t="s">
         <v>118</v>
@@ -3598,7 +6668,7 @@
         <v>-0.37993175416231956</v>
       </c>
       <c r="G22" s="4">
-        <v>17.89815043892197</v>
+        <v>188.33289059090924</v>
       </c>
       <c r="H22" s="4">
         <v>0.55275734181882941</v>
@@ -3611,19 +6681,19 @@
         <v>61</v>
       </c>
       <c r="L22" s="4">
-        <v>71.721081948712694</v>
+        <v>371.35977178888459</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>87</v>
       </c>
       <c r="O22" s="6">
-        <v>36.167181648495081</v>
+        <v>16.104154074250307</v>
       </c>
       <c r="Q22" s="23" t="s">
         <v>113</v>
       </c>
       <c r="R22" s="24">
-        <v>24046.390970622553</v>
+        <v>259477.5692442265</v>
       </c>
       <c r="S22" s="23" t="s">
         <v>129</v>
@@ -3649,7 +6719,7 @@
         <v>-0.19317568283781225</v>
       </c>
       <c r="G23" s="4">
-        <v>17.89815043892197</v>
+        <v>188.33289059090924</v>
       </c>
       <c r="H23" s="4">
         <v>6.518635522826691</v>
@@ -3662,19 +6732,19 @@
         <v>62</v>
       </c>
       <c r="L23" s="4">
-        <v>68.790513232882915</v>
+        <v>401.05368012646488</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>88</v>
       </c>
       <c r="O23" s="6">
-        <v>22.917512377362197</v>
+        <v>21.004494873055776</v>
       </c>
       <c r="Q23" s="23" t="s">
         <v>114</v>
       </c>
       <c r="R23" s="24">
-        <v>42594227.213088371</v>
+        <v>492608866.3924107</v>
       </c>
       <c r="S23" s="23" t="s">
         <v>128</v>
@@ -3700,7 +6770,7 @@
         <v>0.91173151933586583</v>
       </c>
       <c r="G24" s="4">
-        <v>17.89815043892197</v>
+        <v>188.33289059090924</v>
       </c>
       <c r="H24" s="4">
         <v>60.765690527522125</v>
@@ -3713,25 +6783,25 @@
         <v>63</v>
       </c>
       <c r="L24" s="4">
-        <v>2.9238501029143915</v>
+        <v>0.7867525098539554</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>89</v>
       </c>
       <c r="O24" s="15">
-        <v>22.919558145685983</v>
+        <v>21.005280370101076</v>
       </c>
       <c r="Q24" s="23" t="s">
         <v>115</v>
       </c>
       <c r="R24" s="24">
-        <v>2023167.7075799552</v>
+        <v>23402221.401515387</v>
       </c>
       <c r="S24" s="23" t="s">
         <v>127</v>
       </c>
       <c r="T24" s="27">
-        <v>24957461.093185224</v>
+        <v>291669711.90011054</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3743,38 +6813,38 @@
         <v>15</v>
       </c>
       <c r="C25" s="4">
-        <v>396.4382571755965</v>
+        <v>401.06898750789043</v>
       </c>
       <c r="D25" s="5">
         <v>31.569242975234697</v>
       </c>
       <c r="E25" s="4">
-        <v>383.09995906623425</v>
+        <v>390.14483095234505</v>
       </c>
       <c r="F25" s="7">
-        <v>1.100267344850671</v>
+        <v>1.1179345894579515</v>
       </c>
       <c r="G25" s="4">
-        <v>17.89815043892197</v>
+        <v>188.33289059090924</v>
       </c>
       <c r="H25" s="4">
-        <v>74.65315094719746</v>
+        <v>76.430533853647646</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" si="0"/>
-        <v>123.28825717559653</v>
+        <v>127.91898750789045</v>
       </c>
       <c r="K25" s="13" t="s">
         <v>64</v>
       </c>
       <c r="L25" s="4">
-        <v>1275.3830074447171</v>
+        <v>192742.0200749549</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="26">
-        <v>48195801.93395783</v>
+        <v>563723681.88154542</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3786,31 +6856,31 @@
         <v>16</v>
       </c>
       <c r="C26" s="4">
-        <v>368.14329244204333</v>
+        <v>372.78365166096796</v>
       </c>
       <c r="D26" s="5">
         <v>7.8923107438086744</v>
       </c>
       <c r="E26" s="4">
-        <v>342.99545725431005</v>
+        <v>349.53914259179015</v>
       </c>
       <c r="F26" s="7">
-        <v>1.1196252392794583</v>
+        <v>1.1372887578278126</v>
       </c>
       <c r="G26" s="4">
-        <v>17.89815043892197</v>
+        <v>188.33289059090924</v>
       </c>
       <c r="H26" s="4">
-        <v>28.777092911330342</v>
+        <v>30.054400193618669</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" si="0"/>
-        <v>94.993292442043355</v>
-      </c>
-      <c r="N26" s="29" t="s">
+        <v>99.633651660967985</v>
+      </c>
+      <c r="N26" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="O26" s="29"/>
+      <c r="O26" s="31"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
@@ -3837,7 +6907,7 @@
         <v>0.91018564327057938</v>
       </c>
       <c r="G27" s="4">
-        <v>17.89815043892197</v>
+        <v>188.33289059090924</v>
       </c>
       <c r="H27" s="4">
         <v>19.876601402460075</v>
@@ -3850,7 +6920,7 @@
         <v>77</v>
       </c>
       <c r="O27" s="6">
-        <v>0.71269346475761464</v>
+        <v>0.62993827838740779</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -3879,7 +6949,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G28" s="4">
-        <v>345.9386726638856</v>
+        <v>3640.1320020358544</v>
       </c>
       <c r="H28" s="4">
         <v>2.5073905791015251E-5</v>
@@ -3921,7 +6991,7 @@
         <v>0.43672528196163279</v>
       </c>
       <c r="G29" s="4">
-        <v>345.9386726638856</v>
+        <v>3640.1320020358544</v>
       </c>
       <c r="H29" s="4">
         <v>0.17334706272843686</v>
@@ -3951,26 +7021,26 @@
         <v>39</v>
       </c>
       <c r="C30" s="4">
-        <v>304.03312670606874</v>
+        <v>304.11412786051727</v>
       </c>
       <c r="D30" s="5">
         <v>101.325</v>
       </c>
       <c r="E30" s="4">
-        <v>129.51374904828285</v>
+        <v>129.85230577480698</v>
       </c>
       <c r="F30" s="7">
-        <v>0.44888385544072534</v>
+        <v>0.44999725923128103</v>
       </c>
       <c r="G30" s="4">
-        <v>345.9386726638856</v>
+        <v>3640.1320020358544</v>
       </c>
       <c r="H30" s="4">
-        <v>0.23950610643450637</v>
+        <v>0.24610149280446422</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" si="0"/>
-        <v>30.883126706068765</v>
+        <v>30.964127860517294</v>
       </c>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
@@ -3987,26 +7057,26 @@
         <v>29</v>
       </c>
       <c r="C31" s="4">
-        <v>435.4382571755965</v>
+        <v>440.06898750789043</v>
       </c>
       <c r="D31" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E31" s="4">
-        <v>591.20237940555796</v>
+        <v>596.73677012756878</v>
       </c>
       <c r="F31" s="7">
-        <v>2.1610567826542426</v>
+        <v>2.1736996704556586</v>
       </c>
       <c r="G31" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H31" s="4">
-        <v>257.03525167707909</v>
+        <v>258.80016540109756</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" si="0"/>
-        <v>162.28825717559653</v>
+        <v>166.91898750789045</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -4023,26 +7093,26 @@
         <v>30</v>
       </c>
       <c r="C32" s="4">
-        <v>423.35913575479753</v>
+        <v>426.20393967688454</v>
       </c>
       <c r="D32" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E32" s="4">
-        <v>576.60060448894728</v>
+        <v>580.06351274370934</v>
       </c>
       <c r="F32" s="7">
-        <v>2.1270479527453361</v>
+        <v>2.1352002142002786</v>
       </c>
       <c r="G32" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H32" s="4">
-        <v>252.57320939780874</v>
+        <v>253.6055208997798</v>
       </c>
       <c r="I32" s="4">
         <f t="shared" si="0"/>
-        <v>150.20913575479756</v>
+        <v>153.05393967688457</v>
       </c>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
@@ -4071,7 +7141,7 @@
         <v>1.8961819516546079</v>
       </c>
       <c r="G33" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H33" s="4">
         <v>231.85738014859709</v>
@@ -4095,26 +7165,26 @@
         <v>32</v>
       </c>
       <c r="C34" s="4">
-        <v>346.62379557580101</v>
+        <v>346.16670523637293</v>
       </c>
       <c r="D34" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E34" s="4">
-        <v>468.83049635692191</v>
+        <v>467.98922255412117</v>
       </c>
       <c r="F34" s="7">
-        <v>1.8443861945514715</v>
+        <v>1.8419575395601402</v>
       </c>
       <c r="G34" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H34" s="4">
-        <v>229.07870447128417</v>
+        <v>228.96153415414878</v>
       </c>
       <c r="I34" s="4">
         <f t="shared" si="0"/>
-        <v>73.473795575801034</v>
+        <v>73.016705236372957</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.3">
@@ -4134,7 +7204,7 @@
         <v>3.8804887263997387</v>
       </c>
       <c r="G35" s="4">
-        <v>1.1599999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="H35" s="4">
         <v>2.1111792130950945E-2</v>
@@ -4155,16 +7225,16 @@
         <v>0.101325</v>
       </c>
       <c r="E36" s="4">
-        <v>453.10667720162991</v>
+        <v>452.6461066865939</v>
       </c>
       <c r="F36" s="7">
-        <v>3.9723306469545014</v>
+        <v>3.9709195645679616</v>
       </c>
       <c r="G36" s="4">
-        <v>1.1599999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="H36" s="4">
-        <v>1.3090660987003904</v>
+        <v>1.2692097972112533</v>
       </c>
       <c r="I36" s="4">
         <f t="shared" si="0"/>
@@ -4176,26 +7246,26 @@
         <v>32</v>
       </c>
       <c r="C37" s="4">
-        <v>346.62379557580101</v>
+        <v>346.16670523637293</v>
       </c>
       <c r="D37" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E37" s="4">
-        <v>468.83049635692191</v>
+        <v>467.98922255412117</v>
       </c>
       <c r="F37" s="7">
-        <v>1.8443861945514715</v>
+        <v>1.8419575395601402</v>
       </c>
       <c r="G37" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H37" s="4">
-        <v>229.07870447128417</v>
+        <v>228.96153415414878</v>
       </c>
       <c r="I37" s="4">
         <f t="shared" si="0"/>
-        <v>73.473795575801034</v>
+        <v>73.016705236372957</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.3">
@@ -4203,26 +7273,26 @@
         <v>33</v>
       </c>
       <c r="C38" s="4">
-        <v>346.39737970663185</v>
+        <v>346.16482465658697</v>
       </c>
       <c r="D38" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E38" s="4">
-        <v>468.41449334690572</v>
+        <v>467.9857494877009</v>
       </c>
       <c r="F38" s="7">
-        <v>1.8431856450668949</v>
+        <v>1.8419475065836266</v>
       </c>
       <c r="G38" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H38" s="4">
-        <v>229.02064529009442</v>
+        <v>228.96105241967604</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" si="0"/>
-        <v>73.247379706631875</v>
+        <v>73.014824656586995</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.3">
@@ -4230,26 +7300,26 @@
         <v>33</v>
       </c>
       <c r="C39" s="4">
-        <v>346.39737970663185</v>
+        <v>346.16482465658697</v>
       </c>
       <c r="D39" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E39" s="4">
-        <v>468.41449334022548</v>
+        <v>467.98574948113162</v>
       </c>
       <c r="F39" s="7">
-        <v>1.8431856450668949</v>
+        <v>1.8419475065836266</v>
       </c>
       <c r="G39" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H39" s="4">
-        <v>229.02064528341415</v>
+        <v>228.96105241310678</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" si="0"/>
-        <v>73.247379706631875</v>
+        <v>73.014824656586995</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.3">
@@ -4269,7 +7339,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G40" s="4">
-        <v>79.946350834994291</v>
+        <v>812.25202719833999</v>
       </c>
       <c r="H40" s="4">
         <v>224.34458467728319</v>
@@ -4296,7 +7366,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G41" s="4">
-        <v>1.9801295635402501E-2</v>
+        <v>9.3915650980828866E-2</v>
       </c>
       <c r="H41" s="4">
         <v>2.5073905791015251E-5</v>
@@ -4311,26 +7381,26 @@
         <v>20</v>
       </c>
       <c r="C42" s="4">
-        <v>345.39737970663185</v>
+        <v>345.16482465658697</v>
       </c>
       <c r="D42" s="5">
         <v>101.325</v>
       </c>
       <c r="E42" s="4">
-        <v>302.54072536549046</v>
+        <v>301.56600461702902</v>
       </c>
       <c r="F42" s="7">
-        <v>0.98244738595667158</v>
+        <v>0.97962440845434873</v>
       </c>
       <c r="G42" s="4">
-        <v>1.9801295635402501E-2</v>
+        <v>9.3915650980828866E-2</v>
       </c>
       <c r="H42" s="4">
-        <v>14.184515800312743</v>
+        <v>14.051465794168879</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="0"/>
-        <v>72.247379706631875</v>
+        <v>72.014824656586995</v>
       </c>
     </row>
   </sheetData>
@@ -4350,7 +7420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BBA90F-813A-493D-869A-57A3178EDC43}">
   <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4367,10 +7437,10 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>202</v>
@@ -4379,16 +7449,16 @@
         <v>227</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>240</v>
@@ -4405,34 +7475,34 @@
         <v>203</v>
       </c>
       <c r="B2">
-        <v>5.1731913323680587E-2</v>
+        <v>4.5058259292768729E-2</v>
       </c>
       <c r="C2">
-        <v>3914.1005686252538</v>
+        <v>38392.512702731183</v>
       </c>
       <c r="E2" t="s">
         <v>66</v>
       </c>
       <c r="F2">
-        <v>2503.1935161652605</v>
+        <v>25032.061802977114</v>
       </c>
       <c r="G2">
-        <v>154.12694860114715</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="H2">
-        <v>7.9732819458779174</v>
+        <v>69.500414391355164</v>
       </c>
       <c r="I2">
-        <v>99.682486963754258</v>
-      </c>
-      <c r="K2" s="31">
-        <v>0.34909743323706877</v>
-      </c>
-      <c r="L2" s="31">
-        <v>0.91088630043789787</v>
-      </c>
-      <c r="M2" s="31">
-        <v>0.27584737694031641</v>
+        <v>99.723123151501454</v>
+      </c>
+      <c r="K2" s="29">
+        <v>0.32664347494249629</v>
+      </c>
+      <c r="L2" s="29">
+        <v>1.8517120877445366</v>
+      </c>
+      <c r="M2" s="29">
+        <v>0.24453052654182419</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -4440,25 +7510,25 @@
         <v>204</v>
       </c>
       <c r="B3">
-        <v>5.1731913323680594E-2</v>
+        <v>4.5058259292768736E-2</v>
       </c>
       <c r="C3">
-        <v>3550.5739373103711</v>
+        <v>34930.308642619573</v>
       </c>
       <c r="E3" t="s">
         <v>67</v>
       </c>
       <c r="F3">
-        <v>888.25965020835133</v>
+        <v>8882.6414408299115</v>
       </c>
       <c r="G3">
-        <v>280.65325482354871</v>
+        <v>2807.373846715212</v>
       </c>
       <c r="H3">
-        <v>13.912184589022015</v>
+        <v>121.75423588731627</v>
       </c>
       <c r="I3">
-        <v>98.457922975156208</v>
+        <v>98.647835565443472</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -4466,25 +7536,25 @@
         <v>205</v>
       </c>
       <c r="B4">
-        <v>4.9570722412497346E-2</v>
+        <v>4.3369441526206309E-2</v>
       </c>
       <c r="C4">
-        <v>3650.8970996336493</v>
+        <v>36050.758599096102</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
       </c>
       <c r="F4">
-        <v>27.111169102991425</v>
+        <v>413.1727433514576</v>
       </c>
       <c r="G4">
-        <v>311.73934843303778</v>
+        <v>2848.3263976414578</v>
       </c>
       <c r="H4">
-        <v>85.992481554336806</v>
+        <v>696.502753778243</v>
       </c>
       <c r="I4">
-        <v>23.970198084171948</v>
+        <v>37.233654741424409</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -4492,25 +7562,25 @@
         <v>206</v>
       </c>
       <c r="B5">
-        <v>4.9570722412497353E-2</v>
+        <v>4.336944152620633E-2</v>
       </c>
       <c r="C5">
-        <v>3043.2041598578253</v>
+        <v>30234.828063157467</v>
       </c>
       <c r="E5" t="s">
         <v>70</v>
       </c>
       <c r="F5">
-        <v>6.8005339576619255</v>
+        <v>95.502802558342736</v>
       </c>
       <c r="G5">
-        <v>113.83330527634081</v>
+        <v>964.55767849983272</v>
       </c>
       <c r="H5">
-        <v>31.400618668924892</v>
+        <v>235.86379700352367</v>
       </c>
       <c r="I5">
-        <v>17.801907770000021</v>
+        <v>28.820889819498024</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -4518,25 +7588,25 @@
         <v>207</v>
       </c>
       <c r="B6">
-        <v>4.9570722412497326E-2</v>
+        <v>4.336944152620633E-2</v>
       </c>
       <c r="C6">
-        <v>1613.4095672889889</v>
+        <v>14403.380402556113</v>
       </c>
       <c r="E6" t="s">
         <v>59</v>
       </c>
       <c r="F6">
-        <v>10.532285533619728</v>
+        <v>40.473977963797893</v>
       </c>
       <c r="G6">
-        <v>346.91288051130834</v>
+        <v>4555.56180201401</v>
       </c>
       <c r="H6">
-        <v>17.19672210114593</v>
+        <v>197.57217119146574</v>
       </c>
       <c r="I6">
-        <v>37.98291548095186</v>
+        <v>17.002576226258999</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -4544,25 +7614,25 @@
         <v>208</v>
       </c>
       <c r="B7">
-        <v>4.9570722412497346E-2</v>
+        <v>4.3369441526206309E-2</v>
       </c>
       <c r="C7">
-        <v>1274.0737578985556</v>
+        <v>11223.418868047633</v>
       </c>
       <c r="E7" t="s">
         <v>60</v>
       </c>
       <c r="F7">
-        <v>5.1377091499340155</v>
+        <v>15.369049891704023</v>
       </c>
       <c r="G7">
-        <v>714.29330882120883</v>
+        <v>8696.3788936835081</v>
       </c>
       <c r="H7">
-        <v>35.40803533268037</v>
+        <v>377.15709591934177</v>
       </c>
       <c r="I7">
-        <v>12.67138935415778</v>
+        <v>3.915420681072892</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -4570,25 +7640,25 @@
         <v>209</v>
       </c>
       <c r="B8">
-        <v>5.6564567203107923E-5</v>
+        <v>4.3719571166688964E-5</v>
       </c>
       <c r="C8">
-        <v>1.01445300323212</v>
+        <v>7.9662790632337419</v>
       </c>
       <c r="E8" t="s">
         <v>229</v>
       </c>
       <c r="F8">
-        <v>2.0715042857927268</v>
+        <v>5.4655411715622142</v>
       </c>
       <c r="G8">
-        <v>908.7639387171597</v>
+        <v>9946.2077370741645</v>
       </c>
       <c r="H8">
-        <v>45.048084944636095</v>
+        <v>431.36147486053875</v>
       </c>
       <c r="I8">
-        <v>4.3962698309241492</v>
+        <v>1.2511911971947656</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -4596,25 +7666,25 @@
         <v>210</v>
       </c>
       <c r="B9">
-        <v>5.09160848747457E-2</v>
+        <v>4.544016457579185E-2</v>
       </c>
       <c r="C9">
-        <v>1094.0220068462638</v>
+        <v>9914.4754036340255</v>
       </c>
       <c r="E9" t="s">
         <v>230</v>
       </c>
       <c r="F9">
-        <v>14.87368048383521</v>
+        <v>77.924977639318257</v>
       </c>
       <c r="G9">
-        <v>103.30018156282743</v>
+        <v>1086.7646432466843</v>
       </c>
       <c r="H9">
-        <v>128.39674035958012</v>
+        <v>1134.3969269456281</v>
       </c>
       <c r="I9">
-        <v>10.381543096108523</v>
+        <v>6.4277464050273725</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -4622,25 +7692,25 @@
         <v>211</v>
       </c>
       <c r="B10">
-        <v>5.2085507350043407E-2</v>
+        <v>4.6354911775307393E-2</v>
       </c>
       <c r="C10">
-        <v>1438.4955253866315</v>
+        <v>13109.805988034212</v>
       </c>
       <c r="E10" t="s">
         <v>231</v>
       </c>
       <c r="F10">
-        <v>3.0925794872948675E-2</v>
+        <v>0.2032428542650199</v>
       </c>
       <c r="G10">
-        <v>8.3949658717157039E-2</v>
+        <v>0.88335841987004737</v>
       </c>
       <c r="H10">
-        <v>2.3157293152162538E-2</v>
+        <v>0.21600809953597649</v>
       </c>
       <c r="I10">
-        <v>57.182006431640112</v>
+        <v>48.47761285272879</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -4648,25 +7718,25 @@
         <v>212</v>
       </c>
       <c r="B11">
-        <v>0.11301051802733234</v>
+        <v>0.10008769588699151</v>
       </c>
       <c r="C11">
-        <v>782.89811933408907</v>
+        <v>6542.8302026461652</v>
       </c>
       <c r="E11" t="s">
         <v>232</v>
       </c>
       <c r="F11">
-        <v>0.64803276948092892</v>
+        <v>1.6038117139195283</v>
       </c>
       <c r="G11">
-        <v>422.82153795985045</v>
+        <v>4665.6811406944789</v>
       </c>
       <c r="H11">
-        <v>525.54512883262078</v>
+        <v>4870.1753236101495</v>
       </c>
       <c r="I11">
-        <v>0.12315492043033435</v>
+        <v>3.2920452043703807E-2</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -4674,25 +7744,25 @@
         <v>213</v>
       </c>
       <c r="B12">
-        <v>6.4303195245009187E-2</v>
+        <v>5.6443133065265334E-2</v>
       </c>
       <c r="C12">
-        <v>2221.3936447207207</v>
+        <v>19652.636190680376</v>
       </c>
       <c r="E12" t="s">
         <v>63</v>
       </c>
       <c r="F12">
-        <v>0.12782276758325392</v>
+        <v>6.5098067393561485E-2</v>
       </c>
       <c r="G12">
-        <v>3.1475926729674328</v>
+        <v>0.2664800015417999</v>
       </c>
       <c r="H12">
-        <v>0.15602844265927923</v>
+        <v>1.1557088844770453E-2</v>
       </c>
       <c r="I12">
-        <v>45.031609156796392</v>
+        <v>84.92327272957634</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -4700,25 +7770,25 @@
         <v>214</v>
       </c>
       <c r="B13">
-        <v>5.8083608929057957E-2</v>
+        <v>5.0128768442585875E-2</v>
       </c>
       <c r="C13">
-        <v>3661.7205228231765</v>
+        <v>35524.557829245517</v>
       </c>
       <c r="E13" t="s">
         <v>233</v>
       </c>
       <c r="F13">
-        <v>2.9067425972745697</v>
+        <v>38.334090696255963</v>
       </c>
       <c r="G13">
-        <v>373.5531104491323</v>
+        <v>3748.4156267159824</v>
       </c>
       <c r="H13">
-        <v>2.1129870019932807E-2</v>
+        <v>0.1638791237545851</v>
       </c>
       <c r="I13">
-        <v>99.278320000069613</v>
+        <v>99.574317491231952</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -4726,25 +7796,25 @@
         <v>215</v>
       </c>
       <c r="B14">
-        <v>4.9570722412497333E-2</v>
+        <v>4.3369441526206309E-2</v>
       </c>
       <c r="C14">
-        <v>255.49828151238043</v>
-      </c>
-      <c r="E14" s="30" t="s">
+        <v>2107.1741403798442</v>
+      </c>
+      <c r="E14" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="F14" s="30">
-        <v>38.53098439483005</v>
-      </c>
-      <c r="G14" s="30">
-        <v>456.8011680060402</v>
-      </c>
-      <c r="H14" s="30">
-        <v>126.00740397773897</v>
-      </c>
-      <c r="I14" s="30">
-        <v>23.417625987428071</v>
+      <c r="F14" s="28">
+        <v>410.51238807750354</v>
+      </c>
+      <c r="G14" s="28">
+        <v>6406.1012876481363</v>
+      </c>
+      <c r="H14" s="28">
+        <v>1566.4873209488567</v>
+      </c>
+      <c r="I14" s="28">
+        <v>20.76441317635166</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -4752,10 +7822,10 @@
         <v>216</v>
       </c>
       <c r="B15">
-        <v>4.9570722412497367E-2</v>
+        <v>4.3369441526206309E-2</v>
       </c>
       <c r="C15">
-        <v>1018.5754763861755</v>
+        <v>9116.2447276677867</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -4763,10 +7833,10 @@
         <v>217</v>
       </c>
       <c r="B16">
-        <v>4.9570722412497367E-2</v>
+        <v>4.3369441526206289E-2</v>
       </c>
       <c r="C16">
-        <v>0.90783853130662884</v>
+        <v>8.0656089136183216</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -4774,10 +7844,10 @@
         <v>218</v>
       </c>
       <c r="B17">
-        <v>5.6564567203115594E-5</v>
+        <v>4.3719571166701418E-5</v>
       </c>
       <c r="C17">
-        <v>1.0356612988898828</v>
+        <v>8.1307069810118833</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -4788,7 +7858,7 @@
         <v>2E-3</v>
       </c>
       <c r="C18">
-        <v>9.9299164260424743E-10</v>
+        <v>4.7096643699903442E-9</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -4796,10 +7866,10 @@
         <v>219</v>
       </c>
       <c r="B19">
-        <v>10.424510362939218</v>
+        <v>29.173223213902457</v>
       </c>
       <c r="C19">
-        <v>2.9279508939251864</v>
+        <v>38.498518618741471</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -4807,10 +7877,10 @@
         <v>220</v>
       </c>
       <c r="B20">
-        <v>1.2429478672454113</v>
+        <v>1.0438294381354214</v>
       </c>
       <c r="C20">
-        <v>1660.7689273524077</v>
+        <v>15025.281105479558</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -4818,10 +7888,10 @@
         <v>221</v>
       </c>
       <c r="B21">
-        <v>1.2429478672454113</v>
+        <v>1.0438294381354214</v>
       </c>
       <c r="C21">
-        <v>640.18867415890122</v>
+        <v>5908.3168544968667</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -4829,10 +7899,10 @@
         <v>222</v>
       </c>
       <c r="B22">
-        <v>68.250720909430768</v>
+        <v>59.816844075604649</v>
       </c>
       <c r="C22">
-        <v>640.83670692838211</v>
+        <v>5909.9206662107863</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -4840,10 +7910,10 @@
         <v>223</v>
       </c>
       <c r="B23">
-        <v>64.794110996165372</v>
+        <v>56.786751584263364</v>
       </c>
       <c r="C23">
-        <v>641.029785211746</v>
+        <v>5911.6364455538287</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -4851,10 +7921,10 @@
         <v>224</v>
       </c>
       <c r="B24">
-        <v>0.91088630043789787</v>
+        <v>1.8517120877445366</v>
       </c>
       <c r="C24">
-        <v>236.37108787388058</v>
+        <v>2279.0193390532122</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -4869,14 +7939,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="B26" s="30">
-        <v>0.27584737694031641</v>
-      </c>
-      <c r="C26" s="30">
-        <v>197.84010347905053</v>
+      <c r="B26" s="28">
+        <v>0.24453052654182419</v>
+      </c>
+      <c r="C26" s="28">
+        <v>1868.5069509757088</v>
       </c>
     </row>
   </sheetData>
@@ -4884,7 +7954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E0693F-D387-4367-8A44-8725A6CA7BA7}">
   <dimension ref="A1:AF33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tes2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E4C203-A930-4E70-B4A7-E9A2E9CD2DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2577816-9F7D-473F-8819-FCC5616B393D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="3" r:id="rId1"/>
@@ -1392,34 +1392,34 @@
         <v>500</v>
       </c>
       <c r="C3" s="19">
-        <v>79.817560813786429</v>
+        <v>7.9817560813786423E-2</v>
       </c>
       <c r="D3" s="17">
-        <v>5.747836556425975</v>
+        <v>5.7478365564259748E-3</v>
       </c>
       <c r="E3" s="19">
-        <v>44.197489238670407</v>
+        <v>44.1974892386704</v>
       </c>
       <c r="F3" s="19">
-        <v>21.672347119588974</v>
+        <v>22.333328223050525</v>
       </c>
       <c r="G3" s="19">
-        <v>41.608757546050079</v>
+        <v>42.909657240666718</v>
       </c>
       <c r="H3" s="19">
-        <v>18.611139031996345</v>
+        <v>59.52618690796568</v>
       </c>
       <c r="I3" s="19">
-        <v>18.196209309538482</v>
+        <v>58.057505047628197</v>
       </c>
       <c r="J3" s="19">
-        <v>73.740628070018715</v>
+        <v>26</v>
       </c>
       <c r="K3" s="19">
-        <v>32.15627223010955</v>
+        <v>0.10257759171348141</v>
       </c>
       <c r="L3" s="17">
-        <v>287.37040299107491</v>
+        <v>0.91670339327938555</v>
       </c>
       <c r="M3" s="21"/>
       <c r="N3" s="21"/>
@@ -1449,34 +1449,34 @@
         <v>550</v>
       </c>
       <c r="C4" s="17">
-        <v>89.81986854859457</v>
+        <v>8.9819868548594597E-2</v>
       </c>
       <c r="D4" s="17">
-        <v>5.9780007016897558</v>
+        <v>5.9780007016897556E-3</v>
       </c>
       <c r="E4" s="17">
-        <v>46.695266271232683</v>
+        <v>46.695266271232697</v>
       </c>
       <c r="F4" s="17">
-        <v>22.53176363727647</v>
+        <v>23.167507795229405</v>
       </c>
       <c r="G4" s="17">
-        <v>44.157918300212081</v>
+        <v>45.435199171379885</v>
       </c>
       <c r="H4" s="17">
-        <v>18.305365479551135</v>
+        <v>59.443994763217077</v>
       </c>
       <c r="I4" s="17">
-        <v>17.896265272539772</v>
+        <v>57.977325998141247</v>
       </c>
       <c r="J4" s="17">
-        <v>73.494893490611787</v>
+        <v>26</v>
       </c>
       <c r="K4" s="17">
-        <v>32.892461846891408</v>
+        <v>0.10653783387630139</v>
       </c>
       <c r="L4" s="17">
-        <v>293.94949603203861</v>
+        <v>0.95209482105832444</v>
       </c>
       <c r="M4" s="21"/>
       <c r="N4" s="21"/>
@@ -1506,34 +1506,34 @@
         <v>600</v>
       </c>
       <c r="C5" s="17">
-        <v>99.679334582948613</v>
+        <v>9.96793345829486E-2</v>
       </c>
       <c r="D5" s="17">
-        <v>6.2111932846844748</v>
+        <v>6.211193284684475E-3</v>
       </c>
       <c r="E5" s="17">
-        <v>48.86377187044944</v>
+        <v>48.863771870449447</v>
       </c>
       <c r="F5" s="17">
-        <v>23.090535501160087</v>
+        <v>23.701575419361824</v>
       </c>
       <c r="G5" s="17">
-        <v>46.368848492904625</v>
+        <v>47.626800188040562</v>
       </c>
       <c r="H5" s="17">
-        <v>18.010297345414219</v>
+        <v>59.363134451080114</v>
       </c>
       <c r="I5" s="17">
-        <v>17.606853714622613</v>
+        <v>57.898446201289907</v>
       </c>
       <c r="J5" s="17">
-        <v>73.249761451685686</v>
+        <v>26</v>
       </c>
       <c r="K5" s="17">
-        <v>33.62269663607109</v>
+        <v>0.11054310840208127</v>
       </c>
       <c r="L5" s="17">
-        <v>300.47537266795587</v>
+        <v>0.98788868877802594</v>
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
@@ -1563,34 +1563,34 @@
         <v>650</v>
       </c>
       <c r="C6" s="17">
-        <v>109.4252013288348</v>
+        <v>0.10942520132883478</v>
       </c>
       <c r="D6" s="17">
-        <v>6.4473440004104017</v>
+        <v>6.4473440004104016E-3</v>
       </c>
       <c r="E6" s="17">
         <v>50.766607886856718</v>
       </c>
       <c r="F6" s="17">
-        <v>23.373292335921985</v>
+        <v>23.959454721561013</v>
       </c>
       <c r="G6" s="17">
-        <v>48.307040618031941</v>
+        <v>49.549035428021313</v>
       </c>
       <c r="H6" s="17">
-        <v>17.725397978085738</v>
+        <v>59.283542585562842</v>
       </c>
       <c r="I6" s="17">
-        <v>17.327445115447762</v>
+        <v>57.82080382168391</v>
       </c>
       <c r="J6" s="17">
-        <v>73.005361875421784</v>
+        <v>26</v>
       </c>
       <c r="K6" s="17">
-        <v>34.3470096026928</v>
+        <v>0.11459210227772978</v>
       </c>
       <c r="L6" s="17">
-        <v>306.94832785443566</v>
+        <v>1.024073262457061</v>
       </c>
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
@@ -1620,34 +1620,34 @@
         <v>700</v>
       </c>
       <c r="C7" s="17">
-        <v>119.07911442755226</v>
+        <v>0.11907911442755229</v>
       </c>
       <c r="D7" s="17">
-        <v>6.6863221481329127</v>
+        <v>6.6863221481329119E-3</v>
       </c>
       <c r="E7" s="17">
-        <v>52.451199641588154</v>
+        <v>52.451199641588161</v>
       </c>
       <c r="F7" s="17">
-        <v>23.394499986052235</v>
+        <v>23.955025972260994</v>
       </c>
       <c r="G7" s="17">
-        <v>50.021324566011295</v>
+        <v>51.250053435463514</v>
       </c>
       <c r="H7" s="17">
-        <v>17.45023537663441</v>
+        <v>59.205180321408527</v>
       </c>
       <c r="I7" s="17">
-        <v>17.057612887314626</v>
+        <v>57.744360963714044</v>
       </c>
       <c r="J7" s="17">
-        <v>72.761883525800215</v>
+        <v>26</v>
       </c>
       <c r="K7" s="17">
-        <v>35.065255025061845</v>
+        <v>0.11868247534446567</v>
       </c>
       <c r="L7" s="17">
-        <v>313.36705932292415</v>
+        <v>1.0606276288388425</v>
       </c>
       <c r="M7" s="21"/>
       <c r="N7" s="21"/>
@@ -1677,34 +1677,34 @@
         <v>750</v>
       </c>
       <c r="C8" s="17">
-        <v>128.65749758364126</v>
+        <v>0.12865749758364126</v>
       </c>
       <c r="D8" s="17">
-        <v>6.9279630407328954</v>
+        <v>6.927963040732895E-3</v>
       </c>
       <c r="E8" s="17">
         <v>53.9538380140431</v>
       </c>
       <c r="F8" s="17">
-        <v>23.161413501793739</v>
+        <v>23.695038677100754</v>
       </c>
       <c r="G8" s="17">
-        <v>51.549060463654037</v>
+        <v>52.766695897797455</v>
       </c>
       <c r="H8" s="17">
-        <v>17.184435616492426</v>
+        <v>59.128022038629801</v>
       </c>
       <c r="I8" s="17">
-        <v>16.796987643527324</v>
+        <v>57.669092633193216</v>
       </c>
       <c r="J8" s="17">
-        <v>72.519542832587035</v>
+        <v>26</v>
       </c>
       <c r="K8" s="17">
-        <v>35.77720301027054</v>
+        <v>0.12281132001508509</v>
       </c>
       <c r="L8" s="17">
-        <v>319.72951259344148</v>
+        <v>1.0975258037389937</v>
       </c>
       <c r="M8" s="21"/>
       <c r="N8" s="21"/>
@@ -1734,34 +1734,34 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C9" s="17">
-        <v>138.17310399416084</v>
+        <v>0.13817310399416086</v>
       </c>
       <c r="D9" s="17">
-        <v>7.1720857262984268</v>
+        <v>7.1720857262984258E-3</v>
       </c>
       <c r="E9" s="17">
-        <v>55.302895315550607</v>
+        <v>55.302895315550657</v>
       </c>
       <c r="F9" s="17">
-        <v>22.675961009681458</v>
+        <v>23.18096972790984</v>
       </c>
       <c r="G9" s="17">
-        <v>52.919450623537898</v>
+        <v>54.1277629959406</v>
       </c>
       <c r="H9" s="17">
-        <v>16.927655814797117</v>
+        <v>59.052048428258885</v>
       </c>
       <c r="I9" s="17">
-        <v>16.545230654544902</v>
+        <v>57.594979992439178</v>
       </c>
       <c r="J9" s="17">
-        <v>72.278564361019221</v>
+        <v>26</v>
       </c>
       <c r="K9" s="17">
-        <v>36.482598340988282</v>
+        <v>0.12697546806706361</v>
       </c>
       <c r="L9" s="17">
-        <v>326.03340686967459</v>
+        <v>1.1347394737579666</v>
       </c>
       <c r="M9" s="21"/>
       <c r="N9" s="21"/>
@@ -1791,34 +1791,34 @@
         <v>850.00000000000011</v>
       </c>
       <c r="C10" s="17">
-        <v>147.63591018797939</v>
+        <v>0.14763591018797936</v>
       </c>
       <c r="D10" s="17">
-        <v>7.4185008301883553</v>
+        <v>7.4185008301883553E-3</v>
       </c>
       <c r="E10" s="17">
-        <v>56.520932003665223</v>
+        <v>56.520932003665166</v>
       </c>
       <c r="F10" s="17">
-        <v>21.935982366012645</v>
+        <v>22.423582815351114</v>
       </c>
       <c r="G10" s="17">
-        <v>54.155710029492219</v>
+        <v>55.389913311776915</v>
       </c>
       <c r="H10" s="17">
-        <v>16.679572745563277</v>
+        <v>59.851049318689974</v>
       </c>
       <c r="I10" s="17">
-        <v>16.302022661184491</v>
+        <v>58.666599502082221</v>
       </c>
       <c r="J10" s="17">
-        <v>72.039169748600216</v>
+        <v>54.035636198177485</v>
       </c>
       <c r="K10" s="17">
-        <v>37.181184456678366</v>
+        <v>0.13381494524769105</v>
       </c>
       <c r="L10" s="17">
-        <v>332.2764493515034</v>
+        <v>1.1958617114222196</v>
       </c>
       <c r="M10" s="21"/>
       <c r="N10" s="21"/>
@@ -1848,34 +1848,34 @@
         <v>900.00000000000011</v>
       </c>
       <c r="C11" s="20">
-        <v>157.05390229949612</v>
+        <v>0.15705390229949615</v>
       </c>
       <c r="D11" s="20">
-        <v>7.6670200718972215</v>
+        <v>7.6670200718972218E-3</v>
       </c>
       <c r="E11" s="20">
-        <v>57.626171655998625</v>
+        <v>57.62617165599864</v>
       </c>
       <c r="F11" s="20">
-        <v>20.936093045670965</v>
+        <v>21.389489601453477</v>
       </c>
       <c r="G11" s="20">
-        <v>55.276585278728227</v>
+        <v>56.503920904775917</v>
       </c>
       <c r="H11" s="20">
-        <v>16.439872677110039</v>
+        <v>59.781542759070248</v>
       </c>
       <c r="I11" s="20">
-        <v>16.067053897149204</v>
+        <v>58.598902988138313</v>
       </c>
       <c r="J11" s="20">
-        <v>71.80157092940965</v>
+        <v>54.114467173333594</v>
       </c>
       <c r="K11" s="20">
-        <v>37.872730091857683</v>
+        <v>0.13813829320714302</v>
       </c>
       <c r="L11" s="20">
-        <v>338.45657329267715</v>
+        <v>1.2344981005063695</v>
       </c>
       <c r="M11" s="21"/>
       <c r="N11" s="21"/>
@@ -1901,7 +1901,39 @@
       <c r="AH11" s="21"/>
     </row>
     <row r="12" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="L12" s="21"/>
+      <c r="B12" s="17">
+        <v>800.00000000000011</v>
+      </c>
+      <c r="C12" s="17">
+        <v>0.13817310399416086</v>
+      </c>
+      <c r="D12" s="17">
+        <v>7.1720857262984258E-3</v>
+      </c>
+      <c r="E12" s="17">
+        <v>55.302895315550657</v>
+      </c>
+      <c r="F12" s="17">
+        <v>23.18096972790984</v>
+      </c>
+      <c r="G12" s="17">
+        <v>54.1277629959406</v>
+      </c>
+      <c r="H12" s="17">
+        <v>59.052048428258885</v>
+      </c>
+      <c r="I12" s="17">
+        <v>57.594979992439178</v>
+      </c>
+      <c r="J12" s="17">
+        <v>26</v>
+      </c>
+      <c r="K12" s="17">
+        <v>0.12697546806706361</v>
+      </c>
+      <c r="L12" s="21">
+        <v>1.1347394737579666</v>
+      </c>
       <c r="M12" s="21"/>
       <c r="N12" s="21"/>
       <c r="O12" s="21"/>
@@ -2020,64 +2052,64 @@
         <v>500</v>
       </c>
       <c r="C16" s="17">
-        <v>2948.5614292537944</v>
+        <v>2.9485614292537941</v>
       </c>
       <c r="D16" s="17">
-        <v>1356.4262301173844</v>
+        <v>1.3564262301173839</v>
       </c>
       <c r="E16" s="17">
-        <v>1511.9146157877444</v>
+        <v>1.5119146157877403</v>
       </c>
       <c r="F16" s="17">
-        <v>2771.3026251072883</v>
+        <v>2.7713026251072881</v>
       </c>
       <c r="G16" s="17">
-        <v>861.11522976340632</v>
+        <v>0.86111522976340527</v>
       </c>
       <c r="H16" s="17">
-        <v>340.1774796640384</v>
+        <v>0.34017747966403838</v>
       </c>
       <c r="I16" s="17">
-        <v>3028.1716564914286</v>
+        <v>3.0281716564914243</v>
       </c>
       <c r="J16" s="17">
-        <v>11794.615416517447</v>
+        <v>11.794615416517447</v>
       </c>
       <c r="K16" s="17">
-        <v>138639.03314567471</v>
+        <v>138.63903314567469</v>
       </c>
       <c r="L16" s="17">
-        <v>89329.858804423799</v>
+        <v>89.329858804423736</v>
       </c>
       <c r="M16" s="17">
-        <v>29.001404664759903</v>
+        <v>2.3653610419403317</v>
       </c>
       <c r="N16" s="17">
-        <v>14.218380631961351</v>
+        <v>1.6493321533075163</v>
       </c>
       <c r="O16" s="17">
-        <v>6620.1750343054518</v>
+        <v>6.6201750343054497</v>
       </c>
       <c r="P16" s="17">
-        <v>3073.3893335012617</v>
+        <v>3.0733893335012619</v>
       </c>
       <c r="Q16" s="17">
-        <v>0.69940860806835647</v>
+        <v>6.9940860806835565E-4</v>
       </c>
       <c r="R16" s="17">
-        <v>635.37030855789897</v>
+        <v>0.635370308557899</v>
       </c>
       <c r="S16" s="17">
-        <v>3824.7899825655463</v>
+        <v>-0.14548588427793208</v>
       </c>
       <c r="T16" s="17">
-        <v>346597.58286418673</v>
+        <v>346.59758286418668</v>
       </c>
       <c r="U16" s="17">
-        <v>4698.1235087791883</v>
+        <v>2.3954507028929144</v>
       </c>
       <c r="V16" s="17">
-        <v>271476.94399441523</v>
+        <v>269.17546873163661</v>
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.3">
@@ -2085,64 +2117,64 @@
         <v>550</v>
       </c>
       <c r="C17" s="17">
-        <v>2978.2296698241607</v>
+        <v>2.9782296698241626</v>
       </c>
       <c r="D17" s="17">
-        <v>1318.6805418472477</v>
+        <v>1.3186805418472505</v>
       </c>
       <c r="E17" s="17">
-        <v>1521.902528703846</v>
+        <v>1.521902528703853</v>
       </c>
       <c r="F17" s="17">
-        <v>2783.7767920301558</v>
+        <v>2.7837767920301411</v>
       </c>
       <c r="G17" s="17">
-        <v>889.83413920749445</v>
+        <v>0.88983413920749443</v>
       </c>
       <c r="H17" s="17">
-        <v>805.40884684346383</v>
+        <v>0.80540884684346381</v>
       </c>
       <c r="I17" s="17">
-        <v>3649.5425807604643</v>
+        <v>3.6495425807604551</v>
       </c>
       <c r="J17" s="17">
-        <v>15916.416778681467</v>
+        <v>15.916416778681471</v>
       </c>
       <c r="K17" s="17">
-        <v>150741.7278546278</v>
+        <v>150.74172785462781</v>
       </c>
       <c r="L17" s="17">
-        <v>91657.429244218394</v>
+        <v>91.657429244218392</v>
       </c>
       <c r="M17" s="17">
-        <v>28.686520857027716</v>
+        <v>2.3561415778958588</v>
       </c>
       <c r="N17" s="17">
-        <v>13.988711900215982</v>
+        <v>1.6226905804250538</v>
       </c>
       <c r="O17" s="17">
-        <v>7003.0101822417919</v>
+        <v>7.0030101822417947</v>
       </c>
       <c r="P17" s="17">
-        <v>3243.4672934535392</v>
+        <v>3.2434672934535396</v>
       </c>
       <c r="Q17" s="17">
-        <v>0.72279964988682055</v>
+        <v>7.22799649886821E-4</v>
       </c>
       <c r="R17" s="17">
-        <v>665.4563569811354</v>
+        <v>0.66545635698113537</v>
       </c>
       <c r="S17" s="17">
-        <v>3814.9529664057522</v>
+        <v>-0.119990923365371</v>
       </c>
       <c r="T17" s="17">
-        <v>376854.31963656942</v>
+        <v>376.85431963656947</v>
       </c>
       <c r="U17" s="17">
-        <v>4904.2436020032346</v>
+        <v>2.4961883371474878</v>
       </c>
       <c r="V17" s="17">
-        <v>291937.47741023701</v>
+        <v>289.53063518117392</v>
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.3">
@@ -2150,64 +2182,64 @@
         <v>600</v>
       </c>
       <c r="C18" s="17">
-        <v>3007.2656005696876</v>
+        <v>3.0072656005696845</v>
       </c>
       <c r="D18" s="17">
-        <v>1281.507723530028</v>
+        <v>1.281507723530027</v>
       </c>
       <c r="E18" s="17">
-        <v>1528.99071995233</v>
+        <v>1.5289907199523296</v>
       </c>
       <c r="F18" s="17">
-        <v>2792.4530756981671</v>
+        <v>2.7924530756981696</v>
       </c>
       <c r="G18" s="17">
-        <v>918.55320754454283</v>
+        <v>0.91855320754454262</v>
       </c>
       <c r="H18" s="17">
-        <v>1320.1571327557904</v>
+        <v>1.3201571327557904</v>
       </c>
       <c r="I18" s="17">
-        <v>4297.0000918122378</v>
+        <v>4.2970000918122384</v>
       </c>
       <c r="J18" s="17">
-        <v>21237.887994432185</v>
+        <v>21.237887994432182</v>
       </c>
       <c r="K18" s="17">
-        <v>163810.75957825704</v>
+        <v>163.81075957825703</v>
       </c>
       <c r="L18" s="17">
-        <v>94289.610392787596</v>
+        <v>94.28961039278758</v>
       </c>
       <c r="M18" s="17">
-        <v>28.373607129403915</v>
+        <v>2.3462773513724104</v>
       </c>
       <c r="N18" s="17">
-        <v>13.761486434654085</v>
+        <v>1.596332426419806</v>
       </c>
       <c r="O18" s="17">
-        <v>7397.4316456090419</v>
+        <v>7.3974316456089495</v>
       </c>
       <c r="P18" s="17">
-        <v>3421.9548588824719</v>
+        <v>3.4219548588824718</v>
       </c>
       <c r="Q18" s="17">
-        <v>0.74619661227411505</v>
+        <v>7.4619661227411441E-4</v>
       </c>
       <c r="R18" s="17">
-        <v>696.36622761943977</v>
+        <v>0.69636622761943978</v>
       </c>
       <c r="S18" s="17">
-        <v>3803.5124922584241</v>
+        <v>-9.5734326195325889E-2</v>
       </c>
       <c r="T18" s="17">
-        <v>409526.89894564264</v>
+        <v>409.52689894564264</v>
       </c>
       <c r="U18" s="17">
-        <v>5113.586081630544</v>
+        <v>2.5984826855916676</v>
       </c>
       <c r="V18" s="17">
-        <v>314959.91811351595</v>
+        <v>312.44604258325126</v>
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.3">
@@ -2215,64 +2247,64 @@
         <v>650</v>
       </c>
       <c r="C19" s="17">
-        <v>3035.689357492201</v>
+        <v>3.0356893574921995</v>
       </c>
       <c r="D19" s="17">
-        <v>1244.8910840925203</v>
+        <v>1.2448910840925236</v>
       </c>
       <c r="E19" s="17">
-        <v>1533.9874970301762</v>
+        <v>1.5339874970301752</v>
       </c>
       <c r="F19" s="17">
-        <v>2798.4221022535266</v>
+        <v>2.7984221022535349</v>
       </c>
       <c r="G19" s="17">
-        <v>947.25497642047981</v>
+        <v>0.94725497642047962</v>
       </c>
       <c r="H19" s="17">
-        <v>1858.4739014316001</v>
+        <v>1.8584739014314837</v>
       </c>
       <c r="I19" s="17">
-        <v>4970.4374229533005</v>
+        <v>4.9704374229532986</v>
       </c>
       <c r="J19" s="17">
-        <v>28086.836717508984</v>
+        <v>28.08683671750898</v>
       </c>
       <c r="K19" s="17">
-        <v>178143.89492497977</v>
+        <v>178.14389492497978</v>
       </c>
       <c r="L19" s="17">
-        <v>97339.721439540212</v>
+        <v>97.339721439540327</v>
       </c>
       <c r="M19" s="17">
-        <v>28.062814357106859</v>
+        <v>2.3358189626234509</v>
       </c>
       <c r="N19" s="17">
-        <v>13.536801086522916</v>
+        <v>1.570268926036658</v>
       </c>
       <c r="O19" s="17">
-        <v>7803.3521734467595</v>
+        <v>7.8033521734467595</v>
       </c>
       <c r="P19" s="17">
-        <v>3609.2888254336344</v>
+        <v>3.6092888254336803</v>
       </c>
       <c r="Q19" s="17">
-        <v>0.76958539798279801</v>
+        <v>7.6958539798279801E-4</v>
       </c>
       <c r="R19" s="17">
-        <v>728.11563723720315</v>
+        <v>0.72811563723715711</v>
       </c>
       <c r="S19" s="17">
-        <v>3790.5539859561754</v>
+        <v>-7.2692234555451665E-2</v>
       </c>
       <c r="T19" s="17">
-        <v>445359.73731244943</v>
+        <v>445.35973731244945</v>
       </c>
       <c r="U19" s="17">
-        <v>5326.0795830377938</v>
+        <v>2.7023063544155743</v>
       </c>
       <c r="V19" s="17">
-        <v>341259.36882965587</v>
+        <v>338.6368376537385</v>
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.3">
@@ -2280,64 +2312,64 @@
         <v>700</v>
       </c>
       <c r="C20" s="17">
-        <v>3063.5131841675043</v>
+        <v>3.063513184167503</v>
       </c>
       <c r="D20" s="17">
-        <v>1208.8239449501671</v>
+        <v>1.208823944950167</v>
       </c>
       <c r="E20" s="17">
-        <v>1537.4467368248106</v>
+        <v>1.5374467368248153</v>
       </c>
       <c r="F20" s="17">
-        <v>2802.440878422588</v>
+        <v>2.8024408784225816</v>
       </c>
       <c r="G20" s="17">
-        <v>975.91533622180293</v>
+        <v>0.97591533622180304</v>
       </c>
       <c r="H20" s="17">
-        <v>2403.1475528596202</v>
+        <v>2.40314755285962</v>
       </c>
       <c r="I20" s="17">
-        <v>5669.5500958230568</v>
+        <v>5.6695500958230554</v>
       </c>
       <c r="J20" s="17">
-        <v>36894.255484164853</v>
+        <v>36.894255484164844</v>
       </c>
       <c r="K20" s="17">
-        <v>194120.04412755879</v>
+        <v>194.12004412755883</v>
       </c>
       <c r="L20" s="17">
-        <v>100939.4296158151</v>
+        <v>100.93942961581514</v>
       </c>
       <c r="M20" s="17">
-        <v>27.754366169382649</v>
+        <v>2.3248171675699569</v>
       </c>
       <c r="N20" s="17">
-        <v>13.31480330508251</v>
+        <v>1.544517183389571</v>
       </c>
       <c r="O20" s="17">
-        <v>8220.5630927133225</v>
+        <v>8.2205630927133253</v>
       </c>
       <c r="P20" s="17">
-        <v>3805.8664245570199</v>
+        <v>3.8058664245570188</v>
       </c>
       <c r="Q20" s="17">
-        <v>0.79294647204591096</v>
+        <v>7.9294647204591136E-4</v>
       </c>
       <c r="R20" s="17">
-        <v>760.71243566216992</v>
+        <v>0.76071243566216995</v>
       </c>
       <c r="S20" s="17">
-        <v>3776.1643515211672</v>
+        <v>-5.0845216937889411E-2</v>
       </c>
       <c r="T20" s="17">
-        <v>485300.110318897</v>
+        <v>485.30011031889705</v>
       </c>
       <c r="U20" s="17">
-        <v>5541.5981837227364</v>
+        <v>2.807605122699155</v>
       </c>
       <c r="V20" s="17">
-        <v>371761.33356093121</v>
+        <v>369.02859611293366</v>
       </c>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.3">
@@ -2345,64 +2377,64 @@
         <v>750</v>
       </c>
       <c r="C21" s="17">
-        <v>3090.7455465127828</v>
+        <v>3.0907455465127787</v>
       </c>
       <c r="D21" s="17">
-        <v>1173.3045407099946</v>
+        <v>1.1733045407099962</v>
       </c>
       <c r="E21" s="17">
-        <v>1539.7884766306952</v>
+        <v>1.5397884766306962</v>
       </c>
       <c r="F21" s="17">
-        <v>2805.018382007137</v>
+        <v>2.8050183820071397</v>
       </c>
       <c r="G21" s="17">
-        <v>1004.5071167206745</v>
+        <v>1.0045071167206743</v>
       </c>
       <c r="H21" s="17">
-        <v>2942.6310690947575</v>
+        <v>2.9426310690947575</v>
       </c>
       <c r="I21" s="17">
-        <v>6393.8950186234715</v>
+        <v>6.3938950186234722</v>
       </c>
       <c r="J21" s="17">
-        <v>48238.346125543401</v>
+        <v>48.238346125543394</v>
       </c>
       <c r="K21" s="17">
-        <v>212238.23419605001</v>
+        <v>212.23823419605003</v>
       </c>
       <c r="L21" s="17">
-        <v>105253.56004225269</v>
+        <v>105.25356004225264</v>
       </c>
       <c r="M21" s="17">
-        <v>27.448518212909715</v>
+        <v>2.3133222369557052</v>
       </c>
       <c r="N21" s="17">
-        <v>13.095660800528545</v>
+        <v>1.519096652861311</v>
       </c>
       <c r="O21" s="17">
-        <v>8648.773854705054</v>
+        <v>8.6487738547050501</v>
       </c>
       <c r="P21" s="17">
-        <v>4012.0580558999745</v>
+        <v>4.0120580558999741</v>
       </c>
       <c r="Q21" s="17">
-        <v>0.81625778220241141</v>
+        <v>8.1625778220241149E-4</v>
       </c>
       <c r="R21" s="17">
-        <v>794.15965355949538</v>
+        <v>0.79415965355949536</v>
       </c>
       <c r="S21" s="17">
-        <v>3760.4317142229957</v>
+        <v>-3.0174434344084518E-2</v>
       </c>
       <c r="T21" s="17">
-        <v>530595.58549012512</v>
+        <v>530.59558549012502</v>
       </c>
       <c r="U21" s="17">
-        <v>5759.9847247347689</v>
+        <v>2.9143093275293408</v>
       </c>
       <c r="V21" s="17">
-        <v>407696.79895406356</v>
+        <v>404.85239211909459</v>
       </c>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.3">
@@ -2410,64 +2442,64 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C22" s="17">
-        <v>3117.3934843303709</v>
+        <v>3.1173934843303797</v>
       </c>
       <c r="D22" s="17">
-        <v>1138.33305276341</v>
+        <v>1.1383330527634061</v>
       </c>
       <c r="E22" s="17">
-        <v>1541.2694860114752</v>
+        <v>1.5412694860114715</v>
       </c>
       <c r="F22" s="17">
-        <v>2806.532548235491</v>
+        <v>2.8065325482354964</v>
       </c>
       <c r="G22" s="17">
-        <v>1033.0018156282754</v>
+        <v>1.0330018156282741</v>
       </c>
       <c r="H22" s="17">
-        <v>3469.1288051136653</v>
+        <v>3.4691288051130833</v>
       </c>
       <c r="I22" s="17">
-        <v>7142.9330882120803</v>
+        <v>7.1429330882120778</v>
       </c>
       <c r="J22" s="17">
-        <v>62913.606293226985</v>
+        <v>62.913606293226934</v>
       </c>
       <c r="K22" s="17">
-        <v>233177.09736516071</v>
+        <v>233.17709736516051</v>
       </c>
       <c r="L22" s="17">
-        <v>110500.43569183591</v>
+        <v>110.50043569183623</v>
       </c>
       <c r="M22" s="17">
-        <v>27.145532961161859</v>
+        <v>2.3013833668177122</v>
       </c>
       <c r="N22" s="17">
-        <v>12.879543065694394</v>
+        <v>1.4940269956205496</v>
       </c>
       <c r="O22" s="17">
-        <v>9087.6393871715918</v>
+        <v>9.087639387171599</v>
       </c>
       <c r="P22" s="17">
-        <v>4228.2153795985059</v>
+        <v>4.2282153795985042</v>
       </c>
       <c r="Q22" s="17">
-        <v>0.8394965871715695</v>
+        <v>8.3949658717156963E-4</v>
       </c>
       <c r="R22" s="17">
-        <v>828.45750521160619</v>
+        <v>0.82845750521160622</v>
       </c>
       <c r="S22" s="17">
-        <v>3743.4447022741656</v>
+        <v>-1.0659667984780519E-2</v>
       </c>
       <c r="T22" s="17">
-        <v>582942.74341290176</v>
+        <v>582.94274341290134</v>
       </c>
       <c r="U22" s="17">
-        <v>5981.0666103429439</v>
+        <v>3.0223415591440466</v>
       </c>
       <c r="V22" s="17">
-        <v>450749.41978773114</v>
+        <v>447.79197565268419</v>
       </c>
       <c r="W22" s="21"/>
       <c r="X22" s="21"/>
@@ -2479,64 +2511,64 @@
         <v>850.00000000000011</v>
       </c>
       <c r="C23" s="17">
-        <v>3143.463834922105</v>
+        <v>3.1434638349221058</v>
       </c>
       <c r="D23" s="17">
-        <v>1103.9100202102625</v>
+        <v>1.1039100202102636</v>
       </c>
       <c r="E23" s="17">
-        <v>1542.1068241741657</v>
+        <v>1.5421068241741742</v>
       </c>
       <c r="F23" s="17">
-        <v>2807.2526540154367</v>
+        <v>2.8072526540154357</v>
       </c>
       <c r="G23" s="17">
-        <v>1061.3726985385092</v>
+        <v>1.0613726985385084</v>
       </c>
       <c r="H23" s="17">
-        <v>3977.3664473134559</v>
+        <v>3.9773664473136887</v>
       </c>
       <c r="I23" s="17">
-        <v>7916.0573066213656</v>
+        <v>7.9160573066213615</v>
       </c>
       <c r="J23" s="17">
-        <v>82043.236087615151</v>
+        <v>82.043236087615213</v>
       </c>
       <c r="K23" s="17">
-        <v>257890.4091378501</v>
+        <v>257.89040913785033</v>
       </c>
       <c r="L23" s="17">
-        <v>116982.91458223342</v>
+        <v>116.98291458223341</v>
       </c>
       <c r="M23" s="17">
-        <v>26.84566568218715</v>
+        <v>2.2890482532119778</v>
       </c>
       <c r="N23" s="17">
-        <v>12.666611299755765</v>
+        <v>1.4693269107716009</v>
       </c>
       <c r="O23" s="17">
-        <v>9536.7775019646579</v>
+        <v>9.5367775019646093</v>
       </c>
       <c r="P23" s="17">
-        <v>4454.6760841453606</v>
+        <v>4.454676084145361</v>
       </c>
       <c r="Q23" s="17">
-        <v>0.86264049813098698</v>
+        <v>8.6264049813098787E-4</v>
       </c>
       <c r="R23" s="17">
-        <v>863.60461913449035</v>
+        <v>0.86360461913449049</v>
       </c>
       <c r="S23" s="17">
-        <v>3725.2917177400277</v>
+        <v>5.8792565607020501E-3</v>
       </c>
       <c r="T23" s="17">
-        <v>644726.02284462529</v>
+        <v>644.72602284462573</v>
       </c>
       <c r="U23" s="17">
-        <v>6204.6628666425377</v>
+        <v>3.0470747563831502</v>
       </c>
       <c r="V23" s="17">
-        <v>503293.47730060096</v>
+        <v>500.13533961616463</v>
       </c>
       <c r="W23" s="21"/>
       <c r="X23" s="21"/>
@@ -2548,64 +2580,64 @@
         <v>900.00000000000011</v>
       </c>
       <c r="C24" s="20">
-        <v>3168.9638838626593</v>
+        <v>3.1689638838626562</v>
       </c>
       <c r="D24" s="20">
-        <v>1070.0354556951188</v>
+        <v>1.070035455695117</v>
       </c>
       <c r="E24" s="20">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F24" s="20">
-        <v>2807.373846715212</v>
+        <v>2.8073738467151998</v>
       </c>
       <c r="G24" s="20">
-        <v>1089.5931909999586</v>
+        <v>1.089593190999959</v>
       </c>
       <c r="H24" s="20">
-        <v>4463.8000501786591</v>
+        <v>4.4638000501786594</v>
       </c>
       <c r="I24" s="20">
-        <v>8712.6139107183735</v>
+        <v>8.7126139107183764</v>
       </c>
       <c r="J24" s="20">
-        <v>107270.29753288905</v>
+        <v>107.27029753288905</v>
       </c>
       <c r="K24" s="20">
-        <v>287768.98644095648</v>
+        <v>287.7689864409565</v>
       </c>
       <c r="L24" s="20">
-        <v>125140.03470369184</v>
+        <v>125.14003470369184</v>
       </c>
       <c r="M24" s="20">
-        <v>26.549156075515601</v>
+        <v>2.2763627598696385</v>
       </c>
       <c r="N24" s="20">
-        <v>12.457012607361445</v>
+        <v>1.4450134624539273</v>
       </c>
       <c r="O24" s="20">
-        <v>9995.7814728890007</v>
+        <v>9.9957814728889982</v>
       </c>
       <c r="P24" s="20">
-        <v>4691.7661365454696</v>
+        <v>4.6917661365454695</v>
       </c>
       <c r="Q24" s="20">
-        <v>0.88566811717443028</v>
+        <v>8.8566811717443004E-4</v>
       </c>
       <c r="R24" s="20">
-        <v>899.59878338048634</v>
+        <v>0.89959878338048638</v>
       </c>
       <c r="S24" s="20">
-        <v>3706.0602091987898</v>
+        <v>2.308222780014408E-2</v>
       </c>
       <c r="T24" s="20">
-        <v>719422.46610239113</v>
+        <v>719.42246610239113</v>
       </c>
       <c r="U24" s="20">
-        <v>6430.5927883464301</v>
+        <v>3.1543702236463185</v>
       </c>
       <c r="V24" s="20">
-        <v>568797.84695296281</v>
+        <v>565.52101646050482</v>
       </c>
       <c r="W24" s="21"/>
       <c r="X24" s="21"/>
@@ -2613,6 +2645,69 @@
       <c r="Z24" s="21"/>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B25" s="17">
+        <v>800.00000000000011</v>
+      </c>
+      <c r="C25" s="17">
+        <v>3.1173934843303797</v>
+      </c>
+      <c r="D25" s="17">
+        <v>1.1383330527634061</v>
+      </c>
+      <c r="E25" s="17">
+        <v>1.5412694860114715</v>
+      </c>
+      <c r="F25" s="17">
+        <v>2.8065325482354964</v>
+      </c>
+      <c r="G25" s="17">
+        <v>1.0330018156282741</v>
+      </c>
+      <c r="H25" s="17">
+        <v>3.4691288051130833</v>
+      </c>
+      <c r="I25" s="17">
+        <v>7.1429330882120778</v>
+      </c>
+      <c r="J25" s="17">
+        <v>62.913606293226934</v>
+      </c>
+      <c r="K25" s="17">
+        <v>233.17709736516051</v>
+      </c>
+      <c r="L25" s="17">
+        <v>110.50043569183623</v>
+      </c>
+      <c r="M25" s="17">
+        <v>2.3013833668177122</v>
+      </c>
+      <c r="N25" s="17">
+        <v>1.4940269956205496</v>
+      </c>
+      <c r="O25" s="17">
+        <v>9.087639387171599</v>
+      </c>
+      <c r="P25" s="17">
+        <v>4.2282153795985042</v>
+      </c>
+      <c r="Q25" s="17">
+        <v>8.3949658717156963E-4</v>
+      </c>
+      <c r="R25" s="17">
+        <v>0.82845750521160622</v>
+      </c>
+      <c r="S25" s="17">
+        <v>-1.0659667984780519E-2</v>
+      </c>
+      <c r="T25" s="17">
+        <v>582.94274341290134</v>
+      </c>
+      <c r="U25" s="17">
+        <v>3.0223415591440466</v>
+      </c>
+      <c r="V25" s="17">
+        <v>447.79197565268419</v>
+      </c>
       <c r="W25" s="21"/>
       <c r="X25" s="21"/>
       <c r="Y25" s="21"/>
@@ -2651,22 +2746,18 @@
         <v>500</v>
       </c>
       <c r="C29" s="17">
-        <v>0.78326265795336691</v>
+        <v>0.77662246374381749</v>
       </c>
       <c r="D29" s="17">
-        <v>3.6141108927025245</v>
+        <v>3.4774148124606663</v>
       </c>
       <c r="E29" s="21">
-        <v>0.27669322544008323</v>
-      </c>
-      <c r="F29" s="21">
-        <v>1.2361084819537911E-2</v>
-      </c>
-      <c r="G29">
-        <v>0.72330304895887298</v>
-      </c>
+        <v>0.28756994892202298</v>
+      </c>
+      <c r="F29" s="21"/>
+      <c r="G29"/>
       <c r="H29">
-        <v>21.673734204663308</v>
+        <v>22.337753625618252</v>
       </c>
       <c r="I29" s="25"/>
       <c r="J29" s="25"/>
@@ -2676,22 +2767,18 @@
         <v>550</v>
       </c>
       <c r="C30" s="17">
-        <v>0.77466931437000774</v>
+        <v>0.76828264954052083</v>
       </c>
       <c r="D30" s="17">
-        <v>3.4381210758326861</v>
+        <v>3.3162075797325237</v>
       </c>
       <c r="E30" s="21">
-        <v>0.29085653993665939</v>
-      </c>
-      <c r="F30" s="21">
-        <v>1.2174947164356329E-2</v>
-      </c>
-      <c r="G30">
-        <v>0.71310084407837038</v>
-      </c>
+        <v>0.30154927758794198</v>
+      </c>
+      <c r="F30" s="21"/>
+      <c r="G30"/>
       <c r="H30">
-        <v>22.533068562999215</v>
+        <v>23.171735045947916</v>
       </c>
       <c r="I30" s="25"/>
       <c r="J30" s="25"/>
@@ -2701,22 +2788,18 @@
         <v>600</v>
       </c>
       <c r="C31" s="17">
-        <v>0.76908237022867998</v>
+        <v>0.76294388326546259</v>
       </c>
       <c r="D31" s="17">
-        <v>3.3307255701802183</v>
+        <v>3.2189585281416084</v>
       </c>
       <c r="E31" s="21">
-        <v>0.30023488243911134</v>
-      </c>
-      <c r="F31" s="21">
-        <v>1.2032304792923087E-2</v>
-      </c>
-      <c r="G31">
-        <v>0.70528261570011441</v>
-      </c>
+        <v>0.31065948543839333</v>
+      </c>
+      <c r="F31" s="21"/>
+      <c r="G31"/>
       <c r="H31">
-        <v>23.091762977132003</v>
+        <v>23.705611673453742</v>
       </c>
       <c r="I31" s="25"/>
       <c r="J31" s="25"/>
@@ -2726,22 +2809,22 @@
         <v>650</v>
       </c>
       <c r="C32" s="17">
-        <v>0.76625554633431037</v>
+        <v>0.76036697815851795</v>
       </c>
       <c r="D32" s="17">
-        <v>3.2783380934172728</v>
+        <v>3.173557107183524</v>
       </c>
       <c r="E32" s="21">
-        <v>0.3050326023444459</v>
+        <v>0.31510383025294991</v>
       </c>
       <c r="F32" s="21">
-        <v>1.1918890450311831E-2</v>
+        <v>1.093327961204547E-2</v>
       </c>
       <c r="G32">
-        <v>0.69906637558159146</v>
+        <v>0.64504504553621222</v>
       </c>
       <c r="H32">
-        <v>23.374445366568963</v>
+        <v>23.963302184148215</v>
       </c>
       <c r="I32" s="25"/>
       <c r="J32" s="25"/>
@@ -2751,22 +2834,22 @@
         <v>700</v>
       </c>
       <c r="C33" s="17">
-        <v>0.76604419751036534</v>
+        <v>0.76041317169790079</v>
       </c>
       <c r="D33" s="17">
-        <v>3.274462792395989</v>
+        <v>3.1743366614522994</v>
       </c>
       <c r="E33" s="21">
-        <v>0.30539360603584087</v>
+        <v>0.31502644698766363</v>
       </c>
       <c r="F33" s="21">
-        <v>1.1826368829128379E-2</v>
+        <v>1.0936752307543264E-2</v>
       </c>
       <c r="G33">
-        <v>0.69399526552452651</v>
+        <v>0.64523538397644631</v>
       </c>
       <c r="H33">
-        <v>23.395580248963466</v>
+        <v>23.95868283020992</v>
       </c>
       <c r="I33" s="25"/>
       <c r="J33" s="25"/>
@@ -2776,22 +2859,18 @@
         <v>750</v>
       </c>
       <c r="C34" s="17">
-        <v>0.76837578393620309</v>
+        <v>0.76301500274473988</v>
       </c>
       <c r="D34" s="17">
-        <v>3.3174822593478424</v>
+        <v>3.2201466861589432</v>
       </c>
       <c r="E34" s="21">
-        <v>0.30143341299934551</v>
-      </c>
-      <c r="F34" s="21">
-        <v>1.1749324463843415E-2</v>
-      </c>
-      <c r="G34">
-        <v>0.68977246386325763</v>
-      </c>
+        <v>0.31054485943086663</v>
+      </c>
+      <c r="F34" s="21"/>
+      <c r="G34"/>
       <c r="H34">
-        <v>23.162421606379691</v>
+        <v>23.698499725526013</v>
       </c>
       <c r="I34" s="25"/>
       <c r="J34" s="25"/>
@@ -2801,22 +2880,22 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C35" s="17">
-        <v>0.77323103320365494</v>
+        <v>0.76815773197730819</v>
       </c>
       <c r="D35" s="17">
-        <v>3.4099151646694286</v>
+        <v>3.3137428718197577</v>
       </c>
       <c r="E35" s="21">
-        <v>0.29326242786363987</v>
+        <v>0.30177356502342179</v>
       </c>
       <c r="F35" s="21">
-        <v>1.1684219661096553E-2</v>
+        <v>1.0946804887868034E-2</v>
       </c>
       <c r="G35">
-        <v>0.68620406962470215</v>
+        <v>0.64578636590404692</v>
       </c>
       <c r="H35">
-        <v>22.676896679634506</v>
+        <v>23.18422680226918</v>
       </c>
       <c r="I35" s="25"/>
       <c r="J35" s="25"/>
@@ -2826,22 +2905,22 @@
         <v>850.00000000000011</v>
       </c>
       <c r="C36" s="17">
-        <v>0.78063155428409226</v>
+        <v>0.7757331360839046</v>
       </c>
       <c r="D36" s="17">
-        <v>3.5586806246416098</v>
+        <v>3.4594522314821168</v>
       </c>
       <c r="E36" s="17">
-        <v>0.28100301923011389</v>
+        <v>0.28906310395029639</v>
       </c>
       <c r="F36" s="21">
-        <v>1.1628483332333845E-2</v>
+        <v>1.0948878679185562E-2</v>
       </c>
       <c r="G36">
-        <v>0.68314916144521809</v>
+        <v>0.64590003040616073</v>
       </c>
       <c r="H36">
-        <v>21.936844571590786</v>
+        <v>22.42668639160954</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
@@ -2849,26 +2928,46 @@
         <v>900.00000000000011</v>
       </c>
       <c r="C37" s="20">
-        <v>0.79063119898734036</v>
+        <v>0.78607639197636292</v>
       </c>
       <c r="D37" s="20">
-        <v>3.7764027761178784</v>
+        <v>3.6750591370957575</v>
       </c>
       <c r="E37" s="20">
-        <v>0.26480226270461399</v>
+        <v>0.27210446490672185</v>
       </c>
       <c r="F37" s="20">
-        <v>1.1580256134364322E-2</v>
+        <v>1.0952326373580519E-2</v>
       </c>
       <c r="G37" s="20">
-        <v>0.68050582872450849</v>
+        <v>0.64608899853594826</v>
       </c>
       <c r="H37" s="20">
-        <v>20.936880101265952</v>
+        <v>21.392360802363719</v>
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H38" s="21"/>
+      <c r="B38" s="17">
+        <v>800.00000000000011</v>
+      </c>
+      <c r="C38" s="17">
+        <v>0.76815773197730819</v>
+      </c>
+      <c r="D38" s="17">
+        <v>3.3137428718197577</v>
+      </c>
+      <c r="E38" s="17">
+        <v>0.30177356502342179</v>
+      </c>
+      <c r="F38" s="17">
+        <v>1.0946804887868034E-2</v>
+      </c>
+      <c r="G38" s="17">
+        <v>0.64578636590404692</v>
+      </c>
+      <c r="H38" s="21">
+        <v>23.18422680226918</v>
+      </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F39" s="21"/>
@@ -2930,34 +3029,34 @@
         <v>2.5</v>
       </c>
       <c r="C3" s="17">
-        <v>148.16689369741928</v>
+        <v>0.14816689369741928</v>
       </c>
       <c r="D3" s="17">
-        <v>6.7342358759702696</v>
+        <v>6.7342358759702702E-3</v>
       </c>
       <c r="E3" s="17">
         <v>56.964645761388169</v>
       </c>
       <c r="F3" s="17">
-        <v>20.76638257848656</v>
+        <v>21.177717530176274</v>
       </c>
       <c r="G3" s="17">
-        <v>54.828330497626311</v>
+        <v>55.941806182451671</v>
       </c>
       <c r="H3" s="17">
-        <v>17.441013464225993</v>
+        <v>60.13539183455795</v>
       </c>
       <c r="I3" s="17">
-        <v>17.0490261992745</v>
+        <v>58.972944791760909</v>
       </c>
       <c r="J3" s="17">
-        <v>73.324154648869751</v>
+        <v>56.632627091431857</v>
       </c>
       <c r="K3" s="17">
-        <v>35.298899030097473</v>
+        <v>0.12211214723233685</v>
       </c>
       <c r="L3" s="17">
-        <v>315.45506166980897</v>
+        <v>1.0912775183997925</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -2965,34 +3064,34 @@
         <v>2.7</v>
       </c>
       <c r="C4" s="17">
-        <v>155.66697058060771</v>
+        <v>0.15566697058060769</v>
       </c>
       <c r="D4" s="17">
-        <v>7.5293584802110809</v>
+        <v>7.5293584802110817E-3</v>
       </c>
       <c r="E4" s="17">
-        <v>57.545256030232359</v>
+        <v>57.545256030232352</v>
       </c>
       <c r="F4" s="17">
-        <v>20.916342885012611</v>
+        <v>21.364087267029952</v>
       </c>
       <c r="G4" s="17">
-        <v>55.224424495132965</v>
+        <v>56.436459797130688</v>
       </c>
       <c r="H4" s="17">
-        <v>16.577598279744681</v>
+        <v>59.83266920833421</v>
       </c>
       <c r="I4" s="17">
-        <v>16.202117630865612</v>
+        <v>58.653227949931896</v>
       </c>
       <c r="J4" s="17">
-        <v>72.020515667514871</v>
+        <v>54.509173803592262</v>
       </c>
       <c r="K4" s="17">
-        <v>37.505487197563291</v>
+        <v>0.13578470918644805</v>
       </c>
       <c r="L4" s="17">
-        <v>335.17464005819699</v>
+        <v>1.2134648668137162</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -3000,34 +3099,34 @@
         <v>2.9</v>
       </c>
       <c r="C5" s="17">
-        <v>162.27893989998952</v>
+        <v>0.16227893989998951</v>
       </c>
       <c r="D5" s="17">
-        <v>8.1624683336946049</v>
+        <v>8.1624683336946058E-3</v>
       </c>
       <c r="E5" s="17">
-        <v>57.867796024364083</v>
+        <v>57.867796024364097</v>
       </c>
       <c r="F5" s="17">
-        <v>20.991532723655869</v>
+        <v>21.451381804251511</v>
       </c>
       <c r="G5" s="17">
-        <v>55.422986423214837</v>
+        <v>56.667788907976181</v>
       </c>
       <c r="H5" s="17">
-        <v>15.969258491659119</v>
+        <v>58.761692285486703</v>
       </c>
       <c r="I5" s="17">
-        <v>15.605596060142126</v>
+        <v>57.311736430927176</v>
       </c>
       <c r="J5" s="17">
-        <v>71.029884266576062</v>
+        <v>26</v>
       </c>
       <c r="K5" s="17">
-        <v>39.161674085045284</v>
+        <v>0.14379864522624392</v>
       </c>
       <c r="L5" s="17">
-        <v>349.9754568282014</v>
+        <v>1.285082870692426</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -3035,34 +3134,34 @@
         <v>3.1</v>
       </c>
       <c r="C6" s="17">
-        <v>168.16932560061701</v>
+        <v>0.16816932560061704</v>
       </c>
       <c r="D6" s="17">
-        <v>8.686527999868952</v>
+        <v>8.686527999868951E-3</v>
       </c>
       <c r="E6" s="17">
         <v>58.033954827081338</v>
       </c>
       <c r="F6" s="17">
-        <v>21.021563313236495</v>
+        <v>21.498673305116203</v>
       </c>
       <c r="G6" s="17">
-        <v>55.502260178915265</v>
+        <v>56.79378761358371</v>
       </c>
       <c r="H6" s="17">
-        <v>15.510178237410971</v>
+        <v>58.618045868696775</v>
       </c>
       <c r="I6" s="17">
-        <v>15.155540354724605</v>
+        <v>57.171608974412401</v>
       </c>
       <c r="J6" s="17">
-        <v>70.243600700525974</v>
+        <v>26</v>
       </c>
       <c r="K6" s="17">
-        <v>40.473691505924258</v>
+        <v>0.15265687096659597</v>
       </c>
       <c r="L6" s="17">
-        <v>361.70054026670601</v>
+        <v>1.3642460237648557</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -3070,34 +3169,34 @@
         <v>3.3</v>
       </c>
       <c r="C7" s="17">
-        <v>173.45261418436411</v>
+        <v>0.17345261418436411</v>
       </c>
       <c r="D7" s="17">
-        <v>9.1364978290003886</v>
+        <v>9.1364978290003895E-3</v>
       </c>
       <c r="E7" s="17">
         <v>58.09849493424899</v>
       </c>
       <c r="F7" s="17">
-        <v>21.021719048004329</v>
+        <v>21.511617804235726</v>
       </c>
       <c r="G7" s="17">
-        <v>55.502633418048816</v>
+        <v>56.828779788176234</v>
       </c>
       <c r="H7" s="17">
-        <v>15.144272525361949</v>
+        <v>58.499426691536961</v>
       </c>
       <c r="I7" s="17">
-        <v>14.796895802750958</v>
+        <v>57.055895750215626</v>
       </c>
       <c r="J7" s="17">
-        <v>69.596354166304025</v>
+        <v>26</v>
       </c>
       <c r="K7" s="17">
-        <v>41.562555762188133</v>
+        <v>0.16023965484701469</v>
       </c>
       <c r="L7" s="17">
-        <v>371.43137467083</v>
+        <v>1.4320109575829549</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -3105,34 +3204,34 @@
         <v>3.5</v>
       </c>
       <c r="C8" s="17">
-        <v>178.21771118453276</v>
+        <v>0.17821771118453278</v>
       </c>
       <c r="D8" s="17">
-        <v>9.5336854968264078</v>
+        <v>9.5336854968264082E-3</v>
       </c>
       <c r="E8" s="17">
-        <v>58.093587340872247</v>
+        <v>58.093587340872254</v>
       </c>
       <c r="F8" s="17">
-        <v>21.001060822403193</v>
+        <v>21.500883358703305</v>
       </c>
       <c r="G8" s="17">
-        <v>55.448045028227412</v>
+        <v>56.801054877285281</v>
       </c>
       <c r="H8" s="17">
-        <v>14.840909759490916</v>
+        <v>58.397997958337498</v>
       </c>
       <c r="I8" s="17">
-        <v>14.499600926667302</v>
+        <v>56.956951903247862</v>
       </c>
       <c r="J8" s="17">
-        <v>69.048904190007818</v>
+        <v>26</v>
       </c>
       <c r="K8" s="17">
-        <v>42.497762640748867</v>
+        <v>0.16691573452926184</v>
       </c>
       <c r="L8" s="17">
-        <v>379.78902183990635</v>
+        <v>1.4916729636438284</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -3205,64 +3304,64 @@
         <v>2.5</v>
       </c>
       <c r="C16" s="17">
-        <v>2664.8478767473252</v>
+        <v>2.6648478767473245</v>
       </c>
       <c r="D16" s="17">
-        <v>986.37006924873401</v>
+        <v>0.98637006924873272</v>
       </c>
       <c r="E16" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F16" s="17">
-        <v>2398.8101530183258</v>
+        <v>2.3988101530183341</v>
       </c>
       <c r="G16" s="17">
-        <v>997.03770676192551</v>
+        <v>0.99703770676192471</v>
       </c>
       <c r="H16" s="17">
-        <v>6947.6550741795809</v>
+        <v>6.9476550741795799</v>
       </c>
       <c r="I16" s="17">
-        <v>9249.2997745483663</v>
+        <v>9.2492997745483656</v>
       </c>
       <c r="J16" s="17">
-        <v>102375.56157213112</v>
+        <v>102.3755615721311</v>
       </c>
       <c r="K16" s="17">
-        <v>274638.10828811495</v>
+        <v>274.63810828811501</v>
       </c>
       <c r="L16" s="17">
-        <v>119161.08401865959</v>
+        <v>119.16108401865955</v>
       </c>
       <c r="M16" s="17">
-        <v>28.439355661207351</v>
+        <v>2.5016228555001572</v>
       </c>
       <c r="N16" s="17">
-        <v>13.800941887616878</v>
+        <v>1.6009092589635576</v>
       </c>
       <c r="O16" s="17">
-        <v>8175.1551300820374</v>
+        <v>8.1751551300820342</v>
       </c>
       <c r="P16" s="17">
-        <v>3700.0428190667417</v>
+        <v>3.7000428190667423</v>
       </c>
       <c r="Q16" s="17">
-        <v>0.809941181583682</v>
+        <v>8.0994118158368082E-4</v>
       </c>
       <c r="R16" s="17">
-        <v>754.06058026615347</v>
+        <v>0.75406058026615341</v>
       </c>
       <c r="S16" s="17">
-        <v>4793.5371512133352</v>
+        <v>0.73255540084823856</v>
       </c>
       <c r="T16" s="17">
-        <v>686595.27072028746</v>
+        <v>686.59527072028743</v>
       </c>
       <c r="U16" s="17">
-        <v>5581.9131402913681</v>
+        <v>2.7454173458677973</v>
       </c>
       <c r="V16" s="17">
-        <v>544008.9903031555</v>
+        <v>541.17180457528173</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -3270,64 +3369,64 @@
         <v>2.7</v>
       </c>
       <c r="C17" s="17">
-        <v>3087.3746791042909</v>
+        <v>3.0873746791042942</v>
       </c>
       <c r="D17" s="17">
-        <v>1058.1726709377524</v>
+        <v>1.0581726709377508</v>
       </c>
       <c r="E17" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F17" s="17">
-        <v>2741.5191927130818</v>
+        <v>2.74151919271308</v>
       </c>
       <c r="G17" s="17">
-        <v>1076.5328210015157</v>
+        <v>1.0765328210015159</v>
       </c>
       <c r="H17" s="17">
-        <v>4812.2007797128163</v>
+        <v>4.8122007797128168</v>
       </c>
       <c r="I17" s="17">
-        <v>8798.3787257595359</v>
+        <v>8.7983787257595463</v>
       </c>
       <c r="J17" s="17">
-        <v>106472.50431367061</v>
+        <v>106.47250431367063</v>
       </c>
       <c r="K17" s="17">
-        <v>285628.78406094934</v>
+        <v>285.62878406094933</v>
       </c>
       <c r="L17" s="17">
-        <v>124163.1956881715</v>
+        <v>124.16319568817148</v>
       </c>
       <c r="M17" s="17">
-        <v>26.818318458563386</v>
+        <v>2.3094414175745959</v>
       </c>
       <c r="N17" s="17">
-        <v>12.646116251516156</v>
+        <v>1.4669494851758738</v>
       </c>
       <c r="O17" s="17">
-        <v>9724.4418843231942</v>
+        <v>9.724441884323193</v>
       </c>
       <c r="P17" s="17">
-        <v>4529.4501957169959</v>
+        <v>4.529450195716997</v>
       </c>
       <c r="Q17" s="17">
-        <v>0.87497071764366408</v>
+        <v>8.7497071764366474E-4</v>
       </c>
       <c r="R17" s="17">
-        <v>877.17648611728293</v>
+        <v>0.87717648611728305</v>
       </c>
       <c r="S17" s="17">
-        <v>3851.153404008046</v>
+        <v>0.11360130264901518</v>
       </c>
       <c r="T17" s="17">
-        <v>714071.9601523733</v>
+        <v>714.07196015237332</v>
       </c>
       <c r="U17" s="17">
-        <v>6304.9321542947046</v>
+        <v>3.0936444427711418</v>
       </c>
       <c r="V17" s="17">
-        <v>564708.61317200388</v>
+        <v>561.49669982716159</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -3335,64 +3434,64 @@
         <v>2.9</v>
       </c>
       <c r="C18" s="17">
-        <v>3483.3349591886849</v>
+        <v>3.4833349591886873</v>
       </c>
       <c r="D18" s="17">
-        <v>1112.8283922583832</v>
+        <v>1.1128283922583833</v>
       </c>
       <c r="E18" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F18" s="17">
-        <v>3062.6461462244392</v>
+        <v>3.0626461462244623</v>
       </c>
       <c r="G18" s="17">
-        <v>1134.9118833301486</v>
+        <v>1.134911883330149</v>
       </c>
       <c r="H18" s="17">
-        <v>3261.9581509413547</v>
+        <v>3.2619581509413549</v>
       </c>
       <c r="I18" s="17">
-        <v>8389.0102350076741</v>
+        <v>8.3890102350076639</v>
       </c>
       <c r="J18" s="17">
-        <v>110376.27722141369</v>
+        <v>110.37627722141367</v>
       </c>
       <c r="K18" s="17">
-        <v>296101.25219792326</v>
+        <v>296.10125219792326</v>
       </c>
       <c r="L18" s="17">
-        <v>128951.81516126439</v>
+        <v>128.95181516126439</v>
       </c>
       <c r="M18" s="17">
-        <v>25.606427123562518</v>
+        <v>2.1580349110813133</v>
       </c>
       <c r="N18" s="17">
-        <v>11.801660538249831</v>
+        <v>1.3689926224369802</v>
       </c>
       <c r="O18" s="17">
-        <v>10979.19765967354</v>
+        <v>10.97919765967354</v>
       </c>
       <c r="P18" s="17">
-        <v>5326.8577223470802</v>
+        <v>5.3268577223470821</v>
       </c>
       <c r="Q18" s="17">
-        <v>0.92282153852808912</v>
+        <v>9.2282153852808952E-4</v>
       </c>
       <c r="R18" s="17">
-        <v>983.24170106960253</v>
+        <v>0.98324170106960251</v>
       </c>
       <c r="S18" s="17">
-        <v>3228.7579140535781</v>
+        <v>-0.25955065955024703</v>
       </c>
       <c r="T18" s="17">
-        <v>740253.13049480808</v>
+        <v>740.25313049480803</v>
       </c>
       <c r="U18" s="17">
-        <v>6883.9186704482818</v>
+        <v>3.4629181106772062</v>
       </c>
       <c r="V18" s="17">
-        <v>584856.79563444015</v>
+        <v>581.43710594692186</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -3400,64 +3499,64 @@
         <v>3.1</v>
       </c>
       <c r="C19" s="17">
-        <v>3849.8455050005987</v>
+        <v>3.849845505000594</v>
       </c>
       <c r="D19" s="17">
-        <v>1159.2727723247745</v>
+        <v>1.1592727723247735</v>
       </c>
       <c r="E19" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F19" s="17">
-        <v>3364.9348540762367</v>
+        <v>3.3649348540762438</v>
       </c>
       <c r="G19" s="17">
-        <v>1180.0986703582332</v>
+        <v>1.180098670358233</v>
       </c>
       <c r="H19" s="17">
-        <v>2088.2936759883305</v>
+        <v>2.0882936759883304</v>
       </c>
       <c r="I19" s="17">
-        <v>8025.6331977169812</v>
+        <v>8.0256331977169904</v>
       </c>
       <c r="J19" s="17">
-        <v>114055.21230881629</v>
+        <v>114.05521230881628</v>
       </c>
       <c r="K19" s="17">
-        <v>305970.5584796489</v>
+        <v>305.9705584796489</v>
       </c>
       <c r="L19" s="17">
-        <v>133484.92502395887</v>
+        <v>133.48492502395891</v>
       </c>
       <c r="M19" s="17">
-        <v>24.66020890619394</v>
+        <v>2.0354357212835343</v>
       </c>
       <c r="N19" s="17">
-        <v>11.151730495964454</v>
+        <v>1.2936007375318763</v>
       </c>
       <c r="O19" s="17">
-        <v>12030.465799378224</v>
+        <v>12.030465799378224</v>
       </c>
       <c r="P19" s="17">
-        <v>6091.4841011854433</v>
+        <v>6.0914841011854417</v>
       </c>
       <c r="Q19" s="17">
-        <v>0.9599212273135399</v>
+        <v>9.5992122731354003E-4</v>
       </c>
       <c r="R19" s="17">
-        <v>1077.0012172548297</v>
+        <v>1.0770012172548296</v>
       </c>
       <c r="S19" s="17">
-        <v>2798.8045602279121</v>
+        <v>-0.493111310371803</v>
       </c>
       <c r="T19" s="17">
-        <v>764926.39619912219</v>
+        <v>764.92639619912222</v>
       </c>
       <c r="U19" s="17">
-        <v>7365.0996693036432</v>
+        <v>3.6974779927046795</v>
       </c>
       <c r="V19" s="17">
-        <v>604120.85840596433</v>
+        <v>600.45454537817875</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -3465,64 +3564,64 @@
         <v>3.3</v>
       </c>
       <c r="C20" s="17">
-        <v>4189.7807746840863</v>
+        <v>4.1897807746840847</v>
       </c>
       <c r="D20" s="17">
-        <v>1200.5121499819197</v>
+        <v>1.2005121499819216</v>
       </c>
       <c r="E20" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F20" s="17">
-        <v>3650.6399459165932</v>
+        <v>3.6506399459165988</v>
       </c>
       <c r="G20" s="17">
-        <v>1216.8194568160066</v>
+        <v>1.2168194568160069</v>
       </c>
       <c r="H20" s="17">
-        <v>1173.6306340101291</v>
+        <v>1.1736306340101292</v>
       </c>
       <c r="I20" s="17">
-        <v>7700.3977334383871</v>
+        <v>7.7003977334383675</v>
       </c>
       <c r="J20" s="17">
-        <v>117507.74436055892</v>
+        <v>117.50774436055892</v>
       </c>
       <c r="K20" s="17">
-        <v>315232.50397653977</v>
+        <v>315.23250397653982</v>
       </c>
       <c r="L20" s="17">
-        <v>137757.25064697993</v>
+        <v>137.75725064697997</v>
       </c>
       <c r="M20" s="17">
-        <v>23.887054558579301</v>
+        <v>1.9340930512475702</v>
       </c>
       <c r="N20" s="17">
-        <v>10.630116297173496</v>
+        <v>1.2330934904721254</v>
       </c>
       <c r="O20" s="17">
-        <v>12941.619902553473</v>
+        <v>12.941619902553503</v>
       </c>
       <c r="P20" s="17">
-        <v>6829.2880756010709</v>
+        <v>6.8292880756010712</v>
       </c>
       <c r="Q20" s="17">
-        <v>0.99011228412205488</v>
+        <v>9.9011228412205468E-4</v>
       </c>
       <c r="R20" s="17">
-        <v>1162.0598783187363</v>
+        <v>1.1620598783187359</v>
       </c>
       <c r="S20" s="17">
-        <v>2487.1201872007637</v>
+        <v>-0.64423924252588405</v>
       </c>
       <c r="T20" s="17">
-        <v>788081.2599413495</v>
+        <v>788.08125994134957</v>
       </c>
       <c r="U20" s="17">
-        <v>7779.4824577979125</v>
+        <v>3.8996313447041677</v>
       </c>
       <c r="V20" s="17">
-        <v>622406.814173633</v>
+        <v>618.52827300167678</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -3530,64 +3629,64 @@
         <v>3.5</v>
       </c>
       <c r="C21" s="17">
-        <v>4506.4720702113282</v>
+        <v>4.5064720702113261</v>
       </c>
       <c r="D21" s="17">
-        <v>1237.8443466263898</v>
+        <v>1.2378443466263889</v>
       </c>
       <c r="E21" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F21" s="17">
-        <v>3921.6241291317938</v>
+        <v>3.9216241291317857</v>
       </c>
       <c r="G21" s="17">
-        <v>1247.7923804527093</v>
+        <v>1.2477923804527091</v>
       </c>
       <c r="H21" s="17">
-        <v>447.74442370759789</v>
+        <v>0.44774442370759787</v>
       </c>
       <c r="I21" s="17">
-        <v>7405.7577728634324</v>
+        <v>7.4057577728634207</v>
       </c>
       <c r="J21" s="17">
-        <v>120746.12116199643</v>
+        <v>120.74612116199641</v>
       </c>
       <c r="K21" s="17">
-        <v>323919.94524683047</v>
+        <v>323.91994524683048</v>
       </c>
       <c r="L21" s="17">
-        <v>141780.80722790223</v>
+        <v>141.78080722790236</v>
       </c>
       <c r="M21" s="17">
-        <v>23.242725160827526</v>
+        <v>1.8489805188311883</v>
       </c>
       <c r="N21" s="17">
-        <v>10.198269471027357</v>
+        <v>1.1829992586391733</v>
       </c>
       <c r="O21" s="17">
-        <v>13751.892148659181</v>
+        <v>13.751892148659186</v>
       </c>
       <c r="P21" s="17">
-        <v>7545.4352560223924</v>
+        <v>7.5454352560223921</v>
       </c>
       <c r="Q21" s="17">
-        <v>1.0156068599449528</v>
+        <v>1.0156068599449534E-3</v>
       </c>
       <c r="R21" s="17">
-        <v>1240.7425352944572</v>
+        <v>1.240742535294457</v>
       </c>
       <c r="S21" s="17">
-        <v>2251.7511475437595</v>
+        <v>-0.74548183748495012</v>
       </c>
       <c r="T21" s="17">
-        <v>809799.86311707599</v>
+        <v>809.79986311707626</v>
       </c>
       <c r="U21" s="17">
-        <v>8146.1043519154309</v>
+        <v>4.0786349558568915</v>
       </c>
       <c r="V21" s="17">
-        <v>639726.94751074491</v>
+        <v>635.6607839124963</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -3618,22 +3717,22 @@
         <v>2.5</v>
       </c>
       <c r="C29" s="17">
-        <v>0.7923284844832259</v>
+        <v>0.78819623095794678</v>
       </c>
       <c r="D29" s="17">
-        <v>3.8154381558204453</v>
+        <v>3.7218186040815806</v>
       </c>
       <c r="E29" s="17">
-        <v>0.26209309629996269</v>
+        <v>0.26868585129413269</v>
       </c>
       <c r="F29" s="17">
-        <v>1.1916757448054462E-2</v>
+        <v>1.0973501548280534E-2</v>
       </c>
       <c r="G29" s="17">
-        <v>0.69894946572786509</v>
+        <v>0.64724960986125613</v>
       </c>
       <c r="H29" s="17">
-        <v>20.767151551677422</v>
+        <v>21.18037690420531</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -3641,22 +3740,22 @@
         <v>2.7</v>
       </c>
       <c r="C30" s="17">
-        <v>0.79082871851109049</v>
+        <v>0.7863306937683785</v>
       </c>
       <c r="D30" s="17">
-        <v>3.7809129581526921</v>
+        <v>3.6806191808712576</v>
       </c>
       <c r="E30" s="17">
-        <v>0.26448638492026744</v>
+        <v>0.27169341647654105</v>
       </c>
       <c r="F30" s="17">
-        <v>1.161515776460759E-2</v>
+        <v>1.0955380818656758E-2</v>
       </c>
       <c r="G30" s="17">
-        <v>0.68241878707814208</v>
+        <v>0.64625641267057687</v>
       </c>
       <c r="H30" s="17">
-        <v>20.917128148890953</v>
+        <v>21.366930623162162</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -3664,22 +3763,16 @@
         <v>2.9</v>
       </c>
       <c r="C31" s="17">
-        <v>0.79007676096351509</v>
+        <v>0.78545713890905311</v>
       </c>
       <c r="D31" s="17">
-        <v>3.7637878632519213</v>
+        <v>3.6615689659366422</v>
       </c>
       <c r="E31" s="17">
-        <v>0.26568978814230981</v>
-      </c>
-      <c r="F31" s="17">
-        <v>1.1484389958345869E-2</v>
-      </c>
-      <c r="G31" s="17">
-        <v>0.67525140361693714</v>
+        <v>0.27310696843428062</v>
       </c>
       <c r="H31" s="17">
-        <v>20.992323903648501</v>
+        <v>21.454286109094689</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -3687,22 +3780,16 @@
         <v>3.1</v>
       </c>
       <c r="C32" s="17">
-        <v>0.78977645615030179</v>
+        <v>0.78498342894401973</v>
       </c>
       <c r="D32" s="17">
-        <v>3.7569825059252802</v>
+        <v>3.6513110265144189</v>
       </c>
       <c r="E32" s="17">
-        <v>0.26617105574030808</v>
-      </c>
-      <c r="F32" s="17">
-        <v>1.1421118297927127E-2</v>
-      </c>
-      <c r="G32" s="17">
-        <v>0.6717834839093858</v>
+        <v>0.27387423112914344</v>
       </c>
       <c r="H32" s="17">
-        <v>21.022354384969834</v>
+        <v>21.501657105598028</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
@@ -3710,22 +3797,16 @@
         <v>3.3</v>
       </c>
       <c r="C33" s="17">
-        <v>0.78977492019027795</v>
+        <v>0.78485342114049095</v>
       </c>
       <c r="D33" s="17">
-        <v>3.7569473666106021</v>
+        <v>3.6485095090614248</v>
       </c>
       <c r="E33" s="17">
-        <v>0.26617354527970616</v>
-      </c>
-      <c r="F33" s="17">
-        <v>1.1388229853412446E-2</v>
-      </c>
-      <c r="G33" s="17">
-        <v>0.66998086826553627</v>
+        <v>0.27408452616511036</v>
       </c>
       <c r="H33" s="17">
-        <v>21.022507980972204</v>
+        <v>21.514657885950903</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
@@ -3733,22 +3814,16 @@
         <v>3.5</v>
       </c>
       <c r="C34" s="17">
-        <v>0.78998154562327583</v>
+        <v>0.78496034991376151</v>
       </c>
       <c r="D34" s="17">
-        <v>3.7616268640132273</v>
+        <v>3.6508283721097383</v>
       </c>
       <c r="E34" s="17">
-        <v>0.26584242301298167</v>
-      </c>
-      <c r="F34" s="17">
-        <v>1.1370614920618203E-2</v>
-      </c>
-      <c r="G34" s="17">
-        <v>0.6690153937990837</v>
+        <v>0.27391043841979368</v>
       </c>
       <c r="H34" s="17">
-        <v>21.001845437672419</v>
+        <v>21.503965008623858</v>
       </c>
     </row>
   </sheetData>
@@ -3804,34 +3879,34 @@
         <v>0.6</v>
       </c>
       <c r="C3" s="17">
-        <v>84.211561976013954</v>
+        <v>8.4211561976013968E-2</v>
       </c>
       <c r="D3" s="17">
-        <v>7.8630926606964033</v>
+        <v>7.8630926606964024E-3</v>
       </c>
       <c r="E3" s="17">
         <v>41.852285461263897</v>
       </c>
       <c r="F3" s="17">
-        <v>14.609756931868748</v>
+        <v>15.24145462009974</v>
       </c>
       <c r="G3" s="17">
-        <v>38.581243760380737</v>
+        <v>40.291237071467492</v>
       </c>
       <c r="H3" s="17">
-        <v>16.25771923391715</v>
+        <v>59.727872168516029</v>
       </c>
       <c r="I3" s="17">
-        <v>15.888509699581155</v>
+        <v>58.546594548248024</v>
       </c>
       <c r="J3" s="17">
-        <v>71.616789037388912</v>
+        <v>54.171985391620581</v>
       </c>
       <c r="K3" s="17">
-        <v>38.409525516739883</v>
+        <v>0.14154461481035646</v>
       </c>
       <c r="L3" s="17">
-        <v>343.25374370062394</v>
+        <v>1.2649393159814668</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -3839,34 +3914,34 @@
         <v>0.65</v>
       </c>
       <c r="C4" s="17">
-        <v>95.281754998553794</v>
+        <v>9.5281754998553791E-2</v>
       </c>
       <c r="D4" s="17">
-        <v>7.8332887957953403</v>
+        <v>7.8332887957953384E-3</v>
       </c>
       <c r="E4" s="17">
         <v>44.933380647869939</v>
       </c>
       <c r="F4" s="17">
-        <v>15.845474212445962</v>
+        <v>16.442344008453379</v>
       </c>
       <c r="G4" s="17">
-        <v>41.842329326986977</v>
+        <v>43.458044213676864</v>
       </c>
       <c r="H4" s="17">
-        <v>16.28502694489416</v>
+        <v>59.735966243145022</v>
       </c>
       <c r="I4" s="17">
-        <v>15.915275564920073</v>
+        <v>58.554485160804404</v>
       </c>
       <c r="J4" s="17">
-        <v>71.644726145929837</v>
+        <v>54.163497220831061</v>
       </c>
       <c r="K4" s="17">
-        <v>38.328417839914948</v>
+        <v>0.14102710050591502</v>
       </c>
       <c r="L4" s="17">
-        <v>342.528910125138</v>
+        <v>1.2603144548297525</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -3874,34 +3949,34 @@
         <v>0.7</v>
       </c>
       <c r="C5" s="17">
-        <v>106.35197332921997</v>
+        <v>0.10635197332921997</v>
       </c>
       <c r="D5" s="17">
-        <v>7.8034867682354951</v>
+        <v>7.8034867682354944E-3</v>
       </c>
       <c r="E5" s="17">
-        <v>47.714779598232667</v>
+        <v>47.714779598232759</v>
       </c>
       <c r="F5" s="17">
-        <v>16.960993627423512</v>
+        <v>17.526423384732322</v>
       </c>
       <c r="G5" s="17">
-        <v>44.786209962074224</v>
+        <v>46.316817277727253</v>
       </c>
       <c r="H5" s="17">
-        <v>16.312467590576237</v>
+        <v>59.744082530708894</v>
       </c>
       <c r="I5" s="17">
-        <v>15.942171998171231</v>
+        <v>58.562396729475942</v>
       </c>
       <c r="J5" s="17">
-        <v>71.672715315581797</v>
+        <v>54.154919475518398</v>
       </c>
       <c r="K5" s="17">
-        <v>38.247141925589851</v>
+        <v>0.1405095248648236</v>
       </c>
       <c r="L5" s="17">
-        <v>341.80257306448817</v>
+        <v>1.2556890455318568</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -3909,34 +3984,34 @@
         <v>0.75</v>
       </c>
       <c r="C6" s="17">
-        <v>117.42221717459931</v>
+        <v>0.11742221717459934</v>
       </c>
       <c r="D6" s="17">
-        <v>7.7736866894088301</v>
+        <v>7.7736866894088322E-3</v>
       </c>
       <c r="E6" s="17">
-        <v>50.238175942453644</v>
+        <v>50.238175942453665</v>
       </c>
       <c r="F6" s="17">
-        <v>17.973037039039568</v>
+        <v>18.509943306381878</v>
       </c>
       <c r="G6" s="17">
-        <v>47.457015044388491</v>
+        <v>48.91040982949049</v>
       </c>
       <c r="H6" s="17">
-        <v>16.340042169130623</v>
+        <v>59.75222116501245</v>
       </c>
       <c r="I6" s="17">
-        <v>15.969199981553711</v>
+        <v>58.570329377579746</v>
       </c>
       <c r="J6" s="17">
-        <v>71.700756546104344</v>
+        <v>54.146251392484373</v>
       </c>
       <c r="K6" s="17">
-        <v>38.165697124592612</v>
+        <v>0.13999188962571618</v>
       </c>
       <c r="L6" s="17">
-        <v>341.07472671723065</v>
+        <v>1.2510631036254005</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -3944,34 +4019,34 @@
         <v>0.8</v>
       </c>
       <c r="C7" s="17">
-        <v>128.49248674250657</v>
+        <v>0.1284924867425066</v>
       </c>
       <c r="D7" s="17">
-        <v>7.743888671611427</v>
+        <v>7.743888671611427E-3</v>
       </c>
       <c r="E7" s="17">
-        <v>52.537872183380294</v>
+        <v>52.537872183380308</v>
       </c>
       <c r="F7" s="17">
-        <v>18.895361985772201</v>
+        <v>19.40627355648672</v>
       </c>
       <c r="G7" s="17">
-        <v>49.891051034146052</v>
+        <v>51.27407868290198</v>
       </c>
       <c r="H7" s="17">
-        <v>16.36775168897524</v>
+        <v>59.760382281137382</v>
       </c>
       <c r="I7" s="17">
-        <v>15.996360507390436</v>
+        <v>58.57828322960458</v>
       </c>
       <c r="J7" s="17">
-        <v>71.728849836347308</v>
+        <v>54.137492201448424</v>
       </c>
       <c r="K7" s="17">
-        <v>38.084082784419742</v>
+        <v>0.13947419654295456</v>
       </c>
       <c r="L7" s="17">
-        <v>340.34536525214861</v>
+        <v>1.2464366447885584</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -3979,34 +4054,34 @@
         <v>0.85</v>
       </c>
       <c r="C8" s="17">
-        <v>139.56278198500698</v>
+        <v>0.13956278198500702</v>
       </c>
       <c r="D8" s="17">
-        <v>7.7140927853093819</v>
+        <v>7.7140927853093831E-3</v>
       </c>
       <c r="E8" s="17">
-        <v>54.642345188567155</v>
+        <v>54.642345188567177</v>
       </c>
       <c r="F8" s="17">
-        <v>19.73938966239082</v>
+        <v>20.226513368609627</v>
       </c>
       <c r="G8" s="17">
-        <v>52.118458725483521</v>
+        <v>53.437093089396768</v>
       </c>
       <c r="H8" s="17">
-        <v>16.395597206045643</v>
+        <v>59.768566025359505</v>
       </c>
       <c r="I8" s="17">
-        <v>16.023654614611125</v>
+        <v>58.586258420224183</v>
       </c>
       <c r="J8" s="17">
-        <v>71.756995183209312</v>
+        <v>54.128641048997849</v>
       </c>
       <c r="K8" s="17">
-        <v>38.002298124925424</v>
+        <v>0.13895644663801524</v>
       </c>
       <c r="L8" s="17">
-        <v>339.61448169732654</v>
+        <v>1.2418096781499413</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -4014,34 +4089,34 @@
         <v>0.9</v>
       </c>
       <c r="C9" s="17">
-        <v>150.63310366538568</v>
+        <v>0.15063310366538565</v>
       </c>
       <c r="D9" s="17">
-        <v>7.6842992366371705</v>
+        <v>7.684299236637172E-3</v>
       </c>
       <c r="E9" s="17">
         <v>56.575443092400867</v>
       </c>
       <c r="F9" s="17">
-        <v>20.51468447118021</v>
+        <v>20.979957694675662</v>
       </c>
       <c r="G9" s="17">
-        <v>54.164478798760605</v>
+        <v>55.423964332470618</v>
       </c>
       <c r="H9" s="17">
-        <v>16.423579669894796</v>
+        <v>59.77677251407335</v>
       </c>
       <c r="I9" s="17">
-        <v>16.051083238013277</v>
+        <v>58.594255056971043</v>
       </c>
       <c r="J9" s="17">
-        <v>71.785192585913705</v>
+        <v>54.119697313632969</v>
       </c>
       <c r="K9" s="17">
-        <v>37.920342754213891</v>
+        <v>0.13843864330880659</v>
       </c>
       <c r="L9" s="17">
-        <v>338.88207255051623</v>
+        <v>1.2371822340755787</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -4114,64 +4189,64 @@
         <v>0.6</v>
       </c>
       <c r="C16" s="17">
-        <v>3188.5506685029641</v>
+        <v>3.1885506685029612</v>
       </c>
       <c r="D16" s="17">
-        <v>1043.876310747346</v>
+        <v>1.0438763107473461</v>
       </c>
       <c r="E16" s="17">
-        <v>8610.2319558728486</v>
+        <v>8.6102319558728482</v>
       </c>
       <c r="F16" s="17">
-        <v>15551.202889850705</v>
+        <v>15.551202889850712</v>
       </c>
       <c r="G16" s="17">
-        <v>1111.5831277611805</v>
+        <v>1.1115831277611814</v>
       </c>
       <c r="H16" s="17">
-        <v>4828.1167891059304</v>
+        <v>4.8281167891059305</v>
       </c>
       <c r="I16" s="17">
-        <v>9352.6697515099131</v>
+        <v>9.3526697515099073</v>
       </c>
       <c r="J16" s="17">
-        <v>79195.96700526237</v>
+        <v>79.195967005262375</v>
       </c>
       <c r="K16" s="17">
-        <v>212455.29917849187</v>
+        <v>212.45529917849188</v>
       </c>
       <c r="L16" s="17">
-        <v>91682.455189337765</v>
+        <v>91.682455189337773</v>
       </c>
       <c r="M16" s="17">
-        <v>26.319321122467287</v>
+        <v>2.2662069549226316</v>
       </c>
       <c r="N16" s="17">
-        <v>12.295199599041567</v>
+        <v>1.4262431534888216</v>
       </c>
       <c r="O16" s="17">
-        <v>10362.045100531313</v>
+        <v>10.362045100531315</v>
       </c>
       <c r="P16" s="17">
-        <v>4885.1662034555775</v>
+        <v>4.8851662034555785</v>
       </c>
       <c r="Q16" s="17">
-        <v>0.90361665491794607</v>
+        <v>9.0361665491794604E-4</v>
       </c>
       <c r="R16" s="17">
-        <v>928.39153384896269</v>
+        <v>0.92839153384896267</v>
       </c>
       <c r="S16" s="17">
-        <v>3690.2939294248226</v>
+        <v>3.5804149179434662E-2</v>
       </c>
       <c r="T16" s="17">
-        <v>531138.24794622965</v>
+        <v>531.13824794622963</v>
       </c>
       <c r="U16" s="17">
-        <v>6609.1306684771125</v>
+        <v>3.2391739055063429</v>
       </c>
       <c r="V16" s="17">
-        <v>453534.49843955727</v>
+        <v>450.16388748403097</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -4179,64 +4254,64 @@
         <v>0.65</v>
       </c>
       <c r="C17" s="17">
-        <v>3185.6026611351294</v>
+        <v>3.1856026611351265</v>
       </c>
       <c r="D17" s="17">
-        <v>1047.8213709567915</v>
+        <v>1.0478213709567898</v>
       </c>
       <c r="E17" s="17">
-        <v>7544.4300571883768</v>
+        <v>7.5444300571883796</v>
       </c>
       <c r="F17" s="17">
-        <v>13641.822894306615</v>
+        <v>13.641822894306621</v>
       </c>
       <c r="G17" s="17">
-        <v>1108.2559641090977</v>
+        <v>1.1082559641090983</v>
       </c>
       <c r="H17" s="17">
-        <v>4773.8608169536465</v>
+        <v>4.7738608169536452</v>
       </c>
       <c r="I17" s="17">
-        <v>9254.7297393386671</v>
+        <v>9.2547297393386696</v>
       </c>
       <c r="J17" s="17">
-        <v>83462.458846271998</v>
+        <v>83.462458846272</v>
       </c>
       <c r="K17" s="17">
-        <v>223900.81635317404</v>
+        <v>223.90081635317406</v>
       </c>
       <c r="L17" s="17">
-        <v>96731.337537772473</v>
+        <v>96.731337537772518</v>
       </c>
       <c r="M17" s="17">
-        <v>26.354027026530865</v>
+        <v>2.267758230379429</v>
       </c>
       <c r="N17" s="17">
-        <v>12.319597142596336</v>
+        <v>1.4290732685411747</v>
       </c>
       <c r="O17" s="17">
-        <v>10306.14186292257</v>
+        <v>10.306141862922569</v>
       </c>
       <c r="P17" s="17">
-        <v>4855.401858262283</v>
+        <v>4.8554018582622822</v>
       </c>
       <c r="Q17" s="17">
-        <v>0.90090077122570711</v>
+        <v>9.009007712257064E-4</v>
       </c>
       <c r="R17" s="17">
-        <v>923.99223502528923</v>
+        <v>0.92399223502528893</v>
       </c>
       <c r="S17" s="17">
-        <v>3692.7222397455644</v>
+        <v>3.3917216413731265E-2</v>
       </c>
       <c r="T17" s="17">
-        <v>559752.04088293505</v>
+        <v>559.75204088293515</v>
       </c>
       <c r="U17" s="17">
-        <v>6581.9762457248316</v>
+        <v>3.2262748683101767</v>
       </c>
       <c r="V17" s="17">
-        <v>471050.94520782772</v>
+        <v>467.69459668183288</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -4244,64 +4319,64 @@
         <v>0.7</v>
       </c>
       <c r="C18" s="17">
-        <v>3182.644455056779</v>
+        <v>3.1826444550567756</v>
       </c>
       <c r="D18" s="17">
-        <v>1051.7772748712823</v>
+        <v>1.0517772748712815</v>
       </c>
       <c r="E18" s="17">
-        <v>6475.6703599589018</v>
+        <v>6.4756703599588947</v>
       </c>
       <c r="F18" s="17">
-        <v>11722.797219174221</v>
+        <v>11.722797219174215</v>
       </c>
       <c r="G18" s="17">
-        <v>1104.923475024757</v>
+        <v>1.1049234750247561</v>
       </c>
       <c r="H18" s="17">
-        <v>4719.2041314713424</v>
+        <v>4.71920413147111</v>
       </c>
       <c r="I18" s="17">
-        <v>9157.0271064838616</v>
+        <v>9.1570271064838735</v>
       </c>
       <c r="J18" s="17">
-        <v>87728.994646362858</v>
+        <v>87.728994646362665</v>
       </c>
       <c r="K18" s="17">
-        <v>235346.45145481778</v>
+        <v>235.34645145481733</v>
       </c>
       <c r="L18" s="17">
-        <v>101792.88253725517</v>
+        <v>101.79288253725483</v>
       </c>
       <c r="M18" s="17">
-        <v>26.388812877572651</v>
+        <v>2.2693067979055233</v>
       </c>
       <c r="N18" s="17">
-        <v>12.344064045004503</v>
+        <v>1.4319114292205222</v>
       </c>
       <c r="O18" s="17">
-        <v>10250.323800790415</v>
+        <v>10.250323800790419</v>
       </c>
       <c r="P18" s="17">
-        <v>4825.7715495631974</v>
+        <v>4.8257715495631963</v>
       </c>
       <c r="Q18" s="17">
-        <v>0.89818063269454707</v>
+        <v>8.9818063269454654E-4</v>
       </c>
       <c r="R18" s="17">
-        <v>919.60136568056782</v>
+        <v>0.91960136568056761</v>
       </c>
       <c r="S18" s="17">
-        <v>3695.1392369119085</v>
+        <v>3.2013777684334971E-2</v>
       </c>
       <c r="T18" s="17">
-        <v>588366.12863704446</v>
+        <v>588.36612863704318</v>
       </c>
       <c r="U18" s="17">
-        <v>6554.8291499897132</v>
+        <v>3.2133796689570824</v>
       </c>
       <c r="V18" s="17">
-        <v>488567.6688209679</v>
+        <v>485.22557923090994</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -4309,64 +4384,64 @@
         <v>0.75</v>
       </c>
       <c r="C19" s="17">
-        <v>3179.6759917278887</v>
+        <v>3.1796759917278905</v>
       </c>
       <c r="D19" s="17">
-        <v>1055.7440776822809</v>
+        <v>1.0557440776822804</v>
       </c>
       <c r="E19" s="17">
-        <v>5403.9352110712753</v>
+        <v>5.4039352110712793</v>
       </c>
       <c r="F19" s="17">
-        <v>9794.0194828991152</v>
+        <v>9.7940194828991078</v>
       </c>
       <c r="G19" s="17">
-        <v>1101.5856640998954</v>
+        <v>1.1015856640998944</v>
       </c>
       <c r="H19" s="17">
-        <v>4664.1478209078205</v>
+        <v>4.6641478209078198</v>
       </c>
       <c r="I19" s="17">
-        <v>9059.5629791777956</v>
+        <v>9.0595629791778052</v>
       </c>
       <c r="J19" s="17">
-        <v>91995.574525781194</v>
+        <v>91.995574525781194</v>
       </c>
       <c r="K19" s="17">
-        <v>246792.20480600206</v>
+        <v>246.79220480600199</v>
       </c>
       <c r="L19" s="17">
-        <v>106867.21213527194</v>
+        <v>106.86721213527193</v>
       </c>
       <c r="M19" s="17">
-        <v>26.423678762950853</v>
+        <v>2.2708525914225359</v>
       </c>
       <c r="N19" s="17">
-        <v>12.368600444652017</v>
+        <v>1.4347576515796336</v>
       </c>
       <c r="O19" s="17">
-        <v>10194.591485539635</v>
+        <v>10.194591485539634</v>
       </c>
       <c r="P19" s="17">
-        <v>4796.2748915086886</v>
+        <v>4.7962748915086886</v>
       </c>
       <c r="Q19" s="17">
-        <v>0.89545624248824884</v>
+        <v>8.9545624248824843E-4</v>
       </c>
       <c r="R19" s="17">
-        <v>915.21892164972576</v>
+        <v>0.91521892164972585</v>
       </c>
       <c r="S19" s="17">
-        <v>3697.5447688577583</v>
+        <v>3.0093731055990471E-2</v>
       </c>
       <c r="T19" s="17">
-        <v>616980.51201500499</v>
+        <v>616.98051201500505</v>
       </c>
       <c r="U19" s="17">
-        <v>6527.6895138187447</v>
+        <v>3.2004883620793869</v>
       </c>
       <c r="V19" s="17">
-        <v>506084.670011446</v>
+        <v>502.75683578569931</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -4374,64 +4449,64 @@
         <v>0.8</v>
       </c>
       <c r="C20" s="17">
-        <v>3176.6972121346889</v>
+        <v>3.1766972121346844</v>
       </c>
       <c r="D20" s="17">
-        <v>1059.721835024003</v>
+        <v>1.0597218350240001</v>
       </c>
       <c r="E20" s="17">
-        <v>4329.206793663554</v>
+        <v>4.3292067936635572</v>
       </c>
       <c r="F20" s="17">
-        <v>7855.3814543741792</v>
+        <v>7.8553814543741751</v>
       </c>
       <c r="G20" s="17">
-        <v>1098.2430498994579</v>
+        <v>1.0982430498994591</v>
       </c>
       <c r="H20" s="17">
-        <v>4608.6931025683307</v>
+        <v>4.6086931025683295</v>
       </c>
       <c r="I20" s="17">
-        <v>8962.3384882152895</v>
+        <v>8.9623384882152894</v>
       </c>
       <c r="J20" s="17">
-        <v>96262.198605157217</v>
+        <v>96.262198605157224</v>
       </c>
       <c r="K20" s="17">
-        <v>258238.07673033568</v>
+        <v>258.23807673033571</v>
       </c>
       <c r="L20" s="17">
-        <v>111954.45016030467</v>
+        <v>111.95445016030466</v>
       </c>
       <c r="M20" s="17">
-        <v>26.45862476931628</v>
+        <v>2.2723955440679502</v>
       </c>
       <c r="N20" s="17">
-        <v>12.393206479507223</v>
+        <v>1.4376119516228376</v>
       </c>
       <c r="O20" s="17">
-        <v>10138.94548999074</v>
+        <v>10.138945489990787</v>
       </c>
       <c r="P20" s="17">
-        <v>4766.910980901248</v>
+        <v>4.7669109809012475</v>
       </c>
       <c r="Q20" s="17">
-        <v>0.89272760389944328</v>
+        <v>8.9272760389944321E-4</v>
       </c>
       <c r="R20" s="17">
-        <v>910.84489976972441</v>
+        <v>0.91084489976972427</v>
       </c>
       <c r="S20" s="17">
-        <v>3699.9386821275457</v>
+        <v>2.815697403019336E-2</v>
       </c>
       <c r="T20" s="17">
-        <v>645595.19182583911</v>
+        <v>645.59519182583927</v>
       </c>
       <c r="U20" s="17">
-        <v>6500.5574707715496</v>
+        <v>3.1876010027004567</v>
       </c>
       <c r="V20" s="17">
-        <v>523601.94951409067</v>
+        <v>520.28836700236388</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -4439,64 +4514,64 @@
         <v>0.85</v>
       </c>
       <c r="C21" s="17">
-        <v>3173.7080391990989</v>
+        <v>3.1737080391990968</v>
       </c>
       <c r="D21" s="17">
-        <v>1063.7106287563015</v>
+        <v>1.0637106287563038</v>
       </c>
       <c r="E21" s="17">
-        <v>3251.4671250847132</v>
+        <v>3.2514671250847167</v>
       </c>
       <c r="F21" s="17">
-        <v>5906.7693275598585</v>
+        <v>5.9067693275598581</v>
       </c>
       <c r="G21" s="17">
-        <v>1094.8945809626541</v>
+        <v>1.0948945809626529</v>
       </c>
       <c r="H21" s="17">
-        <v>4552.8544882684373</v>
+        <v>4.5528544882684363</v>
       </c>
       <c r="I21" s="17">
-        <v>8865.3546420253879</v>
+        <v>8.8653546420253981</v>
       </c>
       <c r="J21" s="17">
-        <v>100528.87198471166</v>
+        <v>100.52887198471164</v>
       </c>
       <c r="K21" s="17">
-        <v>269684.0809099414</v>
+        <v>269.68408090994143</v>
       </c>
       <c r="L21" s="17">
-        <v>117054.72843049669</v>
+        <v>117.05472843049664</v>
       </c>
       <c r="M21" s="17">
-        <v>26.493650980813314</v>
+        <v>2.2739355842054483</v>
       </c>
       <c r="N21" s="17">
-        <v>12.417882287122572</v>
+        <v>1.4404743453062181</v>
       </c>
       <c r="O21" s="17">
-        <v>10083.386332505124</v>
+        <v>10.083386332505116</v>
       </c>
       <c r="P21" s="17">
-        <v>4737.680452731639</v>
+        <v>4.7376804527316398</v>
       </c>
       <c r="Q21" s="17">
-        <v>0.88999471541966435</v>
+        <v>8.8999471541966455E-4</v>
       </c>
       <c r="R21" s="17">
-        <v>906.47929000459351</v>
+        <v>0.90647929000459382</v>
       </c>
       <c r="S21" s="17">
-        <v>3702.3208011292131</v>
+        <v>2.620338680930415E-2</v>
       </c>
       <c r="T21" s="17">
-        <v>674210.20227485348</v>
+        <v>674.21020227485337</v>
       </c>
       <c r="U21" s="17">
-        <v>6473.4331167445353</v>
+        <v>3.1747176279460891</v>
       </c>
       <c r="V21" s="17">
-        <v>541119.54167810467</v>
+        <v>537.82020717123009</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -4504,64 +4579,64 @@
         <v>0.9</v>
       </c>
       <c r="C22" s="17">
-        <v>3170.7084507537484</v>
+        <v>3.1707084507537511</v>
       </c>
       <c r="D22" s="17">
-        <v>1067.7104599818438</v>
+        <v>1.0677104599818412</v>
       </c>
       <c r="E22" s="17">
-        <v>2170.6980548234433</v>
+        <v>2.1706980548234425</v>
       </c>
       <c r="F22" s="17">
-        <v>3948.0789449175445</v>
+        <v>3.9480789449175355</v>
       </c>
       <c r="G22" s="17">
-        <v>1091.540809577046</v>
+        <v>1.091540809577048</v>
       </c>
       <c r="H22" s="17">
-        <v>4496.6051596002653</v>
+        <v>4.4966051596002652</v>
       </c>
       <c r="I22" s="17">
-        <v>8768.6128540601658</v>
+        <v>8.768612854060164</v>
       </c>
       <c r="J22" s="17">
-        <v>104795.58407176075</v>
+        <v>104.79558407176074</v>
       </c>
       <c r="K22" s="17">
-        <v>281130.18892832403</v>
+        <v>281.130188928324</v>
       </c>
       <c r="L22" s="17">
-        <v>122168.16161023772</v>
+        <v>122.16816161023768</v>
       </c>
       <c r="M22" s="17">
-        <v>26.52875748258317</v>
+        <v>2.2754726519311625</v>
       </c>
       <c r="N22" s="17">
-        <v>12.442628004623598</v>
+        <v>1.4433448485363372</v>
       </c>
       <c r="O22" s="17">
-        <v>10027.914709061537</v>
+        <v>10.027914709061532</v>
       </c>
       <c r="P22" s="17">
-        <v>4708.5824367404157</v>
+        <v>4.708582436740417</v>
       </c>
       <c r="Q22" s="17">
-        <v>0.88725759121543613</v>
+        <v>8.8725759121543654E-4</v>
       </c>
       <c r="R22" s="17">
-        <v>902.12210022993486</v>
+        <v>0.902122100229935</v>
       </c>
       <c r="S22" s="17">
-        <v>3704.6910141341332</v>
+        <v>2.4232901724251073E-2</v>
       </c>
       <c r="T22" s="17">
-        <v>702825.47232081008</v>
+        <v>702.82547232081004</v>
       </c>
       <c r="U22" s="17">
-        <v>6446.3166706272159</v>
+        <v>3.1618383330094</v>
       </c>
       <c r="V22" s="17">
-        <v>558637.37491790799</v>
+        <v>555.35228458286076</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -4592,22 +4667,22 @@
         <v>0.6</v>
       </c>
       <c r="C29" s="17">
-        <v>0.85389161897727106</v>
+        <v>0.84754560460425321</v>
       </c>
       <c r="D29" s="17">
-        <v>5.8446668412028737</v>
+        <v>5.5607921010803549</v>
       </c>
       <c r="E29" s="17">
-        <v>0.17109615093033992</v>
+        <v>0.17983049569605727</v>
       </c>
       <c r="F29" s="17">
-        <v>1.2054140014573155E-2</v>
+        <v>1.0931033749141028E-2</v>
       </c>
       <c r="G29" s="17">
-        <v>0.70647940419875466</v>
+        <v>0.64492194979041984</v>
       </c>
       <c r="H29" s="17">
-        <v>14.610838102272893</v>
+        <v>15.245439539574679</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -4615,22 +4690,22 @@
         <v>0.65</v>
       </c>
       <c r="C30" s="17">
-        <v>0.84153502051516771</v>
+        <v>0.83553888601121706</v>
       </c>
       <c r="D30" s="17">
-        <v>5.3108856777172182</v>
+        <v>5.0816287846893831</v>
       </c>
       <c r="E30" s="17">
-        <v>0.18829251102046518</v>
+        <v>0.19678729839789458</v>
       </c>
       <c r="F30" s="17">
-        <v>1.1935407594307215E-2</v>
+        <v>1.0935217351420626E-2</v>
       </c>
       <c r="G30" s="17">
-        <v>0.69997168024397849</v>
+        <v>0.64515125303136456</v>
       </c>
       <c r="H30" s="17">
-        <v>15.846497948483229</v>
+        <v>16.446111398878294</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -4638,22 +4713,22 @@
         <v>0.7</v>
       </c>
       <c r="C31" s="17">
-        <v>0.83038034489296564</v>
+        <v>0.82470005599224505</v>
       </c>
       <c r="D31" s="17">
-        <v>4.8958236948474463</v>
+        <v>4.7054669277855092</v>
       </c>
       <c r="E31" s="17">
-        <v>0.20425572126962793</v>
+        <v>0.21251876069833964</v>
       </c>
       <c r="F31" s="17">
-        <v>1.1841379034640441E-2</v>
+        <v>1.0938986786365809E-2</v>
       </c>
       <c r="G31" s="17">
-        <v>0.69481797488864261</v>
+        <v>0.64535785576071003</v>
       </c>
       <c r="H31" s="17">
-        <v>16.961965510703447</v>
+        <v>17.529994400775493</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -4661,22 +4736,22 @@
         <v>0.75</v>
       </c>
       <c r="C32" s="17">
-        <v>0.82026038125356215</v>
+        <v>0.81486663840279006</v>
       </c>
       <c r="D32" s="17">
-        <v>4.5638384846804652</v>
+        <v>4.4023183913363981</v>
       </c>
       <c r="E32" s="17">
-        <v>0.21911380154155796</v>
+        <v>0.22715303871886311</v>
       </c>
       <c r="F32" s="17">
-        <v>1.176511508779335E-2</v>
+        <v>1.0942396324374062E-2</v>
       </c>
       <c r="G32" s="17">
-        <v>0.69063794796195355</v>
+        <v>0.6455447325389424</v>
       </c>
       <c r="H32" s="17">
-        <v>17.973961874643784</v>
+        <v>18.513336159721007</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
@@ -4684,22 +4759,22 @@
         <v>0.8</v>
       </c>
       <c r="C33" s="17">
-        <v>0.81103756060088761</v>
+        <v>0.80590495962479369</v>
       </c>
       <c r="D33" s="17">
-        <v>4.2922573338980294</v>
+        <v>4.1528063452213511</v>
       </c>
       <c r="E33" s="17">
-        <v>0.2329776437452892</v>
+        <v>0.24080101908693707</v>
       </c>
       <c r="F33" s="17">
-        <v>1.1701992017364047E-2</v>
+        <v>1.0945495411489195E-2</v>
       </c>
       <c r="G33" s="17">
-        <v>0.68717817247172341</v>
+        <v>0.64571459350372284</v>
       </c>
       <c r="H33" s="17">
-        <v>18.896243939911241</v>
+        <v>19.409504037520641</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
@@ -4707,22 +4782,22 @@
         <v>0.85</v>
       </c>
       <c r="C34" s="17">
-        <v>0.8025976762919228</v>
+        <v>0.79770404742700474</v>
       </c>
       <c r="D34" s="17">
-        <v>4.0659700731330144</v>
+        <v>3.9438534605029605</v>
       </c>
       <c r="E34" s="17">
-        <v>0.24594376791107433</v>
+        <v>0.25355911674072945</v>
       </c>
       <c r="F34" s="17">
-        <v>1.1648885335282464E-2</v>
+        <v>1.0948324843076037E-2</v>
       </c>
       <c r="G34" s="17">
-        <v>0.68426739522683189</v>
+        <v>0.64586967464899758</v>
       </c>
       <c r="H34" s="17">
-        <v>19.740232370807721</v>
+        <v>20.229595257299525</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
@@ -4730,22 +4805,22 @@
         <v>0.9</v>
       </c>
       <c r="C35" s="17">
-        <v>0.79484508874333115</v>
+        <v>0.7901709691155957</v>
       </c>
       <c r="D35" s="17">
-        <v>3.8745177380620159</v>
+        <v>3.7663134531302083</v>
       </c>
       <c r="E35" s="17">
-        <v>0.2580966374669863</v>
+        <v>0.26551162361934938</v>
       </c>
       <c r="F35" s="17">
-        <v>1.1603605702897936E-2</v>
+        <v>1.095091857991398E-2</v>
       </c>
       <c r="G35" s="17">
-        <v>0.68178561857583586</v>
+        <v>0.64601183736508527</v>
       </c>
       <c r="H35" s="17">
-        <v>20.515491125666873</v>
+        <v>20.98290308844043</v>
       </c>
     </row>
   </sheetData>
@@ -4801,34 +4876,34 @@
         <v>0.6</v>
       </c>
       <c r="C3" s="17">
-        <v>130.86918068201132</v>
+        <v>0.13086918068201137</v>
       </c>
       <c r="D3" s="17">
-        <v>8.8141654444115058</v>
+        <v>8.8141654444115064E-3</v>
       </c>
       <c r="E3" s="17">
-        <v>49.878796554537139</v>
+        <v>49.878796554537026</v>
       </c>
       <c r="F3" s="17">
-        <v>17.815192680590009</v>
+        <v>18.37326690227815</v>
       </c>
       <c r="G3" s="17">
-        <v>47.03974603996263</v>
+        <v>48.550442064273085</v>
       </c>
       <c r="H3" s="17">
-        <v>15.454823679518492</v>
+        <v>59.943515535314361</v>
       </c>
       <c r="I3" s="17">
-        <v>15.101699640128905</v>
+        <v>58.920654666082875</v>
       </c>
       <c r="J3" s="17">
-        <v>70.81030342479761</v>
+        <v>70.612173722288844</v>
       </c>
       <c r="K3" s="17">
-        <v>40.922629894870369</v>
+        <v>0.1597339979473</v>
       </c>
       <c r="L3" s="17">
-        <v>365.71256021809842</v>
+        <v>1.4274920622953922</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -4836,34 +4911,34 @@
         <v>0.65</v>
       </c>
       <c r="C4" s="17">
-        <v>137.01888853317391</v>
+        <v>0.13701888853317393</v>
       </c>
       <c r="D4" s="17">
-        <v>8.5397213545798163</v>
+        <v>8.5397213545798153E-3</v>
       </c>
       <c r="E4" s="17">
         <v>51.771991448655704</v>
       </c>
       <c r="F4" s="17">
-        <v>18.577736186967428</v>
+        <v>19.112085785005224</v>
       </c>
       <c r="G4" s="17">
-        <v>49.052303063086939</v>
+        <v>50.498776994288662</v>
       </c>
       <c r="H4" s="17">
-        <v>15.67755876168555</v>
+        <v>60.021929404349727</v>
       </c>
       <c r="I4" s="17">
-        <v>15.319976571220023</v>
+        <v>59.000938788462065</v>
       </c>
       <c r="J4" s="17">
-        <v>71.083142907569311</v>
+        <v>70.881080313060295</v>
       </c>
       <c r="K4" s="17">
-        <v>40.221665830556631</v>
+        <v>0.15497245314779157</v>
       </c>
       <c r="L4" s="17">
-        <v>359.44826676385026</v>
+        <v>1.3849396470744026</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -4871,34 +4946,34 @@
         <v>0.7</v>
       </c>
       <c r="C5" s="17">
-        <v>142.30508065956138</v>
+        <v>0.14230508065956135</v>
       </c>
       <c r="D5" s="17">
-        <v>8.3060695450992057</v>
+        <v>8.3060695450992046E-3</v>
       </c>
       <c r="E5" s="17">
-        <v>53.363862994038215</v>
+        <v>53.3638629940382</v>
       </c>
       <c r="F5" s="17">
-        <v>19.218978885217201</v>
+        <v>19.733339335790927</v>
       </c>
       <c r="G5" s="17">
-        <v>50.744709448083036</v>
+        <v>52.137073147294522</v>
       </c>
       <c r="H5" s="17">
-        <v>15.874683129121278</v>
+        <v>60.090302237082973</v>
       </c>
       <c r="I5" s="17">
-        <v>15.513171109606835</v>
+        <v>59.070937879496412</v>
       </c>
       <c r="J5" s="17">
-        <v>71.319466062871072</v>
+        <v>71.113947469750883</v>
       </c>
       <c r="K5" s="17">
-        <v>39.614661310623802</v>
+        <v>0.15091214122040969</v>
       </c>
       <c r="L5" s="17">
-        <v>354.02365994803995</v>
+        <v>1.3486539275578022</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -4906,34 +4981,34 @@
         <v>0.75</v>
       </c>
       <c r="C6" s="17">
-        <v>146.89827318466655</v>
+        <v>0.14689827318466656</v>
       </c>
       <c r="D6" s="17">
-        <v>8.1049138972325512</v>
+        <v>8.1049138972325522E-3</v>
       </c>
       <c r="E6" s="17">
         <v>54.719894700628537</v>
       </c>
       <c r="F6" s="17">
-        <v>19.765266768229527</v>
+        <v>20.262571228369076</v>
       </c>
       <c r="G6" s="17">
-        <v>52.186501352649742</v>
+        <v>53.532694818694651</v>
       </c>
       <c r="H6" s="17">
-        <v>16.050273489693183</v>
+        <v>60.150427663242837</v>
       </c>
       <c r="I6" s="17">
-        <v>15.685273418138657</v>
+        <v>59.132490246883762</v>
       </c>
       <c r="J6" s="17">
-        <v>71.526102579273243</v>
+        <v>71.317527543858375</v>
       </c>
       <c r="K6" s="17">
-        <v>39.084241310864769</v>
+        <v>0.1474116636772683</v>
       </c>
       <c r="L6" s="17">
-        <v>349.28346469174556</v>
+        <v>1.3173712703195719</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -4941,34 +5016,34 @@
         <v>0.8</v>
       </c>
       <c r="C7" s="17">
-        <v>150.92661980778519</v>
+        <v>0.15092661980778518</v>
       </c>
       <c r="D7" s="17">
-        <v>7.9300370676916589</v>
+        <v>7.9300370676916587E-3</v>
       </c>
       <c r="E7" s="17">
         <v>55.888023789679387</v>
       </c>
       <c r="F7" s="17">
-        <v>20.235891351627959</v>
+        <v>20.718482595841238</v>
       </c>
       <c r="G7" s="17">
-        <v>53.42859555121403</v>
+        <v>54.734960628953523</v>
       </c>
       <c r="H7" s="17">
-        <v>16.207600873594352</v>
+        <v>60.203698420323029</v>
       </c>
       <c r="I7" s="17">
-        <v>15.839485575111897</v>
+        <v>59.187023139449423</v>
       </c>
       <c r="J7" s="17">
-        <v>71.708294275735227</v>
+        <v>71.497000293469625</v>
       </c>
       <c r="K7" s="17">
-        <v>38.617016986964416</v>
+        <v>0.14436476998212663</v>
       </c>
       <c r="L7" s="17">
-        <v>345.10802914108001</v>
+        <v>1.290142148026473</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -4976,34 +5051,34 @@
         <v>0.85</v>
       </c>
       <c r="C8" s="17">
-        <v>154.48837379671122</v>
+        <v>0.15448837379671118</v>
       </c>
       <c r="D8" s="17">
-        <v>7.7766933290369442</v>
+        <v>7.7766933290369447E-3</v>
       </c>
       <c r="E8" s="17">
-        <v>56.904129154565318</v>
+        <v>56.904129154565311</v>
       </c>
       <c r="F8" s="17">
-        <v>20.645294276473038</v>
+        <v>21.115071451650476</v>
       </c>
       <c r="G8" s="17">
-        <v>54.509108246619817</v>
+        <v>55.780785889614293</v>
       </c>
       <c r="H8" s="17">
-        <v>16.349317243377286</v>
+        <v>60.251212163917998</v>
       </c>
       <c r="I8" s="17">
-        <v>15.978403991712717</v>
+        <v>59.235661246611436</v>
       </c>
       <c r="J8" s="17">
-        <v>71.870125868264836</v>
+        <v>71.656400152541778</v>
       </c>
       <c r="K8" s="17">
-        <v>38.202512795285671</v>
+        <v>0.14169016867382303</v>
       </c>
       <c r="L8" s="17">
-        <v>341.40373668603996</v>
+        <v>1.2662400846807105</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -5011,34 +5086,34 @@
         <v>0.9</v>
       </c>
       <c r="C9" s="17">
-        <v>157.6601720704559</v>
+        <v>0.15766017207045593</v>
       </c>
       <c r="D9" s="17">
-        <v>7.6412011923432459</v>
+        <v>7.6412011923432457E-3</v>
       </c>
       <c r="E9" s="17">
-        <v>57.795583221044943</v>
+        <v>57.795583221044957</v>
       </c>
       <c r="F9" s="17">
-        <v>21.004494873055776</v>
+        <v>21.46301763766137</v>
       </c>
       <c r="G9" s="17">
-        <v>55.457122957656523</v>
+        <v>56.698335130922949</v>
       </c>
       <c r="H9" s="17">
-        <v>16.477593217708954</v>
+        <v>60.293845462383622</v>
       </c>
       <c r="I9" s="17">
-        <v>16.104154074250307</v>
+        <v>59.279302589852165</v>
       </c>
       <c r="J9" s="17">
-        <v>72.014824656586995</v>
+        <v>71.798913319337885</v>
       </c>
       <c r="K9" s="17">
-        <v>37.832420978038627</v>
+        <v>0.13932466740652216</v>
       </c>
       <c r="L9" s="17">
-        <v>338.09634353098392</v>
+        <v>1.2451003503360174</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -5111,64 +5186,64 @@
         <v>0.6</v>
       </c>
       <c r="C16" s="17">
-        <v>17223.530390651405</v>
+        <v>17.223530390651401</v>
       </c>
       <c r="D16" s="17">
-        <v>5103.7799140514026</v>
+        <v>5.1037799140514002</v>
       </c>
       <c r="E16" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F16" s="17">
-        <v>2807.373846715212</v>
+        <v>2.8073738467151998</v>
       </c>
       <c r="G16" s="17">
-        <v>1210.8751990759354</v>
+        <v>1.2108751990759339</v>
       </c>
       <c r="H16" s="17">
-        <v>1104.7199639895116</v>
+        <v>1.1047199639898608</v>
       </c>
       <c r="I16" s="17">
-        <v>9283.7734881358447</v>
+        <v>9.283773488135834</v>
       </c>
       <c r="J16" s="17">
-        <v>103269.46782608512</v>
+        <v>103.26946782608539</v>
       </c>
       <c r="K16" s="17">
-        <v>277036.14858994889</v>
+        <v>277.03614858994956</v>
       </c>
       <c r="L16" s="17">
-        <v>120250.45822234853</v>
+        <v>120.25045822234905</v>
       </c>
       <c r="M16" s="17">
-        <v>0.2517453525309708</v>
+        <v>2.9125156004621573E-2</v>
       </c>
       <c r="N16" s="17">
-        <v>0.11458911717440511</v>
+        <v>1.3292337592230991E-2</v>
       </c>
       <c r="O16" s="17">
-        <v>12258.929861073375</v>
+        <v>12.258929861073378</v>
       </c>
       <c r="P16" s="17">
-        <v>5968.311954203029</v>
+        <v>5.9683119542030285</v>
       </c>
       <c r="Q16" s="17">
-        <v>0.98477814386777573</v>
+        <v>9.8477814386777594E-4</v>
       </c>
       <c r="R16" s="17">
-        <v>1077.6192924360903</v>
+        <v>1.0776192924360903</v>
       </c>
       <c r="S16" s="17">
-        <v>3581.036050913548</v>
+        <v>3.5350848909872137</v>
       </c>
       <c r="T16" s="17">
-        <v>692590.37147487211</v>
+        <v>692.59037147487402</v>
       </c>
       <c r="U16" s="17">
-        <v>7478.1116504062575</v>
+        <v>3.5990801600825222</v>
       </c>
       <c r="V16" s="17">
-        <v>569197.94407274295</v>
+        <v>565.31501258162234</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -5176,64 +5251,64 @@
         <v>0.65</v>
       </c>
       <c r="C17" s="17">
-        <v>13889.07170678319</v>
+        <v>13.889071706783179</v>
       </c>
       <c r="D17" s="17">
-        <v>4246.1216538053413</v>
+        <v>4.246121653805341</v>
       </c>
       <c r="E17" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F17" s="17">
-        <v>2807.373846715212</v>
+        <v>2.8073738467151998</v>
       </c>
       <c r="G17" s="17">
-        <v>1182.6470103258118</v>
+        <v>1.1826470103258144</v>
       </c>
       <c r="H17" s="17">
-        <v>1791.6358617457445</v>
+        <v>1.7916358617457444</v>
       </c>
       <c r="I17" s="17">
-        <v>9173.6007419972721</v>
+        <v>9.1736007419972747</v>
       </c>
       <c r="J17" s="17">
-        <v>104168.42351101463</v>
+        <v>104.16842351101462</v>
       </c>
       <c r="K17" s="17">
-        <v>279447.73476298235</v>
+        <v>279.44773476298229</v>
       </c>
       <c r="L17" s="17">
-        <v>121347.12487858563</v>
+        <v>121.34712487858563</v>
       </c>
       <c r="M17" s="17">
-        <v>0.25506000082520519</v>
+        <v>2.9507436703505269E-2</v>
       </c>
       <c r="N17" s="17">
-        <v>0.11686810867505278</v>
+        <v>1.3556700606306121E-2</v>
       </c>
       <c r="O17" s="17">
-        <v>11706.898845704814</v>
+        <v>11.70689884570481</v>
       </c>
       <c r="P17" s="17">
-        <v>5640.9449889946964</v>
+        <v>5.6409449889946401</v>
       </c>
       <c r="Q17" s="17">
-        <v>0.96169692888734515</v>
+        <v>9.6169692888734557E-4</v>
       </c>
       <c r="R17" s="17">
-        <v>1033.7214813554442</v>
+        <v>1.0337214813555018</v>
       </c>
       <c r="S17" s="17">
-        <v>3620.0084021298612</v>
+        <v>3.5735072492326818</v>
       </c>
       <c r="T17" s="17">
-        <v>698619.33690745581</v>
+        <v>698.61933690745582</v>
       </c>
       <c r="U17" s="17">
-        <v>7226.5680808477873</v>
+        <v>3.4801513263757968</v>
       </c>
       <c r="V17" s="17">
-        <v>568825.66610812175</v>
+        <v>565.07544040995276</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -5241,64 +5316,64 @@
         <v>0.7</v>
       </c>
       <c r="C18" s="17">
-        <v>11038.113043195457</v>
+        <v>11.038113043195452</v>
       </c>
       <c r="D18" s="17">
-        <v>3465.8458866495639</v>
+        <v>3.4658458866495603</v>
       </c>
       <c r="E18" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F18" s="17">
-        <v>2807.373846715212</v>
+        <v>2.8073738467151998</v>
       </c>
       <c r="G18" s="17">
-        <v>1158.2224463140453</v>
+        <v>1.1582224463140447</v>
       </c>
       <c r="H18" s="17">
-        <v>2430.7471421233495</v>
+        <v>2.4307471421233493</v>
       </c>
       <c r="I18" s="17">
-        <v>9066.7993777505453</v>
+        <v>9.0667993777505469</v>
       </c>
       <c r="J18" s="17">
-        <v>104959.96261811555</v>
+        <v>104.95996261811557</v>
       </c>
       <c r="K18" s="17">
-        <v>281571.15953029942</v>
+        <v>281.5711595302995</v>
       </c>
       <c r="L18" s="17">
-        <v>122313.69926104051</v>
+        <v>122.31369926104054</v>
       </c>
       <c r="M18" s="17">
-        <v>0.25794191262521177</v>
+        <v>2.9839777350717973E-2</v>
       </c>
       <c r="N18" s="17">
-        <v>0.11885920781892506</v>
+        <v>1.3787668106995304E-2</v>
       </c>
       <c r="O18" s="17">
-        <v>11242.094633094242</v>
+        <v>11.242094633094244</v>
       </c>
       <c r="P18" s="17">
-        <v>5373.4938759398001</v>
+        <v>5.3734938759397997</v>
       </c>
       <c r="Q18" s="17">
-        <v>0.94173270359819072</v>
+        <v>9.4173270359819037E-4</v>
       </c>
       <c r="R18" s="17">
-        <v>997.01597907764994</v>
+        <v>0.99701597907764994</v>
       </c>
       <c r="S18" s="17">
-        <v>3653.1722462794478</v>
+        <v>3.6061916584211962</v>
       </c>
       <c r="T18" s="17">
-        <v>703927.89882574859</v>
+        <v>703.92789882574857</v>
       </c>
       <c r="U18" s="17">
-        <v>7012.7467667503342</v>
+        <v>3.3791102132127113</v>
       </c>
       <c r="V18" s="17">
-        <v>568634.22189726471</v>
+        <v>564.99685540020596</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -5306,64 +5381,64 @@
         <v>0.75</v>
       </c>
       <c r="C19" s="17">
-        <v>8573.5098078967039</v>
+        <v>8.5735098078966985</v>
       </c>
       <c r="D19" s="17">
-        <v>2754.6230259247086</v>
+        <v>2.7546230259247095</v>
       </c>
       <c r="E19" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F19" s="17">
-        <v>2807.373846715212</v>
+        <v>2.8073738467151998</v>
       </c>
       <c r="G19" s="17">
-        <v>1136.9071821083016</v>
+        <v>1.1369071821082999</v>
       </c>
       <c r="H19" s="17">
-        <v>3023.7047411040985</v>
+        <v>3.0237047411040985</v>
       </c>
       <c r="I19" s="17">
-        <v>8965.1619450556045</v>
+        <v>8.9651619450555877</v>
       </c>
       <c r="J19" s="17">
-        <v>105662.76220008062</v>
+        <v>105.66276220008064</v>
       </c>
       <c r="K19" s="17">
-        <v>283456.52694350353</v>
+        <v>283.45652694350355</v>
       </c>
       <c r="L19" s="17">
-        <v>123172.65806338149</v>
+        <v>123.1726580633815</v>
       </c>
       <c r="M19" s="17">
-        <v>0.2604700610476795</v>
+        <v>3.0131298657467248E-2</v>
       </c>
       <c r="N19" s="17">
-        <v>0.12061319440397289</v>
+        <v>1.3991130550860853E-2</v>
       </c>
       <c r="O19" s="17">
-        <v>10845.814830466486</v>
+        <v>10.845814830466487</v>
       </c>
       <c r="P19" s="17">
-        <v>5151.2288603062889</v>
+        <v>5.1512288603062899</v>
       </c>
       <c r="Q19" s="17">
-        <v>0.92431500080570184</v>
+        <v>9.2431500080570217E-4</v>
       </c>
       <c r="R19" s="17">
-        <v>965.89147864161771</v>
+        <v>0.96589147864161762</v>
       </c>
       <c r="S19" s="17">
-        <v>3681.7827674106129</v>
+        <v>3.6343805860073322</v>
       </c>
       <c r="T19" s="17">
-        <v>708641.31735875877</v>
+        <v>708.64131735875878</v>
       </c>
       <c r="U19" s="17">
-        <v>6828.9193675282904</v>
+        <v>3.29227958568387</v>
       </c>
       <c r="V19" s="17">
-        <v>568570.62716847542</v>
+        <v>565.03032655118056</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -5371,64 +5446,64 @@
         <v>0.8</v>
       </c>
       <c r="C20" s="17">
-        <v>6422.209445343934</v>
+        <v>6.4222094453439347</v>
       </c>
       <c r="D20" s="17">
-        <v>2104.9796883973145</v>
+        <v>2.104979688397314</v>
       </c>
       <c r="E20" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F20" s="17">
-        <v>2807.373846715212</v>
+        <v>2.8073738467151998</v>
       </c>
       <c r="G20" s="17">
-        <v>1118.1613002894633</v>
+        <v>1.1181613002894637</v>
       </c>
       <c r="H20" s="17">
-        <v>3573.3140356715885</v>
+        <v>3.5733140356715887</v>
       </c>
       <c r="I20" s="17">
-        <v>8869.4633253153861</v>
+        <v>8.8694633253153885</v>
       </c>
       <c r="J20" s="17">
-        <v>106291.27448128449</v>
+        <v>106.29127448128449</v>
       </c>
       <c r="K20" s="17">
-        <v>285142.60730579839</v>
+        <v>285.14260730579838</v>
       </c>
       <c r="L20" s="17">
-        <v>123941.42024869514</v>
+        <v>123.94142024869507</v>
       </c>
       <c r="M20" s="17">
-        <v>0.26270550768952727</v>
+        <v>3.0389051278727968E-2</v>
       </c>
       <c r="N20" s="17">
-        <v>0.12216974083650543</v>
+        <v>1.417168993703463E-2</v>
       </c>
       <c r="O20" s="17">
-        <v>10504.258527002828</v>
+        <v>10.504258527002829</v>
       </c>
       <c r="P20" s="17">
-        <v>4963.8129009404247</v>
+        <v>4.9638129009404244</v>
       </c>
       <c r="Q20" s="17">
-        <v>0.90900061105456553</v>
+        <v>9.0900061105456586E-4</v>
       </c>
       <c r="R20" s="17">
-        <v>939.18089232948137</v>
+        <v>0.93918089232948121</v>
       </c>
       <c r="S20" s="17">
-        <v>3706.7615776450862</v>
+        <v>3.6589857819692497</v>
       </c>
       <c r="T20" s="17">
-        <v>712856.518264496</v>
+        <v>712.85651826449589</v>
       </c>
       <c r="U20" s="17">
-        <v>6669.3060430568084</v>
+        <v>3.2169127715262071</v>
       </c>
       <c r="V20" s="17">
-        <v>568597.87420444074</v>
+        <v>565.14188100320121</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -5436,64 +5511,64 @@
         <v>0.85</v>
       </c>
       <c r="C21" s="17">
-        <v>4528.3030015852082</v>
+        <v>4.528303001585213</v>
       </c>
       <c r="D21" s="17">
-        <v>1510.2579346330949</v>
+        <v>1.5102579346330967</v>
       </c>
       <c r="E21" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F21" s="17">
-        <v>2807.373846715212</v>
+        <v>2.8073738467151998</v>
       </c>
       <c r="G21" s="17">
-        <v>1101.5597781977049</v>
+        <v>1.1015597781977049</v>
       </c>
       <c r="H21" s="17">
-        <v>4082.8254225992714</v>
+        <v>4.0828254225992717</v>
       </c>
       <c r="I21" s="17">
-        <v>8779.9064915337567</v>
+        <v>8.7799064915337652</v>
       </c>
       <c r="J21" s="17">
-        <v>106856.89298365323</v>
+        <v>106.85689298365322</v>
       </c>
       <c r="K21" s="17">
-        <v>286659.96548306081</v>
+        <v>286.65996548306083</v>
       </c>
       <c r="L21" s="17">
-        <v>124633.73733801451</v>
+        <v>124.63373733801447</v>
       </c>
       <c r="M21" s="17">
-        <v>0.26469613987200663</v>
+        <v>3.0618563448657987E-2</v>
       </c>
       <c r="N21" s="17">
-        <v>0.12356023428108251</v>
+        <v>1.4332987176605571E-2</v>
       </c>
       <c r="O21" s="17">
-        <v>10207.040222168094</v>
+        <v>10.207040222168093</v>
       </c>
       <c r="P21" s="17">
-        <v>4803.7955825387162</v>
+        <v>4.803795582538716</v>
       </c>
       <c r="Q21" s="17">
-        <v>0.89544089482254818</v>
+        <v>8.9544089482254826E-4</v>
       </c>
       <c r="R21" s="17">
-        <v>916.01886380869257</v>
+        <v>0.91601886380869246</v>
       </c>
       <c r="S21" s="17">
-        <v>3728.7978136515972</v>
+        <v>3.6806886285269229</v>
       </c>
       <c r="T21" s="17">
-        <v>716649.91370765201</v>
+        <v>716.64991370765188</v>
       </c>
       <c r="U21" s="17">
-        <v>6529.5033613763208</v>
+        <v>3.1509193724350624</v>
       </c>
       <c r="V21" s="17">
-        <v>568689.71853090066</v>
+        <v>565.30758865108601</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -5501,64 +5576,64 @@
         <v>0.9</v>
       </c>
       <c r="C22" s="17">
-        <v>2848.3263976414578</v>
+        <v>2.8483263976414599</v>
       </c>
       <c r="D22" s="17">
-        <v>964.55767849983272</v>
+        <v>0.96455767849983387</v>
       </c>
       <c r="E22" s="17">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F22" s="17">
-        <v>2807.373846715212</v>
+        <v>2.8073738467151998</v>
       </c>
       <c r="G22" s="17">
-        <v>1086.7646432466843</v>
+        <v>1.0867646432466844</v>
       </c>
       <c r="H22" s="17">
-        <v>4555.56180201401</v>
+        <v>4.5555618020140098</v>
       </c>
       <c r="I22" s="17">
-        <v>8696.3788936835081</v>
+        <v>8.6963788936835122</v>
       </c>
       <c r="J22" s="17">
-        <v>107368.74274104465</v>
+        <v>107.36874274104464</v>
       </c>
       <c r="K22" s="17">
-        <v>288033.08077482571</v>
+        <v>288.03308077482569</v>
       </c>
       <c r="L22" s="17">
-        <v>125260.63692308396</v>
+        <v>125.26063692308392</v>
       </c>
       <c r="M22" s="17">
-        <v>0.2664800015417999</v>
+        <v>3.0824226425290625E-2</v>
       </c>
       <c r="N22" s="17">
-        <v>0.12480980050803024</v>
+        <v>1.4477936858931504E-2</v>
       </c>
       <c r="O22" s="17">
-        <v>9946.2077370741645</v>
+        <v>9.9462077370741646</v>
       </c>
       <c r="P22" s="17">
-        <v>4665.6811406944789</v>
+        <v>4.6656811406944776</v>
       </c>
       <c r="Q22" s="17">
-        <v>0.88335841987004737</v>
+        <v>8.8335841987004747E-4</v>
       </c>
       <c r="R22" s="17">
-        <v>895.75064737944081</v>
+        <v>0.89575064737944088</v>
       </c>
       <c r="S22" s="17">
-        <v>3748.4156267159824</v>
+        <v>3.7000071016729259</v>
       </c>
       <c r="T22" s="17">
-        <v>720082.70193706418</v>
+        <v>720.08270193706414</v>
       </c>
       <c r="U22" s="17">
-        <v>6406.1012876481363</v>
+        <v>3.0926819958197846</v>
       </c>
       <c r="V22" s="17">
-        <v>568827.31149858458</v>
+        <v>565.51039455519515</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -5589,22 +5664,22 @@
         <v>0.6</v>
       </c>
       <c r="C29" s="17">
-        <v>0.82183923934812309</v>
+        <v>0.81623284969697418</v>
       </c>
       <c r="D29" s="17">
-        <v>4.6131369673230234</v>
+        <v>4.4425025448020206</v>
       </c>
       <c r="E29" s="17">
-        <v>0.21677223266585433</v>
+        <v>0.22509835164192682</v>
       </c>
       <c r="F29" s="17">
-        <v>1.1717456361388412E-2</v>
+        <v>1.0904297235548702E-2</v>
       </c>
       <c r="G29" s="17">
-        <v>0.68802577316769886</v>
+        <v>0.64345652148042443</v>
       </c>
       <c r="H29" s="17">
-        <v>17.81607606518768</v>
+        <v>18.376715030302581</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -5612,22 +5687,22 @@
         <v>0.65</v>
       </c>
       <c r="C30" s="17">
-        <v>0.81421403052786179</v>
+        <v>0.80884597742648334</v>
       </c>
       <c r="D30" s="17">
-        <v>4.3827408373849428</v>
+        <v>4.232117763206567</v>
       </c>
       <c r="E30" s="17">
-        <v>0.22816772360116819</v>
+        <v>0.23628832087184778</v>
       </c>
       <c r="F30" s="17">
-        <v>1.1681244010233967E-2</v>
+        <v>1.0918775274592729E-2</v>
       </c>
       <c r="G30" s="17">
-        <v>0.6860409742009238</v>
+        <v>0.64425006280042751</v>
       </c>
       <c r="H30" s="17">
-        <v>18.578596947213832</v>
+        <v>19.115402257351665</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -5635,22 +5710,22 @@
         <v>0.7</v>
       </c>
       <c r="C31" s="17">
-        <v>0.80780179737985547</v>
+        <v>0.80263455439498943</v>
       </c>
       <c r="D31" s="17">
-        <v>4.2031462868258735</v>
+        <v>4.0674035992439865</v>
       </c>
       <c r="E31" s="17">
-        <v>0.23791701067706084</v>
+        <v>0.24585708686147381</v>
       </c>
       <c r="F31" s="17">
-        <v>1.1653403544510034E-2</v>
+        <v>1.0931116707946399E-2</v>
       </c>
       <c r="G31" s="17">
-        <v>0.68451503827459503</v>
+        <v>0.6449264967625421</v>
       </c>
       <c r="H31" s="17">
-        <v>19.219820262014466</v>
+        <v>19.736544560501045</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -5658,22 +5733,22 @@
         <v>0.75</v>
       </c>
       <c r="C32" s="17">
-        <v>0.8023390864191301</v>
+        <v>0.79734318718128983</v>
       </c>
       <c r="D32" s="17">
-        <v>4.0593385145137582</v>
+        <v>3.9350543334053838</v>
       </c>
       <c r="E32" s="17">
-        <v>0.24634555517471632</v>
+        <v>0.25412609719536022</v>
       </c>
       <c r="F32" s="17">
-        <v>1.1631437078375764E-2</v>
+        <v>1.0944911564070405E-2</v>
       </c>
       <c r="G32" s="17">
-        <v>0.6833110562657756</v>
+        <v>0.64568259282669893</v>
       </c>
       <c r="H32" s="17">
-        <v>19.766091358086978</v>
+        <v>20.265681281871029</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
@@ -5681,22 +5756,22 @@
         <v>0.8</v>
       </c>
       <c r="C33" s="17">
-        <v>0.7976329873348651</v>
+        <v>0.79278489643200944</v>
       </c>
       <c r="D33" s="17">
-        <v>3.9416745893464</v>
+        <v>3.8264621589186407</v>
       </c>
       <c r="E33" s="17">
-        <v>0.25369927865248204</v>
+        <v>0.26133800844448968</v>
       </c>
       <c r="F33" s="17">
-        <v>1.1613742892744807E-2</v>
+        <v>1.0954575512681711E-2</v>
       </c>
       <c r="G33" s="17">
-        <v>0.68234123795134294</v>
+        <v>0.64621227385008462</v>
       </c>
       <c r="H33" s="17">
-        <v>20.236701266513492</v>
+        <v>20.721510356799055</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
@@ -5704,22 +5779,22 @@
         <v>0.85</v>
       </c>
       <c r="C34" s="17">
-        <v>0.79353908743075674</v>
+        <v>0.7888197261148292</v>
       </c>
       <c r="D34" s="17">
-        <v>3.8436801956127011</v>
+        <v>3.7358136718650345</v>
       </c>
       <c r="E34" s="17">
-        <v>0.26016732639240692</v>
+        <v>0.26767930304745868</v>
       </c>
       <c r="F34" s="17">
-        <v>1.1599271059708104E-2</v>
+        <v>1.0963902842859219E-2</v>
       </c>
       <c r="G34" s="17">
-        <v>0.68154803678260123</v>
+        <v>0.64672350481711383</v>
       </c>
       <c r="H34" s="17">
-        <v>20.646091256924336</v>
+        <v>21.118027388517071</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
@@ -5727,22 +5802,22 @@
         <v>0.9</v>
       </c>
       <c r="C35" s="17">
-        <v>0.78994719629898924</v>
+        <v>0.78534089630807602</v>
       </c>
       <c r="D35" s="17">
-        <v>3.7608483378113542</v>
+        <v>3.6590423097357503</v>
       </c>
       <c r="E35" s="17">
-        <v>0.26589745455727559</v>
+        <v>0.27329555532584654</v>
       </c>
       <c r="F35" s="17">
-        <v>1.1587241111668242E-2</v>
+        <v>1.0972643120066438E-2</v>
       </c>
       <c r="G35" s="17">
-        <v>0.68088867533053643</v>
+        <v>0.64720255941084148</v>
       </c>
       <c r="H35" s="17">
-        <v>21.005280370101076</v>
+        <v>21.465910369192386</v>
       </c>
     </row>
   </sheetData>
@@ -5809,26 +5884,26 @@
         <v>1</v>
       </c>
       <c r="C3" s="4">
-        <v>1173.1500000000001</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D3" s="5">
         <v>25</v>
       </c>
       <c r="E3" s="4">
-        <v>1480.0123118353019</v>
+        <v>1350.0381316636626</v>
       </c>
       <c r="F3" s="7">
-        <v>3.1463579096737231</v>
+        <v>3.0305681085599816</v>
       </c>
       <c r="G3" s="4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H3" s="4">
-        <v>852.0638237103999</v>
+        <v>756.61237274082237</v>
       </c>
       <c r="I3" s="4">
         <f>C3-273.15</f>
-        <v>900.00000000000011</v>
+        <v>800.00000000000011</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>40</v>
@@ -5854,44 +5929,44 @@
         <v>2</v>
       </c>
       <c r="C4" s="4">
-        <v>1114.5692189136419</v>
+        <v>1018.1871360117831</v>
       </c>
       <c r="D4" s="5">
         <v>17.482517482517483</v>
       </c>
       <c r="E4" s="4">
-        <v>1404.7163794364055</v>
+        <v>1281.3081492359206</v>
       </c>
       <c r="F4" s="7">
-        <v>3.1515313348291665</v>
+        <v>3.0357375517463359</v>
       </c>
       <c r="G4" s="4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H4" s="4">
-        <v>775.22543460140798</v>
+        <v>686.34112082706883</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" ref="I4:I42" si="0">C4-273.15</f>
-        <v>841.41921891364188</v>
+        <v>745.0371360117831</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>42</v>
       </c>
       <c r="L4" s="7">
-        <v>197.01139918140578</v>
+        <v>0.1796736963027683</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>66</v>
       </c>
       <c r="O4" s="10">
-        <v>75295.932398896432</v>
+        <v>68.729982427742101</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>98</v>
       </c>
       <c r="R4" s="6">
-        <v>15996.693529577993</v>
+        <v>336.14916869494635</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
@@ -5899,44 +5974,44 @@
         <v>3</v>
       </c>
       <c r="C5" s="4">
-        <v>1173.1500000000001</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D5" s="5">
         <v>17.482517482517483</v>
       </c>
       <c r="E5" s="4">
-        <v>1480.4942892017907</v>
+        <v>1351.4823193165744</v>
       </c>
       <c r="F5" s="7">
-        <v>3.2177913111550378</v>
+        <v>3.1028601038812176</v>
       </c>
       <c r="G5" s="4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H5" s="4">
-        <v>831.24793242523447</v>
+        <v>736.50270198870771</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="0"/>
-        <v>900.00000000000011</v>
+        <v>800.00000000000011</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>43</v>
       </c>
       <c r="L5" s="7">
-        <v>75.77790976538509</v>
+        <v>7.0174170080653853E-2</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>67</v>
       </c>
       <c r="O5" s="10">
-        <v>131294.66508372221</v>
+        <v>119.78456764170598</v>
       </c>
       <c r="Q5" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R5" s="6">
-        <v>17275.788325127607</v>
+        <v>285.89368248336706</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
@@ -5944,44 +6019,44 @@
         <v>4</v>
       </c>
       <c r="C6" s="4">
-        <v>1069.6344049057263</v>
+        <v>976.21764828798996</v>
       </c>
       <c r="D6" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E6" s="4">
-        <v>1349.1996241180684</v>
+        <v>1231.6977516748684</v>
       </c>
       <c r="F6" s="7">
-        <v>3.227207289175213</v>
+        <v>3.112273260172465</v>
       </c>
       <c r="G6" s="4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H6" s="4">
-        <v>697.14589349479706</v>
+        <v>613.91160179876624</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="0"/>
-        <v>796.48440490572636</v>
+        <v>703.06764828798998</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>47</v>
       </c>
       <c r="L6" s="7">
-        <v>272.78930894679087</v>
+        <v>0.24984786638342216</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>68</v>
       </c>
       <c r="O6" s="10">
-        <v>7647.3866633769367</v>
+        <v>7.1779640670783724</v>
       </c>
       <c r="Q6" s="13" t="s">
         <v>100</v>
       </c>
       <c r="R6" s="6">
-        <v>476246.11519307818</v>
+        <v>1688.3683157601977</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -5989,44 +6064,44 @@
         <v>5</v>
       </c>
       <c r="C7" s="4">
-        <v>592.37305460286814</v>
+        <v>580.60739984606084</v>
       </c>
       <c r="D7" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E7" s="4">
-        <v>772.2645689933064</v>
+        <v>758.77316593152807</v>
       </c>
       <c r="F7" s="7">
-        <v>2.5164974849797748</v>
+        <v>2.493493145865219</v>
       </c>
       <c r="G7" s="4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H7" s="4">
-        <v>332.10896649090478</v>
+        <v>325.47630713613137</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="0"/>
-        <v>319.22305460286816</v>
+        <v>307.45739984606087</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>44</v>
       </c>
       <c r="L7" s="7">
-        <v>591.7282511386129</v>
+        <v>0.4850508570994323</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>69</v>
       </c>
       <c r="O7" s="10">
-        <v>-38822.704532947573</v>
+        <v>-38.640801901504481</v>
       </c>
       <c r="Q7" s="13" t="s">
         <v>105</v>
       </c>
       <c r="R7" s="6">
-        <v>92272.151831478855</v>
+        <v>884.52935792049959</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
@@ -6034,44 +6109,44 @@
         <v>6</v>
       </c>
       <c r="C8" s="4">
-        <v>440.06898750789043</v>
+        <v>435.4382571755965</v>
       </c>
       <c r="D8" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E8" s="4">
-        <v>596.73677012773305</v>
+        <v>591.20237940579909</v>
       </c>
       <c r="F8" s="7">
-        <v>2.1736996704556586</v>
+        <v>2.1610567826542426</v>
       </c>
       <c r="G8" s="4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H8" s="4">
-        <v>258.78633602569676</v>
+        <v>257.02142230175508</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="0"/>
-        <v>166.91898750789045</v>
+        <v>162.28825717559653</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>45</v>
       </c>
       <c r="L8" s="7">
-        <v>175.52779886557337</v>
+        <v>0.16757078652572899</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>70</v>
       </c>
       <c r="O8" s="10">
-        <v>-17748.922071558391</v>
+        <v>-18.872729900081151</v>
       </c>
       <c r="Q8" s="13" t="s">
         <v>104</v>
       </c>
       <c r="R8" s="6">
-        <v>33.890151114468985</v>
+        <v>259.69048700602229</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
@@ -6079,44 +6154,44 @@
         <v>29</v>
       </c>
       <c r="C9" s="4">
-        <v>440.06898750789043</v>
+        <v>435.4382571755965</v>
       </c>
       <c r="D9" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E9" s="4">
-        <v>596.73677012773305</v>
+        <v>591.20237940579909</v>
       </c>
       <c r="F9" s="7">
-        <v>2.1736996704556586</v>
+        <v>2.1610567826542426</v>
       </c>
       <c r="G9" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H9" s="4">
-        <v>258.78633602569676</v>
+        <v>257.02142230175508</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" si="0"/>
-        <v>166.91898750789045</v>
+        <v>162.28825717559653</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>48</v>
       </c>
       <c r="L9" s="7">
-        <v>11.61019553224269</v>
+        <v>1.103370874887479E-2</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>71</v>
       </c>
       <c r="O9" s="10">
-        <v>-6.1854710336906438</v>
+        <v>-5.87834077994729E-3</v>
       </c>
       <c r="Q9" s="13" t="s">
         <v>101</v>
       </c>
       <c r="R9" s="6">
-        <v>8302555.2567487583</v>
+        <v>-6.7709153400709399</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
@@ -6124,44 +6199,44 @@
         <v>30</v>
       </c>
       <c r="C10" s="4">
-        <v>426.20393967688454</v>
+        <v>423.35913575479753</v>
       </c>
       <c r="D10" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E10" s="4">
-        <v>0.58006351274370938</v>
+        <v>0.57660060448894723</v>
       </c>
       <c r="F10" s="7">
-        <v>2.1352002142002785E-3</v>
+        <v>2.1270479527453361E-3</v>
       </c>
       <c r="G10" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H10" s="4">
-        <v>0.25360552089977978</v>
+        <v>0.25257320939780875</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="0"/>
-        <v>153.05393967688457</v>
+        <v>150.20913575479756</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="7">
-        <v>72.258647661746068</v>
+        <v>6.8670753276560997E-2</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>72</v>
       </c>
       <c r="O10" s="10">
-        <v>150018.97087811268</v>
+        <v>131.00101826786243</v>
       </c>
       <c r="Q10" s="13" t="s">
         <v>102</v>
       </c>
       <c r="R10" s="6">
-        <v>6383031.9588786885</v>
+        <v>5826.4193083540094</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
@@ -6181,7 +6256,7 @@
         <v>1.8961819516546078E-3</v>
       </c>
       <c r="G11" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H11" s="4">
         <v>0.23185738014859708</v>
@@ -6194,19 +6269,19 @@
         <v>50</v>
       </c>
       <c r="L11" s="7">
-        <v>14.52880688025372</v>
+        <v>1.2546499075118688E-2</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="O11" s="10">
-        <v>7641.2011923432465</v>
+        <v>7.1720857262984259</v>
       </c>
       <c r="Q11" s="13" t="s">
         <v>103</v>
       </c>
       <c r="R11" s="6">
-        <v>11130190.125276349</v>
+        <v>10154.449238863286</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
@@ -6214,44 +6289,44 @@
         <v>32</v>
       </c>
       <c r="C12" s="4">
-        <v>346.16670523637293</v>
+        <v>346.62379557580101</v>
       </c>
       <c r="D12" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E12" s="4">
-        <v>0.46798922255412118</v>
+        <v>0.46883049635692192</v>
       </c>
       <c r="F12" s="7">
-        <v>1.8419575395601402E-3</v>
+        <v>1.8443861945514714E-3</v>
       </c>
       <c r="G12" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H12" s="4">
-        <v>0.22896153415414877</v>
+        <v>0.22907870447128417</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" si="0"/>
-        <v>73.016705236372957</v>
+        <v>73.473795575801034</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L12" s="7">
-        <v>98.397650074242492</v>
+        <v>9.2250961100554474E-2</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>74</v>
       </c>
       <c r="O12" s="12">
-        <v>157660.17207045591</v>
+        <v>138.17310399416087</v>
       </c>
       <c r="Q12" s="13" t="s">
         <v>106</v>
       </c>
       <c r="R12" s="6">
-        <v>648288.85065978777</v>
+        <v>608.49467667280817</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
@@ -6259,38 +6334,38 @@
         <v>33</v>
       </c>
       <c r="C13" s="4">
-        <v>346.16482465658697</v>
+        <v>328.10044857875562</v>
       </c>
       <c r="D13" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E13" s="4">
-        <v>467.9857494877009</v>
+        <v>427.23019535530364</v>
       </c>
       <c r="F13" s="7">
-        <v>1.8419475065836266</v>
+        <v>1.7207811154245041</v>
       </c>
       <c r="G13" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H13" s="4">
-        <v>228.96105241967604</v>
+        <v>224.33125781137119</v>
       </c>
       <c r="I13" s="4">
         <f t="shared" si="0"/>
-        <v>73.014824656586995</v>
+        <v>54.95044857875564</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>52</v>
       </c>
       <c r="L13" s="7">
-        <v>76.087465131828566</v>
+        <v>7.2309456578341938E-2</v>
       </c>
       <c r="Q13" s="13" t="s">
         <v>107</v>
       </c>
       <c r="R13" s="6">
-        <v>-1475969.3454745074</v>
+        <v>-1469.0537348517778</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
@@ -6298,32 +6373,32 @@
         <v>34</v>
       </c>
       <c r="C14" s="4">
-        <v>440.06898750789043</v>
+        <v>435.4382571755965</v>
       </c>
       <c r="D14" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E14" s="4">
-        <v>596.73677012773305</v>
+        <v>591.20237940579909</v>
       </c>
       <c r="F14" s="7">
-        <v>2.1736996704556586</v>
+        <v>2.1610567826542426</v>
       </c>
       <c r="G14" s="4">
-        <v>187.74797280166001</v>
+        <v>0.20053649165005705</v>
       </c>
       <c r="H14" s="4">
-        <v>258.78633602569676</v>
+        <v>257.02142230175508</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="0"/>
-        <v>166.91898750789045</v>
+        <v>162.28825717559653</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>54</v>
       </c>
       <c r="L14" s="7">
-        <v>14.668983750070673</v>
+        <v>1.2769418795914119E-2</v>
       </c>
       <c r="N14" s="31" t="s">
         <v>75</v>
@@ -6333,7 +6408,7 @@
         <v>108</v>
       </c>
       <c r="R14" s="6">
-        <v>-674782.06910092139</v>
+        <v>-717.50721988726536</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
@@ -6353,7 +6428,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G15" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H15" s="4">
         <v>224.33075530171814</v>
@@ -6366,19 +6441,19 @@
         <v>53</v>
       </c>
       <c r="L15" s="7">
-        <v>90.756448881899232</v>
+        <v>8.5078875374256055E-2</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="O15" s="10">
-        <v>7.7656338200941244</v>
+        <v>7.7745376749850656</v>
       </c>
       <c r="Q15" s="13" t="s">
         <v>109</v>
       </c>
       <c r="R15" s="6">
-        <v>-235.16047485305765</v>
+        <v>-0.22348393544019207</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
@@ -6386,44 +6461,44 @@
         <v>8</v>
       </c>
       <c r="C16" s="4">
-        <v>407.64113086711654</v>
+        <v>407.92598052767181</v>
       </c>
       <c r="D16" s="5">
         <v>25</v>
       </c>
       <c r="E16" s="4">
-        <v>475.17249490805983</v>
+        <v>475.70953285771714</v>
       </c>
       <c r="F16" s="7">
-        <v>1.7329873803681137</v>
+        <v>1.7343043486568708</v>
       </c>
       <c r="G16" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H16" s="4">
-        <v>268.62043009562507</v>
+        <v>268.76481394998945</v>
       </c>
       <c r="I16" s="4">
         <f t="shared" si="0"/>
-        <v>134.49113086711657</v>
+        <v>134.77598052767183</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>46</v>
       </c>
       <c r="L16" s="7">
-        <v>2.8210052404935883E-3</v>
+        <v>3.3257922587167379E-2</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>81</v>
       </c>
       <c r="O16" s="10">
-        <v>54.994446614245696</v>
+        <v>52.432314177470431</v>
       </c>
       <c r="Q16" s="13" t="s">
         <v>110</v>
       </c>
       <c r="R16" s="6">
-        <v>1591444.5174733943</v>
+        <v>1493.7562417078809</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
@@ -6431,44 +6506,44 @@
         <v>9</v>
       </c>
       <c r="C17" s="4">
-        <v>552.25174153326532</v>
+        <v>547.69370647629023</v>
       </c>
       <c r="D17" s="5">
         <v>25</v>
       </c>
       <c r="E17" s="4">
-        <v>691.27266208278832</v>
+        <v>685.31357954095802</v>
       </c>
       <c r="F17" s="7">
-        <v>2.1909309739824532</v>
+        <v>2.180095650521598</v>
       </c>
       <c r="G17" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H17" s="4">
-        <v>348.18471483423826</v>
+        <v>345.4561839822619</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" si="0"/>
-        <v>279.10174153326534</v>
+        <v>274.54370647629025</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>55</v>
       </c>
       <c r="L17" s="16">
-        <v>-32.985255990966728</v>
+        <v>1.1666246047954387E-4</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>82</v>
       </c>
       <c r="O17" s="10">
-        <v>16.477593217708954</v>
+        <v>59.052048428258885</v>
       </c>
       <c r="Q17" s="13" t="s">
         <v>111</v>
       </c>
       <c r="R17" s="6">
-        <v>1331025.8266823676</v>
+        <v>1214.5651249638913</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
@@ -6476,38 +6551,38 @@
         <v>10</v>
       </c>
       <c r="C18" s="4">
-        <v>552.25174153326532</v>
+        <v>547.69370647629023</v>
       </c>
       <c r="D18" s="5">
         <v>25</v>
       </c>
       <c r="E18" s="4">
-        <v>691.27266208278832</v>
+        <v>685.31357954095802</v>
       </c>
       <c r="F18" s="7">
-        <v>2.1909309739824532</v>
+        <v>2.180095650521598</v>
       </c>
       <c r="G18" s="4">
-        <v>187.74797280166001</v>
+        <v>0.20053649165005705</v>
       </c>
       <c r="H18" s="4">
-        <v>348.18471483423826</v>
+        <v>345.4561839822619</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" si="0"/>
-        <v>279.10174153326534</v>
+        <v>274.54370647629025</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>83</v>
       </c>
       <c r="O18" s="10">
-        <v>55.457122957656523</v>
+        <v>54.1277629959406</v>
       </c>
       <c r="Q18" s="13" t="s">
         <v>112</v>
       </c>
       <c r="R18" s="6">
-        <v>244216595.38173544</v>
+        <v>392226.85885319277</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
@@ -6515,26 +6590,26 @@
         <v>11</v>
       </c>
       <c r="C19" s="4">
-        <v>552.25174153326532</v>
+        <v>547.69370647629023</v>
       </c>
       <c r="D19" s="5">
         <v>25</v>
       </c>
       <c r="E19" s="4">
-        <v>691.27266208278832</v>
+        <v>685.31357954095802</v>
       </c>
       <c r="F19" s="7">
-        <v>2.1909309739824532</v>
+        <v>2.180095650521598</v>
       </c>
       <c r="G19" s="4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H19" s="4">
-        <v>348.18471483423826</v>
+        <v>345.4561839822619</v>
       </c>
       <c r="I19" s="4">
         <f t="shared" si="0"/>
-        <v>279.10174153326534</v>
+        <v>274.54370647629025</v>
       </c>
       <c r="K19" s="31" t="s">
         <v>58</v>
@@ -6544,13 +6619,13 @@
         <v>84</v>
       </c>
       <c r="O19" s="10">
-        <v>57.795583221044943</v>
+        <v>55.302895315550657</v>
       </c>
       <c r="Q19" s="13" t="s">
         <v>123</v>
       </c>
       <c r="R19" s="6">
-        <v>291669711.90011054</v>
+        <v>444289.70597502514</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
@@ -6558,38 +6633,38 @@
         <v>12</v>
       </c>
       <c r="C20" s="4">
-        <v>1021.1165618252154</v>
+        <v>932.93660164805499</v>
       </c>
       <c r="D20" s="5">
         <v>25</v>
       </c>
       <c r="E20" s="4">
-        <v>1283.0009126538962</v>
+        <v>1170.3644353608943</v>
       </c>
       <c r="F20" s="7">
-        <v>2.9665368279795343</v>
+        <v>2.8511829889834948</v>
       </c>
       <c r="G20" s="4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H20" s="4">
-        <v>708.66608003611657</v>
+        <v>630.42234983978369</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" si="0"/>
-        <v>747.96656182521542</v>
+        <v>659.78660164805501</v>
       </c>
       <c r="K20" s="13" t="s">
         <v>59</v>
       </c>
       <c r="L20" s="4">
-        <v>11055.95030163149</v>
+        <v>39.195104368098185</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>85</v>
       </c>
       <c r="O20" s="10">
-        <v>3.6384289766431053</v>
+        <v>3.4935322440475982</v>
       </c>
       <c r="Q20" s="30" t="s">
         <v>117</v>
@@ -6617,7 +6692,7 @@
         <v>-0.37994748587359245</v>
       </c>
       <c r="G21" s="4">
-        <v>188.33289059090924</v>
+        <v>0.1789815043892197</v>
       </c>
       <c r="H21" s="4">
         <v>0.52460446529691762</v>
@@ -6630,13 +6705,13 @@
         <v>60</v>
       </c>
       <c r="L21" s="4">
-        <v>2142.0779977592824</v>
+        <v>20.534157255095636</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>86</v>
       </c>
       <c r="O21" s="10">
-        <v>20.833575153875099</v>
+        <v>22.472364524327521</v>
       </c>
       <c r="Q21" s="22" t="s">
         <v>118</v>
@@ -6668,7 +6743,7 @@
         <v>-0.37993175416231956</v>
       </c>
       <c r="G22" s="4">
-        <v>188.33289059090924</v>
+        <v>0.1789815043892197</v>
       </c>
       <c r="H22" s="4">
         <v>0.55275734181882941</v>
@@ -6681,19 +6756,19 @@
         <v>61</v>
       </c>
       <c r="L22" s="4">
-        <v>371.35977178888459</v>
+        <v>7.8036300653483694</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>87</v>
       </c>
       <c r="O22" s="6">
-        <v>16.104154074250307</v>
+        <v>57.594979992439178</v>
       </c>
       <c r="Q22" s="23" t="s">
         <v>113</v>
       </c>
       <c r="R22" s="24">
-        <v>259477.5692442265</v>
+        <v>240.46390970622548</v>
       </c>
       <c r="S22" s="23" t="s">
         <v>129</v>
@@ -6719,7 +6794,7 @@
         <v>-0.19317568283781225</v>
       </c>
       <c r="G23" s="4">
-        <v>188.33289059090924</v>
+        <v>0.1789815043892197</v>
       </c>
       <c r="H23" s="4">
         <v>6.518635522826691</v>
@@ -6732,19 +6807,19 @@
         <v>62</v>
       </c>
       <c r="L23" s="4">
-        <v>401.05368012646488</v>
+        <v>6.6369598496463702</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>88</v>
       </c>
       <c r="O23" s="6">
-        <v>21.004494873055776</v>
+        <v>23.18096972790984</v>
       </c>
       <c r="Q23" s="23" t="s">
         <v>114</v>
       </c>
       <c r="R23" s="24">
-        <v>492608866.3924107</v>
+        <v>768240.42493118276</v>
       </c>
       <c r="S23" s="23" t="s">
         <v>128</v>
@@ -6770,7 +6845,7 @@
         <v>0.91173151933586583</v>
       </c>
       <c r="G24" s="4">
-        <v>188.33289059090924</v>
+        <v>0.1789815043892197</v>
       </c>
       <c r="H24" s="4">
         <v>60.765690527522125</v>
@@ -6783,25 +6858,25 @@
         <v>63</v>
       </c>
       <c r="L24" s="4">
-        <v>0.7867525098539554</v>
+        <v>6.0286583481758358</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>89</v>
       </c>
       <c r="O24" s="15">
-        <v>21.005280370101076</v>
+        <v>23.18422680226918</v>
       </c>
       <c r="Q24" s="23" t="s">
         <v>115</v>
       </c>
       <c r="R24" s="24">
-        <v>23402221.401515387</v>
+        <v>36531.589113909038</v>
       </c>
       <c r="S24" s="23" t="s">
         <v>127</v>
       </c>
       <c r="T24" s="27">
-        <v>291669711.90011054</v>
+        <v>444289.70597502514</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6813,38 +6888,38 @@
         <v>15</v>
       </c>
       <c r="C25" s="4">
-        <v>401.06898750789043</v>
+        <v>396.4382571755965</v>
       </c>
       <c r="D25" s="5">
         <v>31.569242975234697</v>
       </c>
       <c r="E25" s="4">
-        <v>390.14483095234505</v>
+        <v>383.09995906623425</v>
       </c>
       <c r="F25" s="7">
-        <v>1.1179345894579515</v>
+        <v>1.100267344850671</v>
       </c>
       <c r="G25" s="4">
-        <v>188.33289059090924</v>
+        <v>0.1789815043892197</v>
       </c>
       <c r="H25" s="4">
-        <v>76.430533853647646</v>
+        <v>74.65315094719746</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" si="0"/>
-        <v>127.91898750789045</v>
+        <v>123.28825717559653</v>
       </c>
       <c r="K25" s="13" t="s">
         <v>64</v>
       </c>
       <c r="L25" s="4">
-        <v>192742.0200749549</v>
+        <v>-0.15718533150875055</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="26">
-        <v>563723681.88154542</v>
+        <v>857075.32507663034</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -6856,26 +6931,26 @@
         <v>16</v>
       </c>
       <c r="C26" s="4">
-        <v>372.78365166096796</v>
+        <v>368.14329244204333</v>
       </c>
       <c r="D26" s="5">
         <v>7.8923107438086744</v>
       </c>
       <c r="E26" s="4">
-        <v>349.53914259179015</v>
+        <v>342.99545725431005</v>
       </c>
       <c r="F26" s="7">
-        <v>1.1372887578278126</v>
+        <v>1.1196252392794583</v>
       </c>
       <c r="G26" s="4">
-        <v>188.33289059090924</v>
+        <v>0.1789815043892197</v>
       </c>
       <c r="H26" s="4">
-        <v>30.054400193618669</v>
+        <v>28.777092911330342</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" si="0"/>
-        <v>99.633651660967985</v>
+        <v>94.993292442043355</v>
       </c>
       <c r="N26" s="31" t="s">
         <v>76</v>
@@ -6907,7 +6982,7 @@
         <v>0.91018564327057938</v>
       </c>
       <c r="G27" s="4">
-        <v>188.33289059090924</v>
+        <v>0.1789815043892197</v>
       </c>
       <c r="H27" s="4">
         <v>19.876601402460075</v>
@@ -6920,7 +6995,7 @@
         <v>77</v>
       </c>
       <c r="O27" s="6">
-        <v>0.62993827838740779</v>
+        <v>0.71269346475761464</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -6949,7 +7024,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G28" s="4">
-        <v>3640.1320020358544</v>
+        <v>3.4593867266388565</v>
       </c>
       <c r="H28" s="4">
         <v>2.5073905791015251E-5</v>
@@ -6991,7 +7066,7 @@
         <v>0.43672528196163279</v>
       </c>
       <c r="G29" s="4">
-        <v>3640.1320020358544</v>
+        <v>3.4593867266388565</v>
       </c>
       <c r="H29" s="4">
         <v>0.17334706272843686</v>
@@ -7021,26 +7096,26 @@
         <v>39</v>
       </c>
       <c r="C30" s="4">
-        <v>304.11412786051727</v>
+        <v>304.03312670606874</v>
       </c>
       <c r="D30" s="5">
         <v>101.325</v>
       </c>
       <c r="E30" s="4">
-        <v>129.85230577480698</v>
+        <v>129.51374904828285</v>
       </c>
       <c r="F30" s="7">
-        <v>0.44999725923128103</v>
+        <v>0.44888385544072534</v>
       </c>
       <c r="G30" s="4">
-        <v>3640.1320020358544</v>
+        <v>3.4593867266388565</v>
       </c>
       <c r="H30" s="4">
-        <v>0.24610149280446422</v>
+        <v>0.23950610643450637</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" si="0"/>
-        <v>30.964127860517294</v>
+        <v>30.883126706068765</v>
       </c>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
@@ -7057,26 +7132,26 @@
         <v>29</v>
       </c>
       <c r="C31" s="4">
-        <v>440.06898750789043</v>
+        <v>435.4382571755965</v>
       </c>
       <c r="D31" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E31" s="4">
-        <v>596.73677012756878</v>
+        <v>591.20237940555796</v>
       </c>
       <c r="F31" s="7">
-        <v>2.1736996704556586</v>
+        <v>2.1610567826542426</v>
       </c>
       <c r="G31" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H31" s="4">
-        <v>258.80016540109756</v>
+        <v>257.03525167707909</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" si="0"/>
-        <v>166.91898750789045</v>
+        <v>162.28825717559653</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -7093,26 +7168,26 @@
         <v>30</v>
       </c>
       <c r="C32" s="4">
-        <v>426.20393967688454</v>
+        <v>423.35913575479753</v>
       </c>
       <c r="D32" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E32" s="4">
-        <v>580.06351274370934</v>
+        <v>576.60060448894728</v>
       </c>
       <c r="F32" s="7">
-        <v>2.1352002142002786</v>
+        <v>2.1270479527453361</v>
       </c>
       <c r="G32" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H32" s="4">
-        <v>253.6055208997798</v>
+        <v>252.57320939780874</v>
       </c>
       <c r="I32" s="4">
         <f t="shared" si="0"/>
-        <v>153.05393967688457</v>
+        <v>150.20913575479756</v>
       </c>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
@@ -7141,7 +7216,7 @@
         <v>1.8961819516546079</v>
       </c>
       <c r="G33" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H33" s="4">
         <v>231.85738014859709</v>
@@ -7165,26 +7240,26 @@
         <v>32</v>
       </c>
       <c r="C34" s="4">
-        <v>346.16670523637293</v>
+        <v>346.62379557580101</v>
       </c>
       <c r="D34" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E34" s="4">
-        <v>467.98922255412117</v>
+        <v>468.83049635692191</v>
       </c>
       <c r="F34" s="7">
-        <v>1.8419575395601402</v>
+        <v>1.8443861945514715</v>
       </c>
       <c r="G34" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H34" s="4">
-        <v>228.96153415414878</v>
+        <v>229.07870447128417</v>
       </c>
       <c r="I34" s="4">
         <f t="shared" si="0"/>
-        <v>73.016705236372957</v>
+        <v>73.473795575801034</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.3">
@@ -7204,7 +7279,7 @@
         <v>3.8804887263997387</v>
       </c>
       <c r="G35" s="4">
-        <v>0.1</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="H35" s="4">
         <v>2.1111792130950945E-2</v>
@@ -7225,16 +7300,16 @@
         <v>0.101325</v>
       </c>
       <c r="E36" s="4">
-        <v>452.6461066865939</v>
+        <v>453.10667720162991</v>
       </c>
       <c r="F36" s="7">
-        <v>3.9709195645679616</v>
+        <v>3.9723306469545014</v>
       </c>
       <c r="G36" s="4">
-        <v>0.1</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="H36" s="4">
-        <v>1.2692097972112533</v>
+        <v>1.3090660987003904</v>
       </c>
       <c r="I36" s="4">
         <f t="shared" si="0"/>
@@ -7246,26 +7321,26 @@
         <v>32</v>
       </c>
       <c r="C37" s="4">
-        <v>346.16670523637293</v>
+        <v>346.62379557580101</v>
       </c>
       <c r="D37" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E37" s="4">
-        <v>467.98922255412117</v>
+        <v>468.83049635692191</v>
       </c>
       <c r="F37" s="7">
-        <v>1.8419575395601402</v>
+        <v>1.8443861945514715</v>
       </c>
       <c r="G37" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H37" s="4">
-        <v>228.96153415414878</v>
+        <v>229.07870447128417</v>
       </c>
       <c r="I37" s="4">
         <f t="shared" si="0"/>
-        <v>73.016705236372957</v>
+        <v>73.473795575801034</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.3">
@@ -7273,26 +7348,26 @@
         <v>33</v>
       </c>
       <c r="C38" s="4">
-        <v>346.16482465658697</v>
+        <v>328.10044857875562</v>
       </c>
       <c r="D38" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E38" s="4">
-        <v>467.9857494877009</v>
+        <v>427.23019535530364</v>
       </c>
       <c r="F38" s="7">
-        <v>1.8419475065836266</v>
+        <v>1.7207811154245041</v>
       </c>
       <c r="G38" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H38" s="4">
-        <v>228.96105241967604</v>
+        <v>224.33125781137119</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" si="0"/>
-        <v>73.014824656586995</v>
+        <v>54.95044857875564</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.3">
@@ -7300,26 +7375,26 @@
         <v>33</v>
       </c>
       <c r="C39" s="4">
-        <v>346.16482465658697</v>
+        <v>328.10044857875562</v>
       </c>
       <c r="D39" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E39" s="4">
-        <v>467.98574948113162</v>
+        <v>427.23019145290715</v>
       </c>
       <c r="F39" s="7">
-        <v>1.8419475065836266</v>
+        <v>1.7207811154245041</v>
       </c>
       <c r="G39" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H39" s="4">
-        <v>228.96105241310678</v>
+        <v>224.3312539089747</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" si="0"/>
-        <v>73.014824656586995</v>
+        <v>54.95044857875564</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.3">
@@ -7339,7 +7414,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G40" s="4">
-        <v>812.25202719833999</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H40" s="4">
         <v>224.34458467728319</v>
@@ -7366,7 +7441,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G41" s="4">
-        <v>9.3915650980828866E-2</v>
+        <v>3.1520540937721294E-4</v>
       </c>
       <c r="H41" s="4">
         <v>2.5073905791015251E-5</v>
@@ -7381,26 +7456,26 @@
         <v>20</v>
       </c>
       <c r="C42" s="4">
-        <v>345.16482465658697</v>
+        <v>299.14999999999998</v>
       </c>
       <c r="D42" s="5">
         <v>101.325</v>
       </c>
       <c r="E42" s="4">
-        <v>301.56600461702902</v>
+        <v>109.10123710827688</v>
       </c>
       <c r="F42" s="7">
-        <v>0.97962440845434873</v>
+        <v>0.38119971346803067</v>
       </c>
       <c r="G42" s="4">
-        <v>9.3915650980828866E-2</v>
+        <v>3.1520540937721294E-4</v>
       </c>
       <c r="H42" s="4">
-        <v>14.051465794168879</v>
+        <v>7.021095587454511E-3</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="0"/>
-        <v>72.014824656586995</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -7475,34 +7550,34 @@
         <v>203</v>
       </c>
       <c r="B2">
-        <v>4.5058259292768729E-2</v>
+        <v>6.2330613710360416E-2</v>
       </c>
       <c r="C2">
-        <v>38392.512702731183</v>
+        <v>47.160113533787431</v>
       </c>
       <c r="E2" t="s">
         <v>66</v>
       </c>
       <c r="F2">
-        <v>25032.061802977114</v>
+        <v>25.031935161652605</v>
       </c>
       <c r="G2">
-        <v>1542.4567100955248</v>
+        <v>1.5412694860114715</v>
       </c>
       <c r="H2">
-        <v>69.500414391355164</v>
+        <v>9.6068272956146783E-2</v>
       </c>
       <c r="I2">
-        <v>99.723123151501454</v>
+        <v>99.61768441648718</v>
       </c>
       <c r="K2" s="29">
-        <v>0.32664347494249629</v>
+        <v>0.37171801292099393</v>
       </c>
       <c r="L2" s="29">
-        <v>1.8517120877445366</v>
+        <v>0.61795458428505312</v>
       </c>
       <c r="M2" s="29">
-        <v>0.24453052654182419</v>
+        <v>0.30218738767329717</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -7510,25 +7585,25 @@
         <v>204</v>
       </c>
       <c r="B3">
-        <v>4.5058259292768736E-2</v>
+        <v>6.2330613710360409E-2</v>
       </c>
       <c r="C3">
-        <v>34930.308642619573</v>
+        <v>42.780063275807827</v>
       </c>
       <c r="E3" t="s">
         <v>67</v>
       </c>
       <c r="F3">
-        <v>8882.6414408299115</v>
+        <v>8.882596502083512</v>
       </c>
       <c r="G3">
-        <v>2807.373846715212</v>
+        <v>2.8065325482354964</v>
       </c>
       <c r="H3">
-        <v>121.75423588731627</v>
+        <v>0.16684153618357625</v>
       </c>
       <c r="I3">
-        <v>98.647835565443472</v>
+        <v>98.156332631064402</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -7536,25 +7611,25 @@
         <v>205</v>
       </c>
       <c r="B4">
-        <v>4.3369441526206309E-2</v>
+        <v>5.9447568597938295E-2</v>
       </c>
       <c r="C4">
-        <v>36050.758599096102</v>
+        <v>43.783294899040605</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
       </c>
       <c r="F4">
-        <v>413.1727433514576</v>
+        <v>0.27111169102991423</v>
       </c>
       <c r="G4">
-        <v>2848.3263976414578</v>
+        <v>3.1173934843303797</v>
       </c>
       <c r="H4">
-        <v>696.502753778243</v>
+        <v>0.94203699337955504</v>
       </c>
       <c r="I4">
-        <v>37.233654741424409</v>
+        <v>22.347771094677046</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -7562,25 +7637,25 @@
         <v>206</v>
       </c>
       <c r="B5">
-        <v>4.336944152620633E-2</v>
+        <v>5.9447568597938281E-2</v>
       </c>
       <c r="C5">
-        <v>30234.828063157467</v>
+        <v>36.495552061002329</v>
       </c>
       <c r="E5" t="s">
         <v>70</v>
       </c>
       <c r="F5">
-        <v>95.502802558342736</v>
+        <v>6.8005339576619236E-2</v>
       </c>
       <c r="G5">
-        <v>964.55767849983272</v>
+        <v>1.1383330527634061</v>
       </c>
       <c r="H5">
-        <v>235.86379700352367</v>
+        <v>0.34398989151674325</v>
       </c>
       <c r="I5">
-        <v>28.820889819498024</v>
+        <v>16.506341443842707</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -7588,25 +7663,25 @@
         <v>207</v>
       </c>
       <c r="B6">
-        <v>4.336944152620633E-2</v>
+        <v>5.9447568597938309E-2</v>
       </c>
       <c r="C6">
-        <v>14403.380402556113</v>
+        <v>19.348775095478807</v>
       </c>
       <c r="E6" t="s">
         <v>59</v>
       </c>
       <c r="F6">
-        <v>40.473977963797893</v>
+        <v>1.4503104688313615</v>
       </c>
       <c r="G6">
-        <v>4555.56180201401</v>
+        <v>3.4691288051130833</v>
       </c>
       <c r="H6">
-        <v>197.57217119146574</v>
+        <v>0.20623127261704369</v>
       </c>
       <c r="I6">
-        <v>17.002576226258999</v>
+        <v>87.550493449279202</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -7614,25 +7689,25 @@
         <v>208</v>
       </c>
       <c r="B7">
-        <v>4.3369441526206309E-2</v>
+        <v>5.9447568597938295E-2</v>
       </c>
       <c r="C7">
-        <v>11223.418868047633</v>
+        <v>15.279298633423252</v>
       </c>
       <c r="E7" t="s">
         <v>60</v>
       </c>
       <c r="F7">
-        <v>15.369049891704023</v>
+        <v>0.99041125343622705</v>
       </c>
       <c r="G7">
-        <v>8696.3788936835081</v>
+        <v>7.1429330882120778</v>
       </c>
       <c r="H7">
-        <v>377.15709591934177</v>
+        <v>0.42463000475197082</v>
       </c>
       <c r="I7">
-        <v>3.915420681072892</v>
+        <v>69.991687359302716</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -7640,25 +7715,25 @@
         <v>209</v>
       </c>
       <c r="B8">
-        <v>4.3719571166688964E-5</v>
+        <v>1.0945431403057075E-3</v>
       </c>
       <c r="C8">
-        <v>7.9662790632337419</v>
+        <v>0.19630002150696768</v>
       </c>
       <c r="E8" t="s">
         <v>229</v>
       </c>
       <c r="F8">
-        <v>5.4655411715622142</v>
+        <v>0.55964063697403266</v>
       </c>
       <c r="G8">
-        <v>9946.2077370741645</v>
+        <v>9.087639387171599</v>
       </c>
       <c r="H8">
-        <v>431.36147486053875</v>
+        <v>0.54023806586220946</v>
       </c>
       <c r="I8">
-        <v>1.2511911971947656</v>
+        <v>50.88203231237182</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -7666,25 +7741,25 @@
         <v>210</v>
       </c>
       <c r="B9">
-        <v>4.544016457579185E-2</v>
+        <v>5.6519322803764302E-2</v>
       </c>
       <c r="C9">
-        <v>9914.4754036340255</v>
+        <v>12.144174696753895</v>
       </c>
       <c r="E9" t="s">
         <v>230</v>
       </c>
       <c r="F9">
-        <v>77.924977639318257</v>
+        <v>0.5921318853136408</v>
       </c>
       <c r="G9">
-        <v>1086.7646432466843</v>
+        <v>1.0330018156282741</v>
       </c>
       <c r="H9">
-        <v>1134.3969269456281</v>
+        <v>1.630636561151289</v>
       </c>
       <c r="I9">
-        <v>6.4277464050273725</v>
+        <v>26.639386853604201</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -7692,25 +7767,25 @@
         <v>211</v>
       </c>
       <c r="B10">
-        <v>4.6354911775307393E-2</v>
+        <v>6.2293020965969517E-2</v>
       </c>
       <c r="C10">
-        <v>13109.805988034212</v>
+        <v>17.204062412245676</v>
       </c>
       <c r="E10" t="s">
         <v>231</v>
       </c>
       <c r="F10">
-        <v>0.2032428542650199</v>
+        <v>7.7682084525008293E-4</v>
       </c>
       <c r="G10">
-        <v>0.88335841987004737</v>
+        <v>8.3949658717156963E-4</v>
       </c>
       <c r="H10">
-        <v>0.21600809953597649</v>
+        <v>2.5368528063802505E-4</v>
       </c>
       <c r="I10">
-        <v>48.47761285272879</v>
+        <v>75.382457778269426</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -7718,25 +7793,25 @@
         <v>212</v>
       </c>
       <c r="B11">
-        <v>0.10008769588699151</v>
+        <v>0.12753464962125136</v>
       </c>
       <c r="C11">
-        <v>6542.8302026461652</v>
+        <v>8.8351632291660778</v>
       </c>
       <c r="E11" t="s">
         <v>232</v>
       </c>
       <c r="F11">
-        <v>1.6038117139195283</v>
+        <v>0.19480471176576394</v>
       </c>
       <c r="G11">
-        <v>4665.6811406944789</v>
+        <v>4.2282153795985042</v>
       </c>
       <c r="H11">
-        <v>4870.1753236101495</v>
+        <v>6.6744147803865523</v>
       </c>
       <c r="I11">
-        <v>3.2920452043703807E-2</v>
+        <v>2.8359075145046244</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -7744,25 +7819,25 @@
         <v>213</v>
       </c>
       <c r="B12">
-        <v>5.6443133065265334E-2</v>
+        <v>7.5376348286035566E-2</v>
       </c>
       <c r="C12">
-        <v>19652.636190680376</v>
+        <v>26.039225641411754</v>
       </c>
       <c r="E12" t="s">
         <v>63</v>
       </c>
       <c r="F12">
-        <v>6.5098067393561485E-2</v>
+        <v>0.18541322966354401</v>
       </c>
       <c r="G12">
-        <v>0.2664800015417999</v>
+        <v>2.3013833668177122</v>
       </c>
       <c r="H12">
-        <v>1.1557088844770453E-2</v>
+        <v>0.13681164556905009</v>
       </c>
       <c r="I12">
-        <v>84.92327272957634</v>
+        <v>57.541563024799281</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -7770,25 +7845,25 @@
         <v>214</v>
       </c>
       <c r="B13">
-        <v>5.0128768442585875E-2</v>
+        <v>7.0803823955655404E-2</v>
       </c>
       <c r="C13">
-        <v>35524.557829245517</v>
+        <v>44.636313075766651</v>
       </c>
       <c r="E13" t="s">
         <v>233</v>
       </c>
       <c r="F13">
-        <v>38.334090696255963</v>
+        <v>-1.2508376609764744E-3</v>
       </c>
       <c r="G13">
-        <v>3748.4156267159824</v>
+        <v>-1.0659667984780519E-2</v>
       </c>
       <c r="H13">
-        <v>0.1638791237545851</v>
+        <v>-1.166746647067802E-5</v>
       </c>
       <c r="I13">
-        <v>99.574317491231952</v>
+        <v>99.99818001487435</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -7796,25 +7871,25 @@
         <v>215</v>
       </c>
       <c r="B14">
-        <v>4.3369441526206309E-2</v>
+        <v>5.9447568597938275E-2</v>
       </c>
       <c r="C14">
-        <v>2107.1741403798442</v>
+        <v>3.0640569428202089</v>
       </c>
       <c r="E14" s="28" t="s">
         <v>173</v>
       </c>
       <c r="F14" s="28">
-        <v>410.51238807750354</v>
+        <v>0.38530984394830042</v>
       </c>
       <c r="G14" s="28">
-        <v>6406.1012876481363</v>
+        <v>3.0223415591440466</v>
       </c>
       <c r="H14" s="28">
-        <v>1566.4873209488567</v>
+        <v>0.91331350041417936</v>
       </c>
       <c r="I14" s="28">
-        <v>20.76441317635166</v>
+        <v>29.670638959401796</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -7822,10 +7897,10 @@
         <v>216</v>
       </c>
       <c r="B15">
-        <v>4.3369441526206309E-2</v>
+        <v>5.9447568597938281E-2</v>
       </c>
       <c r="C15">
-        <v>9116.2447276677867</v>
+        <v>12.215241690603039</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -7833,10 +7908,10 @@
         <v>217</v>
       </c>
       <c r="B16">
-        <v>4.3369441526206289E-2</v>
+        <v>5.9447568597938275E-2</v>
       </c>
       <c r="C16">
-        <v>8.0656089136183216</v>
+        <v>1.0887231563140623E-2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -7844,10 +7919,10 @@
         <v>218</v>
       </c>
       <c r="B17">
-        <v>4.3719571166701418E-5</v>
+        <v>1.0945431403057205E-3</v>
       </c>
       <c r="C17">
-        <v>8.1307069810118833</v>
+        <v>0.19630046122668465</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -7858,7 +7933,7 @@
         <v>2E-3</v>
       </c>
       <c r="C18">
-        <v>4.7096643699903442E-9</v>
+        <v>1.5806861479085264E-11</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -7866,10 +7941,10 @@
         <v>219</v>
       </c>
       <c r="B19">
-        <v>29.173223213902457</v>
+        <v>-565.00162484106477</v>
       </c>
       <c r="C19">
-        <v>38.498518618741471</v>
+        <v>-1.25039792545502E-3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -7877,10 +7952,10 @@
         <v>220</v>
       </c>
       <c r="B20">
-        <v>1.0438294381354214</v>
+        <v>1.5785418152043924</v>
       </c>
       <c r="C20">
-        <v>15025.281105479558</v>
+        <v>21.091738972349887</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -7888,10 +7963,10 @@
         <v>221</v>
       </c>
       <c r="B21">
-        <v>1.0438294381354214</v>
+        <v>1.5785418152043924</v>
       </c>
       <c r="C21">
-        <v>5908.3168544968667</v>
+        <v>8.1303859832807976</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -7899,10 +7974,10 @@
         <v>222</v>
       </c>
       <c r="B22">
-        <v>59.816844075604649</v>
+        <v>88.665374580191326</v>
       </c>
       <c r="C22">
-        <v>5909.9206662107863</v>
+        <v>8.3251906950465617</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -7910,10 +7985,10 @@
         <v>223</v>
       </c>
       <c r="B23">
-        <v>56.786751584263364</v>
+        <v>84.175302539602072</v>
       </c>
       <c r="C23">
-        <v>5911.6364455538287</v>
+        <v>8.3277438763359566</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -7921,10 +7996,10 @@
         <v>224</v>
       </c>
       <c r="B24">
-        <v>1.8517120877445366</v>
+        <v>0.61795458428505312</v>
       </c>
       <c r="C24">
-        <v>2279.0193390532122</v>
+        <v>2.5526236937473641</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -7943,10 +8018,10 @@
         <v>226</v>
       </c>
       <c r="B26" s="28">
-        <v>0.24453052654182419</v>
+        <v>0.30218738767329717</v>
       </c>
       <c r="C26" s="28">
-        <v>1868.5069509757088</v>
+        <v>2.1673138497990636</v>
       </c>
     </row>
   </sheetData>

--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tes2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2577816-9F7D-473F-8819-FCC5616B393D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593147D4-1451-4B24-B49D-9705148BDCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="246">
   <si>
     <t>T [°C]</t>
   </si>
@@ -766,6 +766,9 @@
   </si>
   <si>
     <t>nc</t>
+  </si>
+  <si>
+    <t>Y TOTAL</t>
   </si>
 </sst>
 </file>
@@ -877,7 +880,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -932,6 +935,7 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1401,25 +1405,25 @@
         <v>44.1974892386704</v>
       </c>
       <c r="F3" s="19">
-        <v>22.333328223050525</v>
+        <v>22.354905020495806</v>
       </c>
       <c r="G3" s="19">
-        <v>42.909657240666718</v>
+        <v>42.952123279499567</v>
       </c>
       <c r="H3" s="19">
-        <v>59.52618690796568</v>
+        <v>60.497549771042344</v>
       </c>
       <c r="I3" s="19">
-        <v>58.057505047628197</v>
+        <v>59.339937648577902</v>
       </c>
       <c r="J3" s="19">
-        <v>26</v>
+        <v>57.599063408747668</v>
       </c>
       <c r="K3" s="19">
-        <v>0.10257759171348141</v>
+        <v>0.10487639653311226</v>
       </c>
       <c r="L3" s="17">
-        <v>0.91670339327938555</v>
+        <v>0.93724708263142997</v>
       </c>
       <c r="M3" s="21"/>
       <c r="N3" s="21"/>
@@ -1458,25 +1462,25 @@
         <v>46.695266271232697</v>
       </c>
       <c r="F4" s="17">
-        <v>23.167507795229405</v>
+        <v>23.188177710084158</v>
       </c>
       <c r="G4" s="17">
-        <v>45.435199171379885</v>
+        <v>45.476727334120156</v>
       </c>
       <c r="H4" s="17">
-        <v>59.443994763217077</v>
+        <v>60.417520328360382</v>
       </c>
       <c r="I4" s="17">
-        <v>57.977325998141247</v>
+        <v>59.261674848403935</v>
       </c>
       <c r="J4" s="17">
-        <v>26</v>
+        <v>57.667797740445906</v>
       </c>
       <c r="K4" s="17">
-        <v>0.10653783387630139</v>
+        <v>0.10893226180812285</v>
       </c>
       <c r="L4" s="17">
-        <v>0.95209482105832444</v>
+        <v>0.97349306382653711</v>
       </c>
       <c r="M4" s="21"/>
       <c r="N4" s="21"/>
@@ -1515,25 +1519,25 @@
         <v>48.863771870449447</v>
       </c>
       <c r="F5" s="17">
-        <v>23.701575419361824</v>
+        <v>23.721367173994736</v>
       </c>
       <c r="G5" s="17">
-        <v>47.626800188040562</v>
+        <v>47.667545596889568</v>
       </c>
       <c r="H5" s="17">
-        <v>59.363134451080114</v>
+        <v>60.338863157325541</v>
       </c>
       <c r="I5" s="17">
-        <v>57.898446201289907</v>
+        <v>59.184684248083506</v>
       </c>
       <c r="J5" s="17">
-        <v>26</v>
+        <v>57.728684382490371</v>
       </c>
       <c r="K5" s="17">
-        <v>0.11054310840208127</v>
+        <v>0.11303458215131838</v>
       </c>
       <c r="L5" s="17">
-        <v>0.98788868877802594</v>
+        <v>1.0101541992276344</v>
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
@@ -1572,25 +1576,25 @@
         <v>50.766607886856718</v>
       </c>
       <c r="F6" s="17">
-        <v>23.959454721561013</v>
+        <v>23.97837322726598</v>
       </c>
       <c r="G6" s="17">
-        <v>49.549035428021313</v>
+        <v>49.589121053564661</v>
       </c>
       <c r="H6" s="17">
-        <v>59.283542585562842</v>
+        <v>60.261517174005974</v>
       </c>
       <c r="I6" s="17">
-        <v>57.82080382168391</v>
+        <v>59.108910725880229</v>
       </c>
       <c r="J6" s="17">
-        <v>26</v>
+        <v>57.782166334695091</v>
       </c>
       <c r="K6" s="17">
-        <v>0.11459210227772978</v>
+        <v>0.11718202834730042</v>
       </c>
       <c r="L6" s="17">
-        <v>1.024073262457061</v>
+        <v>1.0472186100584135</v>
       </c>
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
@@ -1629,25 +1633,25 @@
         <v>52.451199641588161</v>
       </c>
       <c r="F7" s="17">
-        <v>23.955025972260994</v>
+        <v>23.973056603120103</v>
       </c>
       <c r="G7" s="17">
-        <v>51.250053435463514</v>
+        <v>51.289578376708199</v>
       </c>
       <c r="H7" s="17">
-        <v>59.205180321408527</v>
+        <v>60.18544479897475</v>
       </c>
       <c r="I7" s="17">
-        <v>57.744360963714044</v>
+        <v>59.034321922451397</v>
       </c>
       <c r="J7" s="17">
-        <v>26</v>
+        <v>57.828651464528377</v>
       </c>
       <c r="K7" s="17">
-        <v>0.11868247534446567</v>
+        <v>0.12137221903189251</v>
       </c>
       <c r="L7" s="17">
-        <v>1.0606276288388425</v>
+        <v>1.0846650148227439</v>
       </c>
       <c r="M7" s="21"/>
       <c r="N7" s="21"/>
@@ -1686,25 +1690,25 @@
         <v>53.9538380140431</v>
       </c>
       <c r="F8" s="17">
-        <v>23.695038677100754</v>
+        <v>23.712150117659942</v>
       </c>
       <c r="G8" s="17">
-        <v>52.766695897797455</v>
+        <v>52.805741087788945</v>
       </c>
       <c r="H8" s="17">
-        <v>59.128022038629801</v>
+        <v>60.110620931680657</v>
       </c>
       <c r="I8" s="17">
-        <v>57.669092633193216</v>
+        <v>58.960897517023895</v>
       </c>
       <c r="J8" s="17">
-        <v>26</v>
+        <v>57.868527049357624</v>
       </c>
       <c r="K8" s="17">
-        <v>0.12281132001508509</v>
+        <v>0.12560219118958013</v>
       </c>
       <c r="L8" s="17">
-        <v>1.0975258037389937</v>
+        <v>1.1224669339910212</v>
       </c>
       <c r="M8" s="21"/>
       <c r="N8" s="21"/>
@@ -1743,25 +1747,25 @@
         <v>55.302895315550657</v>
       </c>
       <c r="F9" s="17">
-        <v>23.18096972790984</v>
+        <v>23.197115911664334</v>
       </c>
       <c r="G9" s="17">
-        <v>54.1277629959406</v>
+        <v>54.166395266817204</v>
       </c>
       <c r="H9" s="17">
-        <v>59.052048428258885</v>
+        <v>60.037026235722536</v>
       </c>
       <c r="I9" s="17">
-        <v>57.594979992439178</v>
+        <v>58.888622676875549</v>
       </c>
       <c r="J9" s="17">
-        <v>26</v>
+        <v>57.90216663312242</v>
       </c>
       <c r="K9" s="17">
-        <v>0.12697546806706361</v>
+        <v>0.12986871416426851</v>
       </c>
       <c r="L9" s="17">
-        <v>1.1347394737579666</v>
+        <v>1.1605954962146874</v>
       </c>
       <c r="M9" s="21"/>
       <c r="N9" s="21"/>
@@ -1800,25 +1804,25 @@
         <v>56.520932003665166</v>
       </c>
       <c r="F10" s="17">
-        <v>22.423582815351114</v>
+        <v>22.425366441656642</v>
       </c>
       <c r="G10" s="17">
-        <v>55.389913311776915</v>
+        <v>55.394427986534978</v>
       </c>
       <c r="H10" s="17">
-        <v>59.851049318689974</v>
+        <v>59.964644324702697</v>
       </c>
       <c r="I10" s="17">
-        <v>58.666599502082221</v>
+        <v>58.817485312981574</v>
       </c>
       <c r="J10" s="17">
-        <v>54.035636198177485</v>
+        <v>57.929932791292686</v>
       </c>
       <c r="K10" s="17">
-        <v>0.13381494524769105</v>
+        <v>0.13416842834636822</v>
       </c>
       <c r="L10" s="17">
-        <v>1.1958617114222196</v>
+        <v>1.1990206777287142</v>
       </c>
       <c r="M10" s="21"/>
       <c r="N10" s="21"/>
@@ -1857,25 +1861,25 @@
         <v>57.62617165599864</v>
       </c>
       <c r="F11" s="20">
-        <v>21.389489601453477</v>
+        <v>21.391116232475689</v>
       </c>
       <c r="G11" s="20">
-        <v>56.503920904775917</v>
+        <v>56.508324163200641</v>
       </c>
       <c r="H11" s="20">
-        <v>59.781542759070248</v>
+        <v>59.893458865935898</v>
       </c>
       <c r="I11" s="20">
-        <v>58.598902988138313</v>
+        <v>58.747473234144088</v>
       </c>
       <c r="J11" s="20">
-        <v>54.114467173333594</v>
+        <v>57.952177903548829</v>
       </c>
       <c r="K11" s="20">
-        <v>0.13813829320714302</v>
+        <v>0.1384980115890817</v>
       </c>
       <c r="L11" s="20">
-        <v>1.2344981005063695</v>
+        <v>1.2377127895611604</v>
       </c>
       <c r="M11" s="21"/>
       <c r="N11" s="21"/>
@@ -1914,25 +1918,25 @@
         <v>55.302895315550657</v>
       </c>
       <c r="F12" s="17">
-        <v>23.18096972790984</v>
+        <v>23.197115911664334</v>
       </c>
       <c r="G12" s="17">
-        <v>54.1277629959406</v>
+        <v>54.166395266817204</v>
       </c>
       <c r="H12" s="17">
-        <v>59.052048428258885</v>
+        <v>60.037026235722536</v>
       </c>
       <c r="I12" s="17">
-        <v>57.594979992439178</v>
+        <v>58.888622676875549</v>
       </c>
       <c r="J12" s="17">
-        <v>26</v>
+        <v>57.90216663312242</v>
       </c>
       <c r="K12" s="17">
-        <v>0.12697546806706361</v>
+        <v>0.12986871416426851</v>
       </c>
       <c r="L12" s="21">
-        <v>1.1347394737579666</v>
+        <v>1.1605954962146874</v>
       </c>
       <c r="M12" s="21"/>
       <c r="N12" s="21"/>
@@ -2082,10 +2086,10 @@
         <v>89.329858804423736</v>
       </c>
       <c r="M16" s="17">
-        <v>2.3653610419403317</v>
+        <v>1.930081004445823</v>
       </c>
       <c r="N16" s="17">
-        <v>1.6493321533075163</v>
+        <v>1.2227807343486761</v>
       </c>
       <c r="O16" s="17">
         <v>6.6201750343054497</v>
@@ -2100,16 +2104,16 @@
         <v>0.635370308557899</v>
       </c>
       <c r="S16" s="17">
-        <v>-0.14548588427793208</v>
+        <v>0.71454041902522358</v>
       </c>
       <c r="T16" s="17">
         <v>346.59758286418668</v>
       </c>
       <c r="U16" s="17">
-        <v>2.3954507028929144</v>
+        <v>2.3221297488339383</v>
       </c>
       <c r="V16" s="17">
-        <v>269.17546873163661</v>
+        <v>269.10034262442736</v>
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.3">
@@ -2147,10 +2151,10 @@
         <v>91.657429244218392</v>
       </c>
       <c r="M17" s="17">
-        <v>2.3561415778958588</v>
+        <v>1.9186775422157969</v>
       </c>
       <c r="N17" s="17">
-        <v>1.6226905804250538</v>
+        <v>1.2030292234185742</v>
       </c>
       <c r="O17" s="17">
         <v>7.0030101822417947</v>
@@ -2165,16 +2169,16 @@
         <v>0.66545635698113537</v>
       </c>
       <c r="S17" s="17">
-        <v>-0.119990923365371</v>
+        <v>0.73525190064365598</v>
       </c>
       <c r="T17" s="17">
         <v>376.85431963656947</v>
       </c>
       <c r="U17" s="17">
-        <v>2.4961883371474878</v>
+        <v>2.4198198472494696</v>
       </c>
       <c r="V17" s="17">
-        <v>289.53063518117392</v>
+        <v>289.45238412259835</v>
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.3">
@@ -2212,10 +2216,10 @@
         <v>94.28961039278758</v>
       </c>
       <c r="M18" s="17">
-        <v>2.3462773513724104</v>
+        <v>1.9069244306451252</v>
       </c>
       <c r="N18" s="17">
-        <v>1.596332426419806</v>
+        <v>1.1834878333802012</v>
       </c>
       <c r="O18" s="17">
         <v>7.3974316456089495</v>
@@ -2230,16 +2234,16 @@
         <v>0.69636622761943978</v>
       </c>
       <c r="S18" s="17">
-        <v>-9.5734326195325889E-2</v>
+        <v>0.75450271920144385</v>
       </c>
       <c r="T18" s="17">
         <v>409.52689894564264</v>
       </c>
       <c r="U18" s="17">
-        <v>2.5984826855916676</v>
+        <v>2.5190206459099995</v>
       </c>
       <c r="V18" s="17">
-        <v>312.44604258325126</v>
+        <v>312.36462007519947</v>
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.3">
@@ -2277,10 +2281,10 @@
         <v>97.339721439540327</v>
       </c>
       <c r="M19" s="17">
-        <v>2.3358189626234509</v>
+        <v>1.8948558200554169</v>
       </c>
       <c r="N19" s="17">
-        <v>1.570268926036658</v>
+        <v>1.1641648934409707</v>
       </c>
       <c r="O19" s="17">
         <v>7.8033521734467595</v>
@@ -2295,16 +2299,16 @@
         <v>0.72811563723715711</v>
       </c>
       <c r="S19" s="17">
-        <v>-7.2692234555451665E-2</v>
+        <v>0.77233615117360299</v>
       </c>
       <c r="T19" s="17">
         <v>445.35973731244945</v>
       </c>
       <c r="U19" s="17">
-        <v>2.7023063544155743</v>
+        <v>2.6197052171288115</v>
       </c>
       <c r="V19" s="17">
-        <v>338.6368376537385</v>
+        <v>338.55219772701713</v>
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.3">
@@ -2342,10 +2346,10 @@
         <v>100.93942961581514</v>
       </c>
       <c r="M20" s="17">
-        <v>2.3248171675699569</v>
+        <v>1.8825071362629311</v>
       </c>
       <c r="N20" s="17">
-        <v>1.544517183389571</v>
+        <v>1.1450730842370958</v>
       </c>
       <c r="O20" s="17">
         <v>8.2205630927133253</v>
@@ -2360,16 +2364,16 @@
         <v>0.76071243566216995</v>
       </c>
       <c r="S20" s="17">
-        <v>-5.0845216937889411E-2</v>
+        <v>0.78879146182729798</v>
       </c>
       <c r="T20" s="17">
         <v>485.30011031889705</v>
       </c>
       <c r="U20" s="17">
-        <v>2.807605122699155</v>
+        <v>2.7218206058934524</v>
       </c>
       <c r="V20" s="17">
-        <v>369.02859611293366</v>
+        <v>368.94069414443356</v>
       </c>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.3">
@@ -2407,10 +2411,10 @@
         <v>105.25356004225264</v>
       </c>
       <c r="M21" s="17">
-        <v>2.3133222369557052</v>
+        <v>1.8699139571982328</v>
       </c>
       <c r="N21" s="17">
-        <v>1.519096652861311</v>
+        <v>1.1262268288454547</v>
       </c>
       <c r="O21" s="17">
         <v>8.6487738547050501</v>
@@ -2425,16 +2429,16 @@
         <v>0.79415965355949536</v>
       </c>
       <c r="S21" s="17">
-        <v>-3.0174434344084518E-2</v>
+        <v>0.80390730241588804</v>
       </c>
       <c r="T21" s="17">
         <v>530.59558549012502</v>
       </c>
       <c r="U21" s="17">
-        <v>2.9143093275293408</v>
+        <v>2.8252988721133399</v>
       </c>
       <c r="V21" s="17">
-        <v>404.85239211909459</v>
+        <v>404.76118529666508</v>
       </c>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.3">
@@ -2472,10 +2476,10 @@
         <v>110.50043569183623</v>
       </c>
       <c r="M22" s="17">
-        <v>2.3013833668177122</v>
+        <v>1.8571112073122706</v>
       </c>
       <c r="N22" s="17">
-        <v>1.4940269956205496</v>
+        <v>1.1076407036497178</v>
       </c>
       <c r="O22" s="17">
         <v>9.087639387171599</v>
@@ -2490,16 +2494,16 @@
         <v>0.82845750521160622</v>
       </c>
       <c r="S22" s="17">
-        <v>-1.0659667984780519E-2</v>
+        <v>0.81772333798409824</v>
       </c>
       <c r="T22" s="17">
         <v>582.94274341290134</v>
       </c>
       <c r="U22" s="17">
-        <v>3.0223415591440466</v>
+        <v>2.9300645561034075</v>
       </c>
       <c r="V22" s="17">
-        <v>447.79197565268419</v>
+        <v>447.69742320413616</v>
       </c>
       <c r="W22" s="21"/>
       <c r="X22" s="21"/>
@@ -2541,10 +2545,10 @@
         <v>116.98291458223341</v>
       </c>
       <c r="M23" s="17">
-        <v>2.2890482532119778</v>
+        <v>1.8441326568514971</v>
       </c>
       <c r="N23" s="17">
-        <v>1.4693269107716009</v>
+        <v>1.0893285717789456</v>
       </c>
       <c r="O23" s="17">
         <v>9.5367775019646093</v>
@@ -2559,16 +2563,16 @@
         <v>0.86360461913449049</v>
       </c>
       <c r="S23" s="17">
-        <v>5.8792565607020501E-3</v>
+        <v>0.83028085890397618</v>
       </c>
       <c r="T23" s="17">
         <v>644.72602284462573</v>
       </c>
       <c r="U23" s="17">
-        <v>3.0470747563831502</v>
+        <v>3.0360379909835356</v>
       </c>
       <c r="V23" s="17">
-        <v>500.13533961616463</v>
+        <v>500.12379051775497</v>
       </c>
       <c r="W23" s="21"/>
       <c r="X23" s="21"/>
@@ -2610,10 +2614,10 @@
         <v>125.14003470369184</v>
       </c>
       <c r="M24" s="20">
-        <v>2.2763627598696385</v>
+        <v>1.8310105813053528</v>
       </c>
       <c r="N24" s="20">
-        <v>1.4450134624539273</v>
+        <v>1.071303084233084</v>
       </c>
       <c r="O24" s="20">
         <v>9.9957814728889982</v>
@@ -2628,16 +2632,16 @@
         <v>0.89959878338048638</v>
       </c>
       <c r="S24" s="20">
-        <v>2.308222780014408E-2</v>
+        <v>0.84162287618195641</v>
       </c>
       <c r="T24" s="20">
         <v>719.42246610239113</v>
       </c>
       <c r="U24" s="20">
-        <v>3.1543702236463185</v>
+        <v>3.1431393839335158</v>
       </c>
       <c r="V24" s="20">
-        <v>565.52101646050482</v>
+        <v>565.5092637123887</v>
       </c>
       <c r="W24" s="21"/>
       <c r="X24" s="21"/>
@@ -2679,10 +2683,10 @@
         <v>110.50043569183623</v>
       </c>
       <c r="M25" s="17">
-        <v>2.3013833668177122</v>
+        <v>1.8571112073122706</v>
       </c>
       <c r="N25" s="17">
-        <v>1.4940269956205496</v>
+        <v>1.1076407036497178</v>
       </c>
       <c r="O25" s="17">
         <v>9.087639387171599</v>
@@ -2697,16 +2701,16 @@
         <v>0.82845750521160622</v>
       </c>
       <c r="S25" s="17">
-        <v>-1.0659667984780519E-2</v>
+        <v>0.81772333798409824</v>
       </c>
       <c r="T25" s="17">
         <v>582.94274341290134</v>
       </c>
       <c r="U25" s="17">
-        <v>3.0223415591440466</v>
+        <v>2.9300645561034075</v>
       </c>
       <c r="V25" s="17">
-        <v>447.79197565268419</v>
+        <v>447.69742320413616</v>
       </c>
       <c r="W25" s="21"/>
       <c r="X25" s="21"/>
@@ -2746,230 +2750,322 @@
         <v>500</v>
       </c>
       <c r="C29" s="17">
-        <v>0.77662246374381749</v>
+        <v>0.77640571062457064</v>
       </c>
       <c r="D29" s="17">
-        <v>3.4774148124606663</v>
+        <v>3.4730888362653878</v>
       </c>
       <c r="E29" s="21">
-        <v>0.28756994892202298</v>
-      </c>
-      <c r="F29" s="21"/>
-      <c r="G29"/>
+        <v>0.28792813750059443</v>
+      </c>
+      <c r="F29" s="21">
+        <v>1.1528353975643852E-2</v>
+      </c>
+      <c r="G29">
+        <v>0.67766107140503951</v>
+      </c>
       <c r="H29">
-        <v>22.337753625618252</v>
-      </c>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
+        <v>22.359428937542937</v>
+      </c>
+      <c r="I29" s="25">
+        <v>0.58918752020512355</v>
+      </c>
+      <c r="J29" s="25">
+        <v>0.94487128318858982</v>
+      </c>
+      <c r="K29" s="17">
+        <v>0.50713896966741379</v>
+      </c>
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B30" s="17">
         <v>550</v>
       </c>
       <c r="C30" s="17">
-        <v>0.76828264954052083</v>
+        <v>0.76807500681361496</v>
       </c>
       <c r="D30" s="17">
-        <v>3.3162075797325237</v>
+        <v>3.3123560480545731</v>
       </c>
       <c r="E30" s="21">
-        <v>0.30154927758794198</v>
-      </c>
-      <c r="F30" s="21"/>
-      <c r="G30"/>
+        <v>0.30189991217499829</v>
+      </c>
+      <c r="F30" s="21">
+        <v>1.1409508227685178E-2</v>
+      </c>
+      <c r="G30">
+        <v>0.67114713595942466</v>
+      </c>
       <c r="H30">
-        <v>23.171735045947916</v>
-      </c>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
+        <v>23.192499318638504</v>
+      </c>
+      <c r="I30" s="25">
+        <v>0.52903783538001348</v>
+      </c>
+      <c r="J30" s="25">
+        <v>0.85445086957500882</v>
+      </c>
+      <c r="K30" s="17">
+        <v>0.45279817623312379</v>
+      </c>
     </row>
     <row r="31" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B31" s="17">
         <v>600</v>
       </c>
       <c r="C31" s="17">
-        <v>0.76294388326546259</v>
+        <v>0.76274506236197259</v>
       </c>
       <c r="D31" s="17">
-        <v>3.2189585281416084</v>
+        <v>3.2154346617852401</v>
       </c>
       <c r="E31" s="21">
-        <v>0.31065948543839333</v>
-      </c>
-      <c r="F31" s="21"/>
-      <c r="G31"/>
+        <v>0.31099994407747983</v>
+      </c>
+      <c r="F31" s="21">
+        <v>1.1308661811768277E-2</v>
+      </c>
+      <c r="G31">
+        <v>0.66561974390301926</v>
+      </c>
       <c r="H31">
-        <v>23.705611673453742</v>
-      </c>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
+        <v>23.725493763802731</v>
+      </c>
+      <c r="I31" s="25">
+        <v>0.48164948909857774</v>
+      </c>
+      <c r="J31" s="25">
+        <v>0.78200681071062261</v>
+      </c>
+      <c r="K31" s="17">
+        <v>0.40925113824208187</v>
+      </c>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B32" s="17">
         <v>650</v>
       </c>
       <c r="C32" s="17">
-        <v>0.76036697815851795</v>
+        <v>0.76017692971086936</v>
       </c>
       <c r="D32" s="17">
-        <v>3.173557107183524</v>
+        <v>3.1702606448984065</v>
       </c>
       <c r="E32" s="21">
-        <v>0.31510383025294991</v>
+        <v>0.31543147772698221</v>
       </c>
       <c r="F32" s="21">
-        <v>1.093327961204547E-2</v>
+        <v>1.1240873785407897E-2</v>
       </c>
       <c r="G32">
-        <v>0.64504504553621222</v>
+        <v>0.66190428217820685</v>
       </c>
       <c r="H32">
-        <v>23.963302184148215</v>
-      </c>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+        <v>23.982307028913063</v>
+      </c>
+      <c r="I32" s="25">
+        <v>0.44524326931701602</v>
+      </c>
+      <c r="J32" s="25">
+        <v>0.72536254774276887</v>
+      </c>
+      <c r="K32" s="17">
+        <v>0.37516625264250297</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="17">
         <v>700</v>
       </c>
       <c r="C33" s="17">
-        <v>0.76041317169790079</v>
+        <v>0.76023204260554933</v>
       </c>
       <c r="D33" s="17">
-        <v>3.1743366614522994</v>
+        <v>3.1711936245401633</v>
       </c>
       <c r="E33" s="21">
-        <v>0.31502644698766363</v>
+        <v>0.31533867634619894</v>
       </c>
       <c r="F33" s="21">
-        <v>1.0936752307543264E-2</v>
+        <v>1.1179728444851433E-2</v>
       </c>
       <c r="G33">
-        <v>0.64523538397644631</v>
+        <v>0.6585529060623071</v>
       </c>
       <c r="H33">
-        <v>23.95868283020992</v>
-      </c>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+        <v>23.976795739445055</v>
+      </c>
+      <c r="I33" s="25">
+        <v>0.415423297910678</v>
+      </c>
+      <c r="J33" s="25">
+        <v>0.67763408972435935</v>
+      </c>
+      <c r="K33" s="17">
+        <v>0.34644012753811149</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="17">
         <v>750</v>
       </c>
       <c r="C34" s="17">
-        <v>0.76301500274473988</v>
+        <v>0.76284310756708729</v>
       </c>
       <c r="D34" s="17">
-        <v>3.2201466861589432</v>
+        <v>3.2170980015808421</v>
       </c>
       <c r="E34" s="21">
-        <v>0.31054485943086663</v>
-      </c>
-      <c r="F34" s="21"/>
-      <c r="G34"/>
+        <v>0.31083914742684632</v>
+      </c>
+      <c r="F34" s="21">
+        <v>1.1129047836412533E-2</v>
+      </c>
+      <c r="G34">
+        <v>0.65577510191377097</v>
+      </c>
       <c r="H34">
-        <v>23.698499725526013</v>
-      </c>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+        <v>23.715689243291273</v>
+      </c>
+      <c r="I34" s="25">
+        <v>0.39128957847631385</v>
+      </c>
+      <c r="J34" s="25">
+        <v>0.6375117292654856</v>
+      </c>
+      <c r="K34" s="17">
+        <v>0.32227853971765508</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="17">
         <v>800.00000000000011</v>
       </c>
       <c r="C35" s="17">
-        <v>0.76815773197730819</v>
+        <v>0.76799553346018712</v>
       </c>
       <c r="D35" s="17">
-        <v>3.3137428718197577</v>
+        <v>3.3107371467416415</v>
       </c>
       <c r="E35" s="21">
-        <v>0.30177356502342179</v>
+        <v>0.30204753674998908</v>
       </c>
       <c r="F35" s="21">
-        <v>1.0946804887868034E-2</v>
+        <v>1.1090849514401464E-2</v>
       </c>
       <c r="G35">
-        <v>0.64578636590404692</v>
+        <v>0.65368145188434423</v>
       </c>
       <c r="H35">
-        <v>23.18422680226918</v>
-      </c>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+        <v>23.200446653981288</v>
+      </c>
+      <c r="I35" s="25">
+        <v>0.37217854911101822</v>
+      </c>
+      <c r="J35" s="25">
+        <v>0.60389489005271357</v>
+      </c>
+      <c r="K35" s="17">
+        <v>0.30201493343058861</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="17">
         <v>850.00000000000011</v>
       </c>
       <c r="C36" s="17">
-        <v>0.7757331360839046</v>
+        <v>0.77571522289597594</v>
       </c>
       <c r="D36" s="17">
-        <v>3.4594522314821168</v>
+        <v>3.4590972009939254</v>
       </c>
       <c r="E36" s="17">
-        <v>0.28906310395029639</v>
+        <v>0.28909277244729153</v>
       </c>
       <c r="F36" s="21">
-        <v>1.0948878679185562E-2</v>
+        <v>1.1051438639014656E-2</v>
       </c>
       <c r="G36">
-        <v>0.64590003040616073</v>
+        <v>0.65152134180439336</v>
       </c>
       <c r="H36">
-        <v>22.42668639160954</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+        <v>22.428477710402394</v>
+      </c>
+      <c r="I36" s="17">
+        <v>0.35640606581724499</v>
+      </c>
+      <c r="J36" s="17">
+        <v>0.57381526783056802</v>
+      </c>
+      <c r="K36" s="17">
+        <v>0.28388754369627789</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="20">
         <v>900.00000000000011</v>
       </c>
       <c r="C37" s="20">
-        <v>0.78607639197636292</v>
+        <v>0.78606005561119507</v>
       </c>
       <c r="D37" s="20">
-        <v>3.6750591370957575</v>
+        <v>3.6747033070570199</v>
       </c>
       <c r="E37" s="20">
-        <v>0.27210446490672185</v>
+        <v>0.27213081341276379</v>
       </c>
       <c r="F37" s="20">
-        <v>1.0952326373580519E-2</v>
+        <v>1.1019618698023101E-2</v>
       </c>
       <c r="G37" s="20">
-        <v>0.64608899853594826</v>
+        <v>0.64977729083864622</v>
       </c>
       <c r="H37" s="20">
-        <v>21.392360802363719</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+        <v>21.393994438880494</v>
+      </c>
+      <c r="I37" s="17">
+        <v>0.34461609982786973</v>
+      </c>
+      <c r="J37" s="17">
+        <v>0.54797165579528284</v>
+      </c>
+      <c r="K37" s="17">
+        <v>0.26829838841603093</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="17">
         <v>800.00000000000011</v>
       </c>
       <c r="C38" s="17">
-        <v>0.76815773197730819</v>
+        <v>0.76799553346018712</v>
       </c>
       <c r="D38" s="17">
-        <v>3.3137428718197577</v>
+        <v>3.3107371467416415</v>
       </c>
       <c r="E38" s="17">
-        <v>0.30177356502342179</v>
+        <v>0.30204753674998908</v>
       </c>
       <c r="F38" s="17">
-        <v>1.0946804887868034E-2</v>
+        <v>1.1090849514401464E-2</v>
       </c>
       <c r="G38" s="17">
-        <v>0.64578636590404692</v>
+        <v>0.65368145188434423</v>
       </c>
       <c r="H38" s="21">
-        <v>23.18422680226918</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+        <v>23.200446653981288</v>
+      </c>
+      <c r="I38" s="17">
+        <v>0.37217854911101822</v>
+      </c>
+      <c r="J38" s="17">
+        <v>0.60389489005271357</v>
+      </c>
+      <c r="K38" s="17">
+        <v>0.30201493343058861</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="21"/>
@@ -3038,25 +3134,25 @@
         <v>56.964645761388169</v>
       </c>
       <c r="F3" s="17">
-        <v>21.177717530176274</v>
+        <v>21.165348938260554</v>
       </c>
       <c r="G3" s="17">
-        <v>55.941806182451671</v>
+        <v>55.908324645574957</v>
       </c>
       <c r="H3" s="17">
-        <v>60.13539183455795</v>
+        <v>59.189719664805004</v>
       </c>
       <c r="I3" s="17">
-        <v>58.972944791760909</v>
+        <v>57.729279005009204</v>
       </c>
       <c r="J3" s="17">
-        <v>56.632627091431857</v>
+        <v>26</v>
       </c>
       <c r="K3" s="17">
-        <v>0.12211214723233685</v>
+        <v>0.11950172563922697</v>
       </c>
       <c r="L3" s="17">
-        <v>1.0912775183997925</v>
+        <v>1.0679490088069992</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -3073,25 +3169,25 @@
         <v>57.545256030232352</v>
       </c>
       <c r="F4" s="17">
-        <v>21.364087267029952</v>
+        <v>21.351660780792912</v>
       </c>
       <c r="G4" s="17">
-        <v>56.436459797130688</v>
+        <v>56.402821541456284</v>
       </c>
       <c r="H4" s="17">
-        <v>59.83266920833421</v>
+        <v>58.944174168235278</v>
       </c>
       <c r="I4" s="17">
-        <v>58.653227949931896</v>
+        <v>57.489748166950314</v>
       </c>
       <c r="J4" s="17">
-        <v>54.509173803592262</v>
+        <v>26</v>
       </c>
       <c r="K4" s="17">
-        <v>0.13578470918644805</v>
+        <v>0.13305711404850473</v>
       </c>
       <c r="L4" s="17">
-        <v>1.2134648668137162</v>
+        <v>1.1890892144253362</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -3334,10 +3430,10 @@
         <v>119.16108401865955</v>
       </c>
       <c r="M16" s="17">
-        <v>2.5016228555001572</v>
+        <v>3.5346036023974392</v>
       </c>
       <c r="N16" s="17">
-        <v>1.6009092589635576</v>
+        <v>2.7601883775233755</v>
       </c>
       <c r="O16" s="17">
         <v>8.1751551300820342</v>
@@ -3352,16 +3448,16 @@
         <v>0.75406058026615341</v>
       </c>
       <c r="S16" s="17">
-        <v>0.73255540084823856</v>
+        <v>-1.4577184054056023</v>
       </c>
       <c r="T16" s="17">
         <v>686.59527072028743</v>
       </c>
       <c r="U16" s="17">
-        <v>2.7454173458677973</v>
+        <v>2.8287445516591152</v>
       </c>
       <c r="V16" s="17">
-        <v>541.17180457528173</v>
+        <v>541.25711784027646</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -3399,10 +3495,10 @@
         <v>124.16319568817148</v>
       </c>
       <c r="M17" s="17">
-        <v>2.3094414175745959</v>
+        <v>3.1814466598366935</v>
       </c>
       <c r="N17" s="17">
-        <v>1.4669494851758738</v>
+        <v>2.529223250303231</v>
       </c>
       <c r="O17" s="17">
         <v>9.724441884323193</v>
@@ -3417,16 +3513,16 @@
         <v>0.87717648611728305</v>
       </c>
       <c r="S17" s="17">
-        <v>0.11360130264901518</v>
+        <v>-1.8187458306705648</v>
       </c>
       <c r="T17" s="17">
         <v>714.07196015237332</v>
       </c>
       <c r="U17" s="17">
-        <v>3.0936444427711418</v>
+        <v>3.1808572198766729</v>
       </c>
       <c r="V17" s="17">
-        <v>561.49669982716159</v>
+        <v>561.58584447833709</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -3464,10 +3560,10 @@
         <v>128.95181516126439</v>
       </c>
       <c r="M18" s="17">
-        <v>2.1580349110813133</v>
+        <v>2.8853526256065507</v>
       </c>
       <c r="N18" s="17">
-        <v>1.3689926224369802</v>
+        <v>2.3603321076499659</v>
       </c>
       <c r="O18" s="17">
         <v>10.97919765967354</v>
@@ -3482,7 +3578,7 @@
         <v>0.98324170106960251</v>
       </c>
       <c r="S18" s="17">
-        <v>-0.25955065955024703</v>
+        <v>-1.9782079329278976</v>
       </c>
       <c r="T18" s="17">
         <v>740.25313049480803</v>
@@ -3491,7 +3587,7 @@
         <v>3.4629181106772062</v>
       </c>
       <c r="V18" s="17">
-        <v>581.43710594692186</v>
+        <v>581.43710587328212</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -3529,10 +3625,10 @@
         <v>133.48492502395891</v>
       </c>
       <c r="M19" s="17">
-        <v>2.0354357212835343</v>
+        <v>2.6354072076822548</v>
       </c>
       <c r="N19" s="17">
-        <v>1.2936007375318763</v>
+        <v>2.2303460991928903</v>
       </c>
       <c r="O19" s="17">
         <v>12.030465799378224</v>
@@ -3547,7 +3643,7 @@
         <v>1.0770012172548296</v>
       </c>
       <c r="S19" s="17">
-        <v>-0.493111310371803</v>
+        <v>-2.0298275997064565</v>
       </c>
       <c r="T19" s="17">
         <v>764.92639619912222</v>
@@ -3556,7 +3652,7 @@
         <v>3.6974779927046795</v>
       </c>
       <c r="V19" s="17">
-        <v>600.45454537817875</v>
+        <v>600.45454593690408</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -3594,10 +3690,10 @@
         <v>137.75725064697997</v>
       </c>
       <c r="M20" s="17">
-        <v>1.9340930512475702</v>
+        <v>2.4234137716096513</v>
       </c>
       <c r="N20" s="17">
-        <v>1.2330934904721254</v>
+        <v>2.1260232594346991</v>
       </c>
       <c r="O20" s="17">
         <v>12.941619902553503</v>
@@ -3612,7 +3708,7 @@
         <v>1.1620598783187359</v>
       </c>
       <c r="S20" s="17">
-        <v>-0.64423924252588405</v>
+        <v>-2.026489666506686</v>
       </c>
       <c r="T20" s="17">
         <v>788.08125994134957</v>
@@ -3621,7 +3717,7 @@
         <v>3.8996313447041677</v>
       </c>
       <c r="V20" s="17">
-        <v>618.52827300167678</v>
+        <v>618.52827306702056</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -3659,10 +3755,10 @@
         <v>141.78080722790236</v>
       </c>
       <c r="M21" s="17">
-        <v>1.8489805188311883</v>
+        <v>2.2427534299674861</v>
       </c>
       <c r="N21" s="17">
-        <v>1.1829992586391733</v>
+        <v>2.0396538942054714</v>
       </c>
       <c r="O21" s="17">
         <v>13.751892148659186</v>
@@ -3677,7 +3773,7 @@
         <v>1.240742535294457</v>
       </c>
       <c r="S21" s="17">
-        <v>-0.74548183748495012</v>
+        <v>-1.9959093778783614</v>
       </c>
       <c r="T21" s="17">
         <v>809.79986311707626</v>
@@ -3686,7 +3782,7 @@
         <v>4.0786349558568915</v>
       </c>
       <c r="V21" s="17">
-        <v>635.6607839124963</v>
+        <v>635.66078391880546</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -3717,22 +3813,31 @@
         <v>2.5</v>
       </c>
       <c r="C29" s="17">
-        <v>0.78819623095794678</v>
+        <v>0.78832048649630093</v>
       </c>
       <c r="D29" s="17">
-        <v>3.7218186040815806</v>
+        <v>3.7245806284405534</v>
       </c>
       <c r="E29" s="17">
-        <v>0.26868585129413269</v>
+        <v>0.26848660285780696</v>
       </c>
       <c r="F29" s="17">
-        <v>1.0973501548280534E-2</v>
+        <v>1.0953340502488237E-2</v>
       </c>
       <c r="G29" s="17">
-        <v>0.64724960986125613</v>
+        <v>0.64614458294138033</v>
       </c>
       <c r="H29" s="17">
-        <v>21.18037690420531</v>
+        <v>21.167951350369908</v>
+      </c>
+      <c r="I29" s="17">
+        <v>0.34227557338586767</v>
+      </c>
+      <c r="J29" s="17">
+        <v>0.5548833499916922</v>
+      </c>
+      <c r="K29" s="17">
+        <v>0.26660671501238004</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -3740,22 +3845,31 @@
         <v>2.7</v>
       </c>
       <c r="C30" s="17">
-        <v>0.7863306937683785</v>
+        <v>0.78645553363907783</v>
       </c>
       <c r="D30" s="17">
-        <v>3.6806191808712576</v>
+        <v>3.6833459547396958</v>
       </c>
       <c r="E30" s="17">
-        <v>0.27169341647654105</v>
+        <v>0.2714922823671258</v>
       </c>
       <c r="F30" s="17">
-        <v>1.0955380818656758E-2</v>
+        <v>1.094156940291963E-2</v>
       </c>
       <c r="G30" s="17">
-        <v>0.64625641267057687</v>
+        <v>0.64549940897402491</v>
       </c>
       <c r="H30" s="17">
-        <v>21.366930623162162</v>
+        <v>21.354446636092216</v>
+      </c>
+      <c r="I30" s="17">
+        <v>0.34415283549829428</v>
+      </c>
+      <c r="J30" s="17">
+        <v>0.55975126890578497</v>
+      </c>
+      <c r="K30" s="17">
+        <v>0.26807615264009277</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -3763,16 +3877,31 @@
         <v>2.9</v>
       </c>
       <c r="C31" s="17">
-        <v>0.78545713890905311</v>
+        <v>0.78545713880957391</v>
       </c>
       <c r="D31" s="17">
-        <v>3.6615689659366422</v>
+        <v>3.6615689654728993</v>
       </c>
       <c r="E31" s="17">
-        <v>0.27310696843428062</v>
+        <v>0.27310696846887</v>
+      </c>
+      <c r="F31" s="17">
+        <v>1.0928430721673115E-2</v>
+      </c>
+      <c r="G31" s="17">
+        <v>0.64477927785490341</v>
       </c>
       <c r="H31" s="17">
-        <v>21.454286109094689</v>
+        <v>21.4542861190426</v>
+      </c>
+      <c r="I31" s="17">
+        <v>0.34609269486344429</v>
+      </c>
+      <c r="J31" s="17">
+        <v>0.56468232790516182</v>
+      </c>
+      <c r="K31" s="17">
+        <v>0.26990580548077292</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -3780,50 +3909,95 @@
         <v>3.1</v>
       </c>
       <c r="C32" s="17">
-        <v>0.78498342894401973</v>
+        <v>0.7849834296744499</v>
       </c>
       <c r="D32" s="17">
-        <v>3.6513110265144189</v>
+        <v>3.651311029911978</v>
       </c>
       <c r="E32" s="17">
-        <v>0.27387423112914344</v>
+        <v>0.2738742308743024</v>
+      </c>
+      <c r="F32" s="17">
+        <v>1.0919211198850547E-2</v>
+      </c>
+      <c r="G32" s="17">
+        <v>0.64427395580899849</v>
       </c>
       <c r="H32" s="17">
-        <v>21.501657105598028</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+        <v>21.501657032555009</v>
+      </c>
+      <c r="I32" s="17">
+        <v>0.34855819919645442</v>
+      </c>
+      <c r="J32" s="17">
+        <v>0.57006413642300191</v>
+      </c>
+      <c r="K32" s="17">
+        <v>0.27219139747597909</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="17">
         <v>3.3</v>
       </c>
       <c r="C33" s="17">
-        <v>0.78485342114049095</v>
+        <v>0.78485342122340596</v>
       </c>
       <c r="D33" s="17">
-        <v>3.6485095090614248</v>
+        <v>3.6485095094468676</v>
       </c>
       <c r="E33" s="17">
-        <v>0.27408452616511036</v>
+        <v>0.27408452613615497</v>
+      </c>
+      <c r="F33" s="17">
+        <v>1.0910511029656671E-2</v>
+      </c>
+      <c r="G33" s="17">
+        <v>0.64379709953548214</v>
       </c>
       <c r="H33" s="17">
-        <v>21.514657885950903</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+        <v>21.514657877659392</v>
+      </c>
+      <c r="I33" s="17">
+        <v>0.35097320608728932</v>
+      </c>
+      <c r="J33" s="17">
+        <v>0.57505965611498933</v>
+      </c>
+      <c r="K33" s="17">
+        <v>0.27438199685895309</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="17">
         <v>3.5</v>
       </c>
       <c r="C34" s="17">
-        <v>0.78496034991376151</v>
+        <v>0.78496034992155239</v>
       </c>
       <c r="D34" s="17">
-        <v>3.6508283721097383</v>
+        <v>3.6508283721459738</v>
       </c>
       <c r="E34" s="17">
-        <v>0.27391043841979368</v>
+        <v>0.27391043841707502</v>
+      </c>
+      <c r="F34" s="17">
+        <v>1.090316275126973E-2</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0.64339434039709387</v>
       </c>
       <c r="H34" s="17">
-        <v>21.503965008623858</v>
+        <v>21.503965007844748</v>
+      </c>
+      <c r="I34" s="17">
+        <v>0.35352644778452369</v>
+      </c>
+      <c r="J34" s="17">
+        <v>0.58007808048436504</v>
+      </c>
+      <c r="K34" s="17">
+        <v>0.27667135279187088</v>
       </c>
     </row>
   </sheetData>
@@ -3888,25 +4062,25 @@
         <v>41.852285461263897</v>
       </c>
       <c r="F3" s="17">
-        <v>15.24145462009974</v>
+        <v>15.224184069933031</v>
       </c>
       <c r="G3" s="17">
-        <v>40.291237071467492</v>
+        <v>40.244486029293242</v>
       </c>
       <c r="H3" s="17">
-        <v>59.727872168516029</v>
+        <v>58.846679079728716</v>
       </c>
       <c r="I3" s="17">
-        <v>58.546594548248024</v>
+        <v>57.394641330672847</v>
       </c>
       <c r="J3" s="17">
-        <v>54.171985391620581</v>
+        <v>26</v>
       </c>
       <c r="K3" s="17">
-        <v>0.14154461481035646</v>
+        <v>0.1387249120209072</v>
       </c>
       <c r="L3" s="17">
-        <v>1.2649393159814668</v>
+        <v>1.2397405267337387</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -3923,25 +4097,25 @@
         <v>44.933380647869939</v>
       </c>
       <c r="F4" s="17">
-        <v>16.442344008453379</v>
+        <v>16.426025261648309</v>
       </c>
       <c r="G4" s="17">
-        <v>43.458044213676864</v>
+        <v>43.413869684623059</v>
       </c>
       <c r="H4" s="17">
-        <v>59.735966243145022</v>
+        <v>58.855264463648282</v>
       </c>
       <c r="I4" s="17">
-        <v>58.554485160804404</v>
+        <v>57.403016403607651</v>
       </c>
       <c r="J4" s="17">
-        <v>54.163497220831061</v>
+        <v>26</v>
       </c>
       <c r="K4" s="17">
-        <v>0.14102710050591502</v>
+        <v>0.13821926232939638</v>
       </c>
       <c r="L4" s="17">
-        <v>1.2603144548297525</v>
+        <v>1.2352216958636071</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -3958,25 +4132,25 @@
         <v>47.714779598232759</v>
       </c>
       <c r="F5" s="17">
-        <v>17.526423384732322</v>
+        <v>17.510963835453079</v>
       </c>
       <c r="G5" s="17">
-        <v>46.316817277727253</v>
+        <v>46.274968579604028</v>
       </c>
       <c r="H5" s="17">
-        <v>59.744082530708894</v>
+        <v>58.863872564958399</v>
       </c>
       <c r="I5" s="17">
-        <v>58.562396729475942</v>
+        <v>57.41141363788779</v>
       </c>
       <c r="J5" s="17">
-        <v>54.154919475518398</v>
+        <v>26</v>
       </c>
       <c r="K5" s="17">
-        <v>0.1405095248648236</v>
+        <v>0.13771354476645351</v>
       </c>
       <c r="L5" s="17">
-        <v>1.2556890455318568</v>
+        <v>1.2307022584480201</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -3993,25 +4167,25 @@
         <v>50.238175942453665</v>
       </c>
       <c r="F6" s="17">
-        <v>18.509943306381878</v>
+        <v>18.495263231853045</v>
       </c>
       <c r="G6" s="17">
-        <v>48.91040982949049</v>
+        <v>48.870671154301007</v>
       </c>
       <c r="H6" s="17">
-        <v>59.75222116501245</v>
+        <v>58.87250352156601</v>
       </c>
       <c r="I6" s="17">
-        <v>58.570329377579746</v>
+        <v>57.419833168045585</v>
       </c>
       <c r="J6" s="17">
-        <v>54.146251392484373</v>
+        <v>26</v>
       </c>
       <c r="K6" s="17">
-        <v>0.13999188962571618</v>
+        <v>0.13720776102482798</v>
       </c>
       <c r="L6" s="17">
-        <v>1.2510631036254005</v>
+        <v>1.2261822296145422</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -4028,25 +4202,25 @@
         <v>52.537872183380308</v>
       </c>
       <c r="F7" s="17">
-        <v>19.40627355648672</v>
+        <v>19.392303833181266</v>
       </c>
       <c r="G7" s="17">
-        <v>51.27407868290198</v>
+        <v>51.236262914607892</v>
       </c>
       <c r="H7" s="17">
-        <v>59.760382281137382</v>
+        <v>58.881157472721988</v>
       </c>
       <c r="I7" s="17">
-        <v>58.57828322960458</v>
+        <v>57.428275129924344</v>
       </c>
       <c r="J7" s="17">
-        <v>54.137492201448424</v>
+        <v>26</v>
       </c>
       <c r="K7" s="17">
-        <v>0.13947419654295456</v>
+        <v>0.13670191281265232</v>
       </c>
       <c r="L7" s="17">
-        <v>1.2464366447885584</v>
+        <v>1.2216616246282117</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -4063,25 +4237,25 @@
         <v>54.642345188567177</v>
       </c>
       <c r="F8" s="17">
-        <v>20.226513368609627</v>
+        <v>20.213193673801996</v>
       </c>
       <c r="G8" s="17">
-        <v>53.437093089396768</v>
+        <v>53.401036935557514</v>
       </c>
       <c r="H8" s="17">
-        <v>59.768566025359505</v>
+        <v>58.889834571503116</v>
       </c>
       <c r="I8" s="17">
-        <v>58.586258420224183</v>
+        <v>57.436739672854706</v>
       </c>
       <c r="J8" s="17">
-        <v>54.128641048997849</v>
+        <v>26</v>
       </c>
       <c r="K8" s="17">
-        <v>0.13895644663801524</v>
+        <v>0.13619600112778463</v>
       </c>
       <c r="L8" s="17">
-        <v>1.2418096781499413</v>
+        <v>1.2171404524065699</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -4098,25 +4272,25 @@
         <v>56.575443092400867</v>
       </c>
       <c r="F9" s="17">
-        <v>20.979957694675662</v>
+        <v>20.967235070973341</v>
       </c>
       <c r="G9" s="17">
-        <v>55.423964332470618</v>
+        <v>55.389524438458395</v>
       </c>
       <c r="H9" s="17">
-        <v>59.77677251407335</v>
+        <v>58.898534933099697</v>
       </c>
       <c r="I9" s="17">
-        <v>58.594255056971043</v>
+        <v>57.445226909208898</v>
       </c>
       <c r="J9" s="17">
-        <v>54.119697313632969</v>
+        <v>26</v>
       </c>
       <c r="K9" s="17">
-        <v>0.13843864330880659</v>
+        <v>0.13569002927177837</v>
       </c>
       <c r="L9" s="17">
-        <v>1.2371822340755787</v>
+        <v>1.2126187424545529</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -4219,10 +4393,10 @@
         <v>91.682455189337773</v>
       </c>
       <c r="M16" s="17">
-        <v>2.2662069549226316</v>
+        <v>3.1149417500136498</v>
       </c>
       <c r="N16" s="17">
-        <v>1.4262431534888216</v>
+        <v>2.4590399198083133</v>
       </c>
       <c r="O16" s="17">
         <v>10.362045100531315</v>
@@ -4237,16 +4411,16 @@
         <v>0.92839153384896267</v>
       </c>
       <c r="S16" s="17">
-        <v>3.5804149179434662E-2</v>
+        <v>-1.8437574346038494</v>
       </c>
       <c r="T16" s="17">
         <v>531.13824794622963</v>
       </c>
       <c r="U16" s="17">
-        <v>3.2391739055063429</v>
+        <v>3.3293594659212076</v>
       </c>
       <c r="V16" s="17">
-        <v>450.16388748403097</v>
+        <v>450.25604302207307</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -4284,10 +4458,10 @@
         <v>96.731337537772518</v>
       </c>
       <c r="M17" s="17">
-        <v>2.267758230379429</v>
+        <v>3.1154534616739804</v>
       </c>
       <c r="N17" s="17">
-        <v>1.4290732685411747</v>
+        <v>2.4639194285192669</v>
       </c>
       <c r="O17" s="17">
         <v>10.306141862922569</v>
@@ -4302,16 +4476,16 @@
         <v>0.92399223502528893</v>
       </c>
       <c r="S17" s="17">
-        <v>3.3917216413731265E-2</v>
+        <v>-1.8466625091399864</v>
       </c>
       <c r="T17" s="17">
         <v>559.75204088293515</v>
       </c>
       <c r="U17" s="17">
-        <v>3.2262748683101767</v>
+        <v>3.3160809731247927</v>
       </c>
       <c r="V17" s="17">
-        <v>467.69459668183288</v>
+        <v>467.78636445236623</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -4349,10 +4523,10 @@
         <v>101.79288253725483</v>
       </c>
       <c r="M18" s="17">
-        <v>2.2693067979055233</v>
+        <v>3.1159523417777462</v>
       </c>
       <c r="N18" s="17">
-        <v>1.4319114292205222</v>
+        <v>2.4688128090009003</v>
       </c>
       <c r="O18" s="17">
         <v>10.250323800790419</v>
@@ -4367,16 +4541,16 @@
         <v>0.91960136568056761</v>
       </c>
       <c r="S18" s="17">
-        <v>3.2013777684334971E-2</v>
+        <v>-1.8495797963152276</v>
       </c>
       <c r="T18" s="17">
         <v>588.36612863704318</v>
       </c>
       <c r="U18" s="17">
-        <v>3.2133796689570824</v>
+        <v>3.3028065358073517</v>
       </c>
       <c r="V18" s="17">
-        <v>485.22557923090994</v>
+        <v>485.31695944741341</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -4414,10 +4588,10 @@
         <v>106.86721213527193</v>
       </c>
       <c r="M19" s="17">
-        <v>2.2708525914225359</v>
+        <v>3.1164382479094836</v>
       </c>
       <c r="N19" s="17">
-        <v>1.4347576515796336</v>
+        <v>2.4737200889304032</v>
       </c>
       <c r="O19" s="17">
         <v>10.194591485539634</v>
@@ -4432,16 +4606,16 @@
         <v>0.91521892164972585</v>
       </c>
       <c r="S19" s="17">
-        <v>3.0093731055990471E-2</v>
+        <v>-1.8525093332924134</v>
       </c>
       <c r="T19" s="17">
         <v>616.98051201500505</v>
       </c>
       <c r="U19" s="17">
-        <v>3.2004883620793869</v>
+        <v>3.2895362100393175</v>
       </c>
       <c r="V19" s="17">
-        <v>502.75683578569931</v>
+        <v>502.84782866314856</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -4479,10 +4653,10 @@
         <v>111.95445016030466</v>
       </c>
       <c r="M20" s="17">
-        <v>2.2723955440679502</v>
+        <v>3.1169110362992152</v>
       </c>
       <c r="N20" s="17">
-        <v>1.4376119516228376</v>
+        <v>2.4786412959014443</v>
       </c>
       <c r="O20" s="17">
         <v>10.138945489990787</v>
@@ -4497,16 +4671,16 @@
         <v>0.91084489976972427</v>
       </c>
       <c r="S20" s="17">
-        <v>2.815697403019336E-2</v>
+        <v>-1.8554511571884387</v>
       </c>
       <c r="T20" s="17">
         <v>645.59519182583927</v>
       </c>
       <c r="U20" s="17">
-        <v>3.1876010027004567</v>
+        <v>3.2762700522924897</v>
       </c>
       <c r="V20" s="17">
-        <v>520.28836700236388</v>
+        <v>520.37897275724754</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -4544,10 +4718,10 @@
         <v>117.05472843049664</v>
       </c>
       <c r="M21" s="17">
-        <v>2.2739355842054483</v>
+        <v>3.1173705524792377</v>
       </c>
       <c r="N21" s="17">
-        <v>1.4404743453062181</v>
+        <v>2.4835764574245141</v>
       </c>
       <c r="O21" s="17">
         <v>10.083386332505116</v>
@@ -4562,16 +4736,16 @@
         <v>0.90647929000459382</v>
       </c>
       <c r="S21" s="17">
-        <v>2.620338680930415E-2</v>
+        <v>-1.8584053164823766</v>
       </c>
       <c r="T21" s="17">
         <v>674.21020227485337</v>
       </c>
       <c r="U21" s="17">
-        <v>3.1747176279460891</v>
+        <v>3.2630081004215148</v>
       </c>
       <c r="V21" s="17">
-        <v>537.82020717123009</v>
+        <v>537.91042602080574</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -4609,10 +4783,10 @@
         <v>122.16816161023768</v>
       </c>
       <c r="M22" s="17">
-        <v>2.2754726519311625</v>
+        <v>3.117816669947155</v>
       </c>
       <c r="N22" s="17">
-        <v>1.4433448485363372</v>
+        <v>2.4885256009247194</v>
       </c>
       <c r="O22" s="17">
         <v>10.027914709061532</v>
@@ -4627,16 +4801,16 @@
         <v>0.902122100229935</v>
       </c>
       <c r="S22" s="17">
-        <v>2.4232901724251073E-2</v>
+        <v>-1.8613718236550516</v>
       </c>
       <c r="T22" s="17">
         <v>702.82547232081004</v>
       </c>
       <c r="U22" s="17">
-        <v>3.1618383330094</v>
+        <v>3.2497504526612584</v>
       </c>
       <c r="V22" s="17">
-        <v>555.35228458286076</v>
+        <v>555.4421167475374</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -4667,22 +4841,31 @@
         <v>0.6</v>
       </c>
       <c r="C29" s="17">
-        <v>0.84754560460425321</v>
+        <v>0.84771911035044722</v>
       </c>
       <c r="D29" s="17">
-        <v>5.5607921010803549</v>
+        <v>5.5682400216419365</v>
       </c>
       <c r="E29" s="17">
-        <v>0.17983049569605727</v>
+        <v>0.17958995950485709</v>
       </c>
       <c r="F29" s="17">
-        <v>1.0931033749141028E-2</v>
+        <v>1.0912725075627298E-2</v>
       </c>
       <c r="G29" s="17">
-        <v>0.64492194979041984</v>
+        <v>0.64391845139513226</v>
       </c>
       <c r="H29" s="17">
-        <v>15.245439539574679</v>
+        <v>15.228088964955266</v>
+      </c>
+      <c r="I29" s="17">
+        <v>0.19083273687724442</v>
+      </c>
+      <c r="J29" s="17">
+        <v>0.24494005524217421</v>
+      </c>
+      <c r="K29" s="17">
+        <v>8.6858968078692311E-2</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -4690,22 +4873,31 @@
         <v>0.65</v>
       </c>
       <c r="C30" s="17">
-        <v>0.83553888601121706</v>
+        <v>0.83570282962165687</v>
       </c>
       <c r="D30" s="17">
-        <v>5.0816287846893831</v>
+        <v>5.0876752976440773</v>
       </c>
       <c r="E30" s="17">
-        <v>0.19678729839789458</v>
+        <v>0.19655342400940262</v>
       </c>
       <c r="F30" s="17">
-        <v>1.0935217351420626E-2</v>
+        <v>1.0917832748512973E-2</v>
       </c>
       <c r="G30" s="17">
-        <v>0.64515125303136456</v>
+        <v>0.64419840294599606</v>
       </c>
       <c r="H30" s="17">
-        <v>16.446111398878294</v>
+        <v>16.429717037834322</v>
+      </c>
+      <c r="I30" s="17">
+        <v>0.17425836060946925</v>
+      </c>
+      <c r="J30" s="17">
+        <v>0.23053244101116269</v>
+      </c>
+      <c r="K30" s="17">
+        <v>7.860907429569669E-2</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -4713,22 +4905,31 @@
         <v>0.7</v>
       </c>
       <c r="C31" s="17">
-        <v>0.82470005599224505</v>
+        <v>0.82485536781604962</v>
       </c>
       <c r="D31" s="17">
-        <v>4.7054669277855092</v>
+        <v>4.7105080883442261</v>
       </c>
       <c r="E31" s="17">
-        <v>0.21251876069833964</v>
+        <v>0.21229132425744468</v>
       </c>
       <c r="F31" s="17">
-        <v>1.0938986786365809E-2</v>
+        <v>1.0922427251248833E-2</v>
       </c>
       <c r="G31" s="17">
-        <v>0.64535785576071003</v>
+        <v>0.6444502276409485</v>
       </c>
       <c r="H31" s="17">
-        <v>17.529994400775493</v>
+        <v>17.514463218395036</v>
+      </c>
+      <c r="I31" s="17">
+        <v>0.16132366298600376</v>
+      </c>
+      <c r="J31" s="17">
+        <v>0.21924753851545725</v>
+      </c>
+      <c r="K31" s="17">
+        <v>7.2149608613530661E-2</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -4736,91 +4937,127 @@
         <v>0.75</v>
       </c>
       <c r="C32" s="17">
-        <v>0.81486663840279006</v>
+        <v>0.81501411936155166</v>
       </c>
       <c r="D32" s="17">
-        <v>4.4023183913363981</v>
+        <v>4.4066100014078859</v>
       </c>
       <c r="E32" s="17">
-        <v>0.22715303871886311</v>
+        <v>0.22693181372540477</v>
       </c>
       <c r="F32" s="17">
-        <v>1.0942396324374062E-2</v>
+        <v>1.0926582439557082E-2</v>
       </c>
       <c r="G32" s="17">
-        <v>0.6455447325389424</v>
+        <v>0.64467797351212375</v>
       </c>
       <c r="H32" s="17">
-        <v>18.513336159721007</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+        <v>18.498588063844835</v>
+      </c>
+      <c r="I32" s="17">
+        <v>0.15102741645822146</v>
+      </c>
+      <c r="J32" s="17">
+        <v>0.21030068848842684</v>
+      </c>
+      <c r="K32" s="17">
+        <v>6.70308002978134E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="17">
         <v>0.8</v>
       </c>
       <c r="C33" s="17">
-        <v>0.80590495962479369</v>
+        <v>0.8060453041565232</v>
       </c>
       <c r="D33" s="17">
-        <v>4.1528063452213511</v>
+        <v>4.1565216339965589</v>
       </c>
       <c r="E33" s="17">
-        <v>0.24080101908693707</v>
+        <v>0.24058578014388554</v>
       </c>
       <c r="F33" s="17">
-        <v>1.0945495411489195E-2</v>
+        <v>1.0930358656320624E-2</v>
       </c>
       <c r="G33" s="17">
-        <v>0.64571459350372284</v>
+        <v>0.64488494795293339</v>
       </c>
       <c r="H33" s="17">
-        <v>19.409504037520641</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+        <v>19.39546958434768</v>
+      </c>
+      <c r="I33" s="17">
+        <v>0.14280424748686651</v>
+      </c>
+      <c r="J33" s="17">
+        <v>0.2033162158912975</v>
+      </c>
+      <c r="K33" s="17">
+        <v>6.3037490439127375E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="17">
         <v>0.85</v>
       </c>
       <c r="C34" s="17">
-        <v>0.79770404742700474</v>
+        <v>0.79783786155392133</v>
       </c>
       <c r="D34" s="17">
-        <v>3.9438534605029605</v>
+        <v>3.947114317654743</v>
       </c>
       <c r="E34" s="17">
-        <v>0.25355911674072945</v>
+        <v>0.25334964217458239</v>
       </c>
       <c r="F34" s="17">
-        <v>1.0948324843076037E-2</v>
+        <v>1.0933805686844236E-2</v>
       </c>
       <c r="G34" s="17">
-        <v>0.64586967464899758</v>
+        <v>0.64507387969593255</v>
       </c>
       <c r="H34" s="17">
-        <v>20.229595257299525</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+        <v>20.216213844607868</v>
+      </c>
+      <c r="I34" s="17">
+        <v>0.13658193790215301</v>
+      </c>
+      <c r="J34" s="17">
+        <v>0.19856393313649451</v>
+      </c>
+      <c r="K34" s="17">
+        <v>6.032514312375873E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="17">
         <v>0.9</v>
       </c>
       <c r="C35" s="17">
-        <v>0.7901709691155957</v>
+        <v>0.79029878486532934</v>
       </c>
       <c r="D35" s="17">
-        <v>3.7663134531302083</v>
+        <v>3.7692083967685592</v>
       </c>
       <c r="E35" s="17">
-        <v>0.26551162361934938</v>
+        <v>0.26530769719639968</v>
       </c>
       <c r="F35" s="17">
-        <v>1.095091857991398E-2</v>
+        <v>1.0936964974842374E-2</v>
       </c>
       <c r="G35" s="17">
-        <v>0.64601183736508527</v>
+        <v>0.64524704027111057</v>
       </c>
       <c r="H35" s="17">
-        <v>20.98290308844043</v>
+        <v>20.970121513467056</v>
+      </c>
+      <c r="I35" s="17">
+        <v>0.13498053449446543</v>
+      </c>
+      <c r="J35" s="17">
+        <v>0.20078538147008768</v>
+      </c>
+      <c r="K35" s="17">
+        <v>6.1618112153100937E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4885,25 +5122,25 @@
         <v>49.878796554537026</v>
       </c>
       <c r="F3" s="17">
-        <v>18.37326690227815</v>
+        <v>18.373195861739831</v>
       </c>
       <c r="G3" s="17">
-        <v>48.550442064273085</v>
+        <v>48.55024975892259</v>
       </c>
       <c r="H3" s="17">
-        <v>59.943515535314361</v>
+        <v>59.939503250288105</v>
       </c>
       <c r="I3" s="17">
-        <v>58.920654666082875</v>
+        <v>58.915291415536807</v>
       </c>
       <c r="J3" s="17">
-        <v>70.612173722288844</v>
+        <v>70.467849346491846</v>
       </c>
       <c r="K3" s="17">
-        <v>0.1597339979473</v>
+        <v>0.15971887375195662</v>
       </c>
       <c r="L3" s="17">
-        <v>1.4274920622953922</v>
+        <v>1.4273569021599251</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -4920,25 +5157,25 @@
         <v>51.771991448655704</v>
       </c>
       <c r="F4" s="17">
-        <v>19.112085785005224</v>
+        <v>19.112016134944927</v>
       </c>
       <c r="G4" s="17">
-        <v>50.498776994288662</v>
+        <v>50.498588452935046</v>
       </c>
       <c r="H4" s="17">
-        <v>60.021929404349727</v>
+        <v>60.017837430327823</v>
       </c>
       <c r="I4" s="17">
-        <v>59.000938788462065</v>
+        <v>58.995465876775796</v>
       </c>
       <c r="J4" s="17">
-        <v>70.881080313060295</v>
+        <v>70.733893942291786</v>
       </c>
       <c r="K4" s="17">
-        <v>0.15497245314779157</v>
+        <v>0.15495749590016775</v>
       </c>
       <c r="L4" s="17">
-        <v>1.3849396470744026</v>
+        <v>1.3848059788977394</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -4955,25 +5192,25 @@
         <v>53.3638629940382</v>
       </c>
       <c r="F5" s="17">
-        <v>19.733339335790927</v>
+        <v>19.733270889997033</v>
       </c>
       <c r="G5" s="17">
-        <v>52.137073147294522</v>
+        <v>52.13688786586652</v>
       </c>
       <c r="H5" s="17">
-        <v>60.090302237082973</v>
+        <v>60.08613937444035</v>
       </c>
       <c r="I5" s="17">
-        <v>59.070937879496412</v>
+        <v>59.065367664064738</v>
       </c>
       <c r="J5" s="17">
-        <v>71.113947469750883</v>
+        <v>70.964246217707341</v>
       </c>
       <c r="K5" s="17">
-        <v>0.15091214122040969</v>
+        <v>0.15089733089748819</v>
       </c>
       <c r="L5" s="17">
-        <v>1.3486539275578022</v>
+        <v>1.3485215724005901</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -4990,25 +5227,25 @@
         <v>54.719894700628537</v>
       </c>
       <c r="F6" s="17">
-        <v>20.262571228369076</v>
+        <v>20.26250383624782</v>
       </c>
       <c r="G6" s="17">
-        <v>53.532694818694651</v>
+        <v>53.532512389537942</v>
       </c>
       <c r="H6" s="17">
-        <v>60.150427663242837</v>
+        <v>60.146201421712384</v>
       </c>
       <c r="I6" s="17">
-        <v>59.132490246883762</v>
+        <v>59.126833228739414</v>
       </c>
       <c r="J6" s="17">
-        <v>71.317527543858375</v>
+        <v>71.165602215361275</v>
       </c>
       <c r="K6" s="17">
-        <v>0.1474116636772683</v>
+        <v>0.1473969837068114</v>
       </c>
       <c r="L6" s="17">
-        <v>1.3173712703195719</v>
+        <v>1.3172400800809798</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -5025,25 +5262,25 @@
         <v>55.888023789679387</v>
       </c>
       <c r="F7" s="17">
-        <v>20.718482595841238</v>
+        <v>20.718416133758716</v>
       </c>
       <c r="G7" s="17">
-        <v>54.734960628953523</v>
+        <v>54.734780717393491</v>
       </c>
       <c r="H7" s="17">
-        <v>60.203698420323029</v>
+        <v>60.199415246228241</v>
       </c>
       <c r="I7" s="17">
-        <v>59.187023139449423</v>
+        <v>59.18128830008709</v>
       </c>
       <c r="J7" s="17">
-        <v>71.497000293469625</v>
+        <v>71.343096511252043</v>
       </c>
       <c r="K7" s="17">
-        <v>0.14436476998212663</v>
+        <v>0.14435020648564711</v>
       </c>
       <c r="L7" s="17">
-        <v>1.290142148026473</v>
+        <v>1.2900119986788643</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -5060,25 +5297,25 @@
         <v>56.904129154565311</v>
       </c>
       <c r="F8" s="17">
-        <v>21.115071451650476</v>
+        <v>21.115005816784862</v>
       </c>
       <c r="G8" s="17">
-        <v>55.780785889614293</v>
+        <v>55.780608217314288</v>
       </c>
       <c r="H8" s="17">
-        <v>60.251212163917998</v>
+        <v>60.246877622003723</v>
       </c>
       <c r="I8" s="17">
-        <v>59.235661246611436</v>
+        <v>59.229856314830073</v>
       </c>
       <c r="J8" s="17">
-        <v>71.656400152541778</v>
+        <v>71.500726935586954</v>
       </c>
       <c r="K8" s="17">
-        <v>0.14169016867382303</v>
+        <v>0.14167570990752862</v>
       </c>
       <c r="L8" s="17">
-        <v>1.2662400846807105</v>
+        <v>1.2661108712735394</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -5095,25 +5332,25 @@
         <v>57.795583221044957</v>
       </c>
       <c r="F9" s="17">
-        <v>21.46301763766137</v>
+        <v>21.462952743531002</v>
       </c>
       <c r="G9" s="17">
-        <v>56.698335130922949</v>
+        <v>56.698159463778808</v>
       </c>
       <c r="H9" s="17">
-        <v>60.293845462383622</v>
+        <v>60.289464382137304</v>
       </c>
       <c r="I9" s="17">
-        <v>59.279302589852165</v>
+        <v>59.273434254686372</v>
       </c>
       <c r="J9" s="17">
-        <v>71.798913319337885</v>
+        <v>71.641649768227524</v>
       </c>
       <c r="K9" s="17">
-        <v>0.13932466740652216</v>
+        <v>0.13931030334092001</v>
       </c>
       <c r="L9" s="17">
-        <v>1.2451003503360174</v>
+        <v>1.2449719832388881</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -5216,10 +5453,10 @@
         <v>120.25045822234905</v>
       </c>
       <c r="M16" s="17">
-        <v>2.9125156004621573E-2</v>
+        <v>5.0117925165671998E-2</v>
       </c>
       <c r="N16" s="17">
-        <v>1.3292337592230991E-2</v>
+        <v>2.291782343488102E-2</v>
       </c>
       <c r="O16" s="17">
         <v>12.258929861073378</v>
@@ -5234,16 +5471,16 @@
         <v>1.0776192924360903</v>
       </c>
       <c r="S16" s="17">
-        <v>3.5350848909872137</v>
+        <v>3.5044989063272931</v>
       </c>
       <c r="T16" s="17">
         <v>692.59037147487402</v>
       </c>
       <c r="U16" s="17">
-        <v>3.5990801600825222</v>
+        <v>3.5995421709049547</v>
       </c>
       <c r="V16" s="17">
-        <v>565.31501258162234</v>
+        <v>565.3155068627882</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -5281,10 +5518,10 @@
         <v>121.34712487858563</v>
       </c>
       <c r="M17" s="17">
-        <v>2.9507436703505269E-2</v>
+        <v>5.077422903846187E-2</v>
       </c>
       <c r="N17" s="17">
-        <v>1.3556700606306121E-2</v>
+        <v>2.3373621735010557E-2</v>
       </c>
       <c r="O17" s="17">
         <v>11.70689884570481</v>
@@ -5299,16 +5536,16 @@
         <v>1.0337214813555018</v>
       </c>
       <c r="S17" s="17">
-        <v>3.5735072492326818</v>
+        <v>3.5424556315454323</v>
       </c>
       <c r="T17" s="17">
         <v>698.61933690745582</v>
       </c>
       <c r="U17" s="17">
-        <v>3.4801513263757968</v>
+        <v>3.48060805566681</v>
       </c>
       <c r="V17" s="17">
-        <v>565.07544040995276</v>
+        <v>565.07592923502034</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -5346,10 +5583,10 @@
         <v>122.31369926104054</v>
       </c>
       <c r="M18" s="17">
-        <v>2.9839777350717973E-2</v>
+        <v>5.134475467344897E-2</v>
       </c>
       <c r="N18" s="17">
-        <v>1.3787668106995304E-2</v>
+        <v>2.377184156378501E-2</v>
       </c>
       <c r="O18" s="17">
         <v>11.242094633094244</v>
@@ -5364,16 +5601,16 @@
         <v>0.99701597907764994</v>
       </c>
       <c r="S18" s="17">
-        <v>3.6061916584211962</v>
+        <v>3.5747344392650797</v>
       </c>
       <c r="T18" s="17">
         <v>703.92789882574857</v>
       </c>
       <c r="U18" s="17">
-        <v>3.3791102132127113</v>
+        <v>3.379562304940662</v>
       </c>
       <c r="V18" s="17">
-        <v>564.99685540020596</v>
+        <v>564.99733942355761</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -5411,10 +5648,10 @@
         <v>123.1726580633815</v>
       </c>
       <c r="M19" s="17">
-        <v>3.0131298657467248E-2</v>
+        <v>5.1845176613273189E-2</v>
       </c>
       <c r="N19" s="17">
-        <v>1.3991130550860853E-2</v>
+        <v>2.4122638880794574E-2</v>
       </c>
       <c r="O19" s="17">
         <v>10.845814830466487</v>
@@ -5429,16 +5666,16 @@
         <v>0.96589147864161762</v>
       </c>
       <c r="S19" s="17">
-        <v>3.6343805860073322</v>
+        <v>3.6025669776936748</v>
       </c>
       <c r="T19" s="17">
         <v>708.64131735875878</v>
       </c>
       <c r="U19" s="17">
-        <v>3.29227958568387</v>
+        <v>3.2927275709515644</v>
       </c>
       <c r="V19" s="17">
-        <v>565.03032655118056</v>
+        <v>565.03080631442015</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -5476,10 +5713,10 @@
         <v>123.94142024869507</v>
       </c>
       <c r="M20" s="17">
-        <v>3.0389051278727968E-2</v>
+        <v>5.2287609979356685E-2</v>
       </c>
       <c r="N20" s="17">
-        <v>1.417168993703463E-2</v>
+        <v>2.4433948167301087E-2</v>
       </c>
       <c r="O20" s="17">
         <v>10.504258527002829</v>
@@ -5494,16 +5731,16 @@
         <v>0.93918089232948121</v>
       </c>
       <c r="S20" s="17">
-        <v>3.6589857819692497</v>
+        <v>3.6268565995228084</v>
       </c>
       <c r="T20" s="17">
         <v>712.85651826449589</v>
       </c>
       <c r="U20" s="17">
-        <v>3.2169127715262071</v>
+        <v>3.2173570937397304</v>
       </c>
       <c r="V20" s="17">
-        <v>565.14188100320121</v>
+        <v>565.14235695989919</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -5541,10 +5778,10 @@
         <v>124.63373733801447</v>
       </c>
       <c r="M21" s="17">
-        <v>3.0618563448657987E-2</v>
+        <v>5.2681552572014054E-2</v>
       </c>
       <c r="N21" s="17">
-        <v>1.4332987176605571E-2</v>
+        <v>2.4712046856216502E-2</v>
       </c>
       <c r="O21" s="17">
         <v>10.207040222168093</v>
@@ -5559,16 +5796,16 @@
         <v>0.91601886380869246</v>
       </c>
       <c r="S21" s="17">
-        <v>3.6806886285269229</v>
+        <v>3.648278080330789</v>
       </c>
       <c r="T21" s="17">
         <v>716.64991370765188</v>
       </c>
       <c r="U21" s="17">
-        <v>3.1509193724350624</v>
+        <v>3.1513604057888163</v>
       </c>
       <c r="V21" s="17">
-        <v>565.30758865108601</v>
+        <v>565.30806118504643</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -5606,10 +5843,10 @@
         <v>125.26063692308392</v>
       </c>
       <c r="M22" s="17">
-        <v>3.0824226425290625E-2</v>
+        <v>5.3034547836876195E-2</v>
       </c>
       <c r="N22" s="17">
-        <v>1.4477936858931504E-2</v>
+        <v>2.4961960101606045E-2</v>
       </c>
       <c r="O22" s="17">
         <v>9.9462077370741646</v>
@@ -5624,16 +5861,16 @@
         <v>0.89575064737944088</v>
       </c>
       <c r="S22" s="17">
-        <v>3.7000071016729259</v>
+        <v>3.6673441327121901</v>
       </c>
       <c r="T22" s="17">
         <v>720.08270193706414</v>
       </c>
       <c r="U22" s="17">
-        <v>3.0926819958197846</v>
+        <v>3.0931200591283474</v>
       </c>
       <c r="V22" s="17">
-        <v>565.51039455519515</v>
+        <v>565.51086399419739</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -5664,22 +5901,31 @@
         <v>0.6</v>
       </c>
       <c r="C29" s="17">
-        <v>0.81623284969697418</v>
+        <v>0.8162335633672565</v>
       </c>
       <c r="D29" s="17">
-        <v>4.4425025448020206</v>
+        <v>4.4425236061787903</v>
       </c>
       <c r="E29" s="17">
-        <v>0.22509835164192682</v>
+        <v>0.22509728448244395</v>
       </c>
       <c r="F29" s="17">
-        <v>1.0904297235548702E-2</v>
+        <v>1.0904188357996744E-2</v>
       </c>
       <c r="G29" s="17">
-        <v>0.64345652148042443</v>
+        <v>0.6434505539018015</v>
       </c>
       <c r="H29" s="17">
-        <v>18.376715030302581</v>
+        <v>18.376643663274361</v>
+      </c>
+      <c r="I29" s="17">
+        <v>0.41341597674628905</v>
+      </c>
+      <c r="J29" s="17">
+        <v>0.63345210941471208</v>
+      </c>
+      <c r="K29" s="17">
+        <v>0.31969789321370906</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -5687,22 +5933,31 @@
         <v>0.65</v>
       </c>
       <c r="C30" s="17">
-        <v>0.80884597742648334</v>
+        <v>0.80884667712808289</v>
       </c>
       <c r="D30" s="17">
-        <v>4.232117763206567</v>
+        <v>4.2321368474002377</v>
       </c>
       <c r="E30" s="17">
-        <v>0.23628832087184778</v>
+        <v>0.23628725536469614</v>
       </c>
       <c r="F30" s="17">
-        <v>1.0918775274592729E-2</v>
+        <v>1.0918648791163528E-2</v>
       </c>
       <c r="G30" s="17">
-        <v>0.64425006280042751</v>
+        <v>0.64424313024367297</v>
       </c>
       <c r="H30" s="17">
-        <v>19.115402257351665</v>
+        <v>19.115332287191698</v>
+      </c>
+      <c r="I30" s="17">
+        <v>0.39444410274120173</v>
+      </c>
+      <c r="J30" s="17">
+        <v>0.60791796695278866</v>
+      </c>
+      <c r="K30" s="17">
+        <v>0.30513582323874583</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -5710,22 +5965,31 @@
         <v>0.7</v>
       </c>
       <c r="C31" s="17">
-        <v>0.80263455439498943</v>
+        <v>0.80263524199858138</v>
       </c>
       <c r="D31" s="17">
-        <v>4.0674035992439865</v>
+        <v>4.067421191716595</v>
       </c>
       <c r="E31" s="17">
-        <v>0.24585708686147381</v>
+        <v>0.24585602347662569</v>
       </c>
       <c r="F31" s="17">
-        <v>1.0931116707946399E-2</v>
+        <v>1.0931188260214096E-2</v>
       </c>
       <c r="G31" s="17">
-        <v>0.6449264967625421</v>
+        <v>0.64493041854233468</v>
       </c>
       <c r="H31" s="17">
-        <v>19.736544560501045</v>
+        <v>19.736475800141861</v>
+      </c>
+      <c r="I31" s="17">
+        <v>0.37952324743581139</v>
+      </c>
+      <c r="J31" s="17">
+        <v>0.58777374945280458</v>
+      </c>
+      <c r="K31" s="17">
+        <v>0.29365788683812383</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -5733,91 +5997,127 @@
         <v>0.75</v>
       </c>
       <c r="C32" s="17">
-        <v>0.79734318718128983</v>
+        <v>0.79734386419973036</v>
       </c>
       <c r="D32" s="17">
-        <v>3.9350543334053838</v>
+        <v>3.9350707624462138</v>
       </c>
       <c r="E32" s="17">
-        <v>0.25412609719536022</v>
+        <v>0.25412503621112925</v>
       </c>
       <c r="F32" s="17">
-        <v>1.0944911564070405E-2</v>
+        <v>1.0944766551039004E-2</v>
       </c>
       <c r="G32" s="17">
-        <v>0.64568259282669893</v>
+        <v>0.64567464466244784</v>
       </c>
       <c r="H32" s="17">
-        <v>20.265681281871029</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+        <v>20.265613580026965</v>
+      </c>
+      <c r="I32" s="17">
+        <v>0.36787790493733269</v>
+      </c>
+      <c r="J32" s="17">
+        <v>0.57211390257334793</v>
+      </c>
+      <c r="K32" s="17">
+        <v>0.28475653286847541</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="17">
         <v>0.8</v>
       </c>
       <c r="C33" s="17">
-        <v>0.79278489643200944</v>
+        <v>0.79278556410732104</v>
       </c>
       <c r="D33" s="17">
-        <v>3.8264621589186407</v>
+        <v>3.82647765634725</v>
       </c>
       <c r="E33" s="17">
-        <v>0.26133800844448968</v>
+        <v>0.2613369500122989</v>
       </c>
       <c r="F33" s="17">
-        <v>1.0954575512681711E-2</v>
+        <v>1.0953771658947358E-2</v>
       </c>
       <c r="G33" s="17">
-        <v>0.64621227385008462</v>
+        <v>0.64616821462690466</v>
       </c>
       <c r="H33" s="17">
-        <v>20.721510356799055</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+        <v>20.721443589267896</v>
+      </c>
+      <c r="I33" s="17">
+        <v>0.35781457444009379</v>
+      </c>
+      <c r="J33" s="17">
+        <v>0.55836368955805793</v>
+      </c>
+      <c r="K33" s="17">
+        <v>0.27692740932168425</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="17">
         <v>0.85</v>
       </c>
       <c r="C34" s="17">
-        <v>0.7888197261148292</v>
+        <v>0.78882038547995503</v>
       </c>
       <c r="D34" s="17">
-        <v>3.7358136718650345</v>
+        <v>3.7358284071743015</v>
       </c>
       <c r="E34" s="17">
-        <v>0.26767930304745868</v>
+        <v>0.26767824723415978</v>
       </c>
       <c r="F34" s="17">
-        <v>1.0963902842859219E-2</v>
+        <v>1.0963939440872789E-2</v>
       </c>
       <c r="G34" s="17">
-        <v>0.64672350481711383</v>
+        <v>0.64672551075423756</v>
       </c>
       <c r="H34" s="17">
-        <v>21.118027388517071</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+        <v>21.117961452004497</v>
+      </c>
+      <c r="I34" s="17">
+        <v>0.3499049978620189</v>
+      </c>
+      <c r="J34" s="17">
+        <v>0.54760892323226329</v>
+      </c>
+      <c r="K34" s="17">
+        <v>0.27082626625832856</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="17">
         <v>0.9</v>
       </c>
       <c r="C35" s="17">
-        <v>0.78534089630807602</v>
+        <v>0.7853415482318078</v>
       </c>
       <c r="D35" s="17">
-        <v>3.6590423097357503</v>
+        <v>3.6590564104396681</v>
       </c>
       <c r="E35" s="17">
-        <v>0.27329555532584654</v>
+        <v>0.27329450214183526</v>
       </c>
       <c r="F35" s="17">
-        <v>1.0972643120066438E-2</v>
+        <v>1.0972466052867792E-2</v>
       </c>
       <c r="G35" s="17">
-        <v>0.64720255941084148</v>
+        <v>0.6471928543576837</v>
       </c>
       <c r="H35" s="17">
-        <v>21.465910369192386</v>
+        <v>21.465845176819208</v>
+      </c>
+      <c r="I35" s="17">
+        <v>0.34514380975417347</v>
+      </c>
+      <c r="J35" s="17">
+        <v>0.54174875250287391</v>
+      </c>
+      <c r="K35" s="17">
+        <v>0.26759067296811734</v>
       </c>
     </row>
   </sheetData>
@@ -5866,18 +6166,18 @@
       <c r="I2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="30"/>
-      <c r="N2" s="30" t="s">
+      <c r="L2" s="31"/>
+      <c r="N2" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="O2" s="30"/>
-      <c r="Q2" s="30" t="s">
+      <c r="O2" s="31"/>
+      <c r="Q2" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="R2" s="30"/>
+      <c r="R2" s="31"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -5966,7 +6266,7 @@
         <v>98</v>
       </c>
       <c r="R4" s="6">
-        <v>336.14916869494635</v>
+        <v>320.86966102699427</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
@@ -6011,7 +6311,7 @@
         <v>99</v>
       </c>
       <c r="R5" s="6">
-        <v>285.89368248336706</v>
+        <v>272.89851509775946</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
@@ -6056,7 +6356,7 @@
         <v>100</v>
       </c>
       <c r="R6" s="6">
-        <v>1688.3683157601977</v>
+        <v>1611.6243014074614</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -6101,7 +6401,7 @@
         <v>105</v>
       </c>
       <c r="R7" s="6">
-        <v>884.52935792049959</v>
+        <v>844.32347801502237</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
@@ -6146,7 +6446,7 @@
         <v>104</v>
       </c>
       <c r="R8" s="6">
-        <v>259.69048700602229</v>
+        <v>191.51030050030806</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
@@ -6191,7 +6491,7 @@
         <v>101</v>
       </c>
       <c r="R9" s="6">
-        <v>-6.7709153400709399</v>
+        <v>106.29532049093429</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
@@ -6236,7 +6536,7 @@
         <v>102</v>
       </c>
       <c r="R10" s="6">
-        <v>5826.4193083540094</v>
+        <v>5561.582067065191</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
@@ -6281,7 +6581,7 @@
         <v>103</v>
       </c>
       <c r="R11" s="6">
-        <v>10154.449238863286</v>
+        <v>9692.8833643694998</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
@@ -6326,7 +6626,7 @@
         <v>106</v>
       </c>
       <c r="R12" s="6">
-        <v>608.49467667280817</v>
+        <v>580.83582773313503</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
@@ -6334,26 +6634,26 @@
         <v>33</v>
       </c>
       <c r="C13" s="4">
-        <v>328.10044857875562</v>
+        <v>332.0521666331224</v>
       </c>
       <c r="D13" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E13" s="4">
-        <v>427.23019535530364</v>
+        <v>437.98889389020491</v>
       </c>
       <c r="F13" s="7">
-        <v>1.7207811154245041</v>
+        <v>1.7533810774862726</v>
       </c>
       <c r="G13" s="4">
         <v>0.79946350834994295</v>
       </c>
       <c r="H13" s="4">
-        <v>224.33125781137119</v>
+        <v>225.37027765755619</v>
       </c>
       <c r="I13" s="4">
         <f t="shared" si="0"/>
-        <v>54.95044857875564</v>
+        <v>58.90216663312242</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>52</v>
@@ -6365,7 +6665,7 @@
         <v>107</v>
       </c>
       <c r="R13" s="6">
-        <v>-1469.0537348517778</v>
+        <v>1402.2785650857879</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
@@ -6400,15 +6700,15 @@
       <c r="L14" s="7">
         <v>1.2769418795914119E-2</v>
       </c>
-      <c r="N14" s="31" t="s">
+      <c r="N14" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="O14" s="31"/>
+      <c r="O14" s="32"/>
       <c r="Q14" s="13" t="s">
         <v>108</v>
       </c>
       <c r="R14" s="6">
-        <v>-717.50721988726536</v>
+        <v>684.89325534693512</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
@@ -6453,7 +6753,7 @@
         <v>109</v>
       </c>
       <c r="R15" s="6">
-        <v>-0.22348393544019207</v>
+        <v>0.21332557473836516</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
@@ -6486,7 +6786,7 @@
         <v>46</v>
       </c>
       <c r="L16" s="7">
-        <v>3.3257922587167379E-2</v>
+        <v>2.4656735711175819E-2</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>81</v>
@@ -6498,7 +6798,7 @@
         <v>110</v>
       </c>
       <c r="R16" s="6">
-        <v>1493.7562417078809</v>
+        <v>1455.4018193176985</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
@@ -6531,19 +6831,19 @@
         <v>55</v>
       </c>
       <c r="L17" s="16">
-        <v>1.1666246047954387E-4</v>
+        <v>-8.4845275348931753E-3</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>82</v>
       </c>
       <c r="O17" s="10">
-        <v>59.052048428258885</v>
+        <v>60.037026235722536</v>
       </c>
       <c r="Q17" s="13" t="s">
         <v>111</v>
       </c>
       <c r="R17" s="6">
-        <v>1214.5651249638913</v>
+        <v>1185.5793514604527</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
@@ -6576,13 +6876,17 @@
         <v>83</v>
       </c>
       <c r="O18" s="10">
-        <v>54.1277629959406</v>
+        <v>54.166395266817204</v>
       </c>
       <c r="Q18" s="13" t="s">
         <v>112</v>
       </c>
       <c r="R18" s="6">
-        <v>392226.85885319277</v>
+        <v>204302.32267645153</v>
+      </c>
+      <c r="V18" s="6">
+        <f>R23-R9-R6</f>
+        <v>215456.48269446561</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
@@ -6611,10 +6915,10 @@
         <f t="shared" si="0"/>
         <v>274.54370647629025</v>
       </c>
-      <c r="K19" s="31" t="s">
+      <c r="K19" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="L19" s="31"/>
+      <c r="L19" s="32"/>
       <c r="N19" s="9" t="s">
         <v>84</v>
       </c>
@@ -6625,7 +6929,7 @@
         <v>123</v>
       </c>
       <c r="R19" s="6">
-        <v>444289.70597502514</v>
+        <v>245404.71435306963</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
@@ -6666,14 +6970,14 @@
       <c r="O20" s="10">
         <v>3.4935322440475982</v>
       </c>
-      <c r="Q20" s="30" t="s">
+      <c r="Q20" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30" t="s">
+      <c r="R20" s="31"/>
+      <c r="S20" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="T20" s="30"/>
+      <c r="T20" s="31"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
@@ -6762,19 +7066,23 @@
         <v>87</v>
       </c>
       <c r="O22" s="6">
-        <v>57.594979992439178</v>
+        <v>58.888622676875549</v>
       </c>
       <c r="Q22" s="23" t="s">
         <v>113</v>
       </c>
       <c r="R22" s="24">
-        <v>240.46390970622548</v>
+        <v>234.34207371589633</v>
       </c>
       <c r="S22" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="T22" s="27">
         <v>0</v>
+      </c>
+      <c r="V22" s="30">
+        <f>(R23-228195)/228195</f>
+        <v>-4.8294650117820311E-2</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.3">
@@ -6813,19 +7121,23 @@
         <v>88</v>
       </c>
       <c r="O23" s="6">
-        <v>23.18096972790984</v>
+        <v>23.197115911664334</v>
       </c>
       <c r="Q23" s="23" t="s">
         <v>114</v>
       </c>
       <c r="R23" s="24">
-        <v>768240.42493118276</v>
+        <v>217174.40231636399</v>
       </c>
       <c r="S23" s="23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T23" s="27">
         <v>0</v>
+      </c>
+      <c r="V23" s="30">
+        <f>(R24-10815)/10815</f>
+        <v>-9.4614527382855685E-4</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.3">
@@ -6858,25 +7170,25 @@
         <v>63</v>
       </c>
       <c r="L24" s="4">
-        <v>6.0286583481758358</v>
+        <v>4.6575782017682776</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>89</v>
       </c>
       <c r="O24" s="15">
-        <v>23.18422680226918</v>
+        <v>23.200446653981288</v>
       </c>
       <c r="Q24" s="23" t="s">
         <v>115</v>
       </c>
       <c r="R24" s="24">
-        <v>36531.589113909038</v>
+        <v>10804.767438863544</v>
       </c>
       <c r="S24" s="23" t="s">
         <v>127</v>
       </c>
       <c r="T24" s="27">
-        <v>444289.70597502514</v>
+        <v>245404.71435306963</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6913,14 +7225,17 @@
         <v>64</v>
       </c>
       <c r="L25" s="4">
-        <v>-0.15718533150875055</v>
+        <v>2.5851286660570616</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
+      <c r="S25" s="9" t="s">
+        <v>245</v>
+      </c>
       <c r="T25" s="26">
-        <v>857075.32507663034</v>
-      </c>
+        <v>473618.22618201305</v>
+      </c>
+      <c r="U25" s="6"/>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
       <c r="X25" s="9"/>
@@ -6952,10 +7267,10 @@
         <f t="shared" si="0"/>
         <v>94.993292442043355</v>
       </c>
-      <c r="N26" s="31" t="s">
+      <c r="N26" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="O26" s="31"/>
+      <c r="O26" s="32"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
@@ -7279,7 +7594,7 @@
         <v>3.8804887263997387</v>
       </c>
       <c r="G35" s="4">
-        <v>1.1599999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="H35" s="4">
         <v>2.1111792130950945E-2</v>
@@ -7306,7 +7621,7 @@
         <v>3.9723306469545014</v>
       </c>
       <c r="G36" s="4">
-        <v>1.1599999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="H36" s="4">
         <v>1.3090660987003904</v>
@@ -7348,26 +7663,26 @@
         <v>33</v>
       </c>
       <c r="C38" s="4">
-        <v>328.10044857875562</v>
+        <v>332.0521666331224</v>
       </c>
       <c r="D38" s="5">
         <v>9.1240875912408761</v>
       </c>
       <c r="E38" s="4">
-        <v>427.23019535530364</v>
+        <v>437.98889389020491</v>
       </c>
       <c r="F38" s="7">
-        <v>1.7207811154245041</v>
+        <v>1.7533810774862726</v>
       </c>
       <c r="G38" s="4">
         <v>0.79946350834994295</v>
       </c>
       <c r="H38" s="4">
-        <v>224.33125781137119</v>
+        <v>225.37027765755619</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" si="0"/>
-        <v>54.95044857875564</v>
+        <v>58.90216663312242</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.3">
@@ -7375,26 +7690,26 @@
         <v>33</v>
       </c>
       <c r="C39" s="4">
-        <v>328.10044857875562</v>
+        <v>332.0521666331224</v>
       </c>
       <c r="D39" s="5">
         <v>9124.0875912408756</v>
       </c>
       <c r="E39" s="4">
-        <v>427.23019145290715</v>
+        <v>437.98889388965154</v>
       </c>
       <c r="F39" s="7">
-        <v>1.7207811154245041</v>
+        <v>1.7533810774862726</v>
       </c>
       <c r="G39" s="4">
         <v>0.79946350834994295</v>
       </c>
       <c r="H39" s="4">
-        <v>224.3312539089747</v>
+        <v>225.37027765700279</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" si="0"/>
-        <v>54.95044857875564</v>
+        <v>58.90216663312242</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.3">
@@ -7441,7 +7756,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G41" s="4">
-        <v>3.1520540937721294E-4</v>
+        <v>3.2238763783741314E-4</v>
       </c>
       <c r="H41" s="4">
         <v>2.5073905791015251E-5</v>
@@ -7456,26 +7771,26 @@
         <v>20</v>
       </c>
       <c r="C42" s="4">
-        <v>299.14999999999998</v>
+        <v>331.0521666331224</v>
       </c>
       <c r="D42" s="5">
         <v>101.325</v>
       </c>
       <c r="E42" s="4">
-        <v>109.10123710827688</v>
+        <v>242.4702965888271</v>
       </c>
       <c r="F42" s="7">
-        <v>0.38119971346803067</v>
+        <v>0.80481680342880946</v>
       </c>
       <c r="G42" s="4">
-        <v>3.1520540937721294E-4</v>
+        <v>3.2238763783741314E-4</v>
       </c>
       <c r="H42" s="4">
-        <v>7.021095587454511E-3</v>
+        <v>7.0746452043314934</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>57.90216663312242</v>
       </c>
     </row>
   </sheetData>
@@ -7550,10 +7865,10 @@
         <v>203</v>
       </c>
       <c r="B2">
-        <v>6.2330613710360416E-2</v>
+        <v>6.2240819709105791E-2</v>
       </c>
       <c r="C2">
-        <v>47.160113533787431</v>
+        <v>47.092174281440272</v>
       </c>
       <c r="E2" t="s">
         <v>66</v>
@@ -7565,19 +7880,19 @@
         <v>1.5412694860114715</v>
       </c>
       <c r="H2">
-        <v>9.6068272956146783E-2</v>
+        <v>9.5929876201986147E-2</v>
       </c>
       <c r="I2">
-        <v>99.61768441648718</v>
+        <v>99.618233080854779</v>
       </c>
       <c r="K2" s="29">
-        <v>0.37171801292099393</v>
+        <v>0.37217854911101822</v>
       </c>
       <c r="L2" s="29">
-        <v>0.61795458428505312</v>
+        <v>0.60389489005271357</v>
       </c>
       <c r="M2" s="29">
-        <v>0.30218738767329717</v>
+        <v>0.30201493343058861</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -7585,10 +7900,10 @@
         <v>204</v>
       </c>
       <c r="B3">
-        <v>6.2330613710360409E-2</v>
+        <v>6.2240819709105791E-2</v>
       </c>
       <c r="C3">
-        <v>42.780063275807827</v>
+        <v>42.718433960343184</v>
       </c>
       <c r="E3" t="s">
         <v>67</v>
@@ -7600,10 +7915,10 @@
         <v>2.8065325482354964</v>
       </c>
       <c r="H3">
-        <v>0.16684153618357625</v>
+        <v>0.16660669022943383</v>
       </c>
       <c r="I3">
-        <v>98.156332631064402</v>
+        <v>98.158879995412605</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -7611,10 +7926,10 @@
         <v>205</v>
       </c>
       <c r="B4">
-        <v>5.9447568597938295E-2</v>
+        <v>5.9363890268859215E-2</v>
       </c>
       <c r="C4">
-        <v>43.783294899040605</v>
+        <v>43.721665583575962</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
@@ -7626,10 +7941,10 @@
         <v>3.1173934843303797</v>
       </c>
       <c r="H4">
-        <v>0.94203699337955504</v>
+        <v>0.94149938564699032</v>
       </c>
       <c r="I4">
-        <v>22.347771094677046</v>
+        <v>22.357678916547691</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -7637,10 +7952,10 @@
         <v>206</v>
       </c>
       <c r="B5">
-        <v>5.9447568597938281E-2</v>
+        <v>5.9363890268859201E-2</v>
       </c>
       <c r="C5">
-        <v>36.495552061002329</v>
+        <v>36.444180963961543</v>
       </c>
       <c r="E5" t="s">
         <v>70</v>
@@ -7652,10 +7967,10 @@
         <v>1.1383330527634061</v>
       </c>
       <c r="H5">
-        <v>0.34398989151674325</v>
+        <v>0.34379358115217878</v>
       </c>
       <c r="I5">
-        <v>16.506341443842707</v>
+        <v>16.514210250056994</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -7663,10 +7978,10 @@
         <v>207</v>
       </c>
       <c r="B6">
-        <v>5.9447568597938309E-2</v>
+        <v>5.9363890268859201E-2</v>
       </c>
       <c r="C6">
-        <v>19.348775095478807</v>
+        <v>19.321539781942818</v>
       </c>
       <c r="E6" t="s">
         <v>59</v>
@@ -7678,10 +7993,10 @@
         <v>3.4691288051130833</v>
       </c>
       <c r="H6">
-        <v>0.20623127261704369</v>
+        <v>0.20594098171527173</v>
       </c>
       <c r="I6">
-        <v>87.550493449279202</v>
+        <v>87.565838408938305</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -7689,10 +8004,10 @@
         <v>208</v>
       </c>
       <c r="B7">
-        <v>5.9447568597938295E-2</v>
+        <v>5.9363890268859222E-2</v>
       </c>
       <c r="C7">
-        <v>15.279298633423252</v>
+        <v>15.257791510267515</v>
       </c>
       <c r="E7" t="s">
         <v>60</v>
@@ -7704,10 +8019,10 @@
         <v>7.1429330882120778</v>
       </c>
       <c r="H7">
-        <v>0.42463000475197082</v>
+        <v>0.42403229604642539</v>
       </c>
       <c r="I7">
-        <v>69.991687359302716</v>
+        <v>70.021264107604736</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -7715,10 +8030,10 @@
         <v>209</v>
       </c>
       <c r="B8">
-        <v>1.0945431403057075E-3</v>
+        <v>9.6159289231950045E-4</v>
       </c>
       <c r="C8">
-        <v>0.19630002150696768</v>
+        <v>0.17245615864034747</v>
       </c>
       <c r="E8" t="s">
         <v>229</v>
@@ -7730,10 +8045,10 @@
         <v>9.087639387171599</v>
       </c>
       <c r="H8">
-        <v>0.54023806586220946</v>
+        <v>0.53947762738301808</v>
       </c>
       <c r="I8">
-        <v>50.88203231237182</v>
+        <v>50.917235671759556</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -7741,10 +8056,10 @@
         <v>210</v>
       </c>
       <c r="B9">
-        <v>5.6519322803764302E-2</v>
+        <v>5.6377339440876452E-2</v>
       </c>
       <c r="C9">
-        <v>12.144174696753895</v>
+        <v>12.113667063657699</v>
       </c>
       <c r="E9" t="s">
         <v>230</v>
@@ -7756,10 +8071,10 @@
         <v>1.0330018156282741</v>
       </c>
       <c r="H9">
-        <v>1.630636561151289</v>
+        <v>1.6284752057777221</v>
       </c>
       <c r="I9">
-        <v>26.639386853604201</v>
+        <v>26.665315430593594</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -7767,10 +8082,10 @@
         <v>211</v>
       </c>
       <c r="B10">
-        <v>6.2293020965969517E-2</v>
+        <v>6.2161817134139034E-2</v>
       </c>
       <c r="C10">
-        <v>17.204062412245676</v>
+        <v>17.167826588769231</v>
       </c>
       <c r="E10" t="s">
         <v>231</v>
@@ -7782,10 +8097,10 @@
         <v>8.3949658717156963E-4</v>
       </c>
       <c r="H10">
-        <v>2.5368528063802505E-4</v>
+        <v>2.5354050588982793E-4</v>
       </c>
       <c r="I10">
-        <v>75.382457778269426</v>
+        <v>75.393049670454886</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -7793,10 +8108,10 @@
         <v>212</v>
       </c>
       <c r="B11">
-        <v>0.12753464962125136</v>
+        <v>0.12742541145833755</v>
       </c>
       <c r="C11">
-        <v>8.8351632291660778</v>
+        <v>8.8275955838001803</v>
       </c>
       <c r="E11" t="s">
         <v>232</v>
@@ -7808,10 +8123,10 @@
         <v>4.2282153795985042</v>
       </c>
       <c r="H11">
-        <v>6.6744147803865523</v>
+        <v>6.6655680621203937</v>
       </c>
       <c r="I11">
-        <v>2.8359075145046244</v>
+        <v>2.8395645278531121</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -7819,25 +8134,25 @@
         <v>213</v>
       </c>
       <c r="B12">
-        <v>7.5376348286035566E-2</v>
+        <v>7.5249549372386385E-2</v>
       </c>
       <c r="C12">
-        <v>26.039225641411754</v>
+        <v>25.995422172569413</v>
       </c>
       <c r="E12" t="s">
         <v>63</v>
       </c>
       <c r="F12">
-        <v>0.18541322966354401</v>
+        <v>0.16238339350322922</v>
       </c>
       <c r="G12">
-        <v>2.3013833668177122</v>
+        <v>1.8571112073122706</v>
       </c>
       <c r="H12">
-        <v>0.13681164556905009</v>
+        <v>0.11024534592795437</v>
       </c>
       <c r="I12">
-        <v>57.541563024799281</v>
+        <v>59.562096733465516</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -7845,25 +8160,25 @@
         <v>214</v>
       </c>
       <c r="B13">
-        <v>7.0803823955655404E-2</v>
+        <v>7.0696056119752354E-2</v>
       </c>
       <c r="C13">
-        <v>44.636313075766651</v>
+        <v>44.568373823419499</v>
       </c>
       <c r="E13" t="s">
         <v>233</v>
       </c>
       <c r="F13">
-        <v>-1.2508376609764744E-3</v>
+        <v>0.11998394168882738</v>
       </c>
       <c r="G13">
-        <v>-1.0659667984780519E-2</v>
+        <v>0.81772333798409824</v>
       </c>
       <c r="H13">
-        <v>-1.166746647067802E-5</v>
+        <v>7.8631694968928577E-4</v>
       </c>
       <c r="I13">
-        <v>99.99818001487435</v>
+        <v>99.348915073500962</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -7871,10 +8186,10 @@
         <v>215</v>
       </c>
       <c r="B14">
-        <v>5.9447568597938275E-2</v>
+        <v>5.9363890268859236E-2</v>
       </c>
       <c r="C14">
-        <v>3.0640569428202089</v>
+        <v>3.0597439797970734</v>
       </c>
       <c r="E14" s="28" t="s">
         <v>173</v>
@@ -7883,13 +8198,13 @@
         <v>0.38530984394830042</v>
       </c>
       <c r="G14" s="28">
-        <v>3.0223415591440466</v>
+        <v>2.9300645561034075</v>
       </c>
       <c r="H14" s="28">
-        <v>0.91331350041417936</v>
+        <v>0.88492325185889775</v>
       </c>
       <c r="I14" s="28">
-        <v>29.670638959401796</v>
+        <v>30.333790327156184</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -7897,10 +8212,10 @@
         <v>216</v>
       </c>
       <c r="B15">
-        <v>5.9447568597938281E-2</v>
+        <v>5.936389026885925E-2</v>
       </c>
       <c r="C15">
-        <v>12.215241690603039</v>
+        <v>12.198047530470447</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -7908,10 +8223,10 @@
         <v>217</v>
       </c>
       <c r="B16">
-        <v>5.9447568597938275E-2</v>
+        <v>5.9363890268859257E-2</v>
       </c>
       <c r="C16">
-        <v>1.0887231563140623E-2</v>
+        <v>1.0871906708533677E-2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -7919,10 +8234,10 @@
         <v>218</v>
       </c>
       <c r="B17">
-        <v>1.0945431403057205E-3</v>
+        <v>9.6159289231950089E-4</v>
       </c>
       <c r="C17">
-        <v>0.19630046122668465</v>
+        <v>0.17325530021176289</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -7933,7 +8248,7 @@
         <v>2E-3</v>
       </c>
       <c r="C18">
-        <v>1.5806861479085264E-11</v>
+        <v>1.6167034518646481E-11</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -7941,10 +8256,10 @@
         <v>219</v>
       </c>
       <c r="B19">
-        <v>-565.00162484106477</v>
+        <v>52.956962500131382</v>
       </c>
       <c r="C19">
-        <v>-1.25039792545502E-3</v>
+        <v>0.12078308327640971</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -7952,10 +8267,10 @@
         <v>220</v>
       </c>
       <c r="B20">
-        <v>1.5785418152043924</v>
+        <v>1.5764495097109579</v>
       </c>
       <c r="C20">
-        <v>21.091738972349887</v>
+        <v>21.063782562901068</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -7963,10 +8278,10 @@
         <v>221</v>
       </c>
       <c r="B21">
-        <v>1.5785418152043924</v>
+        <v>1.5764495097109579</v>
       </c>
       <c r="C21">
-        <v>8.1303859832807976</v>
+        <v>8.1196094228547704</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -7974,10 +8289,10 @@
         <v>222</v>
       </c>
       <c r="B22">
-        <v>88.665374580191326</v>
+        <v>88.550601501488359</v>
       </c>
       <c r="C22">
-        <v>8.3251906950465617</v>
+        <v>8.3144141346205345</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -7985,10 +8300,10 @@
         <v>223</v>
       </c>
       <c r="B23">
-        <v>84.175302539602072</v>
+        <v>84.066364803290213</v>
       </c>
       <c r="C23">
-        <v>8.3277438763359566</v>
+        <v>8.3169663021651221</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -7996,10 +8311,10 @@
         <v>224</v>
       </c>
       <c r="B24">
-        <v>0.61795458428505312</v>
+        <v>0.60389489005271357</v>
       </c>
       <c r="C24">
-        <v>2.5526236937473641</v>
+        <v>2.5513868371347943</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -8018,10 +8333,10 @@
         <v>226</v>
       </c>
       <c r="B26" s="28">
-        <v>0.30218738767329717</v>
+        <v>0.30201493343058861</v>
       </c>
       <c r="C26" s="28">
-        <v>2.1673138497990636</v>
+        <v>2.1660769931864938</v>
       </c>
     </row>
   </sheetData>

--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tes2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0FCD8C-1AF2-4283-B340-DCB0CD2F1CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A858FA-2336-44E5-A497-0C75CCEB9BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
+    <workbookView xWindow="3336" yWindow="3540" windowWidth="17280" windowHeight="9420" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="257">
   <si>
     <t>T [°C]</t>
   </si>
@@ -799,6 +799,9 @@
   </si>
   <si>
     <t>Condensador RORC</t>
+  </si>
+  <si>
+    <t>XD reg [kW]</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1367,7 @@
     <col min="9" max="9" width="12.6640625" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.44140625" style="16" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" style="16" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5546875" style="16" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.88671875" style="16" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="19.109375" style="16" bestFit="1" customWidth="1"/>
@@ -1419,34 +1422,34 @@
         <v>500</v>
       </c>
       <c r="C3" s="18">
-        <v>79.817560813786429</v>
+        <v>80.075236196655112</v>
       </c>
       <c r="D3" s="16">
-        <v>5.747836556425975</v>
+        <v>6.0055119392946494</v>
       </c>
       <c r="E3" s="18">
-        <v>44.197489238670407</v>
+        <v>44.34017218770186</v>
       </c>
       <c r="F3" s="18">
-        <v>21.677171694785553</v>
+        <v>21.690058820630004</v>
       </c>
       <c r="G3" s="18">
-        <v>41.618252958803971</v>
+        <v>41.643616555414731</v>
       </c>
       <c r="H3" s="18">
-        <v>18.903462401075426</v>
+        <v>18.848834947929483</v>
       </c>
       <c r="I3" s="18">
-        <v>18.48639482005732</v>
+        <v>18.436180391626912</v>
       </c>
       <c r="J3" s="18">
-        <v>77.61995220919249</v>
+        <v>81.282485322238983</v>
       </c>
       <c r="K3" s="18">
-        <v>32.670285338064971</v>
+        <v>34.043287382392478</v>
       </c>
       <c r="L3" s="16">
-        <v>291.96397506058662</v>
+        <v>304.23405873081123</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -1454,34 +1457,34 @@
         <v>550</v>
       </c>
       <c r="C4" s="16">
-        <v>89.81986854859457</v>
+        <v>90.099760632232432</v>
       </c>
       <c r="D4" s="16">
-        <v>5.9780007016897558</v>
+        <v>6.2578927853276172</v>
       </c>
       <c r="E4" s="16">
-        <v>46.695266271232683</v>
+        <v>46.840775673371354</v>
       </c>
       <c r="F4" s="16">
-        <v>22.536994145078911</v>
+        <v>22.549497593185308</v>
       </c>
       <c r="G4" s="16">
-        <v>44.168426973361456</v>
+        <v>44.193547794198203</v>
       </c>
       <c r="H4" s="16">
-        <v>18.63680709238654</v>
+        <v>18.569282786768131</v>
       </c>
       <c r="I4" s="16">
-        <v>18.225175204901593</v>
+        <v>18.162225255928078</v>
       </c>
       <c r="J4" s="16">
-        <v>77.939707184260271</v>
+        <v>81.615235916991878</v>
       </c>
       <c r="K4" s="16">
-        <v>33.498370195705569</v>
+        <v>34.946784744116158</v>
       </c>
       <c r="L4" s="16">
-        <v>299.36430671433357</v>
+        <v>312.30832800810623</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -1489,34 +1492,34 @@
         <v>600</v>
       </c>
       <c r="C5" s="16">
-        <v>99.679334582948613</v>
+        <v>99.981173839880356</v>
       </c>
       <c r="D5" s="16">
-        <v>6.2111932846844748</v>
+        <v>6.5130325416162291</v>
       </c>
       <c r="E5" s="16">
-        <v>48.86377187044944</v>
+        <v>49.011736387407424</v>
       </c>
       <c r="F5" s="16">
-        <v>23.096140404949921</v>
+        <v>23.108230796268519</v>
       </c>
       <c r="G5" s="16">
-        <v>46.38038734333562</v>
+        <v>46.40527790743959</v>
       </c>
       <c r="H5" s="16">
-        <v>18.381896459287887</v>
+        <v>18.303596533693334</v>
       </c>
       <c r="I5" s="16">
-        <v>17.975500010392771</v>
+        <v>17.901905990987522</v>
       </c>
       <c r="J5" s="16">
-        <v>78.285373523673968</v>
+        <v>81.979569400405978</v>
       </c>
       <c r="K5" s="16">
-        <v>34.328266754455306</v>
+        <v>35.850258773202164</v>
       </c>
       <c r="L5" s="16">
-        <v>306.78082896611096</v>
+        <v>320.38238876902079</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -1524,34 +1527,34 @@
         <v>650</v>
       </c>
       <c r="C6" s="16">
-        <v>109.4252013288348</v>
+        <v>109.74867541385149</v>
       </c>
       <c r="D6" s="16">
-        <v>6.4473440004104017</v>
+        <v>6.7708180854270879</v>
       </c>
       <c r="E6" s="16">
-        <v>50.766607886856718</v>
+        <v>50.916680099072742</v>
       </c>
       <c r="F6" s="16">
-        <v>23.379233392080014</v>
+        <v>23.390875924002081</v>
       </c>
       <c r="G6" s="16">
-        <v>48.319628871892832</v>
+        <v>48.344297742800649</v>
       </c>
       <c r="H6" s="16">
-        <v>18.138196399702615</v>
+        <v>18.05106665890689</v>
       </c>
       <c r="I6" s="16">
-        <v>17.736842945242444</v>
+        <v>17.654523062467341</v>
       </c>
       <c r="J6" s="16">
-        <v>78.657618951805773</v>
+        <v>82.376196854637726</v>
       </c>
       <c r="K6" s="16">
-        <v>35.16033473864286</v>
+        <v>36.75418667446764</v>
       </c>
       <c r="L6" s="16">
-        <v>314.21675655811759</v>
+        <v>328.46050564160743</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -1559,34 +1562,34 @@
         <v>700</v>
       </c>
       <c r="C7" s="16">
-        <v>119.07911442755226</v>
+        <v>119.42386413622707</v>
       </c>
       <c r="D7" s="16">
-        <v>6.6863221481329127</v>
+        <v>7.0310718568077251</v>
       </c>
       <c r="E7" s="16">
-        <v>52.451199641588154</v>
+        <v>52.603052767831237</v>
       </c>
       <c r="F7" s="16">
-        <v>23.400730661809668</v>
+        <v>23.411885843230223</v>
       </c>
       <c r="G7" s="16">
-        <v>50.034982828728317</v>
+        <v>50.05943609903629</v>
       </c>
       <c r="H7" s="16">
-        <v>17.905265068043892</v>
+        <v>17.811094265141449</v>
       </c>
       <c r="I7" s="16">
-        <v>17.508768368073106</v>
+        <v>17.419485786127346</v>
       </c>
       <c r="J7" s="16">
-        <v>79.056980765670005</v>
+        <v>82.805678998061069</v>
       </c>
       <c r="K7" s="16">
-        <v>35.994724488327527</v>
+        <v>37.658813728603796</v>
       </c>
       <c r="L7" s="16">
-        <v>321.67343303176642</v>
+        <v>336.54487062158535</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -1594,34 +1597,34 @@
         <v>750</v>
       </c>
       <c r="C8" s="16">
-        <v>128.65749758364126</v>
+        <v>129.02311588889785</v>
       </c>
       <c r="D8" s="16">
-        <v>6.9279630407328954</v>
+        <v>7.2935813459894892</v>
       </c>
       <c r="E8" s="16">
-        <v>53.9538380140431</v>
+        <v>54.107163791298788</v>
       </c>
       <c r="F8" s="16">
-        <v>23.167877476540312</v>
+        <v>23.178501568199025</v>
       </c>
       <c r="G8" s="16">
-        <v>51.563810076417916</v>
+        <v>51.588052318084642</v>
       </c>
       <c r="H8" s="16">
-        <v>17.682710397463307</v>
+        <v>17.583144089105325</v>
       </c>
       <c r="I8" s="16">
-        <v>17.290889626597831</v>
+        <v>17.196266196092065</v>
       </c>
       <c r="J8" s="16">
-        <v>79.483884244625642</v>
+        <v>83.268442408655289</v>
       </c>
       <c r="K8" s="16">
-        <v>36.831475485488056</v>
+        <v>38.564261866794908</v>
       </c>
       <c r="L8" s="16">
-        <v>329.15121122497538</v>
+        <v>344.63657336926462</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -1629,34 +1632,34 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C9" s="16">
-        <v>138.17310399416084</v>
+        <v>138.55913638137596</v>
       </c>
       <c r="D9" s="16">
-        <v>7.1720857262984268</v>
+        <v>7.5581181135135624</v>
       </c>
       <c r="E9" s="16">
-        <v>55.302895315550607</v>
+        <v>55.457402293257886</v>
       </c>
       <c r="F9" s="16">
-        <v>22.682590705779543</v>
+        <v>22.692635964018898</v>
       </c>
       <c r="G9" s="16">
-        <v>52.935313208739778</v>
+        <v>52.95934806076604</v>
       </c>
       <c r="H9" s="16">
-        <v>17.470165800587704</v>
+        <v>17.366718295380426</v>
       </c>
       <c r="I9" s="16">
-        <v>17.082845227237385</v>
+        <v>16.984373320199506</v>
       </c>
       <c r="J9" s="16">
-        <v>79.938657610626422</v>
+        <v>83.76479494046032</v>
       </c>
       <c r="K9" s="16">
-        <v>37.670578278111229</v>
+        <v>39.470595213279822</v>
       </c>
       <c r="L9" s="16">
-        <v>336.65000666810113</v>
+        <v>352.73618694262348</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
@@ -1664,34 +1667,34 @@
         <v>850.00000000000011</v>
       </c>
       <c r="C10" s="16">
-        <v>147.63591018797939</v>
+        <v>148.04185834627998</v>
       </c>
       <c r="D10" s="16">
-        <v>7.4185008301883553</v>
+        <v>7.8244489884889461</v>
       </c>
       <c r="E10" s="16">
-        <v>56.520932003665223</v>
+        <v>56.676345196994049</v>
       </c>
       <c r="F10" s="16">
-        <v>21.942697476803939</v>
+        <v>21.952112320563913</v>
       </c>
       <c r="G10" s="16">
-        <v>54.172707166781088</v>
+        <v>54.19653780739376</v>
       </c>
       <c r="H10" s="16">
-        <v>17.267280674638158</v>
+        <v>17.161343126444446</v>
       </c>
       <c r="I10" s="16">
-        <v>16.884289522133408</v>
+        <v>16.783340068289903</v>
       </c>
       <c r="J10" s="16">
-        <v>80.421544773610378</v>
+        <v>84.294937842312663</v>
       </c>
       <c r="K10" s="16">
-        <v>38.512000313741446</v>
+        <v>40.377855361703119</v>
       </c>
       <c r="L10" s="16">
-        <v>344.16952845017568</v>
+        <v>360.84408305086771</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.3">
@@ -1699,34 +1702,34 @@
         <v>900.00000000000011</v>
       </c>
       <c r="C11" s="19">
-        <v>157.05390229949612</v>
+        <v>157.47922554852343</v>
       </c>
       <c r="D11" s="35">
-        <v>7.6670200718972215</v>
+        <v>8.0923433209245097</v>
       </c>
       <c r="E11" s="19">
-        <v>57.626171655998625</v>
+        <v>57.782231137481588</v>
       </c>
       <c r="F11" s="19">
-        <v>20.942799035421363</v>
+        <v>20.951528074973265</v>
       </c>
       <c r="G11" s="19">
-        <v>55.294738262079335</v>
+        <v>55.318367601752492</v>
       </c>
       <c r="H11" s="19">
-        <v>17.073711247972792</v>
+        <v>16.9665618977976</v>
       </c>
       <c r="I11" s="19">
-        <v>16.694883727410044</v>
+        <v>16.592716345658207</v>
       </c>
       <c r="J11" s="19">
-        <v>80.932712853176668</v>
+        <v>84.858977086928178</v>
       </c>
       <c r="K11" s="19">
-        <v>39.35571409337534</v>
+        <v>41.286081792389979</v>
       </c>
       <c r="L11" s="19">
-        <v>351.70953082133019</v>
+        <v>368.96061451713769</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.3">
@@ -1734,34 +1737,34 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C12" s="16">
-        <v>138.17310399416084</v>
+        <v>138.55913638137596</v>
       </c>
       <c r="D12" s="16">
-        <v>7.1720857262984268</v>
+        <v>7.5581181135135624</v>
       </c>
       <c r="E12" s="16">
-        <v>55.302895315550607</v>
+        <v>55.457402293257886</v>
       </c>
       <c r="F12" s="16">
-        <v>22.682590705779543</v>
+        <v>22.692635964018898</v>
       </c>
       <c r="G12" s="16">
-        <v>52.935313208739778</v>
+        <v>52.95934806076604</v>
       </c>
       <c r="H12" s="16">
-        <v>17.470165800587704</v>
+        <v>17.366718295380426</v>
       </c>
       <c r="I12" s="16">
-        <v>17.082845227237385</v>
+        <v>16.984373320199506</v>
       </c>
       <c r="J12" s="16">
-        <v>79.938657610626422</v>
+        <v>83.76479494046032</v>
       </c>
       <c r="K12" s="16">
-        <v>37.670578278111229</v>
+        <v>39.470595213279822</v>
       </c>
       <c r="L12" s="16">
-        <v>336.65000666810113</v>
+        <v>352.73618694262348</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -1826,7 +1829,7 @@
         <v>121</v>
       </c>
       <c r="V15" s="17" t="s">
-        <v>21</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.3">
@@ -1846,7 +1849,7 @@
         <v>2771.3026251072883</v>
       </c>
       <c r="G16" s="16">
-        <v>861.11522976340632</v>
+        <v>898.27603128406031</v>
       </c>
       <c r="H16" s="16">
         <v>340.1774796640384</v>
@@ -1864,34 +1867,34 @@
         <v>89329.858804423799</v>
       </c>
       <c r="M16" s="16">
-        <v>364.73841978638626</v>
+        <v>419.54531737997803</v>
       </c>
       <c r="N16" s="16">
-        <v>208.28536231148587</v>
+        <v>255.87107705551512</v>
       </c>
       <c r="O16" s="16">
-        <v>5881.3030996340103</v>
+        <v>4968.0468857744854</v>
       </c>
       <c r="P16" s="16">
-        <v>2433.8173080532083</v>
+        <v>2234.5014182525947</v>
       </c>
       <c r="Q16" s="16">
-        <v>0.69940860806835647</v>
+        <v>2.3471414600463723</v>
       </c>
       <c r="R16" s="16">
-        <v>518.90194064976959</v>
+        <v>478.40909329018001</v>
       </c>
       <c r="S16" s="16">
-        <v>4585.2931282176587</v>
+        <v>5313.959773625852</v>
       </c>
       <c r="T16" s="16">
         <v>346597.58286418673</v>
       </c>
       <c r="U16" s="16">
-        <v>4681.5356860310476</v>
+        <v>4894.5992563087448</v>
       </c>
       <c r="V16" s="16">
-        <v>204.39429747568178</v>
+        <v>229.65614489043224</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -1911,7 +1914,7 @@
         <v>2783.7767920301558</v>
       </c>
       <c r="G17" s="16">
-        <v>889.83413920749445</v>
+        <v>929.90885718412142</v>
       </c>
       <c r="H17" s="16">
         <v>805.40884684346383</v>
@@ -1929,34 +1932,34 @@
         <v>91657.429244218394</v>
       </c>
       <c r="M17" s="16">
-        <v>369.13125064937702</v>
+        <v>424.30028424486284</v>
       </c>
       <c r="N17" s="16">
-        <v>211.89585280271399</v>
+        <v>259.97082824934603</v>
       </c>
       <c r="O17" s="16">
-        <v>6202.2793601868398</v>
+        <v>5250.598053142633</v>
       </c>
       <c r="P17" s="16">
-        <v>2518.8359916435102</v>
+        <v>2317.2407129887442</v>
       </c>
       <c r="Q17" s="16">
-        <v>0.72279964988682055</v>
+        <v>2.4296557049723959</v>
       </c>
       <c r="R17" s="16">
-        <v>537.45210945302438</v>
+        <v>496.59664099516397</v>
       </c>
       <c r="S17" s="16">
-        <v>4695.229071043892</v>
+        <v>5434.8419212917788</v>
       </c>
       <c r="T17" s="16">
         <v>376854.31963656942</v>
       </c>
       <c r="U17" s="16">
-        <v>4884.6893691911546</v>
+        <v>5117.5161451365711</v>
       </c>
       <c r="V17" s="16">
-        <v>234.49064526728225</v>
+        <v>263.82115663647943</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -1976,7 +1979,7 @@
         <v>2792.4530756981671</v>
       </c>
       <c r="G18" s="16">
-        <v>918.55320754454283</v>
+        <v>961.45439022993946</v>
       </c>
       <c r="H18" s="16">
         <v>1320.1571327557904</v>
@@ -1994,34 +1997,34 @@
         <v>94289.610392787596</v>
       </c>
       <c r="M18" s="16">
-        <v>373.92798740495391</v>
+        <v>429.56603158351845</v>
       </c>
       <c r="N18" s="16">
-        <v>215.8666140356157</v>
+        <v>264.54602871728474</v>
       </c>
       <c r="O18" s="16">
-        <v>6532.5973901108619</v>
+        <v>5541.2107967023103</v>
       </c>
       <c r="P18" s="16">
-        <v>2604.2673481218885</v>
+        <v>2400.2346993936662</v>
       </c>
       <c r="Q18" s="16">
-        <v>0.74619661227411505</v>
+        <v>2.5119424181456744</v>
       </c>
       <c r="R18" s="16">
-        <v>556.11044603265202</v>
+        <v>514.86231045387774</v>
       </c>
       <c r="S18" s="16">
-        <v>4810.7400846338569</v>
+        <v>5562.4758955544876</v>
       </c>
       <c r="T18" s="16">
         <v>409526.89894564264</v>
       </c>
       <c r="U18" s="16">
-        <v>5090.8146842828555</v>
+        <v>5343.1956951397678</v>
       </c>
       <c r="V18" s="16">
-        <v>267.60276690990355</v>
+        <v>301.42798128774854</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -2041,7 +2044,7 @@
         <v>2798.4221022535266</v>
       </c>
       <c r="G19" s="16">
-        <v>947.25497642047981</v>
+        <v>992.88992097665925</v>
       </c>
       <c r="H19" s="16">
         <v>1858.4739014316001</v>
@@ -2059,34 +2062,34 @@
         <v>97339.721439540212</v>
       </c>
       <c r="M19" s="16">
-        <v>379.14214883706074</v>
+        <v>435.35791883841307</v>
       </c>
       <c r="N19" s="16">
-        <v>220.21335062792764</v>
+        <v>269.61547467781907</v>
       </c>
       <c r="O19" s="16">
-        <v>6872.2433838194966</v>
+        <v>5839.8397993231993</v>
       </c>
       <c r="P19" s="16">
-        <v>2690.0825495870854</v>
+        <v>2483.4516812710835</v>
       </c>
       <c r="Q19" s="16">
-        <v>0.76958539798279801</v>
+        <v>2.5939432755638863</v>
       </c>
       <c r="R19" s="16">
-        <v>574.86925940898868</v>
+        <v>533.19731150033078</v>
       </c>
       <c r="S19" s="16">
-        <v>4932.1282617487568</v>
+        <v>5697.2226437316767</v>
       </c>
       <c r="T19" s="16">
         <v>445359.73731244943</v>
       </c>
       <c r="U19" s="16">
-        <v>5299.8297585510263</v>
+        <v>5571.5094381309173</v>
       </c>
       <c r="V19" s="16">
-        <v>303.9004361775514</v>
+        <v>342.66613614191135</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -2106,7 +2109,7 @@
         <v>2802.440878422588</v>
       </c>
       <c r="G20" s="16">
-        <v>975.91533622180293</v>
+        <v>1024.1858203605748</v>
       </c>
       <c r="H20" s="16">
         <v>2403.1475528596202</v>
@@ -2124,34 +2127,34 @@
         <v>100939.4296158151</v>
       </c>
       <c r="M20" s="16">
-        <v>384.78596195631354</v>
+        <v>441.68980993911111</v>
       </c>
       <c r="N20" s="16">
-        <v>224.95124622887064</v>
+        <v>275.19740001542647</v>
       </c>
       <c r="O20" s="16">
-        <v>7221.1070559381715</v>
+        <v>6146.3542966344639</v>
       </c>
       <c r="P20" s="16">
-        <v>2776.2330469138237</v>
+        <v>2566.841751524832</v>
       </c>
       <c r="Q20" s="16">
-        <v>0.79294647204591096</v>
+        <v>2.6755818790198247</v>
       </c>
       <c r="R20" s="16">
-        <v>593.7163696081052</v>
+        <v>551.58861711889756</v>
       </c>
       <c r="S20" s="16">
-        <v>5059.6601430580004</v>
+        <v>5839.4015948747719</v>
       </c>
       <c r="T20" s="16">
         <v>485300.110318897</v>
       </c>
       <c r="U20" s="16">
-        <v>5511.5991593688577</v>
+        <v>5802.2720393783475</v>
       </c>
       <c r="V20" s="16">
-        <v>343.54423394167185</v>
+        <v>387.71368616097209</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -2171,7 +2174,7 @@
         <v>2805.018382007137</v>
       </c>
       <c r="G21" s="16">
-        <v>1004.5071167206745</v>
+        <v>1055.3088601388242</v>
       </c>
       <c r="H21" s="16">
         <v>2942.6310690947575</v>
@@ -2189,34 +2192,34 @@
         <v>105253.56004225269</v>
       </c>
       <c r="M21" s="16">
-        <v>390.87056758089608</v>
+        <v>448.57424140040712</v>
       </c>
       <c r="N21" s="16">
-        <v>230.09511247905587</v>
+        <v>281.30959256471084</v>
       </c>
       <c r="O21" s="16">
-        <v>7579.01458778299</v>
+        <v>6460.5673761155404</v>
       </c>
       <c r="P21" s="16">
-        <v>2862.6608215877736</v>
+        <v>2650.3468586374765</v>
       </c>
       <c r="Q21" s="16">
-        <v>0.81625778220241141</v>
+        <v>2.7567742375495983</v>
       </c>
       <c r="R21" s="16">
-        <v>612.63733781206997</v>
+        <v>570.02117006884941</v>
       </c>
       <c r="S21" s="16">
-        <v>5193.5753459716925</v>
+        <v>5989.2997160576833</v>
       </c>
       <c r="T21" s="16">
         <v>530595.58549012512</v>
       </c>
       <c r="U21" s="16">
-        <v>5725.9570880680376</v>
+        <v>6035.2672419376922</v>
       </c>
       <c r="V21" s="16">
-        <v>386.68613273264384</v>
+        <v>436.73851125085787</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -2236,7 +2239,7 @@
         <v>2806.532548235491</v>
       </c>
       <c r="G22" s="16">
-        <v>1033.0018156282754</v>
+        <v>1086.2272208333268</v>
       </c>
       <c r="H22" s="16">
         <v>3469.1288051136653</v>
@@ -2254,34 +2257,34 @@
         <v>110500.43569183591</v>
       </c>
       <c r="M22" s="16">
-        <v>397.40619041460195</v>
+        <v>456.02259338253077</v>
       </c>
       <c r="N22" s="16">
-        <v>235.65951150916493</v>
+        <v>287.96951585660918</v>
       </c>
       <c r="O22" s="16">
-        <v>7945.7510262283686</v>
+        <v>6782.2557987781765</v>
       </c>
       <c r="P22" s="16">
-        <v>2949.3048299776801</v>
+        <v>2733.9070991328199</v>
       </c>
       <c r="Q22" s="16">
-        <v>0.8394965871715695</v>
+        <v>2.8374352800170817</v>
       </c>
       <c r="R22" s="16">
-        <v>631.61687142014978</v>
+        <v>588.47927127187018</v>
       </c>
       <c r="S22" s="16">
-        <v>5334.0922622019607</v>
+        <v>6147.1777320041247</v>
       </c>
       <c r="T22" s="16">
         <v>582942.74341290176</v>
       </c>
       <c r="U22" s="16">
-        <v>5942.7230807089181</v>
+        <v>6270.2647481636777</v>
       </c>
       <c r="V22" s="16">
-        <v>433.46994194346053</v>
+        <v>489.8963917659762</v>
       </c>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.3">
@@ -2301,7 +2304,7 @@
         <v>2807.2526540154367</v>
       </c>
       <c r="G23" s="16">
-        <v>1061.3726985385092</v>
+        <v>1116.9084826127057</v>
       </c>
       <c r="H23" s="16">
         <v>3977.3664473134559</v>
@@ -2319,34 +2322,34 @@
         <v>116982.91458223342</v>
       </c>
       <c r="M23" s="16">
-        <v>404.40228516365471</v>
+        <v>464.04521749726689</v>
       </c>
       <c r="N23" s="16">
-        <v>241.65885990869768</v>
+        <v>295.19439221965786</v>
       </c>
       <c r="O23" s="16">
-        <v>8320.6283651456488</v>
+        <v>7111.1725065719374</v>
       </c>
       <c r="P23" s="16">
-        <v>3036.1046909199681</v>
+        <v>2817.464265935208</v>
       </c>
       <c r="Q23" s="16">
-        <v>0.86264049813098698</v>
+        <v>2.9174825238960547</v>
       </c>
       <c r="R23" s="16">
-        <v>650.63964700350743</v>
+        <v>606.94737559374551</v>
       </c>
       <c r="S23" s="16">
-        <v>5481.41188694641</v>
+        <v>6313.2739658952842</v>
       </c>
       <c r="T23" s="16">
         <v>644726.02284462529</v>
       </c>
       <c r="U23" s="16">
-        <v>6161.7090072639021</v>
+        <v>6507.030266974225</v>
       </c>
       <c r="V23" s="16">
-        <v>484.47728840343802</v>
+        <v>547.33450681593331</v>
       </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.3">
@@ -2366,7 +2369,7 @@
         <v>2807.373846715212</v>
       </c>
       <c r="G24" s="19">
-        <v>1089.5931909999586</v>
+        <v>1147.3225668630778</v>
       </c>
       <c r="H24" s="19">
         <v>4463.8000501786591</v>
@@ -2384,34 +2387,34 @@
         <v>125140.03470369184</v>
       </c>
       <c r="M24" s="19">
-        <v>411.86760778021534</v>
+        <v>472.65155422893099</v>
       </c>
       <c r="N24" s="19">
-        <v>248.10746773704571</v>
+        <v>303.00127490721547</v>
       </c>
       <c r="O24" s="19">
-        <v>8701.7503891428678</v>
+        <v>7447.0553439995365</v>
       </c>
       <c r="P24" s="19">
-        <v>3123.0029334100595</v>
+        <v>2900.9640004602402</v>
       </c>
       <c r="Q24" s="19">
-        <v>0.88566811717443028</v>
+        <v>2.9968382791884323</v>
       </c>
       <c r="R24" s="19">
-        <v>669.69080524014873</v>
+        <v>625.4105840642319</v>
       </c>
       <c r="S24" s="19">
-        <v>5635.7198952900644</v>
+        <v>6487.8072322372454</v>
       </c>
       <c r="T24" s="19">
         <v>719422.46610239113</v>
       </c>
       <c r="U24" s="19">
-        <v>6382.7276697191774</v>
+        <v>6745.3321001464137</v>
       </c>
       <c r="V24" s="19">
-        <v>541.47267431641626</v>
+        <v>609.18953047120942</v>
       </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.3">
@@ -2431,7 +2434,7 @@
         <v>2806.532548235491</v>
       </c>
       <c r="G25" s="16">
-        <v>1033.0018156282754</v>
+        <v>1086.2272208333268</v>
       </c>
       <c r="H25" s="16">
         <v>3469.1288051136653</v>
@@ -2449,34 +2452,34 @@
         <v>110500.43569183591</v>
       </c>
       <c r="M25" s="16">
-        <v>397.40619041460195</v>
+        <v>456.02259338253077</v>
       </c>
       <c r="N25" s="16">
-        <v>235.65951150916493</v>
+        <v>287.96951585660918</v>
       </c>
       <c r="O25" s="16">
-        <v>7945.7510262283686</v>
+        <v>6782.2557987781765</v>
       </c>
       <c r="P25" s="16">
-        <v>2949.3048299776801</v>
+        <v>2733.9070991328199</v>
       </c>
       <c r="Q25" s="16">
-        <v>0.8394965871715695</v>
+        <v>2.8374352800170817</v>
       </c>
       <c r="R25" s="16">
-        <v>631.61687142014978</v>
+        <v>588.47927127187018</v>
       </c>
       <c r="S25" s="16">
-        <v>5334.0922622019607</v>
+        <v>6147.1777320041247</v>
       </c>
       <c r="T25" s="16">
         <v>582942.74341290176</v>
       </c>
       <c r="U25" s="16">
-        <v>5942.7230807089181</v>
+        <v>6270.2647481636777</v>
       </c>
       <c r="V25" s="16">
-        <v>433.46994194346053</v>
+        <v>489.8963917659762</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -2510,37 +2513,43 @@
       <c r="K28" s="17" t="s">
         <v>245</v>
       </c>
+      <c r="L28" s="17" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="16">
         <v>500</v>
       </c>
       <c r="C29" s="16">
-        <v>0.78262447402116964</v>
+        <v>0.78242212526834742</v>
       </c>
       <c r="D29" s="16">
-        <v>3.6103624819718991</v>
+        <v>3.6072844787500737</v>
       </c>
       <c r="E29" s="16">
-        <v>0.27698049849383055</v>
+        <v>0.27721683884119408</v>
       </c>
       <c r="F29" s="16">
-        <v>1.281642565387907E-2</v>
+        <v>1.3066538362716359E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.74826028008911183</v>
+        <v>0.76196895766048367</v>
       </c>
       <c r="H29" s="16">
-        <v>21.737552597883049</v>
+        <v>21.757787473165259</v>
       </c>
       <c r="I29" s="27">
-        <v>0.55479532636456386</v>
+        <v>0.55495748925804933</v>
       </c>
       <c r="J29" s="27">
-        <v>2.7100821127250807</v>
+        <v>2.7011621800593781</v>
       </c>
       <c r="K29" s="28">
-        <v>0.44739605061109766</v>
+        <v>0.44440626816651491</v>
+      </c>
+      <c r="L29" s="16">
+        <v>271185.61739746912</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -2548,31 +2557,34 @@
         <v>550</v>
       </c>
       <c r="C30" s="16">
-        <v>0.77399453736568069</v>
+        <v>0.77379109842151894</v>
       </c>
       <c r="D30" s="16">
-        <v>3.4343290519720306</v>
+        <v>3.4315225659633617</v>
       </c>
       <c r="E30" s="16">
-        <v>0.29117768998453675</v>
+        <v>0.29141583095469492</v>
       </c>
       <c r="F30" s="16">
-        <v>1.2617425534863374E-2</v>
+        <v>1.2891638164129249E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.7373530835658616</v>
+        <v>0.75238267777592416</v>
       </c>
       <c r="H30" s="16">
-        <v>22.60054626343193</v>
+        <v>22.620890157848095</v>
       </c>
       <c r="I30" s="27">
-        <v>0.49803482116969444</v>
+        <v>0.49822687482478595</v>
       </c>
       <c r="J30" s="27">
-        <v>2.4959205152111394</v>
+        <v>2.4910433500341069</v>
       </c>
       <c r="K30" s="28">
-        <v>0.40127382417381829</v>
+        <v>0.39883087493488928</v>
+      </c>
+      <c r="L30" s="16">
+        <v>291606.51793647528</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -2580,31 +2592,34 @@
         <v>600</v>
       </c>
       <c r="C31" s="16">
-        <v>0.76837261991511163</v>
+        <v>0.76816856453119997</v>
       </c>
       <c r="D31" s="16">
-        <v>3.3268442538149596</v>
+        <v>3.3242205831492848</v>
       </c>
       <c r="E31" s="16">
-        <v>0.3005851562943711</v>
+        <v>0.30082239580281539</v>
       </c>
       <c r="F31" s="16">
-        <v>1.2473825598042339E-2</v>
+        <v>1.278733576486221E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.72948237102870062</v>
+        <v>0.74666586327209783</v>
       </c>
       <c r="H31" s="16">
-        <v>23.162738008488827</v>
+        <v>23.183143546879993</v>
       </c>
       <c r="I31" s="27">
-        <v>0.45425048223596226</v>
+        <v>0.45446714965679885</v>
       </c>
       <c r="J31" s="27">
-        <v>2.3270277644889958</v>
+        <v>2.3250397584419025</v>
       </c>
       <c r="K31" s="28">
-        <v>0.36467370004283456</v>
+        <v>0.36261809597367145</v>
+      </c>
+      <c r="L31" s="16">
+        <v>314585.69009998813</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -2612,223 +2627,244 @@
         <v>650</v>
       </c>
       <c r="C32" s="16">
-        <v>0.76551349203463515</v>
+        <v>0.76530948809116828</v>
       </c>
       <c r="D32" s="16">
-        <v>3.2743310235910545</v>
+        <v>3.271829112247401</v>
       </c>
       <c r="E32" s="16">
-        <v>0.30540589598154644</v>
+        <v>0.30563943460760568</v>
       </c>
       <c r="F32" s="16">
-        <v>1.2369649611576152E-2</v>
+        <v>1.2743286995087122E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.72377248521048898</v>
+        <v>0.7442515502007252</v>
       </c>
       <c r="H32" s="16">
-        <v>23.448650796536484</v>
+        <v>23.469051190883171</v>
       </c>
       <c r="I32" s="27">
-        <v>0.41966430087213957</v>
+        <v>0.41990490870863312</v>
       </c>
       <c r="J32" s="27">
-        <v>2.1902422405774988</v>
+        <v>2.1903670853712032</v>
       </c>
       <c r="K32" s="28">
-        <v>0.33485134082926482</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.33308227081863279</v>
+      </c>
+      <c r="L32" s="16">
+        <v>340838.03257900785</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="16">
         <v>700</v>
       </c>
       <c r="C33" s="16">
-        <v>0.76527370381661175</v>
+        <v>0.76507062462510711</v>
       </c>
       <c r="D33" s="16">
-        <v>3.2702983290412786</v>
+        <v>3.2678726940159533</v>
       </c>
       <c r="E33" s="16">
-        <v>0.30578250036691917</v>
+        <v>0.30600947271635609</v>
       </c>
       <c r="F33" s="16">
-        <v>1.2295925511029119E-2</v>
+        <v>1.2760809080769826E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.7197316672595061</v>
+        <v>0.74521193571699418</v>
       </c>
       <c r="H33" s="16">
-        <v>23.472629618338825</v>
+        <v>23.49293753748929</v>
       </c>
       <c r="I33" s="27">
-        <v>0.3919406015251149</v>
+        <v>0.39220717719614501</v>
       </c>
       <c r="J33" s="27">
-        <v>2.0770940382010674</v>
+        <v>2.0787757296949785</v>
       </c>
       <c r="K33" s="28">
-        <v>0.3100391304582043</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.30848872359028245</v>
+      </c>
+      <c r="L33" s="16">
+        <v>371288.85853231192</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="16">
         <v>750</v>
       </c>
       <c r="C34" s="16">
-        <v>0.76758206960391329</v>
+        <v>0.76738100799023989</v>
       </c>
       <c r="D34" s="16">
-        <v>3.3131307362151041</v>
+        <v>3.3107446818006947</v>
       </c>
       <c r="E34" s="16">
-        <v>0.30182932085028208</v>
+        <v>0.30204684930766268</v>
       </c>
       <c r="F34" s="16">
-        <v>1.2247524296224374E-2</v>
+        <v>1.2855676451430006E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.71707879667605801</v>
+        <v>0.75041161630287867</v>
       </c>
       <c r="H34" s="16">
-        <v>23.241793039608684</v>
+        <v>23.261899200976021</v>
       </c>
       <c r="I34" s="27">
-        <v>0.36958489916238402</v>
+        <v>0.36988412923629177</v>
       </c>
       <c r="J34" s="27">
-        <v>1.9818647665588232</v>
+        <v>1.9846913920253857</v>
       </c>
       <c r="K34" s="28">
-        <v>0.28904265664208295</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.28766394159577441</v>
+      </c>
+      <c r="L34" s="16">
+        <v>407168.97522858367</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="16">
         <v>800.00000000000011</v>
       </c>
       <c r="C35" s="16">
-        <v>0.77242084233413699</v>
+        <v>0.77222313223091421</v>
       </c>
       <c r="D35" s="16">
-        <v>3.4053466482438601</v>
+        <v>3.4029679648293816</v>
       </c>
       <c r="E35" s="16">
-        <v>0.29365586041459268</v>
+        <v>0.29386112662101954</v>
       </c>
       <c r="F35" s="16">
-        <v>1.2221865877615829E-2</v>
+        <v>1.3075242228025856E-2</v>
       </c>
       <c r="G35" s="16">
-        <v>0.7156724587521236</v>
+        <v>0.76244601651809718</v>
       </c>
       <c r="H35" s="16">
-        <v>22.757915766586301</v>
+        <v>22.777686776908567</v>
       </c>
       <c r="I35" s="27">
-        <v>0.351638456117429</v>
+        <v>0.35198545686127924</v>
       </c>
       <c r="J35" s="27">
-        <v>1.9005496689146004</v>
+        <v>1.904205650074752</v>
       </c>
       <c r="K35" s="28">
-        <v>0.27102443565787682</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.26978389328349178</v>
+      </c>
+      <c r="L35" s="16">
+        <v>450161.87122959318</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="16">
         <v>850.00000000000011</v>
       </c>
       <c r="C36" s="16">
-        <v>0.77981264779428183</v>
+        <v>0.77962057221306336</v>
       </c>
       <c r="D36" s="16">
-        <v>3.5538595408273626</v>
+        <v>3.5514603826199638</v>
       </c>
       <c r="E36" s="16">
-        <v>0.28138422143920555</v>
+        <v>0.28157430810541256</v>
       </c>
       <c r="F36" s="16">
-        <v>1.2218403031162202E-2</v>
+        <v>1.3578355310744016E-2</v>
       </c>
       <c r="G36" s="16">
-        <v>0.71548266013800033</v>
+        <v>0.79002164458187951</v>
       </c>
       <c r="H36" s="16">
-        <v>22.018735220571827</v>
+        <v>22.037942778693676</v>
       </c>
       <c r="I36" s="28">
-        <v>0.33751958014128181</v>
+        <v>0.33795246909963766</v>
       </c>
       <c r="J36" s="28">
-        <v>1.8302565895569651</v>
+        <v>1.834493272206426</v>
       </c>
       <c r="K36" s="28">
-        <v>0.25537881890345748</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.25425185524575955</v>
+      </c>
+      <c r="L36" s="16">
+        <v>502641.67085077928</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="19">
         <v>900.00000000000011</v>
       </c>
       <c r="C37" s="19">
-        <v>0.78981118179505139</v>
+        <v>0.78962936354720115</v>
       </c>
       <c r="D37" s="16">
-        <v>3.7712780438718494</v>
+        <v>3.7688390112720156</v>
       </c>
       <c r="E37" s="16">
-        <v>0.26516209846286815</v>
+        <v>0.26533370011538154</v>
       </c>
       <c r="F37" s="16">
-        <v>1.2238649661083623E-2</v>
+        <v>1.5671120364137446E-2</v>
       </c>
       <c r="G37" s="16">
-        <v>0.71659237792399344</v>
+        <v>0.90472609715837349</v>
       </c>
       <c r="H37" s="16">
-        <v>21.018881820494862</v>
+        <v>21.037063645279886</v>
       </c>
       <c r="I37" s="28">
-        <v>0.32695318462824652</v>
+        <v>0.32766989951505937</v>
       </c>
       <c r="J37" s="28">
-        <v>1.7688468583257713</v>
+        <v>1.7734603234489266</v>
       </c>
       <c r="K37" s="28">
-        <v>0.24165697581777615</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.24062457505250273</v>
+      </c>
+      <c r="L37" s="16">
+        <v>568077.10402998899</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="16">
         <v>800.00000000000011</v>
       </c>
       <c r="C38" s="16">
-        <v>0.77242084233413699</v>
+        <v>0.77222313223091421</v>
       </c>
       <c r="D38" s="18">
-        <v>3.4053466482438601</v>
+        <v>3.4029679648293816</v>
       </c>
       <c r="E38" s="18">
-        <v>0.29365586041459268</v>
+        <v>0.29386112662101954</v>
       </c>
       <c r="F38" s="18">
-        <v>1.2221865877615829E-2</v>
+        <v>1.3075242228025856E-2</v>
       </c>
       <c r="G38" s="18">
-        <v>0.7156724587521236</v>
+        <v>0.76244601651809718</v>
       </c>
       <c r="H38" s="18">
-        <v>22.757915766586301</v>
+        <v>22.777686776908567</v>
       </c>
       <c r="I38" s="29">
-        <v>0.351638456117429</v>
+        <v>0.35198545686127924</v>
       </c>
       <c r="J38" s="29">
-        <v>1.9005496689146004</v>
+        <v>1.904205650074752</v>
       </c>
       <c r="K38" s="29">
-        <v>0.27102443565787682</v>
+        <v>0.26978389328349178</v>
+      </c>
+      <c r="L38" s="16">
+        <v>450161.87122959318</v>
       </c>
     </row>
   </sheetData>
@@ -2886,34 +2922,34 @@
         <v>2.5</v>
       </c>
       <c r="C3" s="16">
-        <v>0.14816689369741928</v>
+        <v>148.47875374177946</v>
       </c>
       <c r="D3" s="16">
-        <v>6.7342358759702702E-3</v>
+        <v>7.0460959203304396</v>
       </c>
       <c r="E3" s="16">
-        <v>56.964645761388169</v>
+        <v>57.084544319769137</v>
       </c>
       <c r="F3" s="16">
-        <v>21.165348938260554</v>
+        <v>20.777443537420119</v>
       </c>
       <c r="G3" s="16">
-        <v>55.908324645574957</v>
+        <v>54.858272297545774</v>
       </c>
       <c r="H3" s="16">
-        <v>59.189719664805004</v>
+        <v>17.761735672472536</v>
       </c>
       <c r="I3" s="16">
-        <v>57.729279005009204</v>
+        <v>17.370675747296715</v>
       </c>
       <c r="J3" s="16">
-        <v>26</v>
+        <v>82.316245968108603</v>
       </c>
       <c r="K3" s="16">
-        <v>0.11950172563922697</v>
+        <v>37.633341482190204</v>
       </c>
       <c r="L3" s="16">
-        <v>1.0679490088069992</v>
+        <v>336.31723323673612</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -2921,34 +2957,34 @@
         <v>2.7</v>
       </c>
       <c r="C4" s="16">
-        <v>0.15566697058060769</v>
+        <v>156.07764404148372</v>
       </c>
       <c r="D4" s="16">
-        <v>7.5293584802110817E-3</v>
+        <v>7.9400319410870903</v>
       </c>
       <c r="E4" s="16">
-        <v>57.545256030232352</v>
+        <v>57.697069284918236</v>
       </c>
       <c r="F4" s="16">
-        <v>21.351660780792912</v>
+        <v>20.931122887739914</v>
       </c>
       <c r="G4" s="16">
-        <v>56.402821541456284</v>
+        <v>55.264433674005062</v>
       </c>
       <c r="H4" s="16">
-        <v>58.944174168235278</v>
+        <v>17.067449346516845</v>
       </c>
       <c r="I4" s="16">
-        <v>57.489748166950314</v>
+        <v>16.691333905799326</v>
       </c>
       <c r="J4" s="16">
-        <v>26</v>
+        <v>84.40849039724651</v>
       </c>
       <c r="K4" s="16">
-        <v>0.13305711404850473</v>
+        <v>40.749675684056633</v>
       </c>
       <c r="L4" s="16">
-        <v>1.1890892144253362</v>
+        <v>364.16692330767307</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -2956,34 +2992,34 @@
         <v>2.9</v>
       </c>
       <c r="C5" s="16">
-        <v>0.16227893989998951</v>
+        <v>162.75131129996333</v>
       </c>
       <c r="D5" s="16">
-        <v>8.1624683336946058E-3</v>
+        <v>8.6348397336684144</v>
       </c>
       <c r="E5" s="16">
-        <v>57.867796024364097</v>
+        <v>58.036241121665519</v>
       </c>
       <c r="F5" s="16">
-        <v>21.451381804251511</v>
+        <v>21.009363217890819</v>
       </c>
       <c r="G5" s="16">
-        <v>56.667788907976181</v>
+        <v>55.471253223051519</v>
       </c>
       <c r="H5" s="16">
-        <v>58.761692285486703</v>
+        <v>16.644428995114723</v>
       </c>
       <c r="I5" s="16">
-        <v>57.311736430927176</v>
+        <v>16.278080188040537</v>
       </c>
       <c r="J5" s="16">
-        <v>26</v>
+        <v>86.6984682173848</v>
       </c>
       <c r="K5" s="16">
-        <v>0.14379864522624392</v>
+        <v>43.218937629596283</v>
       </c>
       <c r="L5" s="16">
-        <v>1.285082870692426</v>
+        <v>386.233933914575</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -2991,34 +3027,34 @@
         <v>3.1</v>
       </c>
       <c r="C6" s="16">
-        <v>0.16816932560061704</v>
+        <v>168.68204688771863</v>
       </c>
       <c r="D6" s="16">
-        <v>8.686527999868951E-3</v>
+        <v>9.1992492869705451</v>
       </c>
       <c r="E6" s="16">
-        <v>58.033954827081338</v>
+        <v>58.210891042459892</v>
       </c>
       <c r="F6" s="16">
-        <v>21.498673305116203</v>
+        <v>21.04199533313205</v>
       </c>
       <c r="G6" s="16">
-        <v>56.79378761358371</v>
+        <v>55.557569257932535</v>
       </c>
       <c r="H6" s="16">
-        <v>58.618045868696775</v>
+        <v>16.366457101782501</v>
       </c>
       <c r="I6" s="16">
-        <v>57.171608974412401</v>
+        <v>16.007011189269914</v>
       </c>
       <c r="J6" s="16">
-        <v>26</v>
+        <v>89.014517329761588</v>
       </c>
       <c r="K6" s="16">
-        <v>0.15265687096659597</v>
+        <v>45.277885494100374</v>
       </c>
       <c r="L6" s="16">
-        <v>1.3642460237648557</v>
+        <v>404.63409775589656</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -3026,34 +3062,34 @@
         <v>3.3</v>
       </c>
       <c r="C7" s="16">
-        <v>0.17345261418436411</v>
+        <v>173.99251938127557</v>
       </c>
       <c r="D7" s="16">
-        <v>9.1364978290003895E-3</v>
+        <v>9.6764030259118439</v>
       </c>
       <c r="E7" s="16">
-        <v>58.09849493424899</v>
+        <v>58.279337866454064</v>
       </c>
       <c r="F7" s="16">
-        <v>21.511617804235726</v>
+        <v>21.044437590006492</v>
       </c>
       <c r="G7" s="16">
-        <v>56.828779788176234</v>
+        <v>55.564132067774985</v>
       </c>
       <c r="H7" s="16">
-        <v>58.499426691536961</v>
+        <v>16.172669607570381</v>
       </c>
       <c r="I7" s="16">
-        <v>57.055895750215626</v>
+        <v>15.818421386676986</v>
       </c>
       <c r="J7" s="16">
-        <v>26</v>
+        <v>91.299177192676552</v>
       </c>
       <c r="K7" s="16">
-        <v>0.16023965484701469</v>
+        <v>47.066082002986029</v>
       </c>
       <c r="L7" s="16">
-        <v>1.4320109575829549</v>
+        <v>420.61464263088794</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -3061,34 +3097,34 @@
         <v>3.5</v>
       </c>
       <c r="C8" s="16">
-        <v>0.17821771118453278</v>
+        <v>178.77612677578253</v>
       </c>
       <c r="D8" s="16">
-        <v>9.5336854968264082E-3</v>
+        <v>10.092101088076173</v>
       </c>
       <c r="E8" s="16">
-        <v>58.093587340872254</v>
+        <v>58.275613945900197</v>
       </c>
       <c r="F8" s="16">
-        <v>21.500883358703305</v>
+        <v>21.025833603341166</v>
       </c>
       <c r="G8" s="16">
-        <v>56.801054877285281</v>
+        <v>55.515104462653355</v>
       </c>
       <c r="H8" s="16">
-        <v>58.397997958337498</v>
+        <v>16.031740671705105</v>
       </c>
       <c r="I8" s="16">
-        <v>56.956951903247862</v>
+        <v>15.681594954806616</v>
       </c>
       <c r="J8" s="16">
-        <v>26</v>
+        <v>93.532298322480699</v>
       </c>
       <c r="K8" s="16">
-        <v>0.16691573452926184</v>
+        <v>48.664309641923587</v>
       </c>
       <c r="L8" s="16">
-        <v>1.4916729636438284</v>
+        <v>434.8974959848569</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -3161,64 +3197,64 @@
         <v>2.5</v>
       </c>
       <c r="C16" s="16">
-        <v>2.6648478767473245</v>
+        <v>2664.8478767473252</v>
       </c>
       <c r="D16" s="16">
-        <v>0.98637006924873272</v>
+        <v>986.37006924873401</v>
       </c>
       <c r="E16" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F16" s="16">
-        <v>2.3988101530183341</v>
+        <v>2398.8101530183258</v>
       </c>
       <c r="G16" s="16">
-        <v>0.99703770676192471</v>
+        <v>1041.3468841175195</v>
       </c>
       <c r="H16" s="16">
-        <v>6.9476550741795799</v>
+        <v>6947.6550741795809</v>
       </c>
       <c r="I16" s="16">
-        <v>9.2492997745483656</v>
+        <v>9249.2997745483663</v>
       </c>
       <c r="J16" s="16">
-        <v>102.3755615721311</v>
+        <v>102375.56157213112</v>
       </c>
       <c r="K16" s="16">
-        <v>274.63810828811501</v>
+        <v>274638.10828811495</v>
       </c>
       <c r="L16" s="16">
-        <v>119.16108401865955</v>
+        <v>119161.08401865959</v>
       </c>
       <c r="M16" s="16">
-        <v>3.5346036023974392</v>
+        <v>430.56666413791532</v>
       </c>
       <c r="N16" s="16">
-        <v>2.7601883775233755</v>
+        <v>263.71291568172506</v>
       </c>
       <c r="O16" s="16">
-        <v>8.1751551300820342</v>
+        <v>6046.2345139607469</v>
       </c>
       <c r="P16" s="16">
-        <v>3.7000428190667423</v>
+        <v>2598.8390560364678</v>
       </c>
       <c r="Q16" s="16">
-        <v>8.0994118158368082E-4</v>
+        <v>2.7206981667653416</v>
       </c>
       <c r="R16" s="16">
-        <v>0.75406058026615341</v>
+        <v>557.37419969541145</v>
       </c>
       <c r="S16" s="16">
-        <v>-1.4577184054056023</v>
+        <v>6888.6844784927525</v>
       </c>
       <c r="T16" s="16">
-        <v>686.59527072028743</v>
+        <v>686595.27072028746</v>
       </c>
       <c r="U16" s="16">
-        <v>2.8287445516591152</v>
+        <v>5818.0961910909264</v>
       </c>
       <c r="V16" s="16">
-        <v>541.25711784027646</v>
+        <v>320.92719452954594</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -3226,64 +3262,64 @@
         <v>2.7</v>
       </c>
       <c r="C17" s="16">
-        <v>3.0873746791042942</v>
+        <v>3087.3746791042909</v>
       </c>
       <c r="D17" s="16">
-        <v>1.0581726709377508</v>
+        <v>1058.1726709377524</v>
       </c>
       <c r="E17" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F17" s="16">
-        <v>2.74151919271308</v>
+        <v>2741.5191927130818</v>
       </c>
       <c r="G17" s="16">
-        <v>1.0765328210015159</v>
+        <v>1132.6607037394215</v>
       </c>
       <c r="H17" s="16">
-        <v>4.8122007797128168</v>
+        <v>4812.2007797128163</v>
       </c>
       <c r="I17" s="16">
-        <v>8.7983787257595463</v>
+        <v>8798.3787257595359</v>
       </c>
       <c r="J17" s="16">
-        <v>106.47250431367063</v>
+        <v>106472.50431367061</v>
       </c>
       <c r="K17" s="16">
-        <v>285.62878406094933</v>
+        <v>285628.78406094934</v>
       </c>
       <c r="L17" s="16">
-        <v>124.16319568817148</v>
+        <v>124163.1956881715</v>
       </c>
       <c r="M17" s="16">
-        <v>3.1814466598366935</v>
+        <v>465.16181761897388</v>
       </c>
       <c r="N17" s="16">
-        <v>2.529223250303231</v>
+        <v>295.92646489174422</v>
       </c>
       <c r="O17" s="16">
-        <v>9.724441884323193</v>
+        <v>7233.1985651124287</v>
       </c>
       <c r="P17" s="16">
-        <v>4.529450195716997</v>
+        <v>2857.8379919673444</v>
       </c>
       <c r="Q17" s="16">
-        <v>8.7497071764366474E-4</v>
+        <v>2.9586199441852878</v>
       </c>
       <c r="R17" s="16">
-        <v>0.87717648611728305</v>
+        <v>615.69121606216436</v>
       </c>
       <c r="S17" s="16">
-        <v>-1.8187458306705648</v>
+        <v>6524.6167069608418</v>
       </c>
       <c r="T17" s="16">
-        <v>714.07196015237332</v>
+        <v>714071.9601523733</v>
       </c>
       <c r="U17" s="16">
-        <v>3.1808572198766729</v>
+        <v>6610.4897515975899</v>
       </c>
       <c r="V17" s="16">
-        <v>561.58584447833709</v>
+        <v>559.45962453110246</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -3291,64 +3327,64 @@
         <v>2.9</v>
       </c>
       <c r="C18" s="16">
-        <v>3.4833349591886873</v>
+        <v>3483.3349591886849</v>
       </c>
       <c r="D18" s="16">
-        <v>1.1128283922583833</v>
+        <v>1112.8283922583832</v>
       </c>
       <c r="E18" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F18" s="16">
-        <v>3.0626461462244623</v>
+        <v>3062.6461462244392</v>
       </c>
       <c r="G18" s="16">
-        <v>1.134911883330149</v>
+        <v>1197.4264255678095</v>
       </c>
       <c r="H18" s="16">
-        <v>3.2619581509413549</v>
+        <v>3261.9581509413547</v>
       </c>
       <c r="I18" s="16">
-        <v>8.3890102350076639</v>
+        <v>8389.0102350076741</v>
       </c>
       <c r="J18" s="16">
-        <v>110.37627722141367</v>
+        <v>110376.27722141369</v>
       </c>
       <c r="K18" s="16">
-        <v>296.10125219792326</v>
+        <v>296101.25219792326</v>
       </c>
       <c r="L18" s="16">
-        <v>128.95181516126439</v>
+        <v>128951.81516126439</v>
       </c>
       <c r="M18" s="16">
-        <v>2.8853526256065507</v>
+        <v>503.48763200050263</v>
       </c>
       <c r="N18" s="16">
-        <v>2.3603321076499659</v>
+        <v>332.52622722948848</v>
       </c>
       <c r="O18" s="16">
-        <v>10.97919765967354</v>
+        <v>8230.0684789243242</v>
       </c>
       <c r="P18" s="16">
-        <v>5.3268577223470821</v>
+        <v>3052.5799129535576</v>
       </c>
       <c r="Q18" s="16">
-        <v>9.2282153852808952E-4</v>
+        <v>3.1274897323413353</v>
       </c>
       <c r="R18" s="16">
-        <v>0.98324170106960251</v>
+        <v>659.54879822657836</v>
       </c>
       <c r="S18" s="16">
-        <v>-1.9782079329278976</v>
+        <v>6419.2510009520001</v>
       </c>
       <c r="T18" s="16">
-        <v>740.25313049480803</v>
+        <v>740253.13049480808</v>
       </c>
       <c r="U18" s="16">
-        <v>3.4629181106772062</v>
+        <v>7224.9070232672921</v>
       </c>
       <c r="V18" s="16">
-        <v>581.43710587328212</v>
+        <v>819.69460213791945</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -3356,64 +3392,64 @@
         <v>3.1</v>
       </c>
       <c r="C19" s="16">
-        <v>3.849845505000594</v>
+        <v>3849.8455050005987</v>
       </c>
       <c r="D19" s="16">
-        <v>1.1592727723247735</v>
+        <v>1159.2727723247745</v>
       </c>
       <c r="E19" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F19" s="16">
-        <v>3.3649348540762438</v>
+        <v>3364.9348540762367</v>
       </c>
       <c r="G19" s="16">
-        <v>1.180098670358233</v>
+        <v>1246.1198012916427</v>
       </c>
       <c r="H19" s="16">
-        <v>2.0882936759883304</v>
+        <v>2088.2936759883305</v>
       </c>
       <c r="I19" s="16">
-        <v>8.0256331977169904</v>
+        <v>8025.6331977169812</v>
       </c>
       <c r="J19" s="16">
-        <v>114.05521230881628</v>
+        <v>114055.21230881629</v>
       </c>
       <c r="K19" s="16">
-        <v>305.9705584796489</v>
+        <v>305970.5584796489</v>
       </c>
       <c r="L19" s="16">
-        <v>133.48492502395891</v>
+        <v>133484.92502395887</v>
       </c>
       <c r="M19" s="16">
-        <v>2.6354072076822548</v>
+        <v>542.96286866639048</v>
       </c>
       <c r="N19" s="16">
-        <v>2.2303460991928903</v>
+        <v>371.22358570482589</v>
       </c>
       <c r="O19" s="16">
-        <v>12.030465799378224</v>
+        <v>9062.4264174487907</v>
       </c>
       <c r="P19" s="16">
-        <v>6.0914841011854417</v>
+        <v>3207.7054900750236</v>
       </c>
       <c r="Q19" s="16">
-        <v>9.5992122731354003E-4</v>
+        <v>3.2545600708319835</v>
       </c>
       <c r="R19" s="16">
-        <v>1.0770012172548296</v>
+        <v>694.3386324507901</v>
       </c>
       <c r="S19" s="16">
-        <v>-2.0298275997064565</v>
+        <v>6454.9424924722334</v>
       </c>
       <c r="T19" s="16">
-        <v>764.92639619912222</v>
+        <v>764926.39619912219</v>
       </c>
       <c r="U19" s="16">
-        <v>3.6974779927046795</v>
+        <v>7722.3379691653845</v>
       </c>
       <c r="V19" s="16">
-        <v>600.45454593690408</v>
+        <v>1117.4058748848802</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -3421,64 +3457,64 @@
         <v>3.3</v>
       </c>
       <c r="C20" s="16">
-        <v>4.1897807746840847</v>
+        <v>4189.7807746840863</v>
       </c>
       <c r="D20" s="16">
-        <v>1.2005121499819216</v>
+        <v>1200.5121499819197</v>
       </c>
       <c r="E20" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F20" s="16">
-        <v>3.6506399459165988</v>
+        <v>3650.6399459165932</v>
       </c>
       <c r="G20" s="16">
-        <v>1.2168194568160069</v>
+        <v>1284.6957381636407</v>
       </c>
       <c r="H20" s="16">
-        <v>1.1736306340101292</v>
+        <v>1173.6306340101291</v>
       </c>
       <c r="I20" s="16">
-        <v>7.7003977334383675</v>
+        <v>7700.3977334383871</v>
       </c>
       <c r="J20" s="16">
-        <v>117.50774436055892</v>
+        <v>117507.74436055892</v>
       </c>
       <c r="K20" s="16">
-        <v>315.23250397653982</v>
+        <v>315232.50397653977</v>
       </c>
       <c r="L20" s="16">
-        <v>137.75725064697997</v>
+        <v>137757.25064697993</v>
       </c>
       <c r="M20" s="16">
-        <v>2.4234137716096513</v>
+        <v>582.62933471651218</v>
       </c>
       <c r="N20" s="16">
-        <v>2.1260232594346991</v>
+        <v>411.08241365598059</v>
       </c>
       <c r="O20" s="16">
-        <v>12.941619902553503</v>
+        <v>9774.1074490298797</v>
       </c>
       <c r="P20" s="16">
-        <v>6.8292880756010712</v>
+        <v>3337.5714984830197</v>
       </c>
       <c r="Q20" s="16">
-        <v>9.9011228412205468E-4</v>
+        <v>3.355315812650959</v>
       </c>
       <c r="R20" s="16">
-        <v>1.1620598783187359</v>
+        <v>723.25774816297871</v>
       </c>
       <c r="S20" s="16">
-        <v>-2.026489666506686</v>
+        <v>6572.6516565008551</v>
       </c>
       <c r="T20" s="16">
-        <v>788.08125994134957</v>
+        <v>788081.2599413495</v>
       </c>
       <c r="U20" s="16">
-        <v>3.8996313447041677</v>
+        <v>8141.364163259821</v>
       </c>
       <c r="V20" s="16">
-        <v>618.52827306702056</v>
+        <v>1441.3207479618454</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -3486,64 +3522,64 @@
         <v>3.5</v>
       </c>
       <c r="C21" s="16">
-        <v>4.5064720702113261</v>
+        <v>4506.4720702113282</v>
       </c>
       <c r="D21" s="16">
-        <v>1.2378443466263889</v>
+        <v>1237.8443466263898</v>
       </c>
       <c r="E21" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F21" s="16">
-        <v>3.9216241291317857</v>
+        <v>3921.6241291317938</v>
       </c>
       <c r="G21" s="16">
-        <v>1.2477923804527091</v>
+        <v>1316.5083531758189</v>
       </c>
       <c r="H21" s="16">
-        <v>0.44774442370759787</v>
+        <v>447.74442370759789</v>
       </c>
       <c r="I21" s="16">
-        <v>7.4057577728634207</v>
+        <v>7405.7577728634324</v>
       </c>
       <c r="J21" s="16">
-        <v>120.74612116199641</v>
+        <v>120746.12116199643</v>
       </c>
       <c r="K21" s="16">
-        <v>323.91994524683048</v>
+        <v>323919.94524683047</v>
       </c>
       <c r="L21" s="16">
-        <v>141.78080722790236</v>
+        <v>141780.80722790223</v>
       </c>
       <c r="M21" s="16">
-        <v>2.2427534299674861</v>
+        <v>622.09377831070992</v>
       </c>
       <c r="N21" s="16">
-        <v>2.0396538942054714</v>
+        <v>451.64555185080081</v>
       </c>
       <c r="O21" s="16">
-        <v>13.751892148659186</v>
+        <v>10394.910711552422</v>
       </c>
       <c r="P21" s="16">
-        <v>7.5454352560223921</v>
+        <v>3450.3707440606868</v>
       </c>
       <c r="Q21" s="16">
-        <v>1.0156068599449534E-3</v>
+        <v>3.4384776896527947</v>
       </c>
       <c r="R21" s="16">
-        <v>1.240742535294457</v>
+        <v>748.15376648165773</v>
       </c>
       <c r="S21" s="16">
-        <v>-1.9959093778783614</v>
+        <v>6741.3478561697184</v>
       </c>
       <c r="T21" s="16">
-        <v>809.79986311707626</v>
+        <v>809799.86311707599</v>
       </c>
       <c r="U21" s="16">
-        <v>4.0786349558568915</v>
+        <v>8505.1460801241319</v>
       </c>
       <c r="V21" s="16">
-        <v>635.66078391880546</v>
+        <v>1783.0262165573138</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -3574,31 +3610,34 @@
         <v>2.5</v>
       </c>
       <c r="C29" s="16">
-        <v>0.78832048649630093</v>
+        <v>0.79174994690516309</v>
       </c>
       <c r="D29" s="16">
-        <v>3.7245806284405534</v>
+        <v>3.8106225411188035</v>
       </c>
       <c r="E29" s="16">
-        <v>0.26848660285780696</v>
+        <v>0.26242431235563907</v>
       </c>
       <c r="F29" s="16">
-        <v>1.0953340502488237E-2</v>
+        <v>1.2687298913338699E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.64614458294138033</v>
+        <v>0.74118284344009411</v>
       </c>
       <c r="H29" s="16">
-        <v>21.167951350369908</v>
+        <v>20.8250053094837</v>
       </c>
       <c r="I29" s="16">
-        <v>0.34227557338586767</v>
+        <v>0.32430261625935458</v>
       </c>
       <c r="J29" s="16">
-        <v>0.5548833499916922</v>
+        <v>1.6805077812729865</v>
       </c>
       <c r="K29" s="16">
-        <v>0.26660671501238004</v>
+        <v>0.23827129619979173</v>
+      </c>
+      <c r="L29" s="16">
+        <v>543611.76913812361</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -3606,31 +3645,34 @@
         <v>2.7</v>
       </c>
       <c r="C30" s="16">
-        <v>0.78645553363907783</v>
+        <v>0.7898967612993093</v>
       </c>
       <c r="D30" s="16">
-        <v>3.6833459547396958</v>
+        <v>3.7737906634812184</v>
       </c>
       <c r="E30" s="16">
-        <v>0.2714922823671258</v>
+        <v>0.26498555144485081</v>
       </c>
       <c r="F30" s="16">
-        <v>1.094156940291963E-2</v>
+        <v>1.3781762480049234E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.64549940897402491</v>
+        <v>0.8011703915314986</v>
       </c>
       <c r="H30" s="16">
-        <v>21.354446636092216</v>
+        <v>21.010323870069069</v>
       </c>
       <c r="I30" s="16">
-        <v>0.34415283549829428</v>
+        <v>0.32689074998505646</v>
       </c>
       <c r="J30" s="16">
-        <v>0.55975126890578497</v>
+        <v>1.7604771696928734</v>
       </c>
       <c r="K30" s="16">
-        <v>0.26807615264009277</v>
+        <v>0.24020565000670163</v>
+      </c>
+      <c r="L30" s="16">
+        <v>564043.12865900912</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -3638,31 +3680,34 @@
         <v>2.9</v>
       </c>
       <c r="C31" s="16">
-        <v>0.78545713880957391</v>
+        <v>0.78879031794552723</v>
       </c>
       <c r="D31" s="16">
-        <v>3.6615689654728993</v>
+        <v>3.7544703747794781</v>
       </c>
       <c r="E31" s="16">
-        <v>0.27310696846887</v>
+        <v>0.26634915185839914</v>
       </c>
       <c r="F31" s="16">
-        <v>1.0928430721673115E-2</v>
+        <v>1.3238832473157039E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.64477927785490341</v>
+        <v>0.77141239785373727</v>
       </c>
       <c r="H31" s="16">
-        <v>21.4542861190426</v>
+        <v>21.120968205447276</v>
       </c>
       <c r="I31" s="16">
-        <v>0.34609269486344429</v>
+        <v>0.3292352858262676</v>
       </c>
       <c r="J31" s="16">
-        <v>0.56468232790516182</v>
+        <v>1.8183987140116196</v>
       </c>
       <c r="K31" s="16">
-        <v>0.26990580548077292</v>
+        <v>0.24236345670487044</v>
+      </c>
+      <c r="L31" s="16">
+        <v>583904.50216317154</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -3670,95 +3715,104 @@
         <v>3.1</v>
       </c>
       <c r="C32" s="16">
-        <v>0.7849834296744499</v>
+        <v>0.78811039511838488</v>
       </c>
       <c r="D32" s="16">
-        <v>3.651311029911978</v>
+        <v>3.7454166424866164</v>
       </c>
       <c r="E32" s="16">
-        <v>0.2738742308743024</v>
+        <v>0.26699299315765596</v>
       </c>
       <c r="F32" s="16">
-        <v>1.0919211198850547E-2</v>
+        <v>1.2331820908740496E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.64427395580899849</v>
+        <v>0.72169909400806664</v>
       </c>
       <c r="H32" s="16">
-        <v>21.501657032555009</v>
+        <v>21.188960488161513</v>
       </c>
       <c r="I32" s="16">
-        <v>0.34855819919645442</v>
+        <v>0.33182971404075401</v>
       </c>
       <c r="J32" s="16">
-        <v>0.57006413642300191</v>
+        <v>1.8633137202480963</v>
       </c>
       <c r="K32" s="16">
-        <v>0.27219139747597909</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.24462927800267664</v>
+      </c>
+      <c r="L32" s="16">
+        <v>602846.44434497238</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="16">
         <v>3.3</v>
       </c>
       <c r="C33" s="16">
-        <v>0.78485342122340596</v>
+        <v>0.7877177948580969</v>
       </c>
       <c r="D33" s="16">
-        <v>3.6485095094468676</v>
+        <v>3.7431164006595523</v>
       </c>
       <c r="E33" s="16">
-        <v>0.27408452613615497</v>
+        <v>0.26715706725652344</v>
       </c>
       <c r="F33" s="16">
-        <v>1.0910511029656671E-2</v>
+        <v>1.1959199986815333E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.64379709953548214</v>
+        <v>0.70127574127734837</v>
       </c>
       <c r="H33" s="16">
-        <v>21.514657877659392</v>
+        <v>21.228220514190312</v>
       </c>
       <c r="I33" s="16">
-        <v>0.35097320608728932</v>
+        <v>0.3346072042296333</v>
       </c>
       <c r="J33" s="16">
-        <v>0.57505965611498933</v>
+        <v>1.9001715417143965</v>
       </c>
       <c r="K33" s="16">
-        <v>0.27438199685895309</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.246951461213615</v>
+      </c>
+      <c r="L33" s="16">
+        <v>620785.63224999048</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="16">
         <v>3.5</v>
       </c>
       <c r="C34" s="16">
-        <v>0.78496034992155239</v>
+        <v>0.78753086713794596</v>
       </c>
       <c r="D34" s="16">
-        <v>3.6508283721459738</v>
+        <v>3.7455393303065105</v>
       </c>
       <c r="E34" s="16">
-        <v>0.27391043841707502</v>
+        <v>0.26698424761118889</v>
       </c>
       <c r="F34" s="16">
-        <v>1.090316275126973E-2</v>
+        <v>1.175660043776486E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.64339434039709387</v>
+        <v>0.69017125999389195</v>
       </c>
       <c r="H34" s="16">
-        <v>21.503965007844748</v>
+        <v>21.246913286205405</v>
       </c>
       <c r="I34" s="16">
-        <v>0.35352644778452369</v>
+        <v>0.33747350997892811</v>
       </c>
       <c r="J34" s="16">
-        <v>0.58007808048436504</v>
+        <v>1.9316824713906868</v>
       </c>
       <c r="K34" s="16">
-        <v>0.27667135279187088</v>
+        <v>0.2492991345617265</v>
+      </c>
+      <c r="L34" s="16">
+        <v>637742.3884087808</v>
       </c>
     </row>
   </sheetData>
@@ -3814,34 +3868,34 @@
         <v>0.6</v>
       </c>
       <c r="C3" s="16">
-        <v>8.4211561976013968E-2</v>
+        <v>84.651663100386017</v>
       </c>
       <c r="D3" s="16">
-        <v>7.8630926606964024E-3</v>
+        <v>8.3031937850684709</v>
       </c>
       <c r="E3" s="16">
-        <v>41.852285461263897</v>
+        <v>42.07101122120514</v>
       </c>
       <c r="F3" s="16">
-        <v>15.224184069933031</v>
+        <v>14.631738688404706</v>
       </c>
       <c r="G3" s="16">
-        <v>40.244486029293242</v>
+        <v>38.640747946232182</v>
       </c>
       <c r="H3" s="16">
-        <v>58.846679079728716</v>
+        <v>16.821059556257197</v>
       </c>
       <c r="I3" s="16">
-        <v>57.394641330672847</v>
+        <v>16.450346936931222</v>
       </c>
       <c r="J3" s="16">
-        <v>26</v>
+        <v>85.324619297444372</v>
       </c>
       <c r="K3" s="16">
-        <v>0.1387249120209072</v>
+        <v>41.998410620174532</v>
       </c>
       <c r="L3" s="16">
-        <v>1.2397405267337387</v>
+        <v>375.32647125692898</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -3849,34 +3903,34 @@
         <v>0.65</v>
       </c>
       <c r="C4" s="16">
-        <v>9.5281754998553791E-2</v>
+        <v>95.719638863224972</v>
       </c>
       <c r="D4" s="16">
-        <v>7.8332887957953384E-3</v>
+        <v>8.2711726604665081</v>
       </c>
       <c r="E4" s="16">
-        <v>44.933380647869939</v>
+        <v>45.139879807873122</v>
       </c>
       <c r="F4" s="16">
-        <v>16.426025261648309</v>
+        <v>15.866175674521301</v>
       </c>
       <c r="G4" s="16">
-        <v>43.413869684623059</v>
+        <v>41.898367780725323</v>
       </c>
       <c r="H4" s="16">
-        <v>58.855264463648282</v>
+        <v>16.842730303208608</v>
       </c>
       <c r="I4" s="16">
-        <v>57.403016403607651</v>
+        <v>16.471549518827615</v>
       </c>
       <c r="J4" s="16">
-        <v>26</v>
+        <v>85.252672669359299</v>
       </c>
       <c r="K4" s="16">
-        <v>0.13821926232939638</v>
+        <v>41.890355298669128</v>
       </c>
       <c r="L4" s="16">
-        <v>1.2352216958636071</v>
+        <v>374.36081513036891</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -3884,34 +3938,34 @@
         <v>0.7</v>
       </c>
       <c r="C5" s="16">
-        <v>0.10635197332921997</v>
+        <v>106.78762964531352</v>
       </c>
       <c r="D5" s="16">
-        <v>7.8034867682354944E-3</v>
+        <v>8.239143084329033</v>
       </c>
       <c r="E5" s="16">
-        <v>47.714779598232759</v>
+        <v>47.910236668301629</v>
       </c>
       <c r="F5" s="16">
-        <v>17.510963835453079</v>
+        <v>16.980539852983494</v>
       </c>
       <c r="G5" s="16">
-        <v>46.274968579604028</v>
+        <v>44.839121213116108</v>
       </c>
       <c r="H5" s="16">
-        <v>58.863872564958399</v>
+        <v>16.864557590846722</v>
       </c>
       <c r="I5" s="16">
-        <v>57.41141363788779</v>
+        <v>16.492905818748895</v>
       </c>
       <c r="J5" s="16">
-        <v>26</v>
+        <v>85.181148108243178</v>
       </c>
       <c r="K5" s="16">
-        <v>0.13771354476645351</v>
+        <v>41.782229312474705</v>
       </c>
       <c r="L5" s="16">
-        <v>1.2307022584480201</v>
+        <v>373.39452749590225</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -3919,34 +3973,34 @@
         <v>0.75</v>
       </c>
       <c r="C6" s="16">
-        <v>0.11742221717459934</v>
+        <v>117.85563567355979</v>
       </c>
       <c r="D6" s="16">
-        <v>7.7736866894088322E-3</v>
+        <v>8.2071051883693009</v>
       </c>
       <c r="E6" s="16">
-        <v>50.238175942453665</v>
+        <v>50.423610652608318</v>
       </c>
       <c r="F6" s="16">
-        <v>18.495263231853045</v>
+        <v>17.991535686290757</v>
       </c>
       <c r="G6" s="16">
-        <v>48.870671154301007</v>
+        <v>47.507090521397558</v>
       </c>
       <c r="H6" s="16">
-        <v>58.87250352156601</v>
+        <v>16.886542655961488</v>
       </c>
       <c r="I6" s="16">
-        <v>57.419833168045585</v>
+        <v>16.514417052706353</v>
       </c>
       <c r="J6" s="16">
-        <v>26</v>
+        <v>85.110046267862344</v>
       </c>
       <c r="K6" s="16">
-        <v>0.13720776102482798</v>
+        <v>41.674031689831082</v>
       </c>
       <c r="L6" s="16">
-        <v>1.2261822296145422</v>
+        <v>372.42759966921648</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -3954,34 +4008,34 @@
         <v>0.8</v>
       </c>
       <c r="C7" s="16">
-        <v>0.1284924867425066</v>
+        <v>128.92365717653769</v>
       </c>
       <c r="D7" s="16">
-        <v>7.743888671611427E-3</v>
+        <v>8.175059105642541</v>
       </c>
       <c r="E7" s="16">
-        <v>52.537872183380308</v>
+        <v>52.714168694769128</v>
       </c>
       <c r="F7" s="16">
-        <v>19.392303833181266</v>
+        <v>18.912906397652986</v>
       </c>
       <c r="G7" s="16">
-        <v>51.236262914607892</v>
+        <v>49.938543414634438</v>
       </c>
       <c r="H7" s="16">
-        <v>58.881157472721988</v>
+        <v>16.908686748389439</v>
       </c>
       <c r="I7" s="16">
-        <v>57.428275129924344</v>
+        <v>16.536084449565948</v>
       </c>
       <c r="J7" s="16">
-        <v>26</v>
+        <v>85.039367798199862</v>
       </c>
       <c r="K7" s="16">
-        <v>0.13670191281265232</v>
+        <v>41.565761451301526</v>
       </c>
       <c r="L7" s="16">
-        <v>1.2216616246282117</v>
+        <v>371.46002289739641</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -3989,34 +4043,34 @@
         <v>0.85</v>
       </c>
       <c r="C8" s="16">
-        <v>0.13956278198500702</v>
+        <v>139.99169412513476</v>
       </c>
       <c r="D8" s="16">
-        <v>7.7140927853093831E-3</v>
+        <v>8.1430049254371397</v>
       </c>
       <c r="E8" s="16">
-        <v>54.642345188567177</v>
+        <v>54.810275097122194</v>
       </c>
       <c r="F8" s="16">
-        <v>20.213193673801996</v>
+        <v>19.756061295659428</v>
       </c>
       <c r="G8" s="16">
-        <v>53.401036935557514</v>
+        <v>52.163588511305669</v>
       </c>
       <c r="H8" s="16">
-        <v>58.889834571503116</v>
+        <v>16.93099116797703</v>
       </c>
       <c r="I8" s="16">
-        <v>57.436739672854706</v>
+        <v>16.557909287288794</v>
       </c>
       <c r="J8" s="16">
-        <v>26</v>
+        <v>84.969113326180548</v>
       </c>
       <c r="K8" s="16">
-        <v>0.13619600112778463</v>
+        <v>41.457417470316159</v>
       </c>
       <c r="L8" s="16">
-        <v>1.2171404524065699</v>
+        <v>370.49178711264432</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -4024,34 +4078,34 @@
         <v>0.9</v>
       </c>
       <c r="C9" s="16">
-        <v>0.15063310366538565</v>
+        <v>151.05974730939982</v>
       </c>
       <c r="D9" s="16">
-        <v>7.684299236637172E-3</v>
+        <v>8.1109428806513328</v>
       </c>
       <c r="E9" s="16">
-        <v>56.575443092400867</v>
+        <v>56.735683787276784</v>
       </c>
       <c r="F9" s="16">
-        <v>20.967235070973341</v>
+        <v>20.530554834676661</v>
       </c>
       <c r="G9" s="16">
-        <v>55.389524438458395</v>
+        <v>54.207439562950576</v>
       </c>
       <c r="H9" s="16">
-        <v>58.898534933099697</v>
+        <v>16.953457112175137</v>
       </c>
       <c r="I9" s="16">
-        <v>57.445226909208898</v>
+        <v>16.57989274351246</v>
       </c>
       <c r="J9" s="16">
-        <v>26</v>
+        <v>84.899283535324514</v>
       </c>
       <c r="K9" s="16">
-        <v>0.13569002927177837</v>
+        <v>41.34899905182413</v>
       </c>
       <c r="L9" s="16">
-        <v>1.2126187424545529</v>
+        <v>369.52288610351127</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -4124,64 +4178,64 @@
         <v>0.6</v>
       </c>
       <c r="C16" s="16">
-        <v>3.1885506685029612</v>
+        <v>3188.5506685029641</v>
       </c>
       <c r="D16" s="16">
-        <v>1.0438763107473461</v>
+        <v>1043.876310747346</v>
       </c>
       <c r="E16" s="16">
-        <v>8.6102319558728482</v>
+        <v>8610.2319558728486</v>
       </c>
       <c r="F16" s="16">
-        <v>15.551202889850712</v>
+        <v>15551.202889850705</v>
       </c>
       <c r="G16" s="16">
-        <v>1.1115831277611814</v>
+        <v>1170.9481617362537</v>
       </c>
       <c r="H16" s="16">
-        <v>4.8281167891059305</v>
+        <v>4828.1167891059304</v>
       </c>
       <c r="I16" s="16">
-        <v>9.3526697515099073</v>
+        <v>9352.6697515099131</v>
       </c>
       <c r="J16" s="16">
-        <v>79.195967005262375</v>
+        <v>79195.96700526237</v>
       </c>
       <c r="K16" s="16">
-        <v>212.45529917849188</v>
+        <v>212455.29917849187</v>
       </c>
       <c r="L16" s="16">
-        <v>91.682455189337773</v>
+        <v>91682.455189337765</v>
       </c>
       <c r="M16" s="16">
-        <v>3.1149417500136498</v>
+        <v>479.80835265660414</v>
       </c>
       <c r="N16" s="16">
-        <v>2.4590399198083133</v>
+        <v>309.53584846505231</v>
       </c>
       <c r="O16" s="16">
-        <v>10.362045100531315</v>
+        <v>7714.9057117973007</v>
       </c>
       <c r="P16" s="16">
-        <v>4.8851662034555785</v>
+        <v>2966.3162908925378</v>
       </c>
       <c r="Q16" s="16">
-        <v>9.0361665491794604E-4</v>
+        <v>3.0584860662206266</v>
       </c>
       <c r="R16" s="16">
-        <v>0.92839153384896267</v>
+        <v>639.86455360544733</v>
       </c>
       <c r="S16" s="16">
-        <v>-1.8437574346038494</v>
+        <v>6630.5857324783947</v>
       </c>
       <c r="T16" s="16">
-        <v>531.13824794622963</v>
+        <v>531138.24794622965</v>
       </c>
       <c r="U16" s="16">
-        <v>3.3293594659212076</v>
+        <v>6932.9761335951862</v>
       </c>
       <c r="V16" s="16">
-        <v>450.25604302207307</v>
+        <v>660.83934535734693</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -4189,64 +4243,64 @@
         <v>0.65</v>
       </c>
       <c r="C17" s="16">
-        <v>3.1856026611351265</v>
+        <v>3185.6026611351294</v>
       </c>
       <c r="D17" s="16">
-        <v>1.0478213709567898</v>
+        <v>1047.8213709567915</v>
       </c>
       <c r="E17" s="16">
-        <v>7.5444300571883796</v>
+        <v>7544.4300571883768</v>
       </c>
       <c r="F17" s="16">
-        <v>13.641822894306621</v>
+        <v>13641.822894306615</v>
       </c>
       <c r="G17" s="16">
-        <v>1.1082559641090983</v>
+        <v>1167.377834047664</v>
       </c>
       <c r="H17" s="16">
-        <v>4.7738608169536452</v>
+        <v>4773.8608169536465</v>
       </c>
       <c r="I17" s="16">
-        <v>9.2547297393386696</v>
+        <v>9254.7297393386671</v>
       </c>
       <c r="J17" s="16">
-        <v>83.462458846272</v>
+        <v>83462.458846271998</v>
       </c>
       <c r="K17" s="16">
-        <v>223.90081635317406</v>
+        <v>223900.81635317404</v>
       </c>
       <c r="L17" s="16">
-        <v>96.731337537772518</v>
+        <v>96731.337537772473</v>
       </c>
       <c r="M17" s="16">
-        <v>3.1154534616739804</v>
+        <v>478.6995829181883</v>
       </c>
       <c r="N17" s="16">
-        <v>2.4639194285192669</v>
+        <v>308.52100323915852</v>
       </c>
       <c r="O17" s="16">
-        <v>10.306141862922569</v>
+        <v>7674.0444047855644</v>
       </c>
       <c r="P17" s="16">
-        <v>4.8554018582622822</v>
+        <v>2956.4116676933759</v>
       </c>
       <c r="Q17" s="16">
-        <v>9.009007712257064E-4</v>
+        <v>3.0491695134966466</v>
       </c>
       <c r="R17" s="16">
-        <v>0.92399223502528893</v>
+        <v>637.6738205926822</v>
       </c>
       <c r="S17" s="16">
-        <v>-1.8466625091399864</v>
+        <v>6608.5906938628559</v>
       </c>
       <c r="T17" s="16">
-        <v>559.75204088293515</v>
+        <v>559752.04088293505</v>
       </c>
       <c r="U17" s="16">
-        <v>3.3160809731247927</v>
+        <v>6904.4750775131142</v>
       </c>
       <c r="V17" s="16">
-        <v>467.78636445236623</v>
+        <v>652.81228129907402</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -4254,64 +4308,64 @@
         <v>0.7</v>
       </c>
       <c r="C18" s="16">
-        <v>3.1826444550567756</v>
+        <v>3182.644455056779</v>
       </c>
       <c r="D18" s="16">
-        <v>1.0517772748712815</v>
+        <v>1051.7772748712823</v>
       </c>
       <c r="E18" s="16">
-        <v>6.4756703599588947</v>
+        <v>6475.6703599589018</v>
       </c>
       <c r="F18" s="16">
-        <v>11.722797219174215</v>
+        <v>11722.797219174221</v>
       </c>
       <c r="G18" s="16">
-        <v>1.1049234750247561</v>
+        <v>1163.8002679140027</v>
       </c>
       <c r="H18" s="16">
-        <v>4.71920413147111</v>
+        <v>4719.2041314713424</v>
       </c>
       <c r="I18" s="16">
-        <v>9.1570271064838735</v>
+        <v>9157.0271064838616</v>
       </c>
       <c r="J18" s="16">
-        <v>87.728994646362665</v>
+        <v>87728.994646362858</v>
       </c>
       <c r="K18" s="16">
-        <v>235.34645145481733</v>
+        <v>235346.45145481778</v>
       </c>
       <c r="L18" s="16">
-        <v>101.79288253725483</v>
+        <v>101792.88253725517</v>
       </c>
       <c r="M18" s="16">
-        <v>3.1159523417777462</v>
+        <v>477.59838298531952</v>
       </c>
       <c r="N18" s="16">
-        <v>2.4688128090009003</v>
+        <v>307.51397795733186</v>
       </c>
       <c r="O18" s="16">
-        <v>10.250323800790419</v>
+        <v>7633.226975656662</v>
       </c>
       <c r="P18" s="16">
-        <v>4.8257715495631963</v>
+        <v>2946.4972692960191</v>
       </c>
       <c r="Q18" s="16">
-        <v>8.9818063269454654E-4</v>
+        <v>3.0398341699894589</v>
       </c>
       <c r="R18" s="16">
-        <v>0.91960136568056761</v>
+        <v>635.48096259737144</v>
       </c>
       <c r="S18" s="16">
-        <v>-1.8495797963152276</v>
+        <v>6586.7021178591458</v>
       </c>
       <c r="T18" s="16">
-        <v>588.36612863704318</v>
+        <v>588366.12863704446</v>
       </c>
       <c r="U18" s="16">
-        <v>3.3028065358073517</v>
+        <v>6875.9679388525192</v>
       </c>
       <c r="V18" s="16">
-        <v>485.31695944741341</v>
+        <v>644.86001309898495</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -4319,64 +4373,64 @@
         <v>0.75</v>
       </c>
       <c r="C19" s="16">
-        <v>3.1796759917278905</v>
+        <v>3179.6759917278887</v>
       </c>
       <c r="D19" s="16">
-        <v>1.0557440776822804</v>
+        <v>1055.7440776822809</v>
       </c>
       <c r="E19" s="16">
-        <v>5.4039352110712793</v>
+        <v>5403.9352110712753</v>
       </c>
       <c r="F19" s="16">
-        <v>9.7940194828991078</v>
+        <v>9794.0194828991152</v>
       </c>
       <c r="G19" s="16">
-        <v>1.1015856640998944</v>
+        <v>1160.2154649607455</v>
       </c>
       <c r="H19" s="16">
-        <v>4.6641478209078198</v>
+        <v>4664.1478209078205</v>
       </c>
       <c r="I19" s="16">
-        <v>9.0595629791778052</v>
+        <v>9059.5629791777956</v>
       </c>
       <c r="J19" s="16">
-        <v>91.995574525781194</v>
+        <v>91995.574525781194</v>
       </c>
       <c r="K19" s="16">
-        <v>246.79220480600199</v>
+        <v>246792.20480600206</v>
       </c>
       <c r="L19" s="16">
-        <v>106.86721213527193</v>
+        <v>106867.21213527194</v>
       </c>
       <c r="M19" s="16">
-        <v>3.1164382479094836</v>
+        <v>476.50475067363294</v>
       </c>
       <c r="N19" s="16">
-        <v>2.4737200889304032</v>
+        <v>306.51475643697756</v>
       </c>
       <c r="O19" s="16">
-        <v>10.194591485539634</v>
+        <v>7592.4695660017896</v>
       </c>
       <c r="P19" s="16">
-        <v>4.7962748915086886</v>
+        <v>2936.5730806933279</v>
       </c>
       <c r="Q19" s="16">
-        <v>8.9545624248824843E-4</v>
+        <v>3.0304800390416675</v>
       </c>
       <c r="R19" s="16">
-        <v>0.91521892164972585</v>
+        <v>633.28598215131888</v>
       </c>
       <c r="S19" s="16">
-        <v>-1.8525093332924134</v>
+        <v>6564.9198074580263</v>
       </c>
       <c r="T19" s="16">
-        <v>616.98051201500505</v>
+        <v>616980.51201500499</v>
       </c>
       <c r="U19" s="16">
-        <v>3.2895362100393175</v>
+        <v>6847.4548807334431</v>
       </c>
       <c r="V19" s="16">
-        <v>502.84782866314856</v>
+        <v>636.96663850310608</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -4384,64 +4438,64 @@
         <v>0.8</v>
       </c>
       <c r="C20" s="16">
-        <v>3.1766972121346844</v>
+        <v>3176.6972121346889</v>
       </c>
       <c r="D20" s="16">
-        <v>1.0597218350240001</v>
+        <v>1059.721835024003</v>
       </c>
       <c r="E20" s="16">
-        <v>4.3292067936635572</v>
+        <v>4329.206793663554</v>
       </c>
       <c r="F20" s="16">
-        <v>7.8553814543741751</v>
+        <v>7855.3814543741792</v>
       </c>
       <c r="G20" s="16">
-        <v>1.0982430498994591</v>
+        <v>1156.6234270305308</v>
       </c>
       <c r="H20" s="16">
-        <v>4.6086931025683295</v>
+        <v>4608.6931025683307</v>
       </c>
       <c r="I20" s="16">
-        <v>8.9623384882152894</v>
+        <v>8962.3384882152895</v>
       </c>
       <c r="J20" s="16">
-        <v>96.262198605157224</v>
+        <v>96262.198605157217</v>
       </c>
       <c r="K20" s="16">
-        <v>258.23807673033571</v>
+        <v>258238.07673033568</v>
       </c>
       <c r="L20" s="16">
-        <v>111.95445016030466</v>
+        <v>111954.45016030467</v>
       </c>
       <c r="M20" s="16">
-        <v>3.1169110362992152</v>
+        <v>475.41868378703322</v>
       </c>
       <c r="N20" s="16">
-        <v>2.4786412959014443</v>
+        <v>305.52332255396959</v>
       </c>
       <c r="O20" s="16">
-        <v>10.138945489990787</v>
+        <v>7551.7725219044723</v>
       </c>
       <c r="P20" s="16">
-        <v>4.7669109809012475</v>
+        <v>2926.6390881218472</v>
       </c>
       <c r="Q20" s="16">
-        <v>8.9272760389944321E-4</v>
+        <v>3.0211071245494749</v>
       </c>
       <c r="R20" s="16">
-        <v>0.91084489976972427</v>
+        <v>631.0888811175264</v>
       </c>
       <c r="S20" s="16">
-        <v>-1.8554511571884387</v>
+        <v>6543.2435634506955</v>
       </c>
       <c r="T20" s="16">
-        <v>645.59519182583927</v>
+        <v>645595.19182583911</v>
       </c>
       <c r="U20" s="16">
-        <v>3.2762700522924897</v>
+        <v>6818.9360678689582</v>
       </c>
       <c r="V20" s="16">
-        <v>520.37897275724754</v>
+        <v>629.13205033856616</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -4449,64 +4503,64 @@
         <v>0.85</v>
       </c>
       <c r="C21" s="16">
-        <v>3.1737080391990968</v>
+        <v>3173.7080391990989</v>
       </c>
       <c r="D21" s="16">
-        <v>1.0637106287563038</v>
+        <v>1063.7106287563015</v>
       </c>
       <c r="E21" s="16">
-        <v>3.2514671250847167</v>
+        <v>3251.4671250847132</v>
       </c>
       <c r="F21" s="16">
-        <v>5.9067693275598581</v>
+        <v>5906.7693275598585</v>
       </c>
       <c r="G21" s="16">
-        <v>1.0948945809626529</v>
+        <v>1153.0241497972104</v>
       </c>
       <c r="H21" s="16">
-        <v>4.5528544882684363</v>
+        <v>4552.8544882684373</v>
       </c>
       <c r="I21" s="16">
-        <v>8.8653546420253981</v>
+        <v>8865.3546420253879</v>
       </c>
       <c r="J21" s="16">
-        <v>100.52887198471164</v>
+        <v>100528.87198471166</v>
       </c>
       <c r="K21" s="16">
-        <v>269.68408090994143</v>
+        <v>269684.0809099414</v>
       </c>
       <c r="L21" s="16">
-        <v>117.05472843049664</v>
+        <v>117054.72843049669</v>
       </c>
       <c r="M21" s="16">
-        <v>3.1173705524792377</v>
+        <v>474.34018002231136</v>
       </c>
       <c r="N21" s="16">
-        <v>2.4835764574245141</v>
+        <v>304.53966024366213</v>
       </c>
       <c r="O21" s="16">
-        <v>10.083386332505116</v>
+        <v>7511.1361485193947</v>
       </c>
       <c r="P21" s="16">
-        <v>4.7376804527316398</v>
+        <v>2916.6952608827623</v>
       </c>
       <c r="Q21" s="16">
-        <v>8.8999471541966455E-4</v>
+        <v>3.0117154142819711</v>
       </c>
       <c r="R21" s="16">
-        <v>0.90647929000459382</v>
+        <v>628.8896592311786</v>
       </c>
       <c r="S21" s="16">
-        <v>-1.8584053164823766</v>
+        <v>6521.6731440447938</v>
       </c>
       <c r="T21" s="16">
-        <v>674.21020227485337</v>
+        <v>674210.20227485348</v>
       </c>
       <c r="U21" s="16">
-        <v>3.2630081004215148</v>
+        <v>6790.4116260048368</v>
       </c>
       <c r="V21" s="16">
-        <v>537.91042602080574</v>
+        <v>621.35613686952445</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -4514,64 +4568,64 @@
         <v>0.9</v>
       </c>
       <c r="C22" s="16">
-        <v>3.1707084507537511</v>
+        <v>3170.7084507537484</v>
       </c>
       <c r="D22" s="16">
-        <v>1.0677104599818412</v>
+        <v>1067.7104599818438</v>
       </c>
       <c r="E22" s="16">
-        <v>2.1706980548234425</v>
+        <v>2170.6980548234433</v>
       </c>
       <c r="F22" s="16">
-        <v>3.9480789449175355</v>
+        <v>3948.0789449175445</v>
       </c>
       <c r="G22" s="16">
-        <v>1.091540809577048</v>
+        <v>1149.4176492962922</v>
       </c>
       <c r="H22" s="16">
-        <v>4.4966051596002652</v>
+        <v>4496.6051596002653</v>
       </c>
       <c r="I22" s="16">
-        <v>8.768612854060164</v>
+        <v>8768.6128540601658</v>
       </c>
       <c r="J22" s="16">
-        <v>104.79558407176074</v>
+        <v>104795.58407176075</v>
       </c>
       <c r="K22" s="16">
-        <v>281.130188928324</v>
+        <v>281130.18892832403</v>
       </c>
       <c r="L22" s="16">
-        <v>122.16816161023768</v>
+        <v>122168.16161023772</v>
       </c>
       <c r="M22" s="16">
-        <v>3.117816669947155</v>
+        <v>473.26923738185826</v>
       </c>
       <c r="N22" s="16">
-        <v>2.4885256009247194</v>
+        <v>303.56375350130452</v>
       </c>
       <c r="O22" s="16">
-        <v>10.027914709061532</v>
+        <v>7470.5608830328774</v>
       </c>
       <c r="P22" s="16">
-        <v>4.708582436740417</v>
+        <v>2906.7416213199263</v>
       </c>
       <c r="Q22" s="16">
-        <v>8.8725759121543654E-4</v>
+        <v>3.0023049491744751</v>
       </c>
       <c r="R22" s="16">
-        <v>0.902122100229935</v>
+        <v>626.68832570193877</v>
       </c>
       <c r="S22" s="16">
-        <v>-1.8613718236550516</v>
+        <v>6500.2084323924255</v>
       </c>
       <c r="T22" s="16">
-        <v>702.82547232081004</v>
+        <v>702825.47232081008</v>
       </c>
       <c r="U22" s="16">
-        <v>3.2497504526612584</v>
+        <v>6761.881810422914</v>
       </c>
       <c r="V22" s="16">
-        <v>555.4421167475374</v>
+        <v>613.63879603503915</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -4602,31 +4656,34 @@
         <v>0.6</v>
       </c>
       <c r="C29" s="16">
-        <v>0.84771911035044722</v>
+        <v>0.85242659657944664</v>
       </c>
       <c r="D29" s="16">
-        <v>5.5682400216419365</v>
+        <v>5.8258735665842218</v>
       </c>
       <c r="E29" s="16">
-        <v>0.17958995950485709</v>
+        <v>0.17164807793559991</v>
       </c>
       <c r="F29" s="16">
-        <v>1.0912725075627298E-2</v>
+        <v>2.0341675998230901E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.64391845139513226</v>
+        <v>1.1607192514630356</v>
       </c>
       <c r="H29" s="16">
-        <v>15.228088964955266</v>
+        <v>14.757340342055347</v>
       </c>
       <c r="I29" s="16">
-        <v>0.19083273687724442</v>
+        <v>0.15189110299219086</v>
       </c>
       <c r="J29" s="16">
-        <v>0.24494005524217421</v>
+        <v>0.56640737464839852</v>
       </c>
       <c r="K29" s="16">
-        <v>8.6858968078692311E-2</v>
+        <v>3.9478837258498566E-2</v>
+      </c>
+      <c r="L29" s="16">
+        <v>452756.36900997476</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -4634,31 +4691,34 @@
         <v>0.65</v>
       </c>
       <c r="C30" s="16">
-        <v>0.83570282962165687</v>
+        <v>0.84016080189624043</v>
       </c>
       <c r="D30" s="16">
-        <v>5.0876752976440773</v>
+        <v>5.295294966671853</v>
       </c>
       <c r="E30" s="16">
-        <v>0.19655342400940262</v>
+        <v>0.1888468926271184</v>
       </c>
       <c r="F30" s="16">
-        <v>1.0917832748512973E-2</v>
+        <v>1.978432924799594E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.64419840294599606</v>
+        <v>1.1301710760826573</v>
       </c>
       <c r="H30" s="16">
-        <v>16.429717037834322</v>
+        <v>15.983919810375957</v>
       </c>
       <c r="I30" s="16">
-        <v>0.17425836060946925</v>
+        <v>0.13963406500419584</v>
       </c>
       <c r="J30" s="16">
-        <v>0.23053244101116269</v>
+        <v>0.54963928725632771</v>
       </c>
       <c r="K30" s="16">
-        <v>7.860907429569669E-2</v>
+        <v>3.6836193073165435E-2</v>
+      </c>
+      <c r="L30" s="16">
+        <v>470281.72353126388</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -4666,31 +4726,34 @@
         <v>0.7</v>
       </c>
       <c r="C31" s="16">
-        <v>0.82485536781604962</v>
+        <v>0.82908796609816826</v>
       </c>
       <c r="D31" s="16">
-        <v>4.7105080883442261</v>
+        <v>4.8825771929300403</v>
       </c>
       <c r="E31" s="16">
-        <v>0.21229132425744468</v>
+        <v>0.20480986996949019</v>
       </c>
       <c r="F31" s="16">
-        <v>1.0922427251248833E-2</v>
+        <v>1.9555506784251827E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.6444502276409485</v>
+        <v>1.1176293168448426</v>
       </c>
       <c r="H31" s="16">
-        <v>17.514463218395036</v>
+        <v>17.091203390183175</v>
       </c>
       <c r="I31" s="16">
-        <v>0.16132366298600376</v>
+        <v>0.13020351945141498</v>
       </c>
       <c r="J31" s="16">
-        <v>0.21924753851545725</v>
+        <v>0.53656271821736845</v>
       </c>
       <c r="K31" s="16">
-        <v>7.2149608613530661E-2</v>
+        <v>3.4796268436626483E-2</v>
+      </c>
+      <c r="L31" s="16">
+        <v>487807.27691274043</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -4698,127 +4761,139 @@
         <v>0.75</v>
       </c>
       <c r="C32" s="16">
-        <v>0.81501411936155166</v>
+        <v>0.81904215118447687</v>
       </c>
       <c r="D32" s="16">
-        <v>4.4066100014078859</v>
+        <v>4.5523748804198689</v>
       </c>
       <c r="E32" s="16">
-        <v>0.22693181372540477</v>
+        <v>0.21966556495623429</v>
       </c>
       <c r="F32" s="16">
-        <v>1.0926582439557082E-2</v>
+        <v>1.9780145140133622E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.64467797351212375</v>
+        <v>1.1299417451307239</v>
       </c>
       <c r="H32" s="16">
-        <v>18.498588063844835</v>
+        <v>18.095784881552312</v>
       </c>
       <c r="I32" s="16">
-        <v>0.15102741645822146</v>
+        <v>0.12283585939108733</v>
       </c>
       <c r="J32" s="16">
-        <v>0.21030068848842684</v>
+        <v>0.52650233392927837</v>
       </c>
       <c r="K32" s="16">
-        <v>6.70308002978134E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+        <v>3.3249815789451624E-2</v>
+      </c>
+      <c r="L32" s="16">
+        <v>505333.04579966969</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="16">
         <v>0.8</v>
       </c>
       <c r="C33" s="16">
-        <v>0.8060453041565232</v>
+        <v>0.80988681090702375</v>
       </c>
       <c r="D33" s="16">
-        <v>4.1565216339965589</v>
+        <v>4.2821911866889346</v>
       </c>
       <c r="E33" s="16">
-        <v>0.24058578014388554</v>
+        <v>0.23352530431347171</v>
       </c>
       <c r="F33" s="16">
-        <v>1.0930358656320624E-2</v>
+        <v>2.1278787193004869E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.64488494795293339</v>
+        <v>1.2120823160485967</v>
       </c>
       <c r="H33" s="16">
-        <v>19.39546958434768</v>
+        <v>19.011318909297625</v>
       </c>
       <c r="I33" s="16">
-        <v>0.14280424748686651</v>
+        <v>0.11719887472150799</v>
       </c>
       <c r="J33" s="16">
-        <v>0.2033162158912975</v>
+        <v>0.51947519143337839</v>
       </c>
       <c r="K33" s="16">
-        <v>6.3037490439127375E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+        <v>3.2201562697492067E-2</v>
+      </c>
+      <c r="L33" s="16">
+        <v>522859.03104473709</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="16">
         <v>0.85</v>
       </c>
       <c r="C34" s="16">
-        <v>0.79783786155392133</v>
+        <v>0.80150858782155698</v>
       </c>
       <c r="D34" s="16">
-        <v>3.947114317654743</v>
+        <v>4.0570262251497224</v>
       </c>
       <c r="E34" s="16">
-        <v>0.25334964217458239</v>
+        <v>0.24648595905073192</v>
       </c>
       <c r="F34" s="16">
-        <v>1.0933805686844236E-2</v>
+        <v>1.9465300659532975E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.64507387969593255</v>
+        <v>1.1126851191490024</v>
       </c>
       <c r="H34" s="16">
-        <v>20.216213844607868</v>
+        <v>19.849141217844313</v>
       </c>
       <c r="I34" s="16">
-        <v>0.13658193790215301</v>
+        <v>0.11300286763090467</v>
       </c>
       <c r="J34" s="16">
-        <v>0.19856393313649451</v>
+        <v>0.51728913977209012</v>
       </c>
       <c r="K34" s="16">
-        <v>6.032514312375873E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+        <v>3.1952881074093976E-2</v>
+      </c>
+      <c r="L34" s="16">
+        <v>540385.26712020405</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="16">
         <v>0.9</v>
       </c>
       <c r="C35" s="16">
-        <v>0.79029878486532934</v>
+        <v>0.79381255307974286</v>
       </c>
       <c r="D35" s="16">
-        <v>3.7692083967685592</v>
+        <v>3.8664934263684487</v>
       </c>
       <c r="E35" s="16">
-        <v>0.26530769719639968</v>
+        <v>0.25863227729297766</v>
       </c>
       <c r="F35" s="16">
-        <v>1.0936964974842374E-2</v>
+        <v>1.6483802014683472E-2</v>
       </c>
       <c r="G35" s="16">
-        <v>0.64524704027111057</v>
+        <v>0.94926917842480119</v>
       </c>
       <c r="H35" s="16">
-        <v>20.970121513467056</v>
+        <v>20.618744692025714</v>
       </c>
       <c r="I35" s="16">
-        <v>0.13498053449446543</v>
+        <v>0.11291062697480642</v>
       </c>
       <c r="J35" s="16">
-        <v>0.20078538147008768</v>
+        <v>0.53677735101387736</v>
       </c>
       <c r="K35" s="16">
-        <v>6.1618112153100937E-2</v>
+        <v>3.5298644970179663E-2</v>
+      </c>
+      <c r="L35" s="16">
+        <v>557911.68255245837</v>
       </c>
     </row>
   </sheetData>
@@ -4874,34 +4949,34 @@
         <v>0.6</v>
       </c>
       <c r="C3" s="16">
-        <v>0.13086918068201137</v>
+        <v>131.37511198083556</v>
       </c>
       <c r="D3" s="16">
-        <v>8.8141654444115064E-3</v>
+        <v>9.3200967432357285</v>
       </c>
       <c r="E3" s="16">
-        <v>49.878796554537026</v>
+        <v>50.071624569453377</v>
       </c>
       <c r="F3" s="16">
-        <v>18.373195861739831</v>
+        <v>17.839741822862763</v>
       </c>
       <c r="G3" s="16">
-        <v>48.55024975892259</v>
+        <v>47.106200088887334</v>
       </c>
       <c r="H3" s="16">
-        <v>59.939503250288105</v>
+        <v>16.462268690205413</v>
       </c>
       <c r="I3" s="16">
-        <v>58.915291415536807</v>
+        <v>16.102972586183899</v>
       </c>
       <c r="J3" s="16">
-        <v>70.467849346491846</v>
+        <v>91.9253559989113</v>
       </c>
       <c r="K3" s="16">
-        <v>0.15971887375195662</v>
+        <v>46.149026428859131</v>
       </c>
       <c r="L3" s="16">
-        <v>1.4273569021599251</v>
+        <v>412.41920791083669</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -4909,34 +4984,34 @@
         <v>0.65</v>
       </c>
       <c r="C4" s="16">
-        <v>0.13701888853317393</v>
+        <v>137.50731004203092</v>
       </c>
       <c r="D4" s="16">
-        <v>8.5397213545798153E-3</v>
+        <v>9.0281428634368091</v>
       </c>
       <c r="E4" s="16">
-        <v>51.771991448655704</v>
+        <v>51.956539392742719</v>
       </c>
       <c r="F4" s="16">
-        <v>19.112016134944927</v>
+        <v>18.600572278859662</v>
       </c>
       <c r="G4" s="16">
-        <v>50.498588452935046</v>
+        <v>49.114119918070912</v>
       </c>
       <c r="H4" s="16">
-        <v>60.017837430327823</v>
+        <v>16.618043449597593</v>
       </c>
       <c r="I4" s="16">
-        <v>58.995465876775796</v>
+        <v>16.255179781923417</v>
       </c>
       <c r="J4" s="16">
-        <v>70.733893942291786</v>
+        <v>90.989305976502749</v>
       </c>
       <c r="K4" s="16">
-        <v>0.15495749590016775</v>
+        <v>45.125682851446044</v>
       </c>
       <c r="L4" s="16">
-        <v>1.3848059788977394</v>
+        <v>403.27391102644947</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -4944,34 +5019,34 @@
         <v>0.7</v>
       </c>
       <c r="C5" s="16">
-        <v>0.14230508065956135</v>
+        <v>142.77772072465743</v>
       </c>
       <c r="D5" s="16">
-        <v>8.3060695450992046E-3</v>
+        <v>8.7787096101952358</v>
       </c>
       <c r="E5" s="16">
-        <v>53.3638629940382</v>
+        <v>53.541101217454965</v>
       </c>
       <c r="F5" s="16">
-        <v>19.733270889997033</v>
+        <v>19.240416855501568</v>
       </c>
       <c r="G5" s="16">
-        <v>52.13688786586652</v>
+        <v>50.802741615166326</v>
       </c>
       <c r="H5" s="16">
-        <v>60.08613937444035</v>
+        <v>16.7600449364352</v>
       </c>
       <c r="I5" s="16">
-        <v>59.065367664064738</v>
+        <v>16.393981062161274</v>
       </c>
       <c r="J5" s="16">
-        <v>70.964246217707341</v>
+        <v>90.230933490109237</v>
       </c>
       <c r="K5" s="16">
-        <v>0.15089733089748819</v>
+        <v>44.253416223389642</v>
       </c>
       <c r="L5" s="16">
-        <v>1.3485215724005901</v>
+        <v>395.4787409076468</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -4979,34 +5054,34 @@
         <v>0.75</v>
       </c>
       <c r="C6" s="16">
-        <v>0.14689827318466656</v>
+        <v>147.35667937941781</v>
       </c>
       <c r="D6" s="16">
-        <v>8.1049138972325522E-3</v>
+        <v>8.563320091983833</v>
       </c>
       <c r="E6" s="16">
-        <v>54.719894700628537</v>
+        <v>54.890651906707951</v>
       </c>
       <c r="F6" s="16">
-        <v>20.26250383624782</v>
+        <v>19.785543457011226</v>
       </c>
       <c r="G6" s="16">
-        <v>53.532512389537942</v>
+        <v>52.241389953373904</v>
       </c>
       <c r="H6" s="16">
-        <v>60.146201421712384</v>
+        <v>16.889621914325545</v>
       </c>
       <c r="I6" s="16">
-        <v>59.126833228739414</v>
+        <v>16.520675581272112</v>
       </c>
       <c r="J6" s="16">
-        <v>71.165602215361275</v>
+        <v>89.606197121539367</v>
       </c>
       <c r="K6" s="16">
-        <v>0.1473969837068114</v>
+        <v>43.501095785145466</v>
       </c>
       <c r="L6" s="16">
-        <v>1.3172400800809798</v>
+        <v>388.75549183295408</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -5014,34 +5089,34 @@
         <v>0.8</v>
       </c>
       <c r="C7" s="16">
-        <v>0.15092661980778518</v>
+        <v>151.37216187198626</v>
       </c>
       <c r="D7" s="16">
-        <v>7.9300370676916587E-3</v>
+        <v>8.375579131892728</v>
       </c>
       <c r="E7" s="16">
-        <v>55.888023789679387</v>
+        <v>56.053007710442238</v>
       </c>
       <c r="F7" s="16">
-        <v>20.718416133758716</v>
+        <v>20.25518900750864</v>
       </c>
       <c r="G7" s="16">
-        <v>54.734780717393491</v>
+        <v>53.480833928986208</v>
       </c>
       <c r="H7" s="16">
-        <v>60.199415246228241</v>
+        <v>17.0080724028589</v>
       </c>
       <c r="I7" s="16">
-        <v>59.18128830008709</v>
+        <v>16.636519309543448</v>
       </c>
       <c r="J7" s="16">
-        <v>71.343096511252043</v>
+        <v>89.084111961747624</v>
       </c>
       <c r="K7" s="16">
-        <v>0.14435020648564711</v>
+        <v>42.845613696759763</v>
       </c>
       <c r="L7" s="16">
-        <v>1.2900119986788643</v>
+        <v>382.89765636791992</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -5049,34 +5124,34 @@
         <v>0.85</v>
       </c>
       <c r="C8" s="16">
-        <v>0.15448837379671118</v>
+        <v>154.92225597135939</v>
       </c>
       <c r="D8" s="16">
-        <v>7.7766933290369447E-3</v>
+        <v>8.2105755036851527</v>
       </c>
       <c r="E8" s="16">
-        <v>56.904129154565311</v>
+        <v>57.063944982107998</v>
       </c>
       <c r="F8" s="16">
-        <v>21.115005816784862</v>
+        <v>20.663755903728628</v>
       </c>
       <c r="G8" s="16">
-        <v>55.780608217314288</v>
+        <v>54.559083511223442</v>
       </c>
       <c r="H8" s="16">
-        <v>60.246877622003723</v>
+        <v>17.116592621779663</v>
       </c>
       <c r="I8" s="16">
-        <v>59.229856314830073</v>
+        <v>16.742672845265915</v>
       </c>
       <c r="J8" s="16">
-        <v>71.500726935586954</v>
+        <v>88.642335977364553</v>
       </c>
       <c r="K8" s="16">
-        <v>0.14167570990752862</v>
+        <v>42.269442031817007</v>
       </c>
       <c r="L8" s="16">
-        <v>1.2661108712735394</v>
+        <v>377.74859299509524</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -5084,34 +5159,34 @@
         <v>0.9</v>
       </c>
       <c r="C9" s="16">
-        <v>0.15766017207045593</v>
+        <v>158.08345354249448</v>
       </c>
       <c r="D9" s="16">
-        <v>7.6412011923432457E-3</v>
+        <v>8.064482664381817</v>
       </c>
       <c r="E9" s="16">
-        <v>57.795583221044957</v>
+        <v>57.9507511320136</v>
       </c>
       <c r="F9" s="16">
-        <v>21.462952743531002</v>
+        <v>21.022234635974197</v>
       </c>
       <c r="G9" s="16">
-        <v>56.698159463778808</v>
+        <v>55.505144149590457</v>
       </c>
       <c r="H9" s="16">
-        <v>60.289464382137304</v>
+        <v>17.216255892025185</v>
       </c>
       <c r="I9" s="16">
-        <v>59.273434254686372</v>
+        <v>16.840179365092585</v>
       </c>
       <c r="J9" s="16">
-        <v>71.641649768227524</v>
+        <v>88.264404798389421</v>
       </c>
       <c r="K9" s="16">
-        <v>0.13931030334092001</v>
+        <v>41.759049116660748</v>
       </c>
       <c r="L9" s="16">
-        <v>1.2449719832388881</v>
+        <v>373.18737344008377</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -5184,64 +5259,64 @@
         <v>0.6</v>
       </c>
       <c r="C16" s="16">
-        <v>17.223530390651401</v>
+        <v>17223.530390651405</v>
       </c>
       <c r="D16" s="16">
-        <v>5.1037799140514002</v>
+        <v>5103.7799140514026</v>
       </c>
       <c r="E16" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F16" s="16">
-        <v>2.8073738467151998</v>
+        <v>2807.373846715212</v>
       </c>
       <c r="G16" s="16">
-        <v>1.2108751990759339</v>
+        <v>1276.8209247155376</v>
       </c>
       <c r="H16" s="16">
-        <v>1.1047199639898608</v>
+        <v>1104.7199639895116</v>
       </c>
       <c r="I16" s="16">
-        <v>9.283773488135834</v>
+        <v>9283.7734881358447</v>
       </c>
       <c r="J16" s="16">
-        <v>103.26946782608539</v>
+        <v>103269.46782608512</v>
       </c>
       <c r="K16" s="16">
-        <v>277.03614858994956</v>
+        <v>277036.14858994889</v>
       </c>
       <c r="L16" s="16">
-        <v>120.25045822234905</v>
+        <v>120250.45822234853</v>
       </c>
       <c r="M16" s="16">
-        <v>5.0117925165671998E-2</v>
+        <v>5.452183432965394</v>
       </c>
       <c r="N16" s="16">
-        <v>2.291782343488102E-2</v>
+        <v>3.5159669301187799</v>
       </c>
       <c r="O16" s="16">
-        <v>12.258929861073378</v>
+        <v>9069.4723274985863</v>
       </c>
       <c r="P16" s="16">
-        <v>5.9683119542030285</v>
+        <v>3270.9717653959974</v>
       </c>
       <c r="Q16" s="16">
-        <v>9.8477814386777594E-4</v>
+        <v>3.3347810802459064</v>
       </c>
       <c r="R16" s="16">
-        <v>1.0776192924360903</v>
+        <v>707.45619070343423</v>
       </c>
       <c r="S16" s="16">
-        <v>3.5044989063272931</v>
+        <v>8247.2828155752686</v>
       </c>
       <c r="T16" s="16">
-        <v>692.59037147487402</v>
+        <v>692590.37147487211</v>
       </c>
       <c r="U16" s="16">
-        <v>3.5995421709049547</v>
+        <v>7815.0223404901808</v>
       </c>
       <c r="V16" s="16">
-        <v>565.3155068627882</v>
+        <v>1006.0994414795861</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -5249,64 +5324,64 @@
         <v>0.65</v>
       </c>
       <c r="C17" s="16">
-        <v>13.889071706783179</v>
+        <v>13889.07170678319</v>
       </c>
       <c r="D17" s="16">
-        <v>4.246121653805341</v>
+        <v>4246.1216538053413</v>
       </c>
       <c r="E17" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F17" s="16">
-        <v>2.8073738467151998</v>
+        <v>2807.373846715212</v>
       </c>
       <c r="G17" s="16">
-        <v>1.1826470103258144</v>
+        <v>1246.9321510205978</v>
       </c>
       <c r="H17" s="16">
-        <v>1.7916358617457444</v>
+        <v>1791.6358617457445</v>
       </c>
       <c r="I17" s="16">
-        <v>9.1736007419972747</v>
+        <v>9173.6007419972721</v>
       </c>
       <c r="J17" s="16">
-        <v>104.16842351101462</v>
+        <v>104168.42351101463</v>
       </c>
       <c r="K17" s="16">
-        <v>279.44773476298229</v>
+        <v>279447.73476298235</v>
       </c>
       <c r="L17" s="16">
-        <v>121.34712487858563</v>
+        <v>121347.12487858563</v>
       </c>
       <c r="M17" s="16">
-        <v>5.077422903846187E-2</v>
+        <v>5.3076931478068436</v>
       </c>
       <c r="N17" s="16">
-        <v>2.3373621735010557E-2</v>
+        <v>3.386088052052231</v>
       </c>
       <c r="O17" s="16">
-        <v>11.70689884570481</v>
+        <v>8681.1360766426478</v>
       </c>
       <c r="P17" s="16">
-        <v>5.6409449889946401</v>
+        <v>3183.8465415175647</v>
       </c>
       <c r="Q17" s="16">
-        <v>9.6169692888734557E-4</v>
+        <v>3.2567627815380549</v>
       </c>
       <c r="R17" s="16">
-        <v>1.0337214813555018</v>
+        <v>688.15375575126609</v>
       </c>
       <c r="S17" s="16">
-        <v>3.5424556315454323</v>
+        <v>7989.1196836424506</v>
       </c>
       <c r="T17" s="16">
-        <v>698.61933690745582</v>
+        <v>698619.33690745581</v>
       </c>
       <c r="U17" s="16">
-        <v>3.48060805566681</v>
+        <v>7556.3627262476602</v>
       </c>
       <c r="V17" s="16">
-        <v>565.07592923502034</v>
+        <v>894.35041221219433</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -5314,64 +5389,64 @@
         <v>0.7</v>
       </c>
       <c r="C18" s="16">
-        <v>11.038113043195452</v>
+        <v>11038.113043195457</v>
       </c>
       <c r="D18" s="16">
-        <v>3.4658458866495603</v>
+        <v>3465.8458866495639</v>
       </c>
       <c r="E18" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F18" s="16">
-        <v>2.8073738467151998</v>
+        <v>2807.373846715212</v>
       </c>
       <c r="G18" s="16">
-        <v>1.1582224463140447</v>
+        <v>1220.9458553359398</v>
       </c>
       <c r="H18" s="16">
-        <v>2.4307471421233493</v>
+        <v>2430.7471421233495</v>
       </c>
       <c r="I18" s="16">
-        <v>9.0667993777505469</v>
+        <v>9066.7993777505453</v>
       </c>
       <c r="J18" s="16">
-        <v>104.95996261811557</v>
+        <v>104959.96261811555</v>
       </c>
       <c r="K18" s="16">
-        <v>281.5711595302995</v>
+        <v>281571.15953029942</v>
       </c>
       <c r="L18" s="16">
-        <v>122.31369926104054</v>
+        <v>122313.69926104051</v>
       </c>
       <c r="M18" s="16">
-        <v>5.134475467344897E-2</v>
+        <v>5.1915365490738949</v>
       </c>
       <c r="N18" s="16">
-        <v>2.377184156378501E-2</v>
+        <v>3.2824943089030691</v>
       </c>
       <c r="O18" s="16">
-        <v>11.242094633094244</v>
+        <v>8350.2774620509263</v>
       </c>
       <c r="P18" s="16">
-        <v>5.3734938759397997</v>
+        <v>3109.0032010434434</v>
       </c>
       <c r="Q18" s="16">
-        <v>9.4173270359819037E-4</v>
+        <v>3.1889412829698629</v>
       </c>
       <c r="R18" s="16">
-        <v>0.99701597907764994</v>
+        <v>671.56089370621544</v>
       </c>
       <c r="S18" s="16">
-        <v>3.5747344392650797</v>
+        <v>7779.7332679045712</v>
       </c>
       <c r="T18" s="16">
-        <v>703.92789882574857</v>
+        <v>703927.89882574859</v>
       </c>
       <c r="U18" s="16">
-        <v>3.379562304940662</v>
+        <v>7335.3153665981044</v>
       </c>
       <c r="V18" s="16">
-        <v>564.99733942355761</v>
+        <v>807.96407777095044</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -5379,64 +5454,64 @@
         <v>0.75</v>
       </c>
       <c r="C19" s="16">
-        <v>8.5735098078966985</v>
+        <v>8573.5098078967039</v>
       </c>
       <c r="D19" s="16">
-        <v>2.7546230259247095</v>
+        <v>2754.6230259247086</v>
       </c>
       <c r="E19" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F19" s="16">
-        <v>2.8073738467151998</v>
+        <v>2807.373846715212</v>
       </c>
       <c r="G19" s="16">
-        <v>1.1369071821082999</v>
+        <v>1198.1746826835815</v>
       </c>
       <c r="H19" s="16">
-        <v>3.0237047411040985</v>
+        <v>3023.7047411040985</v>
       </c>
       <c r="I19" s="16">
-        <v>8.9651619450555877</v>
+        <v>8965.1619450556045</v>
       </c>
       <c r="J19" s="16">
-        <v>105.66276220008064</v>
+        <v>105662.76220008062</v>
       </c>
       <c r="K19" s="16">
-        <v>283.45652694350355</v>
+        <v>283456.52694350353</v>
       </c>
       <c r="L19" s="16">
-        <v>123.1726580633815</v>
+        <v>123172.65806338149</v>
       </c>
       <c r="M19" s="16">
-        <v>5.1845176613273189E-2</v>
+        <v>5.096464270286817</v>
       </c>
       <c r="N19" s="16">
-        <v>2.4122638880794574E-2</v>
+        <v>3.1982574572705684</v>
       </c>
       <c r="O19" s="16">
-        <v>10.845814830466487</v>
+        <v>8065.4790637428705</v>
       </c>
       <c r="P19" s="16">
-        <v>5.1512288603062899</v>
+        <v>3044.0567601831735</v>
       </c>
       <c r="Q19" s="16">
-        <v>9.2431500080570217E-4</v>
+        <v>3.1295180860384573</v>
       </c>
       <c r="R19" s="16">
-        <v>0.96589147864161762</v>
+        <v>657.15647747574963</v>
       </c>
       <c r="S19" s="16">
-        <v>3.6025669776936748</v>
+        <v>7607.0502213785421</v>
       </c>
       <c r="T19" s="16">
-        <v>708.64131735875878</v>
+        <v>708641.31735875877</v>
       </c>
       <c r="U19" s="16">
-        <v>3.2927275709515644</v>
+        <v>7144.4132278211982</v>
       </c>
       <c r="V19" s="16">
-        <v>565.03080631442015</v>
+        <v>739.74586195580275</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -5444,64 +5519,64 @@
         <v>0.8</v>
       </c>
       <c r="C20" s="16">
-        <v>6.4222094453439347</v>
+        <v>6422.209445343934</v>
       </c>
       <c r="D20" s="16">
-        <v>2.104979688397314</v>
+        <v>2104.9796883973145</v>
       </c>
       <c r="E20" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F20" s="16">
-        <v>2.8073738467151998</v>
+        <v>2807.373846715212</v>
       </c>
       <c r="G20" s="16">
-        <v>1.1181613002894637</v>
+        <v>1178.0770331275444</v>
       </c>
       <c r="H20" s="16">
-        <v>3.5733140356715887</v>
+        <v>3573.3140356715885</v>
       </c>
       <c r="I20" s="16">
-        <v>8.8694633253153885</v>
+        <v>8869.4633253153861</v>
       </c>
       <c r="J20" s="16">
-        <v>106.29127448128449</v>
+        <v>106291.27448128449</v>
       </c>
       <c r="K20" s="16">
-        <v>285.14260730579838</v>
+        <v>285142.60730579839</v>
       </c>
       <c r="L20" s="16">
-        <v>123.94142024869507</v>
+        <v>123941.42024869514</v>
       </c>
       <c r="M20" s="16">
-        <v>5.2287609979356685E-2</v>
+        <v>5.0174435715414933</v>
       </c>
       <c r="N20" s="16">
-        <v>2.4433948167301087E-2</v>
+        <v>3.1286281242784804</v>
       </c>
       <c r="O20" s="16">
-        <v>10.504258527002829</v>
+        <v>7818.055233211242</v>
       </c>
       <c r="P20" s="16">
-        <v>4.9638129009404244</v>
+        <v>2987.1979399961638</v>
       </c>
       <c r="Q20" s="16">
-        <v>9.0900061105456586E-4</v>
+        <v>3.0770782045324996</v>
       </c>
       <c r="R20" s="16">
-        <v>0.93918089232948121</v>
+        <v>644.5429633076667</v>
       </c>
       <c r="S20" s="16">
-        <v>3.6268565995228084</v>
+        <v>7462.5927103847625</v>
       </c>
       <c r="T20" s="16">
-        <v>712.85651826449589</v>
+        <v>712856.518264496</v>
       </c>
       <c r="U20" s="16">
-        <v>3.2173570937397304</v>
+        <v>6978.0111597711339</v>
       </c>
       <c r="V20" s="16">
-        <v>565.14235695989919</v>
+        <v>684.87812040966435</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -5509,64 +5584,64 @@
         <v>0.85</v>
       </c>
       <c r="C21" s="16">
-        <v>4.528303001585213</v>
+        <v>4528.3030015852082</v>
       </c>
       <c r="D21" s="16">
-        <v>1.5102579346330967</v>
+        <v>1510.2579346330949</v>
       </c>
       <c r="E21" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F21" s="16">
-        <v>2.8073738467151998</v>
+        <v>2807.373846715212</v>
       </c>
       <c r="G21" s="16">
-        <v>1.1015597781977049</v>
+        <v>1160.2238689842616</v>
       </c>
       <c r="H21" s="16">
-        <v>4.0828254225992717</v>
+        <v>4082.8254225992714</v>
       </c>
       <c r="I21" s="16">
-        <v>8.7799064915337652</v>
+        <v>8779.9064915337567</v>
       </c>
       <c r="J21" s="16">
-        <v>106.85689298365322</v>
+        <v>106856.89298365323</v>
       </c>
       <c r="K21" s="16">
-        <v>286.65996548306083</v>
+        <v>286659.96548306081</v>
       </c>
       <c r="L21" s="16">
-        <v>124.63373733801447</v>
+        <v>124633.73733801451</v>
       </c>
       <c r="M21" s="16">
-        <v>5.2681552572014054E-2</v>
+        <v>4.9508860722283314</v>
       </c>
       <c r="N21" s="16">
-        <v>2.4712046856216502E-2</v>
+        <v>3.0702561566529161</v>
       </c>
       <c r="O21" s="16">
-        <v>10.207040222168093</v>
+        <v>7601.3579951351512</v>
       </c>
       <c r="P21" s="16">
-        <v>4.803795582538716</v>
+        <v>2937.0284324878266</v>
       </c>
       <c r="Q21" s="16">
-        <v>8.9544089482254826E-4</v>
+        <v>3.0304971860907428</v>
       </c>
       <c r="R21" s="16">
-        <v>0.91601886380869246</v>
+        <v>633.41219883005499</v>
       </c>
       <c r="S21" s="16">
-        <v>3.648278080330789</v>
+        <v>7340.2510260677755</v>
       </c>
       <c r="T21" s="16">
-        <v>716.64991370765188</v>
+        <v>716649.91370765201</v>
       </c>
       <c r="U21" s="16">
-        <v>3.1513604057888163</v>
+        <v>6831.7671188620152</v>
       </c>
       <c r="V21" s="16">
-        <v>565.30806118504643</v>
+        <v>639.99376475609347</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -5574,64 +5649,64 @@
         <v>0.9</v>
       </c>
       <c r="C22" s="16">
-        <v>2.8483263976414599</v>
+        <v>2848.3263976414578</v>
       </c>
       <c r="D22" s="16">
-        <v>0.96455767849983387</v>
+        <v>964.55767849983272</v>
       </c>
       <c r="E22" s="16">
-        <v>1.5424567100955173</v>
+        <v>1542.4567100955248</v>
       </c>
       <c r="F22" s="16">
-        <v>2.8073738467151998</v>
+        <v>2807.373846715212</v>
       </c>
       <c r="G22" s="16">
-        <v>1.0867646432466844</v>
+        <v>1144.2692953722533</v>
       </c>
       <c r="H22" s="16">
-        <v>4.5555618020140098</v>
+        <v>4555.56180201401</v>
       </c>
       <c r="I22" s="16">
-        <v>8.6963788936835122</v>
+        <v>8696.3788936835081</v>
       </c>
       <c r="J22" s="16">
-        <v>107.36874274104464</v>
+        <v>107368.74274104465</v>
       </c>
       <c r="K22" s="16">
-        <v>288.03308077482569</v>
+        <v>288033.08077482571</v>
       </c>
       <c r="L22" s="16">
-        <v>125.26063692308392</v>
+        <v>125260.63692308396</v>
       </c>
       <c r="M22" s="16">
-        <v>5.3034547836876195E-2</v>
+        <v>4.894172640608538</v>
       </c>
       <c r="N22" s="16">
-        <v>2.4961960101606045E-2</v>
+        <v>3.020718766159987</v>
       </c>
       <c r="O22" s="16">
-        <v>9.9462077370741646</v>
+        <v>7410.8411867897976</v>
       </c>
       <c r="P22" s="16">
-        <v>4.6656811406944776</v>
+        <v>2892.4513865002973</v>
       </c>
       <c r="Q22" s="16">
-        <v>8.8335841987004747E-4</v>
+        <v>2.9888726843513251</v>
       </c>
       <c r="R22" s="16">
-        <v>0.89575064737944088</v>
+        <v>623.52189457161796</v>
       </c>
       <c r="S22" s="16">
-        <v>3.6673441327121901</v>
+        <v>7235.5211540738865</v>
       </c>
       <c r="T22" s="16">
-        <v>720.08270193706414</v>
+        <v>720082.70193706418</v>
       </c>
       <c r="U22" s="16">
-        <v>3.0931200591283474</v>
+        <v>6702.294145079939</v>
       </c>
       <c r="V22" s="16">
-        <v>565.51086399419739</v>
+        <v>602.06487777685288</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -5662,31 +5737,34 @@
         <v>0.6</v>
       </c>
       <c r="C29" s="16">
-        <v>0.8162335633672565</v>
+        <v>0.82013995810863238</v>
       </c>
       <c r="D29" s="16">
-        <v>4.4425236061787903</v>
+        <v>4.5972636053374432</v>
       </c>
       <c r="E29" s="16">
-        <v>0.22509728448244395</v>
+        <v>0.21752070053998984</v>
       </c>
       <c r="F29" s="16">
-        <v>1.0904188357996744E-2</v>
+        <v>1.3347972360860334E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.6434505539018015</v>
+        <v>0.77739435509875499</v>
       </c>
       <c r="H29" s="16">
-        <v>18.376643663274361</v>
+        <v>17.986004189136761</v>
       </c>
       <c r="I29" s="16">
-        <v>0.41341597674628905</v>
+        <v>0.39256551077722535</v>
       </c>
       <c r="J29" s="16">
-        <v>0.63345210941471208</v>
+        <v>2.0829472070598287</v>
       </c>
       <c r="K29" s="16">
-        <v>0.31969789321370906</v>
+        <v>0.28180602931711179</v>
+      </c>
+      <c r="L29" s="16">
+        <v>568021.03824784374</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -5694,31 +5772,34 @@
         <v>0.65</v>
       </c>
       <c r="C30" s="16">
-        <v>0.80884667712808289</v>
+        <v>0.81270445170592143</v>
       </c>
       <c r="D30" s="16">
-        <v>4.2321368474002377</v>
+        <v>4.3692443410980131</v>
       </c>
       <c r="E30" s="16">
-        <v>0.23628725536469614</v>
+        <v>0.22887252850425274</v>
       </c>
       <c r="F30" s="16">
-        <v>1.0918648791163528E-2</v>
+        <v>1.3291196355712501E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.64424313024367297</v>
+        <v>0.77428246225660224</v>
       </c>
       <c r="H30" s="16">
-        <v>19.115332287191698</v>
+        <v>18.729554829407846</v>
       </c>
       <c r="I30" s="16">
-        <v>0.39444410274120173</v>
+        <v>0.37412604036228386</v>
       </c>
       <c r="J30" s="16">
-        <v>0.60791796695278866</v>
+        <v>1.9926727538831934</v>
       </c>
       <c r="K30" s="16">
-        <v>0.30513582323874583</v>
+        <v>0.27029641704932589</v>
+      </c>
+      <c r="L30" s="16">
+        <v>567771.04515252833</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -5726,31 +5807,34 @@
         <v>0.7</v>
       </c>
       <c r="C31" s="16">
-        <v>0.80263524199858138</v>
+        <v>0.80643863864712118</v>
       </c>
       <c r="D31" s="16">
-        <v>4.067421191716595</v>
+        <v>4.191378205075269</v>
       </c>
       <c r="E31" s="16">
-        <v>0.24585602347662569</v>
+        <v>0.23858500738232519</v>
       </c>
       <c r="F31" s="16">
-        <v>1.0931188260214096E-2</v>
+        <v>1.3259884166837736E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.64493041854233468</v>
+        <v>0.77256624118437633</v>
       </c>
       <c r="H31" s="16">
-        <v>19.736475800141861</v>
+        <v>19.356136135287894</v>
       </c>
       <c r="I31" s="16">
-        <v>0.37952324743581139</v>
+        <v>0.35971940225036453</v>
       </c>
       <c r="J31" s="16">
-        <v>0.58777374945280458</v>
+        <v>1.9200491681929024</v>
       </c>
       <c r="K31" s="16">
-        <v>0.29365788683812383</v>
+        <v>0.26115196917136718</v>
+      </c>
+      <c r="L31" s="16">
+        <v>567674.65643476509</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -5758,127 +5842,139 @@
         <v>0.75</v>
       </c>
       <c r="C32" s="16">
-        <v>0.79734386419973036</v>
+        <v>0.80109149445693062</v>
       </c>
       <c r="D32" s="16">
-        <v>3.9350707624462138</v>
+        <v>4.0488728358535688</v>
       </c>
       <c r="E32" s="16">
-        <v>0.25412503621112925</v>
+        <v>0.24698231842324175</v>
       </c>
       <c r="F32" s="16">
-        <v>1.0944766551039004E-2</v>
+        <v>1.3246821447386169E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.64567464466244784</v>
+        <v>0.77185027353123592</v>
       </c>
       <c r="H32" s="16">
-        <v>20.265613580026965</v>
+        <v>19.890850554306937</v>
       </c>
       <c r="I32" s="16">
-        <v>0.36787790493733269</v>
+        <v>0.34818280949217234</v>
       </c>
       <c r="J32" s="16">
-        <v>0.57211390257334793</v>
+        <v>1.8604600227922072</v>
       </c>
       <c r="K32" s="16">
-        <v>0.28475653286847541</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.25373656750511175</v>
+      </c>
+      <c r="L32" s="16">
+        <v>567686.53195685614</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="16">
         <v>0.8</v>
       </c>
       <c r="C33" s="16">
-        <v>0.79278556410732104</v>
+        <v>0.79647837219656359</v>
       </c>
       <c r="D33" s="16">
-        <v>3.82647765634725</v>
+        <v>3.9322189089487511</v>
       </c>
       <c r="E33" s="16">
-        <v>0.2613369500122989</v>
+        <v>0.25430934115195086</v>
       </c>
       <c r="F33" s="16">
-        <v>1.0953771658947358E-2</v>
+        <v>1.3247346740240681E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.64616821462690466</v>
+        <v>0.77187906483259183</v>
       </c>
       <c r="H33" s="16">
-        <v>20.721443589267896</v>
+        <v>20.35216278034363</v>
       </c>
       <c r="I33" s="16">
-        <v>0.35781457444009379</v>
+        <v>0.33879918838150858</v>
       </c>
       <c r="J33" s="16">
-        <v>0.55836368955805793</v>
+        <v>1.8109826194536935</v>
       </c>
       <c r="K33" s="16">
-        <v>0.27692740932168425</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.24765770129014694</v>
+      </c>
+      <c r="L33" s="16">
+        <v>567774.79927701573</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="16">
         <v>0.85</v>
       </c>
       <c r="C34" s="16">
-        <v>0.78882038547995503</v>
+        <v>0.79246058728103996</v>
       </c>
       <c r="D34" s="16">
-        <v>3.7358284071743015</v>
+        <v>3.8350268507481067</v>
       </c>
       <c r="E34" s="16">
-        <v>0.26767824723415978</v>
+        <v>0.26075436728817891</v>
       </c>
       <c r="F34" s="16">
-        <v>1.0963939440872789E-2</v>
+        <v>1.3258314031391686E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.64672551075423756</v>
+        <v>0.77248018206057834</v>
       </c>
       <c r="H34" s="16">
-        <v>21.117961452004497</v>
+        <v>20.753941271896004</v>
       </c>
       <c r="I34" s="16">
-        <v>0.3499049978620189</v>
+        <v>0.33121770977860687</v>
       </c>
       <c r="J34" s="16">
-        <v>0.54760892323226329</v>
+        <v>1.7702954044804526</v>
       </c>
       <c r="K34" s="16">
-        <v>0.27082626625832856</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.24276579170183107</v>
+      </c>
+      <c r="L34" s="16">
+        <v>567916.81149167253</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="16">
         <v>0.9</v>
       </c>
       <c r="C35" s="16">
-        <v>0.7853415482318078</v>
+        <v>0.78893287821783398</v>
       </c>
       <c r="D35" s="16">
-        <v>3.6590564104396681</v>
+        <v>3.752849741614892</v>
       </c>
       <c r="E35" s="16">
-        <v>0.27329450214183526</v>
+        <v>0.26646417225585195</v>
       </c>
       <c r="F35" s="16">
-        <v>1.0972466052867792E-2</v>
+        <v>1.3277549695321836E-2</v>
       </c>
       <c r="G35" s="16">
-        <v>0.6471928543576837</v>
+        <v>0.77353448880058984</v>
       </c>
       <c r="H35" s="16">
-        <v>21.465845176819208</v>
+        <v>21.106712178216604</v>
       </c>
       <c r="I35" s="16">
-        <v>0.34514380975417347</v>
+        <v>0.32683276216154017</v>
       </c>
       <c r="J35" s="16">
-        <v>0.54174875250287391</v>
+        <v>1.7463699853830885</v>
       </c>
       <c r="K35" s="16">
-        <v>0.26759067296811734</v>
+        <v>0.24046161927493348</v>
+      </c>
+      <c r="L35" s="16">
+        <v>568096.9185940827</v>
       </c>
     </row>
   </sheetData>
@@ -6028,7 +6124,7 @@
         <v>98</v>
       </c>
       <c r="R4" s="5">
-        <v>10393.639419290723</v>
+        <v>6393.9317076702955</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
@@ -6073,7 +6169,7 @@
         <v>99</v>
       </c>
       <c r="R5" s="5">
-        <v>8913.1218548035304</v>
+        <v>7601.6529923868393</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
@@ -6112,13 +6208,13 @@
         <v>68</v>
       </c>
       <c r="O6" s="9">
-        <v>7177.9640670783747</v>
+        <v>7577.9874552343463</v>
       </c>
       <c r="Q6" s="12" t="s">
         <v>100</v>
       </c>
       <c r="R6" s="5">
-        <v>440450.72436765849</v>
+        <v>315741.08336552046</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -6163,7 +6259,7 @@
         <v>105</v>
       </c>
       <c r="R7" s="5">
-        <v>115119.86639696265</v>
+        <v>82524.716891440621</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
@@ -6208,7 +6304,7 @@
         <v>104</v>
       </c>
       <c r="R8" s="5">
-        <v>822.4348761810661</v>
+        <v>619.2519616594775</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
@@ -6241,19 +6337,19 @@
         <v>48</v>
       </c>
       <c r="L9" s="6">
-        <v>0.18121875107696997</v>
+        <v>1.6390047735298752</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>71</v>
       </c>
       <c r="O9" s="9">
-        <v>-5.8783407799472913</v>
+        <v>-19.869341720783179</v>
       </c>
       <c r="Q9" s="12" t="s">
         <v>101</v>
       </c>
       <c r="R9" s="5">
-        <v>26046646.011949766</v>
+        <v>47345560.666325219</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
@@ -6261,32 +6357,32 @@
         <v>30</v>
       </c>
       <c r="C10" s="3">
-        <v>423.35913575479753</v>
+        <v>423.08708102866973</v>
       </c>
       <c r="D10" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E10" s="3">
-        <v>576.60060448894728</v>
+        <v>576.26858667218778</v>
       </c>
       <c r="F10" s="6">
-        <v>2.1270479527453361</v>
+        <v>2.1262634543808296</v>
       </c>
       <c r="G10" s="3">
         <v>799.46350834994291</v>
       </c>
       <c r="H10" s="3">
-        <v>252.57320939780874</v>
+        <v>252.47508976842693</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="0"/>
-        <v>150.20913575479756</v>
+        <v>149.93708102866975</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="6">
-        <v>68.670753276561001</v>
+        <v>61.926848784763543</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>72</v>
@@ -6298,7 +6394,7 @@
         <v>102</v>
       </c>
       <c r="R10" s="5">
-        <v>5561582.0670651915</v>
+        <v>4474545.5721388133</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
@@ -6306,44 +6402,44 @@
         <v>31</v>
       </c>
       <c r="C11" s="3">
-        <v>357.24648058947918</v>
+        <v>362.94904708723425</v>
       </c>
       <c r="D11" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E11" s="3">
-        <v>487.05207701453503</v>
+        <v>496.03640269284398</v>
       </c>
       <c r="F11" s="6">
-        <v>1.8961819516546079</v>
+        <v>1.9211337971705802</v>
       </c>
       <c r="G11" s="3">
         <v>799.46350834994291</v>
       </c>
       <c r="H11" s="3">
-        <v>231.85738014859709</v>
+        <v>233.40231308631894</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="0"/>
-        <v>84.096480589479199</v>
+        <v>89.799047087234271</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>50</v>
       </c>
       <c r="L11" s="6">
-        <v>12.546499075118692</v>
+        <v>12.71856373471684</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>73</v>
       </c>
       <c r="O11" s="9">
-        <v>7172.0857262984273</v>
+        <v>7558.118113513563</v>
       </c>
       <c r="Q11" s="12" t="s">
         <v>103</v>
       </c>
       <c r="R11" s="5">
-        <v>9692883.3643694986</v>
+        <v>7798365.2522427328</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
@@ -6351,44 +6447,44 @@
         <v>32</v>
       </c>
       <c r="C12" s="3">
-        <v>357.0720125338982</v>
+        <v>361.35738649679638</v>
       </c>
       <c r="D12" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E12" s="3">
-        <v>486.76983501001507</v>
+        <v>493.57294248449631</v>
       </c>
       <c r="F12" s="6">
-        <v>1.895391710236477</v>
+        <v>1.9143314943410128</v>
       </c>
       <c r="G12" s="3">
         <v>799.46350834994291</v>
       </c>
       <c r="H12" s="3">
-        <v>231.8107486228929</v>
+        <v>232.96695946660682</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="0"/>
-        <v>83.922012533898226</v>
+        <v>88.207386496796403</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>51</v>
       </c>
       <c r="L12" s="6">
-        <v>81.398471102756673</v>
+        <v>76.284417293010264</v>
       </c>
       <c r="N12" s="10" t="s">
         <v>74</v>
       </c>
       <c r="O12" s="11">
-        <v>138173.10399416083</v>
+        <v>138559.13638137598</v>
       </c>
       <c r="Q12" s="12" t="s">
         <v>106</v>
       </c>
       <c r="R12" s="5">
-        <v>580835.8277331352</v>
+        <v>493351.64968492277</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
@@ -6396,38 +6492,38 @@
         <v>33</v>
       </c>
       <c r="C13" s="3">
-        <v>354.0886576106264</v>
+        <v>357.9147949404603</v>
       </c>
       <c r="D13" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E13" s="3">
-        <v>481.86631527551782</v>
+        <v>488.12887620074639</v>
       </c>
       <c r="F13" s="6">
-        <v>1.8816011465198099</v>
+        <v>1.8991933019420426</v>
       </c>
       <c r="G13" s="3">
         <v>799.46350834994291</v>
       </c>
       <c r="H13" s="3">
-        <v>231.01888546051993</v>
+        <v>232.03634524660981</v>
       </c>
       <c r="I13" s="3">
         <f t="shared" si="0"/>
-        <v>80.938657610626422</v>
+        <v>84.76479494046032</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>52</v>
       </c>
       <c r="L13" s="6">
-        <v>72.309456578341951</v>
+        <v>66.529786632388294</v>
       </c>
       <c r="Q13" s="12" t="s">
         <v>107</v>
       </c>
       <c r="R13" s="5">
-        <v>1402278.565085788</v>
+        <v>1128196.8455462928</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
@@ -6460,7 +6556,7 @@
         <v>54</v>
       </c>
       <c r="L14" s="6">
-        <v>1.9169287981163008</v>
+        <v>2.1965125471084219</v>
       </c>
       <c r="N14" s="37" t="s">
         <v>75</v>
@@ -6470,7 +6566,7 @@
         <v>108</v>
       </c>
       <c r="R14" s="5">
-        <v>684893.25534693513</v>
+        <v>551027.75543821603</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
@@ -6503,19 +6599,19 @@
         <v>53</v>
       </c>
       <c r="L15" s="6">
-        <v>74.226385376458239</v>
+        <v>68.726299179496721</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>80</v>
       </c>
       <c r="O15" s="9">
-        <v>8.8110816200029749</v>
+        <v>9.9078139175955826</v>
       </c>
       <c r="Q15" s="12" t="s">
         <v>109</v>
       </c>
       <c r="R15" s="5">
-        <v>213.32557473836525</v>
+        <v>580.12586564866683</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
@@ -6548,7 +6644,7 @@
         <v>46</v>
       </c>
       <c r="L16" s="6">
-        <v>3.9201850902043516</v>
+        <v>4.3523323308963686</v>
       </c>
       <c r="N16" s="8" t="s">
         <v>81</v>
@@ -6560,7 +6656,7 @@
         <v>110</v>
       </c>
       <c r="R16" s="5">
-        <v>1455401.8193176989</v>
+        <v>1536510.4402931174</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
@@ -6593,13 +6689,13 @@
         <v>55</v>
       </c>
       <c r="L17" s="6">
-        <v>-43.56292476579263</v>
+        <v>-48.569613693804691</v>
       </c>
       <c r="N17" s="8" t="s">
         <v>82</v>
       </c>
       <c r="O17" s="9">
-        <v>17.470165800587704</v>
+        <v>17.366718295380426</v>
       </c>
       <c r="Q17" s="12" t="s">
         <v>111</v>
@@ -6638,23 +6734,23 @@
         <v>248</v>
       </c>
       <c r="L18" s="15">
-        <v>6.0634700969981782E-2</v>
+        <v>7.1463166549765617E-2</v>
       </c>
       <c r="N18" s="8" t="s">
         <v>83</v>
       </c>
       <c r="O18" s="9">
-        <v>52.935313208739778</v>
+        <v>52.95934806076604</v>
       </c>
       <c r="Q18" s="12" t="s">
         <v>112</v>
       </c>
       <c r="R18" s="5">
-        <v>204302322.6764515</v>
+        <v>204873108.96594325</v>
       </c>
       <c r="V18" s="5">
         <f>R23-R9-R6</f>
-        <v>212851807.6838057</v>
+        <v>209111725.97569132</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
@@ -6691,13 +6787,13 @@
         <v>84</v>
       </c>
       <c r="O19" s="9">
-        <v>55.302895315550607</v>
+        <v>55.457402293257886</v>
       </c>
       <c r="Q19" s="12" t="s">
         <v>122</v>
       </c>
       <c r="R19" s="5">
-        <v>268677342.46419758</v>
+        <v>287036742.70045835</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
@@ -6736,13 +6832,13 @@
         <v>85</v>
       </c>
       <c r="O20" s="9">
-        <v>35.584623553072362</v>
+        <v>39.302426699184615</v>
       </c>
       <c r="Q20" s="12" t="s">
         <v>250</v>
       </c>
       <c r="R20">
-        <v>1.6888017918525338</v>
+        <v>1.3892468513357714</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.3">
@@ -6753,19 +6849,19 @@
         <v>313.14999999999998</v>
       </c>
       <c r="D21" s="4">
-        <v>7.8923107438086744</v>
+        <v>24.626111643110118</v>
       </c>
       <c r="E21" s="3">
-        <v>-132.35463919610541</v>
+        <v>-83.029464432834615</v>
       </c>
       <c r="F21" s="6">
-        <v>-0.37994748587359245</v>
+        <v>-0.248662394286851</v>
       </c>
       <c r="G21" s="3">
-        <v>178.98150438921974</v>
+        <v>173.63365867730425</v>
       </c>
       <c r="H21" s="3">
-        <v>0.52460446529691762</v>
+        <v>0.58853908566031532</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="0"/>
@@ -6797,44 +6893,44 @@
         <v>18</v>
       </c>
       <c r="C22" s="3">
-        <v>313.1583575108412</v>
+        <v>313.1790338182704</v>
       </c>
       <c r="D22" s="4">
-        <v>31.569242975234697</v>
+        <v>98.504446572440472</v>
       </c>
       <c r="E22" s="3">
-        <v>-132.32179590986752</v>
+        <v>-82.91503188633331</v>
       </c>
       <c r="F22" s="6">
-        <v>-0.37993175416231956</v>
+        <v>-0.24860758461092747</v>
       </c>
       <c r="G22" s="3">
-        <v>178.98150438921974</v>
+        <v>173.63365867730425</v>
       </c>
       <c r="H22" s="3">
-        <v>0.55275734181882941</v>
+        <v>0.68663012728502504</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="0"/>
-        <v>40.008357510841222</v>
+        <v>40.02903381827042</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>61</v>
       </c>
       <c r="L22" s="3">
-        <v>252.77589910235713</v>
+        <v>216.92132320266333</v>
       </c>
       <c r="N22" s="8" t="s">
         <v>87</v>
       </c>
       <c r="O22" s="5">
-        <v>17.082845227237385</v>
+        <v>16.984373320199506</v>
       </c>
       <c r="Q22" s="21" t="s">
         <v>113</v>
       </c>
       <c r="R22" s="22">
-        <v>234142.27371589636</v>
+        <v>241339.13449454925</v>
       </c>
       <c r="S22" s="21" t="s">
         <v>127</v>
@@ -6844,7 +6940,7 @@
       </c>
       <c r="V22" s="26">
         <f>(R23-228195)/228195</f>
-        <v>1047.8350069901755</v>
+        <v>1124.2351178833105</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.3">
@@ -6852,44 +6948,44 @@
         <v>246</v>
       </c>
       <c r="C23" s="3">
-        <v>346.70426173925563</v>
+        <v>348.52161965954565</v>
       </c>
       <c r="D23" s="4">
-        <v>31.569242975234697</v>
+        <v>98.504446572440472</v>
       </c>
       <c r="E23" s="3">
-        <v>-71.687094939885725</v>
+        <v>-11.451865336567687</v>
       </c>
       <c r="F23" s="6">
-        <v>-0.19609375643926472</v>
+        <v>-3.2596436848179706E-2</v>
       </c>
       <c r="G23" s="3">
-        <v>178.98150438921974</v>
+        <v>173.63365867730425</v>
       </c>
       <c r="H23" s="3">
-        <v>6.3761592906718141</v>
+        <v>7.7460729715874184</v>
       </c>
       <c r="I23" s="3">
         <f t="shared" si="0"/>
-        <v>73.554261739255651</v>
+        <v>75.371619659545672</v>
       </c>
       <c r="K23" s="12" t="s">
         <v>62</v>
       </c>
       <c r="L23" s="3">
-        <v>216.7693432268965</v>
+        <v>257.89462587751922</v>
       </c>
       <c r="N23" s="8" t="s">
         <v>88</v>
       </c>
       <c r="O23" s="5">
-        <v>22.682590705779543</v>
+        <v>22.692635964018898</v>
       </c>
       <c r="Q23" s="21" t="s">
         <v>114</v>
       </c>
       <c r="R23" s="22">
-        <v>239338904.42012313</v>
+        <v>256773027.72538206</v>
       </c>
       <c r="S23" s="21" t="s">
         <v>128</v>
@@ -6899,7 +6995,7 @@
       </c>
       <c r="V23" s="26">
         <f>(R24-10815)/10815</f>
-        <v>1100.5342807427048</v>
+        <v>1180.9828008532231</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.3">
@@ -6907,50 +7003,50 @@
         <v>35</v>
       </c>
       <c r="C24" s="3">
-        <v>347.24648058947918</v>
+        <v>352.94904708723425</v>
       </c>
       <c r="D24" s="4">
-        <v>31.569242975234697</v>
+        <v>98.504446572440472</v>
       </c>
       <c r="E24" s="3">
-        <v>-70.674595063457787</v>
+        <v>-2.0124237788916908</v>
       </c>
       <c r="F24" s="6">
-        <v>-0.19317568283781225</v>
+        <v>-5.6830994971502902E-3</v>
       </c>
       <c r="G24" s="3">
-        <v>178.98150438921974</v>
+        <v>173.63365867730425</v>
       </c>
       <c r="H24" s="3">
-        <v>6.518635522826691</v>
+        <v>9.1613029980539871</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="0"/>
-        <v>74.096480589479199</v>
+        <v>79.799047087234271</v>
       </c>
       <c r="K24" s="12" t="s">
         <v>63</v>
       </c>
       <c r="L24" s="3">
-        <v>20.001821007370641</v>
+        <v>21.008819152365195</v>
       </c>
       <c r="N24" s="10" t="s">
         <v>89</v>
       </c>
       <c r="O24" s="14">
-        <v>22.757915766586301</v>
+        <v>22.777686776908567</v>
       </c>
       <c r="Q24" s="21" t="s">
         <v>115</v>
       </c>
       <c r="R24" s="22">
-        <v>11913093.246232353</v>
+        <v>12783143.991227608</v>
       </c>
       <c r="S24" s="21" t="s">
         <v>126</v>
       </c>
       <c r="T24" s="23">
-        <v>268677342.46419758</v>
+        <v>287036742.70045835</v>
       </c>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
@@ -6962,32 +7058,32 @@
         <v>36</v>
       </c>
       <c r="C25" s="3">
-        <v>347.24648058947918</v>
+        <v>352.94904708723425</v>
       </c>
       <c r="D25" s="4">
-        <v>31.569242975234697</v>
+        <v>98.504446572440472</v>
       </c>
       <c r="E25" s="3">
-        <v>313.00054226931974</v>
+        <v>354.6399053634305</v>
       </c>
       <c r="F25" s="6">
-        <v>0.91173151933586583</v>
+        <v>1.0048092990109321</v>
       </c>
       <c r="G25" s="3">
-        <v>178.98150438921974</v>
+        <v>173.63365867730425</v>
       </c>
       <c r="H25" s="3">
-        <v>60.765690527522125</v>
+        <v>64.535323525191458</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="0"/>
-        <v>74.096480589479199</v>
+        <v>79.799047087234271</v>
       </c>
       <c r="K25" s="12" t="s">
         <v>64</v>
       </c>
       <c r="L25" s="3">
-        <v>633460.91765041498</v>
+        <v>1606251.3860119609</v>
       </c>
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
@@ -6995,7 +7091,7 @@
         <v>242</v>
       </c>
       <c r="T25" s="34">
-        <v>520163482.40426898</v>
+        <v>556834253.55156243</v>
       </c>
       <c r="U25" s="5"/>
       <c r="V25" s="8"/>
@@ -7011,19 +7107,19 @@
         <v>396.4382571755965</v>
       </c>
       <c r="D26" s="4">
-        <v>31.569242975234697</v>
+        <v>98.504446572440472</v>
       </c>
       <c r="E26" s="3">
-        <v>383.09995906623425</v>
+        <v>427.88931928238799</v>
       </c>
       <c r="F26" s="6">
-        <v>1.100267344850671</v>
+        <v>1.2002862817475588</v>
       </c>
       <c r="G26" s="3">
-        <v>178.98150438921974</v>
+        <v>173.63365867730425</v>
       </c>
       <c r="H26" s="3">
-        <v>74.65315094719746</v>
+        <v>79.503275041223674</v>
       </c>
       <c r="I26" s="3">
         <f t="shared" si="0"/>
@@ -7033,7 +7129,7 @@
         <v>249</v>
       </c>
       <c r="L26" s="24">
-        <v>0.43125684163752132</v>
+        <v>0.49488349731612458</v>
       </c>
       <c r="N26" s="37" t="s">
         <v>76</v>
@@ -7053,26 +7149,26 @@
         <v>16</v>
       </c>
       <c r="C27" s="3">
-        <v>368.14329244204333</v>
+        <v>369.43022357479919</v>
       </c>
       <c r="D27" s="4">
-        <v>7.8923107438086744</v>
+        <v>24.626111643110118</v>
       </c>
       <c r="E27" s="3">
-        <v>342.99545725431005</v>
+        <v>384.24577970048045</v>
       </c>
       <c r="F27" s="6">
-        <v>1.1196252392794583</v>
+        <v>1.2212685266545973</v>
       </c>
       <c r="G27" s="3">
-        <v>178.98150438921974</v>
+        <v>173.63365867730425</v>
       </c>
       <c r="H27" s="3">
-        <v>28.777092911330342</v>
+        <v>29.603879140282633</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="0"/>
-        <v>94.993292442043355</v>
+        <v>96.280223574799209</v>
       </c>
       <c r="N27" s="12" t="s">
         <v>77</v>
@@ -7095,26 +7191,26 @@
         <v>247</v>
       </c>
       <c r="C28" s="3">
-        <v>322.00678826390748</v>
+        <v>322.36878194840472</v>
       </c>
       <c r="D28" s="4">
-        <v>7.8923107438086744</v>
+        <v>24.626111643110118</v>
       </c>
       <c r="E28" s="3">
-        <v>282.36075628432832</v>
+        <v>312.78261315071484</v>
       </c>
       <c r="F28" s="6">
-        <v>0.94391023344978242</v>
+        <v>1.0147205242393047</v>
       </c>
       <c r="G28" s="3">
-        <v>178.98150438921974</v>
+        <v>173.63365867730425</v>
       </c>
       <c r="H28" s="3">
-        <v>20.531820929466456</v>
+        <v>19.722999510636438</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="0"/>
-        <v>48.856788263907504</v>
+        <v>49.21878194840474</v>
       </c>
       <c r="N28" s="12" t="s">
         <v>78</v>
@@ -7140,19 +7236,19 @@
         <v>313.14999999999998</v>
       </c>
       <c r="D29" s="4">
-        <v>7.8923107438086744</v>
+        <v>24.626111643110118</v>
       </c>
       <c r="E29" s="3">
-        <v>271.65055019539255</v>
+        <v>300.1323438202125</v>
       </c>
       <c r="F29" s="6">
-        <v>0.91018564327057938</v>
+        <v>0.97491036079233406</v>
       </c>
       <c r="G29" s="3">
-        <v>178.98150438921974</v>
+        <v>173.63365867730425</v>
       </c>
       <c r="H29" s="3">
-        <v>19.876601402460075</v>
+        <v>18.942130411848485</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="0"/>
@@ -7191,7 +7287,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G30" s="3">
-        <v>3459.3867266388565</v>
+        <v>3182.8791377078924</v>
       </c>
       <c r="H30" s="3">
         <v>2.5073905791015251E-5</v>
@@ -7227,7 +7323,7 @@
         <v>0.43672528196163279</v>
       </c>
       <c r="G31" s="3">
-        <v>3459.3867266388565</v>
+        <v>3182.8791377078924</v>
       </c>
       <c r="H31" s="3">
         <v>0.17334706272843686</v>
@@ -7251,26 +7347,26 @@
         <v>39</v>
       </c>
       <c r="C32" s="3">
-        <v>303.28257164276243</v>
+        <v>303.31510401884481</v>
       </c>
       <c r="D32" s="4">
         <v>101.325</v>
       </c>
       <c r="E32" s="3">
-        <v>126.37663520257469</v>
+        <v>126.51261372658171</v>
       </c>
       <c r="F32" s="6">
-        <v>0.43855276906236179</v>
+        <v>0.43900110089670652</v>
       </c>
       <c r="G32" s="3">
-        <v>3459.3867266388565</v>
+        <v>3182.8791377078924</v>
       </c>
       <c r="H32" s="3">
-        <v>0.18260566443543941</v>
+        <v>0.18491405203257455</v>
       </c>
       <c r="I32" s="3">
         <f t="shared" si="0"/>
-        <v>30.132571642762457</v>
+        <v>30.165104018844829</v>
       </c>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
@@ -7323,26 +7419,26 @@
         <v>30</v>
       </c>
       <c r="C34" s="3">
-        <v>423.35913575479753</v>
+        <v>423.08708102866973</v>
       </c>
       <c r="D34" s="4">
         <v>9124.0875912408756</v>
       </c>
       <c r="E34" s="3">
-        <v>576.60060448894728</v>
+        <v>576.26858667218778</v>
       </c>
       <c r="F34" s="6">
-        <v>2.1270479527453361</v>
+        <v>2.1262634543808296</v>
       </c>
       <c r="G34" s="3">
         <v>799.46350834994291</v>
       </c>
       <c r="H34" s="3">
-        <v>252.57320939780874</v>
+        <v>252.47508976842693</v>
       </c>
       <c r="I34" s="3">
         <f t="shared" si="0"/>
-        <v>150.20913575479756</v>
+        <v>149.93708102866975</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.3">
@@ -7350,26 +7446,26 @@
         <v>31</v>
       </c>
       <c r="C35" s="3">
-        <v>357.24648058947918</v>
+        <v>362.94904708723425</v>
       </c>
       <c r="D35" s="4">
         <v>9124.0875912408756</v>
       </c>
       <c r="E35" s="3">
-        <v>487.05207701453503</v>
+        <v>496.03640269284398</v>
       </c>
       <c r="F35" s="6">
-        <v>1.8961819516546079</v>
+        <v>1.9211337971705802</v>
       </c>
       <c r="G35" s="3">
         <v>799.46350834994291</v>
       </c>
       <c r="H35" s="3">
-        <v>231.85738014859709</v>
+        <v>233.40231308631894</v>
       </c>
       <c r="I35" s="3">
         <f t="shared" si="0"/>
-        <v>84.096480589479199</v>
+        <v>89.799047087234271</v>
       </c>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.3">
@@ -7377,26 +7473,26 @@
         <v>32</v>
       </c>
       <c r="C36" s="3">
-        <v>357.0720125338982</v>
+        <v>361.35738649679638</v>
       </c>
       <c r="D36" s="4">
         <v>9124.0875912408756</v>
       </c>
       <c r="E36" s="3">
-        <v>486.76983501001507</v>
+        <v>493.57294248449631</v>
       </c>
       <c r="F36" s="6">
-        <v>1.895391710236477</v>
+        <v>1.9143314943410128</v>
       </c>
       <c r="G36" s="3">
         <v>799.46350834994291</v>
       </c>
       <c r="H36" s="3">
-        <v>231.8107486228929</v>
+        <v>232.96695946660682</v>
       </c>
       <c r="I36" s="3">
         <f t="shared" si="0"/>
-        <v>83.922012533898226</v>
+        <v>88.207386496796403</v>
       </c>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.3">
@@ -7437,16 +7533,16 @@
         <v>0.101325</v>
       </c>
       <c r="E38" s="3">
-        <v>463.63790518370155</v>
+        <v>467.95937759062173</v>
       </c>
       <c r="F38" s="6">
-        <v>4.0040683198491838</v>
+        <v>4.0168081231812165</v>
       </c>
       <c r="G38" s="3">
         <v>100</v>
       </c>
       <c r="H38" s="3">
-        <v>2.3777069072226005</v>
+        <v>2.9008069506970422</v>
       </c>
       <c r="I38" s="3">
         <f t="shared" si="0"/>
@@ -7458,26 +7554,26 @@
         <v>32</v>
       </c>
       <c r="C39" s="3">
-        <v>357.0720125338982</v>
+        <v>361.35738649679638</v>
       </c>
       <c r="D39" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E39" s="3">
-        <v>486.76983501001507</v>
+        <v>493.57294248449631</v>
       </c>
       <c r="F39" s="6">
-        <v>1.895391710236477</v>
+        <v>1.9143314943410128</v>
       </c>
       <c r="G39" s="3">
         <v>799.46350834994291</v>
       </c>
       <c r="H39" s="3">
-        <v>231.8107486228929</v>
+        <v>232.96695946660682</v>
       </c>
       <c r="I39" s="3">
         <f t="shared" si="0"/>
-        <v>83.922012533898226</v>
+        <v>88.207386496796403</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.3">
@@ -7485,26 +7581,26 @@
         <v>33</v>
       </c>
       <c r="C40" s="3">
-        <v>354.0886576106264</v>
+        <v>357.9147949404603</v>
       </c>
       <c r="D40" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E40" s="3">
-        <v>481.86631527551782</v>
+        <v>488.12887620074639</v>
       </c>
       <c r="F40" s="6">
-        <v>1.8816011465198099</v>
+        <v>1.8991933019420426</v>
       </c>
       <c r="G40" s="3">
         <v>799.46350834994291</v>
       </c>
       <c r="H40" s="3">
-        <v>231.01888546051993</v>
+        <v>232.03634524660981</v>
       </c>
       <c r="I40" s="3">
         <f t="shared" si="0"/>
-        <v>80.938657610626422</v>
+        <v>84.76479494046032</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.3">
@@ -7512,26 +7608,26 @@
         <v>33</v>
       </c>
       <c r="C41" s="3">
-        <v>354.0886576106264</v>
+        <v>357.9147949404603</v>
       </c>
       <c r="D41" s="4">
         <v>9124.0875912408756</v>
       </c>
       <c r="E41" s="3">
-        <v>481.86631526601889</v>
+        <v>488.12887619058898</v>
       </c>
       <c r="F41" s="6">
-        <v>1.8816011465198099</v>
+        <v>1.8991933019420426</v>
       </c>
       <c r="G41" s="3">
         <v>799.46350834994291</v>
       </c>
       <c r="H41" s="3">
-        <v>231.01888545102102</v>
+        <v>232.03634523645241</v>
       </c>
       <c r="I41" s="3">
         <f t="shared" si="0"/>
-        <v>80.938657610626422</v>
+        <v>84.76479494046032</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.3">
@@ -7578,7 +7674,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G43" s="3">
-        <v>9.3513890741139208E-2</v>
+        <v>9.7982274150728743E-2</v>
       </c>
       <c r="H43" s="3">
         <v>2.5073905791015251E-5</v>
@@ -7593,26 +7689,26 @@
         <v>20</v>
       </c>
       <c r="C44" s="3">
-        <v>353.0886576106264</v>
+        <v>356.9147949404603</v>
       </c>
       <c r="D44" s="4">
         <v>101.325</v>
       </c>
       <c r="E44" s="3">
-        <v>334.79782589110334</v>
+        <v>350.86067438903575</v>
       </c>
       <c r="F44" s="3">
-        <v>1.0748138131181144</v>
+        <v>1.1200614625361844</v>
       </c>
       <c r="G44" s="3">
-        <v>9.3513890741139208E-2</v>
+        <v>9.7982274150728743E-2</v>
       </c>
       <c r="H44" s="3">
-        <v>18.902566067741457</v>
+        <v>21.47482789167622</v>
       </c>
       <c r="I44" s="3">
         <f t="shared" si="0"/>
-        <v>79.938657610626422</v>
+        <v>83.76479494046032</v>
       </c>
     </row>
   </sheetData>
@@ -7639,11 +7735,11 @@
   <cols>
     <col min="2" max="2" width="22.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7687,10 +7783,10 @@
         <v>202</v>
       </c>
       <c r="B2">
-        <v>9.2705168398387522E-2</v>
+        <v>9.2406574326365926E-2</v>
       </c>
       <c r="C2">
-        <v>70141.877427241488</v>
+        <v>69915.957457922879</v>
       </c>
       <c r="E2" t="s">
         <v>66</v>
@@ -7702,19 +7798,19 @@
         <v>1541.2694860114752</v>
       </c>
       <c r="H2">
-        <v>142.88364724798998</v>
+        <v>142.42343331607918</v>
       </c>
       <c r="I2">
-        <v>99.432434257689778</v>
+        <v>99.434251987875697</v>
       </c>
       <c r="K2" s="25">
-        <v>0.351638456117429</v>
+        <v>0.35198545686127924</v>
       </c>
       <c r="L2" s="25">
-        <v>1.9005496689146004</v>
+        <v>1.904205650074752</v>
       </c>
       <c r="M2" s="25">
-        <v>0.27102443565787682</v>
+        <v>0.26978389328349178</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -7722,10 +7818,10 @@
         <v>203</v>
       </c>
       <c r="B3">
-        <v>9.2705168398387522E-2</v>
+        <v>9.2406574326365953E-2</v>
       </c>
       <c r="C3">
-        <v>63627.369185011448</v>
+        <v>63422.43179494785</v>
       </c>
       <c r="E3" t="s">
         <v>67</v>
@@ -7737,10 +7833,10 @@
         <v>2806.532548235491</v>
       </c>
       <c r="H3">
-        <v>246.28271463304634</v>
+        <v>245.50177594265065</v>
       </c>
       <c r="I3">
-        <v>97.302158252000311</v>
+        <v>97.310482770177444</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -7748,10 +7844,10 @@
         <v>204</v>
       </c>
       <c r="B4">
-        <v>8.7753379089755418E-2</v>
+        <v>8.7475121604059528E-2</v>
       </c>
       <c r="C4">
-        <v>64630.600808244235</v>
+        <v>64425.663418180629</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
@@ -7763,10 +7859,10 @@
         <v>3117.3934843303709</v>
       </c>
       <c r="H4">
-        <v>844.88980981418104</v>
+        <v>841.02255109923738</v>
       </c>
       <c r="I4">
-        <v>24.293129608235933</v>
+        <v>24.377604857384672</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -7774,10 +7870,10 @@
         <v>205</v>
       </c>
       <c r="B5">
-        <v>8.7753379089755418E-2</v>
+        <v>8.7475121604059514E-2</v>
       </c>
       <c r="C5">
-        <v>53872.817520246113</v>
+        <v>53701.992021490041</v>
       </c>
       <c r="E5" t="s">
         <v>70</v>
@@ -7789,10 +7885,10 @@
         <v>1138.33305276341</v>
       </c>
       <c r="H5">
-        <v>308.51607321591132</v>
+        <v>307.1039228277952</v>
       </c>
       <c r="I5">
-        <v>18.06147997593202</v>
+        <v>18.129474900382768</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -7800,10 +7896,10 @@
         <v>206</v>
       </c>
       <c r="B6">
-        <v>8.7753379089755432E-2</v>
+        <v>8.74751216040595E-2</v>
       </c>
       <c r="C6">
-        <v>28561.645764850608</v>
+        <v>28471.079545973313</v>
       </c>
       <c r="E6" t="s">
         <v>59</v>
@@ -7815,10 +7911,10 @@
         <v>3469.1288051136653</v>
       </c>
       <c r="H6">
-        <v>304.42777514632974</v>
+        <v>303.46246408746356</v>
       </c>
       <c r="I6">
-        <v>11.543093954840245</v>
+        <v>11.575562052251838</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -7826,10 +7922,10 @@
         <v>207</v>
       </c>
       <c r="B7">
-        <v>8.7753379089755459E-2</v>
+        <v>8.7475121604059514E-2</v>
       </c>
       <c r="C7">
-        <v>22554.498305434041</v>
+        <v>22482.980170694358</v>
       </c>
       <c r="E7" t="s">
         <v>60</v>
@@ -7841,10 +7937,10 @@
         <v>7142.9330882120803</v>
       </c>
       <c r="H7">
-        <v>626.81651510263214</v>
+        <v>624.82894050101197</v>
       </c>
       <c r="I7">
-        <v>2.7913761489247011</v>
+        <v>2.8000068663790731</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -7852,25 +7948,25 @@
         <v>208</v>
       </c>
       <c r="B8">
-        <v>8.8056030807238755E-2</v>
+        <v>8.7827851562217951E-2</v>
       </c>
       <c r="C8">
-        <v>15792.343037709175</v>
+        <v>15751.420401537414</v>
       </c>
       <c r="E8" t="s">
         <v>253</v>
       </c>
       <c r="F8">
-        <v>4.3558031700714581</v>
+        <v>3.9799033859835076</v>
       </c>
       <c r="G8">
-        <v>7945.7510262283686</v>
+        <v>6782.2557987781765</v>
       </c>
       <c r="H8">
-        <v>697.26650195743093</v>
+        <v>593.27865074795898</v>
       </c>
       <c r="I8">
-        <v>0.62081879926549643</v>
+        <v>0.66636188940894858</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -7878,25 +7974,25 @@
         <v>209</v>
       </c>
       <c r="B9">
-        <v>0.12349953512734348</v>
+        <v>0.1230859866768063</v>
       </c>
       <c r="C9">
-        <v>26536.056257462154</v>
+        <v>26447.19806915136</v>
       </c>
       <c r="E9" t="s">
         <v>254</v>
       </c>
       <c r="F9">
-        <v>0.10137910288596741</v>
+        <v>0.10995398107179184</v>
       </c>
       <c r="G9">
-        <v>433.46994194346053</v>
+        <v>489.8963917659762</v>
       </c>
       <c r="H9">
-        <v>93.762351896132586</v>
+        <v>95.75191476595441</v>
       </c>
       <c r="I9">
-        <v>0.10800668352617204</v>
+        <v>0.11470043564658007</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -7904,25 +8000,25 @@
         <v>210</v>
       </c>
       <c r="B10">
-        <v>0.11789864797223976</v>
+        <v>0.11750793748009437</v>
       </c>
       <c r="C10">
-        <v>32561.202949875686</v>
+        <v>32453.296677427275</v>
       </c>
       <c r="E10" t="s">
         <v>228</v>
       </c>
       <c r="F10">
-        <v>74.544987755493182</v>
+        <v>77.429288617854894</v>
       </c>
       <c r="G10">
-        <v>1033.0018156282754</v>
+        <v>1086.2272208333268</v>
       </c>
       <c r="H10">
-        <v>223.44497362844987</v>
+        <v>212.30680203780128</v>
       </c>
       <c r="I10">
-        <v>25.015939264962761</v>
+        <v>26.724074464674679</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -7930,25 +8026,25 @@
         <v>211</v>
       </c>
       <c r="B11">
-        <v>0.14010474406283235</v>
+        <v>0.13955976303443879</v>
       </c>
       <c r="C11">
-        <v>9705.9762711685507</v>
+        <v>9668.2218541771254</v>
       </c>
       <c r="E11" t="s">
         <v>229</v>
       </c>
       <c r="F11">
-        <v>0.19512857408974876</v>
+        <v>0.51696822047328139</v>
       </c>
       <c r="G11">
-        <v>0.8394965871715695</v>
+        <v>2.8374352800170817</v>
       </c>
       <c r="H11">
-        <v>0.22752408877488822</v>
+        <v>0.76549433678294299</v>
       </c>
       <c r="I11">
-        <v>46.167596050907314</v>
+        <v>40.310589774980528</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -7956,25 +8052,25 @@
         <v>212</v>
       </c>
       <c r="B12">
-        <v>0.12235178057549123</v>
+        <v>0.12193013321124166</v>
       </c>
       <c r="C12">
-        <v>42267.179221044236</v>
+        <v>42121.518531604401</v>
       </c>
       <c r="E12" t="s">
         <v>255</v>
       </c>
       <c r="F12">
-        <v>1.1689883797277512</v>
+        <v>1.2781700334423005</v>
       </c>
       <c r="G12">
-        <v>2949.3048299776801</v>
+        <v>2733.9070991328199</v>
       </c>
       <c r="H12">
-        <v>637.95370926411374</v>
+        <v>534.3514341686647</v>
       </c>
       <c r="I12">
-        <v>0.18290515796689533</v>
+        <v>0.2386294602491788</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -7982,25 +8078,25 @@
         <v>213</v>
       </c>
       <c r="B13">
-        <v>0.10725837525653287</v>
+        <v>0.10690001237587672</v>
       </c>
       <c r="C13">
-        <v>67618.07696922071</v>
+        <v>67392.156999902101</v>
       </c>
       <c r="E13" t="s">
         <v>63</v>
       </c>
       <c r="F13">
-        <v>0.34344487093177295</v>
+        <v>0.35222626491756892</v>
       </c>
       <c r="G13">
-        <v>397.40619041460195</v>
+        <v>456.02259338253077</v>
       </c>
       <c r="H13">
-        <v>34.873736080068078</v>
+        <v>39.890631810335478</v>
       </c>
       <c r="I13">
-        <v>0.97521965602423433</v>
+        <v>0.87525161423404729</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -8008,25 +8104,25 @@
         <v>214</v>
       </c>
       <c r="B14">
-        <v>8.7753379089755418E-2</v>
+        <v>8.74751216040595E-2</v>
       </c>
       <c r="C14">
-        <v>4522.999961098898</v>
+        <v>4508.657965268847</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>230</v>
       </c>
       <c r="F14" s="24">
-        <v>70.662871789501864</v>
+        <v>113.9975296205717</v>
       </c>
       <c r="G14" s="24">
-        <v>5334.0922622019607</v>
+        <v>6147.1777320041247</v>
       </c>
       <c r="H14" s="24">
-        <v>469.69899256910952</v>
+        <v>539.89341337302983</v>
       </c>
       <c r="I14" s="24">
-        <v>13.076953880410485</v>
+        <v>17.433722066660767</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -8034,25 +8130,25 @@
         <v>215</v>
       </c>
       <c r="B15">
-        <v>8.775337908975539E-2</v>
+        <v>8.7475121604059541E-2</v>
       </c>
       <c r="C15">
-        <v>18031.498344335127</v>
+        <v>17974.322205425517</v>
       </c>
       <c r="E15" t="s">
         <v>172</v>
       </c>
       <c r="F15">
-        <v>385.30984394830051</v>
+        <v>406.04887085806683</v>
       </c>
       <c r="G15">
-        <v>5942.7230807089181</v>
+        <v>6270.2647481636777</v>
       </c>
       <c r="H15">
-        <v>1610.6231692201736</v>
+        <v>1691.6164356778302</v>
       </c>
       <c r="I15">
-        <v>19.304748275927082</v>
+        <v>19.357181033261188</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -8060,10 +8156,10 @@
         <v>216</v>
       </c>
       <c r="B16">
-        <v>8.775337908975539E-2</v>
+        <v>8.7475121604059541E-2</v>
       </c>
       <c r="C16">
-        <v>16262.827792951006</v>
+        <v>16292.117424184464</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -8071,10 +8167,10 @@
         <v>217</v>
       </c>
       <c r="B17">
-        <v>8.8056030807238714E-2</v>
+        <v>8.7827851562217937E-2</v>
       </c>
       <c r="C17">
-        <v>16263.171237821938</v>
+        <v>16292.469650449379</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -8085,7 +8181,7 @@
         <v>2E-3</v>
       </c>
       <c r="C18">
-        <v>4.6895169731892359E-9</v>
+        <v>4.9135966224896022E-9</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -8093,10 +8189,10 @@
         <v>218</v>
       </c>
       <c r="B19">
-        <v>306.33344083406104</v>
+        <v>311.3114599283947</v>
       </c>
       <c r="C19">
-        <v>541.49107190695611</v>
+        <v>655.04677853745</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -8104,10 +8200,10 @@
         <v>219</v>
       </c>
       <c r="B20">
-        <v>0.21630646746980772</v>
+        <v>0.19545339866821301</v>
       </c>
       <c r="C20">
-        <v>2890.1860602999263</v>
+        <v>2698.1255985977582</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -8115,10 +8211,10 @@
         <v>220</v>
       </c>
       <c r="B21">
-        <v>0.21630646746980772</v>
+        <v>0.19545339866821301</v>
       </c>
       <c r="C21">
-        <v>1114.1010356965394</v>
+        <v>1004.6753933693218</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -8126,10 +8222,10 @@
         <v>251</v>
       </c>
       <c r="B22">
-        <v>0.21630646746980767</v>
+        <v>0.19545339866821299</v>
       </c>
       <c r="C22">
-        <v>794.88651034824022</v>
+        <v>669.34512865270472</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -8137,10 +8233,10 @@
         <v>221</v>
       </c>
       <c r="B23">
-        <v>8.478191259130254</v>
+        <v>6.5625014272466329</v>
       </c>
       <c r="C23">
-        <v>796.05549872796803</v>
+        <v>670.623298686147</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -8148,10 +8244,10 @@
         <v>222</v>
       </c>
       <c r="B24">
-        <v>8.0644583155531944</v>
+        <v>5.6742893196732593</v>
       </c>
       <c r="C24">
-        <v>797.84380129454769</v>
+        <v>676.50069527303333</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -8159,10 +8255,10 @@
         <v>252</v>
       </c>
       <c r="B25">
-        <v>0.97892168860970719</v>
+        <v>0.75238417935517443</v>
       </c>
       <c r="C25">
-        <v>1117.1597057457327</v>
+        <v>1011.9409139707221</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -8170,10 +8266,10 @@
         <v>223</v>
       </c>
       <c r="B26">
-        <v>1.9005496689146004</v>
+        <v>1.904205650074752</v>
       </c>
       <c r="C26">
-        <v>2329.1203304082451</v>
+        <v>2445.1074014182363</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -8192,10 +8288,10 @@
         <v>225</v>
       </c>
       <c r="B28" s="24">
-        <v>0.27102443565787682</v>
+        <v>0.26978389328349178</v>
       </c>
       <c r="C28" s="24">
-        <v>1943.8104864599447</v>
+        <v>2039.0585305601694</v>
       </c>
     </row>
   </sheetData>

--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tes2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A858FA-2336-44E5-A497-0C75CCEB9BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86FCA34-9C00-4775-A2B5-3CE814481FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3336" yWindow="3540" windowWidth="17280" windowHeight="9420" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="3" r:id="rId1"/>
@@ -2531,10 +2531,10 @@
         <v>0.27721683884119408</v>
       </c>
       <c r="F29" s="16">
-        <v>1.3066538362716359E-2</v>
+        <v>1.2725895991014955E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.76196895766048367</v>
+        <v>0.74329834926752969</v>
       </c>
       <c r="H29" s="16">
         <v>21.757787473165259</v>
@@ -2566,10 +2566,10 @@
         <v>0.29141583095469492</v>
       </c>
       <c r="F30" s="16">
-        <v>1.2891638164129249E-2</v>
+        <v>1.256705583287248E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.75238267777592416</v>
+        <v>0.73459232019974063</v>
       </c>
       <c r="H30" s="16">
         <v>22.620890157848095</v>
@@ -2601,10 +2601,10 @@
         <v>0.30082239580281539</v>
       </c>
       <c r="F31" s="16">
-        <v>1.278733576486221E-2</v>
+        <v>1.2460487945338345E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.74666586327209783</v>
+        <v>0.72875133428399475</v>
       </c>
       <c r="H31" s="16">
         <v>23.183143546879993</v>
@@ -2636,10 +2636,10 @@
         <v>0.30563943460760568</v>
       </c>
       <c r="F32" s="16">
-        <v>1.2743286995087122E-2</v>
+        <v>1.2396637952335364E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.7442515502007252</v>
+        <v>0.72525171616750128</v>
       </c>
       <c r="H32" s="16">
         <v>23.469051190883171</v>
@@ -2671,10 +2671,10 @@
         <v>0.30600947271635609</v>
       </c>
       <c r="F33" s="16">
-        <v>1.2760809080769826E-2</v>
+        <v>1.2373819823211687E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.74521193571699418</v>
+        <v>0.72400105451023267</v>
       </c>
       <c r="H33" s="16">
         <v>23.49293753748929</v>
@@ -2706,10 +2706,10 @@
         <v>0.30204684930766268</v>
       </c>
       <c r="F34" s="16">
-        <v>1.2855676451430006E-2</v>
+        <v>1.2399204794170266E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.75041161630287867</v>
+        <v>0.72539240476847233</v>
       </c>
       <c r="H34" s="16">
         <v>23.261899200976021</v>
@@ -2741,10 +2741,10 @@
         <v>0.29386112662101954</v>
       </c>
       <c r="F35" s="16">
-        <v>1.3075242228025856E-2</v>
+        <v>1.2498061236008415E-2</v>
       </c>
       <c r="G35" s="16">
-        <v>0.76244601651809718</v>
+        <v>0.73081072634562128</v>
       </c>
       <c r="H35" s="16">
         <v>22.777686776908567</v>
@@ -2776,10 +2776,10 @@
         <v>0.28157430810541256</v>
       </c>
       <c r="F36" s="16">
-        <v>1.3578355310744016E-2</v>
+        <v>1.2758135640936705E-2</v>
       </c>
       <c r="G36" s="16">
-        <v>0.79002164458187951</v>
+        <v>0.74506540447974079</v>
       </c>
       <c r="H36" s="16">
         <v>22.037942778693676</v>
@@ -2811,10 +2811,10 @@
         <v>0.26533370011538154</v>
       </c>
       <c r="F37" s="16">
-        <v>1.5671120364137446E-2</v>
+        <v>1.390700110545017E-2</v>
       </c>
       <c r="G37" s="16">
-        <v>0.90472609715837349</v>
+        <v>0.80803472058972381</v>
       </c>
       <c r="H37" s="16">
         <v>21.037063645279886</v>
@@ -2846,10 +2846,10 @@
         <v>0.29386112662101954</v>
       </c>
       <c r="F38" s="18">
-        <v>1.3075242228025856E-2</v>
+        <v>1.2498061236008415E-2</v>
       </c>
       <c r="G38" s="18">
-        <v>0.76244601651809718</v>
+        <v>0.73081072634562128</v>
       </c>
       <c r="H38" s="18">
         <v>22.777686776908567</v>
@@ -3619,10 +3619,10 @@
         <v>0.26242431235563907</v>
       </c>
       <c r="F29" s="16">
-        <v>1.2687298913338699E-2</v>
+        <v>1.2211101410757789E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.74118284344009411</v>
+        <v>0.71508245832363448</v>
       </c>
       <c r="H29" s="16">
         <v>20.8250053094837</v>
@@ -3654,10 +3654,10 @@
         <v>0.26498555144485081</v>
       </c>
       <c r="F30" s="16">
-        <v>1.3781762480049234E-2</v>
+        <v>1.2848659426448708E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.8011703915314986</v>
+        <v>0.75002701316365372</v>
       </c>
       <c r="H30" s="16">
         <v>21.010323870069069</v>
@@ -3689,10 +3689,10 @@
         <v>0.26634915185839914</v>
       </c>
       <c r="F31" s="16">
-        <v>1.3238832473157039E-2</v>
+        <v>1.2569616257764678E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.77141239785373727</v>
+        <v>0.734732657088082</v>
       </c>
       <c r="H31" s="16">
         <v>21.120968205447276</v>
@@ -3724,10 +3724,10 @@
         <v>0.26699299315765596</v>
       </c>
       <c r="F32" s="16">
-        <v>1.2331820908740496E-2</v>
+        <v>1.2084861351781972E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.72169909400806664</v>
+        <v>0.70816324069116998</v>
       </c>
       <c r="H32" s="16">
         <v>21.188960488161513</v>
@@ -3759,10 +3759,10 @@
         <v>0.26715706725652344</v>
       </c>
       <c r="F33" s="16">
-        <v>1.1959199986815333E-2</v>
+        <v>1.1896018768568203E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.70127574127734837</v>
+        <v>0.69781277870522329</v>
       </c>
       <c r="H33" s="16">
         <v>21.228220514190312</v>
@@ -3794,10 +3794,10 @@
         <v>0.26698424761118889</v>
       </c>
       <c r="F34" s="16">
-        <v>1.175660043776486E-2</v>
+        <v>1.1800413306798704E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.69017125999389195</v>
+        <v>0.69257264334563695</v>
       </c>
       <c r="H34" s="16">
         <v>21.246913286205405</v>
@@ -4665,10 +4665,10 @@
         <v>0.17164807793559991</v>
       </c>
       <c r="F29" s="16">
-        <v>2.0341675998230901E-2</v>
+        <v>1.6757024969993196E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>1.1607192514630356</v>
+        <v>0.96424452860532706</v>
       </c>
       <c r="H29" s="16">
         <v>14.757340342055347</v>
@@ -4700,10 +4700,10 @@
         <v>0.1888468926271184</v>
       </c>
       <c r="F30" s="16">
-        <v>1.978432924799594E-2</v>
+        <v>1.6384759955406843E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>1.1301710760826573</v>
+        <v>0.94384068315584913</v>
       </c>
       <c r="H30" s="16">
         <v>15.983919810375957</v>
@@ -4735,10 +4735,10 @@
         <v>0.20480986996949019</v>
       </c>
       <c r="F31" s="16">
-        <v>1.9555506784251827E-2</v>
+        <v>1.6208407990483766E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>1.1176293168448426</v>
+        <v>0.93417483195841522</v>
       </c>
       <c r="H31" s="16">
         <v>17.091203390183175</v>
@@ -4770,10 +4770,10 @@
         <v>0.21966556495623429</v>
       </c>
       <c r="F32" s="16">
-        <v>1.9780145140133622E-2</v>
+        <v>1.6294029696723257E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>1.1299417451307239</v>
+        <v>0.93886775767740172</v>
       </c>
       <c r="H32" s="16">
         <v>18.095784881552312</v>
@@ -4805,10 +4805,10 @@
         <v>0.23352530431347171</v>
       </c>
       <c r="F33" s="16">
-        <v>2.1278787193004869E-2</v>
+        <v>1.7096731860174904E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>1.2120823160485967</v>
+        <v>0.98286386325618658</v>
       </c>
       <c r="H33" s="16">
         <v>19.011318909297625</v>
@@ -4840,10 +4840,10 @@
         <v>0.24648595905073192</v>
       </c>
       <c r="F34" s="16">
-        <v>1.9465300659532975E-2</v>
+        <v>1.6058055835609431E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>1.1126851191490024</v>
+        <v>0.92593403034975297</v>
       </c>
       <c r="H34" s="16">
         <v>19.849141217844313</v>
@@ -4875,10 +4875,10 @@
         <v>0.25863227729297766</v>
       </c>
       <c r="F35" s="16">
-        <v>1.6483802014683472E-2</v>
+        <v>1.4372241813136767E-2</v>
       </c>
       <c r="G35" s="16">
-        <v>0.94926917842480119</v>
+        <v>0.83353456377802626</v>
       </c>
       <c r="H35" s="16">
         <v>20.618744692025714</v>
@@ -5746,10 +5746,10 @@
         <v>0.21752070053998984</v>
       </c>
       <c r="F29" s="16">
-        <v>1.3347972360860334E-2</v>
+        <v>1.2820307346803273E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.77739435509875499</v>
+        <v>0.74847303567828738</v>
       </c>
       <c r="H29" s="16">
         <v>17.986004189136761</v>
@@ -5781,10 +5781,10 @@
         <v>0.22887252850425274</v>
       </c>
       <c r="F30" s="16">
-        <v>1.3291196355712501E-2</v>
+        <v>1.2732527471849048E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.77428246225660224</v>
+        <v>0.74366182073204634</v>
       </c>
       <c r="H30" s="16">
         <v>18.729554829407846</v>
@@ -5816,10 +5816,10 @@
         <v>0.23858500738232519</v>
       </c>
       <c r="F31" s="16">
-        <v>1.3259884166837736E-2</v>
+        <v>1.2670697653095902E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.77256624118437633</v>
+        <v>0.74027292836618641</v>
       </c>
       <c r="H31" s="16">
         <v>19.356136135287894</v>
@@ -5851,10 +5851,10 @@
         <v>0.24698231842324175</v>
       </c>
       <c r="F32" s="16">
-        <v>1.3246821447386169E-2</v>
+        <v>1.262745197607002E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.77185027353123592</v>
+        <v>0.73790263280839785</v>
       </c>
       <c r="H32" s="16">
         <v>19.890850554306937</v>
@@ -5886,10 +5886,10 @@
         <v>0.25430934115195086</v>
       </c>
       <c r="F33" s="16">
-        <v>1.3247346740240681E-2</v>
+        <v>1.259800766538546E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.77187906483259183</v>
+        <v>0.73628879013977711</v>
       </c>
       <c r="H33" s="16">
         <v>20.35216278034363</v>
@@ -5921,10 +5921,10 @@
         <v>0.26075436728817891</v>
       </c>
       <c r="F34" s="16">
-        <v>1.3258314031391686E-2</v>
+        <v>1.257912344780103E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.77248018206057834</v>
+        <v>0.73525374617397443</v>
       </c>
       <c r="H34" s="16">
         <v>20.753941271896004</v>
@@ -5956,10 +5956,10 @@
         <v>0.26646417225585195</v>
       </c>
       <c r="F35" s="16">
-        <v>1.3277549695321836E-2</v>
+        <v>1.2568539303476595E-2</v>
       </c>
       <c r="G35" s="16">
-        <v>0.77353448880058984</v>
+        <v>0.73467362922355217</v>
       </c>
       <c r="H35" s="16">
         <v>21.106712178216604</v>
@@ -6124,7 +6124,7 @@
         <v>98</v>
       </c>
       <c r="R4" s="5">
-        <v>6393.9317076702955</v>
+        <v>3564.7236360481061</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
@@ -6169,7 +6169,7 @@
         <v>99</v>
       </c>
       <c r="R5" s="5">
-        <v>7601.6529923868393</v>
+        <v>4238.0484080694978</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
@@ -6214,7 +6214,7 @@
         <v>100</v>
       </c>
       <c r="R6" s="5">
-        <v>315741.08336552046</v>
+        <v>176030.92341356995</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -6259,7 +6259,7 @@
         <v>105</v>
       </c>
       <c r="R7" s="5">
-        <v>82524.716891440621</v>
+        <v>46008.906930956873</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
@@ -6304,7 +6304,7 @@
         <v>104</v>
       </c>
       <c r="R8" s="5">
-        <v>619.2519616594775</v>
+        <v>345.24330338852025</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
@@ -6349,7 +6349,7 @@
         <v>101</v>
       </c>
       <c r="R9" s="5">
-        <v>47345560.666325219</v>
+        <v>26395940.226689368</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
@@ -6394,7 +6394,7 @@
         <v>102</v>
       </c>
       <c r="R10" s="5">
-        <v>4474545.5721388133</v>
+        <v>7331176.3611313887</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
@@ -6439,7 +6439,7 @@
         <v>103</v>
       </c>
       <c r="R11" s="5">
-        <v>7798365.2522427328</v>
+        <v>12776982.616668882</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
@@ -6484,7 +6484,7 @@
         <v>106</v>
       </c>
       <c r="R12" s="5">
-        <v>493351.64968492277</v>
+        <v>808316.26219563605</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
@@ -6523,7 +6523,7 @@
         <v>107</v>
       </c>
       <c r="R13" s="5">
-        <v>1128196.8455462928</v>
+        <v>1848458.1085221746</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
@@ -6566,7 +6566,7 @@
         <v>108</v>
       </c>
       <c r="R14" s="5">
-        <v>551027.75543821603</v>
+        <v>902813.83659368719</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
@@ -6611,7 +6611,7 @@
         <v>109</v>
       </c>
       <c r="R15" s="5">
-        <v>580.12586564866683</v>
+        <v>950.48870643001896</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="V18" s="5">
         <f>R23-R9-R6</f>
-        <v>209111725.97569132</v>
+        <v>218858501.26033798</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
@@ -6793,7 +6793,7 @@
         <v>122</v>
       </c>
       <c r="R19" s="5">
-        <v>287036742.70045835</v>
+        <v>275127059.32777882</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
@@ -6838,7 +6838,7 @@
         <v>250</v>
       </c>
       <c r="R20">
-        <v>1.3892468513357714</v>
+        <v>0.77452830491154168</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.3">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="V22" s="26">
         <f>(R23-228195)/228195</f>
-        <v>1124.2351178833105</v>
+        <v>1074.5295795720367</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.3">
@@ -6985,7 +6985,7 @@
         <v>114</v>
       </c>
       <c r="R23" s="22">
-        <v>256773027.72538206</v>
+        <v>245430472.41044092</v>
       </c>
       <c r="S23" s="21" t="s">
         <v>128</v>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="V23" s="26">
         <f>(R24-10815)/10815</f>
-        <v>1180.9828008532231</v>
+        <v>1128.5437756346967</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.3">
@@ -7040,13 +7040,13 @@
         <v>115</v>
       </c>
       <c r="R24" s="22">
-        <v>12783143.991227608</v>
+        <v>12216015.933489244</v>
       </c>
       <c r="S24" s="21" t="s">
         <v>126</v>
       </c>
       <c r="T24" s="23">
-        <v>287036742.70045835</v>
+        <v>275127059.32777882</v>
       </c>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
@@ -7091,7 +7091,7 @@
         <v>242</v>
       </c>
       <c r="T25" s="34">
-        <v>556834253.55156243</v>
+        <v>533014886.80620354</v>
       </c>
       <c r="U25" s="5"/>
       <c r="V25" s="8"/>

--- a/Salidas.xlsx
+++ b/Salidas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acih0\Documents\CODIGO\tes2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86FCA34-9C00-4775-A2B5-3CE814481FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04047506-AE37-4C55-8342-6213CA7CD400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C4CE93A3-0861-4D2C-B953-37868A8DFB1C}"/>
   </bookViews>
@@ -21,17 +21,31 @@
     <sheet name="Exergoeconomico" sheetId="5" r:id="rId6"/>
     <sheet name="EXERGO" sheetId="4" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="262">
   <si>
     <t>T [°C]</t>
   </si>
@@ -802,17 +816,31 @@
   </si>
   <si>
     <t>XD reg [kW]</t>
+  </si>
+  <si>
+    <t>n_th_ORC [%]</t>
+  </si>
+  <si>
+    <t>n_th_BRAYTON [%]</t>
+  </si>
+  <si>
+    <t>LCOEn [USD/kWh]</t>
+  </si>
+  <si>
+    <t>c_el [USD/kWh_ex]</t>
+  </si>
+  <si>
+    <t>c_solar [USD/kWh_ex]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
-    <numFmt numFmtId="167" formatCode="0.000000000000000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -981,7 +1009,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -993,7 +1021,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1058,9 +1086,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1098,7 +1126,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1204,7 +1232,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1346,7 +1374,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1355,7 +1383,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959889D7-F248-4C3B-B68C-D47001A5CC86}">
   <dimension ref="B2:V38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="16"/>
     <col min="2" max="2" width="5.5546875" style="16" bestFit="1" customWidth="1"/>
@@ -1422,34 +1450,34 @@
         <v>500</v>
       </c>
       <c r="C3" s="18">
-        <v>80.075236196655112</v>
-      </c>
-      <c r="D3" s="16">
-        <v>6.0055119392946494</v>
+        <v>8.0526303683300007E-2</v>
+      </c>
+      <c r="D3" s="28">
+        <v>6.4565794259395549E-3</v>
       </c>
       <c r="E3" s="18">
-        <v>44.34017218770186</v>
+        <v>44.589942416003034</v>
       </c>
       <c r="F3" s="18">
-        <v>21.690058820630004</v>
+        <v>22.47486145686447</v>
       </c>
       <c r="G3" s="18">
-        <v>41.643616555414731</v>
+        <v>43.188213676973945</v>
       </c>
       <c r="H3" s="18">
-        <v>18.848834947929483</v>
+        <v>60.373080765557631</v>
       </c>
       <c r="I3" s="18">
-        <v>18.436180391626912</v>
+        <v>59.258731330142155</v>
       </c>
       <c r="J3" s="18">
-        <v>81.282485322238983</v>
+        <v>61.741337229740452</v>
       </c>
       <c r="K3" s="18">
-        <v>34.043287382392478</v>
+        <v>0.11765662653570212</v>
       </c>
       <c r="L3" s="16">
-        <v>304.23405873081123</v>
+        <v>1.0514599434966885</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -1457,34 +1485,34 @@
         <v>550</v>
       </c>
       <c r="C4" s="16">
-        <v>90.099760632232432</v>
-      </c>
-      <c r="D4" s="16">
-        <v>6.2578927853276172</v>
+        <v>9.0671008862792779E-2</v>
+      </c>
+      <c r="D4" s="28">
+        <v>6.829141015887932E-3</v>
       </c>
       <c r="E4" s="16">
-        <v>46.840775673371354</v>
+        <v>47.137754378239464</v>
       </c>
       <c r="F4" s="16">
-        <v>22.549497593185308</v>
+        <v>23.31995649946877</v>
       </c>
       <c r="G4" s="16">
-        <v>44.193547794198203</v>
+        <v>45.741485609600964</v>
       </c>
       <c r="H4" s="16">
-        <v>18.569282786768131</v>
+        <v>60.253488612946846</v>
       </c>
       <c r="I4" s="16">
-        <v>18.162225255928078</v>
+        <v>59.140653478648275</v>
       </c>
       <c r="J4" s="16">
-        <v>81.615235916991878</v>
+        <v>61.748903609487513</v>
       </c>
       <c r="K4" s="16">
-        <v>34.946784744116158</v>
+        <v>0.1241976761236304</v>
       </c>
       <c r="L4" s="16">
-        <v>312.30832800810623</v>
+        <v>1.1099152284444098</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -1492,34 +1520,34 @@
         <v>600</v>
       </c>
       <c r="C5" s="16">
-        <v>99.981173839880356</v>
-      </c>
-      <c r="D5" s="16">
-        <v>6.5130325416162291</v>
+        <v>0.10067279804398914</v>
+      </c>
+      <c r="D5" s="28">
+        <v>7.2046567457250098E-3</v>
       </c>
       <c r="E5" s="16">
-        <v>49.011736387407424</v>
+        <v>49.350777247491919</v>
       </c>
       <c r="F5" s="16">
-        <v>23.108230796268519</v>
+        <v>23.8622833259105</v>
       </c>
       <c r="G5" s="16">
-        <v>46.40527790743959</v>
+        <v>47.957650558765302</v>
       </c>
       <c r="H5" s="16">
-        <v>18.303596533693334</v>
+        <v>60.137926812244068</v>
       </c>
       <c r="I5" s="16">
-        <v>17.901905990987522</v>
+        <v>59.026407742274614</v>
       </c>
       <c r="J5" s="16">
-        <v>81.979569400405978</v>
+        <v>61.741121170525673</v>
       </c>
       <c r="K5" s="16">
-        <v>35.850258773202164</v>
+        <v>0.13077373160286609</v>
       </c>
       <c r="L5" s="16">
-        <v>320.38238876902079</v>
+        <v>1.1686833499367433</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -1527,34 +1555,34 @@
         <v>650</v>
       </c>
       <c r="C6" s="16">
-        <v>109.74867541385149</v>
-      </c>
-      <c r="D6" s="16">
-        <v>6.7708180854270879</v>
+        <v>0.11056078597785049</v>
+      </c>
+      <c r="D6" s="28">
+        <v>7.5829286494261215E-3</v>
       </c>
       <c r="E6" s="16">
-        <v>50.916680099072742</v>
+        <v>51.293449783410971</v>
       </c>
       <c r="F6" s="16">
-        <v>23.390875924002081</v>
+        <v>24.125923072132675</v>
       </c>
       <c r="G6" s="16">
-        <v>48.344297742800649</v>
+        <v>49.901758210142674</v>
       </c>
       <c r="H6" s="16">
-        <v>18.05106665890689</v>
+        <v>60.02605440500448</v>
       </c>
       <c r="I6" s="16">
-        <v>17.654523062467341</v>
+        <v>58.915670991729016</v>
       </c>
       <c r="J6" s="16">
-        <v>82.376196854637726</v>
+        <v>61.719233738654736</v>
       </c>
       <c r="K6" s="16">
-        <v>36.75418667446764</v>
+        <v>0.13738146670363119</v>
       </c>
       <c r="L6" s="16">
-        <v>328.46050564160743</v>
+        <v>1.2277345821559782</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -1562,34 +1590,34 @@
         <v>700</v>
       </c>
       <c r="C7" s="16">
-        <v>119.42386413622707</v>
-      </c>
-      <c r="D7" s="16">
-        <v>7.0310718568077251</v>
+        <v>0.12035645965773048</v>
+      </c>
+      <c r="D7" s="28">
+        <v>7.9636673783110984E-3</v>
       </c>
       <c r="E7" s="16">
-        <v>52.603052767831237</v>
+        <v>53.013836423037084</v>
       </c>
       <c r="F7" s="16">
-        <v>23.411885843230223</v>
+        <v>24.124848439648932</v>
       </c>
       <c r="G7" s="16">
-        <v>50.05943609903629</v>
+        <v>51.622321222319435</v>
       </c>
       <c r="H7" s="16">
-        <v>17.811094265141449</v>
+        <v>59.917602707954345</v>
       </c>
       <c r="I7" s="16">
-        <v>17.419485786127346</v>
+        <v>58.808190542626747</v>
       </c>
       <c r="J7" s="16">
-        <v>82.805678998061069</v>
+        <v>61.684414893591736</v>
       </c>
       <c r="K7" s="16">
-        <v>37.658813728603796</v>
+        <v>0.14401597106124334</v>
       </c>
       <c r="L7" s="16">
-        <v>336.54487062158535</v>
+        <v>1.2870250427308154</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -1597,34 +1625,34 @@
         <v>750</v>
       </c>
       <c r="C8" s="16">
-        <v>129.02311588889785</v>
-      </c>
-      <c r="D8" s="16">
-        <v>7.2935813459894892</v>
+        <v>0.13007607499990922</v>
+      </c>
+      <c r="D8" s="28">
+        <v>8.346540457000862E-3</v>
       </c>
       <c r="E8" s="16">
-        <v>54.107163791298788</v>
+        <v>54.548732968205762</v>
       </c>
       <c r="F8" s="16">
-        <v>23.178501568199025</v>
+        <v>23.865856194283836</v>
       </c>
       <c r="G8" s="16">
-        <v>51.588052318084642</v>
+        <v>53.156470352450683</v>
       </c>
       <c r="H8" s="16">
-        <v>17.583144089105325</v>
+        <v>59.812350100425348</v>
       </c>
       <c r="I8" s="16">
-        <v>17.196266196092065</v>
+        <v>58.703759417998292</v>
       </c>
       <c r="J8" s="16">
-        <v>83.268442408655289</v>
+        <v>61.637781904685539</v>
       </c>
       <c r="K8" s="16">
-        <v>38.564261866794908</v>
+        <v>0.15067160934350868</v>
       </c>
       <c r="L8" s="16">
-        <v>344.63657336926462</v>
+        <v>1.3465043704853092</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -1632,34 +1660,34 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C9" s="16">
-        <v>138.55913638137596</v>
-      </c>
-      <c r="D9" s="16">
-        <v>7.5581181135135624</v>
+        <v>0.13973221766874086</v>
+      </c>
+      <c r="D9" s="28">
+        <v>8.7311994008784366E-3</v>
       </c>
       <c r="E9" s="16">
-        <v>55.457402293257886</v>
+        <v>55.926920526231214</v>
       </c>
       <c r="F9" s="16">
-        <v>22.692635964018898</v>
+        <v>23.350437403404296</v>
       </c>
       <c r="G9" s="16">
-        <v>52.95934806076604</v>
+        <v>54.533240924600179</v>
       </c>
       <c r="H9" s="16">
-        <v>17.366718295380426</v>
+        <v>59.710107512679613</v>
       </c>
       <c r="I9" s="16">
-        <v>16.984373320199506</v>
+        <v>58.602202086203761</v>
       </c>
       <c r="J9" s="16">
-        <v>83.76479494046032</v>
+        <v>61.580400411172036</v>
       </c>
       <c r="K9" s="16">
-        <v>39.470595213279822</v>
+        <v>0.1573425008087958</v>
       </c>
       <c r="L9" s="16">
-        <v>352.73618694262348</v>
+        <v>1.4061200110972298</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
@@ -1667,34 +1695,34 @@
         <v>850.00000000000011</v>
       </c>
       <c r="C10" s="16">
-        <v>148.04185834627998</v>
-      </c>
-      <c r="D10" s="16">
-        <v>7.8244489884889461</v>
+        <v>0.14933470529666967</v>
+      </c>
+      <c r="D10" s="28">
+        <v>9.1172959388786771E-3</v>
       </c>
       <c r="E10" s="16">
-        <v>56.676345196994049</v>
+        <v>57.171298724771077</v>
       </c>
       <c r="F10" s="16">
-        <v>21.952112320563913</v>
+        <v>22.576007444576813</v>
       </c>
       <c r="G10" s="16">
-        <v>54.19653780739376</v>
+        <v>55.775727102446339</v>
       </c>
       <c r="H10" s="16">
-        <v>17.161343126444446</v>
+        <v>59.610709482604229</v>
       </c>
       <c r="I10" s="16">
-        <v>16.783340068289903</v>
+        <v>58.503365660619181</v>
       </c>
       <c r="J10" s="16">
-        <v>84.294937842312663</v>
+        <v>61.513285424167464</v>
       </c>
       <c r="K10" s="16">
-        <v>40.377855361703119</v>
+        <v>0.16402280329876123</v>
       </c>
       <c r="L10" s="16">
-        <v>360.84408305086771</v>
+        <v>1.4658197550509493</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.3">
@@ -1702,34 +1730,34 @@
         <v>900.00000000000011</v>
       </c>
       <c r="C11" s="19">
-        <v>157.47922554852343</v>
+        <v>0.15889137447026183</v>
       </c>
       <c r="D11" s="35">
-        <v>8.0923433209245097</v>
+        <v>9.5044922426629139E-3</v>
       </c>
       <c r="E11" s="19">
-        <v>57.782231137481588</v>
+        <v>58.300376404657108</v>
       </c>
       <c r="F11" s="19">
-        <v>20.951528074973265</v>
+        <v>21.536763391264525</v>
       </c>
       <c r="G11" s="19">
-        <v>55.318367601752492</v>
+        <v>56.902588178959753</v>
       </c>
       <c r="H11" s="19">
-        <v>16.9665618977976</v>
+        <v>59.514008305492474</v>
       </c>
       <c r="I11" s="19">
-        <v>16.592716345658207</v>
+        <v>58.407114137429971</v>
       </c>
       <c r="J11" s="19">
-        <v>84.858977086928178</v>
+        <v>61.437400772307171</v>
       </c>
       <c r="K11" s="19">
-        <v>41.286081792389979</v>
+        <v>0.17070688968013925</v>
       </c>
       <c r="L11" s="19">
-        <v>368.96061451713769</v>
+        <v>1.5255533144417424</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.3">
@@ -1737,34 +1765,34 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C12" s="16">
-        <v>138.55913638137596</v>
+        <v>0.13973221766874086</v>
       </c>
       <c r="D12" s="16">
-        <v>7.5581181135135624</v>
+        <v>8.7311994008784366E-3</v>
       </c>
       <c r="E12" s="16">
-        <v>55.457402293257886</v>
+        <v>55.926920526231214</v>
       </c>
       <c r="F12" s="16">
-        <v>22.692635964018898</v>
+        <v>23.350437403404296</v>
       </c>
       <c r="G12" s="16">
-        <v>52.95934806076604</v>
+        <v>54.533240924600179</v>
       </c>
       <c r="H12" s="16">
-        <v>17.366718295380426</v>
+        <v>59.710107512679613</v>
       </c>
       <c r="I12" s="16">
-        <v>16.984373320199506</v>
+        <v>58.602202086203761</v>
       </c>
       <c r="J12" s="16">
-        <v>83.76479494046032</v>
+        <v>61.580400411172036</v>
       </c>
       <c r="K12" s="16">
-        <v>39.470595213279822</v>
+        <v>0.1573425008087958</v>
       </c>
       <c r="L12" s="16">
-        <v>352.73618694262348</v>
+        <v>1.4061200110972298</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -1837,64 +1865,64 @@
         <v>500</v>
       </c>
       <c r="C16" s="16">
-        <v>2948.5614292537944</v>
+        <v>2.9485614292537941</v>
       </c>
       <c r="D16" s="16">
-        <v>1356.4262301173844</v>
+        <v>1.3564262301173839</v>
       </c>
       <c r="E16" s="16">
-        <v>1511.9146157877444</v>
+        <v>1.5119146157877403</v>
       </c>
       <c r="F16" s="16">
-        <v>2771.3026251072883</v>
+        <v>2.7713026251072881</v>
       </c>
       <c r="G16" s="16">
-        <v>898.27603128406031</v>
+        <v>1.0558993918270143</v>
       </c>
       <c r="H16" s="16">
-        <v>340.1774796640384</v>
+        <v>0.34017747966403838</v>
       </c>
       <c r="I16" s="16">
-        <v>3028.1716564914286</v>
+        <v>3.0281716564914243</v>
       </c>
       <c r="J16" s="16">
-        <v>11794.615416517447</v>
+        <v>11.794615416517447</v>
       </c>
       <c r="K16" s="16">
-        <v>138639.03314567471</v>
+        <v>138.63903314567469</v>
       </c>
       <c r="L16" s="16">
-        <v>89329.858804423799</v>
+        <v>89.329858804423736</v>
       </c>
       <c r="M16" s="16">
-        <v>419.54531737997803</v>
+        <v>2.6191366593659655</v>
       </c>
       <c r="N16" s="16">
-        <v>255.87107705551512</v>
+        <v>2.22691604780809</v>
       </c>
       <c r="O16" s="16">
-        <v>4968.0468857744854</v>
+        <v>4.1204925273506943</v>
       </c>
       <c r="P16" s="16">
-        <v>2234.5014182525947</v>
+        <v>2.2683754402637701</v>
       </c>
       <c r="Q16" s="16">
-        <v>2.3471414600463723</v>
+        <v>4.5088010500839229E-2</v>
       </c>
       <c r="R16" s="16">
-        <v>478.40909329018001</v>
+        <v>0.49737118649536521</v>
       </c>
       <c r="S16" s="16">
-        <v>5313.959773625852</v>
+        <v>1.5153815141914335</v>
       </c>
       <c r="T16" s="16">
-        <v>346597.58286418673</v>
+        <v>346.59758286418668</v>
       </c>
       <c r="U16" s="16">
-        <v>4894.5992563087448</v>
+        <v>2.613943596167863</v>
       </c>
       <c r="V16" s="16">
-        <v>229.65614489043224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -1902,64 +1930,64 @@
         <v>550</v>
       </c>
       <c r="C17" s="16">
-        <v>2978.2296698241607</v>
+        <v>2.9782296698241626</v>
       </c>
       <c r="D17" s="16">
-        <v>1318.6805418472477</v>
+        <v>1.3186805418472505</v>
       </c>
       <c r="E17" s="16">
-        <v>1521.902528703846</v>
+        <v>1.521902528703853</v>
       </c>
       <c r="F17" s="16">
-        <v>2783.7767920301558</v>
+        <v>2.7837767920301411</v>
       </c>
       <c r="G17" s="16">
-        <v>929.90885718412142</v>
+        <v>1.107829801583406</v>
       </c>
       <c r="H17" s="16">
-        <v>805.40884684346383</v>
+        <v>0.80540884684346381</v>
       </c>
       <c r="I17" s="16">
-        <v>3649.5425807604643</v>
+        <v>3.6495425807604551</v>
       </c>
       <c r="J17" s="16">
-        <v>15916.416778681467</v>
+        <v>15.916416778681471</v>
       </c>
       <c r="K17" s="16">
-        <v>150741.7278546278</v>
+        <v>150.74172785462781</v>
       </c>
       <c r="L17" s="16">
-        <v>91657.429244218394</v>
+        <v>91.657429244218392</v>
       </c>
       <c r="M17" s="16">
-        <v>424.30028424486284</v>
+        <v>2.5764946879570898</v>
       </c>
       <c r="N17" s="16">
-        <v>259.97082824934603</v>
+        <v>2.1433678536465721</v>
       </c>
       <c r="O17" s="16">
-        <v>5250.598053142633</v>
+        <v>4.422196598899367</v>
       </c>
       <c r="P17" s="16">
-        <v>2317.2407129887442</v>
+        <v>2.4453950272512031</v>
       </c>
       <c r="Q17" s="16">
-        <v>2.4296557049723959</v>
+        <v>4.7120742623562424E-2</v>
       </c>
       <c r="R17" s="16">
-        <v>496.59664099516397</v>
+        <v>0.53311172189374645</v>
       </c>
       <c r="S17" s="16">
-        <v>5434.8419212917788</v>
+        <v>1.5319792762479894</v>
       </c>
       <c r="T17" s="16">
-        <v>376854.31963656942</v>
+        <v>376.85431963656947</v>
       </c>
       <c r="U17" s="16">
-        <v>5117.5161451365711</v>
+        <v>2.7728772231402958</v>
       </c>
       <c r="V17" s="16">
-        <v>263.82115663647943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -1967,64 +1995,64 @@
         <v>600</v>
       </c>
       <c r="C18" s="16">
-        <v>3007.2656005696876</v>
+        <v>3.0072656005696845</v>
       </c>
       <c r="D18" s="16">
-        <v>1281.507723530028</v>
+        <v>1.281507723530027</v>
       </c>
       <c r="E18" s="16">
-        <v>1528.99071995233</v>
+        <v>1.5289907199523296</v>
       </c>
       <c r="F18" s="16">
-        <v>2792.4530756981671</v>
+        <v>2.7924530756981696</v>
       </c>
       <c r="G18" s="16">
-        <v>961.45439022993946</v>
+        <v>1.1593508930651124</v>
       </c>
       <c r="H18" s="16">
-        <v>1320.1571327557904</v>
+        <v>1.3201571327557904</v>
       </c>
       <c r="I18" s="16">
-        <v>4297.0000918122378</v>
+        <v>4.2970000918122384</v>
       </c>
       <c r="J18" s="16">
-        <v>21237.887994432185</v>
+        <v>21.237887994432182</v>
       </c>
       <c r="K18" s="16">
-        <v>163810.75957825704</v>
+        <v>163.81075957825703</v>
       </c>
       <c r="L18" s="16">
-        <v>94289.610392787596</v>
+        <v>94.28961039278758</v>
       </c>
       <c r="M18" s="16">
-        <v>429.56603158351845</v>
+        <v>2.5337431600716043</v>
       </c>
       <c r="N18" s="16">
-        <v>264.54602871728474</v>
+        <v>2.0631505655030526</v>
       </c>
       <c r="O18" s="16">
-        <v>5541.2107967023103</v>
+        <v>4.7319989180319988</v>
       </c>
       <c r="P18" s="16">
-        <v>2400.2346993936662</v>
+        <v>2.6329592517508069</v>
       </c>
       <c r="Q18" s="16">
-        <v>2.5119424181456744</v>
+        <v>4.9126762554551132E-2</v>
       </c>
       <c r="R18" s="16">
-        <v>514.86231045387774</v>
+        <v>0.57002155542473976</v>
       </c>
       <c r="S18" s="16">
-        <v>5562.4758955544876</v>
+        <v>1.5452754473960513</v>
       </c>
       <c r="T18" s="16">
-        <v>409526.89894564264</v>
+        <v>409.52689894564264</v>
       </c>
       <c r="U18" s="16">
-        <v>5343.1956951397678</v>
+        <v>2.9336195314518481</v>
       </c>
       <c r="V18" s="16">
-        <v>301.42798128774854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -2032,64 +2060,64 @@
         <v>650</v>
       </c>
       <c r="C19" s="16">
-        <v>3035.689357492201</v>
+        <v>3.0356893574921995</v>
       </c>
       <c r="D19" s="16">
-        <v>1244.8910840925203</v>
+        <v>1.2448910840925236</v>
       </c>
       <c r="E19" s="16">
-        <v>1533.9874970301762</v>
+        <v>1.5339874970301752</v>
       </c>
       <c r="F19" s="16">
-        <v>2798.4221022535266</v>
+        <v>2.7984221022535349</v>
       </c>
       <c r="G19" s="16">
-        <v>992.88992097665925</v>
+        <v>1.2104286334423342</v>
       </c>
       <c r="H19" s="16">
-        <v>1858.4739014316001</v>
+        <v>1.8584739014314837</v>
       </c>
       <c r="I19" s="16">
-        <v>4970.4374229533005</v>
+        <v>4.9704374229532986</v>
       </c>
       <c r="J19" s="16">
-        <v>28086.836717508984</v>
+        <v>28.08683671750898</v>
       </c>
       <c r="K19" s="16">
-        <v>178143.89492497977</v>
+        <v>178.14389492497978</v>
       </c>
       <c r="L19" s="16">
-        <v>97339.721439540212</v>
+        <v>97.339721439540327</v>
       </c>
       <c r="M19" s="16">
-        <v>435.35791883841307</v>
+        <v>2.4909917652447429</v>
       </c>
       <c r="N19" s="16">
-        <v>269.61547467781907</v>
+        <v>1.9861373826062056</v>
       </c>
       <c r="O19" s="16">
-        <v>5839.8397993231993</v>
+        <v>5.049709890044169</v>
       </c>
       <c r="P19" s="16">
-        <v>2483.4516812710835</v>
+        <v>2.831678052314782</v>
       </c>
       <c r="Q19" s="16">
-        <v>2.5939432755638863</v>
+        <v>5.1105442380682063E-2</v>
       </c>
       <c r="R19" s="16">
-        <v>533.19731150033078</v>
+        <v>0.60812327302000813</v>
       </c>
       <c r="S19" s="16">
-        <v>5697.2226437316767</v>
+        <v>1.5554402347445702</v>
       </c>
       <c r="T19" s="16">
-        <v>445359.73731244943</v>
+        <v>445.35973731244945</v>
       </c>
       <c r="U19" s="16">
-        <v>5571.5094381309173</v>
+        <v>3.0960810402037904</v>
       </c>
       <c r="V19" s="16">
-        <v>342.66613614191135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -2097,64 +2125,64 @@
         <v>700</v>
       </c>
       <c r="C20" s="16">
-        <v>3063.5131841675043</v>
+        <v>3.063513184167503</v>
       </c>
       <c r="D20" s="16">
-        <v>1208.8239449501671</v>
+        <v>1.208823944950167</v>
       </c>
       <c r="E20" s="16">
-        <v>1537.4467368248106</v>
+        <v>1.5374467368248153</v>
       </c>
       <c r="F20" s="16">
-        <v>2802.440878422588</v>
+        <v>2.8024408784225816</v>
       </c>
       <c r="G20" s="16">
-        <v>1024.1858203605748</v>
+        <v>1.2610208717953011</v>
       </c>
       <c r="H20" s="16">
-        <v>2403.1475528596202</v>
+        <v>2.40314755285962</v>
       </c>
       <c r="I20" s="16">
-        <v>5669.5500958230568</v>
+        <v>5.6695500958230554</v>
       </c>
       <c r="J20" s="16">
-        <v>36894.255484164853</v>
+        <v>36.894255484164844</v>
       </c>
       <c r="K20" s="16">
-        <v>194120.04412755879</v>
+        <v>194.12004412755883</v>
       </c>
       <c r="L20" s="16">
-        <v>100939.4296158151</v>
+        <v>100.93942961581514</v>
       </c>
       <c r="M20" s="16">
-        <v>441.68980993911111</v>
+        <v>2.448349687554257</v>
       </c>
       <c r="N20" s="16">
-        <v>275.19740001542647</v>
+        <v>1.9122256047370421</v>
       </c>
       <c r="O20" s="16">
-        <v>6146.3542966344639</v>
+        <v>5.3750504559566545</v>
       </c>
       <c r="P20" s="16">
-        <v>2566.841751524832</v>
+        <v>3.0421077774372409</v>
       </c>
       <c r="Q20" s="16">
-        <v>2.6755818790198247</v>
+        <v>5.3055735422867997E-2</v>
       </c>
       <c r="R20" s="16">
-        <v>551.58861711889756</v>
+        <v>0.64743022246408999</v>
       </c>
       <c r="S20" s="16">
-        <v>5839.4015948747719</v>
+        <v>1.5626381639506877</v>
       </c>
       <c r="T20" s="16">
-        <v>485300.110318897</v>
+        <v>485.30011031889705</v>
       </c>
       <c r="U20" s="16">
-        <v>5802.2720393783475</v>
+        <v>3.2601326474556238</v>
       </c>
       <c r="V20" s="16">
-        <v>387.71368616097209</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -2162,64 +2190,64 @@
         <v>750</v>
       </c>
       <c r="C21" s="16">
-        <v>3090.7455465127828</v>
+        <v>3.0907455465127787</v>
       </c>
       <c r="D21" s="16">
-        <v>1173.3045407099946</v>
+        <v>1.1733045407099962</v>
       </c>
       <c r="E21" s="16">
-        <v>1539.7884766306952</v>
+        <v>1.5397884766306962</v>
       </c>
       <c r="F21" s="16">
-        <v>2805.018382007137</v>
+        <v>2.8050183820071397</v>
       </c>
       <c r="G21" s="16">
-        <v>1055.3088601388242</v>
+        <v>1.3110809858743577</v>
       </c>
       <c r="H21" s="16">
-        <v>2942.6310690947575</v>
+        <v>2.9426310690947575</v>
       </c>
       <c r="I21" s="16">
-        <v>6393.8950186234715</v>
+        <v>6.3938950186234722</v>
       </c>
       <c r="J21" s="16">
-        <v>48238.346125543401</v>
+        <v>48.238346125543394</v>
       </c>
       <c r="K21" s="16">
-        <v>212238.23419605001</v>
+        <v>212.23823419605003</v>
       </c>
       <c r="L21" s="16">
-        <v>105253.56004225269</v>
+        <v>105.25356004225264</v>
       </c>
       <c r="M21" s="16">
-        <v>448.57424140040712</v>
+        <v>2.4059212449514122</v>
       </c>
       <c r="N21" s="16">
-        <v>281.30959256471084</v>
+        <v>1.8413239464199036</v>
       </c>
       <c r="O21" s="16">
-        <v>6460.5673761155404</v>
+        <v>5.7076844573422223</v>
       </c>
       <c r="P21" s="16">
-        <v>2650.3468586374765</v>
+        <v>3.2647615339510341</v>
       </c>
       <c r="Q21" s="16">
-        <v>2.7567742375495983</v>
+        <v>5.4976442991773351E-2</v>
       </c>
       <c r="R21" s="16">
-        <v>570.02117006884941</v>
+        <v>0.68794990297823333</v>
       </c>
       <c r="S21" s="16">
-        <v>5989.2997160576833</v>
+        <v>1.5670318376931678</v>
       </c>
       <c r="T21" s="16">
-        <v>530595.58549012512</v>
+        <v>530.59558549012502</v>
       </c>
       <c r="U21" s="16">
-        <v>6035.2672419376922</v>
+        <v>3.4256258281326053</v>
       </c>
       <c r="V21" s="16">
-        <v>436.73851125085787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -2227,64 +2255,64 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C22" s="16">
-        <v>3117.3934843303709</v>
+        <v>3.1173934843303797</v>
       </c>
       <c r="D22" s="16">
-        <v>1138.33305276341</v>
+        <v>1.1383330527634061</v>
       </c>
       <c r="E22" s="16">
-        <v>1541.2694860114752</v>
+        <v>1.5412694860114715</v>
       </c>
       <c r="F22" s="16">
-        <v>2806.532548235491</v>
+        <v>2.8065325482354964</v>
       </c>
       <c r="G22" s="16">
-        <v>1086.2272208333268</v>
+        <v>1.3605627687494435</v>
       </c>
       <c r="H22" s="16">
-        <v>3469.1288051136653</v>
+        <v>3.4691288051130833</v>
       </c>
       <c r="I22" s="16">
-        <v>7142.9330882120803</v>
+        <v>7.1429330882120778</v>
       </c>
       <c r="J22" s="16">
-        <v>62913.606293226985</v>
+        <v>62.913606293226934</v>
       </c>
       <c r="K22" s="16">
-        <v>233177.09736516071</v>
+        <v>233.17709736516051</v>
       </c>
       <c r="L22" s="16">
-        <v>110500.43569183591</v>
+        <v>110.50043569183623</v>
       </c>
       <c r="M22" s="16">
-        <v>456.02259338253077</v>
+        <v>2.3638032842787435</v>
       </c>
       <c r="N22" s="16">
-        <v>287.96951585660918</v>
+        <v>1.7733455047729523</v>
       </c>
       <c r="O22" s="16">
-        <v>6782.2557987781765</v>
+        <v>6.0472409675346555</v>
       </c>
       <c r="P22" s="16">
-        <v>2733.9070991328199</v>
+        <v>3.5001169170646191</v>
       </c>
       <c r="Q22" s="16">
-        <v>2.8374352800170817</v>
+        <v>5.6866372819326445E-2</v>
       </c>
       <c r="R22" s="16">
-        <v>588.47927127187018</v>
+        <v>0.72968630976222748</v>
       </c>
       <c r="S22" s="16">
-        <v>6147.1777320041247</v>
+        <v>1.5687831328618429</v>
       </c>
       <c r="T22" s="16">
-        <v>582942.74341290176</v>
+        <v>582.94274341290134</v>
       </c>
       <c r="U22" s="16">
-        <v>6270.2647481636777</v>
+        <v>3.5924040888912341</v>
       </c>
       <c r="V22" s="16">
-        <v>489.8963917659762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.3">
@@ -2292,64 +2320,64 @@
         <v>850.00000000000011</v>
       </c>
       <c r="C23" s="16">
-        <v>3143.463834922105</v>
+        <v>3.1434638349221058</v>
       </c>
       <c r="D23" s="16">
-        <v>1103.9100202102625</v>
+        <v>1.1039100202102636</v>
       </c>
       <c r="E23" s="16">
-        <v>1542.1068241741657</v>
+        <v>1.5421068241741742</v>
       </c>
       <c r="F23" s="16">
-        <v>2807.2526540154367</v>
+        <v>2.8072526540154357</v>
       </c>
       <c r="G23" s="16">
-        <v>1116.9084826127057</v>
+        <v>1.4094226215160197</v>
       </c>
       <c r="H23" s="16">
-        <v>3977.3664473134559</v>
+        <v>3.9773664473136887</v>
       </c>
       <c r="I23" s="16">
-        <v>7916.0573066213656</v>
+        <v>7.9160573066213615</v>
       </c>
       <c r="J23" s="16">
-        <v>82043.236087615151</v>
+        <v>82.043236087615213</v>
       </c>
       <c r="K23" s="16">
-        <v>257890.4091378501</v>
+        <v>257.89040913785033</v>
       </c>
       <c r="L23" s="16">
-        <v>116982.91458223342</v>
+        <v>116.98291458223341</v>
       </c>
       <c r="M23" s="16">
-        <v>464.04521749726689</v>
+        <v>2.3220839519793026</v>
       </c>
       <c r="N23" s="16">
-        <v>295.19439221965786</v>
+        <v>1.708204350308886</v>
       </c>
       <c r="O23" s="16">
-        <v>7111.1725065719374</v>
+        <v>6.3933284684315037</v>
       </c>
       <c r="P23" s="16">
-        <v>2817.464265935208</v>
+        <v>3.7486202181996262</v>
       </c>
       <c r="Q23" s="16">
-        <v>2.9174825238960547</v>
+        <v>5.8724422672312072E-2</v>
       </c>
       <c r="R23" s="16">
-        <v>606.94737559374551</v>
+        <v>0.77264132938901409</v>
       </c>
       <c r="S23" s="16">
-        <v>6313.2739658952842</v>
+        <v>1.5680531510701445</v>
       </c>
       <c r="T23" s="16">
-        <v>644726.02284462529</v>
+        <v>644.72602284462573</v>
       </c>
       <c r="U23" s="16">
-        <v>6507.030266974225</v>
+        <v>3.7603099147127264</v>
       </c>
       <c r="V23" s="16">
-        <v>547.33450681593331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.3">
@@ -2357,64 +2385,64 @@
         <v>900.00000000000011</v>
       </c>
       <c r="C24" s="19">
-        <v>3168.9638838626593</v>
+        <v>3.1689638838626562</v>
       </c>
       <c r="D24" s="19">
-        <v>1070.0354556951188</v>
+        <v>1.070035455695117</v>
       </c>
       <c r="E24" s="19">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F24" s="19">
-        <v>2807.373846715212</v>
+        <v>2.8073738467151998</v>
       </c>
       <c r="G24" s="19">
-        <v>1147.3225668630778</v>
+        <v>1.4576207961410272</v>
       </c>
       <c r="H24" s="19">
-        <v>4463.8000501786591</v>
+        <v>4.4638000501786594</v>
       </c>
       <c r="I24" s="19">
-        <v>8712.6139107183735</v>
+        <v>8.7126139107183764</v>
       </c>
       <c r="J24" s="19">
-        <v>107270.29753288905</v>
+        <v>107.27029753288905</v>
       </c>
       <c r="K24" s="19">
-        <v>287768.98644095648</v>
+        <v>287.7689864409565</v>
       </c>
       <c r="L24" s="19">
-        <v>125140.03470369184</v>
+        <v>125.14003470369184</v>
       </c>
       <c r="M24" s="19">
-        <v>472.65155422893099</v>
+        <v>2.2808421653316127</v>
       </c>
       <c r="N24" s="19">
-        <v>303.00127490721547</v>
+        <v>1.6458138969378528</v>
       </c>
       <c r="O24" s="19">
-        <v>7447.0553439995365</v>
+        <v>6.7455449820073499</v>
       </c>
       <c r="P24" s="19">
-        <v>2900.9640004602402</v>
+        <v>4.010689351783931</v>
       </c>
       <c r="Q24" s="19">
-        <v>2.9968382791884323</v>
+        <v>6.0549626026528983E-2</v>
       </c>
       <c r="R24" s="19">
-        <v>625.4105840642319</v>
+        <v>0.81681569164802381</v>
       </c>
       <c r="S24" s="19">
-        <v>6487.8072322372454</v>
+        <v>1.565001589193616</v>
       </c>
       <c r="T24" s="19">
-        <v>719422.46610239113</v>
+        <v>719.42246610239113</v>
       </c>
       <c r="U24" s="19">
-        <v>6745.3321001464137</v>
+        <v>3.9291892339566523</v>
       </c>
       <c r="V24" s="19">
-        <v>609.18953047120942</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.3">
@@ -2422,64 +2450,64 @@
         <v>800.00000000000011</v>
       </c>
       <c r="C25" s="16">
-        <v>3117.3934843303709</v>
+        <v>3.1173934843303797</v>
       </c>
       <c r="D25" s="16">
-        <v>1138.33305276341</v>
+        <v>1.1383330527634061</v>
       </c>
       <c r="E25" s="16">
-        <v>1541.2694860114752</v>
+        <v>1.5412694860114715</v>
       </c>
       <c r="F25" s="16">
-        <v>2806.532548235491</v>
+        <v>2.8065325482354964</v>
       </c>
       <c r="G25" s="16">
-        <v>1086.2272208333268</v>
+        <v>1.3605627687494435</v>
       </c>
       <c r="H25" s="16">
-        <v>3469.1288051136653</v>
+        <v>3.4691288051130833</v>
       </c>
       <c r="I25" s="16">
-        <v>7142.9330882120803</v>
+        <v>7.1429330882120778</v>
       </c>
       <c r="J25" s="16">
-        <v>62913.606293226985</v>
+        <v>62.913606293226934</v>
       </c>
       <c r="K25" s="16">
-        <v>233177.09736516071</v>
+        <v>233.17709736516051</v>
       </c>
       <c r="L25" s="16">
-        <v>110500.43569183591</v>
+        <v>110.50043569183623</v>
       </c>
       <c r="M25" s="16">
-        <v>456.02259338253077</v>
+        <v>2.3638032842787435</v>
       </c>
       <c r="N25" s="16">
-        <v>287.96951585660918</v>
+        <v>1.7733455047729523</v>
       </c>
       <c r="O25" s="16">
-        <v>6782.2557987781765</v>
+        <v>6.0472409675346555</v>
       </c>
       <c r="P25" s="16">
-        <v>2733.9070991328199</v>
+        <v>3.5001169170646191</v>
       </c>
       <c r="Q25" s="16">
-        <v>2.8374352800170817</v>
+        <v>5.6866372819326445E-2</v>
       </c>
       <c r="R25" s="16">
-        <v>588.47927127187018</v>
+        <v>0.72968630976222748</v>
       </c>
       <c r="S25" s="16">
-        <v>6147.1777320041247</v>
+        <v>1.5687831328618429</v>
       </c>
       <c r="T25" s="16">
-        <v>582942.74341290176</v>
+        <v>582.94274341290134</v>
       </c>
       <c r="U25" s="16">
-        <v>6270.2647481636777</v>
+        <v>3.5924040888912341</v>
       </c>
       <c r="V25" s="16">
-        <v>489.8963917659762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -2516,40 +2544,52 @@
       <c r="L28" s="17" t="s">
         <v>21</v>
       </c>
+      <c r="M28" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="16">
         <v>500</v>
       </c>
       <c r="C29" s="16">
-        <v>0.78242212526834742</v>
+        <v>0.77520063341668211</v>
       </c>
       <c r="D29" s="16">
-        <v>3.6072844787500737</v>
+        <v>3.4491898199439781</v>
       </c>
       <c r="E29" s="16">
-        <v>0.27721683884119408</v>
+        <v>0.28992315650990819</v>
       </c>
       <c r="F29" s="16">
-        <v>1.2725895991014955E-2</v>
+        <v>1.1501027911638782E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.74329834926752969</v>
+        <v>0.67616332983692173</v>
       </c>
       <c r="H29" s="16">
-        <v>21.757787473165259</v>
+        <v>22.479936658331788</v>
       </c>
       <c r="I29" s="27">
-        <v>0.55495748925804933</v>
+        <v>0.58163665659906605</v>
       </c>
       <c r="J29" s="27">
-        <v>2.7011621800593781</v>
+        <v>1.0205969579864951</v>
       </c>
       <c r="K29" s="28">
-        <v>0.44440626816651491</v>
+        <v>0.5513087846648963</v>
       </c>
       <c r="L29" s="16">
-        <v>271185.61739746912</v>
+        <v>268.68266577700848</v>
+      </c>
+      <c r="M29" s="16">
+        <v>10.995477783944521</v>
+      </c>
+      <c r="N29" s="16">
+        <v>41.014731688098969</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -2557,34 +2597,40 @@
         <v>550</v>
       </c>
       <c r="C30" s="16">
-        <v>0.77379109842151894</v>
+        <v>0.76675116275552069</v>
       </c>
       <c r="D30" s="16">
-        <v>3.4315225659633617</v>
+        <v>3.2879613766560301</v>
       </c>
       <c r="E30" s="16">
-        <v>0.29141583095469492</v>
+        <v>0.30413982569863229</v>
       </c>
       <c r="F30" s="16">
-        <v>1.256705583287248E-2</v>
+        <v>1.1374816623091307E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.73459232019974063</v>
+        <v>0.66924568911163462</v>
       </c>
       <c r="H30" s="16">
-        <v>22.620890157848095</v>
+        <v>23.324883724447943</v>
       </c>
       <c r="I30" s="27">
-        <v>0.49822687482478595</v>
+        <v>0.52129913820588714</v>
       </c>
       <c r="J30" s="27">
-        <v>2.4910433500341069</v>
+        <v>0.92836567207474396</v>
       </c>
       <c r="K30" s="28">
-        <v>0.39883087493488928</v>
+        <v>0.49553507400335811</v>
       </c>
       <c r="L30" s="16">
-        <v>291606.51793647528</v>
+        <v>288.95348777078027</v>
+      </c>
+      <c r="M30" s="16">
+        <v>10.988368490216915</v>
+      </c>
+      <c r="N30" s="16">
+        <v>43.587442367170809</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -2592,34 +2638,40 @@
         <v>600</v>
       </c>
       <c r="C31" s="16">
-        <v>0.76816856453119997</v>
+        <v>0.76132942475270404</v>
       </c>
       <c r="D31" s="16">
-        <v>3.3242205831492848</v>
+        <v>3.1905137255914902</v>
       </c>
       <c r="E31" s="16">
-        <v>0.30082239580281539</v>
+        <v>0.3134291484091985</v>
       </c>
       <c r="F31" s="16">
-        <v>1.2460487945338345E-2</v>
+        <v>1.127939281035162E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.72875133428399475</v>
+        <v>0.66401550993537228</v>
       </c>
       <c r="H31" s="16">
-        <v>23.183143546879993</v>
+        <v>23.867057524729596</v>
       </c>
       <c r="I31" s="27">
-        <v>0.45446714965679885</v>
+        <v>0.47464802507936671</v>
       </c>
       <c r="J31" s="27">
-        <v>2.3250397584419025</v>
+        <v>0.8566856863956146</v>
       </c>
       <c r="K31" s="28">
-        <v>0.36261809597367145</v>
+        <v>0.45214671860120231</v>
       </c>
       <c r="L31" s="16">
-        <v>314585.69009998813</v>
+        <v>311.78487839504487</v>
+      </c>
+      <c r="M31" s="16">
+        <v>10.979868872004122</v>
+      </c>
+      <c r="N31" s="16">
+        <v>45.818984974791263</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -2627,244 +2679,286 @@
         <v>650</v>
       </c>
       <c r="C32" s="16">
-        <v>0.76530948809116828</v>
+        <v>0.75869465030744332</v>
       </c>
       <c r="D32" s="16">
-        <v>3.271829112247401</v>
+        <v>3.1447279676680844</v>
       </c>
       <c r="E32" s="16">
-        <v>0.30563943460760568</v>
+        <v>0.31799252917305015</v>
       </c>
       <c r="F32" s="16">
-        <v>1.2396637952335364E-2</v>
+        <v>1.1208338766796713E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.72525171616750128</v>
+        <v>0.66012103780812792</v>
       </c>
       <c r="H32" s="16">
-        <v>23.469051190883171</v>
+        <v>24.130534969255667</v>
       </c>
       <c r="I32" s="27">
-        <v>0.41990490870863312</v>
+        <v>0.43813979781718343</v>
       </c>
       <c r="J32" s="27">
-        <v>2.1903670853712032</v>
+        <v>0.80048312975010827</v>
       </c>
       <c r="K32" s="28">
-        <v>0.33308227081863279</v>
+        <v>0.41807194091093991</v>
       </c>
       <c r="L32" s="16">
-        <v>340838.03257900785</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+        <v>337.89205016128363</v>
+      </c>
+      <c r="M32" s="16">
+        <v>10.970046366718318</v>
+      </c>
+      <c r="N32" s="16">
+        <v>47.775434182758048</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B33" s="16">
         <v>700</v>
       </c>
       <c r="C33" s="16">
-        <v>0.76507062462510711</v>
+        <v>0.75870714833633734</v>
       </c>
       <c r="D33" s="16">
-        <v>3.2678726940159533</v>
+        <v>3.1449198540431458</v>
       </c>
       <c r="E33" s="16">
-        <v>0.30600947271635609</v>
+        <v>0.31797312695087865</v>
       </c>
       <c r="F33" s="16">
-        <v>1.2373819823211687E-2</v>
+        <v>1.115141134071782E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.72400105451023267</v>
+        <v>0.65700084558474381</v>
       </c>
       <c r="H33" s="16">
-        <v>23.49293753748929</v>
+        <v>24.129285166366266</v>
       </c>
       <c r="I33" s="27">
-        <v>0.39220717719614501</v>
+        <v>0.40886311779381496</v>
       </c>
       <c r="J33" s="27">
-        <v>2.0787757296949785</v>
+        <v>0.75535114796615432</v>
       </c>
       <c r="K33" s="28">
-        <v>0.30848872359028245</v>
+        <v>0.39065886215107742</v>
       </c>
       <c r="L33" s="16">
-        <v>371288.85853231192</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+        <v>368.20066278736033</v>
+      </c>
+      <c r="M33" s="16">
+        <v>10.958961494742761</v>
+      </c>
+      <c r="N33" s="16">
+        <v>49.506051623435397</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B34" s="16">
         <v>750</v>
       </c>
       <c r="C34" s="16">
-        <v>0.76738100799023989</v>
+        <v>0.76129898292430753</v>
       </c>
       <c r="D34" s="16">
-        <v>3.3107446818006947</v>
+        <v>3.1899085317821028</v>
       </c>
       <c r="E34" s="16">
-        <v>0.30204684930766268</v>
+        <v>0.31348861261590188</v>
       </c>
       <c r="F34" s="16">
-        <v>1.2399204794170266E-2</v>
+        <v>1.1103769648194128E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.72539240476847233</v>
+        <v>0.65438960441752014</v>
       </c>
       <c r="H34" s="16">
-        <v>23.261899200976021</v>
+        <v>23.870101707569248</v>
       </c>
       <c r="I34" s="27">
-        <v>0.36988412923629177</v>
+        <v>0.38518188305798379</v>
       </c>
       <c r="J34" s="27">
-        <v>1.9846913920253857</v>
+        <v>0.71883378865245118</v>
       </c>
       <c r="K34" s="28">
-        <v>0.28766394159577441</v>
+        <v>0.36842357050823132</v>
       </c>
       <c r="L34" s="16">
-        <v>407168.97522858367</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+        <v>403.94187957775966</v>
+      </c>
+      <c r="M34" s="16">
+        <v>10.946675187309518</v>
+      </c>
+      <c r="N34" s="16">
+        <v>51.048525827134007</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B35" s="16">
         <v>800.00000000000011</v>
       </c>
       <c r="C35" s="16">
-        <v>0.77222313223091421</v>
+        <v>0.76645527234079391</v>
       </c>
       <c r="D35" s="16">
-        <v>3.4029679648293816</v>
+        <v>3.282402205575178</v>
       </c>
       <c r="E35" s="16">
-        <v>0.29386112662101954</v>
+        <v>0.30465492568262798</v>
       </c>
       <c r="F35" s="16">
-        <v>1.2498061236008415E-2</v>
+        <v>1.1062549616918996E-2</v>
       </c>
       <c r="G35" s="16">
-        <v>0.73081072634562128</v>
+        <v>0.65213033450333024</v>
       </c>
       <c r="H35" s="16">
-        <v>22.777686776908567</v>
+        <v>23.354472765920619</v>
       </c>
       <c r="I35" s="27">
-        <v>0.35198545686127924</v>
+        <v>0.36596110142425675</v>
       </c>
       <c r="J35" s="27">
-        <v>1.904205650074752</v>
+        <v>0.68927684304305448</v>
       </c>
       <c r="K35" s="28">
-        <v>0.26978389328349178</v>
+        <v>0.35036473015281244</v>
       </c>
       <c r="L35" s="16">
-        <v>450161.87122959318</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+        <v>446.79953916162481</v>
+      </c>
+      <c r="M35" s="16">
+        <v>10.933247310468779</v>
+      </c>
+      <c r="N35" s="16">
+        <v>52.432314177470431</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B36" s="16">
         <v>850.00000000000011</v>
       </c>
       <c r="C36" s="16">
-        <v>0.77962057221306336</v>
+        <v>0.77420188985225213</v>
       </c>
       <c r="D36" s="16">
-        <v>3.5514603826199638</v>
+        <v>3.429312697353093</v>
       </c>
       <c r="E36" s="16">
-        <v>0.28157430810541256</v>
+        <v>0.29160362097391923</v>
       </c>
       <c r="F36" s="16">
-        <v>1.2758135640936705E-2</v>
+        <v>1.1028955032921501E-2</v>
       </c>
       <c r="G36" s="16">
-        <v>0.74506540447974079</v>
+        <v>0.65028901535442751</v>
       </c>
       <c r="H36" s="16">
-        <v>22.037942778693676</v>
+        <v>22.579811014774787</v>
       </c>
       <c r="I36" s="28">
-        <v>0.33795246909963766</v>
+        <v>0.35093728119586881</v>
       </c>
       <c r="J36" s="28">
-        <v>1.834493272206426</v>
+        <v>0.66633362852870348</v>
       </c>
       <c r="K36" s="28">
-        <v>0.25425185524575955</v>
+        <v>0.33625465413724592</v>
       </c>
       <c r="L36" s="16">
-        <v>502641.67085077928</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+        <v>499.14810532323554</v>
+      </c>
+      <c r="M36" s="16">
+        <v>10.918736575521219</v>
+      </c>
+      <c r="N36" s="16">
+        <v>53.680833138434281</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B37" s="19">
         <v>900.00000000000011</v>
       </c>
       <c r="C37" s="19">
-        <v>0.78962936354720115</v>
+        <v>0.78459689051119186</v>
       </c>
       <c r="D37" s="16">
-        <v>3.7688390112720156</v>
+        <v>3.6430585053900457</v>
       </c>
       <c r="E37" s="16">
-        <v>0.26533370011538154</v>
+        <v>0.2744946309592507</v>
       </c>
       <c r="F37" s="16">
-        <v>1.390700110545017E-2</v>
+        <v>1.0998641061841103E-2</v>
       </c>
       <c r="G37" s="16">
-        <v>0.80803472058972381</v>
+        <v>0.64862750659951096</v>
       </c>
       <c r="H37" s="16">
-        <v>21.037063645279886</v>
+        <v>21.540310948880816</v>
       </c>
       <c r="I37" s="28">
-        <v>0.32766989951505937</v>
+        <v>0.33935090075498781</v>
       </c>
       <c r="J37" s="28">
-        <v>1.7734603234489266</v>
+        <v>0.64882498756823903</v>
       </c>
       <c r="K37" s="28">
-        <v>0.24062457505250273</v>
+        <v>0.32538198146565123</v>
       </c>
       <c r="L37" s="16">
-        <v>568077.10402998899</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+        <v>564.45662986782941</v>
+      </c>
+      <c r="M37" s="16">
+        <v>10.903200362831967</v>
+      </c>
+      <c r="N37" s="16">
+        <v>54.81299090541404</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B38" s="16">
         <v>800.00000000000011</v>
       </c>
       <c r="C38" s="16">
-        <v>0.77222313223091421</v>
+        <v>0.76645527234079391</v>
       </c>
       <c r="D38" s="18">
-        <v>3.4029679648293816</v>
+        <v>3.282402205575178</v>
       </c>
       <c r="E38" s="18">
-        <v>0.29386112662101954</v>
+        <v>0.30465492568262798</v>
       </c>
       <c r="F38" s="18">
-        <v>1.2498061236008415E-2</v>
+        <v>1.1062549616918996E-2</v>
       </c>
       <c r="G38" s="18">
-        <v>0.73081072634562128</v>
+        <v>0.65213033450333024</v>
       </c>
       <c r="H38" s="18">
-        <v>22.777686776908567</v>
+        <v>23.354472765920619</v>
       </c>
       <c r="I38" s="29">
-        <v>0.35198545686127924</v>
+        <v>0.36596110142425675</v>
       </c>
       <c r="J38" s="29">
-        <v>1.904205650074752</v>
+        <v>0.68927684304305448</v>
       </c>
       <c r="K38" s="29">
-        <v>0.26978389328349178</v>
+        <v>0.35036473015281244</v>
       </c>
       <c r="L38" s="16">
-        <v>450161.87122959318</v>
+        <v>446.79953916162481</v>
+      </c>
+      <c r="M38" s="16">
+        <v>10.933247310468779</v>
+      </c>
+      <c r="N38" s="16">
+        <v>52.432314177470431</v>
       </c>
     </row>
   </sheetData>
@@ -2875,11 +2969,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC8F8E6-609F-4748-8A52-08E74E409D1F}">
   <dimension ref="B2:V34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="9" width="11.5546875" style="16"/>
-    <col min="10" max="10" width="15" style="16" customWidth="1"/>
-    <col min="11" max="16384" width="11.5546875" style="16"/>
+    <col min="1" max="1" width="11.5546875" style="16"/>
+    <col min="2" max="2" width="4" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="18.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19" style="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" style="16" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.5546875" style="16"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:22" x14ac:dyDescent="0.3">
@@ -2922,34 +3035,34 @@
         <v>2.5</v>
       </c>
       <c r="C3" s="16">
-        <v>148.47875374177946</v>
+        <v>0.14847875374177946</v>
       </c>
       <c r="D3" s="16">
-        <v>7.0460959203304396</v>
+        <v>7.0460959203304391E-3</v>
       </c>
       <c r="E3" s="16">
         <v>57.084544319769137</v>
       </c>
       <c r="F3" s="16">
-        <v>20.777443537420119</v>
+        <v>21.206837150076275</v>
       </c>
       <c r="G3" s="16">
-        <v>54.858272297545774</v>
+        <v>56.020632425096053</v>
       </c>
       <c r="H3" s="16">
-        <v>17.761735672472536</v>
+        <v>60.272729507660863</v>
       </c>
       <c r="I3" s="16">
-        <v>17.370675747296715</v>
+        <v>59.189670847268573</v>
       </c>
       <c r="J3" s="16">
-        <v>82.316245968108603</v>
+        <v>64.776135827888709</v>
       </c>
       <c r="K3" s="16">
-        <v>37.633341482190204</v>
+        <v>0.12825791427583585</v>
       </c>
       <c r="L3" s="16">
-        <v>336.31723323673612</v>
+        <v>1.1462002886556641</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -2957,34 +3070,34 @@
         <v>2.7</v>
       </c>
       <c r="C4" s="16">
-        <v>156.07764404148372</v>
+        <v>0.15607764404148369</v>
       </c>
       <c r="D4" s="16">
-        <v>7.9400319410870903</v>
+        <v>7.9400319410870904E-3</v>
       </c>
       <c r="E4" s="16">
-        <v>57.697069284918236</v>
+        <v>57.697069284918221</v>
       </c>
       <c r="F4" s="16">
-        <v>20.931122887739914</v>
+        <v>21.400648824288343</v>
       </c>
       <c r="G4" s="16">
-        <v>55.264433674005062</v>
+        <v>56.535431218935074</v>
       </c>
       <c r="H4" s="16">
-        <v>17.067449346516845</v>
+        <v>59.985304092052907</v>
       </c>
       <c r="I4" s="16">
-        <v>16.691333905799326</v>
+        <v>58.896149503948294</v>
       </c>
       <c r="J4" s="16">
-        <v>84.40849039724651</v>
+        <v>63.828534187750677</v>
       </c>
       <c r="K4" s="16">
-        <v>40.749675684056633</v>
+        <v>0.14380991630544512</v>
       </c>
       <c r="L4" s="16">
-        <v>364.16692330767307</v>
+        <v>1.2851835967513741</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -2992,34 +3105,34 @@
         <v>2.9</v>
       </c>
       <c r="C5" s="16">
-        <v>162.75131129996333</v>
+        <v>0.16275131129996334</v>
       </c>
       <c r="D5" s="16">
-        <v>8.6348397336684144</v>
+        <v>8.634839733668416E-3</v>
       </c>
       <c r="E5" s="16">
         <v>58.036241121665519</v>
       </c>
       <c r="F5" s="16">
-        <v>21.009363217890819</v>
+        <v>21.504209451046101</v>
       </c>
       <c r="G5" s="16">
-        <v>55.471253223051519</v>
+        <v>56.810792316635428</v>
       </c>
       <c r="H5" s="16">
-        <v>16.644428995114723</v>
+        <v>59.775581482552411</v>
       </c>
       <c r="I5" s="16">
-        <v>16.278080188040537</v>
+        <v>58.680781077313128</v>
       </c>
       <c r="J5" s="16">
-        <v>86.6984682173848</v>
+        <v>63.002993894505607</v>
       </c>
       <c r="K5" s="16">
-        <v>43.218937629596283</v>
+        <v>0.15581938243407464</v>
       </c>
       <c r="L5" s="16">
-        <v>386.233933914575</v>
+        <v>1.3925083854083262</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -3027,34 +3140,34 @@
         <v>3.1</v>
       </c>
       <c r="C6" s="16">
-        <v>168.68204688771863</v>
+        <v>0.1686820468877186</v>
       </c>
       <c r="D6" s="16">
-        <v>9.1992492869705451</v>
+        <v>9.1992492869705442E-3</v>
       </c>
       <c r="E6" s="16">
-        <v>58.210891042459892</v>
+        <v>58.210891042459878</v>
       </c>
       <c r="F6" s="16">
-        <v>21.04199533313205</v>
+        <v>21.553386714527988</v>
       </c>
       <c r="G6" s="16">
-        <v>55.557569257932535</v>
+        <v>56.941895744836977</v>
       </c>
       <c r="H6" s="16">
-        <v>16.366457101782501</v>
+        <v>59.61137447454162</v>
       </c>
       <c r="I6" s="16">
-        <v>16.007011189269914</v>
+        <v>58.511143056617463</v>
       </c>
       <c r="J6" s="16">
-        <v>89.014517329761588</v>
+        <v>62.245051077676692</v>
       </c>
       <c r="K6" s="16">
-        <v>45.277885494100374</v>
+        <v>0.16552167013536886</v>
       </c>
       <c r="L6" s="16">
-        <v>404.63409775589656</v>
+        <v>1.479214652437798</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -3062,34 +3175,34 @@
         <v>3.3</v>
       </c>
       <c r="C7" s="16">
-        <v>173.99251938127557</v>
+        <v>0.17399251938127558</v>
       </c>
       <c r="D7" s="16">
-        <v>9.6764030259118439</v>
+        <v>9.6764030259118422E-3</v>
       </c>
       <c r="E7" s="16">
         <v>58.279337866454064</v>
       </c>
       <c r="F7" s="16">
-        <v>21.044437590006492</v>
+        <v>21.567124704770642</v>
       </c>
       <c r="G7" s="16">
-        <v>55.564132067774985</v>
+        <v>56.9790358844106</v>
       </c>
       <c r="H7" s="16">
-        <v>16.172669607570381</v>
+        <v>59.475987557600519</v>
       </c>
       <c r="I7" s="16">
-        <v>15.818421386676986</v>
+        <v>58.370569027881871</v>
       </c>
       <c r="J7" s="16">
-        <v>91.299177192676552</v>
+        <v>61.541323787813837</v>
       </c>
       <c r="K7" s="16">
-        <v>47.066082002986029</v>
+        <v>0.17368610240558416</v>
       </c>
       <c r="L7" s="16">
-        <v>420.61464263088794</v>
+        <v>1.5521775933811897</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -3097,34 +3210,34 @@
         <v>3.5</v>
       </c>
       <c r="C8" s="16">
-        <v>178.77612677578253</v>
+        <v>0.17877612677578256</v>
       </c>
       <c r="D8" s="16">
-        <v>10.092101088076173</v>
+        <v>1.0092101088076177E-2</v>
       </c>
       <c r="E8" s="16">
-        <v>58.275613945900197</v>
+        <v>58.275613945900204</v>
       </c>
       <c r="F8" s="16">
-        <v>21.025833603341166</v>
+        <v>21.556543874654039</v>
       </c>
       <c r="G8" s="16">
-        <v>55.515104462653355</v>
+        <v>56.951726807451642</v>
       </c>
       <c r="H8" s="16">
-        <v>16.031740671705105</v>
+        <v>59.360333217803884</v>
       </c>
       <c r="I8" s="16">
-        <v>15.681594954806616</v>
+        <v>58.250012419945477</v>
       </c>
       <c r="J8" s="16">
-        <v>93.532298322480699</v>
+        <v>60.887064704183103</v>
       </c>
       <c r="K8" s="16">
-        <v>48.664309641923587</v>
+        <v>0.18077098915647657</v>
       </c>
       <c r="L8" s="16">
-        <v>434.8974959848569</v>
+        <v>1.6154929785160275</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -3197,64 +3310,64 @@
         <v>2.5</v>
       </c>
       <c r="C16" s="16">
-        <v>2664.8478767473252</v>
+        <v>2.6648478767473245</v>
       </c>
       <c r="D16" s="16">
-        <v>986.37006924873401</v>
+        <v>0.98637006924873272</v>
       </c>
       <c r="E16" s="16">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F16" s="16">
-        <v>2398.8101530183258</v>
+        <v>2.3988101530183341</v>
       </c>
       <c r="G16" s="16">
-        <v>1041.3468841175195</v>
+        <v>1.0413468841175191</v>
       </c>
       <c r="H16" s="16">
-        <v>6947.6550741795809</v>
+        <v>6.9476550741795799</v>
       </c>
       <c r="I16" s="16">
-        <v>9249.2997745483663</v>
+        <v>9.2492997745483656</v>
       </c>
       <c r="J16" s="16">
-        <v>102375.56157213112</v>
+        <v>102.3755615721311</v>
       </c>
       <c r="K16" s="16">
-        <v>274638.10828811495</v>
+        <v>274.63810828811501</v>
       </c>
       <c r="L16" s="16">
-        <v>119161.08401865959</v>
+        <v>119.16108401865955</v>
       </c>
       <c r="M16" s="16">
-        <v>430.56666413791532</v>
+        <v>2.6912818058574373</v>
       </c>
       <c r="N16" s="16">
-        <v>263.71291568172506</v>
+        <v>2.1097033254538005</v>
       </c>
       <c r="O16" s="16">
-        <v>6046.2345139607469</v>
+        <v>6.0462345139607443</v>
       </c>
       <c r="P16" s="16">
-        <v>2598.8390560364678</v>
+        <v>2.5988390560364678</v>
       </c>
       <c r="Q16" s="16">
-        <v>2.7206981667653416</v>
+        <v>2.7206981667653451E-3</v>
       </c>
       <c r="R16" s="16">
-        <v>557.37419969541145</v>
+        <v>0.55737419969541158</v>
       </c>
       <c r="S16" s="16">
-        <v>6888.6844784927525</v>
+        <v>2.7806464000045716</v>
       </c>
       <c r="T16" s="16">
-        <v>686595.27072028746</v>
+        <v>686.59527072028743</v>
       </c>
       <c r="U16" s="16">
-        <v>5818.0961910909264</v>
+        <v>2.8576847188422274</v>
       </c>
       <c r="V16" s="16">
-        <v>320.92719452954594</v>
+        <v>0.32092719452954599</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -3262,64 +3375,64 @@
         <v>2.7</v>
       </c>
       <c r="C17" s="16">
-        <v>3087.3746791042909</v>
+        <v>3.0873746791042942</v>
       </c>
       <c r="D17" s="16">
-        <v>1058.1726709377524</v>
+        <v>1.0581726709377508</v>
       </c>
       <c r="E17" s="16">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F17" s="16">
-        <v>2741.5191927130818</v>
+        <v>2.74151919271308</v>
       </c>
       <c r="G17" s="16">
-        <v>1132.6607037394215</v>
+        <v>1.1326607037394234</v>
       </c>
       <c r="H17" s="16">
-        <v>4812.2007797128163</v>
+        <v>4.8122007797128168</v>
       </c>
       <c r="I17" s="16">
-        <v>8798.3787257595359</v>
+        <v>8.7983787257595463</v>
       </c>
       <c r="J17" s="16">
-        <v>106472.50431367061</v>
+        <v>106.47250431367063</v>
       </c>
       <c r="K17" s="16">
-        <v>285628.78406094934</v>
+        <v>285.62878406094933</v>
       </c>
       <c r="L17" s="16">
-        <v>124163.1956881715</v>
+        <v>124.16319568817148</v>
       </c>
       <c r="M17" s="16">
-        <v>465.16181761897388</v>
+        <v>2.7933502406624782</v>
       </c>
       <c r="N17" s="16">
-        <v>295.92646489174422</v>
+        <v>2.3674117191339534</v>
       </c>
       <c r="O17" s="16">
-        <v>7233.1985651124287</v>
+        <v>7.2331985651124286</v>
       </c>
       <c r="P17" s="16">
-        <v>2857.8379919673444</v>
+        <v>2.8578379919673433</v>
       </c>
       <c r="Q17" s="16">
-        <v>2.9586199441852878</v>
+        <v>2.9586199441852868E-3</v>
       </c>
       <c r="R17" s="16">
-        <v>615.69121606216436</v>
+        <v>0.61569121606216437</v>
       </c>
       <c r="S17" s="16">
-        <v>6524.6167069608418</v>
+        <v>2.1236843920598876</v>
       </c>
       <c r="T17" s="16">
-        <v>714071.9601523733</v>
+        <v>714.07196015237332</v>
       </c>
       <c r="U17" s="16">
-        <v>6610.4897515975899</v>
+        <v>3.2435870797906361</v>
       </c>
       <c r="V17" s="16">
-        <v>559.45962453110246</v>
+        <v>0.55945962453110243</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -3327,64 +3440,64 @@
         <v>2.9</v>
       </c>
       <c r="C18" s="16">
-        <v>3483.3349591886849</v>
+        <v>3.4833349591886873</v>
       </c>
       <c r="D18" s="16">
-        <v>1112.8283922583832</v>
+        <v>1.1128283922583833</v>
       </c>
       <c r="E18" s="16">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F18" s="16">
-        <v>3062.6461462244392</v>
+        <v>3.0626461462244623</v>
       </c>
       <c r="G18" s="16">
-        <v>1197.4264255678095</v>
+        <v>1.1974264255678082</v>
       </c>
       <c r="H18" s="16">
-        <v>3261.9581509413547</v>
+        <v>3.2619581509413549</v>
       </c>
       <c r="I18" s="16">
-        <v>8389.0102350076741</v>
+        <v>8.3890102350076639</v>
       </c>
       <c r="J18" s="16">
-        <v>110376.27722141369</v>
+        <v>110.37627722141367</v>
       </c>
       <c r="K18" s="16">
-        <v>296101.25219792326</v>
+        <v>296.10125219792326</v>
       </c>
       <c r="L18" s="16">
-        <v>128951.81516126439</v>
+        <v>128.95181516126439</v>
       </c>
       <c r="M18" s="16">
-        <v>503.48763200050263</v>
+        <v>2.9063546710122252</v>
       </c>
       <c r="N18" s="16">
-        <v>332.52622722948848</v>
+        <v>2.6602098178361233</v>
       </c>
       <c r="O18" s="16">
-        <v>8230.0684789243242</v>
+        <v>8.2300684789244212</v>
       </c>
       <c r="P18" s="16">
-        <v>3052.5799129535576</v>
+        <v>3.0525799129535578</v>
       </c>
       <c r="Q18" s="16">
-        <v>3.1274897323413353</v>
+        <v>3.1274897323413315E-3</v>
       </c>
       <c r="R18" s="16">
-        <v>659.54879822657836</v>
+        <v>0.65954879822657841</v>
       </c>
       <c r="S18" s="16">
-        <v>6419.2510009520001</v>
+        <v>1.6876150578161564</v>
       </c>
       <c r="T18" s="16">
-        <v>740253.13049480808</v>
+        <v>740.25313049480803</v>
       </c>
       <c r="U18" s="16">
-        <v>7224.9070232672921</v>
+        <v>3.5460454372147954</v>
       </c>
       <c r="V18" s="16">
-        <v>819.69460213791945</v>
+        <v>0.81969460213791934</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -3392,64 +3505,64 @@
         <v>3.1</v>
       </c>
       <c r="C19" s="16">
-        <v>3849.8455050005987</v>
+        <v>3.849845505000594</v>
       </c>
       <c r="D19" s="16">
-        <v>1159.2727723247745</v>
+        <v>1.1592727723247735</v>
       </c>
       <c r="E19" s="16">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F19" s="16">
-        <v>3364.9348540762367</v>
+        <v>3.3649348540762438</v>
       </c>
       <c r="G19" s="16">
-        <v>1246.1198012916427</v>
+        <v>1.246119801291643</v>
       </c>
       <c r="H19" s="16">
-        <v>2088.2936759883305</v>
+        <v>2.0882936759883304</v>
       </c>
       <c r="I19" s="16">
-        <v>8025.6331977169812</v>
+        <v>8.0256331977169904</v>
       </c>
       <c r="J19" s="16">
-        <v>114055.21230881629</v>
+        <v>114.05521230881628</v>
       </c>
       <c r="K19" s="16">
-        <v>305970.5584796489</v>
+        <v>305.9705584796489</v>
       </c>
       <c r="L19" s="16">
-        <v>133484.92502395887</v>
+        <v>133.48492502395891</v>
       </c>
       <c r="M19" s="16">
-        <v>542.96286866639048</v>
+        <v>3.0177127726171351</v>
       </c>
       <c r="N19" s="16">
-        <v>371.22358570482589</v>
+        <v>2.9697886856386071</v>
       </c>
       <c r="O19" s="16">
-        <v>9062.4264174487907</v>
+        <v>9.0624264174487941</v>
       </c>
       <c r="P19" s="16">
-        <v>3207.7054900750236</v>
+        <v>3.207705490075023</v>
       </c>
       <c r="Q19" s="16">
-        <v>3.2545600708319835</v>
+        <v>3.2545600708319853E-3</v>
       </c>
       <c r="R19" s="16">
-        <v>694.3386324507901</v>
+        <v>0.69433863245079008</v>
       </c>
       <c r="S19" s="16">
-        <v>6454.9424924722334</v>
+        <v>1.3807716836777117</v>
       </c>
       <c r="T19" s="16">
-        <v>764926.39619912219</v>
+        <v>764.92639619912222</v>
       </c>
       <c r="U19" s="16">
-        <v>7722.3379691653845</v>
+        <v>3.793448800711043</v>
       </c>
       <c r="V19" s="16">
-        <v>1117.4058748848802</v>
+        <v>1.1174058748848799</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -3457,64 +3570,64 @@
         <v>3.3</v>
       </c>
       <c r="C20" s="16">
-        <v>4189.7807746840863</v>
+        <v>4.1897807746840847</v>
       </c>
       <c r="D20" s="16">
-        <v>1200.5121499819197</v>
+        <v>1.2005121499819216</v>
       </c>
       <c r="E20" s="16">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F20" s="16">
-        <v>3650.6399459165932</v>
+        <v>3.6506399459165988</v>
       </c>
       <c r="G20" s="16">
-        <v>1284.6957381636407</v>
+        <v>1.2846957381636421</v>
       </c>
       <c r="H20" s="16">
-        <v>1173.6306340101291</v>
+        <v>1.1736306340101292</v>
       </c>
       <c r="I20" s="16">
-        <v>7700.3977334383871</v>
+        <v>7.7003977334383675</v>
       </c>
       <c r="J20" s="16">
-        <v>117507.74436055892</v>
+        <v>117.50774436055892</v>
       </c>
       <c r="K20" s="16">
-        <v>315232.50397653977</v>
+        <v>315.23250397653982</v>
       </c>
       <c r="L20" s="16">
-        <v>137757.25064697993</v>
+        <v>137.75725064697997</v>
       </c>
       <c r="M20" s="16">
-        <v>582.62933471651218</v>
+        <v>3.1240100726096798</v>
       </c>
       <c r="N20" s="16">
-        <v>411.08241365598059</v>
+        <v>3.2886593092478451</v>
       </c>
       <c r="O20" s="16">
-        <v>9774.1074490298797</v>
+        <v>9.7741074490298807</v>
       </c>
       <c r="P20" s="16">
-        <v>3337.5714984830197</v>
+        <v>3.3375714984830207</v>
       </c>
       <c r="Q20" s="16">
-        <v>3.355315812650959</v>
+        <v>3.3553158126509606E-3</v>
       </c>
       <c r="R20" s="16">
-        <v>723.25774816297871</v>
+        <v>0.72325774816297872</v>
       </c>
       <c r="S20" s="16">
-        <v>6572.6516565008551</v>
+        <v>1.1531086879647943</v>
       </c>
       <c r="T20" s="16">
-        <v>788081.2599413495</v>
+        <v>788.08125994134957</v>
       </c>
       <c r="U20" s="16">
-        <v>8141.364163259821</v>
+        <v>4.0038191008005048</v>
       </c>
       <c r="V20" s="16">
-        <v>1441.3207479618454</v>
+        <v>1.4413207479618455</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -3522,64 +3635,64 @@
         <v>3.5</v>
       </c>
       <c r="C21" s="16">
-        <v>4506.4720702113282</v>
+        <v>4.5064720702113261</v>
       </c>
       <c r="D21" s="16">
-        <v>1237.8443466263898</v>
+        <v>1.2378443466263889</v>
       </c>
       <c r="E21" s="16">
-        <v>1542.4567100955248</v>
+        <v>1.5424567100955173</v>
       </c>
       <c r="F21" s="16">
-        <v>3921.6241291317938</v>
+        <v>3.9216241291317857</v>
       </c>
       <c r="G21" s="16">
-        <v>1316.5083531758189</v>
+        <v>1.3165083531758173</v>
       </c>
       <c r="H21" s="16">
-        <v>447.74442370759789</v>
+        <v>0.44774442370759787</v>
       </c>
       <c r="I21" s="16">
-        <v>7405.7577728634324</v>
+        <v>7.4057577728634207</v>
       </c>
       <c r="J21" s="16">
-        <v>120746.12116199643</v>
+        <v>120.74612116199641</v>
       </c>
       <c r="K21" s="16">
-        <v>323919.94524683047</v>
+        <v>323.91994524683048</v>
       </c>
       <c r="L21" s="16">
-        <v>141780.80722790223</v>
+        <v>141.78080722790236</v>
       </c>
       <c r="M21" s="16">
-        <v>622.09377831070992</v>
+        <v>3.2245721574894319</v>
       </c>
       <c r="N21" s="16">
-        <v>451.64555185080081</v>
+        <v>3.6131644148064064</v>
       </c>
       <c r="O21" s="16">
-        <v>10394.910711552422</v>
+        <v>10.394910711552424</v>
       </c>
       <c r="P21" s="16">
-        <v>3450.3707440606868</v>
+        <v>3.4503707440606868</v>
       </c>
       <c r="Q21" s="16">
-        <v>3.4384776896527947</v>
+        <v>3.4384776896527925E-3</v>
       </c>
       <c r="R21" s="16">
-        <v>748.15376648165773</v>
+        <v>0.74815376648165788</v>
       </c>
       <c r="S21" s="16">
-        <v>6741.3478561697184</v>
+        <v>0.97706388919974141</v>
       </c>
       <c r="T21" s="16">
-        <v>809799.86311707599</v>
+        <v>809.79986311707626</v>
       </c>
       <c r="U21" s="16">
-        <v>8505.1460801241319</v>
+        <v>4.1879918385926507</v>
       </c>
       <c r="V21" s="16">
-        <v>1783.0262165573138</v>
+        <v>1.7830262165573139</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -3604,40 +3717,52 @@
       <c r="H28" s="17" t="s">
         <v>124</v>
       </c>
+      <c r="I28" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="16">
         <v>2.5</v>
       </c>
       <c r="C29" s="16">
-        <v>0.79174994690516309</v>
+        <v>0.78743627897654755</v>
       </c>
       <c r="D29" s="16">
-        <v>3.8106225411188035</v>
+        <v>3.7131245616874811</v>
       </c>
       <c r="E29" s="16">
-        <v>0.26242431235563907</v>
+        <v>0.26931496193748378</v>
       </c>
       <c r="F29" s="16">
-        <v>1.2211101410757789E-2</v>
+        <v>1.0997228710354294E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.71508245832363448</v>
+        <v>0.64855009561451893</v>
       </c>
       <c r="H29" s="16">
-        <v>20.8250053094837</v>
+        <v>21.256372102345232</v>
       </c>
       <c r="I29" s="16">
-        <v>0.32430261625935458</v>
+        <v>0.35098831294958061</v>
       </c>
       <c r="J29" s="16">
-        <v>1.6805077812729865</v>
+        <v>0.54883192349750376</v>
       </c>
       <c r="K29" s="16">
-        <v>0.23827129619979173</v>
+        <v>0.27127798612207926</v>
       </c>
       <c r="L29" s="16">
-        <v>543611.76913812361</v>
+        <v>540.6500251388785</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -3645,34 +3770,34 @@
         <v>2.7</v>
       </c>
       <c r="C30" s="16">
-        <v>0.7898967612993093</v>
+        <v>0.78517992392523905</v>
       </c>
       <c r="D30" s="16">
-        <v>3.7737906634812184</v>
+        <v>3.6689538264564714</v>
       </c>
       <c r="E30" s="16">
-        <v>0.26498555144485081</v>
+        <v>0.27255725945338877</v>
       </c>
       <c r="F30" s="16">
-        <v>1.2848659426448708E-2</v>
+        <v>1.1016222111888416E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.75002701316365372</v>
+        <v>0.6495911239526041</v>
       </c>
       <c r="H30" s="16">
-        <v>21.010323870069069</v>
+        <v>21.482007607476106</v>
       </c>
       <c r="I30" s="16">
-        <v>0.32689074998505646</v>
+        <v>0.35093086912975024</v>
       </c>
       <c r="J30" s="16">
-        <v>1.7604771696928734</v>
+        <v>0.55301157756786723</v>
       </c>
       <c r="K30" s="16">
-        <v>0.24020565000670163</v>
+        <v>0.2721215799162145</v>
       </c>
       <c r="L30" s="16">
-        <v>564043.12865900912</v>
+        <v>560.67496734958672</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -3680,34 +3805,34 @@
         <v>2.9</v>
       </c>
       <c r="C31" s="16">
-        <v>0.78879031794552723</v>
+        <v>0.78381911721975628</v>
       </c>
       <c r="D31" s="16">
-        <v>3.7544703747794781</v>
+        <v>3.6449566723394535</v>
       </c>
       <c r="E31" s="16">
-        <v>0.26634915185839914</v>
+        <v>0.2743516836808288</v>
       </c>
       <c r="F31" s="16">
-        <v>1.2569616257764678E-2</v>
+        <v>1.103590178240826E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.734732657088082</v>
+        <v>0.65066976669379684</v>
       </c>
       <c r="H31" s="16">
-        <v>21.120968205447276</v>
+        <v>21.618088278024373</v>
       </c>
       <c r="I31" s="16">
-        <v>0.3292352858262676</v>
+        <v>0.35119613448215797</v>
       </c>
       <c r="J31" s="16">
-        <v>1.8183987140116196</v>
+        <v>0.55638111653416655</v>
       </c>
       <c r="K31" s="16">
-        <v>0.24236345670487044</v>
+        <v>0.27290188863584475</v>
       </c>
       <c r="L31" s="16">
-        <v>583904.50216317154</v>
+        <v>580.22455526360147</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -3715,34 +3840,34 @@
         <v>3.1</v>
       </c>
       <c r="C32" s="16">
-        <v>0.78811039511838488</v>
+        <v>0.78297297929263887</v>
       </c>
       <c r="D32" s="16">
-        <v>3.7454166424866164</v>
+        <v>3.6327143834192821</v>
       </c>
       <c r="E32" s="16">
-        <v>0.26699299315765596</v>
+        <v>0.27527625198509353</v>
       </c>
       <c r="F32" s="16">
-        <v>1.2084861351781972E-2</v>
+        <v>1.1058445552501973E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.70816324069116998</v>
+        <v>0.65190539073263321</v>
       </c>
       <c r="H32" s="16">
-        <v>21.188960488161513</v>
+        <v>21.702702070736112</v>
       </c>
       <c r="I32" s="16">
-        <v>0.33182971404075401</v>
+        <v>0.3524851112997372</v>
       </c>
       <c r="J32" s="16">
-        <v>1.8633137202480963</v>
+        <v>0.56059959092402722</v>
       </c>
       <c r="K32" s="16">
-        <v>0.24462927800267664</v>
+        <v>0.27442136234970582</v>
       </c>
       <c r="L32" s="16">
-        <v>602846.44434497238</v>
+        <v>598.91669937160816</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
@@ -3750,34 +3875,34 @@
         <v>3.3</v>
       </c>
       <c r="C33" s="16">
-        <v>0.7877177948580969</v>
+        <v>0.78246690182478418</v>
       </c>
       <c r="D33" s="16">
-        <v>3.7431164006595523</v>
+        <v>3.628053866873143</v>
       </c>
       <c r="E33" s="16">
-        <v>0.26715706725652344</v>
+        <v>0.2756298656783327</v>
       </c>
       <c r="F33" s="16">
-        <v>1.1896018768568203E-2</v>
+        <v>1.1078267669082587E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.69781277870522329</v>
+        <v>0.65299184094241669</v>
       </c>
       <c r="H33" s="16">
-        <v>21.228220514190312</v>
+        <v>21.753309817521583</v>
       </c>
       <c r="I33" s="16">
-        <v>0.3346072042296333</v>
+        <v>0.35411786703491061</v>
       </c>
       <c r="J33" s="16">
-        <v>1.9001715417143965</v>
+        <v>0.564886595632204</v>
       </c>
       <c r="K33" s="16">
-        <v>0.246951461213615</v>
+        <v>0.27613125659978288</v>
       </c>
       <c r="L33" s="16">
-        <v>620785.63224999048</v>
+        <v>616.64750185248022</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.3">
@@ -3785,34 +3910,34 @@
         <v>3.5</v>
       </c>
       <c r="C34" s="16">
-        <v>0.78753086713794596</v>
+        <v>0.78219937578680065</v>
       </c>
       <c r="D34" s="16">
-        <v>3.7455393303065105</v>
+        <v>3.6285936202718592</v>
       </c>
       <c r="E34" s="16">
-        <v>0.26698424761118889</v>
+        <v>0.27558886572839164</v>
       </c>
       <c r="F34" s="16">
-        <v>1.1800413306798704E-2</v>
+        <v>1.1097736814647584E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.69257264334563695</v>
+        <v>0.65405894481083415</v>
       </c>
       <c r="H34" s="16">
-        <v>21.246913286205405</v>
+        <v>21.780062421319933</v>
       </c>
       <c r="I34" s="16">
-        <v>0.33747350997892811</v>
+        <v>0.35608240264787838</v>
       </c>
       <c r="J34" s="16">
-        <v>1.9316824713906868</v>
+        <v>0.56934216663942383</v>
       </c>
       <c r="K34" s="16">
-        <v>0.2492991345617265</v>
+        <v>0.27804171826073282</v>
       </c>
       <c r="L34" s="16">
-        <v>637742.3884087808</v>
+        <v>633.42494744241367</v>
       </c>
     </row>
   </sheetData>
@@ -3823,7 +3948,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5BF8E15-0944-4FE7-87E9-AAA093D2FC4F}">
   <dimension ref="B2:V35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="11.5546875" style="16"/>
   </cols>
@@ -3868,34 +3993,34 @@
         <v>0.6</v>
       </c>
       <c r="C3" s="16">
-        <v>84.651663100386017</v>
+        <v>86.156901039217743</v>
       </c>
       <c r="D3" s="16">
-        <v>8.3031937850684709</v>
+        <v>9.8084317239001884</v>
       </c>
       <c r="E3" s="16">
-        <v>42.07101122120514</v>
+        <v>42.819099089721973</v>
       </c>
       <c r="F3" s="16">
-        <v>14.631738688404706</v>
+        <v>14.663864822242006</v>
       </c>
       <c r="G3" s="16">
-        <v>38.640747946232182</v>
+        <v>38.727712763416655</v>
       </c>
       <c r="H3" s="16">
-        <v>16.821059556257197</v>
+        <v>16.016506866358213</v>
       </c>
       <c r="I3" s="16">
-        <v>16.450346936931222</v>
+        <v>15.664532932350181</v>
       </c>
       <c r="J3" s="16">
-        <v>85.324619297444372</v>
+        <v>90.225393350942056</v>
       </c>
       <c r="K3" s="16">
-        <v>41.998410620174532</v>
+        <v>47.243533000228496</v>
       </c>
       <c r="L3" s="16">
-        <v>375.32647125692898</v>
+        <v>422.20046589497224</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -3903,34 +4028,34 @@
         <v>0.65</v>
       </c>
       <c r="C4" s="16">
-        <v>95.719638863224972</v>
+        <v>97.210785133141698</v>
       </c>
       <c r="D4" s="16">
-        <v>8.2711726604665081</v>
+        <v>9.7623189303832358</v>
       </c>
       <c r="E4" s="16">
-        <v>45.139879807873122</v>
+        <v>45.843080992075038</v>
       </c>
       <c r="F4" s="16">
-        <v>15.866175674521301</v>
+        <v>15.896467543144151</v>
       </c>
       <c r="G4" s="16">
-        <v>41.898367780725323</v>
+        <v>41.980367277779763</v>
       </c>
       <c r="H4" s="16">
-        <v>16.842730303208608</v>
+        <v>16.044057225018896</v>
       </c>
       <c r="I4" s="16">
-        <v>16.471549518827615</v>
+        <v>15.691521012346005</v>
       </c>
       <c r="J4" s="16">
-        <v>85.252672669359299</v>
+        <v>90.168789512744638</v>
       </c>
       <c r="K4" s="16">
-        <v>41.890355298669128</v>
+        <v>47.102438442878928</v>
       </c>
       <c r="L4" s="16">
-        <v>374.36081513036891</v>
+        <v>420.93954859973212</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -3938,34 +4063,34 @@
         <v>0.7</v>
       </c>
       <c r="C5" s="16">
-        <v>106.78762964531352</v>
+        <v>108.26466430705101</v>
       </c>
       <c r="D5" s="16">
-        <v>8.239143084329033</v>
+        <v>9.7161777460665224</v>
       </c>
       <c r="E5" s="16">
-        <v>47.910236668301629</v>
+        <v>48.572907807703899</v>
       </c>
       <c r="F5" s="16">
-        <v>16.980539852983494</v>
+        <v>17.00917520233341</v>
       </c>
       <c r="G5" s="16">
-        <v>44.839121213116108</v>
+        <v>44.916636544834539</v>
       </c>
       <c r="H5" s="16">
-        <v>16.864557590846722</v>
+        <v>16.071850720697345</v>
       </c>
       <c r="I5" s="16">
-        <v>16.492905818748895</v>
+        <v>15.718748039933633</v>
       </c>
       <c r="J5" s="16">
-        <v>85.181148108243178</v>
+        <v>90.112853619381781</v>
       </c>
       <c r="K5" s="16">
-        <v>41.782229312474705</v>
+        <v>46.9611556476533</v>
       </c>
       <c r="L5" s="16">
-        <v>373.39452749590225</v>
+        <v>419.67694908231425</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -3973,34 +4098,34 @@
         <v>0.75</v>
       </c>
       <c r="C6" s="16">
-        <v>117.85563567355979</v>
+        <v>119.31853879470879</v>
       </c>
       <c r="D6" s="16">
-        <v>8.2071051883693009</v>
+        <v>9.6700083095183036</v>
       </c>
       <c r="E6" s="16">
-        <v>50.423610652608318</v>
+        <v>51.049502295224535</v>
       </c>
       <c r="F6" s="16">
-        <v>17.991535686290757</v>
+        <v>18.018667526050667</v>
       </c>
       <c r="G6" s="16">
-        <v>47.507090521397558</v>
+        <v>47.580535882004845</v>
       </c>
       <c r="H6" s="16">
-        <v>16.886542655961488</v>
+        <v>16.099889972255145</v>
       </c>
       <c r="I6" s="16">
-        <v>16.514417052706353</v>
+        <v>15.746216593924817</v>
       </c>
       <c r="J6" s="16">
-        <v>85.110046267862344</v>
+        <v>90.057588582861456</v>
       </c>
       <c r="K6" s="16">
-        <v>41.674031689831082</v>
+        <v>46.819682069324237</v>
       </c>
       <c r="L6" s="16">
-        <v>372.42759966921648</v>
+        <v>418.41264459682901</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -4008,34 +4133,34 @@
         <v>0.8</v>
       </c>
       <c r="C7" s="16">
-        <v>128.92365717653769</v>
+        <v>130.37240883262211</v>
       </c>
       <c r="D7" s="16">
-        <v>8.175059105642541</v>
+        <v>9.6238107617269772</v>
       </c>
       <c r="E7" s="16">
-        <v>52.714168694769128</v>
+        <v>53.306532740811406</v>
       </c>
       <c r="F7" s="16">
-        <v>18.912906397652986</v>
+        <v>18.938667386186037</v>
       </c>
       <c r="G7" s="16">
-        <v>49.938543414634438</v>
+        <v>50.008277907730111</v>
       </c>
       <c r="H7" s="16">
-        <v>16.908686748389439</v>
+        <v>16.128177636870465</v>
       </c>
       <c r="I7" s="16">
-        <v>16.536084449565948</v>
+        <v>15.773929290950816</v>
       </c>
       <c r="J7" s="16">
-        <v>85.039367798199862</v>
+        <v>90.002997330808796</v>
       </c>
       <c r="K7" s="16">
-        <v>41.565761451301526</v>
+        <v>46.678015132002621</v>
       </c>
       <c r="L7" s="16">
-        <v>371.46002289739641</v>
+        <v>417.14661212337256</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -4043,34 +4168,34 @@
         <v>0.85</v>
       </c>
       <c r="C8" s="16">
-        <v>139.99169412513476</v>
+        <v>141.42627439275867</v>
       </c>
       <c r="D8" s="16">
-        <v>8.1430049254371397</v>
+        <v>9.5775851930610489</v>
       </c>
       <c r="E8" s="16">
-        <v>54.810275097122194</v>
+        <v>55.371949413650469</v>
       </c>
       <c r="F8" s="16">
-        <v>19.756061295659428</v>
+        <v>19.780567193227284</v>
       </c>
       <c r="G8" s="16">
-        <v>52.163588511305669</v>
+        <v>52.229925497658378</v>
       </c>
       <c r="H8" s="16">
-        <v>16.93099116797703</v>
+        <v>16.156716446102113</v>
       </c>
       <c r="I8" s="16">
-        <v>16.557909287288794</v>
+        <v>15.801888820830188</v>
       </c>
       <c r="J8" s="16">
-        <v>84.969113326180548</v>
+        <v>89.949082784059556</v>
       </c>
       <c r="K8" s="16">
-        <v>41.457417470316159</v>
+        <v>46.536152072899299</v>
       </c>
       <c r="L8" s="16">
-        <v>370.49178711264432</v>
+        <v>415.8788269717748</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -4078,34 +4203,34 @@
         <v>0.9</v>
       </c>
       <c r="C9" s="16">
-        <v>151.05974730939982</v>
+        <v>152.48013629246421</v>
       </c>
       <c r="D9" s="16">
-        <v>8.1109428806513328</v>
+        <v>9.5313318637157156</v>
       </c>
       <c r="E9" s="16">
-        <v>56.735683787276784</v>
+        <v>57.269159724006734</v>
       </c>
       <c r="F9" s="16">
-        <v>20.530554834676661</v>
+        <v>20.553907258954244</v>
       </c>
       <c r="G9" s="16">
-        <v>54.207439562950576</v>
+        <v>54.270654119622705</v>
       </c>
       <c r="H9" s="16">
-        <v>16.953457112175137</v>
+        <v>16.185509060075972</v>
       </c>
       <c r="I9" s="16">
-        <v>16.57989274351246</v>
+        <v>15.830097803601953</v>
       </c>
       <c r="J9" s="16">
-        <v>84.899283535324514</v>
+        <v>89.89584795030737</v>
       </c>
       <c r="K9" s="16">
-        <v>41.34899905182413</v>
+        <v>46.394090588744014</v>
       </c>
       <c r="L9" s="16">
-        <v>369.52288610351127</v>
+        <v>414.60926855844019</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -4190,7 +4315,7 @@
         <v>15551.202889850705</v>
       </c>
       <c r="G16" s="16">
-        <v>1170.9481617362537</v>
+        <v>1494.9001578998882</v>
       </c>
       <c r="H16" s="16">
         <v>4828.1167891059304</v>
@@ -4208,34 +4333,34 @@
         <v>91682.455189337765</v>
       </c>
       <c r="M16" s="16">
-        <v>479.80835265660414</v>
+        <v>559.70414723692443</v>
       </c>
       <c r="N16" s="16">
-        <v>309.53584846505231</v>
+        <v>385.92046636926364</v>
       </c>
       <c r="O16" s="16">
-        <v>7714.9057117973007</v>
+        <v>5182.9446608253566</v>
       </c>
       <c r="P16" s="16">
-        <v>2966.3162908925378</v>
+        <v>2599.3958930640601</v>
       </c>
       <c r="Q16" s="16">
-        <v>3.0584860662206266</v>
+        <v>61.956246946701256</v>
       </c>
       <c r="R16" s="16">
-        <v>639.86455360544733</v>
+        <v>566.51829225748759</v>
       </c>
       <c r="S16" s="16">
-        <v>6630.5857324783947</v>
+        <v>7724.8626950813996</v>
       </c>
       <c r="T16" s="16">
         <v>531138.24794622965</v>
       </c>
       <c r="U16" s="16">
-        <v>6932.9761335951862</v>
+        <v>8267.509663985551</v>
       </c>
       <c r="V16" s="16">
-        <v>660.83934535734693</v>
+        <v>493.70802460681756</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -4255,7 +4380,7 @@
         <v>13641.822894306615</v>
       </c>
       <c r="G17" s="16">
-        <v>1167.377834047664</v>
+        <v>1489.2754312594495</v>
       </c>
       <c r="H17" s="16">
         <v>4773.8608169536465</v>
@@ -4273,34 +4398,34 @@
         <v>96731.337537772473</v>
       </c>
       <c r="M17" s="16">
-        <v>478.6995829181883</v>
+        <v>558.80042843647391</v>
       </c>
       <c r="N17" s="16">
-        <v>308.52100323915852</v>
+        <v>385.05513966887571</v>
       </c>
       <c r="O17" s="16">
-        <v>7674.0444047855644</v>
+        <v>5155.8524344310554</v>
       </c>
       <c r="P17" s="16">
-        <v>2956.4116676933759</v>
+        <v>2589.5176745276844</v>
       </c>
       <c r="Q17" s="16">
-        <v>3.0491695134966466</v>
+        <v>61.744296137899276</v>
       </c>
       <c r="R17" s="16">
-        <v>637.6738205926822</v>
+        <v>564.27229114193301</v>
       </c>
       <c r="S17" s="16">
-        <v>6608.5906938628559</v>
+        <v>7704.9506400740893</v>
       </c>
       <c r="T17" s="16">
         <v>559752.04088293505</v>
       </c>
       <c r="U17" s="16">
-        <v>6904.4750775131142</v>
+        <v>8225.9938968337719</v>
       </c>
       <c r="V17" s="16">
-        <v>652.81228129907402</v>
+        <v>485.8547057348618</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -4320,7 +4445,7 @@
         <v>11722.797219174221</v>
       </c>
       <c r="G18" s="16">
-        <v>1163.8002679140027</v>
+        <v>1483.636101610301</v>
       </c>
       <c r="H18" s="16">
         <v>4719.2041314713424</v>
@@ -4338,34 +4463,34 @@
         <v>101792.88253725517</v>
       </c>
       <c r="M18" s="16">
-        <v>477.59838298531952</v>
+        <v>557.90842568106086</v>
       </c>
       <c r="N18" s="16">
-        <v>307.51397795733186</v>
+        <v>384.20177297981479</v>
       </c>
       <c r="O18" s="16">
-        <v>7633.226975656662</v>
+        <v>5128.7892445000462</v>
       </c>
       <c r="P18" s="16">
-        <v>2946.4972692960191</v>
+        <v>2579.6219098471674</v>
       </c>
       <c r="Q18" s="16">
-        <v>3.0398341699894589</v>
+        <v>61.531695368638609</v>
       </c>
       <c r="R18" s="16">
-        <v>635.48096259737144</v>
+        <v>562.0226668769842</v>
       </c>
       <c r="S18" s="16">
-        <v>6586.7021178591458</v>
+        <v>7685.1916116019038</v>
       </c>
       <c r="T18" s="16">
         <v>588366.12863704446</v>
       </c>
       <c r="U18" s="16">
-        <v>6875.9679388525192</v>
+        <v>8184.4559708224224</v>
       </c>
       <c r="V18" s="16">
-        <v>644.86001309898495</v>
+        <v>478.07335750389097</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -4385,7 +4510,7 @@
         <v>9794.0194828991152</v>
       </c>
       <c r="G19" s="16">
-        <v>1160.2154649607455</v>
+        <v>1477.9821483939998</v>
       </c>
       <c r="H19" s="16">
         <v>4664.1478209078205</v>
@@ -4403,34 +4528,34 @@
         <v>106867.21213527194</v>
       </c>
       <c r="M19" s="16">
-        <v>476.50475067363294</v>
+        <v>557.02817377772647</v>
       </c>
       <c r="N19" s="16">
-        <v>306.51475643697756</v>
+        <v>383.36038489629044</v>
       </c>
       <c r="O19" s="16">
-        <v>7592.4695660017896</v>
+        <v>5101.7552011120097</v>
       </c>
       <c r="P19" s="16">
-        <v>2936.5730806933279</v>
+        <v>2569.7085174588692</v>
       </c>
       <c r="Q19" s="16">
-        <v>3.0304800390416675</v>
+        <v>61.318442775395056</v>
       </c>
       <c r="R19" s="16">
-        <v>633.28598215131888</v>
+        <v>559.76940898281782</v>
       </c>
       <c r="S19" s="16">
-        <v>6564.9198074580263</v>
+        <v>7665.5856936177961</v>
       </c>
       <c r="T19" s="16">
         <v>616980.51201500499</v>
       </c>
       <c r="U19" s="16">
-        <v>6847.4548807334431</v>
+        <v>8142.8961071638169</v>
       </c>
       <c r="V19" s="16">
-        <v>636.96663850310608</v>
+        <v>470.36385339031426</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -4450,7 +4575,7 @@
         <v>7855.3814543741792</v>
       </c>
       <c r="G20" s="16">
-        <v>1156.6234270305308</v>
+        <v>1472.3135513239968</v>
       </c>
       <c r="H20" s="16">
         <v>4608.6931025683307</v>
@@ -4468,34 +4593,34 @@
         <v>111954.45016030467</v>
       </c>
       <c r="M20" s="16">
-        <v>475.41868378703322</v>
+        <v>556.15970793057159</v>
       </c>
       <c r="N20" s="16">
-        <v>305.52332255396959</v>
+        <v>382.53099455459795</v>
       </c>
       <c r="O20" s="16">
-        <v>7551.7725219044723</v>
+        <v>5074.7504129403014</v>
       </c>
       <c r="P20" s="16">
-        <v>2926.6390881218472</v>
+        <v>2559.7774155320412</v>
       </c>
       <c r="Q20" s="16">
-        <v>3.0211071245494749</v>
+        <v>61.104536494338944</v>
       </c>
       <c r="R20" s="16">
-        <v>631.0888811175264</v>
+        <v>557.51250723839519</v>
       </c>
       <c r="S20" s="16">
-        <v>6543.2435634506955</v>
+        <v>7646.1329692745476</v>
       </c>
       <c r="T20" s="16">
         <v>645595.19182583911</v>
       </c>
       <c r="U20" s="16">
-        <v>6818.9360678689582</v>
+        <v>8101.3145304905447</v>
       </c>
       <c r="V20" s="16">
-        <v>629.13205033856616</v>
+        <v>462.72606501276692</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -4515,7 +4640,7 @@
         <v>5906.7693275598585</v>
       </c>
       <c r="G21" s="16">
-        <v>1153.0241497972104</v>
+        <v>1466.6302822671662</v>
       </c>
       <c r="H21" s="16">
         <v>4552.8544882684373</v>
@@ -4533,34 +4658,34 @@
         <v>117054.72843049669</v>
       </c>
       <c r="M21" s="16">
-        <v>474.34018002231136</v>
+        <v>555.30306362012982</v>
       </c>
       <c r="N21" s="16">
-        <v>304.53966024366213</v>
+        <v>381.7136216422723</v>
       </c>
       <c r="O21" s="16">
-        <v>7511.1361485193947</v>
+        <v>5047.7749592625014</v>
       </c>
       <c r="P21" s="16">
-        <v>2916.6952608827623</v>
+        <v>2549.828507954579</v>
       </c>
       <c r="Q21" s="16">
-        <v>3.0117154142819711</v>
+        <v>60.889974324030334</v>
       </c>
       <c r="R21" s="16">
-        <v>628.8896592311786</v>
+        <v>555.25194849347736</v>
       </c>
       <c r="S21" s="16">
-        <v>6521.6731440447938</v>
+        <v>7626.8334735707522</v>
       </c>
       <c r="T21" s="16">
         <v>674210.20227485348</v>
       </c>
       <c r="U21" s="16">
-        <v>6790.4116260048368</v>
+        <v>8059.7114209095162</v>
       </c>
       <c r="V21" s="16">
-        <v>621.35613686952445</v>
+        <v>455.15985959402667</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -4580,7 +4705,7 @@
         <v>3948.0789449175445</v>
       </c>
       <c r="G22" s="16">
-        <v>1149.4176492962922</v>
+        <v>1460.9323389927372</v>
       </c>
       <c r="H22" s="16">
         <v>4496.6051596002653</v>
@@ -4598,34 +4723,34 @@
         <v>122168.16161023772</v>
       </c>
       <c r="M22" s="16">
-        <v>473.26923738185826</v>
+        <v>554.45827713942515</v>
       </c>
       <c r="N22" s="16">
-        <v>303.56375350130452</v>
+        <v>380.90828640749658</v>
       </c>
       <c r="O22" s="16">
-        <v>7470.5608830328774</v>
+        <v>5020.8290061210819</v>
       </c>
       <c r="P22" s="16">
-        <v>2906.7416213199263</v>
+        <v>2539.8617432387591</v>
       </c>
       <c r="Q22" s="16">
-        <v>3.0023049491744751</v>
+        <v>60.674755126432515</v>
       </c>
       <c r="R22" s="16">
-        <v>626.68832570193877</v>
+        <v>552.98772921246893</v>
       </c>
       <c r="S22" s="16">
-        <v>6500.2084323924255</v>
+        <v>7607.6873897981941</v>
       </c>
       <c r="T22" s="16">
         <v>702825.47232081008</v>
       </c>
       <c r="U22" s="16">
-        <v>6761.881810422914</v>
+        <v>8018.0871133723513</v>
       </c>
       <c r="V22" s="16">
-        <v>613.63879603503915</v>
+        <v>447.66511044438738</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -4656,34 +4781,34 @@
         <v>0.6</v>
       </c>
       <c r="C29" s="16">
-        <v>0.85242659657944664</v>
+        <v>0.85241852514485672</v>
       </c>
       <c r="D29" s="16">
-        <v>5.8258735665842218</v>
+        <v>5.8130549856946079</v>
       </c>
       <c r="E29" s="16">
-        <v>0.17164807793559991</v>
+        <v>0.17202658541178567</v>
       </c>
       <c r="F29" s="16">
-        <v>1.6757024969993196E-2</v>
+        <v>1.4735880962343805E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.96424452860532706</v>
+        <v>0.85346562554606398</v>
       </c>
       <c r="H29" s="16">
-        <v>14.757340342055347</v>
+        <v>14.758147485514328</v>
       </c>
       <c r="I29" s="16">
-        <v>0.15189110299219086</v>
+        <v>0.15173117982685616</v>
       </c>
       <c r="J29" s="16">
-        <v>0.56640737464839852</v>
+        <v>0.58955377684907817</v>
       </c>
       <c r="K29" s="16">
-        <v>3.9478837258498566E-2</v>
+        <v>3.865617742874497E-2</v>
       </c>
       <c r="L29" s="16">
-        <v>452756.36900997476</v>
+        <v>452752.08196234831</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -4691,34 +4816,34 @@
         <v>0.65</v>
       </c>
       <c r="C30" s="16">
-        <v>0.84016080189624043</v>
+        <v>0.84015476168306036</v>
       </c>
       <c r="D30" s="16">
-        <v>5.295294966671853</v>
+        <v>5.2851664019243279</v>
       </c>
       <c r="E30" s="16">
-        <v>0.1888468926271184</v>
+        <v>0.18920880137963117</v>
       </c>
       <c r="F30" s="16">
-        <v>1.6384759955406843E-2</v>
+        <v>1.4256080607525746E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.94384068315584913</v>
+        <v>0.82716776809848613</v>
       </c>
       <c r="H30" s="16">
-        <v>15.983919810375957</v>
+        <v>15.984523831693965</v>
       </c>
       <c r="I30" s="16">
-        <v>0.13963406500419584</v>
+        <v>0.13942769502613755</v>
       </c>
       <c r="J30" s="16">
-        <v>0.54963928725632771</v>
+        <v>0.57264323209749335</v>
       </c>
       <c r="K30" s="16">
-        <v>3.6836193073165435E-2</v>
+        <v>3.6160987552076175E-2</v>
       </c>
       <c r="L30" s="16">
-        <v>470281.72353126388</v>
+        <v>470278.34250960895</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -4726,34 +4851,34 @@
         <v>0.7</v>
       </c>
       <c r="C31" s="16">
-        <v>0.82908796609816826</v>
+        <v>0.82908377087366503</v>
       </c>
       <c r="D31" s="16">
-        <v>4.8825771929300403</v>
+        <v>4.8743325940926692</v>
       </c>
       <c r="E31" s="16">
-        <v>0.20480986996949019</v>
+        <v>0.20515629179919442</v>
       </c>
       <c r="F31" s="16">
-        <v>1.6208407990483766E-2</v>
+        <v>1.3874309125541892E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.93417483195841522</v>
+        <v>0.80624287317095111</v>
       </c>
       <c r="H31" s="16">
-        <v>17.091203390183175</v>
+        <v>17.091622912633508</v>
       </c>
       <c r="I31" s="16">
-        <v>0.13020351945141498</v>
+        <v>0.12993056596602254</v>
       </c>
       <c r="J31" s="16">
-        <v>0.53656271821736845</v>
+        <v>0.55935741234628522</v>
       </c>
       <c r="K31" s="16">
-        <v>3.4796268436626483E-2</v>
+        <v>3.4227935730937228E-2</v>
       </c>
       <c r="L31" s="16">
-        <v>487807.27691274043</v>
+        <v>487804.80858474062</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -4761,34 +4886,34 @@
         <v>0.75</v>
       </c>
       <c r="C32" s="16">
-        <v>0.81904215118447687</v>
+        <v>0.81903961513846057</v>
       </c>
       <c r="D32" s="16">
-        <v>4.5523748804198689</v>
+        <v>4.5455060090005324</v>
       </c>
       <c r="E32" s="16">
-        <v>0.21966556495623429</v>
+        <v>0.2199975091925751</v>
       </c>
       <c r="F32" s="16">
-        <v>1.6294029696723257E-2</v>
+        <v>1.356335617041266E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.93886775767740172</v>
+        <v>0.78919954170031792</v>
       </c>
       <c r="H32" s="16">
-        <v>18.095784881552312</v>
+        <v>18.096038486153944</v>
       </c>
       <c r="I32" s="16">
-        <v>0.12283585939108733</v>
+        <v>0.12246041814928492</v>
       </c>
       <c r="J32" s="16">
-        <v>0.52650233392927837</v>
+        <v>0.54906778297915715</v>
       </c>
       <c r="K32" s="16">
-        <v>3.3249815789451624E-2</v>
+        <v>3.2760901155504313E-2</v>
       </c>
       <c r="L32" s="16">
-        <v>505333.04579966969</v>
+        <v>505331.48110870004</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
@@ -4796,34 +4921,34 @@
         <v>0.8</v>
       </c>
       <c r="C33" s="16">
-        <v>0.80988681090702375</v>
+        <v>0.80988577304740417</v>
       </c>
       <c r="D33" s="16">
-        <v>4.2821911866889346</v>
+        <v>4.2763609314884485</v>
       </c>
       <c r="E33" s="16">
-        <v>0.23352530431347171</v>
+        <v>0.23384368532520844</v>
       </c>
       <c r="F33" s="16">
-        <v>1.7096731860174904E-2</v>
+        <v>1.3305183426066024E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.98286386325618658</v>
+        <v>0.77504909358267882</v>
       </c>
       <c r="H33" s="16">
-        <v>19.011318909297625</v>
+        <v>19.011422695259583</v>
       </c>
       <c r="I33" s="16">
-        <v>0.11719887472150799</v>
+        <v>0.11660316652751009</v>
       </c>
       <c r="J33" s="16">
-        <v>0.51947519143337839</v>
+        <v>0.5418333576800487</v>
       </c>
       <c r="K33" s="16">
-        <v>3.2201562697492067E-2</v>
+        <v>3.1771604947176943E-2</v>
       </c>
       <c r="L33" s="16">
-        <v>522859.03104473709</v>
+        <v>522858.3610075569</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.3">
@@ -4831,34 +4956,34 @@
         <v>0.85</v>
       </c>
       <c r="C34" s="16">
-        <v>0.80150858782155698</v>
+        <v>0.80150890776314676</v>
       </c>
       <c r="D34" s="16">
-        <v>4.0570262251497224</v>
+        <v>4.052001643499775</v>
       </c>
       <c r="E34" s="16">
-        <v>0.24648595905073192</v>
+        <v>0.2467916076994196</v>
       </c>
       <c r="F34" s="16">
-        <v>1.6058055835609431E-2</v>
+        <v>1.3087420737113054E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.92593403034975297</v>
+        <v>0.76311352060116655</v>
       </c>
       <c r="H34" s="16">
-        <v>19.849141217844313</v>
+        <v>19.849109223685335</v>
       </c>
       <c r="I34" s="16">
-        <v>0.11300286763090467</v>
+        <v>0.11239929916164836</v>
       </c>
       <c r="J34" s="16">
-        <v>0.51728913977209012</v>
+        <v>0.53955387406135258</v>
       </c>
       <c r="K34" s="16">
-        <v>3.1952881074093976E-2</v>
+        <v>3.1562837809111115E-2</v>
       </c>
       <c r="L34" s="16">
-        <v>540385.26712020405</v>
+        <v>540385.48282808799</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
@@ -4866,34 +4991,34 @@
         <v>0.9</v>
       </c>
       <c r="C35" s="16">
-        <v>0.79381255307974286</v>
+        <v>0.79381410769244976</v>
       </c>
       <c r="D35" s="16">
-        <v>3.8664934263684487</v>
+        <v>3.862108054159032</v>
       </c>
       <c r="E35" s="16">
-        <v>0.25863227729297766</v>
+        <v>0.25892595079599562</v>
       </c>
       <c r="F35" s="16">
-        <v>1.4372241813136767E-2</v>
+        <v>1.2901282569797499E-2</v>
       </c>
       <c r="G35" s="16">
-        <v>0.83353456377802626</v>
+        <v>0.752911287650601</v>
       </c>
       <c r="H35" s="16">
-        <v>20.618744692025714</v>
+        <v>20.618589230755024</v>
       </c>
       <c r="I35" s="16">
-        <v>0.11291062697480642</v>
+        <v>0.11260236824715117</v>
       </c>
       <c r="J35" s="16">
-        <v>0.53677735101387736</v>
+        <v>0.55968680254367753</v>
       </c>
       <c r="K35" s="16">
-        <v>3.5298644970179663E-2</v>
+        <v>3.4903154152639004E-2</v>
       </c>
       <c r="L35" s="16">
-        <v>557911.68255245837</v>
+        <v>557912.7751738684</v>
       </c>
     </row>
   </sheetData>
@@ -4904,7 +5029,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609148A7-EAA7-4F28-BBF6-02D6EA60B99E}">
   <dimension ref="B2:V35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="11.5546875" style="16"/>
   </cols>
@@ -4949,34 +5074,34 @@
         <v>0.6</v>
       </c>
       <c r="C3" s="16">
-        <v>131.37511198083556</v>
+        <v>133.34794298488188</v>
       </c>
       <c r="D3" s="16">
-        <v>9.3200967432357285</v>
+        <v>11.29292774728205</v>
       </c>
       <c r="E3" s="16">
-        <v>50.071624569453377</v>
+        <v>50.823539082667992</v>
       </c>
       <c r="F3" s="16">
-        <v>17.839741822862763</v>
+        <v>17.870345466257085</v>
       </c>
       <c r="G3" s="16">
-        <v>47.106200088887334</v>
+        <v>47.189043554162183</v>
       </c>
       <c r="H3" s="16">
-        <v>16.462268690205413</v>
+        <v>15.503845999051238</v>
       </c>
       <c r="I3" s="16">
-        <v>16.102972586183899</v>
+        <v>15.165716752010718</v>
       </c>
       <c r="J3" s="16">
-        <v>91.9253559989113</v>
+        <v>96.950596455769869</v>
       </c>
       <c r="K3" s="16">
-        <v>46.149026428859131</v>
+        <v>52.664397678347513</v>
       </c>
       <c r="L3" s="16">
-        <v>412.41920791083669</v>
+        <v>470.64501369465466</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -4984,34 +5109,34 @@
         <v>0.65</v>
       </c>
       <c r="C4" s="16">
-        <v>137.50731004203092</v>
+        <v>139.35001364631847</v>
       </c>
       <c r="D4" s="16">
-        <v>9.0281428634368091</v>
+        <v>10.870846467724363</v>
       </c>
       <c r="E4" s="16">
-        <v>51.956539392742719</v>
+        <v>52.652796939894571</v>
       </c>
       <c r="F4" s="16">
-        <v>18.600572278859662</v>
+        <v>18.629509900778704</v>
       </c>
       <c r="G4" s="16">
-        <v>49.114119918070912</v>
+        <v>49.192453495733503</v>
       </c>
       <c r="H4" s="16">
-        <v>16.618043449597593</v>
+        <v>15.700731352257428</v>
       </c>
       <c r="I4" s="16">
-        <v>16.255179781923417</v>
+        <v>15.358410719491728</v>
       </c>
       <c r="J4" s="16">
-        <v>90.989305976502749</v>
+        <v>96.116205587263778</v>
       </c>
       <c r="K4" s="16">
-        <v>45.125682851446044</v>
+        <v>51.33999443789137</v>
       </c>
       <c r="L4" s="16">
-        <v>403.27391102644947</v>
+        <v>458.80924211612592</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -5019,34 +5144,34 @@
         <v>0.7</v>
       </c>
       <c r="C5" s="16">
-        <v>142.77772072465743</v>
+        <v>144.50778451002469</v>
       </c>
       <c r="D5" s="16">
-        <v>8.7787096101952358</v>
+        <v>10.508773395562514</v>
       </c>
       <c r="E5" s="16">
-        <v>53.541101217454965</v>
+        <v>54.189868544562223</v>
       </c>
       <c r="F5" s="16">
-        <v>19.240416855501568</v>
+        <v>19.267922060750973</v>
       </c>
       <c r="G5" s="16">
-        <v>50.802741615166326</v>
+        <v>50.87719766886547</v>
       </c>
       <c r="H5" s="16">
-        <v>16.7600449364352</v>
+        <v>15.882502680877492</v>
       </c>
       <c r="I5" s="16">
-        <v>16.393981062161274</v>
+        <v>15.536374651829526</v>
       </c>
       <c r="J5" s="16">
-        <v>90.230933490109237</v>
+        <v>95.462145694242906</v>
       </c>
       <c r="K5" s="16">
-        <v>44.253416223389642</v>
+        <v>50.205001391427629</v>
       </c>
       <c r="L5" s="16">
-        <v>395.4787409076468</v>
+        <v>448.66616934884934</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -5054,34 +5179,34 @@
         <v>0.75</v>
       </c>
       <c r="C6" s="16">
-        <v>147.35667937941781</v>
+        <v>148.98830428330427</v>
       </c>
       <c r="D6" s="16">
-        <v>8.563320091983833</v>
+        <v>10.194944995870282</v>
       </c>
       <c r="E6" s="16">
-        <v>54.890651906707951</v>
+        <v>55.498435381598455</v>
       </c>
       <c r="F6" s="16">
-        <v>19.785543457011226</v>
+        <v>19.81180204410261</v>
       </c>
       <c r="G6" s="16">
-        <v>52.241389953373904</v>
+        <v>52.312471436053684</v>
       </c>
       <c r="H6" s="16">
-        <v>16.889621914325545</v>
+        <v>16.050355602044668</v>
       </c>
       <c r="I6" s="16">
-        <v>16.520675581272112</v>
+        <v>15.700758934164485</v>
       </c>
       <c r="J6" s="16">
-        <v>89.606197121539367</v>
+        <v>94.941506578418796</v>
       </c>
       <c r="K6" s="16">
-        <v>43.501095785145466</v>
+        <v>49.220982258302961</v>
       </c>
       <c r="L6" s="16">
-        <v>388.75549183295408</v>
+        <v>439.87230254695726</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -5089,34 +5214,34 @@
         <v>0.8</v>
       </c>
       <c r="C7" s="16">
-        <v>151.37216187198626</v>
+        <v>152.91702895935859</v>
       </c>
       <c r="D7" s="16">
-        <v>8.375579131892728</v>
+        <v>9.9204462192650738</v>
       </c>
       <c r="E7" s="16">
-        <v>56.053007710442238</v>
+        <v>56.625070933225054</v>
       </c>
       <c r="F7" s="16">
-        <v>20.25518900750864</v>
+        <v>20.280351456301347</v>
       </c>
       <c r="G7" s="16">
-        <v>53.480833928986208</v>
+        <v>53.54894818668847</v>
       </c>
       <c r="H7" s="16">
-        <v>17.0080724028589</v>
+        <v>16.205516117198815</v>
       </c>
       <c r="I7" s="16">
-        <v>16.636519309543448</v>
+        <v>15.852749821890747</v>
       </c>
       <c r="J7" s="16">
-        <v>89.084111961747624</v>
+        <v>94.521546465530378</v>
       </c>
       <c r="K7" s="16">
-        <v>42.845613696759763</v>
+        <v>48.359332504530663</v>
       </c>
       <c r="L7" s="16">
-        <v>382.89765636791992</v>
+        <v>432.17201206531212</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -5124,34 +5249,34 @@
         <v>0.85</v>
       </c>
       <c r="C8" s="16">
-        <v>154.92225597135939</v>
+        <v>156.39008660616491</v>
       </c>
       <c r="D8" s="16">
-        <v>8.2105755036851527</v>
+        <v>9.6784061384906455</v>
       </c>
       <c r="E8" s="16">
-        <v>57.063944982107998</v>
+        <v>57.60460459271345</v>
       </c>
       <c r="F8" s="16">
-        <v>20.663755903728628</v>
+        <v>20.687946016617072</v>
       </c>
       <c r="G8" s="16">
-        <v>54.559083511223442</v>
+        <v>54.624565674613201</v>
       </c>
       <c r="H8" s="16">
-        <v>17.116592621779663</v>
+        <v>16.349160892882711</v>
       </c>
       <c r="I8" s="16">
-        <v>16.742672845265915</v>
+        <v>15.993489361004398</v>
       </c>
       <c r="J8" s="16">
-        <v>88.642335977364553</v>
+        <v>94.178874289249165</v>
       </c>
       <c r="K8" s="16">
-        <v>42.269442031817007</v>
+        <v>47.598304757676615</v>
       </c>
       <c r="L8" s="16">
-        <v>377.74859299509524</v>
+        <v>425.37094853606186</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -5159,34 +5284,34 @@
         <v>0.9</v>
       </c>
       <c r="C9" s="16">
-        <v>158.08345354249448</v>
+        <v>159.48242028325518</v>
       </c>
       <c r="D9" s="16">
-        <v>8.064482664381817</v>
+        <v>9.4634494051425264</v>
       </c>
       <c r="E9" s="16">
-        <v>57.9507511320136</v>
+        <v>58.463588950387766</v>
       </c>
       <c r="F9" s="16">
-        <v>21.022234635974197</v>
+        <v>21.04555561288613</v>
       </c>
       <c r="G9" s="16">
-        <v>55.505144149590457</v>
+        <v>55.568273578857628</v>
       </c>
       <c r="H9" s="16">
-        <v>17.216255892025185</v>
+        <v>16.482381431698961</v>
       </c>
       <c r="I9" s="16">
-        <v>16.840179365092585</v>
+        <v>16.124039019017342</v>
       </c>
       <c r="J9" s="16">
-        <v>88.264404798389421</v>
+        <v>93.89643459040991</v>
       </c>
       <c r="K9" s="16">
-        <v>41.759049116660748</v>
+        <v>46.921057458241748</v>
       </c>
       <c r="L9" s="16">
-        <v>373.18737344008377</v>
+        <v>419.31860428513284</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -5271,7 +5396,7 @@
         <v>2807.373846715212</v>
       </c>
       <c r="G16" s="16">
-        <v>1276.8209247155376</v>
+        <v>1664.7034737094584</v>
       </c>
       <c r="H16" s="16">
         <v>1104.7199639895116</v>
@@ -5289,34 +5414,34 @@
         <v>120250.45822234853</v>
       </c>
       <c r="M16" s="16">
-        <v>5.452183432965394</v>
+        <v>6.2485536870211744</v>
       </c>
       <c r="N16" s="16">
-        <v>3.5159669301187799</v>
+        <v>4.2509494476148886</v>
       </c>
       <c r="O16" s="16">
-        <v>9069.4723274985863</v>
+        <v>6093.0916069702953</v>
       </c>
       <c r="P16" s="16">
-        <v>3270.9717653959974</v>
+        <v>2903.6773280167959</v>
       </c>
       <c r="Q16" s="16">
-        <v>3.3347810802459064</v>
+        <v>68.217739946875895</v>
       </c>
       <c r="R16" s="16">
-        <v>707.45619070343423</v>
+        <v>636.22254790976308</v>
       </c>
       <c r="S16" s="16">
-        <v>8247.2828155752686</v>
+        <v>9425.1569383103433</v>
       </c>
       <c r="T16" s="16">
         <v>692590.37147487211</v>
       </c>
       <c r="U16" s="16">
-        <v>7815.0223404901808</v>
+        <v>9575.8876491927022</v>
       </c>
       <c r="V16" s="16">
-        <v>1006.0994414795861</v>
+        <v>815.03996781423018</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
@@ -5336,7 +5461,7 @@
         <v>2807.373846715212</v>
       </c>
       <c r="G17" s="16">
-        <v>1246.9321510205978</v>
+        <v>1617.4571038473882</v>
       </c>
       <c r="H17" s="16">
         <v>1791.6358617457445</v>
@@ -5354,34 +5479,34 @@
         <v>121347.12487858563</v>
       </c>
       <c r="M17" s="16">
-        <v>5.3076931478068436</v>
+        <v>6.1139985977899594</v>
       </c>
       <c r="N17" s="16">
-        <v>3.386088052052231</v>
+        <v>4.1246023647080197</v>
       </c>
       <c r="O17" s="16">
-        <v>8681.1360766426478</v>
+        <v>5829.1762754868196</v>
       </c>
       <c r="P17" s="16">
-        <v>3183.8465415175647</v>
+        <v>2817.8479749916446</v>
       </c>
       <c r="Q17" s="16">
-        <v>3.2567627815380549</v>
+        <v>66.480891156226164</v>
       </c>
       <c r="R17" s="16">
-        <v>688.15375575126609</v>
+        <v>616.5594824618322</v>
       </c>
       <c r="S17" s="16">
-        <v>7989.1196836424506</v>
+        <v>9179.4853643105471</v>
       </c>
       <c r="T17" s="16">
         <v>698619.33690745581</v>
       </c>
       <c r="U17" s="16">
-        <v>7556.3627262476602</v>
+        <v>9196.8997950678531</v>
       </c>
       <c r="V17" s="16">
-        <v>894.35041221219433</v>
+        <v>714.61349609765091</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
@@ -5401,7 +5526,7 @@
         <v>2807.373846715212</v>
       </c>
       <c r="G18" s="16">
-        <v>1220.9458553359398</v>
+        <v>1576.1265620255674</v>
       </c>
       <c r="H18" s="16">
         <v>2430.7471421233495</v>
@@ -5419,34 +5544,34 @@
         <v>122313.69926104051</v>
       </c>
       <c r="M18" s="16">
-        <v>5.1915365490738949</v>
+        <v>6.0091698841287293</v>
       </c>
       <c r="N18" s="16">
-        <v>3.2824943089030691</v>
+        <v>4.0267651386649792</v>
       </c>
       <c r="O18" s="16">
-        <v>8350.2774620509263</v>
+        <v>5606.3403100045025</v>
       </c>
       <c r="P18" s="16">
-        <v>3109.0032010434434</v>
+        <v>2743.5671131508311</v>
       </c>
       <c r="Q18" s="16">
-        <v>3.1889412829698629</v>
+        <v>64.955347215322192</v>
       </c>
       <c r="R18" s="16">
-        <v>671.56089370621544</v>
+        <v>599.55268836504126</v>
       </c>
       <c r="S18" s="16">
-        <v>7779.7332679045712</v>
+        <v>8984.6758004859348</v>
       </c>
       <c r="T18" s="16">
         <v>703927.89882574859</v>
       </c>
       <c r="U18" s="16">
-        <v>7335.3153665981044</v>
+        <v>8871.7674451347448</v>
       </c>
       <c r="V18" s="16">
-        <v>807.96407777095044</v>
+        <v>634.93527696956335</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
@@ -5466,7 +5591,7 @@
         <v>2807.373846715212</v>
       </c>
       <c r="G19" s="16">
-        <v>1198.1746826835815</v>
+        <v>1539.7051248627733</v>
       </c>
       <c r="H19" s="16">
         <v>3023.7047411040985</v>
@@ -5484,34 +5609,34 @@
         <v>123172.65806338149</v>
       </c>
       <c r="M19" s="16">
-        <v>5.096464270286817</v>
+        <v>5.9261344867245338</v>
       </c>
       <c r="N19" s="16">
-        <v>3.1982574572705684</v>
+        <v>3.9496447193692417</v>
       </c>
       <c r="O19" s="16">
-        <v>8065.4790637428705</v>
+        <v>5415.833424784003</v>
       </c>
       <c r="P19" s="16">
-        <v>3044.0567601831735</v>
+        <v>2678.666539682963</v>
       </c>
       <c r="Q19" s="16">
-        <v>3.1295180860384573</v>
+        <v>63.606264568035435</v>
       </c>
       <c r="R19" s="16">
-        <v>657.15647747574963</v>
+        <v>584.7046159803092</v>
       </c>
       <c r="S19" s="16">
-        <v>7607.0502213785421</v>
+        <v>8827.6715982668629</v>
       </c>
       <c r="T19" s="16">
         <v>708641.31735875877</v>
       </c>
       <c r="U19" s="16">
-        <v>7144.4132278211982</v>
+        <v>8589.9733514149102</v>
       </c>
       <c r="V19" s="16">
-        <v>739.74586195580275</v>
+        <v>570.52947461212136</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
@@ -5531,7 +5656,7 @@
         <v>2807.373846715212</v>
       </c>
       <c r="G20" s="16">
-        <v>1178.0770331275444</v>
+        <v>1507.3930697774049</v>
       </c>
       <c r="H20" s="16">
         <v>3573.3140356715885</v>
@@ -5549,34 +5674,34 @@
         <v>123941.42024869514</v>
       </c>
       <c r="M20" s="16">
-        <v>5.0174435715414933</v>
+        <v>5.8594225452478934</v>
       </c>
       <c r="N20" s="16">
-        <v>3.1286281242784804</v>
+        <v>3.8879295495433666</v>
       </c>
       <c r="O20" s="16">
-        <v>7818.055233211242</v>
+        <v>5251.1924673540425</v>
       </c>
       <c r="P20" s="16">
-        <v>2987.1979399961638</v>
+        <v>2621.486912539684</v>
       </c>
       <c r="Q20" s="16">
-        <v>3.0770782045324996</v>
+        <v>62.405700879869343</v>
       </c>
       <c r="R20" s="16">
-        <v>644.5429633076667</v>
+        <v>571.63339543794234</v>
       </c>
       <c r="S20" s="16">
-        <v>7462.5927103847625</v>
+        <v>8699.3668967628055</v>
       </c>
       <c r="T20" s="16">
         <v>712856.518264496</v>
       </c>
       <c r="U20" s="16">
-        <v>6978.0111597711339</v>
+        <v>8343.5305619193114</v>
       </c>
       <c r="V20" s="16">
-        <v>684.87812040966435</v>
+        <v>517.62545631113949</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
@@ -5596,7 +5721,7 @@
         <v>2807.373846715212</v>
       </c>
       <c r="G21" s="16">
-        <v>1160.2238689842616</v>
+        <v>1478.5496147774384</v>
       </c>
       <c r="H21" s="16">
         <v>4082.8254225992714</v>
@@ -5614,34 +5739,34 @@
         <v>124633.73733801451</v>
       </c>
       <c r="M21" s="16">
-        <v>4.9508860722283314</v>
+        <v>5.8051653963669905</v>
       </c>
       <c r="N21" s="16">
-        <v>3.0702561566529161</v>
+        <v>3.8378987309076815</v>
       </c>
       <c r="O21" s="16">
-        <v>7601.3579951351512</v>
+        <v>5107.548709889993</v>
       </c>
       <c r="P21" s="16">
-        <v>2937.0284324878266</v>
+        <v>2570.736673048893</v>
       </c>
       <c r="Q21" s="16">
-        <v>3.0304971860907428</v>
+        <v>61.331088748034034</v>
       </c>
       <c r="R21" s="16">
-        <v>633.41219883005499</v>
+        <v>560.04131441443894</v>
       </c>
       <c r="S21" s="16">
-        <v>7340.2510260677755</v>
+        <v>8593.2487974830983</v>
       </c>
       <c r="T21" s="16">
         <v>716649.91370765201</v>
       </c>
       <c r="U21" s="16">
-        <v>6831.7671188620152</v>
+        <v>8126.2741391992404</v>
       </c>
       <c r="V21" s="16">
-        <v>639.99376475609347</v>
+        <v>473.55751635338527</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -5661,7 +5786,7 @@
         <v>2807.373846715212</v>
       </c>
       <c r="G22" s="16">
-        <v>1144.2692953722533</v>
+        <v>1452.6568297515009</v>
       </c>
       <c r="H22" s="16">
         <v>4555.56180201401</v>
@@ -5679,34 +5804,34 @@
         <v>125260.63692308396</v>
       </c>
       <c r="M22" s="16">
-        <v>4.894172640608538</v>
+        <v>5.760565671615657</v>
       </c>
       <c r="N22" s="16">
-        <v>3.020718766159987</v>
+        <v>3.7968831806835492</v>
       </c>
       <c r="O22" s="16">
-        <v>7410.8411867897976</v>
+        <v>4981.1698983017413</v>
       </c>
       <c r="P22" s="16">
-        <v>2892.4513865002973</v>
+        <v>2525.3956451508438</v>
       </c>
       <c r="Q22" s="16">
-        <v>2.9888726843513251</v>
+        <v>60.364063604110385</v>
       </c>
       <c r="R22" s="16">
-        <v>623.52189457161796</v>
+        <v>549.69302590922791</v>
       </c>
       <c r="S22" s="16">
-        <v>7235.5211540738865</v>
+        <v>8504.5558296246054</v>
       </c>
       <c r="T22" s="16">
         <v>720082.70193706418</v>
       </c>
       <c r="U22" s="16">
-        <v>6702.294145079939</v>
+        <v>7933.375711818293</v>
       </c>
       <c r="V22" s="16">
-        <v>602.06487777685288</v>
+        <v>436.39717314265835</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -5737,34 +5862,34 @@
         <v>0.6</v>
       </c>
       <c r="C29" s="16">
-        <v>0.82013995810863238</v>
+        <v>0.82010837737991815</v>
       </c>
       <c r="D29" s="16">
-        <v>4.5972636053374432</v>
+        <v>4.5892138958838418</v>
       </c>
       <c r="E29" s="16">
-        <v>0.21752070053998984</v>
+        <v>0.21790224266881963</v>
       </c>
       <c r="F29" s="16">
-        <v>1.2820307346803273E-2</v>
+        <v>1.2816957885473839E-2</v>
       </c>
       <c r="G29" s="16">
-        <v>0.74847303567828738</v>
+        <v>0.74828945170282113</v>
       </c>
       <c r="H29" s="16">
-        <v>17.986004189136761</v>
+        <v>17.989162262008172</v>
       </c>
       <c r="I29" s="16">
-        <v>0.39256551077722535</v>
+        <v>0.39277195256478425</v>
       </c>
       <c r="J29" s="16">
-        <v>2.0829472070598287</v>
+        <v>2.1795612919769543</v>
       </c>
       <c r="K29" s="16">
-        <v>0.28180602931711179</v>
+        <v>0.27694286363008547</v>
       </c>
       <c r="L29" s="16">
-        <v>568021.03824784374</v>
+        <v>567999.16573921219</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
@@ -5772,34 +5897,34 @@
         <v>0.65</v>
       </c>
       <c r="C30" s="16">
-        <v>0.81270445170592143</v>
+        <v>0.8126710200654208</v>
       </c>
       <c r="D30" s="16">
-        <v>4.3692443410980131</v>
+        <v>4.3622780437796251</v>
       </c>
       <c r="E30" s="16">
-        <v>0.22887252850425274</v>
+        <v>0.22923802425339357</v>
       </c>
       <c r="F30" s="16">
-        <v>1.2732527471849048E-2</v>
+        <v>1.2728149016334204E-2</v>
       </c>
       <c r="G30" s="16">
-        <v>0.74366182073204634</v>
+        <v>0.7434218375852778</v>
       </c>
       <c r="H30" s="16">
-        <v>18.729554829407846</v>
+        <v>18.732897993457918</v>
       </c>
       <c r="I30" s="16">
-        <v>0.37412604036228386</v>
+        <v>0.37430369381755624</v>
       </c>
       <c r="J30" s="16">
-        <v>1.9926727538831934</v>
+        <v>2.0816745948771174</v>
       </c>
       <c r="K30" s="16">
-        <v>0.27029641704932589</v>
+        <v>0.26610389176083016</v>
       </c>
       <c r="L30" s="16">
-        <v>567771.04515252833</v>
+        <v>567747.68916200998</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
@@ -5807,34 +5932,34 @@
         <v>0.7</v>
       </c>
       <c r="C31" s="16">
-        <v>0.80643863864712118</v>
+        <v>0.8064081272589364</v>
       </c>
       <c r="D31" s="16">
-        <v>4.191378205075269</v>
+        <v>4.1852366057759864</v>
       </c>
       <c r="E31" s="16">
-        <v>0.23858500738232519</v>
+        <v>0.23893511746024443</v>
       </c>
       <c r="F31" s="16">
-        <v>1.2670697653095902E-2</v>
+        <v>1.2659564072005773E-2</v>
       </c>
       <c r="G31" s="16">
-        <v>0.74027292836618641</v>
+        <v>0.73966269678663643</v>
       </c>
       <c r="H31" s="16">
-        <v>19.356136135287894</v>
+        <v>19.359187274106372</v>
       </c>
       <c r="I31" s="16">
-        <v>0.35971940225036453</v>
+        <v>0.35986734789658548</v>
       </c>
       <c r="J31" s="16">
-        <v>1.9200491681929024</v>
+        <v>2.0022469880054845</v>
       </c>
       <c r="K31" s="16">
-        <v>0.26115196917136718</v>
+        <v>0.25746458694793295</v>
       </c>
       <c r="L31" s="16">
-        <v>567674.65643476509</v>
+        <v>567653.17861738987</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
@@ -5842,34 +5967,34 @@
         <v>0.75</v>
       </c>
       <c r="C32" s="16">
-        <v>0.80109149445693062</v>
+        <v>0.80106649171732347</v>
       </c>
       <c r="D32" s="16">
-        <v>4.0488728358535688</v>
+        <v>4.0433802535180154</v>
       </c>
       <c r="E32" s="16">
-        <v>0.24698231842324175</v>
+        <v>0.24731782253967632</v>
       </c>
       <c r="F32" s="16">
-        <v>1.262745197607002E-2</v>
+        <v>1.2605124026752883E-2</v>
       </c>
       <c r="G32" s="16">
-        <v>0.73790263280839785</v>
+        <v>0.7366788379063256</v>
       </c>
       <c r="H32" s="16">
-        <v>19.890850554306937</v>
+        <v>19.893350828267664</v>
       </c>
       <c r="I32" s="16">
-        <v>0.34818280949217234</v>
+        <v>0.34830159757646667</v>
       </c>
       <c r="J32" s="16">
-        <v>1.8604600227922072</v>
+        <v>1.9365725544212677</v>
       </c>
       <c r="K32" s="16">
-        <v>0.25373656750511175</v>
+        <v>0.2504416957185735</v>
       </c>
       <c r="L32" s="16">
-        <v>567686.53195685614</v>
+        <v>567668.81398252328</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
@@ -5877,34 +6002,34 @@
         <v>0.8</v>
       </c>
       <c r="C33" s="16">
-        <v>0.79647837219656359</v>
+        <v>0.79646021449918547</v>
       </c>
       <c r="D33" s="16">
-        <v>3.9322189089487511</v>
+        <v>3.9272505519213565</v>
       </c>
       <c r="E33" s="16">
-        <v>0.25430934115195086</v>
+        <v>0.25463106740433533</v>
       </c>
       <c r="F33" s="16">
-        <v>1.259800766538546E-2</v>
+        <v>1.256092085749282E-2</v>
       </c>
       <c r="G33" s="16">
-        <v>0.73628879013977711</v>
+        <v>0.73425606219918149</v>
       </c>
       <c r="H33" s="16">
-        <v>20.35216278034363</v>
+        <v>20.353978550081454</v>
       </c>
       <c r="I33" s="16">
-        <v>0.33879918838150858</v>
+        <v>0.33888996356461915</v>
       </c>
       <c r="J33" s="16">
-        <v>1.8109826194536935</v>
+        <v>1.8816431996129253</v>
       </c>
       <c r="K33" s="16">
-        <v>0.24765770129014694</v>
+        <v>0.24467505864683292</v>
       </c>
       <c r="L33" s="16">
-        <v>567774.79927701573</v>
+        <v>567761.85544408299</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.3">
@@ -5912,34 +6037,34 @@
         <v>0.85</v>
       </c>
       <c r="C34" s="16">
-        <v>0.79246058728103996</v>
+        <v>0.79244981650168778</v>
       </c>
       <c r="D34" s="16">
-        <v>3.8350268507481067</v>
+        <v>3.8304905468390742</v>
       </c>
       <c r="E34" s="16">
-        <v>0.26075436728817891</v>
+        <v>0.26106316874354418</v>
       </c>
       <c r="F34" s="16">
-        <v>1.257912344780103E-2</v>
+        <v>1.2524338436629916E-2</v>
       </c>
       <c r="G34" s="16">
-        <v>0.73525374617397443</v>
+        <v>0.73225097971168573</v>
       </c>
       <c r="H34" s="16">
-        <v>20.753941271896004</v>
+        <v>20.755018349831232</v>
       </c>
       <c r="I34" s="16">
-        <v>0.33121770977860687</v>
+        <v>0.33128127708956262</v>
       </c>
       <c r="J34" s="16">
-        <v>1.7702954044804526</v>
+        <v>1.8360763962093123</v>
       </c>
       <c r="K34" s="16">
-        <v>0.24276579170183107</v>
+        <v>0.24003385181240608</v>
       </c>
       <c r="L34" s="16">
-        <v>567916.81149167253</v>
+        <v>567909.09261357912</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
@@ -5947,34 +6072,34 @@
         <v>0.9</v>
       </c>
       <c r="C35" s="16">
-        <v>0.78893287821783398</v>
+        <v>0.78892866429426911</v>
       </c>
       <c r="D35" s="16">
-        <v>3.752849741614892</v>
+        <v>3.7486711152031096</v>
       </c>
       <c r="E35" s="16">
-        <v>0.26646417225585195</v>
+        <v>0.26676119864033959</v>
       </c>
       <c r="F35" s="16">
-        <v>1.2568539303476595E-2</v>
+        <v>1.2493575624894261E-2</v>
       </c>
       <c r="G35" s="16">
-        <v>0.73467362922355217</v>
+        <v>0.73056487000045445</v>
       </c>
       <c r="H35" s="16">
-        <v>21.106712178216604</v>
+        <v>21.107133570573101</v>
       </c>
       <c r="I35" s="16">
-        <v>0.32683276216154017</v>
+        <v>0.3268682465053947</v>
       </c>
       <c r="J35" s="16">
-        <v>1.7463699853830885</v>
+        <v>1.8080333560987463</v>
       </c>
       <c r="K35" s="16">
-        <v>0.24046161927493348</v>
+        <v>0.23790846143761119</v>
       </c>
       <c r="L35" s="16">
-        <v>568096.9185940827</v>
+        <v>568093.88422061631</v>
       </c>
     </row>
   </sheetData>
@@ -5985,7 +6110,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E91C93-8228-4E85-B9E3-FB80BE715EB6}">
   <dimension ref="B2:Y44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.5546875" style="32"/>
     <col min="4" max="4" width="11.5546875" style="2"/>
@@ -6054,7 +6179,7 @@
         <v>3.0305681085599816</v>
       </c>
       <c r="G3" s="3">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3">
         <v>756.61237274082237</v>
@@ -6099,7 +6224,7 @@
         <v>3.0357375517463359</v>
       </c>
       <c r="G4" s="3">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3">
         <v>686.34112082706883</v>
@@ -6112,19 +6237,19 @@
         <v>42</v>
       </c>
       <c r="L4" s="6">
-        <v>179.67369630276852</v>
+        <v>0.1796736963027683</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>66</v>
       </c>
       <c r="O4" s="9">
-        <v>68729.982427742099</v>
+        <v>68.729982427742101</v>
       </c>
       <c r="Q4" s="12" t="s">
         <v>98</v>
       </c>
       <c r="R4" s="5">
-        <v>3564.7236360481061</v>
+        <v>85.041008555659317</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
@@ -6144,7 +6269,7 @@
         <v>3.1028601038812176</v>
       </c>
       <c r="G5" s="3">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3">
         <v>736.50270198870771</v>
@@ -6157,19 +6282,19 @@
         <v>43</v>
       </c>
       <c r="L5" s="6">
-        <v>70.174170080653866</v>
+        <v>7.0174170080653853E-2</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>67</v>
       </c>
       <c r="O5" s="9">
-        <v>119784.56764170597</v>
+        <v>119.78456764170598</v>
       </c>
       <c r="Q5" s="12" t="s">
         <v>99</v>
       </c>
       <c r="R5" s="5">
-        <v>4238.0484080694978</v>
+        <v>107.41263143484889</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
@@ -6189,7 +6314,7 @@
         <v>3.112273260172465</v>
       </c>
       <c r="G6" s="3">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3">
         <v>613.91160179876624</v>
@@ -6202,19 +6327,19 @@
         <v>47</v>
       </c>
       <c r="L6" s="6">
-        <v>249.84786638342237</v>
+        <v>0.24984786638342216</v>
       </c>
       <c r="N6" s="8" t="s">
         <v>68</v>
       </c>
       <c r="O6" s="9">
-        <v>7577.9874552343463</v>
+        <v>9.1301926814182846</v>
       </c>
       <c r="Q6" s="12" t="s">
         <v>100</v>
       </c>
       <c r="R6" s="5">
-        <v>176030.92341356995</v>
+        <v>1263.8433507778232</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -6234,7 +6359,7 @@
         <v>2.493493145865219</v>
       </c>
       <c r="G7" s="3">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3">
         <v>325.47630713613137</v>
@@ -6247,19 +6372,19 @@
         <v>44</v>
       </c>
       <c r="L7" s="6">
-        <v>485.05085709943228</v>
+        <v>0.4850508570994323</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>69</v>
       </c>
       <c r="O7" s="9">
-        <v>-38640.801901504477</v>
+        <v>-38.640801901504481</v>
       </c>
       <c r="Q7" s="12" t="s">
         <v>105</v>
       </c>
       <c r="R7" s="5">
-        <v>46008.906930956873</v>
+        <v>552.14183910822305</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
@@ -6279,7 +6404,7 @@
         <v>2.1610567826542426</v>
       </c>
       <c r="G8" s="3">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3">
         <v>257.02142230175508</v>
@@ -6292,19 +6417,19 @@
         <v>45</v>
       </c>
       <c r="L8" s="6">
-        <v>167.57078652572901</v>
+        <v>0.16757078652572899</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>70</v>
       </c>
       <c r="O8" s="9">
-        <v>-18872.729900081154</v>
+        <v>-18.872729900081151</v>
       </c>
       <c r="Q8" s="12" t="s">
         <v>104</v>
       </c>
       <c r="R8" s="5">
-        <v>345.24330338852025</v>
+        <v>220.10427797124143</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
@@ -6324,7 +6449,7 @@
         <v>2.1610567826542426</v>
       </c>
       <c r="G9" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H9" s="3">
         <v>257.02142230175508</v>
@@ -6337,19 +6462,19 @@
         <v>48</v>
       </c>
       <c r="L9" s="6">
-        <v>1.6390047735298752</v>
+        <v>2.6986863112883855E-2</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>71</v>
       </c>
       <c r="O9" s="9">
-        <v>-19.869341720783179</v>
+        <v>-0.39899328053984756</v>
       </c>
       <c r="Q9" s="12" t="s">
         <v>101</v>
       </c>
       <c r="R9" s="5">
-        <v>26395940.226689368</v>
+        <v>231.8240623558037</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
@@ -6357,44 +6482,44 @@
         <v>30</v>
       </c>
       <c r="C10" s="3">
-        <v>423.08708102866973</v>
+        <v>425.599195454219</v>
       </c>
       <c r="D10" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E10" s="3">
-        <v>576.26858667218778</v>
+        <v>579.32870756571242</v>
       </c>
       <c r="F10" s="6">
-        <v>2.1262634543808296</v>
+        <v>2.1334749202803449</v>
       </c>
       <c r="G10" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H10" s="3">
-        <v>252.47508976842693</v>
+        <v>253.38511210401094</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="0"/>
-        <v>149.93708102866975</v>
+        <v>152.44919545421902</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="6">
-        <v>61.926848784763543</v>
+        <v>4.2999332517137619E-2</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>72</v>
       </c>
       <c r="O10" s="9">
-        <v>131001.01826786241</v>
+        <v>131.00101826786243</v>
       </c>
       <c r="Q10" s="12" t="s">
         <v>102</v>
       </c>
       <c r="R10" s="5">
-        <v>7331176.3611313887</v>
+        <v>5561.582067065191</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
@@ -6402,44 +6527,44 @@
         <v>31</v>
       </c>
       <c r="C11" s="3">
-        <v>362.94904708723425</v>
+        <v>382.74751534537711</v>
       </c>
       <c r="D11" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E11" s="3">
-        <v>496.03640269284398</v>
+        <v>524.59629845796826</v>
       </c>
       <c r="F11" s="6">
-        <v>1.9211337971705802</v>
+        <v>1.9977907986920829</v>
       </c>
       <c r="G11" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H11" s="3">
-        <v>233.40231308631894</v>
+        <v>239.1069238478072</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="0"/>
-        <v>89.799047087234271</v>
+        <v>109.59751534537713</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>50</v>
       </c>
       <c r="L11" s="6">
-        <v>12.71856373471684</v>
+        <v>9.8729638030424609E-3</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>73</v>
       </c>
       <c r="O11" s="9">
-        <v>7558.118113513563</v>
+        <v>8.7311994008784364</v>
       </c>
       <c r="Q11" s="12" t="s">
         <v>103</v>
       </c>
       <c r="R11" s="5">
-        <v>12776982.616668882</v>
+        <v>9692.8833643694998</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
@@ -6447,44 +6572,44 @@
         <v>32</v>
       </c>
       <c r="C12" s="3">
-        <v>361.35738649679638</v>
+        <v>355.85332053913208</v>
       </c>
       <c r="D12" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E12" s="3">
-        <v>493.57294248449631</v>
+        <v>484.78478220557434</v>
       </c>
       <c r="F12" s="6">
-        <v>1.9143314943410128</v>
+        <v>1.8898229319183995</v>
       </c>
       <c r="G12" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H12" s="3">
-        <v>232.96695946660682</v>
+        <v>231.48602707398695</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="0"/>
-        <v>88.207386496796403</v>
+        <v>82.703320539132108</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>51</v>
       </c>
       <c r="L12" s="6">
-        <v>76.284417293010264</v>
+        <v>7.9859159433063931E-2</v>
       </c>
       <c r="N12" s="10" t="s">
         <v>74</v>
       </c>
       <c r="O12" s="11">
-        <v>138559.13638137598</v>
+        <v>139.73221766874087</v>
       </c>
       <c r="Q12" s="12" t="s">
         <v>106</v>
       </c>
       <c r="R12" s="5">
-        <v>808316.26219563605</v>
+        <v>738.80880064549069</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
@@ -6492,38 +6617,38 @@
         <v>33</v>
       </c>
       <c r="C13" s="3">
-        <v>357.9147949404603</v>
+        <v>335.73040041117201</v>
       </c>
       <c r="D13" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E13" s="3">
-        <v>488.12887620074639</v>
+        <v>446.78618016032357</v>
       </c>
       <c r="F13" s="6">
-        <v>1.8991933019420426</v>
+        <v>1.7797317171225744</v>
       </c>
       <c r="G13" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H13" s="3">
-        <v>232.03634524660981</v>
+        <v>226.31112072011146</v>
       </c>
       <c r="I13" s="3">
         <f t="shared" si="0"/>
-        <v>84.76479494046032</v>
+        <v>62.580400411172036</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>52</v>
       </c>
       <c r="L13" s="6">
-        <v>66.529786632388294</v>
+        <v>5.7340899988327594E-2</v>
       </c>
       <c r="Q13" s="12" t="s">
         <v>107</v>
       </c>
       <c r="R13" s="5">
-        <v>1848458.1085221746</v>
+        <v>1402.2785650857879</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
@@ -6543,7 +6668,7 @@
         <v>2.1610567826542426</v>
       </c>
       <c r="G14" s="3">
-        <v>200.53649165005706</v>
+        <v>0.20053649165005705</v>
       </c>
       <c r="H14" s="3">
         <v>257.02142230175508</v>
@@ -6556,7 +6681,7 @@
         <v>54</v>
       </c>
       <c r="L14" s="6">
-        <v>2.1965125471084219</v>
+        <v>1.3787060043857914E-2</v>
       </c>
       <c r="N14" s="37" t="s">
         <v>75</v>
@@ -6566,7 +6691,7 @@
         <v>108</v>
       </c>
       <c r="R14" s="5">
-        <v>902813.83659368719</v>
+        <v>684.89325534693512</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
@@ -6586,7 +6711,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G15" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H15" s="3">
         <v>224.33075530171814</v>
@@ -6599,19 +6724,19 @@
         <v>53</v>
       </c>
       <c r="L15" s="6">
-        <v>68.726299179496721</v>
+        <v>7.1127960032185508E-2</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>80</v>
       </c>
       <c r="O15" s="9">
-        <v>9.9078139175955826</v>
+        <v>10.933247310468779</v>
       </c>
       <c r="Q15" s="12" t="s">
         <v>109</v>
       </c>
       <c r="R15" s="5">
-        <v>950.48870643001896</v>
+        <v>14.479506050119126</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
@@ -6631,7 +6756,7 @@
         <v>1.7343043486568708</v>
       </c>
       <c r="G16" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H16" s="3">
         <v>268.76481394998945</v>
@@ -6644,19 +6769,19 @@
         <v>46</v>
       </c>
       <c r="L16" s="6">
-        <v>4.3523323308963686</v>
+        <v>3.0378495703489477E-2</v>
       </c>
       <c r="N16" s="8" t="s">
         <v>81</v>
       </c>
       <c r="O16" s="9">
-        <v>52.432314177470374</v>
+        <v>52.432314177470431</v>
       </c>
       <c r="Q16" s="12" t="s">
         <v>110</v>
       </c>
       <c r="R16" s="5">
-        <v>1536510.4402931174</v>
+        <v>1851.2351016359887</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.3">
@@ -6676,7 +6801,7 @@
         <v>2.180095650521598</v>
       </c>
       <c r="G17" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H17" s="3">
         <v>345.4561839822619</v>
@@ -6689,19 +6814,19 @@
         <v>55</v>
       </c>
       <c r="L17" s="6">
-        <v>-48.569613693804691</v>
+        <v>-1.5517636879531452E-2</v>
       </c>
       <c r="N17" s="8" t="s">
         <v>82</v>
       </c>
       <c r="O17" s="9">
-        <v>17.366718295380426</v>
+        <v>59.710107512679613</v>
       </c>
       <c r="Q17" s="12" t="s">
         <v>111</v>
       </c>
       <c r="R17" s="5">
-        <v>1183381.5514604528</v>
+        <v>1185.5793514604527</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.3">
@@ -6721,7 +6846,7 @@
         <v>2.180095650521598</v>
       </c>
       <c r="G18" s="3">
-        <v>200.53649165005706</v>
+        <v>0.20053649165005705</v>
       </c>
       <c r="H18" s="3">
         <v>345.4561839822619</v>
@@ -6734,23 +6859,23 @@
         <v>248</v>
       </c>
       <c r="L18" s="15">
-        <v>7.1463166549765617E-2</v>
+        <v>0</v>
       </c>
       <c r="N18" s="8" t="s">
         <v>83</v>
       </c>
       <c r="O18" s="9">
-        <v>52.95934806076604</v>
+        <v>54.533240924600179</v>
       </c>
       <c r="Q18" s="12" t="s">
         <v>112</v>
       </c>
       <c r="R18" s="5">
-        <v>204873108.96594325</v>
+        <v>206607.62331619667</v>
       </c>
       <c r="V18" s="5">
         <f>R23-R9-R6</f>
-        <v>218858501.26033798</v>
+        <v>217544.61505479633</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.3">
@@ -6770,7 +6895,7 @@
         <v>2.180095650521598</v>
       </c>
       <c r="G19" s="3">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H19" s="3">
         <v>345.4561839822619</v>
@@ -6787,13 +6912,13 @@
         <v>84</v>
       </c>
       <c r="O19" s="9">
-        <v>55.457402293257886</v>
+        <v>55.926920526231214</v>
       </c>
       <c r="Q19" s="12" t="s">
         <v>122</v>
       </c>
       <c r="R19" s="5">
-        <v>275127059.32777882</v>
+        <v>15470.399698991729</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.3">
@@ -6801,44 +6926,44 @@
         <v>12</v>
       </c>
       <c r="C20" s="3">
-        <v>932.93660164805476</v>
+        <v>932.93660164805499</v>
       </c>
       <c r="D20" s="4">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>1170.364435360894</v>
+        <v>1170.3644353608943</v>
       </c>
       <c r="F20" s="6">
-        <v>2.8511829889834956</v>
+        <v>2.8511829889834948</v>
       </c>
       <c r="G20" s="3">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H20" s="3">
-        <v>630.42234983978312</v>
+        <v>630.42234983978369</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="0"/>
-        <v>659.78660164805478</v>
+        <v>659.78660164805501</v>
       </c>
       <c r="K20" s="12" t="s">
         <v>59</v>
       </c>
       <c r="L20" s="3">
-        <v>10711.871306183628</v>
+        <v>30.736985037643443</v>
       </c>
       <c r="N20" s="8" t="s">
         <v>85</v>
       </c>
       <c r="O20" s="9">
-        <v>39.302426699184615</v>
+        <v>42.769352704733009</v>
       </c>
       <c r="Q20" s="12" t="s">
         <v>250</v>
       </c>
       <c r="R20">
-        <v>0.77452830491154168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.3">
@@ -6849,19 +6974,19 @@
         <v>313.14999999999998</v>
       </c>
       <c r="D21" s="4">
-        <v>24.626111643110118</v>
+        <v>378.48516056463825</v>
       </c>
       <c r="E21" s="3">
-        <v>-83.029464432834615</v>
+        <v>296.81701942671828</v>
       </c>
       <c r="F21" s="6">
-        <v>-0.248662394286851</v>
+        <v>1.3288165220551185</v>
       </c>
       <c r="G21" s="3">
-        <v>173.63365867730425</v>
+        <v>0.16599534381649897</v>
       </c>
       <c r="H21" s="3">
-        <v>0.58853908566031532</v>
+        <v>36.677930334608249</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="0"/>
@@ -6871,13 +6996,13 @@
         <v>60</v>
       </c>
       <c r="L21" s="3">
-        <v>2799.7438201508498</v>
+        <v>13.428227032156792</v>
       </c>
       <c r="N21" s="8" t="s">
         <v>86</v>
       </c>
       <c r="O21" s="9">
-        <v>22.472364524327499</v>
+        <v>22.472364524327521</v>
       </c>
       <c r="Q21" s="36" t="s">
         <v>117</v>
@@ -6893,44 +7018,44 @@
         <v>18</v>
       </c>
       <c r="C22" s="3">
-        <v>313.1790338182704</v>
+        <v>313.85772974398833</v>
       </c>
       <c r="D22" s="4">
-        <v>98.504446572440472</v>
+        <v>1513.940642258553</v>
       </c>
       <c r="E22" s="3">
-        <v>-82.91503188633331</v>
+        <v>299.22066082632841</v>
       </c>
       <c r="F22" s="6">
-        <v>-0.24860758461092747</v>
+        <v>1.32996553469988</v>
       </c>
       <c r="G22" s="3">
-        <v>173.63365867730425</v>
+        <v>0.16599534381649897</v>
       </c>
       <c r="H22" s="3">
-        <v>0.68663012728502504</v>
+        <v>38.738993614182689</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="0"/>
-        <v>40.02903381827042</v>
+        <v>40.707729743988352</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>61</v>
       </c>
       <c r="L22" s="3">
-        <v>216.92132320266333</v>
+        <v>2.0682185066311423</v>
       </c>
       <c r="N22" s="8" t="s">
         <v>87</v>
       </c>
       <c r="O22" s="5">
-        <v>16.984373320199506</v>
+        <v>58.602202086203761</v>
       </c>
       <c r="Q22" s="21" t="s">
         <v>113</v>
       </c>
       <c r="R22" s="22">
-        <v>241339.13449454925</v>
+        <v>269.4648139393471</v>
       </c>
       <c r="S22" s="21" t="s">
         <v>127</v>
@@ -6940,7 +7065,7 @@
       </c>
       <c r="V22" s="26">
         <f>(R23-228195)/228195</f>
-        <v>1074.5295795720367</v>
+        <v>-4.0117958465654649E-2</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.3">
@@ -6948,44 +7073,44 @@
         <v>246</v>
       </c>
       <c r="C23" s="3">
-        <v>348.52161965954565</v>
+        <v>313.85772974398833</v>
       </c>
       <c r="D23" s="4">
-        <v>98.504446572440472</v>
+        <v>1513.940642258553</v>
       </c>
       <c r="E23" s="3">
-        <v>-11.451865336567687</v>
+        <v>299.22066082632841</v>
       </c>
       <c r="F23" s="6">
-        <v>-3.2596436848179706E-2</v>
+        <v>1.32996553469988</v>
       </c>
       <c r="G23" s="3">
-        <v>173.63365867730425</v>
+        <v>0.16599534381649897</v>
       </c>
       <c r="H23" s="3">
-        <v>7.7460729715874184</v>
+        <v>38.738993614182689</v>
       </c>
       <c r="I23" s="3">
         <f t="shared" si="0"/>
-        <v>75.371619659545672</v>
+        <v>40.707729743988352</v>
       </c>
       <c r="K23" s="12" t="s">
         <v>62</v>
       </c>
       <c r="L23" s="3">
-        <v>257.89462587751922</v>
+        <v>2.6123019464674564</v>
       </c>
       <c r="N23" s="8" t="s">
         <v>88</v>
       </c>
       <c r="O23" s="5">
-        <v>22.692635964018898</v>
+        <v>23.350437403404296</v>
       </c>
       <c r="Q23" s="21" t="s">
         <v>114</v>
       </c>
       <c r="R23" s="22">
-        <v>245430472.41044092</v>
+        <v>219040.28246792994</v>
       </c>
       <c r="S23" s="21" t="s">
         <v>128</v>
@@ -6995,7 +7120,7 @@
       </c>
       <c r="V23" s="26">
         <f>(R24-10815)/10815</f>
-        <v>1128.5437756346967</v>
+        <v>6.9332608590334634E-3</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.3">
@@ -7003,50 +7128,50 @@
         <v>35</v>
       </c>
       <c r="C24" s="3">
-        <v>352.94904708723425</v>
+        <v>372.74751534537711</v>
       </c>
       <c r="D24" s="4">
-        <v>98.504446572440472</v>
+        <v>1513.940642258553</v>
       </c>
       <c r="E24" s="3">
-        <v>-2.0124237788916908</v>
+        <v>461.79668550516948</v>
       </c>
       <c r="F24" s="6">
-        <v>-5.6830994971502902E-3</v>
+        <v>1.8033524508158914</v>
       </c>
       <c r="G24" s="3">
-        <v>173.63365867730425</v>
+        <v>0.16599534381649897</v>
       </c>
       <c r="H24" s="3">
-        <v>9.1613029980539871</v>
+        <v>60.174709253035019</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="0"/>
-        <v>79.799047087234271</v>
+        <v>99.597515345377133</v>
       </c>
       <c r="K24" s="12" t="s">
         <v>63</v>
       </c>
       <c r="L24" s="3">
-        <v>21.008819152365195</v>
+        <v>5.3529908548869454</v>
       </c>
       <c r="N24" s="10" t="s">
         <v>89</v>
       </c>
       <c r="O24" s="14">
-        <v>22.777686776908567</v>
+        <v>23.354472765920619</v>
       </c>
       <c r="Q24" s="21" t="s">
         <v>115</v>
       </c>
       <c r="R24" s="22">
-        <v>12216015.933489244</v>
+        <v>10889.983216190447</v>
       </c>
       <c r="S24" s="21" t="s">
         <v>126</v>
       </c>
       <c r="T24" s="23">
-        <v>275127059.32777882</v>
+        <v>15470.399698991729</v>
       </c>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
@@ -7058,32 +7183,32 @@
         <v>36</v>
       </c>
       <c r="C25" s="3">
-        <v>352.94904708723425</v>
+        <v>372.74751534537711</v>
       </c>
       <c r="D25" s="4">
-        <v>98.504446572440472</v>
+        <v>1513.940642258553</v>
       </c>
       <c r="E25" s="3">
-        <v>354.6399053634305</v>
+        <v>720.83607497546461</v>
       </c>
       <c r="F25" s="6">
-        <v>1.0048092990109321</v>
+        <v>2.4982984365195833</v>
       </c>
       <c r="G25" s="3">
-        <v>173.63365867730425</v>
+        <v>0.16599534381649897</v>
       </c>
       <c r="H25" s="3">
-        <v>64.535323525191458</v>
+        <v>112.01595308577436</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="0"/>
-        <v>79.799047087234271</v>
+        <v>99.597515345377133</v>
       </c>
       <c r="K25" s="12" t="s">
         <v>64</v>
       </c>
       <c r="L25" s="3">
-        <v>1606251.3860119609</v>
+        <v>5.6380189298069876</v>
       </c>
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
@@ -7091,7 +7216,7 @@
         <v>242</v>
       </c>
       <c r="T25" s="34">
-        <v>533014886.80620354</v>
+        <v>245670.13019705148</v>
       </c>
       <c r="U25" s="5"/>
       <c r="V25" s="8"/>
@@ -7107,19 +7232,19 @@
         <v>396.4382571755965</v>
       </c>
       <c r="D26" s="4">
-        <v>98.504446572440472</v>
+        <v>1513.940642258553</v>
       </c>
       <c r="E26" s="3">
-        <v>427.88931928238799</v>
+        <v>780.31342883399589</v>
       </c>
       <c r="F26" s="6">
-        <v>1.2002862817475588</v>
+        <v>2.6530353973219061</v>
       </c>
       <c r="G26" s="3">
-        <v>173.63365867730425</v>
+        <v>0.16599534381649897</v>
       </c>
       <c r="H26" s="3">
-        <v>79.503275041223674</v>
+        <v>125.35848208109306</v>
       </c>
       <c r="I26" s="3">
         <f t="shared" si="0"/>
@@ -7129,7 +7254,7 @@
         <v>249</v>
       </c>
       <c r="L26" s="24">
-        <v>0.49488349731612458</v>
+        <v>0</v>
       </c>
       <c r="N26" s="37" t="s">
         <v>76</v>
@@ -7149,26 +7274,26 @@
         <v>16</v>
       </c>
       <c r="C27" s="3">
-        <v>369.43022357479919</v>
+        <v>355.48092980123221</v>
       </c>
       <c r="D27" s="4">
-        <v>24.626111643110118</v>
+        <v>378.48516056463825</v>
       </c>
       <c r="E27" s="3">
-        <v>384.24577970048045</v>
+        <v>725.31072531532766</v>
       </c>
       <c r="F27" s="6">
-        <v>1.2212685266545973</v>
+        <v>2.6805262279794495</v>
       </c>
       <c r="G27" s="3">
-        <v>173.63365867730425</v>
+        <v>0.16599534381649897</v>
       </c>
       <c r="H27" s="3">
-        <v>29.603879140282633</v>
+        <v>62.159387401878277</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="0"/>
-        <v>96.280223574799209</v>
+        <v>82.33092980123223</v>
       </c>
       <c r="N27" s="12" t="s">
         <v>77</v>
@@ -7191,26 +7316,26 @@
         <v>247</v>
       </c>
       <c r="C28" s="3">
-        <v>322.36878194840472</v>
+        <v>355.48092980123221</v>
       </c>
       <c r="D28" s="4">
-        <v>24.626111643110118</v>
+        <v>378.48516056463825</v>
       </c>
       <c r="E28" s="3">
-        <v>312.78261315071484</v>
+        <v>725.31072531532766</v>
       </c>
       <c r="F28" s="6">
-        <v>1.0147205242393047</v>
+        <v>2.6805262279794495</v>
       </c>
       <c r="G28" s="3">
-        <v>173.63365867730425</v>
+        <v>0.16599534381649897</v>
       </c>
       <c r="H28" s="3">
-        <v>19.722999510636438</v>
+        <v>62.159387401878277</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="0"/>
-        <v>49.21878194840474</v>
+        <v>82.33092980123223</v>
       </c>
       <c r="N28" s="12" t="s">
         <v>78</v>
@@ -7236,19 +7361,19 @@
         <v>313.14999999999998</v>
       </c>
       <c r="D29" s="4">
-        <v>24.626111643110118</v>
+        <v>378.48516056463825</v>
       </c>
       <c r="E29" s="3">
-        <v>300.1323438202125</v>
+        <v>642.25381704988297</v>
       </c>
       <c r="F29" s="6">
-        <v>0.97491036079233406</v>
+        <v>2.4319198195904663</v>
       </c>
       <c r="G29" s="3">
-        <v>173.63365867730425</v>
+        <v>0.16599534381649897</v>
       </c>
       <c r="H29" s="3">
-        <v>18.942130411848485</v>
+        <v>53.224479797608936</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="0"/>
@@ -7287,7 +7412,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G30" s="3">
-        <v>3182.8791377078924</v>
+        <v>2.7432697976126201</v>
       </c>
       <c r="H30" s="3">
         <v>2.5073905791015251E-5</v>
@@ -7323,7 +7448,7 @@
         <v>0.43672528196163279</v>
       </c>
       <c r="G31" s="3">
-        <v>3182.8791377078924</v>
+        <v>2.7432697976126201</v>
       </c>
       <c r="H31" s="3">
         <v>0.17334706272843686</v>
@@ -7347,26 +7472,26 @@
         <v>39</v>
       </c>
       <c r="C32" s="3">
-        <v>303.31510401884481</v>
+        <v>304.35242224144457</v>
       </c>
       <c r="D32" s="4">
         <v>101.325</v>
       </c>
       <c r="E32" s="3">
-        <v>126.51261372658171</v>
+        <v>130.84828751625821</v>
       </c>
       <c r="F32" s="6">
-        <v>0.43900110089670652</v>
+        <v>0.453271003020907</v>
       </c>
       <c r="G32" s="3">
-        <v>3182.8791377078924</v>
+        <v>2.7432697976126201</v>
       </c>
       <c r="H32" s="3">
-        <v>0.18491405203257455</v>
+        <v>0.26601652337869747</v>
       </c>
       <c r="I32" s="3">
         <f t="shared" si="0"/>
-        <v>30.165104018844829</v>
+        <v>31.202422241444594</v>
       </c>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
@@ -7395,7 +7520,7 @@
         <v>2.1610567826542426</v>
       </c>
       <c r="G33" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H33" s="3">
         <v>257.03525167707909</v>
@@ -7419,26 +7544,26 @@
         <v>30</v>
       </c>
       <c r="C34" s="3">
-        <v>423.08708102866973</v>
+        <v>425.599195454219</v>
       </c>
       <c r="D34" s="4">
         <v>9124.0875912408756</v>
       </c>
       <c r="E34" s="3">
-        <v>576.26858667218778</v>
+        <v>579.32870756571242</v>
       </c>
       <c r="F34" s="6">
-        <v>2.1262634543808296</v>
+        <v>2.1334749202803449</v>
       </c>
       <c r="G34" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H34" s="3">
-        <v>252.47508976842693</v>
+        <v>253.38511210401094</v>
       </c>
       <c r="I34" s="3">
         <f t="shared" si="0"/>
-        <v>149.93708102866975</v>
+        <v>152.44919545421902</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.3">
@@ -7446,26 +7571,26 @@
         <v>31</v>
       </c>
       <c r="C35" s="3">
-        <v>362.94904708723425</v>
+        <v>382.74751534537711</v>
       </c>
       <c r="D35" s="4">
         <v>9124.0875912408756</v>
       </c>
       <c r="E35" s="3">
-        <v>496.03640269284398</v>
+        <v>524.59629845796826</v>
       </c>
       <c r="F35" s="6">
-        <v>1.9211337971705802</v>
+        <v>1.9977907986920829</v>
       </c>
       <c r="G35" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H35" s="3">
-        <v>233.40231308631894</v>
+        <v>239.1069238478072</v>
       </c>
       <c r="I35" s="3">
         <f t="shared" si="0"/>
-        <v>89.799047087234271</v>
+        <v>109.59751534537713</v>
       </c>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.3">
@@ -7473,26 +7598,26 @@
         <v>32</v>
       </c>
       <c r="C36" s="3">
-        <v>361.35738649679638</v>
+        <v>355.85332053913208</v>
       </c>
       <c r="D36" s="4">
         <v>9124.0875912408756</v>
       </c>
       <c r="E36" s="3">
-        <v>493.57294248449631</v>
+        <v>484.78478220557434</v>
       </c>
       <c r="F36" s="6">
-        <v>1.9143314943410128</v>
+        <v>1.8898229319183995</v>
       </c>
       <c r="G36" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H36" s="3">
-        <v>232.96695946660682</v>
+        <v>231.48602707398695</v>
       </c>
       <c r="I36" s="3">
         <f t="shared" si="0"/>
-        <v>88.207386496796403</v>
+        <v>82.703320539132108</v>
       </c>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.3">
@@ -7512,7 +7637,7 @@
         <v>3.8804887263997387</v>
       </c>
       <c r="G37" s="3">
-        <v>100</v>
+        <v>0.8</v>
       </c>
       <c r="H37" s="3">
         <v>2.1111792130950945E-2</v>
@@ -7533,16 +7658,16 @@
         <v>0.101325</v>
       </c>
       <c r="E38" s="3">
-        <v>467.95937759062173</v>
+        <v>462.40917391101988</v>
       </c>
       <c r="F38" s="6">
-        <v>4.0168081231812165</v>
+        <v>4.000416406253489</v>
       </c>
       <c r="G38" s="3">
-        <v>100</v>
+        <v>0.8</v>
       </c>
       <c r="H38" s="3">
-        <v>2.9008069506970422</v>
+        <v>2.2377936730971415</v>
       </c>
       <c r="I38" s="3">
         <f t="shared" si="0"/>
@@ -7554,26 +7679,26 @@
         <v>32</v>
       </c>
       <c r="C39" s="3">
-        <v>361.35738649679638</v>
+        <v>355.85332053913208</v>
       </c>
       <c r="D39" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E39" s="3">
-        <v>493.57294248449631</v>
+        <v>484.78478220557434</v>
       </c>
       <c r="F39" s="6">
-        <v>1.9143314943410128</v>
+        <v>1.8898229319183995</v>
       </c>
       <c r="G39" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H39" s="3">
-        <v>232.96695946660682</v>
+        <v>231.48602707398695</v>
       </c>
       <c r="I39" s="3">
         <f t="shared" si="0"/>
-        <v>88.207386496796403</v>
+        <v>82.703320539132108</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.3">
@@ -7581,26 +7706,26 @@
         <v>33</v>
       </c>
       <c r="C40" s="3">
-        <v>357.9147949404603</v>
+        <v>335.73040041117201</v>
       </c>
       <c r="D40" s="4">
         <v>9.1240875912408761</v>
       </c>
       <c r="E40" s="3">
-        <v>488.12887620074639</v>
+        <v>446.78618016032357</v>
       </c>
       <c r="F40" s="6">
-        <v>1.8991933019420426</v>
+        <v>1.7797317171225744</v>
       </c>
       <c r="G40" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H40" s="3">
-        <v>232.03634524660981</v>
+        <v>226.31112072011146</v>
       </c>
       <c r="I40" s="3">
         <f t="shared" si="0"/>
-        <v>84.76479494046032</v>
+        <v>62.580400411172036</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.3">
@@ -7608,26 +7733,26 @@
         <v>33</v>
       </c>
       <c r="C41" s="3">
-        <v>357.9147949404603</v>
+        <v>335.73040041117201</v>
       </c>
       <c r="D41" s="4">
         <v>9124.0875912408756</v>
       </c>
       <c r="E41" s="3">
-        <v>488.12887619058898</v>
+        <v>446.78618015873252</v>
       </c>
       <c r="F41" s="6">
-        <v>1.8991933019420426</v>
+        <v>1.7797317171225744</v>
       </c>
       <c r="G41" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H41" s="3">
-        <v>232.03634523645241</v>
+        <v>226.31112071852041</v>
       </c>
       <c r="I41" s="3">
         <f t="shared" si="0"/>
-        <v>84.76479494046032</v>
+        <v>62.580400411172036</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.3">
@@ -7647,7 +7772,7 @@
         <v>1.72122584179495</v>
       </c>
       <c r="G42" s="3">
-        <v>799.46350834994291</v>
+        <v>0.79946350834994295</v>
       </c>
       <c r="H42" s="3">
         <v>224.34458467728319</v>
@@ -7674,7 +7799,7 @@
         <v>0.36719964130372146</v>
       </c>
       <c r="G43" s="3">
-        <v>9.7982274150728743E-2</v>
+        <v>3.9058889197145273E-4</v>
       </c>
       <c r="H43" s="3">
         <v>2.5073905791015251E-5</v>
@@ -7689,26 +7814,26 @@
         <v>20</v>
       </c>
       <c r="C44" s="3">
-        <v>356.9147949404603</v>
+        <v>334.73040041117201</v>
       </c>
       <c r="D44" s="4">
         <v>101.325</v>
       </c>
       <c r="E44" s="3">
-        <v>350.86067438903575</v>
+        <v>257.86315019881482</v>
       </c>
       <c r="F44" s="3">
-        <v>1.1200614625361844</v>
+        <v>0.8510571395108496</v>
       </c>
       <c r="G44" s="3">
-        <v>9.7982274150728743E-2</v>
+        <v>3.9058889197145273E-4</v>
       </c>
       <c r="H44" s="3">
-        <v>21.47482789167622</v>
+        <v>8.6809426114589439</v>
       </c>
       <c r="I44" s="3">
         <f t="shared" si="0"/>
-        <v>83.76479494046032</v>
+        <v>61.580400411172036</v>
       </c>
     </row>
   </sheetData>
@@ -7730,8 +7855,8 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BBA90F-813A-493D-869A-57A3178EDC43}">
-  <dimension ref="A1:M28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N28"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -7743,7 +7868,7 @@
     <col min="13" max="13" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>235</v>
       </c>
@@ -7778,388 +7903,541 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>202</v>
       </c>
       <c r="B2">
-        <v>9.2406574326365926E-2</v>
+        <v>0.16438224088424386</v>
       </c>
       <c r="C2">
-        <v>69915.957457922879</v>
+        <v>124.37363731188117</v>
       </c>
       <c r="E2" t="s">
         <v>66</v>
       </c>
       <c r="F2">
-        <v>25031.935161652607</v>
+        <v>25.031935161652605</v>
       </c>
       <c r="G2">
-        <v>1541.2694860114752</v>
+        <v>1.5412694860114715</v>
       </c>
       <c r="H2">
-        <v>142.42343331607918</v>
+        <v>0.25335733191707244</v>
       </c>
       <c r="I2">
-        <v>99.434251987875697</v>
+        <v>0.16438224088424386</v>
+      </c>
+      <c r="J2">
+        <v>0.35036473015281244</v>
       </c>
       <c r="K2" s="25">
-        <v>0.35198545686127924</v>
+        <v>0.36596110142425675</v>
       </c>
       <c r="L2" s="25">
-        <v>1.904205650074752</v>
+        <v>0.68927684304305448</v>
       </c>
       <c r="M2" s="25">
-        <v>0.26978389328349178</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.35036473015281244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>203</v>
       </c>
       <c r="B3">
-        <v>9.2406574326365953E-2</v>
+        <v>0.16438224088424386</v>
       </c>
       <c r="C3">
-        <v>63422.43179494785</v>
+        <v>112.82229145255715</v>
       </c>
       <c r="E3" t="s">
         <v>67</v>
       </c>
       <c r="F3">
-        <v>8882.596502083512</v>
+        <v>8.882596502083512</v>
       </c>
       <c r="G3">
-        <v>2806.532548235491</v>
+        <v>2.8065325482354964</v>
       </c>
       <c r="H3">
-        <v>245.50177594265065</v>
+        <v>0.44240121382791286</v>
       </c>
       <c r="I3">
-        <v>97.310482770177444</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.15763266814990487</v>
+      </c>
+      <c r="J3">
+        <v>0.35036473015281244</v>
+      </c>
+      <c r="K3">
+        <v>95.255749896077361</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>204</v>
       </c>
       <c r="B4">
-        <v>8.7475121604059528E-2</v>
+        <v>0.15763266814990487</v>
       </c>
       <c r="C4">
-        <v>64425.663418180629</v>
+        <v>116.09688601409424</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
       </c>
       <c r="F4">
-        <v>271.11169102991431</v>
+        <v>0.27111169102991423</v>
       </c>
       <c r="G4">
-        <v>3117.3934843303709</v>
+        <v>3.1173934843303797</v>
       </c>
       <c r="H4">
-        <v>841.02255109923738</v>
+        <v>1.0922247269175491</v>
       </c>
       <c r="I4">
-        <v>24.377604857384672</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.35036473015281244</v>
+      </c>
+      <c r="J4">
+        <v>0.19965470509438668</v>
+      </c>
+      <c r="K4">
+        <v>19.885898114427221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>205</v>
       </c>
       <c r="B5">
-        <v>8.7475121604059514E-2</v>
+        <v>0.15763266814990487</v>
       </c>
       <c r="C5">
-        <v>53701.992021490041</v>
+        <v>96.772523799721455</v>
       </c>
       <c r="E5" t="s">
         <v>70</v>
       </c>
       <c r="F5">
-        <v>68.005339576619249</v>
+        <v>6.8005339576619236E-2</v>
       </c>
       <c r="G5">
-        <v>1138.33305276341</v>
+        <v>1.1383330527634061</v>
       </c>
       <c r="H5">
-        <v>307.1039228277952</v>
+        <v>0.39883175285547801</v>
       </c>
       <c r="I5">
-        <v>18.129474900382768</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.35036473015281244</v>
+      </c>
+      <c r="J5">
+        <v>0.2137096924662919</v>
+      </c>
+      <c r="K5" t="s">
+        <v>261</v>
+      </c>
+      <c r="L5" t="s">
+        <v>259</v>
+      </c>
+      <c r="M5" t="s">
+        <v>238</v>
+      </c>
+      <c r="N5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>206</v>
       </c>
       <c r="B6">
-        <v>8.74751216040595E-2</v>
+        <v>0.1576326681499049</v>
       </c>
       <c r="C6">
-        <v>28471.079545973313</v>
+        <v>51.305698713446318</v>
       </c>
       <c r="E6" t="s">
         <v>59</v>
       </c>
       <c r="F6">
-        <v>39.725992780971197</v>
+        <v>1.2565343104128937</v>
       </c>
       <c r="G6">
-        <v>3469.1288051136653</v>
+        <v>3.4691288051130833</v>
       </c>
       <c r="H6">
-        <v>303.46246408746356</v>
+        <v>0.5468480297056667</v>
       </c>
       <c r="I6">
-        <v>11.575562052251838</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.15763266814990487</v>
+      </c>
+      <c r="J6">
+        <v>0.18398677812523287</v>
+      </c>
+      <c r="K6">
+        <v>0.01</v>
+      </c>
+      <c r="L6">
+        <v>0.32317635654000804</v>
+      </c>
+      <c r="M6">
+        <v>0.61886717126424606</v>
+      </c>
+      <c r="N6">
+        <v>0.30908708844465482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>207</v>
       </c>
       <c r="B7">
-        <v>8.7475121604059514E-2</v>
+        <v>0.15763266814990487</v>
       </c>
       <c r="C7">
-        <v>22482.980170694358</v>
+        <v>40.514972569109119</v>
       </c>
       <c r="E7" t="s">
         <v>60</v>
       </c>
       <c r="F7">
-        <v>17.999232996962466</v>
+        <v>0.77087724001891422</v>
       </c>
       <c r="G7">
-        <v>7142.9330882120803</v>
+        <v>7.1429330882120778</v>
       </c>
       <c r="H7">
-        <v>624.82894050101197</v>
+        <v>1.1259596011111099</v>
       </c>
       <c r="I7">
-        <v>2.8000068663790731</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.1576326681499049</v>
+      </c>
+      <c r="J7">
+        <v>0.19719392874189862</v>
+      </c>
+      <c r="K7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="L7">
+        <v>0.34456872898213237</v>
+      </c>
+      <c r="M7">
+        <v>0.65407200715365021</v>
+      </c>
+      <c r="N7">
+        <v>0.32972590929873358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>208</v>
       </c>
       <c r="B8">
-        <v>8.7827851562217951E-2</v>
+        <v>0.16220120384819151</v>
       </c>
       <c r="C8">
-        <v>15751.420401537414</v>
+        <v>29.089853685404357</v>
       </c>
       <c r="E8" t="s">
         <v>253</v>
       </c>
       <c r="F8">
-        <v>3.9799033859835076</v>
+        <v>0.2556560606844126</v>
       </c>
       <c r="G8">
-        <v>6782.2557987781765</v>
+        <v>6.0472409675346555</v>
       </c>
       <c r="H8">
-        <v>593.27865074795898</v>
+        <v>0.95324272865789994</v>
       </c>
       <c r="I8">
-        <v>0.66636188940894858</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.15763266814990487</v>
+      </c>
+      <c r="J8">
+        <v>0.35810316249745311</v>
+      </c>
+      <c r="K8">
+        <v>0.02</v>
+      </c>
+      <c r="L8">
+        <v>0.36596110142425675</v>
+      </c>
+      <c r="M8">
+        <v>0.68927684304305448</v>
+      </c>
+      <c r="N8">
+        <v>0.35036473015281244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>209</v>
       </c>
       <c r="B9">
-        <v>0.1230859866768063</v>
+        <v>0.19965470509438668</v>
       </c>
       <c r="C9">
-        <v>26447.19806915136</v>
+        <v>42.899339507543168</v>
       </c>
       <c r="E9" t="s">
         <v>254</v>
       </c>
       <c r="F9">
-        <v>0.10995398107179184</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>489.8963917659762</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>95.75191476595441</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.11470043564658007</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.35810316249745311</v>
+      </c>
+      <c r="J9">
+        <v>0.61862680329527819</v>
+      </c>
+      <c r="K9">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L9">
+        <v>0.38735347386638114</v>
+      </c>
+      <c r="M9">
+        <v>0.72448167893245874</v>
+      </c>
+      <c r="N9">
+        <v>0.37100355100689131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>210</v>
       </c>
       <c r="B10">
-        <v>0.11750793748009437</v>
+        <v>0.19719392874189862</v>
       </c>
       <c r="C10">
-        <v>32453.296677427275</v>
+        <v>54.460942891899279</v>
       </c>
       <c r="E10" t="s">
         <v>228</v>
       </c>
       <c r="F10">
-        <v>77.429288617854894</v>
+        <v>0.70073451890397209</v>
       </c>
       <c r="G10">
-        <v>1086.2272208333268</v>
+        <v>1.3605627687494435</v>
       </c>
       <c r="H10">
-        <v>212.30680203780128</v>
+        <v>0.48722183026546667</v>
       </c>
       <c r="I10">
-        <v>26.724074464674679</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.35810316249745311</v>
+      </c>
+      <c r="J10">
+        <v>0.35036473015281244</v>
+      </c>
+      <c r="K10">
+        <v>0.03</v>
+      </c>
+      <c r="L10">
+        <v>0.40874584630850552</v>
+      </c>
+      <c r="M10">
+        <v>0.75968651482186289</v>
+      </c>
+      <c r="N10">
+        <v>0.39164237186097006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>211</v>
       </c>
       <c r="B11">
-        <v>0.13955976303443879</v>
+        <v>0.2137096924662919</v>
       </c>
       <c r="C11">
-        <v>9668.2218541771254</v>
+        <v>14.805074716572907</v>
       </c>
       <c r="E11" t="s">
         <v>229</v>
       </c>
       <c r="F11">
-        <v>0.51696822047328139</v>
+        <v>2.2682427363801154E-2</v>
       </c>
       <c r="G11">
-        <v>2.8374352800170817</v>
+        <v>5.6866372819326445E-2</v>
       </c>
       <c r="H11">
-        <v>0.76549433678294299</v>
+        <v>1.992397136761254E-2</v>
       </c>
       <c r="I11">
-        <v>40.310589774980528</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.35036473015281244</v>
+      </c>
+      <c r="J11">
+        <v>0.61862680329527819</v>
+      </c>
+      <c r="K11">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="L11">
+        <v>0.43013821875062996</v>
+      </c>
+      <c r="M11">
+        <v>0.79489135071126726</v>
+      </c>
+      <c r="N11">
+        <v>0.41228119271504898</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>212</v>
       </c>
       <c r="B12">
-        <v>0.12193013321124166</v>
+        <v>0.20050594205610972</v>
       </c>
       <c r="C12">
-        <v>42121.518531604401</v>
+        <v>69.266017608472183</v>
       </c>
       <c r="E12" t="s">
         <v>255</v>
       </c>
       <c r="F12">
-        <v>1.2781700334423005</v>
+        <v>0.12063054984907384</v>
       </c>
       <c r="G12">
-        <v>2733.9070991328199</v>
+        <v>3.5001169170646191</v>
       </c>
       <c r="H12">
-        <v>534.3514341686647</v>
+        <v>1.2534029371116759</v>
       </c>
       <c r="I12">
-        <v>0.2386294602491788</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.35810316249745311</v>
+      </c>
+      <c r="J12">
+        <v>0.6267034001337185</v>
+      </c>
+      <c r="K12">
+        <v>0.04</v>
+      </c>
+      <c r="L12">
+        <v>0.45153059119275429</v>
+      </c>
+      <c r="M12">
+        <v>0.8300961866006713</v>
+      </c>
+      <c r="N12">
+        <v>0.43292001356912768</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>213</v>
       </c>
       <c r="B13">
-        <v>0.10690001237587672</v>
+        <v>0.18398677812523287</v>
       </c>
       <c r="C13">
-        <v>67392.156999902101</v>
+        <v>115.98937700516022</v>
       </c>
       <c r="E13" t="s">
         <v>63</v>
       </c>
       <c r="F13">
-        <v>0.35222626491756892</v>
+        <v>0.17442386067719509</v>
       </c>
       <c r="G13">
-        <v>456.02259338253077</v>
+        <v>2.3638032842787435</v>
       </c>
       <c r="H13">
-        <v>39.890631810335478</v>
+        <v>0.37261261868236645</v>
       </c>
       <c r="I13">
-        <v>0.87525161423404729</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.15763266814990487</v>
+      </c>
+      <c r="J13">
+        <v>0.16220120384819153</v>
+      </c>
+      <c r="K13">
+        <v>31.885233847914563</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>214</v>
       </c>
       <c r="B14">
-        <v>8.74751216040595E-2</v>
+        <v>0.15763266814990484</v>
       </c>
       <c r="C14">
-        <v>4508.657965268847</v>
+        <v>8.1247304583074396</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>230</v>
       </c>
       <c r="F14" s="24">
-        <v>113.9975296205717</v>
+        <v>0.17913742591867288</v>
       </c>
       <c r="G14" s="24">
-        <v>6147.1777320041247</v>
+        <v>1.5687831328618429</v>
       </c>
       <c r="H14" s="24">
-        <v>539.89341337302983</v>
+        <v>0.25445851272692832</v>
       </c>
       <c r="I14" s="24">
-        <v>17.433722066660767</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.16220120384819153</v>
+      </c>
+      <c r="J14">
+        <v>128.56985934193858</v>
+      </c>
+      <c r="K14">
+        <v>41.314368967161961</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>215</v>
       </c>
       <c r="B15">
-        <v>8.7475121604059541E-2</v>
+        <v>0.15763266814990487</v>
       </c>
       <c r="C15">
-        <v>17974.322205425517</v>
+        <v>32.390242110801672</v>
       </c>
       <c r="E15" t="s">
         <v>172</v>
       </c>
       <c r="F15">
-        <v>406.04887085806683</v>
+        <v>0.46907095188476866</v>
       </c>
       <c r="G15">
-        <v>6270.2647481636777</v>
+        <v>3.5924040888912341</v>
       </c>
       <c r="H15">
-        <v>1691.6164356778302</v>
+        <v>1.2586516892042372</v>
       </c>
       <c r="I15">
-        <v>19.357181033261188</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0.35036473015281244</v>
+      </c>
+      <c r="J15">
+        <v>0.68927684304305448</v>
+      </c>
+      <c r="K15">
+        <v>27.149667471458685</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>216</v>
       </c>
       <c r="B16">
-        <v>8.7475121604059541E-2</v>
+        <v>0.15763266814990487</v>
       </c>
       <c r="C16">
-        <v>16292.117424184464</v>
+        <v>29.172231618075632</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -8167,10 +8445,10 @@
         <v>217</v>
       </c>
       <c r="B17">
-        <v>8.7827851562217937E-2</v>
+        <v>0.16220120384819153</v>
       </c>
       <c r="C17">
-        <v>16292.469650449379</v>
+        <v>29.346655478752826</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -8181,7 +8459,7 @@
         <v>2E-3</v>
       </c>
       <c r="C18">
-        <v>4.9135966224896022E-9</v>
+        <v>1.958717816061848E-11</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -8189,10 +8467,10 @@
         <v>218</v>
       </c>
       <c r="B19">
-        <v>311.3114599283947</v>
+        <v>128.56985934193858</v>
       </c>
       <c r="C19">
-        <v>655.04677853745</v>
+        <v>0.43593921928673118</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -8200,10 +8478,10 @@
         <v>219</v>
       </c>
       <c r="B20">
-        <v>0.19545339866821301</v>
+        <v>0.35810316249745311</v>
       </c>
       <c r="C20">
-        <v>2698.1255985977582</v>
+        <v>7.4517416119483801</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -8211,10 +8489,10 @@
         <v>220</v>
       </c>
       <c r="B21">
-        <v>0.19545339866821301</v>
+        <v>0.35810316249745311</v>
       </c>
       <c r="C21">
-        <v>1004.6753933693218</v>
+        <v>3.6949689082559241</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -8222,10 +8500,10 @@
         <v>251</v>
       </c>
       <c r="B22">
-        <v>0.19545339866821299</v>
+        <v>0.35810316249745311</v>
       </c>
       <c r="C22">
-        <v>669.34512865270472</v>
+        <v>3.6949689082559241</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -8233,10 +8511,10 @@
         <v>221</v>
       </c>
       <c r="B23">
-        <v>6.5625014272466329</v>
+        <v>0.6267034001337185</v>
       </c>
       <c r="C23">
-        <v>670.623298686147</v>
+        <v>3.8155994581049977</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -8244,10 +8522,10 @@
         <v>222</v>
       </c>
       <c r="B24">
-        <v>5.6742893196732593</v>
+        <v>0.61862680329527819</v>
       </c>
       <c r="C24">
-        <v>676.50069527303333</v>
+        <v>3.9780750585379279</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -8255,10 +8533,10 @@
         <v>252</v>
       </c>
       <c r="B25">
-        <v>0.75238417935517443</v>
+        <v>0.61862680329527819</v>
       </c>
       <c r="C25">
-        <v>1011.9409139707221</v>
+        <v>3.9780750585379279</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -8266,10 +8544,10 @@
         <v>223</v>
       </c>
       <c r="B26">
-        <v>1.904205650074752</v>
+        <v>0.68927684304305448</v>
       </c>
       <c r="C26">
-        <v>2445.1074014182363</v>
+        <v>3.52817527388394</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -8288,10 +8566,10 @@
         <v>225</v>
       </c>
       <c r="B28" s="24">
-        <v>0.26978389328349178</v>
+        <v>0.35036473015281244</v>
       </c>
       <c r="C28" s="24">
-        <v>2039.0585305601694</v>
+        <v>3.0591043219991709</v>
       </c>
     </row>
   </sheetData>
@@ -8302,7 +8580,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E0693F-D387-4367-8A44-8725A6CA7BA7}">
   <dimension ref="A1:AF33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
